--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8FFAD0-BBCF-7C4A-9F46-9354CAB76C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75A060D-8C3C-5A4B-A9D3-F7AC49307262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="500" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="2520" yWindow="760" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1097,7 +1097,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1159,31 +1159,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1208,9 +1183,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1234,19 +1206,46 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1783,60 +1782,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="23" t="s">
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="41"/>
+      <c r="H1" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="23" t="s">
+      <c r="I1" s="42"/>
+      <c r="J1" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="25" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="25"/>
-      <c r="N1" s="27" t="s">
+      <c r="M1" s="44"/>
+      <c r="N1" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="25" t="s">
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="26" t="s">
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="26"/>
+      <c r="V1" s="45"/>
       <c r="W1" s="4" t="s">
         <v>46</v>
       </c>
       <c r="X1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AC1" s="23" t="s">
+      <c r="AC1" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
       <c r="AI1" s="7" t="s">
         <v>37</v>
       </c>
@@ -6373,16 +6372,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="R1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6393,9 +6392,9 @@
   <dimension ref="A1:AN159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="62.1640625" style="33" customWidth="1"/>
-    <col min="2" max="2" width="14" style="36" customWidth="1"/>
-    <col min="3" max="3" width="4.1640625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="62.1640625" style="24" customWidth="1"/>
+    <col min="2" max="2" width="14" style="27" customWidth="1"/>
+    <col min="3" max="3" width="4.1640625" style="23" customWidth="1"/>
     <col min="4" max="4" width="27" style="22" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="44" style="10" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="4" customWidth="1"/>
@@ -6414,7 +6413,7 @@
     <col min="22" max="22" width="12.5" style="4" customWidth="1"/>
     <col min="23" max="23" width="9.1640625" style="5" customWidth="1"/>
     <col min="24" max="25" width="13.33203125" style="4" customWidth="1"/>
-    <col min="26" max="26" width="62.1640625" style="33" customWidth="1"/>
+    <col min="26" max="26" width="62.1640625" style="24" customWidth="1"/>
     <col min="27" max="29" width="14.6640625" customWidth="1"/>
     <col min="30" max="32" width="14.1640625" customWidth="1"/>
     <col min="33" max="33" width="4.1640625" customWidth="1"/>
@@ -6422,9 +6421,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="32"/>
+      <c r="A1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="22"/>
       <c r="E1" s="10"/>
       <c r="F1" s="5" t="s">
@@ -6453,12 +6452,12 @@
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
       <c r="Y1" s="5"/>
-      <c r="Z1" s="33"/>
+      <c r="Z1" s="24"/>
     </row>
     <row r="2" spans="1:40" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="32"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="22"/>
       <c r="E2" s="10"/>
       <c r="F2" s="5" t="s">
@@ -6467,10 +6466,10 @@
       <c r="G2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="43">
         <v>150</v>
       </c>
-      <c r="I2" s="27"/>
+      <c r="I2" s="43"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -6489,22 +6488,22 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
-      <c r="Z2" s="33"/>
+      <c r="Z2" s="24"/>
     </row>
     <row r="3" spans="1:40" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="32"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="22"/>
       <c r="E3" s="10"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="43">
         <v>30</v>
       </c>
-      <c r="I3" s="27"/>
+      <c r="I3" s="43"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -6521,7 +6520,7 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
-      <c r="Z3" s="33"/>
+      <c r="Z3" s="24"/>
     </row>
     <row r="4" spans="1:40" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F4" s="8">
@@ -6558,11 +6557,11 @@
         <v>6</v>
       </c>
       <c r="Y4" s="20"/>
-      <c r="AD4" s="30" t="s">
+      <c r="AD4" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
+      <c r="AE4" s="51"/>
+      <c r="AF4" s="51"/>
       <c r="AK4" t="s">
         <v>94</v>
       </c>
@@ -6577,51 +6576,51 @@
       </c>
     </row>
     <row r="5" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="29"/>
+      <c r="G5" s="52"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="L5" s="29" t="s">
+      <c r="J5" s="52"/>
+      <c r="L5" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="M5" s="29"/>
-      <c r="O5" s="29" t="s">
+      <c r="M5" s="52"/>
+      <c r="O5" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="P5" s="29"/>
-      <c r="R5" s="29" t="s">
+      <c r="P5" s="52"/>
+      <c r="R5" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="S5" s="29"/>
-      <c r="U5" s="29" t="s">
+      <c r="S5" s="52"/>
+      <c r="U5" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="V5" s="29"/>
-      <c r="X5" s="29" t="s">
+      <c r="V5" s="52"/>
+      <c r="X5" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="33" t="s">
+      <c r="Y5" s="52"/>
+      <c r="Z5" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="AC5" s="46" t="s">
+      <c r="AC5" s="36" t="s">
         <v>234</v>
       </c>
       <c r="AD5" s="21" t="s">
@@ -6647,7 +6646,7 @@
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="B6" s="39"/>
+      <c r="B6" s="30"/>
       <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
@@ -6714,10 +6713,10 @@
       </c>
     </row>
     <row r="7" spans="1:40" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E7" s="10" t="s">
@@ -6777,7 +6776,7 @@
         <f>MAX(V7-V9,0)</f>
         <v>249360</v>
       </c>
-      <c r="Z7" s="49" t="s">
+      <c r="Z7" s="38" t="s">
         <v>285</v>
       </c>
       <c r="AD7" s="19">
@@ -6804,10 +6803,10 @@
       </c>
     </row>
     <row r="8" spans="1:40" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E8" s="10" t="s">
@@ -6869,7 +6868,7 @@
         <f>V8-V9+V12</f>
         <v>249801</v>
       </c>
-      <c r="Z8" s="49" t="s">
+      <c r="Z8" s="38" t="s">
         <v>286</v>
       </c>
       <c r="AD8" s="19">
@@ -6896,10 +6895,10 @@
       </c>
     </row>
     <row r="9" spans="1:40" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E9" s="10" t="s">
@@ -6947,7 +6946,7 @@
       <c r="Y9" s="4">
         <v>116</v>
       </c>
-      <c r="Z9" s="49" t="s">
+      <c r="Z9" s="38" t="s">
         <v>288</v>
       </c>
       <c r="AD9" s="19">
@@ -6974,10 +6973,10 @@
       </c>
     </row>
     <row r="10" spans="1:40" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E10" s="10" t="s">
@@ -7011,7 +7010,7 @@
         <f>-MIN(Y7-Y9,0)</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="49" t="s">
+      <c r="Z10" s="38" t="s">
         <v>289</v>
       </c>
       <c r="AD10" s="19">
@@ -7026,10 +7025,10 @@
       </c>
     </row>
     <row r="11" spans="1:40" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E11" s="10" t="s">
@@ -7063,7 +7062,7 @@
         <f>MAX(Y10-Y25,0)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="49" t="s">
+      <c r="Z11" s="38" t="s">
         <v>290</v>
       </c>
       <c r="AD11" s="19">
@@ -7078,10 +7077,10 @@
       </c>
     </row>
     <row r="12" spans="1:40" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E12" s="10" t="s">
@@ -7108,7 +7107,7 @@
       <c r="Y12" s="4">
         <v>110</v>
       </c>
-      <c r="Z12" s="49" t="s">
+      <c r="Z12" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AD12" s="19">
@@ -7123,10 +7122,10 @@
       </c>
     </row>
     <row r="13" spans="1:40" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E13" s="10" t="s">
@@ -7188,7 +7187,7 @@
         <f>MAX(Y7-Y9,0)</f>
         <v>249244</v>
       </c>
-      <c r="Z13" s="49" t="s">
+      <c r="Z13" s="38" t="s">
         <v>291</v>
       </c>
       <c r="AD13" s="19"/>
@@ -7196,10 +7195,10 @@
       <c r="AF13" s="19"/>
     </row>
     <row r="14" spans="1:40" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E14" s="10" t="s">
@@ -7226,7 +7225,7 @@
       <c r="X14" s="4">
         <v>0.7</v>
       </c>
-      <c r="Z14" s="49" t="s">
+      <c r="Z14" s="38" t="s">
         <v>292</v>
       </c>
       <c r="AD14" s="19">
@@ -7241,10 +7240,10 @@
       </c>
     </row>
     <row r="15" spans="1:40" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="31" t="s">
         <v>162</v>
       </c>
       <c r="D15" s="22" t="s">
@@ -7295,7 +7294,7 @@
       <c r="Y15" s="4">
         <v>9</v>
       </c>
-      <c r="Z15" s="49" t="s">
+      <c r="Z15" s="38" t="s">
         <v>296</v>
       </c>
       <c r="AD15" s="19"/>
@@ -7303,10 +7302,10 @@
       <c r="AF15" s="19"/>
     </row>
     <row r="16" spans="1:40" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E16" s="10" t="s">
@@ -7315,25 +7314,7 @@
       <c r="F16" s="4">
         <v>1E-3</v>
       </c>
-      <c r="I16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="O16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="R16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="U16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="X16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="Z16" s="49" t="s">
+      <c r="Z16" s="38" t="s">
         <v>293</v>
       </c>
       <c r="AD16" s="19">
@@ -7348,13 +7329,13 @@
       </c>
     </row>
     <row r="17" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="49" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="10" t="s">
@@ -7363,7 +7344,7 @@
       <c r="F17" s="4">
         <v>0.2</v>
       </c>
-      <c r="Z17" s="49" t="s">
+      <c r="Z17" s="38" t="s">
         <v>294</v>
       </c>
       <c r="AD17" s="19">
@@ -7378,20 +7359,20 @@
       </c>
     </row>
     <row r="18" spans="1:32" ht="51" x14ac:dyDescent="0.2">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="28"/>
+      <c r="D18" s="49"/>
       <c r="E18" s="10" t="s">
         <v>138</v>
       </c>
       <c r="F18" s="4">
         <v>0.67</v>
       </c>
-      <c r="Z18" s="53" t="s">
+      <c r="Z18" s="40" t="s">
         <v>295</v>
       </c>
       <c r="AD18" s="19">
@@ -7406,10 +7387,10 @@
       </c>
     </row>
     <row r="19" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E19" s="10" t="s">
@@ -7421,7 +7402,7 @@
       <c r="G19" s="4">
         <v>100</v>
       </c>
-      <c r="Z19" s="49" t="s">
+      <c r="Z19" s="38" t="s">
         <v>297</v>
       </c>
       <c r="AD19" s="19">
@@ -7436,10 +7417,10 @@
       </c>
     </row>
     <row r="20" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E20" s="10" t="s">
@@ -7451,7 +7432,7 @@
       <c r="G20" s="4">
         <v>0.25</v>
       </c>
-      <c r="Z20" s="49" t="s">
+      <c r="Z20" s="38" t="s">
         <v>298</v>
       </c>
       <c r="AD20" s="19"/>
@@ -7459,10 +7440,10 @@
       <c r="AF20" s="19"/>
     </row>
     <row r="21" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="32" t="s">
         <v>174</v>
       </c>
       <c r="E21" s="10" t="s">
@@ -7476,7 +7457,7 @@
         <f>G$19*$F$16</f>
         <v>0.1</v>
       </c>
-      <c r="Z21" s="49"/>
+      <c r="Z21" s="38"/>
       <c r="AD21" s="19">
         <v>12</v>
       </c>
@@ -7489,10 +7470,10 @@
       </c>
     </row>
     <row r="22" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="32" t="s">
         <v>174</v>
       </c>
       <c r="E22" s="10" t="s">
@@ -7506,7 +7487,7 @@
         <f>G19-G21</f>
         <v>99.9</v>
       </c>
-      <c r="Z22" s="49" t="s">
+      <c r="Z22" s="38" t="s">
         <v>299</v>
       </c>
       <c r="AD22" s="19">
@@ -7533,10 +7514,10 @@
       </c>
     </row>
     <row r="24" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E24" s="10" t="s">
@@ -7584,7 +7565,7 @@
       <c r="Y24" s="4">
         <v>49500</v>
       </c>
-      <c r="Z24" s="49"/>
+      <c r="Z24" s="38"/>
       <c r="AD24" s="19">
         <v>10</v>
       </c>
@@ -7597,10 +7578,10 @@
       </c>
     </row>
     <row r="25" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E25" s="14" t="s">
@@ -7634,7 +7615,7 @@
         <f>MAX(Y$24-Y$13, 0)</f>
         <v>0</v>
       </c>
-      <c r="Z25" s="49"/>
+      <c r="Z25" s="38"/>
       <c r="AD25" s="19">
         <v>6</v>
       </c>
@@ -7647,10 +7628,10 @@
       </c>
     </row>
     <row r="26" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E26" s="14" t="s">
@@ -7712,7 +7693,7 @@
         <f>MIN(Y13,Y24)</f>
         <v>49500</v>
       </c>
-      <c r="Z26" s="49"/>
+      <c r="Z26" s="38"/>
       <c r="AD26" s="19">
         <v>3</v>
       </c>
@@ -7754,16 +7735,16 @@
       </c>
     </row>
     <row r="28" spans="1:32" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="25" t="s">
         <v>68</v>
       </c>
       <c r="F28" s="4">
@@ -7772,17 +7753,17 @@
       <c r="G28" s="4">
         <v>0.92</v>
       </c>
-      <c r="Z28" s="49"/>
+      <c r="Z28" s="38"/>
     </row>
     <row r="29" spans="1:32" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="34" t="s">
+      <c r="D29" s="49"/>
+      <c r="E29" s="25" t="s">
         <v>171</v>
       </c>
       <c r="F29" s="4">
@@ -7793,10 +7774,10 @@
         <f>F29</f>
         <v>2E-3</v>
       </c>
-      <c r="Z29" s="49"/>
+      <c r="Z29" s="38"/>
     </row>
     <row r="30" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="35"/>
+      <c r="D30" s="26"/>
     </row>
     <row r="31" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="E31" s="15" t="s">
@@ -7818,10 +7799,10 @@
       <c r="Y31" s="8"/>
     </row>
     <row r="32" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E32" s="10" t="s">
@@ -7848,7 +7829,7 @@
       <c r="X32" s="4">
         <v>2520000</v>
       </c>
-      <c r="Z32" s="49"/>
+      <c r="Z32" s="38"/>
     </row>
     <row r="34" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="E34" s="11" t="s">
@@ -7891,7 +7872,7 @@
       </c>
     </row>
     <row r="36" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="24" t="s">
         <v>179</v>
       </c>
       <c r="E36" s="14" t="s">
@@ -7944,10 +7925,10 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="47" t="s">
+      <c r="A37" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E37" s="14" t="s">
@@ -8032,11 +8013,11 @@
         <f>V37-X37</f>
         <v>85</v>
       </c>
-      <c r="Z37" s="51"/>
+      <c r="Z37" s="37"/>
     </row>
     <row r="38" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="48"/>
-      <c r="B38" s="37"/>
+      <c r="B38" s="47"/>
       <c r="E38" s="14" t="s">
         <v>69</v>
       </c>
@@ -8118,11 +8099,11 @@
         <f>V38-X38</f>
         <v>80</v>
       </c>
-      <c r="Z38" s="49"/>
+      <c r="Z38" s="38"/>
     </row>
     <row r="39" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="48"/>
-      <c r="B39" s="37"/>
+      <c r="B39" s="47"/>
       <c r="E39" s="14" t="s">
         <v>79</v>
       </c>
@@ -8203,11 +8184,11 @@
         <f>V39-X39</f>
         <v>92</v>
       </c>
-      <c r="Z39" s="49"/>
+      <c r="Z39" s="38"/>
     </row>
     <row r="40" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="48"/>
-      <c r="B40" s="37"/>
+      <c r="B40" s="47"/>
       <c r="E40" s="14" t="s">
         <v>80</v>
       </c>
@@ -8287,7 +8268,7 @@
         <f>V40-X40</f>
         <v>43</v>
       </c>
-      <c r="Z40" s="49"/>
+      <c r="Z40" s="38"/>
     </row>
     <row r="41" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="E41" s="14" t="s">
@@ -8301,7 +8282,7 @@
       <c r="A42" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E42" s="14" t="s">
@@ -8334,11 +8315,11 @@
         <f>IF(V37=0, 0, V95*X37/V37)</f>
         <v>0</v>
       </c>
-      <c r="Z42" s="49"/>
+      <c r="Z42" s="38"/>
     </row>
     <row r="43" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="48"/>
-      <c r="B43" s="37"/>
+      <c r="B43" s="47"/>
       <c r="E43" s="14" t="s">
         <v>196</v>
       </c>
@@ -8369,11 +8350,11 @@
         <f>IF(V38=0, 0, V96*X38/V38)</f>
         <v>0</v>
       </c>
-      <c r="Z43" s="49"/>
+      <c r="Z43" s="38"/>
     </row>
     <row r="44" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="48"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="47"/>
       <c r="E44" s="14" t="s">
         <v>197</v>
       </c>
@@ -8404,11 +8385,11 @@
         <f>IF(V39=0, 0, V97*X39/V39)</f>
         <v>0</v>
       </c>
-      <c r="Z44" s="49"/>
+      <c r="Z44" s="38"/>
     </row>
     <row r="45" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="48"/>
-      <c r="B45" s="37"/>
+      <c r="B45" s="47"/>
       <c r="E45" s="14" t="s">
         <v>198</v>
       </c>
@@ -8439,13 +8420,13 @@
         <f>IF(V40=0, 0, V98*X40/V40)</f>
         <v>0</v>
       </c>
-      <c r="Z45" s="49"/>
+      <c r="Z45" s="38"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="B46" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E46" s="14"/>
@@ -8477,7 +8458,7 @@
         <f>SUM(Y42:Y45)</f>
         <v>0</v>
       </c>
-      <c r="Z46" s="49"/>
+      <c r="Z46" s="38"/>
     </row>
     <row r="47" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="E47" s="14" t="s">
@@ -8491,10 +8472,10 @@
       <c r="A48" s="48" t="s">
         <v>263</v>
       </c>
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="D48" s="28" t="s">
+      <c r="D48" s="49" t="s">
         <v>251</v>
       </c>
       <c r="E48" s="14" t="s">
@@ -8528,12 +8509,12 @@
         <f>MIN(Y42,Y$15*X37)</f>
         <v>0</v>
       </c>
-      <c r="Z48" s="49"/>
+      <c r="Z48" s="38"/>
     </row>
     <row r="49" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="48"/>
-      <c r="B49" s="37"/>
-      <c r="D49" s="28"/>
+      <c r="B49" s="47"/>
+      <c r="D49" s="49"/>
       <c r="E49" s="14" t="s">
         <v>252</v>
       </c>
@@ -8565,12 +8546,12 @@
         <f t="shared" ref="Y49" si="8">MIN(Y43,Y$15*X38)</f>
         <v>0</v>
       </c>
-      <c r="Z49" s="49"/>
+      <c r="Z49" s="38"/>
     </row>
     <row r="50" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="48"/>
-      <c r="B50" s="37"/>
-      <c r="D50" s="28"/>
+      <c r="B50" s="47"/>
+      <c r="D50" s="49"/>
       <c r="E50" s="14" t="s">
         <v>253</v>
       </c>
@@ -8602,12 +8583,12 @@
         <f>MIN(Y44,Y$15*X39)</f>
         <v>0</v>
       </c>
-      <c r="Z50" s="49"/>
+      <c r="Z50" s="38"/>
     </row>
     <row r="51" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="48"/>
-      <c r="B51" s="37"/>
-      <c r="D51" s="28"/>
+      <c r="B51" s="47"/>
+      <c r="D51" s="49"/>
       <c r="E51" s="14" t="s">
         <v>254</v>
       </c>
@@ -8639,13 +8620,13 @@
         <f>MIN(Y45,Y$15*X40)</f>
         <v>0</v>
       </c>
-      <c r="Z51" s="49"/>
+      <c r="Z51" s="38"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="49" t="s">
+      <c r="A52" s="38" t="s">
         <v>264</v>
       </c>
-      <c r="B52" s="40" t="s">
+      <c r="B52" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E52" s="14"/>
@@ -8677,13 +8658,13 @@
         <f>SUM(Y48:Y51)</f>
         <v>0</v>
       </c>
-      <c r="Z52" s="49"/>
+      <c r="Z52" s="38"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A53" s="49" t="s">
+      <c r="A53" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="B53" s="40"/>
+      <c r="B53" s="28"/>
       <c r="E53" s="14"/>
       <c r="G53" s="4">
         <f>G46-G52</f>
@@ -8713,7 +8694,7 @@
         <f>Y46-Y52</f>
         <v>0</v>
       </c>
-      <c r="Z53" s="49"/>
+      <c r="Z53" s="38"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E54" s="14"/>
@@ -8722,7 +8703,7 @@
       <c r="A55" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="37" t="s">
+      <c r="B55" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E55" s="14" t="s">
@@ -8756,11 +8737,11 @@
         <f>Y42*$G$20</f>
         <v>0</v>
       </c>
-      <c r="Z55" s="49"/>
+      <c r="Z55" s="38"/>
     </row>
     <row r="56" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="48"/>
-      <c r="B56" s="37"/>
+      <c r="B56" s="47"/>
       <c r="E56" s="14" t="s">
         <v>200</v>
       </c>
@@ -8792,11 +8773,11 @@
         <f>Y43*$G$20</f>
         <v>0</v>
       </c>
-      <c r="Z56" s="49"/>
+      <c r="Z56" s="38"/>
     </row>
     <row r="57" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="48"/>
-      <c r="B57" s="37"/>
+      <c r="B57" s="47"/>
       <c r="E57" s="14" t="s">
         <v>201</v>
       </c>
@@ -8828,11 +8809,11 @@
         <f>Y44*$G$20</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="49"/>
+      <c r="Z57" s="38"/>
     </row>
     <row r="58" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="48"/>
-      <c r="B58" s="37"/>
+      <c r="B58" s="47"/>
       <c r="E58" s="14" t="s">
         <v>202</v>
       </c>
@@ -8864,13 +8845,13 @@
         <f>Y45*$G$20</f>
         <v>0</v>
       </c>
-      <c r="Z58" s="49"/>
+      <c r="Z58" s="38"/>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A59" s="49" t="s">
+      <c r="A59" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="B59" s="40" t="s">
+      <c r="B59" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E59" s="14"/>
@@ -8902,7 +8883,7 @@
         <f>SUM(Y55:Y58)</f>
         <v>0</v>
       </c>
-      <c r="Z59" s="49"/>
+      <c r="Z59" s="38"/>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E60" s="14"/>
@@ -8911,7 +8892,7 @@
       <c r="A61" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="B61" s="37" t="s">
+      <c r="B61" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E61" s="14" t="s">
@@ -8945,11 +8926,11 @@
         <f>AD14</f>
         <v>0.6</v>
       </c>
-      <c r="Z61" s="49"/>
+      <c r="Z61" s="38"/>
     </row>
     <row r="62" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="48"/>
-      <c r="B62" s="37"/>
+      <c r="B62" s="47"/>
       <c r="E62" s="14" t="s">
         <v>91</v>
       </c>
@@ -8979,11 +8960,11 @@
         <f>AD12</f>
         <v>0.36</v>
       </c>
-      <c r="Z62" s="49"/>
+      <c r="Z62" s="38"/>
     </row>
     <row r="63" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="48"/>
-      <c r="B63" s="37"/>
+      <c r="B63" s="47"/>
       <c r="E63" s="14" t="s">
         <v>92</v>
       </c>
@@ -9012,11 +8993,11 @@
         <f>AD11</f>
         <v>0.2</v>
       </c>
-      <c r="Z63" s="49"/>
+      <c r="Z63" s="38"/>
     </row>
     <row r="64" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" s="48"/>
-      <c r="B64" s="37"/>
+      <c r="B64" s="47"/>
       <c r="E64" s="14" t="s">
         <v>93</v>
       </c>
@@ -9044,7 +9025,7 @@
         <f>AD9</f>
         <v>0.12</v>
       </c>
-      <c r="Z64" s="49"/>
+      <c r="Z64" s="38"/>
     </row>
     <row r="65" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="E65" s="14" t="s">
@@ -9058,7 +9039,7 @@
       <c r="A67" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="B67" s="37" t="s">
+      <c r="B67" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E67" s="14" t="s">
@@ -9092,11 +9073,11 @@
         <f>V67*(1- $F$29)+Y37*Y61</f>
         <v>113.66742611453597</v>
       </c>
-      <c r="Z67" s="49"/>
+      <c r="Z67" s="38"/>
     </row>
     <row r="68" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="48"/>
-      <c r="B68" s="37"/>
+      <c r="B68" s="47"/>
       <c r="E68" s="14" t="s">
         <v>110</v>
       </c>
@@ -9124,12 +9105,12 @@
         <f>V68*(1- $F$29)+Y38*Y62</f>
         <v>59.099305542412793</v>
       </c>
-      <c r="Z68" s="49"/>
+      <c r="Z68" s="38"/>
     </row>
     <row r="69" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="48"/>
-      <c r="B69" s="37"/>
-      <c r="D69" s="28"/>
+      <c r="B69" s="47"/>
+      <c r="D69" s="49"/>
       <c r="E69" s="14" t="s">
         <v>111</v>
       </c>
@@ -9153,12 +9134,12 @@
         <f>V69*(1- $F$29)+Y39*Y63</f>
         <v>34.91402943264</v>
       </c>
-      <c r="Z69" s="49"/>
+      <c r="Z69" s="38"/>
     </row>
     <row r="70" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="48"/>
-      <c r="B70" s="37"/>
-      <c r="D70" s="28"/>
+      <c r="B70" s="47"/>
+      <c r="D70" s="49"/>
       <c r="E70" s="14" t="s">
         <v>112</v>
       </c>
@@ -9182,17 +9163,17 @@
         <f>V70*(1- $F$29)+Y40*Y64</f>
         <v>7.7339817200000001</v>
       </c>
-      <c r="Z70" s="49"/>
+      <c r="Z70" s="38"/>
     </row>
     <row r="71" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="D71" s="28"/>
+      <c r="D71" s="49"/>
       <c r="E71" s="14"/>
     </row>
     <row r="72" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="B72" s="37" t="s">
+      <c r="B72" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E72" s="14" t="s">
@@ -9225,11 +9206,11 @@
         <f>INT(X$4-$AF$6 &gt; $D80)*MAX(V95-$G$21*V37-Y42,0)</f>
         <v>30.582999999999998</v>
       </c>
-      <c r="Z72" s="49"/>
+      <c r="Z72" s="38"/>
     </row>
     <row r="73" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="48"/>
-      <c r="B73" s="37"/>
+      <c r="B73" s="47"/>
       <c r="E73" s="14" t="s">
         <v>128</v>
       </c>
@@ -9260,12 +9241,12 @@
         <f>INT(X$4-$AF$6 &gt; $D81)*MAX(V96-$G$21*V38-Y43,0)</f>
         <v>15.984000000000002</v>
       </c>
-      <c r="Z73" s="49"/>
+      <c r="Z73" s="38"/>
     </row>
     <row r="74" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" s="48"/>
-      <c r="B74" s="37"/>
-      <c r="D74" s="28" t="s">
+      <c r="B74" s="47"/>
+      <c r="D74" s="49" t="s">
         <v>152</v>
       </c>
       <c r="E74" s="14" t="s">
@@ -9298,12 +9279,12 @@
         <f>INT(X$4-$AF$6 &gt; $D82)*MAX(V97-$G$21*V39-Y44,0)</f>
         <v>7.3471236799999975</v>
       </c>
-      <c r="Z74" s="49"/>
+      <c r="Z74" s="38"/>
     </row>
     <row r="75" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="48"/>
-      <c r="B75" s="37"/>
-      <c r="D75" s="28"/>
+      <c r="B75" s="47"/>
+      <c r="D75" s="49"/>
       <c r="E75" s="14" t="s">
         <v>130</v>
       </c>
@@ -9334,16 +9315,16 @@
         <f>INT(X$4-$AF$6 &gt; $D83)*MAX(V98-$G$21*V40-Y45,0)</f>
         <v>0</v>
       </c>
-      <c r="Z75" s="49"/>
+      <c r="Z75" s="38"/>
     </row>
     <row r="76" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" s="49" t="s">
+      <c r="A76" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="D76" s="28"/>
+      <c r="D76" s="49"/>
       <c r="E76" s="14" t="s">
         <v>147</v>
       </c>
@@ -9374,13 +9355,13 @@
         <f>SUM(Y72:Y75)</f>
         <v>53.914123679999996</v>
       </c>
-      <c r="Z76" s="49"/>
+      <c r="Z76" s="38"/>
       <c r="AE76" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="D77" s="28"/>
+      <c r="D77" s="49"/>
       <c r="E77" s="14"/>
       <c r="AC77" t="s">
         <v>85</v>
@@ -9393,7 +9374,7 @@
       <c r="A78" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="B78" s="37" t="s">
+      <c r="B78" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E78" s="14" t="s">
@@ -9420,14 +9401,14 @@
       <c r="X78" s="4">
         <v>0</v>
       </c>
-      <c r="Z78" s="52"/>
+      <c r="Z78" s="39"/>
       <c r="AC78" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A79" s="50"/>
-      <c r="B79" s="37"/>
+      <c r="B79" s="47"/>
       <c r="E79" s="14" t="s">
         <v>148</v>
       </c>
@@ -9487,11 +9468,11 @@
         <f>IF(X79&gt;=X$131, IF(X78&lt;X$131, X$131-X78, 0),Y72)</f>
         <v>30.582999999999998</v>
       </c>
-      <c r="Z79" s="52"/>
+      <c r="Z79" s="39"/>
     </row>
     <row r="80" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="50"/>
-      <c r="B80" s="37"/>
+      <c r="B80" s="47"/>
       <c r="D80" s="22">
         <v>0</v>
       </c>
@@ -9554,11 +9535,11 @@
         <f>IF(X80&gt;=X$131, IF(X79&lt;X$131, X$131-X79, 0),Y73)</f>
         <v>15.984000000000002</v>
       </c>
-      <c r="Z80" s="52"/>
+      <c r="Z80" s="39"/>
     </row>
     <row r="81" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A81" s="50"/>
-      <c r="B81" s="37"/>
+      <c r="B81" s="47"/>
       <c r="D81" s="22">
         <v>1</v>
       </c>
@@ -9621,11 +9602,11 @@
         <f>IF(X81&gt;=X$131, IF(X80&lt;X$131, X$131-X80, 0),Y74)</f>
         <v>7.3471236799999957</v>
       </c>
-      <c r="Z81" s="52"/>
+      <c r="Z81" s="39"/>
     </row>
     <row r="82" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A82" s="50"/>
-      <c r="B82" s="37"/>
+      <c r="B82" s="47"/>
       <c r="D82" s="22">
         <v>2</v>
       </c>
@@ -9688,7 +9669,7 @@
         <f>IF(X82&gt;=X$131, IF(X81&lt;X$131, X$131-X81, 0),Y75)</f>
         <v>0</v>
       </c>
-      <c r="Z82" s="52"/>
+      <c r="Z82" s="39"/>
     </row>
     <row r="83" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D83" s="22">
@@ -9718,10 +9699,10 @@
       </c>
     </row>
     <row r="85" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="47" t="s">
+      <c r="A85" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="37" t="s">
+      <c r="B85" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E85" s="14" t="s">
@@ -9779,11 +9760,11 @@
         <f>Y61*X85</f>
         <v>0.5573184044275703</v>
       </c>
-      <c r="Z85" s="51"/>
+      <c r="Z85" s="37"/>
     </row>
     <row r="86" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="47"/>
-      <c r="B86" s="37"/>
+      <c r="A86" s="46"/>
+      <c r="B86" s="47"/>
       <c r="E86" s="14" t="s">
         <v>132</v>
       </c>
@@ -9839,11 +9820,11 @@
         <f>Y62</f>
         <v>0.36</v>
       </c>
-      <c r="Z86" s="51"/>
+      <c r="Z86" s="37"/>
     </row>
     <row r="87" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="47"/>
-      <c r="B87" s="37"/>
+      <c r="A87" s="46"/>
+      <c r="B87" s="47"/>
       <c r="E87" s="14" t="s">
         <v>133</v>
       </c>
@@ -9899,11 +9880,11 @@
         <f>Y63</f>
         <v>0.2</v>
       </c>
-      <c r="Z87" s="51"/>
+      <c r="Z87" s="37"/>
     </row>
     <row r="88" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
-      <c r="B88" s="37"/>
+      <c r="A88" s="46"/>
+      <c r="B88" s="47"/>
       <c r="E88" s="14" t="s">
         <v>134</v>
       </c>
@@ -9959,16 +9940,16 @@
         <f>Y64</f>
         <v>0.12</v>
       </c>
-      <c r="Z88" s="51"/>
+      <c r="Z88" s="37"/>
     </row>
     <row r="89" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E89" s="14"/>
     </row>
     <row r="90" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="47" t="s">
+      <c r="A90" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="B90" s="37" t="s">
+      <c r="B90" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E90" s="14" t="s">
@@ -10002,11 +9983,11 @@
         <f>(V95-Y79-Y42)*$F$29</f>
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="Z90" s="51"/>
+      <c r="Z90" s="37"/>
     </row>
     <row r="91" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="47"/>
-      <c r="B91" s="37"/>
+      <c r="A91" s="46"/>
+      <c r="B91" s="47"/>
       <c r="E91" s="14" t="s">
         <v>206</v>
       </c>
@@ -10038,11 +10019,11 @@
         <f>(V96-Y80-Y43)*$F$29</f>
         <v>1.6E-2</v>
       </c>
-      <c r="Z91" s="51"/>
+      <c r="Z91" s="37"/>
     </row>
     <row r="92" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A92" s="47"/>
-      <c r="B92" s="37"/>
+      <c r="A92" s="46"/>
+      <c r="B92" s="47"/>
       <c r="E92" s="14" t="s">
         <v>207</v>
       </c>
@@ -10074,11 +10055,11 @@
         <f>(V97-Y81-Y44)*$F$29</f>
         <v>1.8400000000000007E-2</v>
       </c>
-      <c r="Z92" s="51"/>
+      <c r="Z92" s="37"/>
     </row>
     <row r="93" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A93" s="47"/>
-      <c r="B93" s="37"/>
+      <c r="A93" s="46"/>
+      <c r="B93" s="47"/>
       <c r="E93" s="14" t="s">
         <v>208</v>
       </c>
@@ -10110,16 +10091,16 @@
         <f>(V98-Y82-Y45)*$F$29</f>
         <v>5.1582799999999995E-3</v>
       </c>
-      <c r="Z93" s="51"/>
+      <c r="Z93" s="37"/>
     </row>
     <row r="94" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E94" s="14"/>
     </row>
     <row r="95" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="47" t="s">
+      <c r="A95" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="37" t="s">
+      <c r="B95" s="47" t="s">
         <v>174</v>
       </c>
       <c r="E95" s="14" t="s">
@@ -10153,11 +10134,11 @@
         <f>V95 - Y79 - Y90 - Y42 + Y37*Y85</f>
         <v>55.855064376343478</v>
       </c>
-      <c r="Z95" s="51"/>
+      <c r="Z95" s="37"/>
     </row>
     <row r="96" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="47"/>
-      <c r="B96" s="37"/>
+      <c r="A96" s="46"/>
+      <c r="B96" s="47"/>
       <c r="E96" s="14" t="s">
         <v>71</v>
       </c>
@@ -10189,11 +10170,11 @@
         <f>V96 - Y80 - Y91 - Y43 + Y38*Y86</f>
         <v>36.783999999999999</v>
       </c>
-      <c r="Z96" s="51"/>
+      <c r="Z96" s="37"/>
     </row>
     <row r="97" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A97" s="47"/>
-      <c r="B97" s="37"/>
+      <c r="A97" s="46"/>
+      <c r="B97" s="47"/>
       <c r="E97" s="14" t="s">
         <v>72</v>
       </c>
@@ -10225,11 +10206,11 @@
         <f>V97 - Y81 - Y92 - Y44 + Y39*Y87</f>
         <v>27.581600000000005</v>
       </c>
-      <c r="Z97" s="51"/>
+      <c r="Z97" s="37"/>
     </row>
     <row r="98" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="47"/>
-      <c r="B98" s="37"/>
+      <c r="A98" s="46"/>
+      <c r="B98" s="47"/>
       <c r="E98" s="14" t="s">
         <v>81</v>
       </c>
@@ -10261,20 +10242,20 @@
         <f>V98 - Y82 - Y93 - Y45 + Y40*Y88</f>
         <v>7.7339817200000001</v>
       </c>
-      <c r="Z98" s="51"/>
+      <c r="Z98" s="37"/>
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="D99" s="35"/>
+      <c r="D99" s="26"/>
       <c r="E99" s="14"/>
     </row>
     <row r="100" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A100" s="47" t="s">
+      <c r="A100" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="B100" s="37" t="s">
+      <c r="B100" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="D100" s="35"/>
+      <c r="D100" s="26"/>
       <c r="E100" s="14" t="s">
         <v>211</v>
       </c>
@@ -10306,12 +10287,12 @@
         <f>Y95*$G$20</f>
         <v>13.963766094085869</v>
       </c>
-      <c r="Z100" s="51"/>
+      <c r="Z100" s="37"/>
     </row>
     <row r="101" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="37"/>
-      <c r="D101" s="35"/>
+      <c r="A101" s="46"/>
+      <c r="B101" s="47"/>
+      <c r="D101" s="26"/>
       <c r="E101" s="14" t="s">
         <v>212</v>
       </c>
@@ -10343,12 +10324,12 @@
         <f t="shared" ref="Y101:Y103" si="15">Y96*$G$20</f>
         <v>9.1959999999999997</v>
       </c>
-      <c r="Z101" s="51"/>
+      <c r="Z101" s="37"/>
     </row>
     <row r="102" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A102" s="47"/>
-      <c r="B102" s="37"/>
-      <c r="D102" s="35"/>
+      <c r="A102" s="46"/>
+      <c r="B102" s="47"/>
+      <c r="D102" s="26"/>
       <c r="E102" s="14" t="s">
         <v>213</v>
       </c>
@@ -10380,12 +10361,12 @@
         <f>Y97*$G$20</f>
         <v>6.8954000000000013</v>
       </c>
-      <c r="Z102" s="51"/>
+      <c r="Z102" s="37"/>
     </row>
     <row r="103" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="47"/>
-      <c r="B103" s="37"/>
-      <c r="D103" s="35"/>
+      <c r="A103" s="46"/>
+      <c r="B103" s="47"/>
+      <c r="D103" s="26"/>
       <c r="E103" s="14" t="s">
         <v>214</v>
       </c>
@@ -10417,24 +10398,24 @@
         <f t="shared" si="15"/>
         <v>1.93349543</v>
       </c>
-      <c r="Z103" s="51"/>
+      <c r="Z103" s="37"/>
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A104" s="38"/>
-      <c r="B104" s="45"/>
-      <c r="D104" s="35"/>
+      <c r="A104" s="29"/>
+      <c r="B104" s="35"/>
+      <c r="D104" s="26"/>
       <c r="E104" s="14"/>
-      <c r="Z104" s="38"/>
+      <c r="Z104" s="29"/>
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A105" s="38"/>
-      <c r="B105" s="45"/>
-      <c r="D105" s="35"/>
+      <c r="A105" s="29"/>
+      <c r="B105" s="35"/>
+      <c r="D105" s="26"/>
       <c r="E105" s="14"/>
-      <c r="Z105" s="38"/>
+      <c r="Z105" s="29"/>
     </row>
     <row r="106" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="D106" s="35"/>
+      <c r="D106" s="26"/>
       <c r="E106" s="15" t="s">
         <v>140</v>
       </c>
@@ -10444,13 +10425,13 @@
       <c r="G106" s="8"/>
     </row>
     <row r="107" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="49" t="s">
+      <c r="A107" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="B107" s="44" t="s">
+      <c r="B107" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="D107" s="35"/>
+      <c r="D107" s="26"/>
       <c r="E107" s="14" t="s">
         <v>90</v>
       </c>
@@ -10510,13 +10491,13 @@
         <f>$G$28</f>
         <v>0.92</v>
       </c>
-      <c r="Z107" s="49"/>
+      <c r="Z107" s="38"/>
     </row>
     <row r="108" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A108" s="49" t="s">
+      <c r="A108" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="40" t="s">
+      <c r="B108" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E108" s="14" t="s">
@@ -10578,13 +10559,13 @@
         <f>Y7*$G$19</f>
         <v>24936000</v>
       </c>
-      <c r="Z108" s="49"/>
+      <c r="Z108" s="38"/>
     </row>
     <row r="109" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="49" t="s">
+      <c r="A109" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="B109" s="40" t="s">
+      <c r="B109" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E109" s="14" t="s">
@@ -10644,13 +10625,13 @@
         <f>IF(V111=0,0,MIN(MAX((V111/V108-$F$16)/($F$18-$F$16), 0), 1))</f>
         <v>0.89478919993714923</v>
       </c>
-      <c r="Z109" s="49"/>
+      <c r="Z109" s="38"/>
     </row>
     <row r="110" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A110" s="49" t="s">
+      <c r="A110" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="B110" s="43" t="s">
+      <c r="B110" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E110" s="14" t="s">
@@ -10712,13 +10693,13 @@
         <f>Y107*Y109</f>
         <v>0.82320606394217732</v>
       </c>
-      <c r="Z110" s="49"/>
+      <c r="Z110" s="38"/>
     </row>
     <row r="111" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A111" s="49" t="s">
+      <c r="A111" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="B111" s="43" t="s">
+      <c r="B111" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E111" s="14" t="s">
@@ -10780,13 +10761,13 @@
         <f>V111 - V132 - V120 - V143 + Y110*Y7</f>
         <v>3187373.6439100648</v>
       </c>
-      <c r="Z111" s="49"/>
+      <c r="Z111" s="38"/>
     </row>
     <row r="112" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="49" t="s">
+      <c r="A112" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="B112" s="43" t="s">
+      <c r="B112" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E112" s="14" t="s">
@@ -10848,13 +10829,13 @@
         <f>Y111/Y7</f>
         <v>12.782217051291566</v>
       </c>
-      <c r="Z112" s="49"/>
+      <c r="Z112" s="38"/>
     </row>
     <row r="113" spans="1:26" ht="34" x14ac:dyDescent="0.2">
-      <c r="A113" s="49" t="s">
+      <c r="A113" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B113" s="40" t="s">
+      <c r="B113" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E113" s="10" t="s">
@@ -10916,7 +10897,7 @@
         <f>MAX(Y112-$G21,0)</f>
         <v>12.682217051291566</v>
       </c>
-      <c r="Z113" s="49"/>
+      <c r="Z113" s="38"/>
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E114" s="13"/>
@@ -10941,10 +10922,10 @@
       <c r="Y115" s="12"/>
     </row>
     <row r="116" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="49" t="s">
+      <c r="A116" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="B116" s="44" t="s">
+      <c r="B116" s="34" t="s">
         <v>182</v>
       </c>
       <c r="E116" s="10" t="s">
@@ -11006,13 +10987,13 @@
         <f>Y112*Y7</f>
         <v>3187373.6439100648</v>
       </c>
-      <c r="Z116" s="49"/>
+      <c r="Z116" s="38"/>
     </row>
     <row r="117" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="49" t="s">
+      <c r="A117" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="B117" s="43" t="s">
+      <c r="B117" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E117" s="10" t="s">
@@ -11046,13 +11027,13 @@
         <f>SUM(Y95:Y98)</f>
         <v>127.95464609634348</v>
       </c>
-      <c r="Z117" s="49"/>
+      <c r="Z117" s="38"/>
     </row>
     <row r="118" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A118" s="49" t="s">
+      <c r="A118" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="B118" s="43" t="s">
+      <c r="B118" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E118" s="10" t="s">
@@ -11114,13 +11095,13 @@
         <f>Y116+Y117</f>
         <v>3187501.5985561614</v>
       </c>
-      <c r="Z118" s="49"/>
+      <c r="Z118" s="38"/>
     </row>
     <row r="119" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A119" s="49" t="s">
+      <c r="A119" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="B119" s="43" t="s">
+      <c r="B119" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E119" s="10" t="s">
@@ -11182,13 +11163,13 @@
         <f>Y111*$G$20</f>
         <v>796843.41097751621</v>
       </c>
-      <c r="Z119" s="49"/>
+      <c r="Z119" s="38"/>
     </row>
     <row r="120" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A120" s="49" t="s">
+      <c r="A120" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="B120" s="40" t="s">
+      <c r="B120" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E120" s="10" t="s">
@@ -11250,13 +11231,13 @@
         <f>Y9*Y112</f>
         <v>1482.7371779498217</v>
       </c>
-      <c r="Z120" s="49"/>
+      <c r="Z120" s="38"/>
     </row>
     <row r="121" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A121" s="49" t="s">
+      <c r="A121" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="B121" s="40" t="s">
+      <c r="B121" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E121" s="10" t="s">
@@ -11318,13 +11299,13 @@
         <f>MIN(Y120,Y9*Y15)</f>
         <v>1044</v>
       </c>
-      <c r="Z121" s="49"/>
+      <c r="Z121" s="38"/>
     </row>
     <row r="122" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A122" s="49" t="s">
+      <c r="A122" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="B122" s="40" t="s">
+      <c r="B122" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E122" s="10" t="s">
@@ -11386,13 +11367,13 @@
         <f>(Y120-Y121+Y53)*$F$14</f>
         <v>307.11602456487515</v>
       </c>
-      <c r="Z122" s="49"/>
+      <c r="Z122" s="38"/>
     </row>
     <row r="123" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="49" t="s">
+      <c r="A123" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="B123" s="43" t="s">
+      <c r="B123" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E123" s="14" t="s">
@@ -11426,13 +11407,13 @@
         <f>MIN(X122+Y122, X32)</f>
         <v>5839.4603133048031</v>
       </c>
-      <c r="Z123" s="49"/>
+      <c r="Z123" s="38"/>
     </row>
     <row r="124" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A124" s="49" t="s">
+      <c r="A124" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="B124" s="40" t="s">
+      <c r="B124" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E124" s="14" t="s">
@@ -11494,13 +11475,13 @@
         <f>Y122/(X122+Y122)</f>
         <v>5.2593220620942092E-2</v>
       </c>
-      <c r="Z124" s="49"/>
+      <c r="Z124" s="38"/>
     </row>
     <row r="125" spans="1:26" ht="34" x14ac:dyDescent="0.2">
-      <c r="A125" s="49" t="s">
+      <c r="A125" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="B125" s="40" t="s">
+      <c r="B125" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E125" s="10" t="s">
@@ -11562,7 +11543,7 @@
         <f>MAX(Y13-Y26, 0)*Y113</f>
         <v>2533196.7626931826</v>
       </c>
-      <c r="Z125" s="49"/>
+      <c r="Z125" s="38"/>
     </row>
     <row r="127" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="E127" s="15" t="s">
@@ -11584,10 +11565,10 @@
       <c r="Y127" s="8"/>
     </row>
     <row r="128" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A128" s="49" t="s">
+      <c r="A128" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="B128" s="40" t="s">
+      <c r="B128" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E128" s="14" t="s">
@@ -11621,13 +11602,13 @@
         <f>MAX(X32-X123,0)</f>
         <v>2514160.5396866952</v>
       </c>
-      <c r="Z128" s="49"/>
+      <c r="Z128" s="38"/>
     </row>
     <row r="129" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A129" s="49" t="s">
+      <c r="A129" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="B129" s="40" t="s">
+      <c r="B129" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E129" s="10" t="s">
@@ -11661,13 +11642,13 @@
         <f>MIN(X139,X128)</f>
         <v>1789059.8013981958</v>
       </c>
-      <c r="Z129" s="49"/>
+      <c r="Z129" s="38"/>
     </row>
     <row r="130" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A130" s="49" t="s">
+      <c r="A130" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="B130" s="40" t="s">
+      <c r="B130" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E130" s="10" t="s">
@@ -11701,13 +11682,13 @@
         <f>X128-X129</f>
         <v>725100.73828849941</v>
       </c>
-      <c r="Z130" s="49"/>
+      <c r="Z130" s="38"/>
     </row>
     <row r="131" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A131" s="49" t="s">
+      <c r="A131" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="B131" s="40" t="s">
+      <c r="B131" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E131" s="10" t="s">
@@ -11741,13 +11722,13 @@
         <f>MIN(X130,Y76)</f>
         <v>53.914123679999996</v>
       </c>
-      <c r="Z131" s="49"/>
+      <c r="Z131" s="38"/>
     </row>
     <row r="132" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A132" s="49" t="s">
+      <c r="A132" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="B132" s="40" t="s">
+      <c r="B132" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E132" s="10" t="s">
@@ -11809,13 +11790,13 @@
         <f>Y140*X129</f>
         <v>1595269.5105861374</v>
       </c>
-      <c r="Z132" s="49"/>
+      <c r="Z132" s="38"/>
     </row>
     <row r="133" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A133" s="49" t="s">
+      <c r="A133" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="43" t="s">
+      <c r="B133" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E133" s="10" t="s">
@@ -11877,7 +11858,7 @@
         <f>Y132+X131</f>
         <v>1595323.4247098174</v>
       </c>
-      <c r="Z133" s="49"/>
+      <c r="Z133" s="38"/>
     </row>
     <row r="134" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="E134" s="15" t="s">
@@ -11899,10 +11880,10 @@
       <c r="Y134" s="8"/>
     </row>
     <row r="135" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A135" s="49" t="s">
+      <c r="A135" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="B135" s="40" t="s">
+      <c r="B135" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E135" s="10" t="s">
@@ -11964,7 +11945,7 @@
         <f>Y113/$G$22</f>
         <v>0.12694911963254821</v>
       </c>
-      <c r="Z135" s="49"/>
+      <c r="Z135" s="38"/>
       <c r="AA135">
         <v>0.5</v>
       </c>
@@ -11977,10 +11958,10 @@
       </c>
     </row>
     <row r="136" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A136" s="49" t="s">
+      <c r="A136" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="B136" s="40" t="s">
+      <c r="B136" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E136" s="10" t="s">
@@ -12042,7 +12023,7 @@
         <f>MAX(MIN((Y135-$F$16)/$F$17, 1), 0)</f>
         <v>0.629745598162741</v>
       </c>
-      <c r="Z136" s="49"/>
+      <c r="Z136" s="38"/>
       <c r="AA136">
         <v>0.3</v>
       </c>
@@ -12055,8 +12036,8 @@
       </c>
     </row>
     <row r="137" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A137" s="49"/>
-      <c r="Z137" s="49"/>
+      <c r="A137" s="38"/>
+      <c r="Z137" s="38"/>
       <c r="AA137">
         <v>0.2</v>
       </c>
@@ -12069,10 +12050,10 @@
       </c>
     </row>
     <row r="138" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A138" s="49" t="s">
+      <c r="A138" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="B138" s="40" t="s">
+      <c r="B138" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E138" s="10" t="s">
@@ -12134,7 +12115,7 @@
         <f>Y125*Y136</f>
         <v>1595269.5105861374</v>
       </c>
-      <c r="Z138" s="49"/>
+      <c r="Z138" s="38"/>
       <c r="AA138">
         <v>0.125</v>
       </c>
@@ -12147,10 +12128,10 @@
       </c>
     </row>
     <row r="139" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A139" s="49" t="s">
+      <c r="A139" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="B139" s="40" t="s">
+      <c r="B139" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E139" s="10" t="s">
@@ -12212,13 +12193,13 @@
         <f>X139</f>
         <v>1789059.8013981958</v>
       </c>
-      <c r="Z139" s="49"/>
+      <c r="Z139" s="38"/>
     </row>
     <row r="140" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A140" s="49" t="s">
+      <c r="A140" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="B140" s="40" t="s">
+      <c r="B140" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E140" s="10" t="s">
@@ -12280,7 +12261,7 @@
         <f>Y138/Y139</f>
         <v>0.89168037275187428</v>
       </c>
-      <c r="Z140" s="49"/>
+      <c r="Z140" s="38"/>
     </row>
     <row r="142" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="E142" s="15" t="s">
@@ -12302,10 +12283,10 @@
       <c r="Y142" s="8"/>
     </row>
     <row r="143" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A143" s="49" t="s">
+      <c r="A143" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="B143" s="43" t="s">
+      <c r="B143" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E143" s="10" t="s">
@@ -12367,13 +12348,13 @@
         <f>(Y111 - Y132 - Y120)*$G$29+SUM(Y90:Y93)</f>
         <v>3181.2993505719551</v>
       </c>
-      <c r="Z143" s="49"/>
+      <c r="Z143" s="38"/>
     </row>
     <row r="144" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A144" s="49" t="s">
+      <c r="A144" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="B144" s="43" t="s">
+      <c r="B144" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E144" s="14" t="s">
@@ -12435,13 +12416,13 @@
         <f>(Y132+X131)*$G20</f>
         <v>398830.85617745435</v>
       </c>
-      <c r="Z144" s="49"/>
+      <c r="Z144" s="38"/>
     </row>
     <row r="145" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A145" s="49" t="s">
+      <c r="A145" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="B145" s="43" t="s">
+      <c r="B145" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E145" s="10" t="s">
@@ -12503,13 +12484,13 @@
         <f>Y120-X123*Y124-Y121+Y53</f>
         <v>131.62115338494641</v>
       </c>
-      <c r="Z145" s="49"/>
+      <c r="Z145" s="38"/>
     </row>
     <row r="146" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A146" s="49" t="s">
+      <c r="A146" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="B146" s="43" t="s">
+      <c r="B146" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E146" s="10" t="s">
@@ -12571,10 +12552,10 @@
         <f>(Y120+Y53)*$G20</f>
         <v>370.68429448745542</v>
       </c>
-      <c r="Z146" s="49"/>
+      <c r="Z146" s="38"/>
     </row>
     <row r="149" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A149" s="33" t="s">
+      <c r="A149" s="24" t="s">
         <v>267</v>
       </c>
       <c r="F149" s="4">
@@ -12635,10 +12616,10 @@
       </c>
     </row>
     <row r="151" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A151" s="49" t="s">
+      <c r="A151" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="B151" s="43" t="s">
+      <c r="B151" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F151" s="4">
@@ -12669,7 +12650,7 @@
         <f>X123+X132+Y132</f>
         <v>1794899.2617115006</v>
       </c>
-      <c r="Z151" s="49"/>
+      <c r="Z151" s="38"/>
     </row>
     <row r="152" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F152" s="4">
@@ -12739,37 +12720,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="D48:D51"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A61:A64"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="A85:A88"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="L5:M5"/>
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="D74:D77"/>
@@ -12778,6 +12728,37 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="U5:V5"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="D48:D51"/>
+    <mergeCell ref="A78:A82"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="A85:A88"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75A060D-8C3C-5A4B-A9D3-F7AC49307262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB018337-E483-704D-B091-748AC3E41FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="760" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="260" yWindow="760" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="301">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -944,6 +944,9 @@
   </si>
   <si>
     <t>k_{heav}</t>
+  </si>
+  <si>
+    <t>rrr</t>
   </si>
 </sst>
 </file>
@@ -7314,6 +7317,9 @@
       <c r="F16" s="4">
         <v>1E-3</v>
       </c>
+      <c r="G16" s="4">
+        <v>1E-3</v>
+      </c>
       <c r="Z16" s="38" t="s">
         <v>293</v>
       </c>
@@ -7344,6 +7350,9 @@
       <c r="F17" s="4">
         <v>0.2</v>
       </c>
+      <c r="G17" s="4">
+        <v>0.2</v>
+      </c>
       <c r="Z17" s="38" t="s">
         <v>294</v>
       </c>
@@ -7454,7 +7463,7 @@
         <v>0.15</v>
       </c>
       <c r="G21" s="4">
-        <f>G$19*$F$16</f>
+        <f>G$19*$G$16</f>
         <v>0.1</v>
       </c>
       <c r="Z21" s="38"/>
@@ -10582,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="J109" s="4">
-        <f>IF(G111=0,0,MIN(MAX((G111/G108-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(G111=0,0,MIN(MAX((G111/G108-$G$16)/($F$18-$G$16), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="L109" s="4">
@@ -10590,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="M109" s="4">
-        <f>IF(J111=0,0,MIN(MAX((J111/J108-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(J111=0,0,MIN(MAX((J111/J108-$G$16)/($F$18-$G$16), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="O109" s="4">
@@ -10598,7 +10607,7 @@
         <v>1</v>
       </c>
       <c r="P109" s="4">
-        <f>IF(M111=0,0,MIN(MAX((M111/M108-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(M111=0,0,MIN(MAX((M111/M108-$G$16)/($F$18-$G$16), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="R109" s="4">
@@ -10606,7 +10615,7 @@
         <v>1</v>
       </c>
       <c r="S109" s="4">
-        <f>IF(P111=0,0,MIN(MAX((P111/P108-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(P111=0,0,MIN(MAX((P111/P108-$G$16)/($F$18-$G$16), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="U109" s="4">
@@ -10614,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="V109" s="4">
-        <f>IF(S111=0,0,MIN(MAX((S111/S108-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(S111=0,0,MIN(MAX((S111/S108-$G$16)/($F$18-$G$16), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="X109" s="4">
@@ -10622,10 +10631,12 @@
         <v>1</v>
       </c>
       <c r="Y109" s="4">
-        <f>IF(V111=0,0,MIN(MAX((V111/V108-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(V111=0,0,MIN(MAX((V111/V108-$G$16)/($F$18-$G$16), 0), 1))</f>
         <v>0.89478919993714923</v>
       </c>
-      <c r="Z109" s="38"/>
+      <c r="Z109" s="38" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="110" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" s="38" t="s">
@@ -11972,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="4">
-        <f>MAX(MIN((G135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((G135-$G$16)/$G$17, 1), 0)</f>
         <v>1</v>
       </c>
       <c r="I136" s="4">
@@ -11980,7 +11991,7 @@
         <v>1</v>
       </c>
       <c r="J136" s="4">
-        <f>MAX(MIN((J135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((J135-$G$16)/$G$17, 1), 0)</f>
         <v>1</v>
       </c>
       <c r="L136" s="4">
@@ -11988,7 +11999,7 @@
         <v>1</v>
       </c>
       <c r="M136" s="4">
-        <f>MAX(MIN((M135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((M135-$G$16)/$G$17, 1), 0)</f>
         <v>1</v>
       </c>
       <c r="O136" s="4">
@@ -11996,7 +12007,7 @@
         <v>1</v>
       </c>
       <c r="P136" s="4">
-        <f>MAX(MIN((P135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((P135-$G$16)/$G$17, 1), 0)</f>
         <v>1</v>
       </c>
       <c r="R136" s="4">
@@ -12004,7 +12015,7 @@
         <v>1</v>
       </c>
       <c r="S136" s="4">
-        <f>MAX(MIN((S135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((S135-$G$16)/$G$17, 1), 0)</f>
         <v>1</v>
       </c>
       <c r="U136" s="4">
@@ -12012,7 +12023,7 @@
         <v>1</v>
       </c>
       <c r="V136" s="4">
-        <f>MAX(MIN((V135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((V135-$G$16)/$G$17, 1), 0)</f>
         <v>1</v>
       </c>
       <c r="X136" s="4">
@@ -12020,7 +12031,7 @@
         <v>1</v>
       </c>
       <c r="Y136" s="4">
-        <f>MAX(MIN((Y135-$F$16)/$F$17, 1), 0)</f>
+        <f>MAX(MIN((Y135-$G$16)/$G$17, 1), 0)</f>
         <v>0.629745598162741</v>
       </c>
       <c r="Z136" s="38"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB018337-E483-704D-B091-748AC3E41FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD09B239-9DD4-0540-ADDC-8B25C9444167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="760" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="620" yWindow="500" windowWidth="37780" windowHeight="19040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7436,7 +7436,7 @@
         <v>173</v>
       </c>
       <c r="F20" s="4">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="G20" s="4">
         <v>0.25</v>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="F119" s="4">
         <f>F111*$F$20</f>
-        <v>450000</v>
+        <v>315000</v>
       </c>
       <c r="G119" s="4">
         <f>G111*$G$20</f>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="I119" s="4">
         <f>I111*$F$20</f>
-        <v>426426.94265947182</v>
+        <v>298498.85986163025</v>
       </c>
       <c r="J119" s="4">
         <f>J111*$G$20</f>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="L119" s="4">
         <f>L111*$F$20</f>
-        <v>401729.40564975084</v>
+        <v>281210.58395482559</v>
       </c>
       <c r="M119" s="4">
         <f>M111*$G$20</f>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="O119" s="4">
         <f>O111*$F$20</f>
-        <v>378689.78824255464</v>
+        <v>265082.85176978825</v>
       </c>
       <c r="P119" s="4">
         <f>P111*$G$20</f>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="R119" s="4">
         <f>R111*$F$20</f>
-        <v>356485.31955472904</v>
+        <v>249539.7236883103</v>
       </c>
       <c r="S119" s="4">
         <f>S111*$G$20</f>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="U119" s="4">
         <f>U111*$F$20</f>
-        <v>329374.48540307593</v>
+        <v>230562.13978215316</v>
       </c>
       <c r="V119" s="4">
         <f>V111*$G$20</f>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="X119" s="4">
         <f>X111*$F$20</f>
-        <v>245972.17525771659</v>
+        <v>172180.5226804016</v>
       </c>
       <c r="Y119" s="4">
         <f>Y111*$G$20</f>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F144" s="4">
         <f>F132*$F20</f>
-        <v>21365.788918364884</v>
+        <v>14956.05224285542</v>
       </c>
       <c r="G144" s="4">
         <f>(G132+F131)*$G20</f>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="I144" s="4">
         <f>I132*$F20</f>
-        <v>22127.038759307754</v>
+        <v>15488.927131515427</v>
       </c>
       <c r="J144" s="4">
         <f>(J132+I131)*$G20</f>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="L144" s="4">
         <f>L132*$F20</f>
-        <v>20810.770497264373</v>
+        <v>14567.539348085062</v>
       </c>
       <c r="M144" s="4">
         <f>(M132+L131)*$G20</f>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="O144" s="4">
         <f>O132*$F20</f>
-        <v>19673.557629791878</v>
+        <v>13771.490340854314</v>
       </c>
       <c r="P144" s="4">
         <f>(P132+O131)*$G20</f>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="R144" s="4">
         <f>R132*$F20</f>
-        <v>23669.393807170058</v>
+        <v>16568.575665019041</v>
       </c>
       <c r="S144" s="4">
         <f>(S132+R131)*$G20</f>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="U144" s="4">
         <f>U132*$F20</f>
-        <v>80430.204256942568</v>
+        <v>56301.142979859804</v>
       </c>
       <c r="V144" s="4">
         <f>(V132+U131)*$G20</f>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="X144" s="4">
         <f>X132*$F20</f>
-        <v>58137.087243617476</v>
+        <v>40695.961070532234</v>
       </c>
       <c r="Y144" s="4">
         <f>(Y132+X131)*$G20</f>
@@ -12508,60 +12508,60 @@
         <v>167</v>
       </c>
       <c r="F146" s="4">
-        <f>F120*$F20</f>
+        <f>(F120 - F121)*$F20</f>
+        <v>1522.5</v>
+      </c>
+      <c r="G146" s="4">
+        <f>(G120-G121+G53)*$G20</f>
         <v>2250</v>
       </c>
-      <c r="G146" s="4">
-        <f>(G120+G53)*$G20</f>
-        <v>2500</v>
-      </c>
       <c r="I146" s="4">
-        <f>I120*$F20</f>
-        <v>2657.1327080288697</v>
+        <f>(I120 - I121)*$F20</f>
+        <v>1793.5908956202086</v>
       </c>
       <c r="J146" s="4">
-        <f>(J120+J53)*$G20</f>
-        <v>2559.2229710466122</v>
+        <f>(J120-J121+J53)*$G20</f>
+        <v>2289.7229710466122</v>
       </c>
       <c r="L146" s="4">
-        <f>L120*$F20</f>
-        <v>2356.4224845960307</v>
+        <f>(L120 - L121)*$F20</f>
+        <v>1586.1597392172214</v>
       </c>
       <c r="M146" s="4">
-        <f>(M120+M53)*$G20</f>
-        <v>2019.8305166694299</v>
+        <f>(M120-M121+M53)*$G20</f>
+        <v>1789.53051666943</v>
       </c>
       <c r="O146" s="4">
-        <f>O120*$F20</f>
-        <v>2696.6719406896059</v>
+        <f>(O120 - O121)*$F20</f>
+        <v>1818.580358482724</v>
       </c>
       <c r="P146" s="4">
-        <f>(P120+P53)*$G20</f>
-        <v>3772.0021262214559</v>
+        <f>(P120-P121+P53)*$G20</f>
+        <v>3296.8021262214561</v>
       </c>
       <c r="R146" s="4">
-        <f>R120*$F20</f>
-        <v>3652.513520027961</v>
+        <f>(R120 - R121)*$F20</f>
+        <v>2447.5594640195727</v>
       </c>
       <c r="S146" s="4">
-        <f>(S120+S53)*$G20</f>
-        <v>690.59087551194818</v>
+        <f>(S120-S121+S53)*$G20</f>
+        <v>592.11587551194816</v>
       </c>
       <c r="U146" s="4">
-        <f>U120*$F20</f>
-        <v>3341.4802866978721</v>
+        <f>(U120 - U121)*$F20</f>
+        <v>2254.6582006885105</v>
       </c>
       <c r="V146" s="4">
-        <f>(V120+V53)*$G20</f>
-        <v>1573.9866837396262</v>
+        <f>(V120-V121+V53)*$G20</f>
+        <v>1285.2366837396262</v>
       </c>
       <c r="X146" s="4">
-        <f>X120*$F20</f>
-        <v>2520.9446951742548</v>
+        <f>(X120 - X121)*$F20</f>
+        <v>1659.7032866219784</v>
       </c>
       <c r="Y146" s="4">
-        <f>(Y120+Y53)*$G20</f>
-        <v>370.68429448745542</v>
+        <f>(Y120-Y121+Y53)*$G20</f>
+        <v>109.68429448745542</v>
       </c>
       <c r="Z146" s="38"/>
     </row>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD09B239-9DD4-0540-ADDC-8B25C9444167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A80088C-E4B0-914A-82C9-BC19D659508B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="620" yWindow="500" windowWidth="37780" windowHeight="19040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="6860" yWindow="760" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A80088C-E4B0-914A-82C9-BC19D659508B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F350A9A-DF78-DF44-80EF-AAEC8D1A81A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6860" yWindow="760" windowWidth="33680" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="220" yWindow="760" windowWidth="23640" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="302">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -947,6 +947,9 @@
   </si>
   <si>
     <t>rrr</t>
+  </si>
+  <si>
+    <t>arr_biomass_c_average_bg_stock_in_conversion_targets</t>
   </si>
 </sst>
 </file>
@@ -6392,7 +6395,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F0562-A765-A442-B9DB-CF71D123E451}">
-  <dimension ref="A1:AN159"/>
+  <dimension ref="A1:AN160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="24" customWidth="1"/>
@@ -7038,31 +7041,31 @@
         <v>113</v>
       </c>
       <c r="G11" s="4">
-        <f>MAX(G10-G25,0)</f>
+        <f>MAX(G10-G26,0)</f>
         <v>0</v>
       </c>
       <c r="J11" s="4">
-        <f>MAX(J10-J25,0)</f>
+        <f>MAX(J10-J26,0)</f>
         <v>0</v>
       </c>
       <c r="M11" s="4">
-        <f>MAX(M10-M25,0)</f>
+        <f>MAX(M10-M26,0)</f>
         <v>0</v>
       </c>
       <c r="P11" s="4">
-        <f>MAX(P10-P25,0)</f>
+        <f>MAX(P10-P26,0)</f>
         <v>0</v>
       </c>
       <c r="S11" s="4">
-        <f>MAX(S10-S25,0)</f>
+        <f>MAX(S10-S26,0)</f>
         <v>0</v>
       </c>
       <c r="V11" s="4">
-        <f>MAX(V10-V25,0)</f>
+        <f>MAX(V10-V26,0)</f>
         <v>0</v>
       </c>
       <c r="Y11" s="4">
-        <f>MAX(Y10-Y25,0)</f>
+        <f>MAX(Y10-Y26,0)</f>
         <v>0</v>
       </c>
       <c r="Z11" s="38" t="s">
@@ -7304,122 +7307,158 @@
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
     </row>
-    <row r="16" spans="1:40" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="F16" s="4">
+        <f>F15*0.187</f>
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="G16" s="4">
+        <f>G15*0.192</f>
+        <v>1.92</v>
+      </c>
+      <c r="I16" s="4">
+        <f>I15*0.187</f>
+        <v>0.95369999999999988</v>
+      </c>
+      <c r="J16" s="4">
+        <f>J15*0.192</f>
+        <v>1.8816000000000002</v>
+      </c>
+      <c r="L16" s="4">
+        <f>L15*0.187</f>
+        <v>0.97240000000000004</v>
+      </c>
+      <c r="M16" s="4">
+        <f>M15*0.192</f>
+        <v>1.8816000000000002</v>
+      </c>
+      <c r="O16" s="4">
+        <f>O15*0.187</f>
+        <v>0.87890000000000001</v>
+      </c>
+      <c r="P16" s="4">
+        <f>P15*0.192</f>
+        <v>1.9008</v>
+      </c>
+      <c r="R16" s="4">
+        <f>R15*0.187</f>
+        <v>0.97240000000000004</v>
+      </c>
+      <c r="S16" s="4">
+        <f>S15*0.192</f>
+        <v>1.9392</v>
+      </c>
+      <c r="U16" s="4">
+        <f>U15*0.187</f>
+        <v>0.76669999999999994</v>
+      </c>
+      <c r="V16" s="4">
+        <f>V15*0.192</f>
+        <v>2.1120000000000001</v>
+      </c>
+      <c r="X16" s="4">
+        <f>X15*0.187</f>
+        <v>0.95369999999999988</v>
+      </c>
+      <c r="Y16" s="4">
+        <f>Y15*0.192</f>
+        <v>1.728</v>
+      </c>
+      <c r="Z16" s="38"/>
+      <c r="AD16" s="19"/>
+      <c r="AE16" s="19"/>
+      <c r="AF16" s="19"/>
+    </row>
+    <row r="17" spans="1:32" ht="51" x14ac:dyDescent="0.2">
+      <c r="A17" s="38" t="s">
         <v>226</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="G16" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="Z16" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="AD16" s="19">
-        <v>1.8</v>
-      </c>
-      <c r="AE16" s="19">
-        <f>SUM(AD$6:AD16)</f>
-        <v>3.34</v>
-      </c>
-      <c r="AF16" s="19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="38" t="s">
-        <v>227</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="49" t="s">
-        <v>118</v>
-      </c>
       <c r="E17" s="10" t="s">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="F17" s="4">
-        <v>0.2</v>
+        <v>0.33057704999999998</v>
       </c>
       <c r="G17" s="4">
-        <v>0.2</v>
+        <v>0.37800893000000002</v>
       </c>
       <c r="Z17" s="38" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AD17" s="19">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" s="19">
         <f>SUM(AD$6:AD17)</f>
-        <v>6.34</v>
+        <v>3.34</v>
       </c>
       <c r="AF17" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="51" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="49"/>
+      <c r="D18" s="49" t="s">
+        <v>118</v>
+      </c>
       <c r="E18" s="10" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="F18" s="4">
-        <v>0.67</v>
-      </c>
-      <c r="Z18" s="40" t="s">
-        <v>295</v>
+        <v>0.43057705000000002</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.47800893</v>
+      </c>
+      <c r="Z18" s="38" t="s">
+        <v>294</v>
       </c>
       <c r="AD18" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE18" s="19">
         <f>SUM(AD$6:AD18)</f>
-        <v>12.34</v>
+        <v>6.34</v>
       </c>
       <c r="AF18" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>162</v>
       </c>
+      <c r="D19" s="49"/>
       <c r="E19" s="10" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F19" s="4">
-        <v>150</v>
-      </c>
-      <c r="G19" s="4">
-        <v>100</v>
-      </c>
-      <c r="Z19" s="38" t="s">
-        <v>297</v>
+        <v>0.67</v>
+      </c>
+      <c r="Z19" s="40" t="s">
+        <v>295</v>
       </c>
       <c r="AD19" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19" s="19">
         <f>SUM(AD$6:AD19)</f>
-        <v>22.34</v>
+        <v>12.34</v>
       </c>
       <c r="AF19" s="19">
         <v>20</v>
@@ -7427,160 +7466,126 @@
     </row>
     <row r="20" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="F20" s="4">
-        <v>0.21</v>
+        <v>150</v>
       </c>
       <c r="G20" s="4">
-        <v>0.25</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="19"/>
+        <v>297</v>
+      </c>
+      <c r="AD20" s="19">
+        <v>10</v>
+      </c>
+      <c r="AE20" s="19">
+        <f>SUM(AD$6:AD20)</f>
+        <v>22.34</v>
+      </c>
+      <c r="AF20" s="19">
+        <v>20</v>
+      </c>
     </row>
     <row r="21" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>174</v>
+        <v>232</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>162</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="F21" s="4">
-        <f>F$19*$F$16</f>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="G21" s="4">
-        <f>G$19*$G$16</f>
-        <v>0.1</v>
-      </c>
-      <c r="Z21" s="38"/>
-      <c r="AD21" s="19">
-        <v>12</v>
-      </c>
-      <c r="AE21" s="19">
-        <f>SUM(AD$6:AD21)</f>
-        <v>34.340000000000003</v>
-      </c>
-      <c r="AF21" s="19">
-        <v>20</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="Z21" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD21" s="19"/>
+      <c r="AE21" s="19"/>
+      <c r="AF21" s="19"/>
     </row>
     <row r="22" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="38" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="B22" s="32" t="s">
         <v>174</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="F22" s="4">
-        <f>F19-F21</f>
-        <v>149.85</v>
+        <f>F$20*$F$17</f>
+        <v>49.586557499999998</v>
       </c>
       <c r="G22" s="4">
-        <f>G19-G21</f>
-        <v>99.9</v>
-      </c>
-      <c r="Z22" s="38" t="s">
-        <v>299</v>
-      </c>
+        <f>G$20*$G$17</f>
+        <v>37.800893000000002</v>
+      </c>
+      <c r="Z22" s="38"/>
       <c r="AD22" s="19">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE22" s="19">
         <f>SUM(AD$6:AD22)</f>
-        <v>47.84</v>
+        <v>34.340000000000003</v>
       </c>
       <c r="AF22" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="4">
+        <f>F20-F22</f>
+        <v>100.4134425</v>
+      </c>
+      <c r="G23" s="4">
+        <f>G20-G22</f>
+        <v>62.199106999999998</v>
+      </c>
+      <c r="Z23" s="38" t="s">
+        <v>299</v>
+      </c>
       <c r="AD23" s="19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" s="19">
         <f>SUM(AD$6:AD23)</f>
-        <v>59.84</v>
+        <v>47.84</v>
       </c>
       <c r="AF23" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="4">
-        <v>5000</v>
-      </c>
-      <c r="G24" s="4">
-        <v>50000</v>
-      </c>
-      <c r="I24" s="4">
-        <v>5000</v>
-      </c>
-      <c r="J24" s="4">
-        <v>50000</v>
-      </c>
-      <c r="L24" s="4">
-        <v>5500</v>
-      </c>
-      <c r="M24" s="4">
-        <v>50000</v>
-      </c>
-      <c r="O24" s="4">
-        <v>6000</v>
-      </c>
-      <c r="P24" s="4">
-        <v>50000</v>
-      </c>
-      <c r="R24" s="4">
-        <v>6500</v>
-      </c>
-      <c r="S24" s="4">
-        <v>49000</v>
-      </c>
-      <c r="U24" s="4">
-        <v>7200</v>
-      </c>
-      <c r="V24" s="4">
-        <v>49500</v>
-      </c>
-      <c r="X24" s="4">
-        <v>7200</v>
-      </c>
-      <c r="Y24" s="4">
-        <v>49500</v>
-      </c>
-      <c r="Z24" s="38"/>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="AD24" s="19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE24" s="19">
         <f>SUM(AD$6:AD24)</f>
-        <v>69.84</v>
+        <v>59.84</v>
       </c>
       <c r="AF24" s="19">
         <v>20</v>
@@ -7588,49 +7593,63 @@
     </row>
     <row r="25" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>108</v>
+        <v>159</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="4">
+        <v>5000</v>
       </c>
       <c r="G25" s="4">
-        <f>MAX(G$24-G$13, 0)</f>
-        <v>0</v>
+        <v>50000</v>
+      </c>
+      <c r="I25" s="4">
+        <v>5000</v>
       </c>
       <c r="J25" s="4">
-        <f>MAX(J$24-J$13, 0)</f>
-        <v>0</v>
+        <v>50000</v>
+      </c>
+      <c r="L25" s="4">
+        <v>5500</v>
       </c>
       <c r="M25" s="4">
-        <f>MAX(M$24-M$13, 0)</f>
-        <v>0</v>
+        <v>50000</v>
+      </c>
+      <c r="O25" s="4">
+        <v>6000</v>
       </c>
       <c r="P25" s="4">
-        <f>MAX(P$24-P$13, 0)</f>
-        <v>0</v>
+        <v>50000</v>
+      </c>
+      <c r="R25" s="4">
+        <v>6500</v>
       </c>
       <c r="S25" s="4">
-        <f>MAX(S$24-S$13, 0)</f>
-        <v>0</v>
+        <v>49000</v>
+      </c>
+      <c r="U25" s="4">
+        <v>7200</v>
       </c>
       <c r="V25" s="4">
-        <f>MAX(V$24-V$13, 0)</f>
-        <v>0</v>
+        <v>49500</v>
+      </c>
+      <c r="X25" s="4">
+        <v>7200</v>
       </c>
       <c r="Y25" s="4">
-        <f>MAX(Y$24-Y$13, 0)</f>
-        <v>0</v>
+        <v>49500</v>
       </c>
       <c r="Z25" s="38"/>
       <c r="AD25" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE25" s="19">
         <f>SUM(AD$6:AD25)</f>
-        <v>75.84</v>
+        <v>69.84</v>
       </c>
       <c r="AF25" s="19">
         <v>20</v>
@@ -7638,406 +7657,374 @@
     </row>
     <row r="26" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="38" t="s">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="F26" s="4">
-        <f>MIN(F13,F24)</f>
-        <v>5000</v>
+        <v>108</v>
       </c>
       <c r="G26" s="4">
-        <f>MIN(G13,G24)</f>
-        <v>50000</v>
-      </c>
-      <c r="I26" s="4">
-        <f>MIN(I13,I24)</f>
-        <v>5000</v>
+        <f>MAX(G$25-G$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="J26" s="4">
-        <f>MIN(J13,J24)</f>
-        <v>50000</v>
-      </c>
-      <c r="L26" s="4">
-        <f>MIN(L13,L24)</f>
-        <v>5500</v>
+        <f>MAX(J$25-J$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="M26" s="4">
-        <f>MIN(M13,M24)</f>
-        <v>50000</v>
-      </c>
-      <c r="O26" s="4">
-        <f>MIN(O13,O24)</f>
-        <v>6000</v>
+        <f>MAX(M$25-M$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="P26" s="4">
-        <f>MIN(P13,P24)</f>
-        <v>50000</v>
-      </c>
-      <c r="R26" s="4">
-        <f>MIN(R13,R24)</f>
-        <v>6500</v>
+        <f>MAX(P$25-P$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="S26" s="4">
-        <f>MIN(S13,S24)</f>
-        <v>49000</v>
-      </c>
-      <c r="U26" s="4">
-        <f>MIN(U13,U24)</f>
-        <v>7200</v>
+        <f>MAX(S$25-S$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="V26" s="4">
-        <f>MIN(V13,V24)</f>
-        <v>49500</v>
-      </c>
-      <c r="X26" s="4">
-        <f>MIN(X13,X24)</f>
-        <v>7200</v>
+        <f>MAX(V$25-V$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="Y26" s="4">
-        <f>MIN(Y13,Y24)</f>
-        <v>49500</v>
+        <f>MAX(Y$25-Y$13, 0)</f>
+        <v>0</v>
       </c>
       <c r="Z26" s="38"/>
       <c r="AD26" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE26" s="19">
         <f>SUM(AD$6:AD26)</f>
-        <v>78.84</v>
+        <v>75.84</v>
       </c>
       <c r="AF26" s="19">
         <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="E27" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
+      <c r="A27" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="4">
+        <f>MIN(F13,F25)</f>
+        <v>5000</v>
+      </c>
+      <c r="G27" s="4">
+        <f>MIN(G13,G25)</f>
+        <v>50000</v>
+      </c>
+      <c r="I27" s="4">
+        <f>MIN(I13,I25)</f>
+        <v>5000</v>
+      </c>
+      <c r="J27" s="4">
+        <f>MIN(J13,J25)</f>
+        <v>50000</v>
+      </c>
+      <c r="L27" s="4">
+        <f>MIN(L13,L25)</f>
+        <v>5500</v>
+      </c>
+      <c r="M27" s="4">
+        <f>MIN(M13,M25)</f>
+        <v>50000</v>
+      </c>
+      <c r="O27" s="4">
+        <f>MIN(O13,O25)</f>
+        <v>6000</v>
+      </c>
+      <c r="P27" s="4">
+        <f>MIN(P13,P25)</f>
+        <v>50000</v>
+      </c>
+      <c r="R27" s="4">
+        <f>MIN(R13,R25)</f>
+        <v>6500</v>
+      </c>
+      <c r="S27" s="4">
+        <f>MIN(S13,S25)</f>
+        <v>49000</v>
+      </c>
+      <c r="U27" s="4">
+        <f>MIN(U13,U25)</f>
+        <v>7200</v>
+      </c>
+      <c r="V27" s="4">
+        <f>MIN(V13,V25)</f>
+        <v>49500</v>
+      </c>
+      <c r="X27" s="4">
+        <f>MIN(X13,X25)</f>
+        <v>7200</v>
+      </c>
+      <c r="Y27" s="4">
+        <f>MIN(Y13,Y25)</f>
+        <v>49500</v>
+      </c>
+      <c r="Z27" s="38"/>
       <c r="AD27" s="19">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AE27" s="19">
         <f>SUM(AD$6:AD27)</f>
-        <v>80.64</v>
+        <v>78.84</v>
       </c>
       <c r="AF27" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="G28" s="4">
-        <v>0.92</v>
-      </c>
-      <c r="Z28" s="38"/>
+    <row r="28" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="E28" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
+      <c r="AD28" s="19">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" s="19">
+        <f>SUM(AD$6:AD28)</f>
+        <v>80.64</v>
+      </c>
+      <c r="AF28" s="19">
+        <v>20</v>
+      </c>
     </row>
     <row r="29" spans="1:32" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0.92</v>
+      </c>
+      <c r="Z29" s="38"/>
+    </row>
+    <row r="30" spans="1:32" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B30" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="25" t="s">
+      <c r="D30" s="49"/>
+      <c r="E30" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="F29" s="4">
-        <f>F28/F19</f>
+      <c r="F30" s="4">
+        <f>0.01327547</f>
+        <v>1.3275469999999999E-2</v>
+      </c>
+      <c r="G30" s="4">
+        <f>F30</f>
+        <v>1.3275469999999999E-2</v>
+      </c>
+      <c r="I30" s="4">
+        <f>F29/F20</f>
         <v>2E-3</v>
       </c>
-      <c r="G29" s="4">
-        <f>F29</f>
-        <v>2E-3</v>
-      </c>
-      <c r="Z29" s="38"/>
-    </row>
-    <row r="30" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D30" s="26"/>
-    </row>
-    <row r="31" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="E31" s="15" t="s">
+      <c r="Z30" s="38"/>
+    </row>
+    <row r="31" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="26"/>
+    </row>
+    <row r="32" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="E32" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="8"/>
-    </row>
-    <row r="32" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="38" t="s">
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="U32" s="8"/>
+      <c r="V32" s="8"/>
+      <c r="X32" s="8"/>
+      <c r="Y32" s="8"/>
+    </row>
+    <row r="33" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B33" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E33" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F33" s="4">
         <v>2000000</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I33" s="4">
         <v>2050000</v>
       </c>
-      <c r="L32" s="4">
+      <c r="L33" s="4">
         <v>2110000</v>
       </c>
-      <c r="O32" s="4">
+      <c r="O33" s="4">
         <v>2210000</v>
       </c>
-      <c r="R32" s="4">
+      <c r="R33" s="4">
         <v>3000000</v>
       </c>
-      <c r="U32" s="4">
+      <c r="U33" s="4">
         <v>25000000</v>
       </c>
-      <c r="X32" s="4">
+      <c r="X33" s="4">
         <v>2520000</v>
       </c>
-      <c r="Z32" s="38"/>
-    </row>
-    <row r="34" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="E34" s="11" t="s">
+      <c r="Z33" s="38"/>
+    </row>
+    <row r="35" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="E35" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="U34" s="12"/>
-      <c r="V34" s="12"/>
-      <c r="X34" s="12"/>
-      <c r="Y34" s="12"/>
-    </row>
-    <row r="35" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="E35" s="15" t="s">
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="12"/>
+    </row>
+    <row r="36" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="E36" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F36" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G35" s="8"/>
-      <c r="I35" s="4" t="s">
+      <c r="G36" s="8"/>
+      <c r="I36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="N35" s="5" t="s">
+      <c r="N36" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="O35" s="4" t="s">
+      <c r="O36" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E37" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G36" s="4">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5">
-        <f>SUM(J$36:J36)</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="4">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5">
-        <f>SUM(M$36:M36)</f>
-        <v>0</v>
-      </c>
-      <c r="M36" s="4">
-        <v>0</v>
-      </c>
-      <c r="N36" s="5">
-        <f>SUM(P$36:P36)</f>
-        <v>0</v>
-      </c>
-      <c r="P36" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5">
-        <f>SUM(S$36:S36)</f>
-        <v>0</v>
-      </c>
-      <c r="S36" s="4">
-        <v>0</v>
-      </c>
-      <c r="T36" s="5">
-        <f>SUM(V$36:V36)</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="4">
-        <v>0</v>
-      </c>
-      <c r="W36" s="5">
-        <f>SUM(Y$36:Y36)</f>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="46" t="s">
+      <c r="G37" s="4">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5">
+        <f>SUM(J$37:J37)</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <f>SUM(M$37:M37)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5">
+        <f>SUM(P$37:P37)</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5">
+        <f>SUM(S$37:S37)</f>
+        <v>0</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5">
+        <f>SUM(V$37:V37)</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="4">
+        <v>0</v>
+      </c>
+      <c r="W37" s="5">
+        <f>SUM(Y$37:Y37)</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="47" t="s">
+      <c r="B38" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E38" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="F37" s="4">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4">
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
         <f>G12</f>
         <v>85</v>
       </c>
-      <c r="H37" s="5">
-        <f>SUM(G$36:G37)</f>
-        <v>85</v>
-      </c>
-      <c r="I37" s="4">
-        <f>IF(H37&gt;=J$11, IF(H36&lt;J$11, J$11-H36, 0),G37)</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="4">
-        <f>G37-I37</f>
-        <v>85</v>
-      </c>
-      <c r="K37" s="5">
-        <f>SUM(J$36:J37)</f>
-        <v>85</v>
-      </c>
-      <c r="L37" s="4">
-        <f>IF(K37&gt;=M$11, IF(K36&lt;M$11, M$11-K36, 0),J37)</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="4">
-        <f>J37-L37</f>
-        <v>85</v>
-      </c>
-      <c r="N37" s="5">
-        <f>SUM(M$36:M37)</f>
-        <v>85</v>
-      </c>
-      <c r="O37" s="4">
-        <f>IF(N37&gt;=P$11, IF(N36&lt;P$11, P$11-N36, 0),M37)</f>
-        <v>0</v>
-      </c>
-      <c r="P37" s="4">
-        <f>M37-O37</f>
-        <v>85</v>
-      </c>
-      <c r="Q37" s="5">
-        <f>SUM(P$36:P37)</f>
-        <v>85</v>
-      </c>
-      <c r="R37" s="4">
-        <f>IF(Q37&gt;=S$11, IF(Q36&lt;S$11, S$11-Q36, 0),P37)</f>
-        <v>0</v>
-      </c>
-      <c r="S37" s="4">
-        <f>P37-R37</f>
-        <v>85</v>
-      </c>
-      <c r="T37" s="5">
-        <f>SUM(S$36:S37)</f>
-        <v>85</v>
-      </c>
-      <c r="U37" s="4">
-        <f>IF(T37&gt;=V$11, IF(T36&lt;V$11, V$11-T36, 0),S37)</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="4">
-        <f>S37-U37</f>
-        <v>85</v>
-      </c>
-      <c r="W37" s="5">
-        <f>SUM(V$36:V37)</f>
-        <v>85</v>
-      </c>
-      <c r="X37" s="4">
-        <f>IF(W37&gt;=Y$11, IF(W36&lt;Y$11, Y$11-W36, 0),V37)</f>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="4">
-        <f>V37-X37</f>
-        <v>85</v>
-      </c>
-      <c r="Z37" s="37"/>
-    </row>
-    <row r="38" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="48"/>
-      <c r="B38" s="47"/>
-      <c r="E38" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4">
-        <v>0</v>
-      </c>
       <c r="H38" s="5">
-        <f>SUM(G$36:G38)</f>
+        <f>SUM(G$37:G38)</f>
         <v>85</v>
       </c>
       <c r="I38" s="4">
@@ -8045,12 +8032,12 @@
         <v>0</v>
       </c>
       <c r="J38" s="4">
-        <f>J12</f>
-        <v>80</v>
+        <f>G38-I38</f>
+        <v>85</v>
       </c>
       <c r="K38" s="5">
-        <f>SUM(J$36:J38)</f>
-        <v>165</v>
+        <f>SUM(J$37:J38)</f>
+        <v>85</v>
       </c>
       <c r="L38" s="4">
         <f>IF(K38&gt;=M$11, IF(K37&lt;M$11, M$11-K37, 0),J38)</f>
@@ -8058,63 +8045,63 @@
       </c>
       <c r="M38" s="4">
         <f>J38-L38</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N38" s="5">
-        <f>SUM(M$36:M38)</f>
-        <v>165</v>
+        <f>SUM(M$37:M38)</f>
+        <v>85</v>
       </c>
       <c r="O38" s="4">
-        <f t="shared" ref="O38:O40" si="0">IF(N38&gt;=P$11, IF(N37&lt;P$11, P$11-N37, 0),M38)</f>
+        <f>IF(N38&gt;=P$11, IF(N37&lt;P$11, P$11-N37, 0),M38)</f>
         <v>0</v>
       </c>
       <c r="P38" s="4">
         <f>M38-O38</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q38" s="5">
-        <f>SUM(P$36:P38)</f>
-        <v>165</v>
+        <f>SUM(P$37:P38)</f>
+        <v>85</v>
       </c>
       <c r="R38" s="4">
-        <f t="shared" ref="R38:R40" si="1">IF(Q38&gt;=S$11, IF(Q37&lt;S$11, S$11-Q37, 0),P38)</f>
+        <f>IF(Q38&gt;=S$11, IF(Q37&lt;S$11, S$11-Q37, 0),P38)</f>
         <v>0</v>
       </c>
       <c r="S38" s="4">
         <f>P38-R38</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="T38" s="5">
-        <f>SUM(S$36:S38)</f>
-        <v>165</v>
+        <f>SUM(S$37:S38)</f>
+        <v>85</v>
       </c>
       <c r="U38" s="4">
-        <f t="shared" ref="U38:U40" si="2">IF(T38&gt;=V$11, IF(T37&lt;V$11, V$11-T37, 0),S38)</f>
+        <f>IF(T38&gt;=V$11, IF(T37&lt;V$11, V$11-T37, 0),S38)</f>
         <v>0</v>
       </c>
       <c r="V38" s="4">
         <f>S38-U38</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="W38" s="5">
-        <f>SUM(V$36:V38)</f>
-        <v>165</v>
+        <f>SUM(V$37:V38)</f>
+        <v>85</v>
       </c>
       <c r="X38" s="4">
-        <f t="shared" ref="X38:X40" si="3">IF(W38&gt;=Y$11, IF(W37&lt;Y$11, Y$11-W37, 0),V38)</f>
+        <f>IF(W38&gt;=Y$11, IF(W37&lt;Y$11, Y$11-W37, 0),V38)</f>
         <v>0</v>
       </c>
       <c r="Y38" s="4">
         <f>V38-X38</f>
-        <v>80</v>
-      </c>
-      <c r="Z38" s="38"/>
+        <v>85</v>
+      </c>
+      <c r="Z38" s="37"/>
     </row>
     <row r="39" spans="1:27" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="48"/>
       <c r="B39" s="47"/>
       <c r="E39" s="14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F39" s="4">
         <v>0</v>
@@ -8123,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="5">
-        <f>SUM(G$36:G39)</f>
+        <f>SUM(G$37:G39)</f>
         <v>85</v>
       </c>
       <c r="I39" s="4">
@@ -8131,67 +8118,68 @@
         <v>0</v>
       </c>
       <c r="J39" s="4">
-        <v>0</v>
+        <f>J12</f>
+        <v>80</v>
       </c>
       <c r="K39" s="5">
-        <f>SUM(J$36:J39)</f>
+        <f>SUM(J$37:J39)</f>
         <v>165</v>
       </c>
       <c r="L39" s="4">
-        <f t="shared" ref="L39:L40" si="4">IF(K39&gt;=M$11, IF(K38&lt;M$11, M$11-K38, 0),J39)</f>
+        <f>IF(K39&gt;=M$11, IF(K38&lt;M$11, M$11-K38, 0),J39)</f>
         <v>0</v>
       </c>
       <c r="M39" s="4">
-        <f>M12</f>
-        <v>92</v>
+        <f>J39-L39</f>
+        <v>80</v>
       </c>
       <c r="N39" s="5">
-        <f>SUM(M$36:M39)</f>
-        <v>257</v>
+        <f>SUM(M$37:M39)</f>
+        <v>165</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="O39:O41" si="0">IF(N39&gt;=P$11, IF(N38&lt;P$11, P$11-N38, 0),M39)</f>
         <v>0</v>
       </c>
       <c r="P39" s="4">
         <f>M39-O39</f>
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="5">
-        <f>SUM(P$36:P39)</f>
-        <v>257</v>
+        <f>SUM(P$37:P39)</f>
+        <v>165</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="R39:R41" si="1">IF(Q39&gt;=S$11, IF(Q38&lt;S$11, S$11-Q38, 0),P39)</f>
         <v>0</v>
       </c>
       <c r="S39" s="4">
         <f>P39-R39</f>
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="T39" s="5">
-        <f>SUM(S$36:S39)</f>
-        <v>257</v>
+        <f>SUM(S$37:S39)</f>
+        <v>165</v>
       </c>
       <c r="U39" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="U39:U41" si="2">IF(T39&gt;=V$11, IF(T38&lt;V$11, V$11-T38, 0),S39)</f>
         <v>0</v>
       </c>
       <c r="V39" s="4">
         <f>S39-U39</f>
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="W39" s="5">
-        <f>SUM(V$36:V39)</f>
-        <v>257</v>
+        <f>SUM(V$37:V39)</f>
+        <v>165</v>
       </c>
       <c r="X39" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="X39:X41" si="3">IF(W39&gt;=Y$11, IF(W38&lt;Y$11, Y$11-W38, 0),V39)</f>
         <v>0</v>
       </c>
       <c r="Y39" s="4">
         <f>V39-X39</f>
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="Z39" s="38"/>
     </row>
@@ -8199,7 +8187,7 @@
       <c r="A40" s="48"/>
       <c r="B40" s="47"/>
       <c r="E40" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F40" s="4">
         <v>0</v>
@@ -8208,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="5">
-        <f>SUM(G$36:G40)</f>
+        <f>SUM(G$37:G40)</f>
         <v>85</v>
       </c>
       <c r="I40" s="4">
@@ -8219,18 +8207,19 @@
         <v>0</v>
       </c>
       <c r="K40" s="5">
-        <f>SUM(J$36:J40)</f>
+        <f>SUM(J$37:J40)</f>
         <v>165</v>
       </c>
       <c r="L40" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="L40:L41" si="4">IF(K40&gt;=M$11, IF(K39&lt;M$11, M$11-K39, 0),J40)</f>
         <v>0</v>
       </c>
       <c r="M40" s="4">
-        <v>0</v>
+        <f>M12</f>
+        <v>92</v>
       </c>
       <c r="N40" s="5">
-        <f>SUM(M$36:M40)</f>
+        <f>SUM(M$37:M40)</f>
         <v>257</v>
       </c>
       <c r="O40" s="4">
@@ -8238,99 +8227,148 @@
         <v>0</v>
       </c>
       <c r="P40" s="4">
+        <f>M40-O40</f>
+        <v>92</v>
+      </c>
+      <c r="Q40" s="5">
+        <f>SUM(P$37:P40)</f>
+        <v>257</v>
+      </c>
+      <c r="R40" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="4">
+        <f>P40-R40</f>
+        <v>92</v>
+      </c>
+      <c r="T40" s="5">
+        <f>SUM(S$37:S40)</f>
+        <v>257</v>
+      </c>
+      <c r="U40" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="4">
+        <f>S40-U40</f>
+        <v>92</v>
+      </c>
+      <c r="W40" s="5">
+        <f>SUM(V$37:V40)</f>
+        <v>257</v>
+      </c>
+      <c r="X40" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="4">
+        <f>V40-X40</f>
+        <v>92</v>
+      </c>
+      <c r="Z40" s="38"/>
+    </row>
+    <row r="41" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="48"/>
+      <c r="B41" s="47"/>
+      <c r="E41" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5">
+        <f>SUM(G$37:G41)</f>
+        <v>85</v>
+      </c>
+      <c r="I41" s="4">
+        <f>IF(H41&gt;=J$11, IF(H40&lt;J$11, J$11-H40, 0),G41)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5">
+        <f>SUM(J$37:J41)</f>
+        <v>165</v>
+      </c>
+      <c r="L41" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="4">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5">
+        <f>SUM(M$37:M41)</f>
+        <v>257</v>
+      </c>
+      <c r="O41" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="4">
         <f>P12</f>
         <v>43</v>
       </c>
-      <c r="Q40" s="5">
-        <f>SUM(P$36:P40)</f>
+      <c r="Q41" s="5">
+        <f>SUM(P$37:P41)</f>
         <v>300</v>
       </c>
-      <c r="R40" s="4">
+      <c r="R41" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S40" s="4">
-        <f>P40-R40</f>
+      <c r="S41" s="4">
+        <f>P41-R41</f>
         <v>43</v>
       </c>
-      <c r="T40" s="5">
-        <f>SUM(S$36:S40)</f>
+      <c r="T41" s="5">
+        <f>SUM(S$37:S41)</f>
         <v>300</v>
       </c>
-      <c r="U40" s="4">
+      <c r="U41" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V40" s="4">
-        <f>S40-U40</f>
+      <c r="V41" s="4">
+        <f>S41-U41</f>
         <v>43</v>
       </c>
-      <c r="W40" s="5">
-        <f>SUM(V$36:V40)</f>
+      <c r="W41" s="5">
+        <f>SUM(V$37:V41)</f>
         <v>300</v>
       </c>
-      <c r="X40" s="4">
+      <c r="X41" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y40" s="4">
-        <f>V40-X40</f>
+      <c r="Y41" s="4">
+        <f>V41-X41</f>
         <v>43</v>
       </c>
-      <c r="Z40" s="38"/>
-    </row>
-    <row r="41" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="E41" s="14" t="s">
+      <c r="Z41" s="38"/>
+    </row>
+    <row r="42" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="E42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AA42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="48" t="s">
+    <row r="43" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="47" t="s">
+      <c r="B43" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E43" s="14" t="s">
         <v>195</v>
-      </c>
-      <c r="G42" s="4">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4">
-        <f>IF(G37=0, 0, G95*I37/G37)</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="4">
-        <f>IF(J37=0, 0, J95*L37/J37)</f>
-        <v>0</v>
-      </c>
-      <c r="P42" s="4">
-        <f>IF(M37=0, 0, M95*O37/M37)</f>
-        <v>0</v>
-      </c>
-      <c r="S42" s="4">
-        <f>IF(P37=0, 0, P95*R37/P37)</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="4">
-        <f>IF(S37=0, 0, S95*U37/S37)</f>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="4">
-        <f>IF(V37=0, 0, V95*X37/V37)</f>
-        <v>0</v>
-      </c>
-      <c r="Z42" s="38"/>
-    </row>
-    <row r="43" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="48"/>
-      <c r="B43" s="47"/>
-      <c r="E43" s="14" t="s">
-        <v>196</v>
       </c>
       <c r="G43" s="4">
         <v>0</v>
@@ -8365,7 +8403,7 @@
       <c r="A44" s="48"/>
       <c r="B44" s="47"/>
       <c r="E44" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G44" s="4">
         <v>0</v>
@@ -8400,7 +8438,7 @@
       <c r="A45" s="48"/>
       <c r="B45" s="47"/>
       <c r="E45" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G45" s="4">
         <v>0</v>
@@ -8431,101 +8469,99 @@
       </c>
       <c r="Z45" s="38"/>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A46" s="38" t="s">
+    <row r="46" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="A46" s="48"/>
+      <c r="B46" s="47"/>
+      <c r="E46" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4">
+        <f>IF(G41=0, 0, G99*I41/G41)</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="4">
+        <f>IF(J41=0, 0, J99*L41/J41)</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="4">
+        <f>IF(M41=0, 0, M99*O41/M41)</f>
+        <v>0</v>
+      </c>
+      <c r="S46" s="4">
+        <f>IF(P41=0, 0, P99*R41/P41)</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="4">
+        <f>IF(S41=0, 0, S99*U41/S41)</f>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="4">
+        <f>IF(V41=0, 0, V99*X41/V41)</f>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="38"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A47" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B47" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E46" s="14"/>
-      <c r="G46" s="4">
-        <f>SUM(G42:G45)</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="4">
-        <f>SUM(J42:J45)</f>
-        <v>0</v>
-      </c>
-      <c r="M46" s="4">
-        <f>SUM(M42:M45)</f>
-        <v>0</v>
-      </c>
-      <c r="P46" s="4">
-        <f>SUM(P42:P45)</f>
-        <v>0</v>
-      </c>
-      <c r="S46" s="4">
-        <f>SUM(S42:S45)</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="4">
-        <f>SUM(V42:V45)</f>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="4">
-        <f>SUM(Y42:Y45)</f>
-        <v>0</v>
-      </c>
-      <c r="Z46" s="38"/>
-    </row>
-    <row r="47" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="14"/>
+      <c r="G47" s="4">
+        <f>SUM(G43:G46)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="4">
+        <f>SUM(J43:J46)</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="4">
+        <f>SUM(M43:M46)</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="4">
+        <f>SUM(P43:P46)</f>
+        <v>0</v>
+      </c>
+      <c r="S47" s="4">
+        <f>SUM(S43:S46)</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="4">
+        <f>SUM(V43:V46)</f>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="4">
+        <f>SUM(Y43:Y46)</f>
+        <v>0</v>
+      </c>
+      <c r="Z47" s="38"/>
+    </row>
+    <row r="48" spans="1:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="E48" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AA48" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="48" t="s">
+    <row r="49" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A49" s="48" t="s">
         <v>263</v>
       </c>
-      <c r="B48" s="47" t="s">
+      <c r="B49" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="D48" s="49" t="s">
+      <c r="D49" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E49" s="14" t="s">
         <v>250</v>
-      </c>
-      <c r="G48" s="4">
-        <f>MIN(G42,G$15*F37)</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="4">
-        <f>MIN(J42,J$15*I37)</f>
-        <v>0</v>
-      </c>
-      <c r="M48" s="4">
-        <f>MIN(M42,M$15*L37)</f>
-        <v>0</v>
-      </c>
-      <c r="P48" s="4">
-        <f>MIN(P42,P$15*O37)</f>
-        <v>0</v>
-      </c>
-      <c r="S48" s="4">
-        <f>MIN(S42,S$15*R37)</f>
-        <v>0</v>
-      </c>
-      <c r="V48" s="4">
-        <f>MIN(V42,V$15*U37)</f>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="4">
-        <f>MIN(Y42,Y$15*X37)</f>
-        <v>0</v>
-      </c>
-      <c r="Z48" s="38"/>
-    </row>
-    <row r="49" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="48"/>
-      <c r="B49" s="47"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="14" t="s">
-        <v>252</v>
       </c>
       <c r="G49" s="4">
         <f>MIN(G43,G$15*F38)</f>
@@ -8540,19 +8576,19 @@
         <v>0</v>
       </c>
       <c r="P49" s="4">
-        <f t="shared" ref="P49" si="5">MIN(P43,P$15*O38)</f>
+        <f>MIN(P43,P$15*O38)</f>
         <v>0</v>
       </c>
       <c r="S49" s="4">
-        <f t="shared" ref="S49" si="6">MIN(S43,S$15*R38)</f>
+        <f>MIN(S43,S$15*R38)</f>
         <v>0</v>
       </c>
       <c r="V49" s="4">
-        <f t="shared" ref="V49" si="7">MIN(V43,V$15*U38)</f>
+        <f>MIN(V43,V$15*U38)</f>
         <v>0</v>
       </c>
       <c r="Y49" s="4">
-        <f t="shared" ref="Y49" si="8">MIN(Y43,Y$15*X38)</f>
+        <f>MIN(Y43,Y$15*X38)</f>
         <v>0</v>
       </c>
       <c r="Z49" s="38"/>
@@ -8562,7 +8598,7 @@
       <c r="B50" s="47"/>
       <c r="D50" s="49"/>
       <c r="E50" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G50" s="4">
         <f>MIN(G44,G$15*F39)</f>
@@ -8577,19 +8613,19 @@
         <v>0</v>
       </c>
       <c r="P50" s="4">
-        <f>MIN(P44,P$15*O39)</f>
+        <f t="shared" ref="P50" si="5">MIN(P44,P$15*O39)</f>
         <v>0</v>
       </c>
       <c r="S50" s="4">
-        <f>MIN(S44,S$15*R39)</f>
+        <f t="shared" ref="S50" si="6">MIN(S44,S$15*R39)</f>
         <v>0</v>
       </c>
       <c r="V50" s="4">
-        <f>MIN(V44,V$15*U39)</f>
+        <f t="shared" ref="V50" si="7">MIN(V44,V$15*U39)</f>
         <v>0</v>
       </c>
       <c r="Y50" s="4">
-        <f>MIN(Y44,Y$15*X39)</f>
+        <f t="shared" ref="Y50" si="8">MIN(Y44,Y$15*X39)</f>
         <v>0</v>
       </c>
       <c r="Z50" s="38"/>
@@ -8599,7 +8635,7 @@
       <c r="B51" s="47"/>
       <c r="D51" s="49"/>
       <c r="E51" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G51" s="4">
         <f>MIN(G45,G$15*F40)</f>
@@ -8631,155 +8667,156 @@
       </c>
       <c r="Z51" s="38"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="E52" s="14"/>
+    <row r="52" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="48"/>
+      <c r="B52" s="47"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="14" t="s">
+        <v>254</v>
+      </c>
       <c r="G52" s="4">
-        <f>SUM(G48:G51)</f>
+        <f>MIN(G46,G$15*F41)</f>
         <v>0</v>
       </c>
       <c r="J52" s="4">
-        <f>SUM(J48:J51)</f>
+        <f>MIN(J46,J$15*I41)</f>
         <v>0</v>
       </c>
       <c r="M52" s="4">
-        <f>SUM(M48:M51)</f>
+        <f>MIN(M46,M$15*L41)</f>
         <v>0</v>
       </c>
       <c r="P52" s="4">
-        <f>SUM(P48:P51)</f>
+        <f>MIN(P46,P$15*O41)</f>
         <v>0</v>
       </c>
       <c r="S52" s="4">
-        <f>SUM(S48:S51)</f>
+        <f>MIN(S46,S$15*R41)</f>
         <v>0</v>
       </c>
       <c r="V52" s="4">
-        <f>SUM(V48:V51)</f>
+        <f>MIN(V46,V$15*U41)</f>
         <v>0</v>
       </c>
       <c r="Y52" s="4">
-        <f>SUM(Y48:Y51)</f>
+        <f>MIN(Y46,Y$15*X41)</f>
         <v>0</v>
       </c>
       <c r="Z52" s="38"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="B53" s="28"/>
+        <v>264</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>174</v>
+      </c>
       <c r="E53" s="14"/>
       <c r="G53" s="4">
-        <f>G46-G52</f>
+        <f>SUM(G49:G52)</f>
         <v>0</v>
       </c>
       <c r="J53" s="4">
-        <f>J46-J52</f>
+        <f>SUM(J49:J52)</f>
         <v>0</v>
       </c>
       <c r="M53" s="4">
-        <f>M46-M52</f>
+        <f>SUM(M49:M52)</f>
         <v>0</v>
       </c>
       <c r="P53" s="4">
-        <f>P46-P52</f>
+        <f>SUM(P49:P52)</f>
         <v>0</v>
       </c>
       <c r="S53" s="4">
-        <f>S46-S52</f>
+        <f>SUM(S49:S52)</f>
         <v>0</v>
       </c>
       <c r="V53" s="4">
-        <f>V46-V52</f>
+        <f>SUM(V49:V52)</f>
         <v>0</v>
       </c>
       <c r="Y53" s="4">
-        <f>Y46-Y52</f>
+        <f>SUM(Y49:Y52)</f>
         <v>0</v>
       </c>
       <c r="Z53" s="38"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A54" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="B54" s="28"/>
       <c r="E54" s="14"/>
-    </row>
-    <row r="55" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="48" t="s">
+      <c r="G54" s="4">
+        <f>G47-G53</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="4">
+        <f>J47-J53</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="4">
+        <f>M47-M53</f>
+        <v>0</v>
+      </c>
+      <c r="P54" s="4">
+        <f>P47-P53</f>
+        <v>0</v>
+      </c>
+      <c r="S54" s="4">
+        <f>S47-S53</f>
+        <v>0</v>
+      </c>
+      <c r="V54" s="4">
+        <f>V47-V53</f>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="4">
+        <f>Y47-Y53</f>
+        <v>0</v>
+      </c>
+      <c r="Z54" s="38"/>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E55" s="14"/>
+    </row>
+    <row r="56" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A56" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="47" t="s">
+      <c r="B56" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E56" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G55" s="4">
-        <f>G42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="4">
-        <f>J42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="M55" s="4">
-        <f>M42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="P55" s="4">
-        <f>P42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="S55" s="4">
-        <f>S42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="V55" s="4">
-        <f>V42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="Y55" s="4">
-        <f>Y42*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="Z55" s="38"/>
-    </row>
-    <row r="56" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A56" s="48"/>
-      <c r="B56" s="47"/>
-      <c r="E56" s="14" t="s">
-        <v>200</v>
-      </c>
       <c r="G56" s="4">
-        <f>G43*$G$20</f>
+        <f>G43*$G$21</f>
         <v>0</v>
       </c>
       <c r="J56" s="4">
-        <f>J43*$G$20</f>
+        <f>J43*$G$21</f>
         <v>0</v>
       </c>
       <c r="M56" s="4">
-        <f>M43*$G$20</f>
+        <f>M43*$G$21</f>
         <v>0</v>
       </c>
       <c r="P56" s="4">
-        <f>P43*$G$20</f>
+        <f>P43*$G$21</f>
         <v>0</v>
       </c>
       <c r="S56" s="4">
-        <f>S43*$G$20</f>
+        <f>S43*$G$21</f>
         <v>0</v>
       </c>
       <c r="V56" s="4">
-        <f>V43*$G$20</f>
+        <f>V43*$G$21</f>
         <v>0</v>
       </c>
       <c r="Y56" s="4">
-        <f>Y43*$G$20</f>
+        <f>Y43*$G$21</f>
         <v>0</v>
       </c>
       <c r="Z56" s="38"/>
@@ -8788,34 +8825,34 @@
       <c r="A57" s="48"/>
       <c r="B57" s="47"/>
       <c r="E57" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G57" s="4">
-        <f>G44*$G$20</f>
+        <f>G44*$G$21</f>
         <v>0</v>
       </c>
       <c r="J57" s="4">
-        <f>J44*$G$20</f>
+        <f>J44*$G$21</f>
         <v>0</v>
       </c>
       <c r="M57" s="4">
-        <f>M44*$G$20</f>
+        <f>M44*$G$21</f>
         <v>0</v>
       </c>
       <c r="P57" s="4">
-        <f>P44*$G$20</f>
+        <f>P44*$G$21</f>
         <v>0</v>
       </c>
       <c r="S57" s="4">
-        <f>S44*$G$20</f>
+        <f>S44*$G$21</f>
         <v>0</v>
       </c>
       <c r="V57" s="4">
-        <f>V44*$G$20</f>
+        <f>V44*$G$21</f>
         <v>0</v>
       </c>
       <c r="Y57" s="4">
-        <f>Y44*$G$20</f>
+        <f>Y44*$G$21</f>
         <v>0</v>
       </c>
       <c r="Z57" s="38"/>
@@ -8824,150 +8861,152 @@
       <c r="A58" s="48"/>
       <c r="B58" s="47"/>
       <c r="E58" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="G58" s="4">
+        <f>G45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4">
+        <f>J45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="4">
+        <f>M45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="P58" s="4">
+        <f>P45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="S58" s="4">
+        <f>S45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>V45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="Y58" s="4">
+        <f>Y45*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="Z58" s="38"/>
+    </row>
+    <row r="59" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A59" s="48"/>
+      <c r="B59" s="47"/>
+      <c r="E59" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G58" s="4">
-        <f>G45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="4">
-        <f>J45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="M58" s="4">
-        <f>M45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="P58" s="4">
-        <f>P45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="S58" s="4">
-        <f>S45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="V58" s="4">
-        <f>V45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="Y58" s="4">
-        <f>Y45*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="Z58" s="38"/>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A59" s="38" t="s">
+      <c r="G59" s="4">
+        <f>G46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="4">
+        <f>J46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="4">
+        <f>M46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="P59" s="4">
+        <f>P46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="S59" s="4">
+        <f>S46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="V59" s="4">
+        <f>V46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="4">
+        <f>Y46*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="Z59" s="38"/>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A60" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B60" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E59" s="14"/>
-      <c r="G59" s="4">
-        <f>SUM(G55:G58)</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="4">
-        <f>SUM(J55:J58)</f>
-        <v>0</v>
-      </c>
-      <c r="M59" s="4">
-        <f>SUM(M55:M58)</f>
-        <v>0</v>
-      </c>
-      <c r="P59" s="4">
-        <f>SUM(P55:P58)</f>
-        <v>0</v>
-      </c>
-      <c r="S59" s="4">
-        <f>SUM(S55:S58)</f>
-        <v>0</v>
-      </c>
-      <c r="V59" s="4">
-        <f>SUM(V55:V58)</f>
-        <v>0</v>
-      </c>
-      <c r="Y59" s="4">
-        <f>SUM(Y55:Y58)</f>
-        <v>0</v>
-      </c>
-      <c r="Z59" s="38"/>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E60" s="14"/>
-    </row>
-    <row r="61" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="48" t="s">
+      <c r="G60" s="4">
+        <f>SUM(G56:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
+        <f>SUM(J56:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="4">
+        <f>SUM(M56:M59)</f>
+        <v>0</v>
+      </c>
+      <c r="P60" s="4">
+        <f>SUM(P56:P59)</f>
+        <v>0</v>
+      </c>
+      <c r="S60" s="4">
+        <f>SUM(S56:S59)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="4">
+        <f>SUM(V56:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="4">
+        <f>SUM(Y56:Y59)</f>
+        <v>0</v>
+      </c>
+      <c r="Z60" s="38"/>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E61" s="14"/>
+    </row>
+    <row r="62" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="B61" s="47" t="s">
+      <c r="B62" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E62" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G62" s="4">
         <f>AD6</f>
         <v>0</v>
       </c>
-      <c r="J61" s="4">
+      <c r="J62" s="4">
         <f>AD7</f>
         <v>0.01</v>
       </c>
-      <c r="M61" s="4">
+      <c r="M62" s="4">
         <f>AD8</f>
         <v>0.05</v>
       </c>
-      <c r="P61" s="4">
+      <c r="P62" s="4">
         <f>AD9</f>
         <v>0.12</v>
       </c>
-      <c r="S61" s="4">
+      <c r="S62" s="4">
         <f>AD11</f>
         <v>0.2</v>
       </c>
-      <c r="V61" s="4">
+      <c r="V62" s="4">
         <f>AD12</f>
         <v>0.36</v>
       </c>
-      <c r="Y61" s="4">
+      <c r="Y62" s="4">
         <f>AD14</f>
         <v>0.6</v>
-      </c>
-      <c r="Z61" s="38"/>
-    </row>
-    <row r="62" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="48"/>
-      <c r="B62" s="47"/>
-      <c r="E62" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G62" s="4">
-        <v>0</v>
-      </c>
-      <c r="J62" s="4">
-        <v>0</v>
-      </c>
-      <c r="M62" s="4">
-        <f>AD7</f>
-        <v>0.01</v>
-      </c>
-      <c r="P62" s="4">
-        <f>AD8</f>
-        <v>0.05</v>
-      </c>
-      <c r="S62" s="4">
-        <f>AD9</f>
-        <v>0.12</v>
-      </c>
-      <c r="V62" s="4">
-        <f>AD11</f>
-        <v>0.2</v>
-      </c>
-      <c r="Y62" s="4">
-        <f>AD12</f>
-        <v>0.36</v>
       </c>
       <c r="Z62" s="38"/>
     </row>
@@ -8975,7 +9014,7 @@
       <c r="A63" s="48"/>
       <c r="B63" s="47"/>
       <c r="E63" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G63" s="4">
         <v>0</v>
@@ -8984,23 +9023,24 @@
         <v>0</v>
       </c>
       <c r="M63" s="4">
-        <v>0</v>
-      </c>
-      <c r="P63" s="4">
         <f>AD7</f>
         <v>0.01</v>
       </c>
-      <c r="S63" s="4">
+      <c r="P63" s="4">
         <f>AD8</f>
         <v>0.05</v>
       </c>
-      <c r="V63" s="4">
+      <c r="S63" s="4">
         <f>AD9</f>
         <v>0.12</v>
       </c>
-      <c r="Y63" s="4">
+      <c r="V63" s="4">
         <f>AD11</f>
         <v>0.2</v>
+      </c>
+      <c r="Y63" s="4">
+        <f>AD12</f>
+        <v>0.36</v>
       </c>
       <c r="Z63" s="38"/>
     </row>
@@ -9008,7 +9048,7 @@
       <c r="A64" s="48"/>
       <c r="B64" s="47"/>
       <c r="E64" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -9020,128 +9060,132 @@
         <v>0</v>
       </c>
       <c r="P64" s="4">
-        <v>0</v>
-      </c>
-      <c r="S64" s="4">
         <f>AD7</f>
         <v>0.01</v>
       </c>
-      <c r="V64" s="4">
+      <c r="S64" s="4">
         <f>AD8</f>
         <v>0.05</v>
       </c>
-      <c r="Y64" s="4">
+      <c r="V64" s="4">
         <f>AD9</f>
         <v>0.12</v>
       </c>
+      <c r="Y64" s="4">
+        <f>AD11</f>
+        <v>0.2</v>
+      </c>
       <c r="Z64" s="38"/>
     </row>
     <row r="65" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="A65" s="48"/>
+      <c r="B65" s="47"/>
       <c r="E65" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G65" s="4">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0</v>
+      </c>
+      <c r="M65" s="4">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4">
+        <v>0</v>
+      </c>
+      <c r="S65" s="4">
+        <f>AD7</f>
+        <v>0.01</v>
+      </c>
+      <c r="V65" s="4">
+        <f>AD8</f>
+        <v>0.05</v>
+      </c>
+      <c r="Y65" s="4">
+        <f>AD9</f>
+        <v>0.12</v>
+      </c>
+      <c r="Z65" s="38"/>
+    </row>
+    <row r="66" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="E66" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="E66" s="14"/>
-    </row>
-    <row r="67" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="48" t="s">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="E67" s="14"/>
+    </row>
+    <row r="68" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="A68" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="B67" s="47" t="s">
+      <c r="B68" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E68" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G67" s="4">
-        <f>G37*G61</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="4">
-        <f>J37*J61</f>
-        <v>0.85</v>
-      </c>
-      <c r="M67" s="4">
-        <f>J67*(1- $F$29)+M37*M61</f>
-        <v>5.0983000000000001</v>
-      </c>
-      <c r="P67" s="4">
-        <f>M67*(1- $F$29)+P37*P61</f>
-        <v>15.288103399999999</v>
-      </c>
-      <c r="S67" s="4">
-        <f>P67*(1- $F$29)+S37*S61</f>
-        <v>32.257527193199998</v>
-      </c>
-      <c r="V67" s="4">
-        <f>S67*(1- $F$29)+V37*V61</f>
-        <v>62.793012138813594</v>
-      </c>
-      <c r="Y67" s="4">
-        <f>V67*(1- $F$29)+Y37*Y61</f>
-        <v>113.66742611453597</v>
-      </c>
-      <c r="Z67" s="38"/>
-    </row>
-    <row r="68" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="48"/>
-      <c r="B68" s="47"/>
-      <c r="E68" s="14" t="s">
-        <v>110</v>
+      <c r="G68" s="4">
+        <f>G38*G62</f>
+        <v>0</v>
       </c>
       <c r="J68" s="4">
         <f>J38*J62</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M68" s="4">
-        <f>J68*(1- $F$29)+M38*M62</f>
-        <v>0.8</v>
+        <f>J68*(1- $F$30)+M38*M62</f>
+        <v>5.0887158504999999</v>
       </c>
       <c r="P68" s="4">
-        <f>M68*(1- $F$29)+P38*P62</f>
-        <v>4.7984</v>
+        <f>M68*(1- $F$30)+P38*P62</f>
+        <v>15.221160755888162</v>
       </c>
       <c r="S68" s="4">
-        <f>P68*(1- $F$29)+S38*S62</f>
-        <v>14.3888032</v>
+        <f>P68*(1- $F$30)+S38*S62</f>
+        <v>32.019092692908188</v>
       </c>
       <c r="V68" s="4">
-        <f>S68*(1- $F$29)+V38*V62</f>
-        <v>30.3600255936</v>
+        <f>S68*(1- $F$30)+V38*V62</f>
+        <v>62.194024188436266</v>
       </c>
       <c r="Y68" s="4">
-        <f>V68*(1- $F$29)+Y38*Y62</f>
-        <v>59.099305542412793</v>
+        <f>V68*(1- $F$30)+Y38*Y62</f>
+        <v>112.36836928614341</v>
       </c>
       <c r="Z68" s="38"/>
     </row>
     <row r="69" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="48"/>
       <c r="B69" s="47"/>
-      <c r="D69" s="49"/>
       <c r="E69" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="J69" s="4">
+        <f>J39*J63</f>
+        <v>0</v>
       </c>
       <c r="M69" s="4">
-        <f>J69*(1- $F$29)+M39*M63</f>
-        <v>0</v>
+        <f>J69*(1- $F$30)+M39*M63</f>
+        <v>0.8</v>
       </c>
       <c r="P69" s="4">
-        <f>M69*(1- $F$29)+P39*P63</f>
-        <v>0.92</v>
+        <f>M69*(1- $F$30)+P39*P63</f>
+        <v>4.7893796240000004</v>
       </c>
       <c r="S69" s="4">
-        <f>P69*(1- $F$29)+S39*S63</f>
-        <v>5.5181600000000008</v>
+        <f>P69*(1- $F$30)+S39*S63</f>
+        <v>14.325798358482977</v>
       </c>
       <c r="V69" s="4">
-        <f>S69*(1- $F$29)+V39*V63</f>
-        <v>16.547123679999999</v>
+        <f>S69*(1- $F$30)+V39*V63</f>
+        <v>30.13561665214889</v>
       </c>
       <c r="Y69" s="4">
-        <f>V69*(1- $F$29)+Y39*Y63</f>
-        <v>34.91402943264</v>
+        <f>V69*(1- $F$30)+Y39*Y63</f>
+        <v>58.535552177351789</v>
       </c>
       <c r="Z69" s="38"/>
     </row>
@@ -9150,399 +9194,361 @@
       <c r="B70" s="47"/>
       <c r="D70" s="49"/>
       <c r="E70" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="M70" s="4">
+        <f>J70*(1- $F$30)+M40*M64</f>
+        <v>0</v>
+      </c>
+      <c r="P70" s="4">
+        <f>M70*(1- $F$30)+P40*P64</f>
+        <v>0.92</v>
+      </c>
+      <c r="S70" s="4">
+        <f>P70*(1- $F$30)+S40*S64</f>
+        <v>5.5077865676000002</v>
+      </c>
+      <c r="V70" s="4">
+        <f>S70*(1- $F$30)+V40*V64</f>
+        <v>16.474668112255422</v>
+      </c>
+      <c r="Y70" s="4">
+        <f>V70*(1- $F$30)+Y40*Y64</f>
+        <v>34.655959149971224</v>
+      </c>
+      <c r="Z70" s="38"/>
+    </row>
+    <row r="71" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="48"/>
+      <c r="B71" s="47"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="M70" s="4">
-        <f>J70*(1- $F$29)+M40*M64</f>
-        <v>0</v>
-      </c>
-      <c r="P70" s="4">
-        <f>M70*(1- $F$29)+P40*P64</f>
-        <v>0</v>
-      </c>
-      <c r="S70" s="4">
-        <f>P70*(1- $F$29)+S40*S64</f>
+      <c r="M71" s="4">
+        <f>J71*(1- $F$30)+M41*M65</f>
+        <v>0</v>
+      </c>
+      <c r="P71" s="4">
+        <f>M71*(1- $F$30)+P41*P65</f>
+        <v>0</v>
+      </c>
+      <c r="S71" s="4">
+        <f>P71*(1- $F$30)+S41*S65</f>
         <v>0.43</v>
       </c>
-      <c r="V70" s="4">
-        <f>S70*(1- $F$29)+V40*V64</f>
-        <v>2.5791399999999998</v>
-      </c>
-      <c r="Y70" s="4">
-        <f>V70*(1- $F$29)+Y40*Y64</f>
-        <v>7.7339817200000001</v>
-      </c>
-      <c r="Z70" s="38"/>
-    </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="D71" s="49"/>
-      <c r="E71" s="14"/>
-    </row>
-    <row r="72" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A72" s="48" t="s">
+      <c r="V71" s="4">
+        <f>S71*(1- $F$30)+V41*V65</f>
+        <v>2.5742915478999997</v>
+      </c>
+      <c r="Y71" s="4">
+        <f>V71*(1- $F$30)+Y41*Y65</f>
+        <v>7.7001166176845999</v>
+      </c>
+      <c r="Z71" s="38"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="D72" s="49"/>
+      <c r="E72" s="14"/>
+    </row>
+    <row r="73" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="B72" s="47" t="s">
+      <c r="B73" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E73" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="G72" s="4">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4">
-        <f>INT(I$4-$AF$6 &gt; $D80)*MAX(G95-$G$21*G37-J42,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M72" s="4">
-        <f>INT(L$4-$AF$6 &gt; $D80)*MAX(J95-$G$21*J37-M42,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P72" s="4">
-        <f>INT(O$4-$AF$6 &gt; $D80)*MAX(M95-$G$21*M37-P42,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S72" s="4">
-        <f>INT(R$4-$AF$6 &gt; $D80)*MAX(P95-$G$21*P37-S42,0)</f>
-        <v>6.7881033999999989</v>
-      </c>
-      <c r="V72" s="4">
-        <f>INT(U$4-$AF$6 &gt; $D80)*MAX(S95-$G$21*S37-V42,0)</f>
-        <v>23.757527193199998</v>
-      </c>
-      <c r="Y72" s="4">
-        <f>INT(X$4-$AF$6 &gt; $D80)*MAX(V95-$G$21*V37-Y42,0)</f>
-        <v>30.582999999999998</v>
-      </c>
-      <c r="Z72" s="38"/>
-    </row>
-    <row r="73" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" s="48"/>
-      <c r="B73" s="47"/>
-      <c r="E73" s="14" t="s">
-        <v>128</v>
-      </c>
       <c r="G73" s="4">
         <v>0</v>
       </c>
       <c r="J73" s="4">
-        <f>INT(I$4-$AF$6 &gt; $D81)*MAX(G96-$G$21*G38-J43,0)</f>
+        <f>INT(I$4-$AF$6 &gt; $D81)*MAX(G96-$G$22*G38-J43,0)</f>
         <v>0</v>
       </c>
       <c r="M73" s="4">
-        <f>INT(L$4-$AF$6 &gt; $D81)*MAX(J96-$G$21*J38-M43,0)</f>
+        <f>INT(L$4-$AF$6 &gt; $D81)*MAX(J96-$G$22*J38-M43,0)</f>
         <v>0</v>
       </c>
       <c r="P73" s="4">
-        <f>INT(O$4-$AF$6 &gt; $D81)*MAX(M96-$G$21*M38-P43,0)</f>
+        <f>INT(O$4-$AF$6 &gt; $D81)*MAX(M96-$G$22*M38-P43,0)</f>
         <v>0</v>
       </c>
       <c r="S73" s="4">
-        <f>INT(R$4-$AF$6 &gt; $D81)*MAX(P96-$G$21*P38-S43,0)</f>
+        <f>INT(R$4-$AF$6 &gt; $D81)*MAX(P96-$G$22*P38-S43,0)</f>
         <v>0</v>
       </c>
       <c r="V73" s="4">
-        <f>INT(U$4-$AF$6 &gt; $D81)*MAX(S96-$G$21*S38-V43,0)</f>
-        <v>6.3888031999999999</v>
+        <f>INT(U$4-$AF$6 &gt; $D81)*MAX(S96-$G$22*S38-V43,0)</f>
+        <v>0</v>
       </c>
       <c r="Y73" s="4">
-        <f>INT(X$4-$AF$6 &gt; $D81)*MAX(V96-$G$21*V38-Y43,0)</f>
-        <v>15.984000000000002</v>
+        <f>INT(X$4-$AF$6 &gt; $D81)*MAX(V96-$G$22*V38-Y43,0)</f>
+        <v>0</v>
       </c>
       <c r="Z73" s="38"/>
     </row>
     <row r="74" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" s="48"/>
       <c r="B74" s="47"/>
-      <c r="D74" s="49" t="s">
-        <v>152</v>
-      </c>
       <c r="E74" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G74" s="4">
         <v>0</v>
       </c>
       <c r="J74" s="4">
-        <f>INT(I$4-$AF$6 &gt; $D82)*MAX(G97-$G$21*G39-J44,0)</f>
+        <f>INT(I$4-$AF$6 &gt; $D82)*MAX(G97-$G$22*G39-J44,0)</f>
         <v>0</v>
       </c>
       <c r="M74" s="4">
-        <f>INT(L$4-$AF$6 &gt; $D82)*MAX(J97-$G$21*J39-M44,0)</f>
+        <f>INT(L$4-$AF$6 &gt; $D82)*MAX(J97-$G$22*J39-M44,0)</f>
         <v>0</v>
       </c>
       <c r="P74" s="4">
-        <f>INT(O$4-$AF$6 &gt; $D82)*MAX(M97-$G$21*M39-P44,0)</f>
+        <f>INT(O$4-$AF$6 &gt; $D82)*MAX(M97-$G$22*M39-P44,0)</f>
         <v>0</v>
       </c>
       <c r="S74" s="4">
-        <f>INT(R$4-$AF$6 &gt; $D82)*MAX(P97-$G$21*P39-S44,0)</f>
+        <f>INT(R$4-$AF$6 &gt; $D82)*MAX(P97-$G$22*P39-S44,0)</f>
         <v>0</v>
       </c>
       <c r="V74" s="4">
-        <f>INT(U$4-$AF$6 &gt; $D82)*MAX(S97-$G$21*S39-V44,0)</f>
+        <f>INT(U$4-$AF$6 &gt; $D82)*MAX(S97-$G$22*S39-V44,0)</f>
         <v>0</v>
       </c>
       <c r="Y74" s="4">
-        <f>INT(X$4-$AF$6 &gt; $D82)*MAX(V97-$G$21*V39-Y44,0)</f>
-        <v>7.3471236799999975</v>
+        <f>INT(X$4-$AF$6 &gt; $D82)*MAX(V97-$G$22*V39-Y44,0)</f>
+        <v>0</v>
       </c>
       <c r="Z74" s="38"/>
     </row>
     <row r="75" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="48"/>
       <c r="B75" s="47"/>
-      <c r="D75" s="49"/>
+      <c r="D75" s="49" t="s">
+        <v>152</v>
+      </c>
       <c r="E75" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G75" s="4">
         <v>0</v>
       </c>
       <c r="J75" s="4">
-        <f>INT(I$4-$AF$6 &gt; $D83)*MAX(G98-$G$21*G40-J45,0)</f>
+        <f>INT(I$4-$AF$6 &gt; $D83)*MAX(G98-$G$22*G40-J45,0)</f>
         <v>0</v>
       </c>
       <c r="M75" s="4">
-        <f>INT(L$4-$AF$6 &gt; $D83)*MAX(J98-$G$21*J40-M45,0)</f>
+        <f>INT(L$4-$AF$6 &gt; $D83)*MAX(J98-$G$22*J40-M45,0)</f>
         <v>0</v>
       </c>
       <c r="P75" s="4">
-        <f>INT(O$4-$AF$6 &gt; $D83)*MAX(M98-$G$21*M40-P45,0)</f>
+        <f>INT(O$4-$AF$6 &gt; $D83)*MAX(M98-$G$22*M40-P45,0)</f>
         <v>0</v>
       </c>
       <c r="S75" s="4">
-        <f>INT(R$4-$AF$6 &gt; $D83)*MAX(P98-$G$21*P40-S45,0)</f>
+        <f>INT(R$4-$AF$6 &gt; $D83)*MAX(P98-$G$22*P40-S45,0)</f>
         <v>0</v>
       </c>
       <c r="V75" s="4">
-        <f>INT(U$4-$AF$6 &gt; $D83)*MAX(S98-$G$21*S40-V45,0)</f>
+        <f>INT(U$4-$AF$6 &gt; $D83)*MAX(S98-$G$22*S40-V45,0)</f>
         <v>0</v>
       </c>
       <c r="Y75" s="4">
-        <f>INT(X$4-$AF$6 &gt; $D83)*MAX(V98-$G$21*V40-Y45,0)</f>
+        <f>INT(X$4-$AF$6 &gt; $D83)*MAX(V98-$G$22*V40-Y45,0)</f>
         <v>0</v>
       </c>
       <c r="Z75" s="38"/>
     </row>
     <row r="76" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="B76" s="28" t="s">
-        <v>174</v>
-      </c>
+      <c r="A76" s="48"/>
+      <c r="B76" s="47"/>
       <c r="D76" s="49"/>
       <c r="E76" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G76" s="4">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4">
+        <f>INT(I$4-$AF$6 &gt; $D84)*MAX(G99-$G$22*G41-J46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="4">
+        <f>INT(L$4-$AF$6 &gt; $D84)*MAX(J99-$G$22*J41-M46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P76" s="4">
+        <f>INT(O$4-$AF$6 &gt; $D84)*MAX(M99-$G$22*M41-P46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S76" s="4">
+        <f>INT(R$4-$AF$6 &gt; $D84)*MAX(P99-$G$22*P41-S46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V76" s="4">
+        <f>INT(U$4-$AF$6 &gt; $D84)*MAX(S99-$G$22*S41-V46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y76" s="4">
+        <f>INT(X$4-$AF$6 &gt; $D84)*MAX(V99-$G$22*V41-Y46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z76" s="38"/>
+    </row>
+    <row r="77" spans="1:31" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D77" s="49"/>
+      <c r="E77" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="4">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4">
-        <f>SUM(J72:J75)</f>
-        <v>0</v>
-      </c>
-      <c r="M76" s="4">
-        <f>SUM(M72:M75)</f>
-        <v>0</v>
-      </c>
-      <c r="P76" s="4">
-        <f>SUM(P72:P75)</f>
-        <v>0</v>
-      </c>
-      <c r="S76" s="4">
-        <f>SUM(S72:S75)</f>
-        <v>6.7881033999999989</v>
-      </c>
-      <c r="V76" s="4">
-        <f>SUM(V72:V75)</f>
-        <v>30.146330393199996</v>
-      </c>
-      <c r="Y76" s="4">
-        <f>SUM(Y72:Y75)</f>
-        <v>53.914123679999996</v>
-      </c>
-      <c r="Z76" s="38"/>
-      <c r="AE76" t="s">
+      <c r="G77" s="4">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4">
+        <f>SUM(J73:J76)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="4">
+        <f>SUM(M73:M76)</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="4">
+        <f>SUM(P73:P76)</f>
+        <v>0</v>
+      </c>
+      <c r="S77" s="4">
+        <f>SUM(S73:S76)</f>
+        <v>0</v>
+      </c>
+      <c r="V77" s="4">
+        <f>SUM(V73:V76)</f>
+        <v>0</v>
+      </c>
+      <c r="Y77" s="4">
+        <f>SUM(Y73:Y76)</f>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="38"/>
+      <c r="AE77" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="D77" s="49"/>
-      <c r="E77" s="14"/>
-      <c r="AC77" t="s">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="D78" s="49"/>
+      <c r="E78" s="14"/>
+      <c r="AC78" t="s">
         <v>85</v>
       </c>
-      <c r="AE77" t="s">
+      <c r="AE78" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="50" t="s">
+    <row r="79" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="B78" s="47" t="s">
+      <c r="B79" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E79" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="I78" s="4">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4">
-        <v>0</v>
-      </c>
-      <c r="O78" s="4">
-        <v>0</v>
-      </c>
-      <c r="R78" s="4">
-        <v>0</v>
-      </c>
-      <c r="U78" s="4">
-        <v>0</v>
-      </c>
-      <c r="X78" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="39"/>
-      <c r="AC78" t="s">
+      <c r="F79" s="4">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4">
+        <v>0</v>
+      </c>
+      <c r="L79" s="4">
+        <v>0</v>
+      </c>
+      <c r="O79" s="4">
+        <v>0</v>
+      </c>
+      <c r="R79" s="4">
+        <v>0</v>
+      </c>
+      <c r="U79" s="4">
+        <v>0</v>
+      </c>
+      <c r="X79" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="39"/>
+      <c r="AC79" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="79" spans="1:31" ht="17" x14ac:dyDescent="0.2">
-      <c r="A79" s="50"/>
-      <c r="B79" s="47"/>
-      <c r="E79" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F79" s="4">
-        <f>SUM(G$72:G72)</f>
-        <v>0</v>
-      </c>
-      <c r="G79" s="4">
-        <f>IF(F79&gt;=F$131, IF(F78&lt;F$131, F$131-F78, 0),G72)</f>
-        <v>0</v>
-      </c>
-      <c r="I79" s="4">
-        <f>SUM(J$72:J72)</f>
-        <v>0</v>
-      </c>
-      <c r="J79" s="4">
-        <f>IF(I79&gt;=I$131, IF(I78&lt;I$131, I$131-I78, 0),J72)</f>
-        <v>0</v>
-      </c>
-      <c r="L79" s="4">
-        <f>SUM(M$72:M72)</f>
-        <v>0</v>
-      </c>
-      <c r="M79" s="4">
-        <f>IF(L79&gt;=L$131, IF(L78&lt;L$131, L$131-L78, 0),M72)</f>
-        <v>0</v>
-      </c>
-      <c r="O79" s="4">
-        <f>SUM(P$72:P72)</f>
-        <v>0</v>
-      </c>
-      <c r="P79" s="4">
-        <f>IF(O79&gt;=O$131, IF(O78&lt;O$131, O$131-O78, 0),P72)</f>
-        <v>0</v>
-      </c>
-      <c r="R79" s="4">
-        <f>SUM(S$72:S72)</f>
-        <v>6.7881033999999989</v>
-      </c>
-      <c r="S79" s="4">
-        <f>IF(R79&gt;=R$131, IF(R78&lt;R$131, R$131-R78, 0),S72)</f>
-        <v>0</v>
-      </c>
-      <c r="U79" s="4">
-        <f>SUM(V$72:V72)</f>
-        <v>23.757527193199998</v>
-      </c>
-      <c r="V79" s="4">
-        <f>IF(U79&gt;=U$131, IF(U78&lt;U$131, U$131-U78, 0),V72)</f>
-        <v>23.757527193199998</v>
-      </c>
-      <c r="X79" s="4">
-        <f>SUM(Y$72:Y72)</f>
-        <v>30.582999999999998</v>
-      </c>
-      <c r="Y79" s="4">
-        <f>IF(X79&gt;=X$131, IF(X78&lt;X$131, X$131-X78, 0),Y72)</f>
-        <v>30.582999999999998</v>
-      </c>
-      <c r="Z79" s="39"/>
     </row>
     <row r="80" spans="1:31" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="50"/>
       <c r="B80" s="47"/>
-      <c r="D80" s="22">
-        <v>0</v>
-      </c>
       <c r="E80" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F80" s="4">
-        <f>SUM(G$72:G73)</f>
+        <f>SUM(G$73:G73)</f>
         <v>0</v>
       </c>
       <c r="G80" s="4">
-        <f>IF(F80&gt;=F$131, IF(F79&lt;F$131, F$131-F79, 0),G73)</f>
+        <f>IF(F80&gt;=F$132, IF(F79&lt;F$132, F$132-F79, 0),G73)</f>
         <v>0</v>
       </c>
       <c r="I80" s="4">
-        <f>SUM(J$72:J73)</f>
+        <f>SUM(J$73:J73)</f>
         <v>0</v>
       </c>
       <c r="J80" s="4">
-        <f>IF(I80&gt;=I$131, IF(I79&lt;I$131, I$131-I79, 0),J73)</f>
+        <f>IF(I80&gt;=I$132, IF(I79&lt;I$132, I$132-I79, 0),J73)</f>
         <v>0</v>
       </c>
       <c r="L80" s="4">
-        <f>SUM(M$72:M73)</f>
+        <f>SUM(M$73:M73)</f>
         <v>0</v>
       </c>
       <c r="M80" s="4">
-        <f>IF(L80&gt;=L$131, IF(L79&lt;L$131, L$131-L79, 0),M73)</f>
+        <f>IF(L80&gt;=L$132, IF(L79&lt;L$132, L$132-L79, 0),M73)</f>
         <v>0</v>
       </c>
       <c r="O80" s="4">
-        <f>SUM(P$72:P73)</f>
+        <f>SUM(P$73:P73)</f>
         <v>0</v>
       </c>
       <c r="P80" s="4">
-        <f>IF(O80&gt;=O$131, IF(O79&lt;O$131, O$131-O79, 0),P73)</f>
+        <f>IF(O80&gt;=O$132, IF(O79&lt;O$132, O$132-O79, 0),P73)</f>
         <v>0</v>
       </c>
       <c r="R80" s="4">
-        <f>SUM(S$72:S73)</f>
-        <v>6.7881033999999989</v>
+        <f>SUM(S$73:S73)</f>
+        <v>0</v>
       </c>
       <c r="S80" s="4">
-        <f>IF(R80&gt;=R$131, IF(R79&lt;R$131, R$131-R79, 0),S73)</f>
+        <f>IF(R80&gt;=R$132, IF(R79&lt;R$132, R$132-R79, 0),S73)</f>
         <v>0</v>
       </c>
       <c r="U80" s="4">
-        <f>SUM(V$72:V73)</f>
-        <v>30.146330393199996</v>
+        <f>SUM(V$73:V73)</f>
+        <v>0</v>
       </c>
       <c r="V80" s="4">
-        <f>IF(U80&gt;=U$131, IF(U79&lt;U$131, U$131-U79, 0),V73)</f>
-        <v>6.3888031999999981</v>
+        <f>IF(U80&gt;=U$132, IF(U79&lt;U$132, U$132-U79, 0),V73)</f>
+        <v>0</v>
       </c>
       <c r="X80" s="4">
-        <f>SUM(Y$72:Y73)</f>
-        <v>46.567</v>
+        <f>SUM(Y$73:Y73)</f>
+        <v>0</v>
       </c>
       <c r="Y80" s="4">
-        <f>IF(X80&gt;=X$131, IF(X79&lt;X$131, X$131-X79, 0),Y73)</f>
-        <v>15.984000000000002</v>
+        <f>IF(X80&gt;=X$132, IF(X79&lt;X$132, X$132-X79, 0),Y73)</f>
+        <v>0</v>
       </c>
       <c r="Z80" s="39"/>
     </row>
@@ -9550,66 +9556,66 @@
       <c r="A81" s="50"/>
       <c r="B81" s="47"/>
       <c r="D81" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F81" s="4">
-        <f>SUM(G$72:G74)</f>
+        <f>SUM(G$73:G74)</f>
         <v>0</v>
       </c>
       <c r="G81" s="4">
-        <f>IF(F81&gt;=F$131, IF(F80&lt;F$131, F$131-F80, 0),G74)</f>
+        <f>IF(F81&gt;=F$132, IF(F80&lt;F$132, F$132-F80, 0),G74)</f>
         <v>0</v>
       </c>
       <c r="I81" s="4">
-        <f>SUM(J$72:J74)</f>
+        <f>SUM(J$73:J74)</f>
         <v>0</v>
       </c>
       <c r="J81" s="4">
-        <f>IF(I81&gt;=I$131, IF(I80&lt;I$131, I$131-I80, 0),J74)</f>
+        <f>IF(I81&gt;=I$132, IF(I80&lt;I$132, I$132-I80, 0),J74)</f>
         <v>0</v>
       </c>
       <c r="L81" s="4">
-        <f>SUM(M$72:M74)</f>
+        <f>SUM(M$73:M74)</f>
         <v>0</v>
       </c>
       <c r="M81" s="4">
-        <f>IF(L81&gt;=L$131, IF(L80&lt;L$131, L$131-L80, 0),M74)</f>
+        <f>IF(L81&gt;=L$132, IF(L80&lt;L$132, L$132-L80, 0),M74)</f>
         <v>0</v>
       </c>
       <c r="O81" s="4">
-        <f>SUM(P$72:P74)</f>
+        <f>SUM(P$73:P74)</f>
         <v>0</v>
       </c>
       <c r="P81" s="4">
-        <f>IF(O81&gt;=O$131, IF(O80&lt;O$131, O$131-O80, 0),P74)</f>
+        <f>IF(O81&gt;=O$132, IF(O80&lt;O$132, O$132-O80, 0),P74)</f>
         <v>0</v>
       </c>
       <c r="R81" s="4">
-        <f>SUM(S$72:S74)</f>
-        <v>6.7881033999999989</v>
+        <f>SUM(S$73:S74)</f>
+        <v>0</v>
       </c>
       <c r="S81" s="4">
-        <f>IF(R81&gt;=R$131, IF(R80&lt;R$131, R$131-R80, 0),S74)</f>
+        <f>IF(R81&gt;=R$132, IF(R80&lt;R$132, R$132-R80, 0),S74)</f>
         <v>0</v>
       </c>
       <c r="U81" s="4">
-        <f>SUM(V$72:V74)</f>
-        <v>30.146330393199996</v>
+        <f>SUM(V$73:V74)</f>
+        <v>0</v>
       </c>
       <c r="V81" s="4">
-        <f>IF(U81&gt;=U$131, IF(U80&lt;U$131, U$131-U80, 0),V74)</f>
+        <f>IF(U81&gt;=U$132, IF(U80&lt;U$132, U$132-U80, 0),V74)</f>
         <v>0</v>
       </c>
       <c r="X81" s="4">
-        <f>SUM(Y$72:Y74)</f>
-        <v>53.914123679999996</v>
+        <f>SUM(Y$73:Y74)</f>
+        <v>0</v>
       </c>
       <c r="Y81" s="4">
-        <f>IF(X81&gt;=X$131, IF(X80&lt;X$131, X$131-X80, 0),Y74)</f>
-        <v>7.3471236799999957</v>
+        <f>IF(X81&gt;=X$132, IF(X80&lt;X$132, X$132-X80, 0),Y74)</f>
+        <v>0</v>
       </c>
       <c r="Z81" s="39"/>
     </row>
@@ -9617,217 +9623,224 @@
       <c r="A82" s="50"/>
       <c r="B82" s="47"/>
       <c r="D82" s="22">
+        <v>1</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F82" s="4">
+        <f>SUM(G$73:G75)</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
+        <f>IF(F82&gt;=F$132, IF(F81&lt;F$132, F$132-F81, 0),G75)</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="4">
+        <f>SUM(J$73:J75)</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="4">
+        <f>IF(I82&gt;=I$132, IF(I81&lt;I$132, I$132-I81, 0),J75)</f>
+        <v>0</v>
+      </c>
+      <c r="L82" s="4">
+        <f>SUM(M$73:M75)</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="4">
+        <f>IF(L82&gt;=L$132, IF(L81&lt;L$132, L$132-L81, 0),M75)</f>
+        <v>0</v>
+      </c>
+      <c r="O82" s="4">
+        <f>SUM(P$73:P75)</f>
+        <v>0</v>
+      </c>
+      <c r="P82" s="4">
+        <f>IF(O82&gt;=O$132, IF(O81&lt;O$132, O$132-O81, 0),P75)</f>
+        <v>0</v>
+      </c>
+      <c r="R82" s="4">
+        <f>SUM(S$73:S75)</f>
+        <v>0</v>
+      </c>
+      <c r="S82" s="4">
+        <f>IF(R82&gt;=R$132, IF(R81&lt;R$132, R$132-R81, 0),S75)</f>
+        <v>0</v>
+      </c>
+      <c r="U82" s="4">
+        <f>SUM(V$73:V75)</f>
+        <v>0</v>
+      </c>
+      <c r="V82" s="4">
+        <f>IF(U82&gt;=U$132, IF(U81&lt;U$132, U$132-U81, 0),V75)</f>
+        <v>0</v>
+      </c>
+      <c r="X82" s="4">
+        <f>SUM(Y$73:Y75)</f>
+        <v>0</v>
+      </c>
+      <c r="Y82" s="4">
+        <f>IF(X82&gt;=X$132, IF(X81&lt;X$132, X$132-X81, 0),Y75)</f>
+        <v>0</v>
+      </c>
+      <c r="Z82" s="39"/>
+    </row>
+    <row r="83" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A83" s="50"/>
+      <c r="B83" s="47"/>
+      <c r="D83" s="22">
         <v>2</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E83" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="F82" s="4">
-        <f>SUM(G$72:G75)</f>
-        <v>0</v>
-      </c>
-      <c r="G82" s="4">
-        <f>IF(F82&gt;=F$131, IF(F81&lt;F$131, F$131-F81, 0),G75)</f>
-        <v>0</v>
-      </c>
-      <c r="I82" s="4">
-        <f>SUM(J$72:J75)</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="4">
-        <f>IF(I82&gt;=I$131, IF(I81&lt;I$131, I$131-I81, 0),J75)</f>
-        <v>0</v>
-      </c>
-      <c r="L82" s="4">
-        <f>SUM(M$72:M75)</f>
-        <v>0</v>
-      </c>
-      <c r="M82" s="4">
-        <f>IF(L82&gt;=L$131, IF(L81&lt;L$131, L$131-L81, 0),M75)</f>
-        <v>0</v>
-      </c>
-      <c r="O82" s="4">
-        <f>SUM(P$72:P75)</f>
-        <v>0</v>
-      </c>
-      <c r="P82" s="4">
-        <f>IF(O82&gt;=O$131, IF(O81&lt;O$131, O$131-O81, 0),P75)</f>
-        <v>0</v>
-      </c>
-      <c r="R82" s="4">
-        <f>SUM(S$72:S75)</f>
-        <v>6.7881033999999989</v>
-      </c>
-      <c r="S82" s="4">
-        <f>IF(R82&gt;=R$131, IF(R81&lt;R$131, R$131-R81, 0),S75)</f>
-        <v>0</v>
-      </c>
-      <c r="U82" s="4">
-        <f>SUM(V$72:V75)</f>
-        <v>30.146330393199996</v>
-      </c>
-      <c r="V82" s="4">
-        <f>IF(U82&gt;=U$131, IF(U81&lt;U$131, U$131-U81, 0),V75)</f>
-        <v>0</v>
-      </c>
-      <c r="X82" s="4">
-        <f>SUM(Y$72:Y75)</f>
-        <v>53.914123679999996</v>
-      </c>
-      <c r="Y82" s="4">
-        <f>IF(X82&gt;=X$131, IF(X81&lt;X$131, X$131-X81, 0),Y75)</f>
-        <v>0</v>
-      </c>
-      <c r="Z82" s="39"/>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="D83" s="22">
+      <c r="F83" s="4">
+        <f>SUM(G$73:G76)</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
+        <f>IF(F83&gt;=F$132, IF(F82&lt;F$132, F$132-F82, 0),G76)</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="4">
+        <f>SUM(J$73:J76)</f>
+        <v>0</v>
+      </c>
+      <c r="J83" s="4">
+        <f>IF(I83&gt;=I$132, IF(I82&lt;I$132, I$132-I82, 0),J76)</f>
+        <v>0</v>
+      </c>
+      <c r="L83" s="4">
+        <f>SUM(M$73:M76)</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="4">
+        <f>IF(L83&gt;=L$132, IF(L82&lt;L$132, L$132-L82, 0),M76)</f>
+        <v>0</v>
+      </c>
+      <c r="O83" s="4">
+        <f>SUM(P$73:P76)</f>
+        <v>0</v>
+      </c>
+      <c r="P83" s="4">
+        <f>IF(O83&gt;=O$132, IF(O82&lt;O$132, O$132-O82, 0),P76)</f>
+        <v>0</v>
+      </c>
+      <c r="R83" s="4">
+        <f>SUM(S$73:S76)</f>
+        <v>0</v>
+      </c>
+      <c r="S83" s="4">
+        <f>IF(R83&gt;=R$132, IF(R82&lt;R$132, R$132-R82, 0),S76)</f>
+        <v>0</v>
+      </c>
+      <c r="U83" s="4">
+        <f>SUM(V$73:V76)</f>
+        <v>0</v>
+      </c>
+      <c r="V83" s="4">
+        <f>IF(U83&gt;=U$132, IF(U82&lt;U$132, U$132-U82, 0),V76)</f>
+        <v>0</v>
+      </c>
+      <c r="X83" s="4">
+        <f>SUM(Y$73:Y76)</f>
+        <v>0</v>
+      </c>
+      <c r="Y83" s="4">
+        <f>IF(X83&gt;=X$132, IF(X82&lt;X$132, X$132-X82, 0),Y76)</f>
+        <v>0</v>
+      </c>
+      <c r="Z83" s="39"/>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D84" s="22">
         <v>3</v>
       </c>
-      <c r="E83" s="14"/>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.2">
       <c r="E84" s="14"/>
-      <c r="I84" s="4" t="s">
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E85" s="14"/>
+      <c r="I85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="L84" s="4" t="s">
+      <c r="L85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="O84" s="4" t="s">
+      <c r="O85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="R84" s="4" t="s">
+      <c r="R85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="U84" s="4" t="s">
+      <c r="U85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="X84" s="4" t="s">
+      <c r="X85" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="85" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="46" t="s">
+    <row r="86" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A86" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="47" t="s">
+      <c r="B86" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E86" s="14" t="s">
         <v>131</v>
-      </c>
-      <c r="G85" s="4">
-        <f>G61</f>
-        <v>0</v>
-      </c>
-      <c r="I85" s="4">
-        <f>IF(G95=0,1,MIN(MAX((G95/G67-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="J85" s="4">
-        <f>J61*I85</f>
-        <v>0.01</v>
-      </c>
-      <c r="L85" s="4">
-        <f>IF(J95=0,1,MIN(MAX((J95/J67-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="M85" s="4">
-        <f>M61*L85</f>
-        <v>0.05</v>
-      </c>
-      <c r="O85" s="4">
-        <f>IF(M95=0,1,MIN(MAX((M95/M67-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="P85" s="4">
-        <f>P61*O85</f>
-        <v>0.12</v>
-      </c>
-      <c r="R85" s="4">
-        <f>IF(P95=0,1,MIN(MAX((P95/P67-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="S85" s="4">
-        <f>S61*R85</f>
-        <v>0.2</v>
-      </c>
-      <c r="U85" s="4">
-        <f>IF(S95=0,1,MIN(MAX((S95/S67-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="V85" s="4">
-        <f>V61*U85</f>
-        <v>0.36</v>
-      </c>
-      <c r="X85" s="4">
-        <f>IF(V95=0,1,MIN(MAX((V95/V67-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>0.92886400737928387</v>
-      </c>
-      <c r="Y85" s="4">
-        <f>Y61*X85</f>
-        <v>0.5573184044275703</v>
-      </c>
-      <c r="Z85" s="37"/>
-    </row>
-    <row r="86" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="46"/>
-      <c r="B86" s="47"/>
-      <c r="E86" s="14" t="s">
-        <v>132</v>
       </c>
       <c r="G86" s="4">
         <f>G62</f>
         <v>0</v>
       </c>
       <c r="I86" s="4">
-        <f>IF(G96=0,1,MIN(MAX((G96/G68-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(G96=0,1,MIN(MAX((G96/G68-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="J86" s="4">
-        <f>J62</f>
-        <v>0</v>
+        <f>J62*I86</f>
+        <v>0.01</v>
       </c>
       <c r="L86" s="4">
-        <f>IF(J96=0,1,MIN(MAX((J96/J68-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(J96=0,1,MIN(MAX((J96/J68-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="M86" s="4">
-        <f>M62</f>
-        <v>0.01</v>
+        <f>M62*L86</f>
+        <v>0.05</v>
       </c>
       <c r="O86" s="4">
-        <f>IF(M96=0,1,MIN(MAX((M96/M68-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(M96=0,1,MIN(MAX((M96/M68-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="P86" s="4">
-        <f>P62</f>
-        <v>0.05</v>
+        <f>P62*O86</f>
+        <v>0.12</v>
       </c>
       <c r="R86" s="4">
-        <f>IF(P96=0,1,MIN(MAX((P96/P68-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(P96=0,1,MIN(MAX((P96/P68-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="S86" s="4">
-        <f>S62</f>
-        <v>0.12</v>
+        <f>S62*R86</f>
+        <v>0.2</v>
       </c>
       <c r="U86" s="4">
-        <f>IF(S96=0,1,MIN(MAX((S96/S68-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(S96=0,1,MIN(MAX((S96/S68-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="V86" s="4">
-        <f>V62</f>
-        <v>0.2</v>
+        <f>V62*U86</f>
+        <v>0.36</v>
       </c>
       <c r="X86" s="4">
-        <f>IF(V96=0,1,MIN(MAX((V96/V68-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(V96=0,1,MIN(MAX((V96/V68-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Y86" s="4">
-        <f>Y62</f>
-        <v>0.36</v>
+        <f>Y62*X86</f>
+        <v>0.6</v>
       </c>
       <c r="Z86" s="37"/>
     </row>
@@ -9835,14 +9848,14 @@
       <c r="A87" s="46"/>
       <c r="B87" s="47"/>
       <c r="E87" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G87" s="4">
         <f>G63</f>
         <v>0</v>
       </c>
       <c r="I87" s="4">
-        <f>IF(G97=0,1,MIN(MAX((G97/G69-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(G97=0,1,MIN(MAX((G97/G69-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="J87" s="4">
@@ -9850,44 +9863,44 @@
         <v>0</v>
       </c>
       <c r="L87" s="4">
-        <f>IF(J97=0,1,MIN(MAX((J97/J69-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(J97=0,1,MIN(MAX((J97/J69-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="M87" s="4">
         <f>M63</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O87" s="4">
-        <f>IF(M97=0,1,MIN(MAX((M97/M69-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(M97=0,1,MIN(MAX((M97/M69-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="P87" s="4">
         <f>P63</f>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="R87" s="4">
-        <f>IF(P97=0,1,MIN(MAX((P97/P69-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(P97=0,1,MIN(MAX((P97/P69-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="S87" s="4">
         <f>S63</f>
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="U87" s="4">
-        <f>IF(S97=0,1,MIN(MAX((S97/S69-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(S97=0,1,MIN(MAX((S97/S69-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="V87" s="4">
         <f>V63</f>
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="X87" s="4">
-        <f>IF(V97=0,1,MIN(MAX((V97/V69-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(V97=0,1,MIN(MAX((V97/V69-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Y87" s="4">
         <f>Y63</f>
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="Z87" s="37"/>
     </row>
@@ -9895,14 +9908,14 @@
       <c r="A88" s="46"/>
       <c r="B88" s="47"/>
       <c r="E88" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G88" s="4">
         <f>G64</f>
         <v>0</v>
       </c>
       <c r="I88" s="4">
-        <f>IF(G98=0,1,MIN(MAX((G98/G70-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(G98=0,1,MIN(MAX((G98/G70-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="J88" s="4">
@@ -9910,7 +9923,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="4">
-        <f>IF(J98=0,1,MIN(MAX((J98/J70-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(J98=0,1,MIN(MAX((J98/J70-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="M88" s="4">
@@ -9918,115 +9931,139 @@
         <v>0</v>
       </c>
       <c r="O88" s="4">
-        <f>IF(M98=0,1,MIN(MAX((M98/M70-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(M98=0,1,MIN(MAX((M98/M70-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="P88" s="4">
         <f>P64</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R88" s="4">
-        <f>IF(P98=0,1,MIN(MAX((P98/P70-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(P98=0,1,MIN(MAX((P98/P70-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="S88" s="4">
         <f>S64</f>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="U88" s="4">
-        <f>IF(S98=0,1,MIN(MAX((S98/S70-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(S98=0,1,MIN(MAX((S98/S70-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="V88" s="4">
         <f>V64</f>
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="X88" s="4">
-        <f>IF(V98=0,1,MIN(MAX((V98/V70-$F$16)/($F$18-$F$16), 0), 1))</f>
+        <f>IF(V98=0,1,MIN(MAX((V98/V70-$F$17)/($F$19-$F$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Y88" s="4">
         <f>Y64</f>
+        <v>0.2</v>
+      </c>
+      <c r="Z88" s="37"/>
+    </row>
+    <row r="89" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A89" s="46"/>
+      <c r="B89" s="47"/>
+      <c r="E89" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G89" s="4">
+        <f>G65</f>
+        <v>0</v>
+      </c>
+      <c r="I89" s="4">
+        <f>IF(G99=0,1,MIN(MAX((G99/G71-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="J89" s="4">
+        <f>J65</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="4">
+        <f>IF(J99=0,1,MIN(MAX((J99/J71-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="M89" s="4">
+        <f>M65</f>
+        <v>0</v>
+      </c>
+      <c r="O89" s="4">
+        <f>IF(M99=0,1,MIN(MAX((M99/M71-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="P89" s="4">
+        <f>P65</f>
+        <v>0</v>
+      </c>
+      <c r="R89" s="4">
+        <f>IF(P99=0,1,MIN(MAX((P99/P71-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="S89" s="4">
+        <f>S65</f>
+        <v>0.01</v>
+      </c>
+      <c r="U89" s="4">
+        <f>IF(S99=0,1,MIN(MAX((S99/S71-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="V89" s="4">
+        <f>V65</f>
+        <v>0.05</v>
+      </c>
+      <c r="X89" s="4">
+        <f>IF(V99=0,1,MIN(MAX((V99/V71-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="Y89" s="4">
+        <f>Y65</f>
         <v>0.12</v>
       </c>
-      <c r="Z88" s="37"/>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E89" s="14"/>
-    </row>
-    <row r="90" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="46" t="s">
+      <c r="Z89" s="37"/>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E90" s="14"/>
+    </row>
+    <row r="91" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A91" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="B90" s="47" t="s">
+      <c r="B91" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E90" s="14" t="s">
+      <c r="E91" s="14" t="s">
         <v>205</v>
-      </c>
-      <c r="G90" s="4">
-        <f>G56*G32</f>
-        <v>0</v>
-      </c>
-      <c r="J90" s="4">
-        <f>(G95-J79-J42)*$F$29</f>
-        <v>0</v>
-      </c>
-      <c r="M90" s="4">
-        <f>(J95-M79-M42)*$F$29</f>
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="P90" s="4">
-        <f>(M95-P79-P42)*$F$29</f>
-        <v>1.01966E-2</v>
-      </c>
-      <c r="S90" s="4">
-        <f>(P95-S79-S42)*$F$29</f>
-        <v>3.0576206799999998E-2</v>
-      </c>
-      <c r="V90" s="4">
-        <f>(S95-V79-V42)*$F$29</f>
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="Y90" s="4">
-        <f>(V95-Y79-Y42)*$F$29</f>
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="Z90" s="37"/>
-    </row>
-    <row r="91" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="46"/>
-      <c r="B91" s="47"/>
-      <c r="E91" s="14" t="s">
-        <v>206</v>
       </c>
       <c r="G91" s="4">
         <f>G57*G33</f>
         <v>0</v>
       </c>
       <c r="J91" s="4">
-        <f>(G96-J80-J43)*$F$29</f>
+        <f>(G96-J80-J43)*$F$30</f>
         <v>0</v>
       </c>
       <c r="M91" s="4">
-        <f>(J96-M80-M43)*$F$29</f>
-        <v>0</v>
+        <f>(J96-M80-M43)*$F$30</f>
+        <v>1.1284149499999998E-2</v>
       </c>
       <c r="P91" s="4">
-        <f>(M96-P80-P43)*$F$29</f>
-        <v>1.6000000000000001E-3</v>
+        <f>(M96-P80-P43)*$F$30</f>
+        <v>6.755509461183723E-2</v>
       </c>
       <c r="S91" s="4">
-        <f>(P96-S80-S43)*$F$29</f>
-        <v>9.5968000000000008E-3</v>
+        <f>(P96-S80-S43)*$F$30</f>
+        <v>0.2020680629799706</v>
       </c>
       <c r="V91" s="4">
-        <f>(S96-V80-V43)*$F$29</f>
-        <v>1.6000000000000004E-2</v>
+        <f>(S96-V80-V43)*$F$30</f>
+        <v>0.42506850447192185</v>
       </c>
       <c r="Y91" s="4">
-        <f>(V96-Y80-Y43)*$F$29</f>
-        <v>1.6E-2</v>
+        <f>(V96-Y80-Y43)*$F$30</f>
+        <v>0.82565490229285987</v>
       </c>
       <c r="Z91" s="37"/>
     </row>
@@ -10034,35 +10071,35 @@
       <c r="A92" s="46"/>
       <c r="B92" s="47"/>
       <c r="E92" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G92" s="4">
         <f>G58*G34</f>
         <v>0</v>
       </c>
       <c r="J92" s="4">
-        <f>(G97-J81-J44)*$F$29</f>
+        <f>(G97-J81-J44)*$F$30</f>
         <v>0</v>
       </c>
       <c r="M92" s="4">
-        <f>(J97-M81-M44)*$F$29</f>
+        <f>(J97-M81-M44)*$F$30</f>
         <v>0</v>
       </c>
       <c r="P92" s="4">
-        <f>(M97-P81-P44)*$F$29</f>
-        <v>0</v>
+        <f>(M97-P81-P44)*$F$30</f>
+        <v>1.0620376000000001E-2</v>
       </c>
       <c r="S92" s="4">
-        <f>(P97-S81-S44)*$F$29</f>
-        <v>1.8400000000000001E-3</v>
+        <f>(P97-S81-S44)*$F$30</f>
+        <v>6.3581265517023283E-2</v>
       </c>
       <c r="V92" s="4">
-        <f>(S97-V81-V44)*$F$29</f>
-        <v>1.1036320000000002E-2</v>
+        <f>(S97-V81-V44)*$F$30</f>
+        <v>0.19018170633409001</v>
       </c>
       <c r="Y92" s="4">
-        <f>(V97-Y81-Y44)*$F$29</f>
-        <v>1.8400000000000007E-2</v>
+        <f>(V97-Y81-Y44)*$F$30</f>
+        <v>0.40006447479710294</v>
       </c>
       <c r="Z92" s="37"/>
     </row>
@@ -10070,86 +10107,86 @@
       <c r="A93" s="46"/>
       <c r="B93" s="47"/>
       <c r="E93" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G93" s="4">
         <f>G59*G35</f>
         <v>0</v>
       </c>
       <c r="J93" s="4">
-        <f>(G98-J82-J45)*$F$29</f>
+        <f>(G98-J82-J45)*$F$30</f>
         <v>0</v>
       </c>
       <c r="M93" s="4">
-        <f>(J98-M82-M45)*$F$29</f>
+        <f>(J98-M82-M45)*$F$30</f>
         <v>0</v>
       </c>
       <c r="P93" s="4">
-        <f>(M98-P82-P45)*$F$29</f>
+        <f>(M98-P82-P45)*$F$30</f>
         <v>0</v>
       </c>
       <c r="S93" s="4">
-        <f>(P98-S82-S45)*$F$29</f>
-        <v>0</v>
+        <f>(P98-S82-S45)*$F$30</f>
+        <v>1.22134324E-2</v>
       </c>
       <c r="V93" s="4">
-        <f>(S98-V82-V45)*$F$29</f>
-        <v>8.5999999999999998E-4</v>
+        <f>(S98-V82-V45)*$F$30</f>
+        <v>7.3118455344576769E-2</v>
       </c>
       <c r="Y93" s="4">
-        <f>(V98-Y82-Y45)*$F$29</f>
-        <v>5.1582799999999995E-3</v>
+        <f>(V98-Y82-Y45)*$F$30</f>
+        <v>0.21870896228420347</v>
       </c>
       <c r="Z93" s="37"/>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E94" s="14"/>
-    </row>
-    <row r="95" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="46" t="s">
+    <row r="94" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A94" s="46"/>
+      <c r="B94" s="47"/>
+      <c r="E94" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="G94" s="4">
+        <f>G60*G36</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="4">
+        <f>(G99-J83-J46)*$F$30</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="4">
+        <f>(J99-M83-M46)*$F$30</f>
+        <v>0</v>
+      </c>
+      <c r="P94" s="4">
+        <f>(M99-P83-P46)*$F$30</f>
+        <v>0</v>
+      </c>
+      <c r="S94" s="4">
+        <f>(P99-S83-S46)*$F$30</f>
+        <v>0</v>
+      </c>
+      <c r="V94" s="4">
+        <f>(S99-V83-V46)*$F$30</f>
+        <v>5.7084520999999997E-3</v>
+      </c>
+      <c r="Y94" s="4">
+        <f>(V99-Y83-Y46)*$F$30</f>
+        <v>3.417493021540001E-2</v>
+      </c>
+      <c r="Z94" s="37"/>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E95" s="14"/>
+    </row>
+    <row r="96" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A96" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="47" t="s">
+      <c r="B96" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="E95" s="14" t="s">
+      <c r="E96" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="G95" s="4">
-        <f>G61*G37</f>
-        <v>0</v>
-      </c>
-      <c r="J95" s="4">
-        <f>G95 - J79 - J90 - J42 + J37*J85</f>
-        <v>0.85</v>
-      </c>
-      <c r="M95" s="4">
-        <f>J95 - M79 - M90 - M42 + M37*M85</f>
-        <v>5.0983000000000001</v>
-      </c>
-      <c r="P95" s="4">
-        <f>M95 - P79 - P90 - P42 + P37*P85</f>
-        <v>15.288103399999999</v>
-      </c>
-      <c r="S95" s="4">
-        <f>P95 - S79 - S90 - S42 + S37*S85</f>
-        <v>32.257527193199998</v>
-      </c>
-      <c r="V95" s="4">
-        <f>S95 - V79 - V90 - V42 + V37*V85</f>
-        <v>39.082999999999998</v>
-      </c>
-      <c r="Y95" s="4">
-        <f>V95 - Y79 - Y90 - Y42 + Y37*Y85</f>
-        <v>55.855064376343478</v>
-      </c>
-      <c r="Z95" s="37"/>
-    </row>
-    <row r="96" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="46"/>
-      <c r="B96" s="47"/>
-      <c r="E96" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="G96" s="4">
         <f>G62*G38</f>
@@ -10157,27 +10194,27 @@
       </c>
       <c r="J96" s="4">
         <f>G96 - J80 - J91 - J43 + J38*J86</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M96" s="4">
         <f>J96 - M80 - M91 - M43 + M38*M86</f>
-        <v>0.8</v>
+        <v>5.0887158504999999</v>
       </c>
       <c r="P96" s="4">
         <f>M96 - P80 - P91 - P43 + P38*P86</f>
-        <v>4.7984</v>
+        <v>15.221160755888162</v>
       </c>
       <c r="S96" s="4">
         <f>P96 - S80 - S91 - S43 + S38*S86</f>
-        <v>14.3888032</v>
+        <v>32.019092692908188</v>
       </c>
       <c r="V96" s="4">
         <f>S96 - V80 - V91 - V43 + V38*V86</f>
-        <v>23.984000000000002</v>
+        <v>62.194024188436259</v>
       </c>
       <c r="Y96" s="4">
         <f>V96 - Y80 - Y91 - Y43 + Y38*Y86</f>
-        <v>36.783999999999999</v>
+        <v>112.36836928614341</v>
       </c>
       <c r="Z96" s="37"/>
     </row>
@@ -10185,7 +10222,7 @@
       <c r="A97" s="46"/>
       <c r="B97" s="47"/>
       <c r="E97" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G97" s="4">
         <f>G63*G39</f>
@@ -10197,31 +10234,31 @@
       </c>
       <c r="M97" s="4">
         <f>J97 - M81 - M92 - M44 + M39*M87</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P97" s="4">
         <f>M97 - P81 - P92 - P44 + P39*P87</f>
-        <v>0.92</v>
+        <v>4.7893796240000004</v>
       </c>
       <c r="S97" s="4">
         <f>P97 - S81 - S92 - S44 + S39*S87</f>
-        <v>5.5181600000000008</v>
+        <v>14.325798358482977</v>
       </c>
       <c r="V97" s="4">
         <f>S97 - V81 - V92 - V44 + V39*V87</f>
-        <v>16.547123679999999</v>
+        <v>30.135616652148887</v>
       </c>
       <c r="Y97" s="4">
         <f>V97 - Y81 - Y92 - Y44 + Y39*Y87</f>
-        <v>27.581600000000005</v>
+        <v>58.535552177351782</v>
       </c>
       <c r="Z97" s="37"/>
     </row>
-    <row r="98" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" s="46"/>
       <c r="B98" s="47"/>
       <c r="E98" s="14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="G98" s="4">
         <f>G64*G40</f>
@@ -10237,101 +10274,100 @@
       </c>
       <c r="P98" s="4">
         <f>M98 - P82 - P93 - P45 + P40*P88</f>
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="S98" s="4">
         <f>P98 - S82 - S93 - S45 + S40*S88</f>
-        <v>0.43</v>
+        <v>5.5077865676000002</v>
       </c>
       <c r="V98" s="4">
         <f>S98 - V82 - V93 - V45 + V40*V88</f>
-        <v>2.5791399999999998</v>
+        <v>16.474668112255422</v>
       </c>
       <c r="Y98" s="4">
         <f>V98 - Y82 - Y93 - Y45 + Y40*Y88</f>
-        <v>7.7339817200000001</v>
+        <v>34.655959149971224</v>
       </c>
       <c r="Z98" s="37"/>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="D99" s="26"/>
-      <c r="E99" s="14"/>
-    </row>
-    <row r="100" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A100" s="46" t="s">
+    <row r="99" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="46"/>
+      <c r="B99" s="47"/>
+      <c r="E99" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G99" s="4">
+        <f>G65*G41</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="4">
+        <f>G99 - J83 - J94 - J46 + J41*J89</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="4">
+        <f>J99 - M83 - M94 - M46 + M41*M89</f>
+        <v>0</v>
+      </c>
+      <c r="P99" s="4">
+        <f>M99 - P83 - P94 - P46 + P41*P89</f>
+        <v>0</v>
+      </c>
+      <c r="S99" s="4">
+        <f>P99 - S83 - S94 - S46 + S41*S89</f>
+        <v>0.43</v>
+      </c>
+      <c r="V99" s="4">
+        <f>S99 - V83 - V94 - V46 + V41*V89</f>
+        <v>2.5742915478999997</v>
+      </c>
+      <c r="Y99" s="4">
+        <f>V99 - Y83 - Y94 - Y46 + Y41*Y89</f>
+        <v>7.7001166176845999</v>
+      </c>
+      <c r="Z99" s="37"/>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D100" s="26"/>
+      <c r="E100" s="14"/>
+    </row>
+    <row r="101" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A101" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="B100" s="47" t="s">
+      <c r="B101" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="D100" s="26"/>
-      <c r="E100" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="G100" s="4">
-        <f>G95*$G$20</f>
-        <v>0</v>
-      </c>
-      <c r="J100" s="4">
-        <f>J95*$G$20</f>
-        <v>0.21249999999999999</v>
-      </c>
-      <c r="M100" s="4">
-        <f>M95*$G$20</f>
-        <v>1.274575</v>
-      </c>
-      <c r="P100" s="4">
-        <f>P95*$G$20</f>
-        <v>3.8220258499999997</v>
-      </c>
-      <c r="S100" s="4">
-        <f>S95*$G$20</f>
-        <v>8.0643817982999995</v>
-      </c>
-      <c r="V100" s="4">
-        <f>V95*$G$20</f>
-        <v>9.7707499999999996</v>
-      </c>
-      <c r="Y100" s="4">
-        <f>Y95*$G$20</f>
-        <v>13.963766094085869</v>
-      </c>
-      <c r="Z100" s="37"/>
-    </row>
-    <row r="101" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="46"/>
-      <c r="B101" s="47"/>
       <c r="D101" s="26"/>
       <c r="E101" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G101" s="4">
-        <f t="shared" ref="G101:G103" si="9">G96*$G$20</f>
+        <f>G96*$G$21</f>
         <v>0</v>
       </c>
       <c r="J101" s="4">
-        <f t="shared" ref="J101:J103" si="10">J96*$G$20</f>
-        <v>0</v>
+        <f>J96*$G$21</f>
+        <v>0.21249999999999999</v>
       </c>
       <c r="M101" s="4">
-        <f t="shared" ref="M101:M103" si="11">M96*$G$20</f>
-        <v>0.2</v>
+        <f>M96*$G$21</f>
+        <v>1.272178962625</v>
       </c>
       <c r="P101" s="4">
-        <f t="shared" ref="P101:P103" si="12">P96*$G$20</f>
-        <v>1.1996</v>
+        <f>P96*$G$21</f>
+        <v>3.8052901889720405</v>
       </c>
       <c r="S101" s="4">
-        <f t="shared" ref="S101:S103" si="13">S96*$G$20</f>
-        <v>3.5972008</v>
+        <f>S96*$G$21</f>
+        <v>8.0047731732270471</v>
       </c>
       <c r="V101" s="4">
-        <f t="shared" ref="V101:V103" si="14">V96*$G$20</f>
-        <v>5.9960000000000004</v>
+        <f>V96*$G$21</f>
+        <v>15.548506047109065</v>
       </c>
       <c r="Y101" s="4">
-        <f t="shared" ref="Y101:Y103" si="15">Y96*$G$20</f>
-        <v>9.1959999999999997</v>
+        <f>Y96*$G$21</f>
+        <v>28.092092321535851</v>
       </c>
       <c r="Z101" s="37"/>
     </row>
@@ -10340,35 +10376,35 @@
       <c r="B102" s="47"/>
       <c r="D102" s="26"/>
       <c r="E102" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G102" s="4">
-        <f>G97*$G$20</f>
+        <f t="shared" ref="G102:G104" si="9">G97*$G$21</f>
         <v>0</v>
       </c>
       <c r="J102" s="4">
-        <f>J97*$G$20</f>
+        <f t="shared" ref="J102:J104" si="10">J97*$G$21</f>
         <v>0</v>
       </c>
       <c r="M102" s="4">
-        <f>M97*$G$20</f>
-        <v>0</v>
+        <f t="shared" ref="M102:M104" si="11">M97*$G$21</f>
+        <v>0.2</v>
       </c>
       <c r="P102" s="4">
-        <f>P97*$G$20</f>
-        <v>0.23</v>
+        <f t="shared" ref="P102:P104" si="12">P97*$G$21</f>
+        <v>1.1973449060000001</v>
       </c>
       <c r="S102" s="4">
-        <f>S97*$G$20</f>
-        <v>1.3795400000000002</v>
+        <f t="shared" ref="S102:S104" si="13">S97*$G$21</f>
+        <v>3.5814495896207443</v>
       </c>
       <c r="V102" s="4">
-        <f>V97*$G$20</f>
-        <v>4.1367809199999996</v>
+        <f t="shared" ref="V102:V104" si="14">V97*$G$21</f>
+        <v>7.5339041630372217</v>
       </c>
       <c r="Y102" s="4">
-        <f>Y97*$G$20</f>
-        <v>6.8954000000000013</v>
+        <f t="shared" ref="Y102:Y104" si="15">Y97*$G$21</f>
+        <v>14.633888044337946</v>
       </c>
       <c r="Z102" s="37"/>
     </row>
@@ -10377,44 +10413,74 @@
       <c r="B103" s="47"/>
       <c r="D103" s="26"/>
       <c r="E103" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G103" s="4">
+        <f>G98*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="J103" s="4">
+        <f>J98*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="4">
+        <f>M98*$G$21</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="4">
+        <f>P98*$G$21</f>
+        <v>0.23</v>
+      </c>
+      <c r="S103" s="4">
+        <f>S98*$G$21</f>
+        <v>1.3769466419</v>
+      </c>
+      <c r="V103" s="4">
+        <f>V98*$G$21</f>
+        <v>4.1186670280638555</v>
+      </c>
+      <c r="Y103" s="4">
+        <f>Y98*$G$21</f>
+        <v>8.663989787492806</v>
+      </c>
+      <c r="Z103" s="37"/>
+    </row>
+    <row r="104" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A104" s="46"/>
+      <c r="B104" s="47"/>
+      <c r="D104" s="26"/>
+      <c r="E104" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G104" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J103" s="4">
+      <c r="J104" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M103" s="4">
+      <c r="M104" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P103" s="4">
+      <c r="P104" s="4">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S103" s="4">
+      <c r="S104" s="4">
         <f t="shared" si="13"/>
         <v>0.1075</v>
       </c>
-      <c r="V103" s="4">
+      <c r="V104" s="4">
         <f t="shared" si="14"/>
-        <v>0.64478499999999994</v>
-      </c>
-      <c r="Y103" s="4">
+        <v>0.64357288697499992</v>
+      </c>
+      <c r="Y104" s="4">
         <f t="shared" si="15"/>
-        <v>1.93349543</v>
-      </c>
-      <c r="Z103" s="37"/>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A104" s="29"/>
-      <c r="B104" s="35"/>
-      <c r="D104" s="26"/>
-      <c r="E104" s="14"/>
-      <c r="Z104" s="29"/>
+        <v>1.92502915442115</v>
+      </c>
+      <c r="Z104" s="37"/>
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A105" s="29"/>
@@ -10423,1716 +10489,1645 @@
       <c r="E105" s="14"/>
       <c r="Z105" s="29"/>
     </row>
-    <row r="106" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A106" s="29"/>
+      <c r="B106" s="35"/>
       <c r="D106" s="26"/>
-      <c r="E106" s="15" t="s">
+      <c r="E106" s="14"/>
+      <c r="Z106" s="29"/>
+    </row>
+    <row r="107" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="D107" s="26"/>
+      <c r="E107" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F107" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G106" s="8"/>
-    </row>
-    <row r="107" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="B107" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="D107" s="26"/>
-      <c r="E107" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="G107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="I107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="J107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="L107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="M107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="O107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="P107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="R107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="S107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="U107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="V107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="X107" s="4">
-        <f>$F$28</f>
-        <v>0.3</v>
-      </c>
-      <c r="Y107" s="4">
-        <f>$G$28</f>
-        <v>0.92</v>
-      </c>
-      <c r="Z107" s="38"/>
+      <c r="G107" s="8"/>
     </row>
     <row r="108" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>174</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="B108" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" s="26"/>
       <c r="E108" s="14" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="F108" s="4">
-        <f>F7*$F$19</f>
-        <v>1500000</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="G108" s="4">
-        <f>G7*$G$19</f>
-        <v>25000000</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="I108" s="4">
-        <f>I7*$F$19</f>
-        <v>1492500</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="J108" s="4">
-        <f>J7*$G$19</f>
-        <v>24990000</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="L108" s="4">
-        <f>L7*$F$19</f>
-        <v>1483200</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="M108" s="4">
-        <f>M7*$G$19</f>
-        <v>24979000</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="O108" s="4">
-        <f>O7*$F$19</f>
-        <v>1474500</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="P108" s="4">
-        <f>P7*$G$19</f>
-        <v>24969600</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="R108" s="4">
-        <f>R7*$F$19</f>
-        <v>1464000</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="S108" s="4">
-        <f>S7*$G$19</f>
-        <v>24950400</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="U108" s="4">
-        <f>U7*$F$19</f>
-        <v>1449000</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="V108" s="4">
-        <f>V7*$G$19</f>
-        <v>24946500</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="X108" s="4">
-        <f>X7*$F$19</f>
-        <v>1434300</v>
+        <f>$F$29</f>
+        <v>0.3</v>
       </c>
       <c r="Y108" s="4">
-        <f>Y7*$G$19</f>
-        <v>24936000</v>
+        <f>$G$29</f>
+        <v>0.92</v>
       </c>
       <c r="Z108" s="38"/>
     </row>
     <row r="109" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A109" s="38" t="s">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="B109" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="F109" s="4">
-        <v>1</v>
+        <f>F7*$F$20</f>
+        <v>1500000</v>
       </c>
       <c r="G109" s="4">
-        <v>1</v>
+        <f>G7*$G$20</f>
+        <v>25000000</v>
       </c>
       <c r="I109" s="4">
-        <f>IF(F111=0,0,MIN(MAX((F111/F108-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
+        <f>I7*$F$20</f>
+        <v>1492500</v>
       </c>
       <c r="J109" s="4">
-        <f>IF(G111=0,0,MIN(MAX((G111/G108-$G$16)/($F$18-$G$16), 0), 1))</f>
-        <v>1</v>
+        <f>J7*$G$20</f>
+        <v>24990000</v>
       </c>
       <c r="L109" s="4">
-        <f>IF(I111=0,0,MIN(MAX((I111/I108-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
+        <f>L7*$F$20</f>
+        <v>1483200</v>
       </c>
       <c r="M109" s="4">
-        <f>IF(J111=0,0,MIN(MAX((J111/J108-$G$16)/($F$18-$G$16), 0), 1))</f>
-        <v>1</v>
+        <f>M7*$G$20</f>
+        <v>24979000</v>
       </c>
       <c r="O109" s="4">
-        <f>IF(L111=0,0,MIN(MAX((L111/L108-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
+        <f>O7*$F$20</f>
+        <v>1474500</v>
       </c>
       <c r="P109" s="4">
-        <f>IF(M111=0,0,MIN(MAX((M111/M108-$G$16)/($F$18-$G$16), 0), 1))</f>
-        <v>1</v>
+        <f>P7*$G$20</f>
+        <v>24969600</v>
       </c>
       <c r="R109" s="4">
-        <f>IF(O111=0,0,MIN(MAX((O111/O108-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
+        <f>R7*$F$20</f>
+        <v>1464000</v>
       </c>
       <c r="S109" s="4">
-        <f>IF(P111=0,0,MIN(MAX((P111/P108-$G$16)/($F$18-$G$16), 0), 1))</f>
-        <v>1</v>
+        <f>S7*$G$20</f>
+        <v>24950400</v>
       </c>
       <c r="U109" s="4">
-        <f>IF(R111=0,0,MIN(MAX((R111/R108-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
+        <f>U7*$F$20</f>
+        <v>1449000</v>
       </c>
       <c r="V109" s="4">
-        <f>IF(S111=0,0,MIN(MAX((S111/S108-$G$16)/($F$18-$G$16), 0), 1))</f>
-        <v>1</v>
+        <f>V7*$G$20</f>
+        <v>24946500</v>
       </c>
       <c r="X109" s="4">
-        <f>IF(U111=0,0,MIN(MAX((U111/U108-$F$16)/($F$18-$F$16), 0), 1))</f>
-        <v>1</v>
+        <f>X7*$F$20</f>
+        <v>1434300</v>
       </c>
       <c r="Y109" s="4">
-        <f>IF(V111=0,0,MIN(MAX((V111/V108-$G$16)/($F$18-$G$16), 0), 1))</f>
-        <v>0.89478919993714923</v>
-      </c>
-      <c r="Z109" s="38" t="s">
-        <v>300</v>
-      </c>
+        <f>Y7*$G$20</f>
+        <v>24936000</v>
+      </c>
+      <c r="Z109" s="38"/>
     </row>
     <row r="110" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="B110" s="33" t="s">
-        <v>163</v>
+        <v>183</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>174</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="F110" s="4">
-        <f>F107</f>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G110" s="4">
-        <f>G107</f>
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="I110" s="4">
-        <f xml:space="preserve"> I107*I109</f>
-        <v>0.3</v>
+        <f>IF(F112=0,0,MIN(MAX((F112/F109-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="J110" s="4">
-        <f>J107*J109</f>
-        <v>0.92</v>
+        <f>IF(G112=0,0,MIN(MAX((G112/G109-$G$17)/($F$19-$G$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="L110" s="4">
-        <f xml:space="preserve"> L107*L109</f>
-        <v>0.3</v>
+        <f>IF(I112=0,0,MIN(MAX((I112/I109-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="M110" s="4">
-        <f>M107*M109</f>
-        <v>0.92</v>
+        <f>IF(J112=0,0,MIN(MAX((J112/J109-$G$17)/($F$19-$G$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="O110" s="4">
-        <f xml:space="preserve"> O107*O109</f>
-        <v>0.3</v>
+        <f>IF(L112=0,0,MIN(MAX((L112/L109-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="P110" s="4">
-        <f>P107*P109</f>
-        <v>0.92</v>
+        <f>IF(M112=0,0,MIN(MAX((M112/M109-$G$17)/($F$19-$G$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="R110" s="4">
-        <f xml:space="preserve"> R107*R109</f>
-        <v>0.3</v>
+        <f>IF(O112=0,0,MIN(MAX((O112/O109-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="S110" s="4">
-        <f>S107*S109</f>
-        <v>0.92</v>
+        <f>IF(P112=0,0,MIN(MAX((P112/P109-$G$17)/($F$19-$G$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="U110" s="4">
-        <f xml:space="preserve"> U107*U109</f>
-        <v>0.3</v>
+        <f>IF(R112=0,0,MIN(MAX((R112/R109-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="V110" s="4">
-        <f>V107*V109</f>
-        <v>0.92</v>
+        <f>IF(S112=0,0,MIN(MAX((S112/S109-$G$17)/($F$19-$G$17), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="X110" s="4">
-        <f xml:space="preserve"> X107*X109</f>
-        <v>0.3</v>
+        <f>IF(U112=0,0,MIN(MAX((U112/U109-$F$17)/($F$19-$F$17), 0), 1))</f>
+        <v>0.89228649746988453</v>
       </c>
       <c r="Y110" s="4">
-        <f>Y107*Y109</f>
-        <v>0.82320606394217732</v>
-      </c>
-      <c r="Z110" s="38"/>
+        <f>IF(V112=0,0,MIN(MAX((V112/V109-$G$17)/($F$19-$G$17), 0), 1))</f>
+        <v>0.85022774788522248</v>
+      </c>
+      <c r="Z110" s="38" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="111" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A111" s="38" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="B111" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="F111" s="4">
-        <f>F7*F19</f>
-        <v>1500000</v>
+        <f>F108</f>
+        <v>0.3</v>
       </c>
       <c r="G111" s="4">
-        <f>G7*G19</f>
-        <v>25000000</v>
+        <f>G108</f>
+        <v>0.92</v>
       </c>
       <c r="I111" s="4">
-        <f>F111 - F132 - F120 - F143+I110*I7</f>
-        <v>1421423.1421982395</v>
+        <f xml:space="preserve"> I108*I110</f>
+        <v>0.3</v>
       </c>
       <c r="J111" s="4">
-        <f>G111 - G132 - G120 - G143 + J110*J7</f>
-        <v>23256357.107801761</v>
+        <f>J108*J110</f>
+        <v>0.92</v>
       </c>
       <c r="L111" s="4">
-        <f>I111 - I132 - I120 - I143+L110*L7</f>
-        <v>1339098.0188325029</v>
+        <f xml:space="preserve"> L108*L110</f>
+        <v>0.3</v>
       </c>
       <c r="M111" s="4">
-        <f>J111 - J132 - J120 - J143 + M110*M7</f>
-        <v>21469509.138674762</v>
+        <f>M108*M110</f>
+        <v>0.92</v>
       </c>
       <c r="O111" s="4">
-        <f>L111 - L132 - L120 - L143+O110*O7</f>
-        <v>1262299.2941418488</v>
+        <f xml:space="preserve"> O108*O110</f>
+        <v>0.3</v>
       </c>
       <c r="P111" s="4">
-        <f>M111 - M132 - M120 - M143 + P110*P7</f>
-        <v>19621955.060604014</v>
+        <f>P108*P110</f>
+        <v>0.92</v>
       </c>
       <c r="R111" s="4">
-        <f>O111 - O132 - O120 - O143+R110*R7</f>
-        <v>1188284.3985157635</v>
+        <f xml:space="preserve"> R108*R110</f>
+        <v>0.3</v>
       </c>
       <c r="S111" s="4">
-        <f>P111 - P132 - P120 - P143 + S110*S7</f>
-        <v>17672326.749100834</v>
+        <f>S108*S110</f>
+        <v>0.92</v>
       </c>
       <c r="U111" s="4">
-        <f>R111 - R132 - R120 - R143+U110*U7</f>
-        <v>1097914.9513435864</v>
+        <f xml:space="preserve"> U108*U110</f>
+        <v>0.3</v>
       </c>
       <c r="V111" s="4">
-        <f>S111 - S132 - S120 - S143 + V110*V7</f>
-        <v>14958270.021299271</v>
+        <f>V108*V110</f>
+        <v>0.92</v>
       </c>
       <c r="X111" s="4">
-        <f>U111 - U132 - U120 - U143+X110*X7</f>
-        <v>819907.25085905532</v>
+        <f xml:space="preserve"> X108*X110</f>
+        <v>0.26768594924096534</v>
       </c>
       <c r="Y111" s="4">
-        <f>V111 - V132 - V120 - V143 + Y110*Y7</f>
-        <v>3187373.6439100648</v>
+        <f>Y108*Y110</f>
+        <v>0.78220952805440469</v>
       </c>
       <c r="Z111" s="38"/>
     </row>
     <row r="112" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" s="38" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B112" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E112" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F112" s="4">
+        <f>F7*F20</f>
+        <v>1500000</v>
+      </c>
+      <c r="G112" s="4">
+        <f>G7*G20</f>
+        <v>25000000</v>
+      </c>
+      <c r="I112" s="4">
+        <f>F112 - F133 - F121 - F144+I111*I7</f>
+        <v>1400244.5781226705</v>
+      </c>
+      <c r="J112" s="4">
+        <f>G112 - G133 - G121 - G144 + J111*J7</f>
+        <v>23001355.719131082</v>
+      </c>
+      <c r="L112" s="4">
+        <f>I112 - I133 - I121 - I144+L111*L7</f>
+        <v>1296616.445847953</v>
+      </c>
+      <c r="M112" s="4">
+        <f>J112 - J133 - J121 - J144 + M111*M7</f>
+        <v>20984486.203669269</v>
+      </c>
+      <c r="O112" s="4">
+        <f>L112 - L133 - L121 - L144+O111*O7</f>
+        <v>1175936.6610351533</v>
+      </c>
+      <c r="P112" s="4">
+        <f>M112 - M133 - M121 - M144 + P111*P7</f>
+        <v>18954620.865377408</v>
+      </c>
+      <c r="R112" s="4">
+        <f>O112 - O133 - O121 - O144+R111*R7</f>
+        <v>1032133.964000222</v>
+      </c>
+      <c r="S112" s="4">
+        <f>P112 - P133 - P121 - P144 + S111*S7</f>
+        <v>16874657.962828044</v>
+      </c>
+      <c r="U112" s="4">
+        <f>R112 - R133 - R121 - R144+U111*U7</f>
+        <v>917853.92999855743</v>
+      </c>
+      <c r="V112" s="4">
+        <f>S112 - S133 - S121 - S144 + V111*V7</f>
+        <v>15623190.666785505</v>
+      </c>
+      <c r="X112" s="4">
+        <f>U112 - U133 - U121 - U144+X111*X7</f>
+        <v>869078.45031468186</v>
+      </c>
+      <c r="Y112" s="4">
+        <f>V112 - V133 - V121 - V144 + Y111*Y7</f>
+        <v>15387963.591322072</v>
+      </c>
+      <c r="Z112" s="38"/>
+    </row>
+    <row r="113" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A113" s="38" t="s">
+        <v>244</v>
+      </c>
+      <c r="B113" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E113" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="F112" s="4">
-        <f>F111/F7</f>
+      <c r="F113" s="4">
+        <f>F112/F7</f>
         <v>150</v>
       </c>
-      <c r="G112" s="4">
-        <f>G111/G7</f>
+      <c r="G113" s="4">
+        <f>G112/G7</f>
         <v>100</v>
       </c>
-      <c r="I112" s="4">
-        <f>I111/I7</f>
-        <v>142.85659720585321</v>
-      </c>
-      <c r="J112" s="4">
-        <f>J111/J7</f>
-        <v>93.062653492604085</v>
-      </c>
-      <c r="L112" s="4">
-        <f>L111/L7</f>
-        <v>135.42657957448452</v>
-      </c>
-      <c r="M112" s="4">
-        <f>M111/M7</f>
-        <v>85.950234751890633</v>
-      </c>
-      <c r="O112" s="4">
-        <f>O111/O7</f>
-        <v>128.4129495566479</v>
-      </c>
-      <c r="P112" s="4">
-        <f>P111/P7</f>
-        <v>78.583377629613665</v>
-      </c>
-      <c r="R112" s="4">
-        <f>R111/R7</f>
-        <v>121.75045066759871</v>
-      </c>
-      <c r="S112" s="4">
-        <f>S111/S7</f>
-        <v>70.829833385840843</v>
-      </c>
-      <c r="U112" s="4">
-        <f>U111/U7</f>
-        <v>113.65579206455347</v>
-      </c>
-      <c r="V112" s="4">
-        <f>V111/V7</f>
-        <v>59.961397475795287</v>
-      </c>
-      <c r="X112" s="4">
-        <f>X111/X7</f>
-        <v>85.746418203205948</v>
-      </c>
-      <c r="Y112" s="4">
-        <f>Y111/Y7</f>
-        <v>12.782217051291566</v>
-      </c>
-      <c r="Z112" s="38"/>
-    </row>
-    <row r="113" spans="1:26" ht="34" x14ac:dyDescent="0.2">
-      <c r="A113" s="38" t="s">
+      <c r="I113" s="4">
+        <f>I112/I7</f>
+        <v>140.72809830378597</v>
+      </c>
+      <c r="J113" s="4">
+        <f>J112/J7</f>
+        <v>92.042239772433305</v>
+      </c>
+      <c r="L113" s="4">
+        <f>L112/L7</f>
+        <v>131.13030398947745</v>
+      </c>
+      <c r="M113" s="4">
+        <f>M112/M7</f>
+        <v>84.008511964727447</v>
+      </c>
+      <c r="O113" s="4">
+        <f>O112/O7</f>
+        <v>119.62733072585486</v>
+      </c>
+      <c r="P113" s="4">
+        <f>P112/P7</f>
+        <v>75.910790983345379</v>
+      </c>
+      <c r="R113" s="4">
+        <f>R112/R7</f>
+        <v>105.75143073772767</v>
+      </c>
+      <c r="S113" s="4">
+        <f>S112/S7</f>
+        <v>67.63281535698043</v>
+      </c>
+      <c r="U113" s="4">
+        <f>U112/U7</f>
+        <v>95.015934782459368</v>
+      </c>
+      <c r="V113" s="4">
+        <f>V112/V7</f>
+        <v>62.62678398486964</v>
+      </c>
+      <c r="X113" s="4">
+        <f>X112/X7</f>
+        <v>90.888773302100176</v>
+      </c>
+      <c r="Y113" s="4">
+        <f>Y112/Y7</f>
+        <v>61.709831534015365</v>
+      </c>
+      <c r="Z113" s="38"/>
+    </row>
+    <row r="114" spans="1:26" ht="34" x14ac:dyDescent="0.2">
+      <c r="A114" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B113" s="28" t="s">
+      <c r="B114" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="E114" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F113" s="4">
-        <f>MAX(F112-$F21,0)</f>
-        <v>149.85</v>
-      </c>
-      <c r="G113" s="4">
-        <f>MAX(G112-$G21,0)</f>
-        <v>99.9</v>
-      </c>
-      <c r="I113" s="4">
-        <f>MAX(I112-$F21,0)</f>
-        <v>142.7065972058532</v>
-      </c>
-      <c r="J113" s="4">
-        <f>MAX(J112-$G21,0)</f>
-        <v>92.96265349260409</v>
-      </c>
-      <c r="L113" s="4">
-        <f>MAX(L112-$F21,0)</f>
-        <v>135.27657957448451</v>
-      </c>
-      <c r="M113" s="4">
-        <f>MAX(M112-$G21,0)</f>
-        <v>85.850234751890639</v>
-      </c>
-      <c r="O113" s="4">
-        <f>MAX(O112-$F21,0)</f>
-        <v>128.2629495566479</v>
-      </c>
-      <c r="P113" s="4">
-        <f>MAX(P112-$G21,0)</f>
-        <v>78.48337762961367</v>
-      </c>
-      <c r="R113" s="4">
-        <f>MAX(R112-$F21,0)</f>
-        <v>121.60045066759871</v>
-      </c>
-      <c r="S113" s="4">
-        <f>MAX(S112-$G21,0)</f>
-        <v>70.729833385840848</v>
-      </c>
-      <c r="U113" s="4">
-        <f>MAX(U112-$F21,0)</f>
-        <v>113.50579206455346</v>
-      </c>
-      <c r="V113" s="4">
-        <f>MAX(V112-$G21,0)</f>
-        <v>59.861397475795286</v>
-      </c>
-      <c r="X113" s="4">
-        <f>MAX(X112-$F21,0)</f>
-        <v>85.596418203205943</v>
-      </c>
-      <c r="Y113" s="4">
-        <f>MAX(Y112-$G21,0)</f>
-        <v>12.682217051291566</v>
-      </c>
-      <c r="Z113" s="38"/>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="E114" s="13"/>
-    </row>
-    <row r="115" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="E115" s="11" t="s">
+      <c r="F114" s="4">
+        <f>MAX(F113-$F22,0)</f>
+        <v>100.4134425</v>
+      </c>
+      <c r="G114" s="4">
+        <f>MAX(G113-$G22,0)</f>
+        <v>62.199106999999998</v>
+      </c>
+      <c r="I114" s="4">
+        <f>MAX(I113-$F22,0)</f>
+        <v>91.141540803785972</v>
+      </c>
+      <c r="J114" s="4">
+        <f>MAX(J113-$G22,0)</f>
+        <v>54.241346772433303</v>
+      </c>
+      <c r="L114" s="4">
+        <f>MAX(L113-$F22,0)</f>
+        <v>81.543746489477456</v>
+      </c>
+      <c r="M114" s="4">
+        <f>MAX(M113-$G22,0)</f>
+        <v>46.207618964727445</v>
+      </c>
+      <c r="O114" s="4">
+        <f>MAX(O113-$F22,0)</f>
+        <v>70.040773225854863</v>
+      </c>
+      <c r="P114" s="4">
+        <f>MAX(P113-$G22,0)</f>
+        <v>38.109897983345377</v>
+      </c>
+      <c r="R114" s="4">
+        <f>MAX(R113-$F22,0)</f>
+        <v>56.164873237727676</v>
+      </c>
+      <c r="S114" s="4">
+        <f>MAX(S113-$G22,0)</f>
+        <v>29.831922356980428</v>
+      </c>
+      <c r="U114" s="4">
+        <f>MAX(U113-$F22,0)</f>
+        <v>45.42937728245937</v>
+      </c>
+      <c r="V114" s="4">
+        <f>MAX(V113-$G22,0)</f>
+        <v>24.825890984869638</v>
+      </c>
+      <c r="X114" s="4">
+        <f>MAX(X113-$F22,0)</f>
+        <v>41.302215802100179</v>
+      </c>
+      <c r="Y114" s="4">
+        <f>MAX(Y113-$G22,0)</f>
+        <v>23.908938534015363</v>
+      </c>
+      <c r="Z114" s="38"/>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="E115" s="13"/>
+    </row>
+    <row r="116" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="E116" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F115" s="12"/>
-      <c r="G115" s="12"/>
-      <c r="I115" s="12"/>
-      <c r="J115" s="12"/>
-      <c r="L115" s="12"/>
-      <c r="M115" s="12"/>
-      <c r="O115" s="12"/>
-      <c r="P115" s="12"/>
-      <c r="R115" s="12"/>
-      <c r="S115" s="12"/>
-      <c r="U115" s="12"/>
-      <c r="V115" s="12"/>
-      <c r="X115" s="12"/>
-      <c r="Y115" s="12"/>
-    </row>
-    <row r="116" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="B116" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F116" s="4">
-        <f>F112*F7</f>
-        <v>1500000</v>
-      </c>
-      <c r="G116" s="4">
-        <f>G112*G7</f>
-        <v>25000000</v>
-      </c>
-      <c r="I116" s="4">
-        <f>I112*I7</f>
-        <v>1421423.1421982395</v>
-      </c>
-      <c r="J116" s="4">
-        <f>J112*J7</f>
-        <v>23256357.107801761</v>
-      </c>
-      <c r="L116" s="4">
-        <f>L112*L7</f>
-        <v>1339098.0188325029</v>
-      </c>
-      <c r="M116" s="4">
-        <f>M112*M7</f>
-        <v>21469509.138674762</v>
-      </c>
-      <c r="O116" s="4">
-        <f>O112*O7</f>
-        <v>1262299.2941418488</v>
-      </c>
-      <c r="P116" s="4">
-        <f>P112*P7</f>
-        <v>19621955.060604014</v>
-      </c>
-      <c r="R116" s="4">
-        <f>R112*R7</f>
-        <v>1188284.3985157635</v>
-      </c>
-      <c r="S116" s="4">
-        <f>S112*S7</f>
-        <v>17672326.749100834</v>
-      </c>
-      <c r="U116" s="4">
-        <f>U112*U7</f>
-        <v>1097914.9513435864</v>
-      </c>
-      <c r="V116" s="4">
-        <f>V112*V7</f>
-        <v>14958270.021299271</v>
-      </c>
-      <c r="X116" s="4">
-        <f>X112*X7</f>
-        <v>819907.25085905532</v>
-      </c>
-      <c r="Y116" s="4">
-        <f>Y112*Y7</f>
-        <v>3187373.6439100648</v>
-      </c>
-      <c r="Z116" s="38"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="I116" s="12"/>
+      <c r="J116" s="12"/>
+      <c r="L116" s="12"/>
+      <c r="M116" s="12"/>
+      <c r="O116" s="12"/>
+      <c r="P116" s="12"/>
+      <c r="R116" s="12"/>
+      <c r="S116" s="12"/>
+      <c r="U116" s="12"/>
+      <c r="V116" s="12"/>
+      <c r="X116" s="12"/>
+      <c r="Y116" s="12"/>
     </row>
     <row r="117" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="B117" s="33" t="s">
-        <v>163</v>
+        <v>246</v>
+      </c>
+      <c r="B117" s="34" t="s">
+        <v>182</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="F117" s="4">
+        <f>F113*F7</f>
+        <v>1500000</v>
       </c>
       <c r="G117" s="4">
-        <f>SUM(G95:G98)</f>
-        <v>0</v>
+        <f>G113*G7</f>
+        <v>25000000</v>
+      </c>
+      <c r="I117" s="4">
+        <f>I113*I7</f>
+        <v>1400244.5781226703</v>
       </c>
       <c r="J117" s="4">
-        <f>SUM(J95:J98)</f>
-        <v>0.85</v>
+        <f>J113*J7</f>
+        <v>23001355.719131082</v>
+      </c>
+      <c r="L117" s="4">
+        <f>L113*L7</f>
+        <v>1296616.445847953</v>
       </c>
       <c r="M117" s="4">
-        <f>SUM(M95:M98)</f>
-        <v>5.8982999999999999</v>
+        <f>M113*M7</f>
+        <v>20984486.203669269</v>
+      </c>
+      <c r="O117" s="4">
+        <f>O113*O7</f>
+        <v>1175936.6610351533</v>
       </c>
       <c r="P117" s="4">
-        <f>SUM(P95:P98)</f>
-        <v>21.0065034</v>
+        <f>P113*P7</f>
+        <v>18954620.865377408</v>
+      </c>
+      <c r="R117" s="4">
+        <f>R113*R7</f>
+        <v>1032133.964000222</v>
       </c>
       <c r="S117" s="4">
-        <f>SUM(S95:S98)</f>
-        <v>52.594490393199997</v>
+        <f>S113*S7</f>
+        <v>16874657.962828044</v>
+      </c>
+      <c r="U117" s="4">
+        <f>U113*U7</f>
+        <v>917853.92999855755</v>
       </c>
       <c r="V117" s="4">
-        <f>SUM(V95:V98)</f>
-        <v>82.193263680000001</v>
+        <f>V113*V7</f>
+        <v>15623190.666785505</v>
+      </c>
+      <c r="X117" s="4">
+        <f>X113*X7</f>
+        <v>869078.45031468186</v>
       </c>
       <c r="Y117" s="4">
-        <f>SUM(Y95:Y98)</f>
-        <v>127.95464609634348</v>
+        <f>Y113*Y7</f>
+        <v>15387963.591322072</v>
       </c>
       <c r="Z117" s="38"/>
     </row>
     <row r="118" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" s="38" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B118" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="F118" s="4">
-        <f>F116+F117</f>
-        <v>1500000</v>
+        <v>218</v>
       </c>
       <c r="G118" s="4">
-        <f>G116+G117</f>
-        <v>25000000</v>
-      </c>
-      <c r="I118" s="4">
-        <f>I116+I117</f>
-        <v>1421423.1421982395</v>
+        <f>SUM(G96:G99)</f>
+        <v>0</v>
       </c>
       <c r="J118" s="4">
-        <f>J116+J117</f>
-        <v>23256357.957801763</v>
-      </c>
-      <c r="L118" s="4">
-        <f>L116+L117</f>
-        <v>1339098.0188325029</v>
+        <f>SUM(J96:J99)</f>
+        <v>0.85</v>
       </c>
       <c r="M118" s="4">
-        <f>M116+M117</f>
-        <v>21469515.036974762</v>
-      </c>
-      <c r="O118" s="4">
-        <f>O116+O117</f>
-        <v>1262299.2941418488</v>
+        <f>SUM(M96:M99)</f>
+        <v>5.8887158504999997</v>
       </c>
       <c r="P118" s="4">
-        <f>P116+P117</f>
-        <v>19621976.067107413</v>
-      </c>
-      <c r="R118" s="4">
-        <f>R116+R117</f>
-        <v>1188284.3985157635</v>
+        <f>SUM(P96:P99)</f>
+        <v>20.930540379888164</v>
       </c>
       <c r="S118" s="4">
-        <f>S116+S117</f>
-        <v>17672379.343591228</v>
-      </c>
-      <c r="U118" s="4">
-        <f>U116+U117</f>
-        <v>1097914.9513435864</v>
+        <f>SUM(S96:S99)</f>
+        <v>52.282677618991166</v>
       </c>
       <c r="V118" s="4">
-        <f>V116+V117</f>
-        <v>14958352.214562951</v>
-      </c>
-      <c r="X118" s="4">
-        <f>X116+X117</f>
-        <v>819907.25085905532</v>
+        <f>SUM(V96:V99)</f>
+        <v>111.37860050074056</v>
       </c>
       <c r="Y118" s="4">
-        <f>Y116+Y117</f>
-        <v>3187501.5985561614</v>
+        <f>SUM(Y96:Y99)</f>
+        <v>213.25999723115103</v>
       </c>
       <c r="Z118" s="38"/>
     </row>
     <row r="119" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A119" s="38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B119" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F119" s="4">
-        <f>F111*$F$20</f>
-        <v>315000</v>
+        <f>F117+F118</f>
+        <v>1500000</v>
       </c>
       <c r="G119" s="4">
-        <f>G111*$G$20</f>
-        <v>6250000</v>
+        <f>G117+G118</f>
+        <v>25000000</v>
       </c>
       <c r="I119" s="4">
-        <f>I111*$F$20</f>
-        <v>298498.85986163025</v>
+        <f>I117+I118</f>
+        <v>1400244.5781226703</v>
       </c>
       <c r="J119" s="4">
-        <f>J111*$G$20</f>
-        <v>5814089.2769504404</v>
+        <f>J117+J118</f>
+        <v>23001356.569131084</v>
       </c>
       <c r="L119" s="4">
-        <f>L111*$F$20</f>
-        <v>281210.58395482559</v>
+        <f>L117+L118</f>
+        <v>1296616.445847953</v>
       </c>
       <c r="M119" s="4">
-        <f>M111*$G$20</f>
-        <v>5367377.2846686905</v>
+        <f>M117+M118</f>
+        <v>20984492.092385121</v>
       </c>
       <c r="O119" s="4">
-        <f>O111*$F$20</f>
-        <v>265082.85176978825</v>
+        <f>O117+O118</f>
+        <v>1175936.6610351533</v>
       </c>
       <c r="P119" s="4">
-        <f>P111*$G$20</f>
-        <v>4905488.7651510034</v>
+        <f>P117+P118</f>
+        <v>18954641.795917787</v>
       </c>
       <c r="R119" s="4">
-        <f>R111*$F$20</f>
-        <v>249539.7236883103</v>
+        <f>R117+R118</f>
+        <v>1032133.964000222</v>
       </c>
       <c r="S119" s="4">
-        <f>S111*$G$20</f>
-        <v>4418081.6872752085</v>
+        <f>S117+S118</f>
+        <v>16874710.245505664</v>
       </c>
       <c r="U119" s="4">
-        <f>U111*$F$20</f>
-        <v>230562.13978215316</v>
+        <f>U117+U118</f>
+        <v>917853.92999855755</v>
       </c>
       <c r="V119" s="4">
-        <f>V111*$G$20</f>
-        <v>3739567.5053248177</v>
+        <f>V117+V118</f>
+        <v>15623302.045386005</v>
       </c>
       <c r="X119" s="4">
-        <f>X111*$F$20</f>
-        <v>172180.5226804016</v>
+        <f>X117+X118</f>
+        <v>869078.45031468186</v>
       </c>
       <c r="Y119" s="4">
-        <f>Y111*$G$20</f>
-        <v>796843.41097751621</v>
+        <f>Y117+Y118</f>
+        <v>15388176.851319304</v>
       </c>
       <c r="Z119" s="38"/>
     </row>
     <row r="120" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="B120" s="28" t="s">
-        <v>174</v>
+        <v>243</v>
+      </c>
+      <c r="B120" s="33" t="s">
+        <v>163</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="F120" s="4">
-        <f>F9*F112</f>
-        <v>7500</v>
+        <f>F112*$F$21</f>
+        <v>450000</v>
       </c>
       <c r="G120" s="4">
-        <f>G9*G112</f>
-        <v>10000</v>
+        <f>G112*$G$21</f>
+        <v>6250000</v>
       </c>
       <c r="I120" s="4">
-        <f>I9*I112</f>
-        <v>8857.1090267628988</v>
+        <f>I112*$F$21</f>
+        <v>420073.37343680114</v>
       </c>
       <c r="J120" s="4">
-        <f>J9*J112</f>
-        <v>10236.891884186449</v>
+        <f>J112*$G$21</f>
+        <v>5750338.9297827706</v>
       </c>
       <c r="L120" s="4">
-        <f>L9*L112</f>
-        <v>7854.741615320102</v>
+        <f>L112*$F$21</f>
+        <v>388984.93375438586</v>
       </c>
       <c r="M120" s="4">
-        <f>M9*M112</f>
-        <v>8079.3220666777197</v>
+        <f>M112*$G$21</f>
+        <v>5246121.5509173172</v>
       </c>
       <c r="O120" s="4">
-        <f>O9*O112</f>
-        <v>8988.9064689653533</v>
+        <f>O112*$F$21</f>
+        <v>352780.99831054598</v>
       </c>
       <c r="P120" s="4">
-        <f>P9*P112</f>
-        <v>15088.008504885824</v>
+        <f>P112*$G$21</f>
+        <v>4738655.2163443519</v>
       </c>
       <c r="R120" s="4">
-        <f>R9*R112</f>
-        <v>12175.045066759871</v>
+        <f>R112*$F$21</f>
+        <v>309640.18920006661</v>
       </c>
       <c r="S120" s="4">
-        <f>S9*S112</f>
-        <v>2762.3635020477927</v>
+        <f>S112*$G$21</f>
+        <v>4218664.490707011</v>
       </c>
       <c r="U120" s="4">
-        <f>U9*U112</f>
-        <v>11138.267622326241</v>
+        <f>U112*$F$21</f>
+        <v>275356.17899956723</v>
       </c>
       <c r="V120" s="4">
-        <f>V9*V112</f>
-        <v>6295.9467349585047</v>
+        <f>V112*$G$21</f>
+        <v>3905797.6666963762</v>
       </c>
       <c r="X120" s="4">
-        <f>X9*X112</f>
-        <v>8403.1489839141832</v>
+        <f>X112*$F$21</f>
+        <v>260723.53509440453</v>
       </c>
       <c r="Y120" s="4">
-        <f>Y9*Y112</f>
-        <v>1482.7371779498217</v>
+        <f>Y112*$G$21</f>
+        <v>3846990.897830518</v>
       </c>
       <c r="Z120" s="38"/>
     </row>
     <row r="121" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" s="38" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B121" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F121" s="4">
-        <f>MIN(F120,F9*F15)</f>
-        <v>250</v>
+        <f>F9*F113</f>
+        <v>7500</v>
       </c>
       <c r="G121" s="4">
-        <f>MIN(G120,G9*G15)</f>
-        <v>1000</v>
+        <f>G9*G113</f>
+        <v>10000</v>
       </c>
       <c r="I121" s="4">
-        <f>MIN(I120,I9*I15)</f>
-        <v>316.2</v>
+        <f>I9*I113</f>
+        <v>8725.1420948347295</v>
       </c>
       <c r="J121" s="4">
-        <f>MIN(J120,J9*J15)</f>
-        <v>1078</v>
+        <f>J9*J113</f>
+        <v>10124.646374967664</v>
       </c>
       <c r="L121" s="4">
-        <f>MIN(L120,L9*L15)</f>
-        <v>301.60000000000002</v>
+        <f>L9*L113</f>
+        <v>7605.5576313896927</v>
       </c>
       <c r="M121" s="4">
-        <f>MIN(M120,M9*M15)</f>
-        <v>921.2</v>
+        <f>M9*M113</f>
+        <v>7896.8001246843796</v>
       </c>
       <c r="O121" s="4">
-        <f>MIN(O120,O9*O15)</f>
-        <v>329</v>
+        <f>O9*O113</f>
+        <v>8373.9131508098399</v>
       </c>
       <c r="P121" s="4">
-        <f>MIN(P120,P9*P15)</f>
-        <v>1900.8000000000002</v>
+        <f>P9*P113</f>
+        <v>14574.871868802313</v>
       </c>
       <c r="R121" s="4">
-        <f>MIN(R120,R9*R15)</f>
-        <v>520</v>
+        <f>R9*R113</f>
+        <v>10575.143073772768</v>
       </c>
       <c r="S121" s="4">
-        <f>MIN(S120,S9*S15)</f>
-        <v>393.9</v>
+        <f>S9*S113</f>
+        <v>2637.6797989222368</v>
       </c>
       <c r="U121" s="4">
-        <f>MIN(U120,U9*U15)</f>
-        <v>401.79999999999995</v>
+        <f>U9*U113</f>
+        <v>9311.5616086810187</v>
       </c>
       <c r="V121" s="4">
-        <f>MIN(V120,V9*V15)</f>
-        <v>1155</v>
+        <f>V9*V113</f>
+        <v>6575.8123184113119</v>
       </c>
       <c r="X121" s="4">
-        <f>MIN(X120,X9*X15)</f>
-        <v>499.79999999999995</v>
+        <f>X9*X113</f>
+        <v>8907.0997836058177</v>
       </c>
       <c r="Y121" s="4">
-        <f>MIN(Y120,Y9*Y15)</f>
-        <v>1044</v>
+        <f>Y9*Y113</f>
+        <v>7158.340457945782</v>
       </c>
       <c r="Z121" s="38"/>
     </row>
     <row r="122" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A122" s="38" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="B122" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F122" s="4">
-        <f>(F120-F121)*$F$14</f>
-        <v>5075</v>
+        <f>MIN(F121,F9*F15)</f>
+        <v>250</v>
       </c>
       <c r="G122" s="4">
-        <f>(G120-G121+G53)*$F$14</f>
-        <v>6300</v>
+        <f>MIN(G121,G9*G15)</f>
+        <v>1000</v>
       </c>
       <c r="I122" s="4">
-        <f>(I120-I121)*$F$14</f>
-        <v>5978.6363187340285</v>
+        <f>MIN(I121,I9*I15)</f>
+        <v>316.2</v>
       </c>
       <c r="J122" s="4">
-        <f>(J120-J121+J53)*$F$14</f>
-        <v>6411.2243189305136</v>
+        <f>MIN(J121,J9*J15)</f>
+        <v>1078</v>
       </c>
       <c r="L122" s="4">
-        <f>(L120-L121)*$F$14</f>
-        <v>5287.1991307240705</v>
+        <f>MIN(L121,L9*L15)</f>
+        <v>301.60000000000002</v>
       </c>
       <c r="M122" s="4">
-        <f>(M120-M121+M53)*$F$14</f>
-        <v>5010.6854466744035</v>
+        <f>MIN(M121,M9*M15)</f>
+        <v>921.2</v>
       </c>
       <c r="O122" s="4">
-        <f>(O120-O121)*$F$14</f>
-        <v>6061.9345282757467</v>
+        <f>MIN(O121,O9*O15)</f>
+        <v>329</v>
       </c>
       <c r="P122" s="4">
-        <f>(P120-P121+P53)*$F$14</f>
-        <v>9231.0459534200763</v>
+        <f>MIN(P121,P9*P15)</f>
+        <v>1900.8000000000002</v>
       </c>
       <c r="R122" s="4">
-        <f>(R120-R121)*$F$14</f>
-        <v>8158.5315467319087</v>
+        <f>MIN(R121,R9*R15)</f>
+        <v>520</v>
       </c>
       <c r="S122" s="4">
-        <f>(S120-S121+S53)*$F$14</f>
-        <v>1657.9244514334548</v>
+        <f>MIN(S121,S9*S15)</f>
+        <v>393.9</v>
       </c>
       <c r="U122" s="4">
-        <f>(U120-U121)*$F$14</f>
-        <v>7515.5273356283687</v>
+        <f>MIN(U121,U9*U15)</f>
+        <v>401.79999999999995</v>
       </c>
       <c r="V122" s="4">
-        <f>(V120-V121+V53)*$F$14</f>
-        <v>3598.6627144709532</v>
+        <f>MIN(V121,V9*V15)</f>
+        <v>1155</v>
       </c>
       <c r="X122" s="4">
-        <f>(X120-X121)*$F$14</f>
-        <v>5532.3442887399278</v>
+        <f>MIN(X121,X9*X15)</f>
+        <v>499.79999999999995</v>
       </c>
       <c r="Y122" s="4">
-        <f>(Y120-Y121+Y53)*$F$14</f>
-        <v>307.11602456487515</v>
+        <f>MIN(Y121,Y9*Y15)</f>
+        <v>1044</v>
       </c>
       <c r="Z122" s="38"/>
     </row>
     <row r="123" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="B123" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>255</v>
+        <v>283</v>
+      </c>
+      <c r="B123" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>257</v>
       </c>
       <c r="F123" s="4">
-        <f>MIN(F122+G122, F32)</f>
-        <v>11375</v>
+        <f>(F121-F122)*$F$14</f>
+        <v>5075</v>
+      </c>
+      <c r="G123" s="4">
+        <f>(G121-G122+G54)*$F$14</f>
+        <v>6300</v>
       </c>
       <c r="I123" s="4">
-        <f>MIN(I122+J122, I32)</f>
-        <v>12389.860637664542</v>
+        <f>(I121-I122)*$F$14</f>
+        <v>5886.2594663843101</v>
+      </c>
+      <c r="J123" s="4">
+        <f>(J121-J122+J54)*$F$14</f>
+        <v>6332.6524624773647</v>
       </c>
       <c r="L123" s="4">
-        <f>MIN(L122+M122, L32)</f>
-        <v>10297.884577398474</v>
+        <f>(L121-L122)*$F$14</f>
+        <v>5112.7703419727841</v>
+      </c>
+      <c r="M123" s="4">
+        <f>(M121-M122+M54)*$F$14</f>
+        <v>4882.9200872790652</v>
       </c>
       <c r="O123" s="4">
-        <f>MIN(O122+P122, O32)</f>
-        <v>15292.980481695824</v>
+        <f>(O121-O122)*$F$14</f>
+        <v>5631.4392055668877</v>
+      </c>
+      <c r="P123" s="4">
+        <f>(P121-P122+P54)*$F$14</f>
+        <v>8871.8503081616182</v>
       </c>
       <c r="R123" s="4">
-        <f>MIN(R122+S122, R32)</f>
-        <v>9816.4559981653638</v>
+        <f>(R121-R122)*$F$14</f>
+        <v>7038.6001516409369</v>
+      </c>
+      <c r="S123" s="4">
+        <f>(S121-S122+S54)*$F$14</f>
+        <v>1570.6458592455656</v>
       </c>
       <c r="U123" s="4">
-        <f>MIN(U122+V122, U32)</f>
-        <v>11114.190050099322</v>
+        <f>(U121-U122)*$F$14</f>
+        <v>6236.8331260767136</v>
+      </c>
+      <c r="V123" s="4">
+        <f>(V121-V122+V54)*$F$14</f>
+        <v>3794.5686228879181</v>
       </c>
       <c r="X123" s="4">
-        <f>MIN(X122+Y122, X32)</f>
-        <v>5839.4603133048031</v>
+        <f>(X121-X122)*$F$14</f>
+        <v>5885.1098485240727</v>
+      </c>
+      <c r="Y123" s="4">
+        <f>(Y121-Y122+Y54)*$F$14</f>
+        <v>4280.0383205620474</v>
       </c>
       <c r="Z123" s="38"/>
     </row>
     <row r="124" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A124" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="F124" s="4">
+        <f>MIN(F123+G123, F33)</f>
+        <v>11375</v>
+      </c>
+      <c r="I124" s="4">
+        <f>MIN(I123+J123, I33)</f>
+        <v>12218.911928861675</v>
+      </c>
+      <c r="L124" s="4">
+        <f>MIN(L123+M123, L33)</f>
+        <v>9995.6904292518484</v>
+      </c>
+      <c r="O124" s="4">
+        <f>MIN(O123+P123, O33)</f>
+        <v>14503.289513728505</v>
+      </c>
+      <c r="R124" s="4">
+        <f>MIN(R123+S123, R33)</f>
+        <v>8609.2460108865016</v>
+      </c>
+      <c r="U124" s="4">
+        <f>MIN(U123+V123, U33)</f>
+        <v>10031.401748964632</v>
+      </c>
+      <c r="X124" s="4">
+        <f>MIN(X123+Y123, X33)</f>
+        <v>10165.14816908612</v>
+      </c>
+      <c r="Z124" s="38"/>
+    </row>
+    <row r="125" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="A125" s="38" t="s">
         <v>259</v>
-      </c>
-      <c r="B124" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="F124" s="4">
-        <f>F122/(F122+G122)</f>
-        <v>0.44615384615384618</v>
-      </c>
-      <c r="G124" s="4">
-        <f>G122/(F122+G122)</f>
-        <v>0.55384615384615388</v>
-      </c>
-      <c r="I124" s="4">
-        <f>I122/(I122+J122)</f>
-        <v>0.48254266077531816</v>
-      </c>
-      <c r="J124" s="4">
-        <f>J122/(I122+J122)</f>
-        <v>0.51745733922468184</v>
-      </c>
-      <c r="L124" s="4">
-        <f>L122/(L122+M122)</f>
-        <v>0.51342575176345207</v>
-      </c>
-      <c r="M124" s="4">
-        <f>M122/(L122+M122)</f>
-        <v>0.48657424823654793</v>
-      </c>
-      <c r="O124" s="4">
-        <f>O122/(O122+P122)</f>
-        <v>0.39638673020810294</v>
-      </c>
-      <c r="P124" s="4">
-        <f>P122/(O122+P122)</f>
-        <v>0.603613269791897</v>
-      </c>
-      <c r="R124" s="4">
-        <f>R122/(R122+S122)</f>
-        <v>0.83110763683519684</v>
-      </c>
-      <c r="S124" s="4">
-        <f>S122/(R122+S122)</f>
-        <v>0.16889236316480316</v>
-      </c>
-      <c r="U124" s="4">
-        <f>U122/(U122+V122)</f>
-        <v>0.67621007934457689</v>
-      </c>
-      <c r="V124" s="4">
-        <f>V122/(U122+V122)</f>
-        <v>0.32378992065542317</v>
-      </c>
-      <c r="X124" s="4">
-        <f>X122/(X122+Y122)</f>
-        <v>0.94740677937905793</v>
-      </c>
-      <c r="Y124" s="4">
-        <f>Y122/(X122+Y122)</f>
-        <v>5.2593220620942092E-2</v>
-      </c>
-      <c r="Z124" s="38"/>
-    </row>
-    <row r="125" spans="1:26" ht="34" x14ac:dyDescent="0.2">
-      <c r="A125" s="38" t="s">
-        <v>185</v>
       </c>
       <c r="B125" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E125" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="F125" s="4">
+        <f>F123/(F123+G123)</f>
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="G125" s="4">
+        <f>G123/(F123+G123)</f>
+        <v>0.55384615384615388</v>
+      </c>
+      <c r="I125" s="4">
+        <f>I123/(I123+J123)</f>
+        <v>0.48173352100858291</v>
+      </c>
+      <c r="J125" s="4">
+        <f>J123/(I123+J123)</f>
+        <v>0.51826647899141709</v>
+      </c>
+      <c r="L125" s="4">
+        <f>L123/(L123+M123)</f>
+        <v>0.51149746764971205</v>
+      </c>
+      <c r="M125" s="4">
+        <f>M123/(L123+M123)</f>
+        <v>0.48850253235028801</v>
+      </c>
+      <c r="O125" s="4">
+        <f>O123/(O123+P123)</f>
+        <v>0.3882870296587741</v>
+      </c>
+      <c r="P125" s="4">
+        <f>P123/(O123+P123)</f>
+        <v>0.61171297034122596</v>
+      </c>
+      <c r="R125" s="4">
+        <f>R123/(R123+S123)</f>
+        <v>0.81756290187788072</v>
+      </c>
+      <c r="S125" s="4">
+        <f>S123/(R123+S123)</f>
+        <v>0.18243709812211939</v>
+      </c>
+      <c r="U125" s="4">
+        <f>U123/(U123+V123)</f>
+        <v>0.62173096862763311</v>
+      </c>
+      <c r="V125" s="4">
+        <f>V123/(U123+V123)</f>
+        <v>0.37826903137236684</v>
+      </c>
+      <c r="X125" s="4">
+        <f>X123/(X123+Y123)</f>
+        <v>0.57894973596367783</v>
+      </c>
+      <c r="Y125" s="4">
+        <f>Y123/(X123+Y123)</f>
+        <v>0.42105026403632212</v>
+      </c>
+      <c r="Z125" s="38"/>
+    </row>
+    <row r="126" spans="1:26" ht="34" x14ac:dyDescent="0.2">
+      <c r="A126" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B126" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E126" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F125" s="4">
-        <f>MAX(F13-F26, 0)*F113</f>
-        <v>741757.5</v>
-      </c>
-      <c r="G125" s="4">
-        <f>MAX(G13-G26, 0)*G113</f>
-        <v>19970010</v>
-      </c>
-      <c r="I125" s="4">
-        <f>MAX(I13-I26, 0)*I113</f>
-        <v>697549.84714221046</v>
-      </c>
-      <c r="J125" s="4">
-        <f>MAX(J13-J26, 0)*J113</f>
-        <v>18573008.54128737</v>
-      </c>
-      <c r="L125" s="4">
-        <f>MAX(L13-L26, 0)*L113</f>
-        <v>585747.5895575179</v>
-      </c>
-      <c r="M125" s="4">
-        <f>MAX(M13-M26, 0)*M113</f>
-        <v>17143948.479013555</v>
-      </c>
-      <c r="O125" s="4">
-        <f>MAX(O13-O26, 0)*O113</f>
-        <v>482268.69033299608</v>
-      </c>
-      <c r="P125" s="4">
-        <f>MAX(P13-P26, 0)*P113</f>
-        <v>15657747.770618446</v>
-      </c>
-      <c r="R125" s="4">
-        <f>MAX(R13-R26, 0)*R113</f>
-        <v>384257.42410961189</v>
-      </c>
-      <c r="S125" s="4">
-        <f>MAX(S13-S26, 0)*S113</f>
-        <v>14178856.049692586</v>
-      </c>
-      <c r="U125" s="4">
-        <f>MAX(U13-U26, 0)*U113</f>
-        <v>268100.68085647526</v>
-      </c>
-      <c r="V125" s="4">
-        <f>MAX(V13-V26, 0)*V113</f>
-        <v>11963898.899512446</v>
-      </c>
-      <c r="X125" s="4">
-        <f>MAX(X13-X26, 0)*X113</f>
-        <v>193790.29081205826</v>
-      </c>
-      <c r="Y125" s="4">
-        <f>MAX(Y13-Y26, 0)*Y113</f>
-        <v>2533196.7626931826</v>
-      </c>
-      <c r="Z125" s="38"/>
-    </row>
-    <row r="127" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="E127" s="15" t="s">
+      <c r="F126" s="4">
+        <f>MAX(F13-F27, 0)*F114</f>
+        <v>497046.54037499998</v>
+      </c>
+      <c r="G126" s="4">
+        <f>MAX(G13-G27, 0)*G114</f>
+        <v>12433601.4893</v>
+      </c>
+      <c r="I126" s="4">
+        <f>MAX(I13-I27, 0)*I114</f>
+        <v>445499.85144890583</v>
+      </c>
+      <c r="J126" s="4">
+        <f>MAX(J13-J27, 0)*J114</f>
+        <v>10836878.67166445</v>
+      </c>
+      <c r="L126" s="4">
+        <f>MAX(L13-L27, 0)*L114</f>
+        <v>353084.4222994374</v>
+      </c>
+      <c r="M126" s="4">
+        <f>MAX(M13-M27, 0)*M114</f>
+        <v>9227476.6767802127</v>
+      </c>
+      <c r="O126" s="4">
+        <f>MAX(O13-O27, 0)*O114</f>
+        <v>263353.30732921429</v>
+      </c>
+      <c r="P126" s="4">
+        <f>MAX(P13-P27, 0)*P114</f>
+        <v>7603077.087269336</v>
+      </c>
+      <c r="R126" s="4">
+        <f>MAX(R13-R27, 0)*R114</f>
+        <v>177480.99943121945</v>
+      </c>
+      <c r="S126" s="4">
+        <f>MAX(S13-S27, 0)*S114</f>
+        <v>5980256.3152920818</v>
+      </c>
+      <c r="U126" s="4">
+        <f>MAX(U13-U27, 0)*U114</f>
+        <v>107304.18914116903</v>
+      </c>
+      <c r="V126" s="4">
+        <f>MAX(V13-V27, 0)*V114</f>
+        <v>4961702.5722360462</v>
+      </c>
+      <c r="X126" s="4">
+        <f>MAX(X13-X27, 0)*X114</f>
+        <v>93508.216575954808</v>
+      </c>
+      <c r="Y126" s="4">
+        <f>MAX(Y13-Y27, 0)*Y114</f>
+        <v>4775667.0185383642</v>
+      </c>
+      <c r="Z126" s="38"/>
+    </row>
+    <row r="128" spans="1:26" ht="17" x14ac:dyDescent="0.2">
+      <c r="E128" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
-      <c r="O127" s="8"/>
-      <c r="P127" s="8"/>
-      <c r="R127" s="8"/>
-      <c r="S127" s="8"/>
-      <c r="U127" s="8"/>
-      <c r="V127" s="8"/>
-      <c r="X127" s="8"/>
-      <c r="Y127" s="8"/>
-    </row>
-    <row r="128" spans="1:26" ht="17" x14ac:dyDescent="0.2">
-      <c r="A128" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="B128" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="E128" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="F128" s="4">
-        <f>MAX(F32-F123,0)</f>
-        <v>1988625</v>
-      </c>
-      <c r="I128" s="4">
-        <f>MAX(I32-I123,0)</f>
-        <v>2037610.1393623354</v>
-      </c>
-      <c r="L128" s="4">
-        <f>MAX(L32-L123,0)</f>
-        <v>2099702.1154226013</v>
-      </c>
-      <c r="O128" s="4">
-        <f>MAX(O32-O123,0)</f>
-        <v>2194707.0195183042</v>
-      </c>
-      <c r="R128" s="4">
-        <f>MAX(R32-R123,0)</f>
-        <v>2990183.5440018345</v>
-      </c>
-      <c r="U128" s="4">
-        <f>MAX(U32-U123,0)</f>
-        <v>24988885.809949901</v>
-      </c>
-      <c r="X128" s="4">
-        <f>MAX(X32-X123,0)</f>
-        <v>2514160.5396866952</v>
-      </c>
-      <c r="Z128" s="38"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
+      <c r="L128" s="8"/>
+      <c r="M128" s="8"/>
+      <c r="O128" s="8"/>
+      <c r="P128" s="8"/>
+      <c r="R128" s="8"/>
+      <c r="S128" s="8"/>
+      <c r="U128" s="8"/>
+      <c r="V128" s="8"/>
+      <c r="X128" s="8"/>
+      <c r="Y128" s="8"/>
     </row>
     <row r="129" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A129" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B129" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E129" s="10" t="s">
-        <v>165</v>
+      <c r="E129" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="F129" s="4">
-        <f>MIN(F139,F128)</f>
+        <f>MAX(F33-F124,0)</f>
         <v>1988625</v>
       </c>
       <c r="I129" s="4">
-        <f>MIN(I139,I128)</f>
-        <v>2037610.1393623354</v>
+        <f>MAX(I33-I124,0)</f>
+        <v>2037781.0880711384</v>
       </c>
       <c r="L129" s="4">
-        <f>MIN(L139,L128)</f>
-        <v>2099702.1154226013</v>
+        <f>MAX(L33-L124,0)</f>
+        <v>2100004.3095707484</v>
       </c>
       <c r="O129" s="4">
-        <f>MIN(O139,O128)</f>
-        <v>2194707.0195183042</v>
+        <f>MAX(O33-O124,0)</f>
+        <v>2195496.7104862714</v>
       </c>
       <c r="R129" s="4">
-        <f>MIN(R139,R128)</f>
-        <v>2990183.5440018345</v>
+        <f>MAX(R33-R124,0)</f>
+        <v>2991390.7539891135</v>
       </c>
       <c r="U129" s="4">
-        <f>MIN(U139,U128)</f>
-        <v>12231999.580368921</v>
+        <f>MAX(U33-U124,0)</f>
+        <v>24989968.598251034</v>
       </c>
       <c r="X129" s="4">
-        <f>MIN(X139,X128)</f>
-        <v>1789059.8013981958</v>
+        <f>MAX(X33-X124,0)</f>
+        <v>2509834.8518309137</v>
       </c>
       <c r="Z129" s="38"/>
     </row>
     <row r="130" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A130" s="38" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B130" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="F130" s="4">
-        <f>F128-F129</f>
-        <v>0</v>
+        <f>MIN(F140,F129)</f>
+        <v>1988625</v>
       </c>
       <c r="I130" s="4">
-        <f>I128-I129</f>
-        <v>0</v>
+        <f>MIN(I140,I129)</f>
+        <v>2037781.0880711384</v>
       </c>
       <c r="L130" s="4">
-        <f>L128-L129</f>
-        <v>0</v>
+        <f>MIN(L140,L129)</f>
+        <v>2100004.3095707484</v>
       </c>
       <c r="O130" s="4">
-        <f>O128-O129</f>
-        <v>0</v>
+        <f>MIN(O140,O129)</f>
+        <v>2195496.7104862714</v>
       </c>
       <c r="R130" s="4">
-        <f>R128-R129</f>
-        <v>0</v>
+        <f>MIN(R140,R129)</f>
+        <v>1365522.3071443853</v>
       </c>
       <c r="U130" s="4">
-        <f>U128-U129</f>
-        <v>12756886.22958098</v>
+        <f>MIN(U140,U129)</f>
+        <v>249661.00634800739</v>
       </c>
       <c r="X130" s="4">
-        <f>X128-X129</f>
-        <v>725100.73828849941</v>
+        <f>MIN(X140,X129)</f>
+        <v>81322.864565083524</v>
       </c>
       <c r="Z130" s="38"/>
     </row>
     <row r="131" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A131" s="38" t="s">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="B131" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F131" s="4">
-        <f>MIN(F130,G76)</f>
+        <f>F129-F130</f>
         <v>0</v>
       </c>
       <c r="I131" s="4">
-        <f>MIN(I130,J76)</f>
+        <f>I129-I130</f>
         <v>0</v>
       </c>
       <c r="L131" s="4">
-        <f>MIN(L130,M76)</f>
+        <f>L129-L130</f>
         <v>0</v>
       </c>
       <c r="O131" s="4">
-        <f>MIN(O130,P76)</f>
+        <f>O129-O130</f>
         <v>0</v>
       </c>
       <c r="R131" s="4">
-        <f>MIN(R130,S76)</f>
-        <v>0</v>
+        <f>R129-R130</f>
+        <v>1625868.4468447282</v>
       </c>
       <c r="U131" s="4">
-        <f>MIN(U130,V76)</f>
-        <v>30.146330393199996</v>
+        <f>U129-U130</f>
+        <v>24740307.591903027</v>
       </c>
       <c r="X131" s="4">
-        <f>MIN(X130,Y76)</f>
-        <v>53.914123679999996</v>
+        <f>X129-X130</f>
+        <v>2428511.9872658299</v>
       </c>
       <c r="Z131" s="38"/>
     </row>
     <row r="132" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A132" s="38" t="s">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="B132" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="F132" s="4">
-        <f>F140*F129</f>
-        <v>71219.296394549616</v>
-      </c>
-      <c r="G132" s="4">
-        <f>G140*F129</f>
-        <v>1917405.7036054505</v>
+        <f>MIN(F131,G77)</f>
+        <v>0</v>
       </c>
       <c r="I132" s="4">
-        <f>I140*I129</f>
-        <v>73756.795864359185</v>
-      </c>
-      <c r="J132" s="4">
-        <f>J140*I129</f>
-        <v>1963853.343497976</v>
+        <f>MIN(I131,J77)</f>
+        <v>0</v>
       </c>
       <c r="L132" s="4">
-        <f>L140*L129</f>
-        <v>69369.234990881247</v>
-      </c>
-      <c r="M132" s="4">
-        <f>M140*L129</f>
-        <v>2030332.8804317201</v>
+        <f>MIN(L131,M77)</f>
+        <v>0</v>
       </c>
       <c r="O132" s="4">
-        <f>O140*O129</f>
-        <v>65578.525432639595</v>
-      </c>
-      <c r="P132" s="4">
-        <f>P140*O129</f>
-        <v>2129128.4940856644</v>
+        <f>MIN(O131,P77)</f>
+        <v>0</v>
       </c>
       <c r="R132" s="4">
-        <f>R140*R129</f>
-        <v>78897.979357233533</v>
-      </c>
-      <c r="S132" s="4">
-        <f>S140*R129</f>
-        <v>2911285.5646446007</v>
+        <f>MIN(R131,S77)</f>
+        <v>0</v>
       </c>
       <c r="U132" s="4">
-        <f>U140*U129</f>
-        <v>268100.68085647526</v>
-      </c>
-      <c r="V132" s="4">
-        <f>V140*U129</f>
-        <v>11963898.899512446</v>
+        <f>MIN(U131,V77)</f>
+        <v>0</v>
       </c>
       <c r="X132" s="4">
-        <f>X140*X129</f>
-        <v>193790.29081205826</v>
-      </c>
-      <c r="Y132" s="4">
-        <f>Y140*X129</f>
-        <v>1595269.5105861374</v>
+        <f>MIN(X131,Y77)</f>
+        <v>0</v>
       </c>
       <c r="Z132" s="38"/>
     </row>
     <row r="133" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="B133" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F133" s="4">
+        <f>F141*F130</f>
+        <v>76441.580815194291</v>
+      </c>
+      <c r="G133" s="4">
+        <f>G141*F130</f>
+        <v>1912183.4191848056</v>
+      </c>
+      <c r="I133" s="4">
+        <f>I141*I130</f>
+        <v>80464.51997345034</v>
+      </c>
+      <c r="J133" s="4">
+        <f>J141*I130</f>
+        <v>1957316.568097688</v>
+      </c>
+      <c r="L133" s="4">
+        <f>L141*L130</f>
+        <v>100241.7582597421</v>
+      </c>
+      <c r="M133" s="4">
+        <f>M141*L130</f>
+        <v>1999762.5513110063</v>
+      </c>
+      <c r="O133" s="4">
+        <f>O141*O130</f>
+        <v>124509.76530548533</v>
+      </c>
+      <c r="P133" s="4">
+        <f>P141*O130</f>
+        <v>2070986.9451807863</v>
+      </c>
+      <c r="R133" s="4">
+        <f>R141*R130</f>
+        <v>94293.001358187947</v>
+      </c>
+      <c r="S133" s="4">
+        <f>S141*R130</f>
+        <v>1271229.3057861973</v>
+      </c>
+      <c r="U133" s="4">
+        <f>U141*U130</f>
+        <v>30365.318035164255</v>
+      </c>
+      <c r="V133" s="4">
+        <f>V141*U130</f>
+        <v>219295.68831284312</v>
+      </c>
+      <c r="X133" s="4">
+        <f>X141*X130</f>
+        <v>17535.251773675584</v>
+      </c>
+      <c r="Y133" s="4">
+        <f>Y141*X130</f>
+        <v>63787.612791407948</v>
+      </c>
+      <c r="Z133" s="38"/>
+    </row>
+    <row r="134" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A134" s="38" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="33" t="s">
+      <c r="B134" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="E134" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F133" s="4">
-        <f>F132</f>
-        <v>71219.296394549616</v>
-      </c>
-      <c r="G133" s="4">
-        <f>G132+F131</f>
-        <v>1917405.7036054505</v>
-      </c>
-      <c r="I133" s="4">
-        <f>I132</f>
-        <v>73756.795864359185</v>
-      </c>
-      <c r="J133" s="4">
-        <f>J132+I131</f>
-        <v>1963853.343497976</v>
-      </c>
-      <c r="L133" s="4">
-        <f>L132</f>
-        <v>69369.234990881247</v>
-      </c>
-      <c r="M133" s="4">
-        <f>M132+L131</f>
-        <v>2030332.8804317201</v>
-      </c>
-      <c r="O133" s="4">
-        <f>O132</f>
-        <v>65578.525432639595</v>
-      </c>
-      <c r="P133" s="4">
-        <f>P132+O131</f>
-        <v>2129128.4940856644</v>
-      </c>
-      <c r="R133" s="4">
-        <f>R132</f>
-        <v>78897.979357233533</v>
-      </c>
-      <c r="S133" s="4">
-        <f>S132+R131</f>
-        <v>2911285.5646446007</v>
-      </c>
-      <c r="U133" s="4">
-        <f>U132</f>
-        <v>268100.68085647526</v>
-      </c>
-      <c r="V133" s="4">
-        <f>V132+U131</f>
-        <v>11963929.045842839</v>
-      </c>
-      <c r="X133" s="4">
-        <f>X132</f>
-        <v>193790.29081205826</v>
-      </c>
-      <c r="Y133" s="4">
-        <f>Y132+X131</f>
-        <v>1595323.4247098174</v>
-      </c>
-      <c r="Z133" s="38"/>
-    </row>
-    <row r="134" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="E134" s="15" t="s">
+      <c r="F134" s="4">
+        <f>F133</f>
+        <v>76441.580815194291</v>
+      </c>
+      <c r="G134" s="4">
+        <f>G133+F132</f>
+        <v>1912183.4191848056</v>
+      </c>
+      <c r="I134" s="4">
+        <f>I133</f>
+        <v>80464.51997345034</v>
+      </c>
+      <c r="J134" s="4">
+        <f>J133+I132</f>
+        <v>1957316.568097688</v>
+      </c>
+      <c r="L134" s="4">
+        <f>L133</f>
+        <v>100241.7582597421</v>
+      </c>
+      <c r="M134" s="4">
+        <f>M133+L132</f>
+        <v>1999762.5513110063</v>
+      </c>
+      <c r="O134" s="4">
+        <f>O133</f>
+        <v>124509.76530548533</v>
+      </c>
+      <c r="P134" s="4">
+        <f>P133+O132</f>
+        <v>2070986.9451807863</v>
+      </c>
+      <c r="R134" s="4">
+        <f>R133</f>
+        <v>94293.001358187947</v>
+      </c>
+      <c r="S134" s="4">
+        <f>S133+R132</f>
+        <v>1271229.3057861973</v>
+      </c>
+      <c r="U134" s="4">
+        <f>U133</f>
+        <v>30365.318035164255</v>
+      </c>
+      <c r="V134" s="4">
+        <f>V133+U132</f>
+        <v>219295.68831284312</v>
+      </c>
+      <c r="X134" s="4">
+        <f>X133</f>
+        <v>17535.251773675584</v>
+      </c>
+      <c r="Y134" s="4">
+        <f>Y133+X132</f>
+        <v>63787.612791407948</v>
+      </c>
+      <c r="Z134" s="38"/>
+    </row>
+    <row r="135" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="E135" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="I134" s="8"/>
-      <c r="J134" s="8"/>
-      <c r="L134" s="8"/>
-      <c r="M134" s="8"/>
-      <c r="O134" s="8"/>
-      <c r="P134" s="8"/>
-      <c r="R134" s="8"/>
-      <c r="S134" s="8"/>
-      <c r="U134" s="8"/>
-      <c r="V134" s="8"/>
-      <c r="X134" s="8"/>
-      <c r="Y134" s="8"/>
-    </row>
-    <row r="135" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A135" s="38" t="s">
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8"/>
+      <c r="L135" s="8"/>
+      <c r="M135" s="8"/>
+      <c r="O135" s="8"/>
+      <c r="P135" s="8"/>
+      <c r="R135" s="8"/>
+      <c r="S135" s="8"/>
+      <c r="U135" s="8"/>
+      <c r="V135" s="8"/>
+      <c r="X135" s="8"/>
+      <c r="Y135" s="8"/>
+    </row>
+    <row r="136" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A136" s="38" t="s">
         <v>276</v>
-      </c>
-      <c r="B135" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F135" s="4">
-        <f>F113/$F$22</f>
-        <v>1</v>
-      </c>
-      <c r="G135" s="4">
-        <f>G113/$G$22</f>
-        <v>1</v>
-      </c>
-      <c r="I135" s="4">
-        <f>I113/$F$22</f>
-        <v>0.95232964435003808</v>
-      </c>
-      <c r="J135" s="4">
-        <f>J113/$G$22</f>
-        <v>0.93055709201805892</v>
-      </c>
-      <c r="L135" s="4">
-        <f>L113/$F$22</f>
-        <v>0.9027466104403371</v>
-      </c>
-      <c r="M135" s="4">
-        <f>M113/$G$22</f>
-        <v>0.85936170922813448</v>
-      </c>
-      <c r="O135" s="4">
-        <f>O113/$F$22</f>
-        <v>0.85594227265030298</v>
-      </c>
-      <c r="P135" s="4">
-        <f>P113/$G$22</f>
-        <v>0.78561939569182848</v>
-      </c>
-      <c r="R135" s="4">
-        <f>R113/$F$22</f>
-        <v>0.81148115226959439</v>
-      </c>
-      <c r="S135" s="4">
-        <f>S113/$G$22</f>
-        <v>0.70800634019860709</v>
-      </c>
-      <c r="U135" s="4">
-        <f>U113/$F$22</f>
-        <v>0.75746274317353002</v>
-      </c>
-      <c r="V135" s="4">
-        <f>V113/$G$22</f>
-        <v>0.59921318794589873</v>
-      </c>
-      <c r="X135" s="4">
-        <f>X113/$F$22</f>
-        <v>0.57121400202339634</v>
-      </c>
-      <c r="Y135" s="4">
-        <f>Y113/$G$22</f>
-        <v>0.12694911963254821</v>
-      </c>
-      <c r="Z135" s="38"/>
-      <c r="AA135">
-        <v>0.5</v>
-      </c>
-      <c r="AB135">
-        <f>SUM(AA$6:AA135)</f>
-        <v>0.5</v>
-      </c>
-      <c r="AC135">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="136" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A136" s="38" t="s">
-        <v>186</v>
       </c>
       <c r="B136" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="F136" s="4">
-        <f>MAX(MIN((F135-$F$16)/$F$17, 1), 0)</f>
+        <f>F114/$F$23</f>
         <v>1</v>
       </c>
       <c r="G136" s="4">
-        <f>MAX(MIN((G135-$G$16)/$G$17, 1), 0)</f>
+        <f>G114/$G$23</f>
         <v>1</v>
       </c>
       <c r="I136" s="4">
-        <f>MAX(MIN((I135-$F$16)/$F$17, 1), 0)</f>
-        <v>1</v>
+        <f>I114/$F$23</f>
+        <v>0.90766274449544915</v>
       </c>
       <c r="J136" s="4">
-        <f>MAX(MIN((J135-$G$16)/$G$17, 1), 0)</f>
-        <v>1</v>
+        <f>J114/$G$23</f>
+        <v>0.87205989585080868</v>
       </c>
       <c r="L136" s="4">
-        <f>MAX(MIN((L135-$F$16)/$F$17, 1), 0)</f>
-        <v>1</v>
+        <f>L114/$F$23</f>
+        <v>0.81207998111883728</v>
       </c>
       <c r="M136" s="4">
-        <f>MAX(MIN((M135-$G$16)/$G$17, 1), 0)</f>
-        <v>1</v>
+        <f>M114/$G$23</f>
+        <v>0.74289843043449877</v>
       </c>
       <c r="O136" s="4">
-        <f>MAX(MIN((O135-$F$16)/$F$17, 1), 0)</f>
-        <v>1</v>
+        <f>O114/$F$23</f>
+        <v>0.69752387212354428</v>
       </c>
       <c r="P136" s="4">
-        <f>MAX(MIN((P135-$G$16)/$G$17, 1), 0)</f>
-        <v>1</v>
+        <f>P114/$G$23</f>
+        <v>0.61270812108838446</v>
       </c>
       <c r="R136" s="4">
-        <f>MAX(MIN((R135-$F$16)/$F$17, 1), 0)</f>
-        <v>1</v>
+        <f>R114/$F$23</f>
+        <v>0.55933619881349728</v>
       </c>
       <c r="S136" s="4">
-        <f>MAX(MIN((S135-$G$16)/$G$17, 1), 0)</f>
-        <v>1</v>
+        <f>S114/$G$23</f>
+        <v>0.47961978548953171</v>
       </c>
       <c r="U136" s="4">
-        <f>MAX(MIN((U135-$F$16)/$F$17, 1), 0)</f>
-        <v>1</v>
+        <f>U114/$F$23</f>
+        <v>0.45242326277638945</v>
       </c>
       <c r="V136" s="4">
-        <f>MAX(MIN((V135-$G$16)/$G$17, 1), 0)</f>
-        <v>1</v>
+        <f>V114/$G$23</f>
+        <v>0.3991358105007784</v>
       </c>
       <c r="X136" s="4">
-        <f>MAX(MIN((X135-$F$16)/$F$17, 1), 0)</f>
-        <v>1</v>
+        <f>X114/$F$23</f>
+        <v>0.41132157979844358</v>
       </c>
       <c r="Y136" s="4">
-        <f>MAX(MIN((Y135-$G$16)/$G$17, 1), 0)</f>
-        <v>0.629745598162741</v>
+        <f>Y114/$G$23</f>
+        <v>0.38439359803052098</v>
       </c>
       <c r="Z136" s="38"/>
       <c r="AA136">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AB136">
         <f>SUM(AA$6:AA136)</f>
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AC136">
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A137" s="38"/>
+    <row r="137" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A137" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B137" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F137" s="4">
+        <f>MAX(MIN((F136-$F$17)/$F$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="G137" s="4">
+        <f>MAX(MIN((G136-$G$17)/$G$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="I137" s="4">
+        <f>MAX(MIN((I136-$F$17)/$F$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J137" s="4">
+        <f>MAX(MIN((J136-$G$17)/$G$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="L137" s="4">
+        <f>MAX(MIN((L136-$F$17)/$F$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="M137" s="4">
+        <f>MAX(MIN((M136-$G$17)/$G$18, 1), 0)</f>
+        <v>0.76335289475554091</v>
+      </c>
+      <c r="O137" s="4">
+        <f>MAX(MIN((O136-$F$17)/$F$18, 1), 0)</f>
+        <v>0.85222104179390024</v>
+      </c>
+      <c r="P137" s="4">
+        <f>MAX(MIN((P136-$G$17)/$G$18, 1), 0)</f>
+        <v>0.49099331907540816</v>
+      </c>
+      <c r="R137" s="4">
+        <f>MAX(MIN((R136-$F$17)/$F$18, 1), 0)</f>
+        <v>0.53128504831712997</v>
+      </c>
+      <c r="S137" s="4">
+        <f>MAX(MIN((S136-$G$17)/$G$18, 1), 0)</f>
+        <v>0.2125710402304235</v>
+      </c>
+      <c r="U137" s="4">
+        <f>MAX(MIN((U136-$F$17)/$F$18, 1), 0)</f>
+        <v>0.28298352821263806</v>
+      </c>
+      <c r="V137" s="4">
+        <f>MAX(MIN((V136-$G$17)/$G$18, 1), 0)</f>
+        <v>4.4197669070279458E-2</v>
+      </c>
+      <c r="X137" s="4">
+        <f>MAX(MIN((X136-$F$17)/$F$18, 1), 0)</f>
+        <v>0.18752632031466515</v>
+      </c>
+      <c r="Y137" s="4">
+        <f>MAX(MIN((Y136-$G$17)/$G$18, 1), 0)</f>
+        <v>1.3356796557170923E-2</v>
+      </c>
       <c r="Z137" s="38"/>
       <c r="AA137">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AB137">
         <f>SUM(AA$6:AA137)</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AC137">
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A138" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="B138" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="E138" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F138" s="4">
-        <f>F125*F136</f>
-        <v>741757.5</v>
-      </c>
-      <c r="G138" s="4">
-        <f>G125*G136</f>
-        <v>19970010</v>
-      </c>
-      <c r="I138" s="4">
-        <f>I125*I136</f>
-        <v>697549.84714221046</v>
-      </c>
-      <c r="J138" s="4">
-        <f>J125*J136</f>
-        <v>18573008.54128737</v>
-      </c>
-      <c r="L138" s="4">
-        <f>L125*L136</f>
-        <v>585747.5895575179</v>
-      </c>
-      <c r="M138" s="4">
-        <f>M125*M136</f>
-        <v>17143948.479013555</v>
-      </c>
-      <c r="O138" s="4">
-        <f>O125*O136</f>
-        <v>482268.69033299608</v>
-      </c>
-      <c r="P138" s="4">
-        <f>P125*P136</f>
-        <v>15657747.770618446</v>
-      </c>
-      <c r="R138" s="4">
-        <f>R125*R136</f>
-        <v>384257.42410961189</v>
-      </c>
-      <c r="S138" s="4">
-        <f>S125*S136</f>
-        <v>14178856.049692586</v>
-      </c>
-      <c r="U138" s="4">
-        <f>U125*U136</f>
-        <v>268100.68085647526</v>
-      </c>
-      <c r="V138" s="4">
-        <f>V125*V136</f>
-        <v>11963898.899512446</v>
-      </c>
-      <c r="X138" s="4">
-        <f>X125*X136</f>
-        <v>193790.29081205826</v>
-      </c>
-      <c r="Y138" s="4">
-        <f>Y125*Y136</f>
-        <v>1595269.5105861374</v>
-      </c>
+    <row r="138" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A138" s="38"/>
       <c r="Z138" s="38"/>
       <c r="AA138">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="AB138">
-        <f>SUM(AA$6:AA156)</f>
-        <v>1.125</v>
+        <f>SUM(AA$6:AA138)</f>
+        <v>1</v>
       </c>
       <c r="AC138">
         <v>20</v>
@@ -12140,578 +12135,644 @@
     </row>
     <row r="139" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A139" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B139" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F139" s="4">
-        <f>F138+G138</f>
-        <v>20711767.5</v>
+        <f>F126*F137</f>
+        <v>497046.54037499998</v>
       </c>
       <c r="G139" s="4">
-        <f>F139</f>
-        <v>20711767.5</v>
+        <f>G126*G137</f>
+        <v>12433601.4893</v>
       </c>
       <c r="I139" s="4">
-        <f>I138+J138</f>
-        <v>19270558.388429582</v>
+        <f>I126*I137</f>
+        <v>445499.85144890583</v>
       </c>
       <c r="J139" s="4">
-        <f>I139</f>
-        <v>19270558.388429582</v>
+        <f>J126*J137</f>
+        <v>10836878.67166445</v>
       </c>
       <c r="L139" s="4">
-        <f>L138+M138</f>
-        <v>17729696.068571072</v>
+        <f>L126*L137</f>
+        <v>353084.4222994374</v>
       </c>
       <c r="M139" s="4">
-        <f>L139</f>
-        <v>17729696.068571072</v>
+        <f>M126*M137</f>
+        <v>7043821.0325094145</v>
       </c>
       <c r="O139" s="4">
-        <f>O138+P138</f>
-        <v>16140016.460951442</v>
+        <f>O126*O137</f>
+        <v>224435.22993197219</v>
       </c>
       <c r="P139" s="4">
-        <f>O139</f>
-        <v>16140016.460951442</v>
+        <f>P126*P137</f>
+        <v>3733060.054264558</v>
       </c>
       <c r="R139" s="4">
-        <f>R138+S138</f>
-        <v>14563113.473802198</v>
+        <f>R126*R137</f>
+        <v>94293.001358187947</v>
       </c>
       <c r="S139" s="4">
-        <f>R139</f>
-        <v>14563113.473802198</v>
+        <f>S126*S137</f>
+        <v>1271229.3057861973</v>
       </c>
       <c r="U139" s="4">
-        <f>U138+V138</f>
-        <v>12231999.580368921</v>
+        <f>U126*U137</f>
+        <v>30365.318035164255</v>
       </c>
       <c r="V139" s="4">
-        <f>U139</f>
-        <v>12231999.580368921</v>
+        <f>V126*V137</f>
+        <v>219295.68831284312</v>
       </c>
       <c r="X139" s="4">
-        <f>X138+Y138</f>
-        <v>1789059.8013981958</v>
+        <f>X126*X137</f>
+        <v>17535.251773675584</v>
       </c>
       <c r="Y139" s="4">
-        <f>X139</f>
-        <v>1789059.8013981958</v>
+        <f>Y126*Y137</f>
+        <v>63787.612791407948</v>
       </c>
       <c r="Z139" s="38"/>
+      <c r="AA139">
+        <v>0.125</v>
+      </c>
+      <c r="AB139">
+        <f>SUM(AA$6:AA157)</f>
+        <v>1.125</v>
+      </c>
+      <c r="AC139">
+        <v>20</v>
+      </c>
     </row>
     <row r="140" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A140" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B140" s="28" t="s">
         <v>174</v>
       </c>
       <c r="E140" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F140" s="4">
+        <f>F139+G139</f>
+        <v>12930648.029674999</v>
+      </c>
+      <c r="G140" s="4">
+        <f>F140</f>
+        <v>12930648.029674999</v>
+      </c>
+      <c r="I140" s="4">
+        <f>I139+J139</f>
+        <v>11282378.523113357</v>
+      </c>
+      <c r="J140" s="4">
+        <f>I140</f>
+        <v>11282378.523113357</v>
+      </c>
+      <c r="L140" s="4">
+        <f>L139+M139</f>
+        <v>7396905.4548088517</v>
+      </c>
+      <c r="M140" s="4">
+        <f>L140</f>
+        <v>7396905.4548088517</v>
+      </c>
+      <c r="O140" s="4">
+        <f>O139+P139</f>
+        <v>3957495.28419653</v>
+      </c>
+      <c r="P140" s="4">
+        <f>O140</f>
+        <v>3957495.28419653</v>
+      </c>
+      <c r="R140" s="4">
+        <f>R139+S139</f>
+        <v>1365522.3071443853</v>
+      </c>
+      <c r="S140" s="4">
+        <f>R140</f>
+        <v>1365522.3071443853</v>
+      </c>
+      <c r="U140" s="4">
+        <f>U139+V139</f>
+        <v>249661.00634800739</v>
+      </c>
+      <c r="V140" s="4">
+        <f>U140</f>
+        <v>249661.00634800739</v>
+      </c>
+      <c r="X140" s="4">
+        <f>X139+Y139</f>
+        <v>81322.864565083524</v>
+      </c>
+      <c r="Y140" s="4">
+        <f>X140</f>
+        <v>81322.864565083524</v>
+      </c>
+      <c r="Z140" s="38"/>
+    </row>
+    <row r="141" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A141" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B141" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E141" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F140" s="4">
-        <f>F138/F139</f>
-        <v>3.5813336548896658E-2</v>
-      </c>
-      <c r="G140" s="4">
-        <f>G138/G139</f>
-        <v>0.96418666345110338</v>
-      </c>
-      <c r="I140" s="4">
-        <f>I138/I139</f>
-        <v>3.6197697704547727E-2</v>
-      </c>
-      <c r="J140" s="4">
-        <f>J138/J139</f>
-        <v>0.96380230229545216</v>
-      </c>
-      <c r="L140" s="4">
-        <f>L138/L139</f>
-        <v>3.3037655428050795E-2</v>
-      </c>
-      <c r="M140" s="4">
-        <f>M138/M139</f>
-        <v>0.96696234457194918</v>
-      </c>
-      <c r="O140" s="4">
-        <f>O138/O139</f>
-        <v>2.9880309694836998E-2</v>
-      </c>
-      <c r="P140" s="4">
-        <f>P138/P139</f>
-        <v>0.97011969030516298</v>
-      </c>
-      <c r="R140" s="4">
-        <f>R138/R139</f>
-        <v>2.6385664356791447E-2</v>
-      </c>
-      <c r="S140" s="4">
-        <f>S138/S139</f>
-        <v>0.97361433564320854</v>
-      </c>
-      <c r="U140" s="4">
-        <f>U138/U139</f>
-        <v>2.1917976623114736E-2</v>
-      </c>
-      <c r="V140" s="4">
-        <f>V138/V139</f>
-        <v>0.97808202337688521</v>
-      </c>
-      <c r="X140" s="4">
-        <f>X138/X139</f>
-        <v>0.10831962724812565</v>
-      </c>
-      <c r="Y140" s="4">
-        <f>Y138/Y139</f>
-        <v>0.89168037275187428</v>
-      </c>
-      <c r="Z140" s="38"/>
-    </row>
-    <row r="142" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="E142" s="15" t="s">
+      <c r="F141" s="4">
+        <f>F139/F140</f>
+        <v>3.8439414578009576E-2</v>
+      </c>
+      <c r="G141" s="4">
+        <f>G139/G140</f>
+        <v>0.96156058542199041</v>
+      </c>
+      <c r="I141" s="4">
+        <f>I139/I140</f>
+        <v>3.9486341513559745E-2</v>
+      </c>
+      <c r="J141" s="4">
+        <f>J139/J140</f>
+        <v>0.96051365848644021</v>
+      </c>
+      <c r="L141" s="4">
+        <f>L139/L140</f>
+        <v>4.773407264113283E-2</v>
+      </c>
+      <c r="M141" s="4">
+        <f>M139/M140</f>
+        <v>0.95226592735886717</v>
+      </c>
+      <c r="O141" s="4">
+        <f>O139/O140</f>
+        <v>5.6711433322033163E-2</v>
+      </c>
+      <c r="P141" s="4">
+        <f>P139/P140</f>
+        <v>0.9432885666779669</v>
+      </c>
+      <c r="R141" s="4">
+        <f>R139/R140</f>
+        <v>6.9052699369939879E-2</v>
+      </c>
+      <c r="S141" s="4">
+        <f>S139/S140</f>
+        <v>0.93094730063006004</v>
+      </c>
+      <c r="U141" s="4">
+        <f>U139/U140</f>
+        <v>0.12162619417161781</v>
+      </c>
+      <c r="V141" s="4">
+        <f>V139/V140</f>
+        <v>0.87837380582838209</v>
+      </c>
+      <c r="X141" s="4">
+        <f>X139/X140</f>
+        <v>0.21562511192214512</v>
+      </c>
+      <c r="Y141" s="4">
+        <f>Y139/Y140</f>
+        <v>0.78437488807785494</v>
+      </c>
+      <c r="Z141" s="38"/>
+    </row>
+    <row r="143" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="E143" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
-      <c r="I142" s="8"/>
-      <c r="J142" s="8"/>
-      <c r="L142" s="8"/>
-      <c r="M142" s="8"/>
-      <c r="O142" s="8"/>
-      <c r="P142" s="8"/>
-      <c r="R142" s="8"/>
-      <c r="S142" s="8"/>
-      <c r="U142" s="8"/>
-      <c r="V142" s="8"/>
-      <c r="X142" s="8"/>
-      <c r="Y142" s="8"/>
-    </row>
-    <row r="143" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A143" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="B143" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F143" s="4">
-        <f>(F111 - F132 - F120)*$F$29</f>
-        <v>2842.5614072109011</v>
-      </c>
-      <c r="G143" s="4">
-        <f>(G111 - G132 - G120)*$G$29+SUM(G90:G93)</f>
-        <v>46145.188592789098</v>
-      </c>
-      <c r="I143" s="4">
-        <f>(I111 - I132 - I120)*$F$29</f>
-        <v>2677.6184746142349</v>
-      </c>
-      <c r="J143" s="4">
-        <f>(J111 - J132 - J120)*$G$29+SUM(J90:J93)</f>
-        <v>42564.533744839202</v>
-      </c>
-      <c r="L143" s="4">
-        <f>(L111 - L132 - L120)*$F$29</f>
-        <v>2523.7480844526031</v>
-      </c>
-      <c r="M143" s="4">
-        <f>(M111 - M132 - M120)*$G$29+SUM(M90:M93)</f>
-        <v>38862.195572352735</v>
-      </c>
-      <c r="O143" s="4">
-        <f>(O111 - O132 - O120)*$F$29</f>
-        <v>2375.4637244804881</v>
-      </c>
-      <c r="P143" s="4">
-        <f>(P111 - P132 - P120)*$G$29+SUM(P90:P93)</f>
-        <v>34955.488912626926</v>
-      </c>
-      <c r="R143" s="4">
-        <f>(R111 - R132 - R120)*$F$29</f>
-        <v>2194.4227481835401</v>
-      </c>
-      <c r="S143" s="4">
-        <f>(S111 - S132 - S120)*$G$29+SUM(S90:S93)</f>
-        <v>29516.599654915171</v>
-      </c>
-      <c r="U143" s="4">
-        <f>(U111 - U132 - U120)*$F$29</f>
-        <v>1637.3520057295698</v>
-      </c>
-      <c r="V143" s="4">
-        <f>(V111 - V132 - V120)*$G$29+SUM(V90:V93)</f>
-        <v>5976.1952464237338</v>
-      </c>
-      <c r="X143" s="4">
-        <f>(X111 - X132 - X120)*$F$29</f>
-        <v>1235.4276221261657</v>
-      </c>
-      <c r="Y143" s="4">
-        <f>(Y111 - Y132 - Y120)*$G$29+SUM(Y90:Y93)</f>
-        <v>3181.2993505719551</v>
-      </c>
-      <c r="Z143" s="38"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8"/>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8"/>
+      <c r="L143" s="8"/>
+      <c r="M143" s="8"/>
+      <c r="O143" s="8"/>
+      <c r="P143" s="8"/>
+      <c r="R143" s="8"/>
+      <c r="S143" s="8"/>
+      <c r="U143" s="8"/>
+      <c r="V143" s="8"/>
+      <c r="X143" s="8"/>
+      <c r="Y143" s="8"/>
     </row>
     <row r="144" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B144" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E144" s="14" t="s">
-        <v>215</v>
+      <c r="E144" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="F144" s="4">
-        <f>F132*$F20</f>
-        <v>14956.05224285542</v>
+        <f>(F112 - F133 - F121)*$F$30</f>
+        <v>18798.841062135314</v>
       </c>
       <c r="G144" s="4">
-        <f>(G132+F131)*$G20</f>
-        <v>479351.42590136261</v>
+        <f>(G112 - G133 - G121)*$G$30+SUM(G91:G94)</f>
+        <v>306368.86168411467</v>
       </c>
       <c r="I144" s="4">
-        <f>I132*$F20</f>
-        <v>15488.927131515427</v>
+        <f>(I112 - I133 - I121)*$F$30</f>
+        <v>17404.870206432512</v>
       </c>
       <c r="J144" s="4">
-        <f>(J132+I131)*$G20</f>
-        <v>490963.33587449399</v>
+        <f>(J112 - J133 - J121)*$G$30+SUM(J91:J94)</f>
+        <v>279235.1009891578</v>
       </c>
       <c r="L144" s="4">
-        <f>L132*$F20</f>
-        <v>14567.539348085062</v>
+        <f>(L112 - L133 - L121)*$F$30</f>
+        <v>15781.46892166788</v>
       </c>
       <c r="M144" s="4">
-        <f>(M132+L131)*$G20</f>
-        <v>507583.22010793001</v>
+        <f>(M112 - M133 - M121)*$G$30+SUM(M91:M94)</f>
+        <v>251926.30685617079</v>
       </c>
       <c r="O144" s="4">
-        <f>O132*$F20</f>
-        <v>13771.490340854314</v>
+        <f>(O112 - O133 - O121)*$F$30</f>
+        <v>13847.018578636153</v>
       </c>
       <c r="P144" s="4">
-        <f>(P132+O131)*$G20</f>
-        <v>532282.1235214161</v>
+        <f>(P112 - P133 - P121)*$G$30+SUM(P91:P94)</f>
+        <v>223944.76549977509</v>
       </c>
       <c r="R144" s="4">
-        <f>R132*$F20</f>
-        <v>16568.575665019041</v>
+        <f>(R112 - R133 - R121)*$F$30</f>
+        <v>12309.889569703864</v>
       </c>
       <c r="S144" s="4">
-        <f>(S132+R131)*$G20</f>
-        <v>727821.39116115018</v>
+        <f>(S112 - S133 - S121)*$G$30+SUM(S91:S94)</f>
+        <v>207108.11045742003</v>
       </c>
       <c r="U144" s="4">
-        <f>U132*$F20</f>
-        <v>56301.142979859804</v>
+        <f>(U112 - U133 - U121)*$F$30</f>
+        <v>11658.213086672471</v>
       </c>
       <c r="V144" s="4">
-        <f>(V132+U131)*$G20</f>
-        <v>2990982.2614607099</v>
+        <f>(V112 - V133 - V121)*$G$30+SUM(V91:V94)</f>
+        <v>204407.342747824</v>
       </c>
       <c r="X144" s="4">
-        <f>X132*$F20</f>
-        <v>40695.961070532234</v>
+        <f>(X112 - X133 - X121)*$F$30</f>
+        <v>11186.390249970907</v>
       </c>
       <c r="Y144" s="4">
-        <f>(Y132+X131)*$G20</f>
-        <v>398830.85617745435</v>
+        <f>(Y112 - Y133 - Y121)*$G$30+SUM(Y91:Y94)</f>
+        <v>203342.08674697479</v>
       </c>
       <c r="Z144" s="38"/>
     </row>
     <row r="145" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A145" s="38" t="s">
-        <v>176</v>
+        <v>275</v>
       </c>
       <c r="B145" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E145" s="10" t="s">
-        <v>166</v>
+      <c r="E145" s="14" t="s">
+        <v>215</v>
       </c>
       <c r="F145" s="4">
-        <f>F120-F123*F124-F121</f>
-        <v>2175</v>
+        <f>F133*$F21</f>
+        <v>22932.474244558285</v>
       </c>
       <c r="G145" s="4">
-        <f>G120-F123*G124-G121+G53</f>
-        <v>2700</v>
+        <f>(G133+F132)*$G21</f>
+        <v>478045.8547962014</v>
       </c>
       <c r="I145" s="4">
-        <f>I120-I123*I124-I121</f>
-        <v>2562.2727080288705</v>
+        <f>I133*$F21</f>
+        <v>24139.3559920351</v>
       </c>
       <c r="J145" s="4">
-        <f>J120-I123*J124-J121+J53</f>
-        <v>2747.6675652559352</v>
+        <f>(J133+I132)*$G21</f>
+        <v>489329.14202442201</v>
       </c>
       <c r="L145" s="4">
-        <f>L120-L123*L124-L121</f>
-        <v>2265.9424845960316</v>
+        <f>L133*$F21</f>
+        <v>30072.527477922627</v>
       </c>
       <c r="M145" s="4">
-        <f>M120-L123*M124-M121+M53</f>
-        <v>2147.4366200033164</v>
+        <f>(M133+L132)*$G21</f>
+        <v>499940.63782775158</v>
       </c>
       <c r="O145" s="4">
-        <f>O120-O123*O124-O121</f>
-        <v>2597.9719406896065</v>
+        <f>O133*$F21</f>
+        <v>37352.929591645596</v>
       </c>
       <c r="P145" s="4">
-        <f>P120-O123*P124-P121+P53</f>
-        <v>3956.1625514657471</v>
+        <f>(P133+O132)*$G21</f>
+        <v>517746.73629519658</v>
       </c>
       <c r="R145" s="4">
-        <f>R120-R123*R124-R121</f>
-        <v>3496.5135200279619</v>
+        <f>R133*$F21</f>
+        <v>28287.900407456382</v>
       </c>
       <c r="S145" s="4">
-        <f>S120-R123*S124-S121+S53</f>
-        <v>710.53905061433773</v>
+        <f>(S133+R132)*$G21</f>
+        <v>317807.32644654933</v>
       </c>
       <c r="U145" s="4">
-        <f>U120-U123*U124-U121</f>
-        <v>3220.9402866978717</v>
+        <f>U133*$F21</f>
+        <v>9109.5954105492765</v>
       </c>
       <c r="V145" s="4">
-        <f>V120-U123*V124-V121+V53</f>
-        <v>1542.284020487552</v>
+        <f>(V133+U132)*$G21</f>
+        <v>54823.92207821078</v>
       </c>
       <c r="X145" s="4">
-        <f>X120-X123*X124-X121</f>
-        <v>2371.0046951742552</v>
+        <f>X133*$F21</f>
+        <v>5260.5755321026745</v>
       </c>
       <c r="Y145" s="4">
-        <f>Y120-X123*Y124-Y121+Y53</f>
-        <v>131.62115338494641</v>
+        <f>(Y133+X132)*$G21</f>
+        <v>15946.903197851987</v>
       </c>
       <c r="Z145" s="38"/>
     </row>
     <row r="146" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A146" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B146" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E146" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F146" s="4">
+        <f>F121-F124*F125-F122</f>
+        <v>2175</v>
+      </c>
+      <c r="G146" s="4">
+        <f>G121-F124*G125-G122+G54</f>
+        <v>2700</v>
+      </c>
+      <c r="I146" s="4">
+        <f>I121-I124*I125-I122</f>
+        <v>2522.6826284504195</v>
+      </c>
+      <c r="J146" s="4">
+        <f>J121-I124*J125-J122+J54</f>
+        <v>2713.9939124902994</v>
+      </c>
+      <c r="L146" s="4">
+        <f>L121-L124*L125-L122</f>
+        <v>2191.1872894169087</v>
+      </c>
+      <c r="M146" s="4">
+        <f>M121-L124*M125-M122+M54</f>
+        <v>2092.6800374053146</v>
+      </c>
+      <c r="O146" s="4">
+        <f>O121-O124*O125-O122</f>
+        <v>2413.4739452429521</v>
+      </c>
+      <c r="P146" s="4">
+        <f>P121-O124*P125-P122+P54</f>
+        <v>3802.2215606406944</v>
+      </c>
+      <c r="R146" s="4">
+        <f>R121-R124*R125-R122</f>
+        <v>3016.5429221318309</v>
+      </c>
+      <c r="S146" s="4">
+        <f>S121-R124*S125-S122+S54</f>
+        <v>673.13393967667128</v>
+      </c>
+      <c r="U146" s="4">
+        <f>U121-U124*U125-U122</f>
+        <v>2672.9284826043049</v>
+      </c>
+      <c r="V146" s="4">
+        <f>V121-U124*V125-V122+V54</f>
+        <v>1626.2436955233939</v>
+      </c>
+      <c r="X146" s="4">
+        <f>X121-X124*X125-X122</f>
+        <v>2522.1899350817448</v>
+      </c>
+      <c r="Y146" s="4">
+        <f>Y121-X124*Y125-Y122+Y54</f>
+        <v>1834.3021373837346</v>
+      </c>
+      <c r="Z146" s="38"/>
+    </row>
+    <row r="147" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B147" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E147" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="F146" s="4">
-        <f>(F120 - F121)*$F20</f>
-        <v>1522.5</v>
-      </c>
-      <c r="G146" s="4">
-        <f>(G120-G121+G53)*$G20</f>
-        <v>2250</v>
-      </c>
-      <c r="I146" s="4">
-        <f>(I120 - I121)*$F20</f>
-        <v>1793.5908956202086</v>
-      </c>
-      <c r="J146" s="4">
-        <f>(J120-J121+J53)*$G20</f>
-        <v>2289.7229710466122</v>
-      </c>
-      <c r="L146" s="4">
-        <f>(L120 - L121)*$F20</f>
-        <v>1586.1597392172214</v>
-      </c>
-      <c r="M146" s="4">
-        <f>(M120-M121+M53)*$G20</f>
-        <v>1789.53051666943</v>
-      </c>
-      <c r="O146" s="4">
-        <f>(O120 - O121)*$F20</f>
-        <v>1818.580358482724</v>
-      </c>
-      <c r="P146" s="4">
-        <f>(P120-P121+P53)*$G20</f>
-        <v>3296.8021262214561</v>
-      </c>
-      <c r="R146" s="4">
-        <f>(R120 - R121)*$F20</f>
-        <v>2447.5594640195727</v>
-      </c>
-      <c r="S146" s="4">
-        <f>(S120-S121+S53)*$G20</f>
-        <v>592.11587551194816</v>
-      </c>
-      <c r="U146" s="4">
-        <f>(U120 - U121)*$F20</f>
-        <v>2254.6582006885105</v>
-      </c>
-      <c r="V146" s="4">
-        <f>(V120-V121+V53)*$G20</f>
-        <v>1285.2366837396262</v>
-      </c>
-      <c r="X146" s="4">
-        <f>(X120 - X121)*$F20</f>
-        <v>1659.7032866219784</v>
-      </c>
-      <c r="Y146" s="4">
-        <f>(Y120-Y121+Y53)*$G20</f>
-        <v>109.68429448745542</v>
-      </c>
-      <c r="Z146" s="38"/>
-    </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A149" s="24" t="s">
+      <c r="F147" s="4">
+        <f>MAX((F121 - F122)*$F21-F16*F9,0)</f>
+        <v>2128.25</v>
+      </c>
+      <c r="G147" s="4">
+        <f>MAX((G121-G122+G54)*$G21-G16*G9,0)</f>
+        <v>2058</v>
+      </c>
+      <c r="I147" s="4">
+        <f>MAX((I121 - I122)*$F21-I16*I9,0)</f>
+        <v>2463.5532284504188</v>
+      </c>
+      <c r="J147" s="4">
+        <f>MAX((J121-J122+J54)*$G21-J16*J9,0)</f>
+        <v>2054.6855937419159</v>
+      </c>
+      <c r="L147" s="4">
+        <f>MAX((L121 - L122)*$F21-L16*L9,0)</f>
+        <v>2134.788089416908</v>
+      </c>
+      <c r="M147" s="4">
+        <f>MAX((M121-M122+M54)*$G21-M16*M9,0)</f>
+        <v>1567.0296311710949</v>
+      </c>
+      <c r="O147" s="4">
+        <f>MAX((O121 - O122)*$F21-O16*O9,0)</f>
+        <v>2351.9509452429515</v>
+      </c>
+      <c r="P147" s="4">
+        <f>MAX((P121-P122+P54)*$G21-P16*P9,0)</f>
+        <v>2803.5643672005781</v>
+      </c>
+      <c r="R147" s="4">
+        <f>MAX((R121 - R122)*$F21-R16*R9,0)</f>
+        <v>2919.3029221318302</v>
+      </c>
+      <c r="S147" s="4">
+        <f>MAX((S121-S122+S54)*$G21-S16*S9,0)</f>
+        <v>485.31614973055918</v>
+      </c>
+      <c r="U147" s="4">
+        <f>MAX((U121 - U122)*$F21-U16*U9,0)</f>
+        <v>2597.791882604306</v>
+      </c>
+      <c r="V147" s="4">
+        <f>MAX((V121-V122+V54)*$G21-V16*V9,0)</f>
+        <v>1133.443079602828</v>
+      </c>
+      <c r="X147" s="4">
+        <f>MAX((X121 - X122)*$F21-X16*X9,0)</f>
+        <v>2428.7273350817454</v>
+      </c>
+      <c r="Y147" s="4">
+        <f>MAX((Y121-Y122+Y54)*$G21-Y16*Y9,0)</f>
+        <v>1328.1371144864454</v>
+      </c>
+      <c r="Z147" s="38"/>
+    </row>
+    <row r="150" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A150" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="F149" s="4">
-        <f>F145+F121</f>
+      <c r="F150" s="4">
+        <f>F146+F122</f>
         <v>2425</v>
       </c>
-      <c r="G149" s="4">
-        <f>G145+G121</f>
+      <c r="G150" s="4">
+        <f>G146+G122</f>
         <v>3700</v>
       </c>
-      <c r="I149" s="4">
-        <f>I145+I121</f>
-        <v>2878.4727080288703</v>
-      </c>
-      <c r="J149" s="4">
-        <f>J145+J121</f>
-        <v>3825.6675652559352</v>
-      </c>
-      <c r="L149" s="4">
-        <f>L145+L121</f>
-        <v>2567.5424845960315</v>
-      </c>
-      <c r="M149" s="4">
-        <f>M145+M121</f>
-        <v>3068.6366200033162</v>
-      </c>
-      <c r="O149" s="4">
-        <f>O145+O121</f>
-        <v>2926.9719406896065</v>
-      </c>
-      <c r="P149" s="4">
-        <f>P145+P121</f>
-        <v>5856.9625514657473</v>
-      </c>
-      <c r="R149" s="4">
-        <f>R145+R121</f>
-        <v>4016.5135200279619</v>
-      </c>
-      <c r="S149" s="4">
-        <f>S145+S121</f>
-        <v>1104.4390506143377</v>
-      </c>
-      <c r="U149" s="4">
-        <f>U145+U121</f>
-        <v>3622.7402866978719</v>
-      </c>
-      <c r="V149" s="4">
-        <f>V145+V121</f>
-        <v>2697.284020487552</v>
-      </c>
-      <c r="X149" s="4">
-        <f>X145+X121</f>
-        <v>2870.8046951742554</v>
-      </c>
-      <c r="Y149" s="4">
-        <f>Y145+Y121</f>
-        <v>1175.6211533849464</v>
-      </c>
-    </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A151" s="38" t="s">
+      <c r="I150" s="4">
+        <f>I146+I122</f>
+        <v>2838.8826284504194</v>
+      </c>
+      <c r="J150" s="4">
+        <f>J146+J122</f>
+        <v>3791.9939124902994</v>
+      </c>
+      <c r="L150" s="4">
+        <f>L146+L122</f>
+        <v>2492.7872894169086</v>
+      </c>
+      <c r="M150" s="4">
+        <f>M146+M122</f>
+        <v>3013.8800374053144</v>
+      </c>
+      <c r="O150" s="4">
+        <f>O146+O122</f>
+        <v>2742.4739452429521</v>
+      </c>
+      <c r="P150" s="4">
+        <f>P146+P122</f>
+        <v>5703.0215606406946</v>
+      </c>
+      <c r="R150" s="4">
+        <f>R146+R122</f>
+        <v>3536.5429221318309</v>
+      </c>
+      <c r="S150" s="4">
+        <f>S146+S122</f>
+        <v>1067.0339396766713</v>
+      </c>
+      <c r="U150" s="4">
+        <f>U146+U122</f>
+        <v>3074.7284826043051</v>
+      </c>
+      <c r="V150" s="4">
+        <f>V146+V122</f>
+        <v>2781.2436955233939</v>
+      </c>
+      <c r="X150" s="4">
+        <f>X146+X122</f>
+        <v>3021.989935081745</v>
+      </c>
+      <c r="Y150" s="4">
+        <f>Y146+Y122</f>
+        <v>2878.3021373837346</v>
+      </c>
+    </row>
+    <row r="152" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A152" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="B151" s="33" t="s">
+      <c r="B152" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F151" s="4">
-        <f>F123+F132+G132+F131</f>
+      <c r="F152" s="4">
+        <f>F124+F133+G133+F132</f>
         <v>2000000</v>
       </c>
-      <c r="I151" s="4">
-        <f>I123+I132+J132</f>
-        <v>2049999.9999999998</v>
-      </c>
-      <c r="L151" s="4">
-        <f>L123+L132+M132</f>
-        <v>2110000</v>
-      </c>
-      <c r="O151" s="4">
-        <f>O123+O132+P132</f>
+      <c r="I152" s="4">
+        <f>I124+I133+J133</f>
+        <v>2050000</v>
+      </c>
+      <c r="L152" s="4">
+        <f>L124+L133+M133</f>
+        <v>2110000.0000000005</v>
+      </c>
+      <c r="O152" s="4">
+        <f>O124+O133+P133</f>
         <v>2210000</v>
       </c>
-      <c r="R151" s="4">
-        <f>R123+R132+S132</f>
-        <v>2999999.9999999995</v>
-      </c>
-      <c r="U151" s="4">
-        <f>U123+U132+V132</f>
-        <v>12243113.77041902</v>
-      </c>
-      <c r="X151" s="4">
-        <f>X123+X132+Y132</f>
-        <v>1794899.2617115006</v>
-      </c>
-      <c r="Z151" s="38"/>
-    </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F152" s="4">
-        <f>F151/F32</f>
+      <c r="R152" s="4">
+        <f>R124+R133+S133</f>
+        <v>1374131.5531552718</v>
+      </c>
+      <c r="U152" s="4">
+        <f>U124+U133+V133</f>
+        <v>259692.40809697201</v>
+      </c>
+      <c r="X152" s="4">
+        <f>X124+X133+Y133</f>
+        <v>91488.01273416965</v>
+      </c>
+      <c r="Z152" s="38"/>
+    </row>
+    <row r="153" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F153" s="4">
+        <f>F152/F33</f>
         <v>1</v>
       </c>
-      <c r="I152" s="4">
-        <f>I151/I32</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="L152" s="4">
-        <f>L151/L32</f>
+      <c r="I153" s="4">
+        <f>I152/I33</f>
         <v>1</v>
       </c>
-      <c r="O152" s="4">
-        <f>O151/O32</f>
+      <c r="L153" s="4">
+        <f>L152/L33</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="O153" s="4">
+        <f>O152/O33</f>
         <v>1</v>
       </c>
-      <c r="R152" s="4">
-        <f>R151/R32</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="U152" s="4">
-        <f>U151/U32</f>
-        <v>0.48972455081676081</v>
-      </c>
-      <c r="X152" s="4">
-        <f>X151/X32</f>
-        <v>0.71226161179027803</v>
-      </c>
-    </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="AA157">
-        <v>0.1225</v>
-      </c>
-      <c r="AB157">
-        <f>SUM(AA$6:AA157)</f>
-        <v>1.2475000000000001</v>
-      </c>
-      <c r="AC157">
-        <v>20</v>
+      <c r="R153" s="4">
+        <f>R152/R33</f>
+        <v>0.45804385105175727</v>
+      </c>
+      <c r="U153" s="4">
+        <f>U152/U33</f>
+        <v>1.038769632387888E-2</v>
+      </c>
+      <c r="X153" s="4">
+        <f>X152/X33</f>
+        <v>3.6304766958003831E-2</v>
       </c>
     </row>
     <row r="158" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AA158">
-        <v>0.12239999999999999</v>
+        <v>0.1225</v>
       </c>
       <c r="AB158">
         <f>SUM(AA$6:AA158)</f>
-        <v>1.3699000000000001</v>
+        <v>1.2475000000000001</v>
       </c>
       <c r="AC158">
         <v>20</v>
@@ -12719,21 +12780,33 @@
     </row>
     <row r="159" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AA159">
-        <v>0.12230000000000001</v>
+        <v>0.12239999999999999</v>
       </c>
       <c r="AB159">
         <f>SUM(AA$6:AA159)</f>
-        <v>1.4922000000000002</v>
+        <v>1.3699000000000001</v>
       </c>
       <c r="AC159">
         <v>20</v>
       </c>
     </row>
+    <row r="160" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AA160">
+        <v>0.12230000000000001</v>
+      </c>
+      <c r="AB160">
+        <f>SUM(AA$6:AA160)</f>
+        <v>1.4922000000000002</v>
+      </c>
+      <c r="AC160">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D70:D72"/>
+    <mergeCell ref="D75:D78"/>
     <mergeCell ref="X5:Y5"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="R5:S5"/>
@@ -12744,32 +12817,32 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A61:A64"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="D48:D51"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="B95:B98"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="A85:A88"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="A101:A104"/>
+    <mergeCell ref="B101:B104"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="B73:B76"/>
+    <mergeCell ref="A86:A89"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F350A9A-DF78-DF44-80EF-AAEC8D1A81A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8C1182-B23A-DD4C-B000-5DF68ADA57A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="760" windowWidth="23640" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="23640" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="303">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -950,6 +950,9 @@
   </si>
   <si>
     <t>arr_biomass_c_average_bg_stock_in_conversion_targets</t>
+  </si>
+  <si>
+    <t>arr_biomass_c_total_growth</t>
   </si>
 </sst>
 </file>
@@ -6395,7 +6398,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F0562-A765-A442-B9DB-CF71D123E451}">
-  <dimension ref="A1:AN160"/>
+  <dimension ref="A1:AN161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="24" customWidth="1"/>
@@ -12204,7 +12207,7 @@
         <v>0.125</v>
       </c>
       <c r="AB139">
-        <f>SUM(AA$6:AA157)</f>
+        <f>SUM(AA$6:AA158)</f>
         <v>1.125</v>
       </c>
       <c r="AC139">
@@ -12638,153 +12641,206 @@
       </c>
       <c r="Z147" s="38"/>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A150" s="24" t="s">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A148" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="B148" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F148" s="4">
+        <f>I111*I7*(1+$F21)</f>
+        <v>3880.5</v>
+      </c>
+      <c r="G148" s="4">
+        <f>(J111*J7+SUMPRODUCT(G38:G41,G86:G89))*(1+$G21)</f>
+        <v>287385</v>
+      </c>
+      <c r="I148" s="4">
+        <f>L111*L7*(1+$F21)</f>
+        <v>3856.32</v>
+      </c>
+      <c r="J148" s="4">
+        <f>(M111*M7+SUMPRODUCT(J38:J41,J86:J89))*(1+$G21)</f>
+        <v>287259.5625</v>
+      </c>
+      <c r="L148" s="4">
+        <f>O111*O7*(1+$F21)</f>
+        <v>3833.7000000000003</v>
+      </c>
+      <c r="M148" s="4">
+        <f>(P111*P7+SUMPRODUCT(M38:M41,M86:M89))*(1+$G21)</f>
+        <v>287156.71250000002</v>
+      </c>
+      <c r="O148" s="4">
+        <f>R111*R7*(1+$F21)</f>
+        <v>3806.4</v>
+      </c>
+      <c r="P148" s="4">
+        <f>(S111*S7+SUMPRODUCT(P38:P41,P86:P89))*(1+$G21)</f>
+        <v>286948.5</v>
+      </c>
+      <c r="R148" s="4">
+        <f>U111*U7*(1+$F21)</f>
+        <v>3767.4</v>
+      </c>
+      <c r="S148" s="4">
+        <f>(V111*V7+SUMPRODUCT(S38:S41,S86:S89))*(1+$G21)</f>
+        <v>286924.28750000003</v>
+      </c>
+      <c r="U148" s="4">
+        <f>X111*X7*(1+$F21)</f>
+        <v>3327.4969606347436</v>
+      </c>
+      <c r="V148" s="4">
+        <f>(Y111*Y7+SUMPRODUCT(V38:V41,V86:V89))*(1+$G21)</f>
+        <v>243889.44739455794</v>
+      </c>
+      <c r="X148" s="4">
+        <f>AA111*AA7*(1+$F21)</f>
+        <v>0</v>
+      </c>
+      <c r="Y148" s="4">
+        <f>(AB111*AB7+SUMPRODUCT(Y38:Y41,Y86:Y89))*(1+$G21)</f>
+        <v>129.19999999999999</v>
+      </c>
+      <c r="Z148" s="38"/>
+    </row>
+    <row r="151" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A151" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F151" s="4">
         <f>F146+F122</f>
         <v>2425</v>
       </c>
-      <c r="G150" s="4">
+      <c r="G151" s="4">
         <f>G146+G122</f>
         <v>3700</v>
       </c>
-      <c r="I150" s="4">
+      <c r="I151" s="4">
         <f>I146+I122</f>
         <v>2838.8826284504194</v>
       </c>
-      <c r="J150" s="4">
+      <c r="J151" s="4">
         <f>J146+J122</f>
         <v>3791.9939124902994</v>
       </c>
-      <c r="L150" s="4">
+      <c r="L151" s="4">
         <f>L146+L122</f>
         <v>2492.7872894169086</v>
       </c>
-      <c r="M150" s="4">
+      <c r="M151" s="4">
         <f>M146+M122</f>
         <v>3013.8800374053144</v>
       </c>
-      <c r="O150" s="4">
+      <c r="O151" s="4">
         <f>O146+O122</f>
         <v>2742.4739452429521</v>
       </c>
-      <c r="P150" s="4">
+      <c r="P151" s="4">
         <f>P146+P122</f>
         <v>5703.0215606406946</v>
       </c>
-      <c r="R150" s="4">
+      <c r="R151" s="4">
         <f>R146+R122</f>
         <v>3536.5429221318309</v>
       </c>
-      <c r="S150" s="4">
+      <c r="S151" s="4">
         <f>S146+S122</f>
         <v>1067.0339396766713</v>
       </c>
-      <c r="U150" s="4">
+      <c r="U151" s="4">
         <f>U146+U122</f>
         <v>3074.7284826043051</v>
       </c>
-      <c r="V150" s="4">
+      <c r="V151" s="4">
         <f>V146+V122</f>
         <v>2781.2436955233939</v>
       </c>
-      <c r="X150" s="4">
+      <c r="X151" s="4">
         <f>X146+X122</f>
         <v>3021.989935081745</v>
       </c>
-      <c r="Y150" s="4">
+      <c r="Y151" s="4">
         <f>Y146+Y122</f>
         <v>2878.3021373837346</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A152" s="38" t="s">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A153" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="B152" s="33" t="s">
+      <c r="B153" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F153" s="4">
         <f>F124+F133+G133+F132</f>
         <v>2000000</v>
       </c>
-      <c r="I152" s="4">
+      <c r="I153" s="4">
         <f>I124+I133+J133</f>
         <v>2050000</v>
       </c>
-      <c r="L152" s="4">
+      <c r="L153" s="4">
         <f>L124+L133+M133</f>
         <v>2110000.0000000005</v>
       </c>
-      <c r="O152" s="4">
+      <c r="O153" s="4">
         <f>O124+O133+P133</f>
         <v>2210000</v>
       </c>
-      <c r="R152" s="4">
+      <c r="R153" s="4">
         <f>R124+R133+S133</f>
         <v>1374131.5531552718</v>
       </c>
-      <c r="U152" s="4">
+      <c r="U153" s="4">
         <f>U124+U133+V133</f>
         <v>259692.40809697201</v>
       </c>
-      <c r="X152" s="4">
+      <c r="X153" s="4">
         <f>X124+X133+Y133</f>
         <v>91488.01273416965</v>
       </c>
-      <c r="Z152" s="38"/>
-    </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F153" s="4">
-        <f>F152/F33</f>
+      <c r="Z153" s="38"/>
+    </row>
+    <row r="154" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F154" s="4">
+        <f>F153/F33</f>
         <v>1</v>
       </c>
-      <c r="I153" s="4">
-        <f>I152/I33</f>
+      <c r="I154" s="4">
+        <f>I153/I33</f>
         <v>1</v>
       </c>
-      <c r="L153" s="4">
-        <f>L152/L33</f>
+      <c r="L154" s="4">
+        <f>L153/L33</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="O153" s="4">
-        <f>O152/O33</f>
+      <c r="O154" s="4">
+        <f>O153/O33</f>
         <v>1</v>
       </c>
-      <c r="R153" s="4">
-        <f>R152/R33</f>
+      <c r="R154" s="4">
+        <f>R153/R33</f>
         <v>0.45804385105175727</v>
       </c>
-      <c r="U153" s="4">
-        <f>U152/U33</f>
+      <c r="U154" s="4">
+        <f>U153/U33</f>
         <v>1.038769632387888E-2</v>
       </c>
-      <c r="X153" s="4">
-        <f>X152/X33</f>
+      <c r="X154" s="4">
+        <f>X153/X33</f>
         <v>3.6304766958003831E-2</v>
-      </c>
-    </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="AA158">
-        <v>0.1225</v>
-      </c>
-      <c r="AB158">
-        <f>SUM(AA$6:AA158)</f>
-        <v>1.2475000000000001</v>
-      </c>
-      <c r="AC158">
-        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AA159">
-        <v>0.12239999999999999</v>
+        <v>0.1225</v>
       </c>
       <c r="AB159">
         <f>SUM(AA$6:AA159)</f>
-        <v>1.3699000000000001</v>
+        <v>1.2475000000000001</v>
       </c>
       <c r="AC159">
         <v>20</v>
@@ -12792,13 +12848,25 @@
     </row>
     <row r="160" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AA160">
-        <v>0.12230000000000001</v>
+        <v>0.12239999999999999</v>
       </c>
       <c r="AB160">
         <f>SUM(AA$6:AA160)</f>
+        <v>1.3699000000000001</v>
+      </c>
+      <c r="AC160">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" spans="27:29" x14ac:dyDescent="0.2">
+      <c r="AA161">
+        <v>0.12230000000000001</v>
+      </c>
+      <c r="AB161">
+        <f>SUM(AA$6:AA161)</f>
         <v>1.4922000000000002</v>
       </c>
-      <c r="AC160">
+      <c r="AC161">
         <v>20</v>
       </c>
     </row>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8C1182-B23A-DD4C-B000-5DF68ADA57A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8405E880-F68F-1F45-BDD6-B68CBF1F15C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="23640" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="780" yWindow="760" windowWidth="33780" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="cl_1" sheetId="2" r:id="rId2"/>
     <sheet name="cl_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="304">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -953,6 +954,9 @@
   </si>
   <si>
     <t>arr_biomass_c_total_growth</t>
+  </si>
+  <si>
+    <t>arr_biomass_c_bg_lost_decomposition</t>
   </si>
 </sst>
 </file>
@@ -6398,7 +6402,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F0562-A765-A442-B9DB-CF71D123E451}">
-  <dimension ref="A1:AN161"/>
+  <dimension ref="A1:AN162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="24" customWidth="1"/>
@@ -7848,12 +7852,12 @@
         <v>171</v>
       </c>
       <c r="F30" s="4">
-        <f>0.01327547</f>
-        <v>1.3275469999999999E-2</v>
+        <f>0.00157</f>
+        <v>1.57E-3</v>
       </c>
       <c r="G30" s="4">
         <f>F30</f>
-        <v>1.3275469999999999E-2</v>
+        <v>1.57E-3</v>
       </c>
       <c r="I30" s="4">
         <f>F29/F20</f>
@@ -9140,23 +9144,23 @@
       </c>
       <c r="M68" s="4">
         <f>J68*(1- $F$30)+M38*M62</f>
-        <v>5.0887158504999999</v>
+        <v>5.0986655000000001</v>
       </c>
       <c r="P68" s="4">
         <f>M68*(1- $F$30)+P38*P62</f>
-        <v>15.221160755888162</v>
+        <v>15.290660595165001</v>
       </c>
       <c r="S68" s="4">
         <f>P68*(1- $F$30)+S38*S62</f>
-        <v>32.019092692908188</v>
+        <v>32.266654258030592</v>
       </c>
       <c r="V68" s="4">
         <f>S68*(1- $F$30)+V38*V62</f>
-        <v>62.194024188436266</v>
+        <v>62.815995610845476</v>
       </c>
       <c r="Y68" s="4">
         <f>V68*(1- $F$30)+Y38*Y62</f>
-        <v>112.36836928614341</v>
+        <v>113.71737449773644</v>
       </c>
       <c r="Z68" s="38"/>
     </row>
@@ -9176,19 +9180,19 @@
       </c>
       <c r="P69" s="4">
         <f>M69*(1- $F$30)+P39*P63</f>
-        <v>4.7893796240000004</v>
+        <v>4.7987440000000001</v>
       </c>
       <c r="S69" s="4">
         <f>P69*(1- $F$30)+S39*S63</f>
-        <v>14.325798358482977</v>
+        <v>14.39120997192</v>
       </c>
       <c r="V69" s="4">
         <f>S69*(1- $F$30)+V39*V63</f>
-        <v>30.13561665214889</v>
+        <v>30.368615772264086</v>
       </c>
       <c r="Y69" s="4">
         <f>V69*(1- $F$30)+Y39*Y63</f>
-        <v>58.535552177351789</v>
+        <v>59.120937045501634</v>
       </c>
       <c r="Z69" s="38"/>
     </row>
@@ -9209,15 +9213,15 @@
       </c>
       <c r="S70" s="4">
         <f>P70*(1- $F$30)+S40*S64</f>
-        <v>5.5077865676000002</v>
+        <v>5.5185556000000009</v>
       </c>
       <c r="V70" s="4">
         <f>S70*(1- $F$30)+V40*V64</f>
-        <v>16.474668112255422</v>
+        <v>16.549891467708001</v>
       </c>
       <c r="Y70" s="4">
         <f>V70*(1- $F$30)+Y40*Y64</f>
-        <v>34.655959149971224</v>
+        <v>34.923908138103698</v>
       </c>
       <c r="Z70" s="38"/>
     </row>
@@ -9242,11 +9246,11 @@
       </c>
       <c r="V71" s="4">
         <f>S71*(1- $F$30)+V41*V65</f>
-        <v>2.5742915478999997</v>
+        <v>2.5793249</v>
       </c>
       <c r="Y71" s="4">
         <f>V71*(1- $F$30)+Y41*Y65</f>
-        <v>7.7001166176845999</v>
+        <v>7.7352753599069999</v>
       </c>
       <c r="Z71" s="38"/>
     </row>
@@ -10050,23 +10054,23 @@
       </c>
       <c r="M91" s="4">
         <f>(J96-M80-M43)*$F$30</f>
-        <v>1.1284149499999998E-2</v>
+        <v>1.3345E-3</v>
       </c>
       <c r="P91" s="4">
         <f>(M96-P80-P43)*$F$30</f>
-        <v>6.755509461183723E-2</v>
+        <v>8.0049048349999999E-3</v>
       </c>
       <c r="S91" s="4">
         <f>(P96-S80-S43)*$F$30</f>
-        <v>0.2020680629799706</v>
+        <v>2.4006337134409049E-2</v>
       </c>
       <c r="V91" s="4">
         <f>(S96-V80-V43)*$F$30</f>
-        <v>0.42506850447192185</v>
+        <v>5.0658647185108027E-2</v>
       </c>
       <c r="Y91" s="4">
         <f>(V96-Y80-Y43)*$F$30</f>
-        <v>0.82565490229285987</v>
+        <v>9.8621113109027395E-2</v>
       </c>
       <c r="Z91" s="37"/>
     </row>
@@ -10090,19 +10094,19 @@
       </c>
       <c r="P92" s="4">
         <f>(M97-P81-P44)*$F$30</f>
-        <v>1.0620376000000001E-2</v>
+        <v>1.2560000000000002E-3</v>
       </c>
       <c r="S92" s="4">
         <f>(P97-S81-S44)*$F$30</f>
-        <v>6.3581265517023283E-2</v>
+        <v>7.5340280800000005E-3</v>
       </c>
       <c r="V92" s="4">
         <f>(S97-V81-V44)*$F$30</f>
-        <v>0.19018170633409001</v>
+        <v>2.2594199655914398E-2</v>
       </c>
       <c r="Y92" s="4">
         <f>(V97-Y81-Y44)*$F$30</f>
-        <v>0.40006447479710294</v>
+        <v>4.7678726762454618E-2</v>
       </c>
       <c r="Z92" s="37"/>
     </row>
@@ -10130,15 +10134,15 @@
       </c>
       <c r="S93" s="4">
         <f>(P98-S82-S45)*$F$30</f>
-        <v>1.22134324E-2</v>
+        <v>1.4444E-3</v>
       </c>
       <c r="V93" s="4">
         <f>(S98-V82-V45)*$F$30</f>
-        <v>7.3118455344576769E-2</v>
+        <v>8.664132292000002E-3</v>
       </c>
       <c r="Y93" s="4">
         <f>(V98-Y82-Y45)*$F$30</f>
-        <v>0.21870896228420347</v>
+        <v>2.5983329604301563E-2</v>
       </c>
       <c r="Z93" s="37"/>
     </row>
@@ -10170,11 +10174,11 @@
       </c>
       <c r="V94" s="4">
         <f>(S99-V83-V46)*$F$30</f>
-        <v>5.7084520999999997E-3</v>
+        <v>6.7509999999999998E-4</v>
       </c>
       <c r="Y94" s="4">
         <f>(V99-Y83-Y46)*$F$30</f>
-        <v>3.417493021540001E-2</v>
+        <v>4.049540093E-3</v>
       </c>
       <c r="Z94" s="37"/>
     </row>
@@ -10201,23 +10205,23 @@
       </c>
       <c r="M96" s="4">
         <f>J96 - M80 - M91 - M43 + M38*M86</f>
-        <v>5.0887158504999999</v>
+        <v>5.0986655000000001</v>
       </c>
       <c r="P96" s="4">
         <f>M96 - P80 - P91 - P43 + P38*P86</f>
-        <v>15.221160755888162</v>
+        <v>15.290660595164999</v>
       </c>
       <c r="S96" s="4">
         <f>P96 - S80 - S91 - S43 + S38*S86</f>
-        <v>32.019092692908188</v>
+        <v>32.266654258030592</v>
       </c>
       <c r="V96" s="4">
         <f>S96 - V80 - V91 - V43 + V38*V86</f>
-        <v>62.194024188436259</v>
+        <v>62.815995610845476</v>
       </c>
       <c r="Y96" s="4">
         <f>V96 - Y80 - Y91 - Y43 + Y38*Y86</f>
-        <v>112.36836928614341</v>
+        <v>113.71737449773644</v>
       </c>
       <c r="Z96" s="37"/>
     </row>
@@ -10241,19 +10245,19 @@
       </c>
       <c r="P97" s="4">
         <f>M97 - P81 - P92 - P44 + P39*P87</f>
-        <v>4.7893796240000004</v>
+        <v>4.7987440000000001</v>
       </c>
       <c r="S97" s="4">
         <f>P97 - S81 - S92 - S44 + S39*S87</f>
-        <v>14.325798358482977</v>
+        <v>14.391209971919999</v>
       </c>
       <c r="V97" s="4">
         <f>S97 - V81 - V92 - V44 + V39*V87</f>
-        <v>30.135616652148887</v>
+        <v>30.368615772264086</v>
       </c>
       <c r="Y97" s="4">
         <f>V97 - Y81 - Y92 - Y44 + Y39*Y87</f>
-        <v>58.535552177351782</v>
+        <v>59.120937045501627</v>
       </c>
       <c r="Z97" s="37"/>
     </row>
@@ -10281,15 +10285,15 @@
       </c>
       <c r="S98" s="4">
         <f>P98 - S82 - S93 - S45 + S40*S88</f>
-        <v>5.5077865676000002</v>
+        <v>5.5185556000000009</v>
       </c>
       <c r="V98" s="4">
         <f>S98 - V82 - V93 - V45 + V40*V88</f>
-        <v>16.474668112255422</v>
+        <v>16.549891467708001</v>
       </c>
       <c r="Y98" s="4">
         <f>V98 - Y82 - Y93 - Y45 + Y40*Y88</f>
-        <v>34.655959149971224</v>
+        <v>34.923908138103698</v>
       </c>
       <c r="Z98" s="37"/>
     </row>
@@ -10321,11 +10325,11 @@
       </c>
       <c r="V99" s="4">
         <f>S99 - V83 - V94 - V46 + V41*V89</f>
-        <v>2.5742915478999997</v>
+        <v>2.5793249</v>
       </c>
       <c r="Y99" s="4">
         <f>V99 - Y83 - Y94 - Y46 + Y41*Y89</f>
-        <v>7.7001166176845999</v>
+        <v>7.7352753599069999</v>
       </c>
       <c r="Z99" s="37"/>
     </row>
@@ -10354,23 +10358,23 @@
       </c>
       <c r="M101" s="4">
         <f>M96*$G$21</f>
-        <v>1.272178962625</v>
+        <v>1.274666375</v>
       </c>
       <c r="P101" s="4">
         <f>P96*$G$21</f>
-        <v>3.8052901889720405</v>
+        <v>3.8226651487912497</v>
       </c>
       <c r="S101" s="4">
         <f>S96*$G$21</f>
-        <v>8.0047731732270471</v>
+        <v>8.0666635645076479</v>
       </c>
       <c r="V101" s="4">
         <f>V96*$G$21</f>
-        <v>15.548506047109065</v>
+        <v>15.703998902711369</v>
       </c>
       <c r="Y101" s="4">
         <f>Y96*$G$21</f>
-        <v>28.092092321535851</v>
+        <v>28.429343624434111</v>
       </c>
       <c r="Z101" s="37"/>
     </row>
@@ -10395,19 +10399,19 @@
       </c>
       <c r="P102" s="4">
         <f t="shared" ref="P102:P104" si="12">P97*$G$21</f>
-        <v>1.1973449060000001</v>
+        <v>1.199686</v>
       </c>
       <c r="S102" s="4">
         <f t="shared" ref="S102:S104" si="13">S97*$G$21</f>
-        <v>3.5814495896207443</v>
+        <v>3.5978024929799997</v>
       </c>
       <c r="V102" s="4">
         <f t="shared" ref="V102:V104" si="14">V97*$G$21</f>
-        <v>7.5339041630372217</v>
+        <v>7.5921539430660214</v>
       </c>
       <c r="Y102" s="4">
         <f t="shared" ref="Y102:Y104" si="15">Y97*$G$21</f>
-        <v>14.633888044337946</v>
+        <v>14.780234261375407</v>
       </c>
       <c r="Z102" s="37"/>
     </row>
@@ -10436,15 +10440,15 @@
       </c>
       <c r="S103" s="4">
         <f>S98*$G$21</f>
-        <v>1.3769466419</v>
+        <v>1.3796389000000002</v>
       </c>
       <c r="V103" s="4">
         <f>V98*$G$21</f>
-        <v>4.1186670280638555</v>
+        <v>4.1374728669270002</v>
       </c>
       <c r="Y103" s="4">
         <f>Y98*$G$21</f>
-        <v>8.663989787492806</v>
+        <v>8.7309770345259246</v>
       </c>
       <c r="Z103" s="37"/>
     </row>
@@ -10477,11 +10481,11 @@
       </c>
       <c r="V104" s="4">
         <f t="shared" si="14"/>
-        <v>0.64357288697499992</v>
+        <v>0.64483122500000001</v>
       </c>
       <c r="Y104" s="4">
         <f t="shared" si="15"/>
-        <v>1.92502915442115</v>
+        <v>1.93381883997675</v>
       </c>
       <c r="Z104" s="37"/>
     </row>
@@ -10704,11 +10708,11 @@
       </c>
       <c r="X110" s="4">
         <f>IF(U112=0,0,MIN(MAX((U112/U109-$F$17)/($F$19-$F$17), 0), 1))</f>
-        <v>0.89228649746988453</v>
+        <v>0.96349966843506474</v>
       </c>
       <c r="Y110" s="4">
         <f>IF(V112=0,0,MIN(MAX((V112/V109-$G$17)/($F$19-$G$17), 0), 1))</f>
-        <v>0.85022774788522248</v>
+        <v>0.86560925711218095</v>
       </c>
       <c r="Z110" s="38" t="s">
         <v>300</v>
@@ -10774,11 +10778,11 @@
       </c>
       <c r="X111" s="4">
         <f xml:space="preserve"> X108*X110</f>
-        <v>0.26768594924096534</v>
+        <v>0.28904990053051943</v>
       </c>
       <c r="Y111" s="4">
         <f>Y108*Y110</f>
-        <v>0.78220952805440469</v>
+        <v>0.7963605165432065</v>
       </c>
       <c r="Z111" s="38"/>
     </row>
@@ -10802,51 +10806,51 @@
       </c>
       <c r="I112" s="4">
         <f>F112 - F133 - F121 - F144+I111*I7</f>
-        <v>1400244.5781226705</v>
+        <v>1416820.2074666857</v>
       </c>
       <c r="J112" s="4">
         <f>G112 - G133 - G121 - G144 + J111*J7</f>
-        <v>23001355.719131082</v>
+        <v>23271492.408783317</v>
       </c>
       <c r="L112" s="4">
         <f>I112 - I133 - I121 - I144+L111*L7</f>
-        <v>1296616.445847953</v>
+        <v>1328540.482773518</v>
       </c>
       <c r="M112" s="4">
         <f>J112 - J133 - J121 - J144 + M111*M7</f>
-        <v>20984486.203669269</v>
+        <v>21500316.163346589</v>
       </c>
       <c r="O112" s="4">
         <f>L112 - L133 - L121 - L144+O111*O7</f>
-        <v>1175936.6610351533</v>
+        <v>1229960.5227370157</v>
       </c>
       <c r="P112" s="4">
         <f>M112 - M133 - M121 - M144 + P111*P7</f>
-        <v>18954620.865377408</v>
+        <v>19683424.583337996</v>
       </c>
       <c r="R112" s="4">
         <f>O112 - O133 - O121 - O144+R111*R7</f>
-        <v>1032133.964000222</v>
+        <v>1102712.6301399493</v>
       </c>
       <c r="S112" s="4">
         <f>P112 - P133 - P121 - P144 + S111*S7</f>
-        <v>16874657.962828044</v>
+        <v>17795064.508199312</v>
       </c>
       <c r="U112" s="4">
         <f>R112 - R133 - R121 - R144+U111*U7</f>
-        <v>917853.92999855743</v>
+        <v>952878.26623738057</v>
       </c>
       <c r="V112" s="4">
         <f>S112 - S133 - S121 - S144 + V111*V7</f>
-        <v>15623190.666785505</v>
+        <v>15735231.967631815</v>
       </c>
       <c r="X112" s="4">
         <f>U112 - U133 - U121 - U144+X111*X7</f>
-        <v>869078.45031468186</v>
+        <v>902055.81293937785</v>
       </c>
       <c r="Y112" s="4">
         <f>V112 - V133 - V121 - V144 + Y111*Y7</f>
-        <v>15387963.591322072</v>
+        <v>15603395.572368858</v>
       </c>
       <c r="Z112" s="38"/>
     </row>
@@ -10870,51 +10874,51 @@
       </c>
       <c r="I113" s="4">
         <f>I112/I7</f>
-        <v>140.72809830378597</v>
+        <v>142.39399070016941</v>
       </c>
       <c r="J113" s="4">
         <f>J112/J7</f>
-        <v>92.042239772433305</v>
+        <v>93.12321892270235</v>
       </c>
       <c r="L113" s="4">
         <f>L112/L7</f>
-        <v>131.13030398947745</v>
+        <v>134.35886759440919</v>
       </c>
       <c r="M113" s="4">
         <f>M112/M7</f>
-        <v>84.008511964727447</v>
+        <v>86.073566449203682</v>
       </c>
       <c r="O113" s="4">
         <f>O112/O7</f>
-        <v>119.62733072585486</v>
+        <v>125.12314575147667</v>
       </c>
       <c r="P113" s="4">
         <f>P112/P7</f>
-        <v>75.910790983345379</v>
+        <v>78.82955507231992</v>
       </c>
       <c r="R113" s="4">
         <f>R112/R7</f>
-        <v>105.75143073772767</v>
+        <v>112.98285144876529</v>
       </c>
       <c r="S113" s="4">
         <f>S112/S7</f>
-        <v>67.63281535698043</v>
+        <v>71.321760405441637</v>
       </c>
       <c r="U113" s="4">
         <f>U112/U7</f>
-        <v>95.015934782459368</v>
+        <v>98.641642467637737</v>
       </c>
       <c r="V113" s="4">
         <f>V112/V7</f>
-        <v>62.62678398486964</v>
+        <v>63.075910318609083</v>
       </c>
       <c r="X113" s="4">
         <f>X112/X7</f>
-        <v>90.888773302100176</v>
+        <v>94.337566716103098</v>
       </c>
       <c r="Y113" s="4">
         <f>Y112/Y7</f>
-        <v>61.709831534015365</v>
+        <v>62.573771143603061</v>
       </c>
       <c r="Z113" s="38"/>
     </row>
@@ -10938,51 +10942,51 @@
       </c>
       <c r="I114" s="4">
         <f>MAX(I113-$F22,0)</f>
-        <v>91.141540803785972</v>
+        <v>92.807433200169413</v>
       </c>
       <c r="J114" s="4">
         <f>MAX(J113-$G22,0)</f>
-        <v>54.241346772433303</v>
+        <v>55.322325922702348</v>
       </c>
       <c r="L114" s="4">
         <f>MAX(L113-$F22,0)</f>
-        <v>81.543746489477456</v>
+        <v>84.772310094409193</v>
       </c>
       <c r="M114" s="4">
         <f>MAX(M113-$G22,0)</f>
-        <v>46.207618964727445</v>
+        <v>48.27267344920368</v>
       </c>
       <c r="O114" s="4">
         <f>MAX(O113-$F22,0)</f>
-        <v>70.040773225854863</v>
+        <v>75.536588251476672</v>
       </c>
       <c r="P114" s="4">
         <f>MAX(P113-$G22,0)</f>
-        <v>38.109897983345377</v>
+        <v>41.028662072319918</v>
       </c>
       <c r="R114" s="4">
         <f>MAX(R113-$F22,0)</f>
-        <v>56.164873237727676</v>
+        <v>63.39629394876529</v>
       </c>
       <c r="S114" s="4">
         <f>MAX(S113-$G22,0)</f>
-        <v>29.831922356980428</v>
+        <v>33.520867405441635</v>
       </c>
       <c r="U114" s="4">
         <f>MAX(U113-$F22,0)</f>
-        <v>45.42937728245937</v>
+        <v>49.05508496763774</v>
       </c>
       <c r="V114" s="4">
         <f>MAX(V113-$G22,0)</f>
-        <v>24.825890984869638</v>
+        <v>25.275017318609081</v>
       </c>
       <c r="X114" s="4">
         <f>MAX(X113-$F22,0)</f>
-        <v>41.302215802100179</v>
+        <v>44.7510092161031</v>
       </c>
       <c r="Y114" s="4">
         <f>MAX(Y113-$G22,0)</f>
-        <v>23.908938534015363</v>
+        <v>24.772878143603059</v>
       </c>
       <c r="Z114" s="38"/>
     </row>
@@ -11028,51 +11032,51 @@
       </c>
       <c r="I117" s="4">
         <f>I113*I7</f>
-        <v>1400244.5781226703</v>
+        <v>1416820.2074666857</v>
       </c>
       <c r="J117" s="4">
         <f>J113*J7</f>
-        <v>23001355.719131082</v>
+        <v>23271492.408783317</v>
       </c>
       <c r="L117" s="4">
         <f>L113*L7</f>
-        <v>1296616.445847953</v>
+        <v>1328540.4827735182</v>
       </c>
       <c r="M117" s="4">
         <f>M113*M7</f>
-        <v>20984486.203669269</v>
+        <v>21500316.163346589</v>
       </c>
       <c r="O117" s="4">
         <f>O113*O7</f>
-        <v>1175936.6610351533</v>
+        <v>1229960.5227370157</v>
       </c>
       <c r="P117" s="4">
         <f>P113*P7</f>
-        <v>18954620.865377408</v>
+        <v>19683424.583337996</v>
       </c>
       <c r="R117" s="4">
         <f>R113*R7</f>
-        <v>1032133.964000222</v>
+        <v>1102712.6301399493</v>
       </c>
       <c r="S117" s="4">
         <f>S113*S7</f>
-        <v>16874657.962828044</v>
+        <v>17795064.508199312</v>
       </c>
       <c r="U117" s="4">
         <f>U113*U7</f>
-        <v>917853.92999855755</v>
+        <v>952878.26623738057</v>
       </c>
       <c r="V117" s="4">
         <f>V113*V7</f>
-        <v>15623190.666785505</v>
+        <v>15735231.967631815</v>
       </c>
       <c r="X117" s="4">
         <f>X113*X7</f>
-        <v>869078.45031468186</v>
+        <v>902055.81293937785</v>
       </c>
       <c r="Y117" s="4">
         <f>Y113*Y7</f>
-        <v>15387963.591322072</v>
+        <v>15603395.572368858</v>
       </c>
       <c r="Z117" s="38"/>
     </row>
@@ -11096,23 +11100,23 @@
       </c>
       <c r="M118" s="4">
         <f>SUM(M96:M99)</f>
-        <v>5.8887158504999997</v>
+        <v>5.8986654999999999</v>
       </c>
       <c r="P118" s="4">
         <f>SUM(P96:P99)</f>
-        <v>20.930540379888164</v>
+        <v>21.009404595165002</v>
       </c>
       <c r="S118" s="4">
         <f>SUM(S96:S99)</f>
-        <v>52.282677618991166</v>
+        <v>52.606419829950589</v>
       </c>
       <c r="V118" s="4">
         <f>SUM(V96:V99)</f>
-        <v>111.37860050074056</v>
+        <v>112.31382775081757</v>
       </c>
       <c r="Y118" s="4">
         <f>SUM(Y96:Y99)</f>
-        <v>213.25999723115103</v>
+        <v>215.49749504124878</v>
       </c>
       <c r="Z118" s="38"/>
     </row>
@@ -11136,51 +11140,51 @@
       </c>
       <c r="I119" s="4">
         <f>I117+I118</f>
-        <v>1400244.5781226703</v>
+        <v>1416820.2074666857</v>
       </c>
       <c r="J119" s="4">
         <f>J117+J118</f>
-        <v>23001356.569131084</v>
+        <v>23271493.258783318</v>
       </c>
       <c r="L119" s="4">
         <f>L117+L118</f>
-        <v>1296616.445847953</v>
+        <v>1328540.4827735182</v>
       </c>
       <c r="M119" s="4">
         <f>M117+M118</f>
-        <v>20984492.092385121</v>
+        <v>21500322.062012088</v>
       </c>
       <c r="O119" s="4">
         <f>O117+O118</f>
-        <v>1175936.6610351533</v>
+        <v>1229960.5227370157</v>
       </c>
       <c r="P119" s="4">
         <f>P117+P118</f>
-        <v>18954641.795917787</v>
+        <v>19683445.592742592</v>
       </c>
       <c r="R119" s="4">
         <f>R117+R118</f>
-        <v>1032133.964000222</v>
+        <v>1102712.6301399493</v>
       </c>
       <c r="S119" s="4">
         <f>S117+S118</f>
-        <v>16874710.245505664</v>
+        <v>17795117.114619143</v>
       </c>
       <c r="U119" s="4">
         <f>U117+U118</f>
-        <v>917853.92999855755</v>
+        <v>952878.26623738057</v>
       </c>
       <c r="V119" s="4">
         <f>V117+V118</f>
-        <v>15623302.045386005</v>
+        <v>15735344.281459566</v>
       </c>
       <c r="X119" s="4">
         <f>X117+X118</f>
-        <v>869078.45031468186</v>
+        <v>902055.81293937785</v>
       </c>
       <c r="Y119" s="4">
         <f>Y117+Y118</f>
-        <v>15388176.851319304</v>
+        <v>15603611.069863901</v>
       </c>
       <c r="Z119" s="38"/>
     </row>
@@ -11195,60 +11199,60 @@
         <v>220</v>
       </c>
       <c r="F120" s="4">
-        <f>F112*$F$21</f>
+        <f>F119*$F$21</f>
         <v>450000</v>
       </c>
       <c r="G120" s="4">
-        <f>G112*$G$21</f>
+        <f>G119*$G$21</f>
         <v>6250000</v>
       </c>
       <c r="I120" s="4">
-        <f>I112*$F$21</f>
-        <v>420073.37343680114</v>
+        <f>I119*$F$21</f>
+        <v>425046.0622400057</v>
       </c>
       <c r="J120" s="4">
-        <f>J112*$G$21</f>
-        <v>5750338.9297827706</v>
+        <f>J119*$G$21</f>
+        <v>5817873.3146958295</v>
       </c>
       <c r="L120" s="4">
-        <f>L112*$F$21</f>
-        <v>388984.93375438586</v>
+        <f>L119*$F$21</f>
+        <v>398562.14483205543</v>
       </c>
       <c r="M120" s="4">
-        <f>M112*$G$21</f>
-        <v>5246121.5509173172</v>
+        <f>M119*$G$21</f>
+        <v>5375080.5155030219</v>
       </c>
       <c r="O120" s="4">
-        <f>O112*$F$21</f>
-        <v>352780.99831054598</v>
+        <f>O119*$F$21</f>
+        <v>368988.1568211047</v>
       </c>
       <c r="P120" s="4">
-        <f>P112*$G$21</f>
-        <v>4738655.2163443519</v>
+        <f>P119*$G$21</f>
+        <v>4920861.398185648</v>
       </c>
       <c r="R120" s="4">
-        <f>R112*$F$21</f>
-        <v>309640.18920006661</v>
+        <f>R119*$F$21</f>
+        <v>330813.78904198477</v>
       </c>
       <c r="S120" s="4">
-        <f>S112*$G$21</f>
-        <v>4218664.490707011</v>
+        <f>S119*$G$21</f>
+        <v>4448779.2786547858</v>
       </c>
       <c r="U120" s="4">
-        <f>U112*$F$21</f>
-        <v>275356.17899956723</v>
+        <f>U119*$F$21</f>
+        <v>285863.47987121413</v>
       </c>
       <c r="V120" s="4">
-        <f>V112*$G$21</f>
-        <v>3905797.6666963762</v>
+        <f>V119*$G$21</f>
+        <v>3933836.0703648916</v>
       </c>
       <c r="X120" s="4">
-        <f>X112*$F$21</f>
-        <v>260723.53509440453</v>
+        <f>X119*$F$21</f>
+        <v>270616.74388181337</v>
       </c>
       <c r="Y120" s="4">
-        <f>Y112*$G$21</f>
-        <v>3846990.897830518</v>
+        <f>Y119*$G$21</f>
+        <v>3900902.7674659751</v>
       </c>
       <c r="Z120" s="38"/>
     </row>
@@ -11272,51 +11276,51 @@
       </c>
       <c r="I121" s="4">
         <f>I9*I113</f>
-        <v>8725.1420948347295</v>
+        <v>8828.4274234105033</v>
       </c>
       <c r="J121" s="4">
         <f>J9*J113</f>
-        <v>10124.646374967664</v>
+        <v>10243.554081497259</v>
       </c>
       <c r="L121" s="4">
         <f>L9*L113</f>
-        <v>7605.5576313896927</v>
+        <v>7792.8143204757334</v>
       </c>
       <c r="M121" s="4">
         <f>M9*M113</f>
-        <v>7896.8001246843796</v>
+        <v>8090.9152462251459</v>
       </c>
       <c r="O121" s="4">
         <f>O9*O113</f>
-        <v>8373.9131508098399</v>
+        <v>8758.6202026033661</v>
       </c>
       <c r="P121" s="4">
         <f>P9*P113</f>
-        <v>14574.871868802313</v>
+        <v>15135.274573885425</v>
       </c>
       <c r="R121" s="4">
         <f>R9*R113</f>
-        <v>10575.143073772768</v>
+        <v>11298.285144876529</v>
       </c>
       <c r="S121" s="4">
         <f>S9*S113</f>
-        <v>2637.6797989222368</v>
+        <v>2781.5486558122238</v>
       </c>
       <c r="U121" s="4">
         <f>U9*U113</f>
-        <v>9311.5616086810187</v>
+        <v>9666.8809618284977</v>
       </c>
       <c r="V121" s="4">
         <f>V9*V113</f>
-        <v>6575.8123184113119</v>
+        <v>6622.9705834539536</v>
       </c>
       <c r="X121" s="4">
         <f>X9*X113</f>
-        <v>8907.0997836058177</v>
+        <v>9245.0815381781031</v>
       </c>
       <c r="Y121" s="4">
         <f>Y9*Y113</f>
-        <v>7158.340457945782</v>
+        <v>7258.5574526579549</v>
       </c>
       <c r="Z121" s="38"/>
     </row>
@@ -11408,51 +11412,51 @@
       </c>
       <c r="I123" s="4">
         <f>(I121-I122)*$F$14</f>
-        <v>5886.2594663843101</v>
+        <v>5958.5591963873512</v>
       </c>
       <c r="J123" s="4">
         <f>(J121-J122+J54)*$F$14</f>
-        <v>6332.6524624773647</v>
+        <v>6415.8878570480811</v>
       </c>
       <c r="L123" s="4">
         <f>(L121-L122)*$F$14</f>
-        <v>5112.7703419727841</v>
+        <v>5243.8500243330127</v>
       </c>
       <c r="M123" s="4">
         <f>(M121-M122+M54)*$F$14</f>
-        <v>4882.9200872790652</v>
+        <v>5018.8006723576018</v>
       </c>
       <c r="O123" s="4">
         <f>(O121-O122)*$F$14</f>
-        <v>5631.4392055668877</v>
+        <v>5900.7341418223559</v>
       </c>
       <c r="P123" s="4">
         <f>(P121-P122+P54)*$F$14</f>
-        <v>8871.8503081616182</v>
+        <v>9264.1322017197963</v>
       </c>
       <c r="R123" s="4">
         <f>(R121-R122)*$F$14</f>
-        <v>7038.6001516409369</v>
+        <v>7544.7996014135697</v>
       </c>
       <c r="S123" s="4">
         <f>(S121-S122+S54)*$F$14</f>
-        <v>1570.6458592455656</v>
+        <v>1671.3540590685566</v>
       </c>
       <c r="U123" s="4">
         <f>(U121-U122)*$F$14</f>
-        <v>6236.8331260767136</v>
+        <v>6485.5566732799489</v>
       </c>
       <c r="V123" s="4">
         <f>(V121-V122+V54)*$F$14</f>
-        <v>3794.5686228879181</v>
+        <v>3827.5794084177674</v>
       </c>
       <c r="X123" s="4">
         <f>(X121-X122)*$F$14</f>
-        <v>5885.1098485240727</v>
+        <v>6121.6970767246721</v>
       </c>
       <c r="Y123" s="4">
         <f>(Y121-Y122+Y54)*$F$14</f>
-        <v>4280.0383205620474</v>
+        <v>4350.1902168605684</v>
       </c>
       <c r="Z123" s="38"/>
     </row>
@@ -11472,27 +11476,27 @@
       </c>
       <c r="I124" s="4">
         <f>MIN(I123+J123, I33)</f>
-        <v>12218.911928861675</v>
+        <v>12374.447053435433</v>
       </c>
       <c r="L124" s="4">
         <f>MIN(L123+M123, L33)</f>
-        <v>9995.6904292518484</v>
+        <v>10262.650696690614</v>
       </c>
       <c r="O124" s="4">
         <f>MIN(O123+P123, O33)</f>
-        <v>14503.289513728505</v>
+        <v>15164.866343542151</v>
       </c>
       <c r="R124" s="4">
         <f>MIN(R123+S123, R33)</f>
-        <v>8609.2460108865016</v>
+        <v>9216.1536604821267</v>
       </c>
       <c r="U124" s="4">
         <f>MIN(U123+V123, U33)</f>
-        <v>10031.401748964632</v>
+        <v>10313.136081697716</v>
       </c>
       <c r="X124" s="4">
         <f>MIN(X123+Y123, X33)</f>
-        <v>10165.14816908612</v>
+        <v>10471.887293585241</v>
       </c>
       <c r="Z124" s="38"/>
     </row>
@@ -11516,51 +11520,51 @@
       </c>
       <c r="I125" s="4">
         <f>I123/(I123+J123)</f>
-        <v>0.48173352100858291</v>
+        <v>0.48152124863899409</v>
       </c>
       <c r="J125" s="4">
         <f>J123/(I123+J123)</f>
-        <v>0.51826647899141709</v>
+        <v>0.51847875136100585</v>
       </c>
       <c r="L125" s="4">
         <f>L123/(L123+M123)</f>
-        <v>0.51149746764971205</v>
+        <v>0.51096448464566679</v>
       </c>
       <c r="M125" s="4">
         <f>M123/(L123+M123)</f>
-        <v>0.48850253235028801</v>
+        <v>0.48903551535433326</v>
       </c>
       <c r="O125" s="4">
         <f>O123/(O123+P123)</f>
-        <v>0.3882870296587741</v>
+        <v>0.38910558181972643</v>
       </c>
       <c r="P125" s="4">
         <f>P123/(O123+P123)</f>
-        <v>0.61171297034122596</v>
+        <v>0.61089441818027368</v>
       </c>
       <c r="R125" s="4">
         <f>R123/(R123+S123)</f>
-        <v>0.81756290187788072</v>
+        <v>0.81864950166411143</v>
       </c>
       <c r="S125" s="4">
         <f>S123/(R123+S123)</f>
-        <v>0.18243709812211939</v>
+        <v>0.18135049833588848</v>
       </c>
       <c r="U125" s="4">
         <f>U123/(U123+V123)</f>
-        <v>0.62173096862763311</v>
+        <v>0.62886367656775044</v>
       </c>
       <c r="V125" s="4">
         <f>V123/(U123+V123)</f>
-        <v>0.37826903137236684</v>
+        <v>0.37113632343224967</v>
       </c>
       <c r="X125" s="4">
         <f>X123/(X123+Y123)</f>
-        <v>0.57894973596367783</v>
+        <v>0.58458393459549907</v>
       </c>
       <c r="Y125" s="4">
         <f>Y123/(X123+Y123)</f>
-        <v>0.42105026403632212</v>
+        <v>0.41541606540450088</v>
       </c>
       <c r="Z125" s="38"/>
     </row>
@@ -11584,51 +11588,51 @@
       </c>
       <c r="I126" s="4">
         <f>MAX(I13-I27, 0)*I114</f>
-        <v>445499.85144890583</v>
+        <v>453642.73348242807</v>
       </c>
       <c r="J126" s="4">
         <f>MAX(J13-J27, 0)*J114</f>
-        <v>10836878.67166445</v>
+        <v>11052847.496096702</v>
       </c>
       <c r="L126" s="4">
         <f>MAX(L13-L27, 0)*L114</f>
-        <v>353084.4222994374</v>
+        <v>367064.10270879179</v>
       </c>
       <c r="M126" s="4">
         <f>MAX(M13-M27, 0)*M114</f>
-        <v>9227476.6767802127</v>
+        <v>9639859.7971121781</v>
       </c>
       <c r="O126" s="4">
         <f>MAX(O13-O27, 0)*O114</f>
-        <v>263353.30732921429</v>
+        <v>284017.57182555227</v>
       </c>
       <c r="P126" s="4">
         <f>MAX(P13-P27, 0)*P114</f>
-        <v>7603077.087269336</v>
+        <v>8185382.1980761131</v>
       </c>
       <c r="R126" s="4">
         <f>MAX(R13-R27, 0)*R114</f>
-        <v>177480.99943121945</v>
+        <v>200332.2888780983</v>
       </c>
       <c r="S126" s="4">
         <f>MAX(S13-S27, 0)*S114</f>
-        <v>5980256.3152920818</v>
+        <v>6719760.6844318574</v>
       </c>
       <c r="U126" s="4">
         <f>MAX(U13-U27, 0)*U114</f>
-        <v>107304.18914116903</v>
+        <v>115868.11069356035</v>
       </c>
       <c r="V126" s="4">
         <f>MAX(V13-V27, 0)*V114</f>
-        <v>4961702.5722360462</v>
+        <v>5051464.9612972112</v>
       </c>
       <c r="X126" s="4">
         <f>MAX(X13-X27, 0)*X114</f>
-        <v>93508.216575954808</v>
+        <v>101316.28486525742</v>
       </c>
       <c r="Y126" s="4">
         <f>MAX(Y13-Y27, 0)*Y114</f>
-        <v>4775667.0185383642</v>
+        <v>4948233.7719158493</v>
       </c>
       <c r="Z126" s="38"/>
     </row>
@@ -11667,27 +11671,27 @@
       </c>
       <c r="I129" s="4">
         <f>MAX(I33-I124,0)</f>
-        <v>2037781.0880711384</v>
+        <v>2037625.5529465645</v>
       </c>
       <c r="L129" s="4">
         <f>MAX(L33-L124,0)</f>
-        <v>2100004.3095707484</v>
+        <v>2099737.3493033093</v>
       </c>
       <c r="O129" s="4">
         <f>MAX(O33-O124,0)</f>
-        <v>2195496.7104862714</v>
+        <v>2194835.133656458</v>
       </c>
       <c r="R129" s="4">
         <f>MAX(R33-R124,0)</f>
-        <v>2991390.7539891135</v>
+        <v>2990783.8463395177</v>
       </c>
       <c r="U129" s="4">
         <f>MAX(U33-U124,0)</f>
-        <v>24989968.598251034</v>
+        <v>24989686.863918301</v>
       </c>
       <c r="X129" s="4">
         <f>MAX(X33-X124,0)</f>
-        <v>2509834.8518309137</v>
+        <v>2509528.1127064149</v>
       </c>
       <c r="Z129" s="38"/>
     </row>
@@ -11707,27 +11711,27 @@
       </c>
       <c r="I130" s="4">
         <f>MIN(I140,I129)</f>
-        <v>2037781.0880711384</v>
+        <v>2037625.5529465645</v>
       </c>
       <c r="L130" s="4">
         <f>MIN(L140,L129)</f>
-        <v>2100004.3095707484</v>
+        <v>2099737.3493033093</v>
       </c>
       <c r="O130" s="4">
         <f>MIN(O140,O129)</f>
-        <v>2195496.7104862714</v>
+        <v>2194835.133656458</v>
       </c>
       <c r="R130" s="4">
         <f>MIN(R140,R129)</f>
-        <v>1365522.3071443853</v>
+        <v>2402116.7562237582</v>
       </c>
       <c r="U130" s="4">
         <f>MIN(U140,U129)</f>
-        <v>249661.00634800739</v>
+        <v>342075.56862017012</v>
       </c>
       <c r="X130" s="4">
         <f>MIN(X140,X129)</f>
-        <v>81322.864565083524</v>
+        <v>236958.69160889552</v>
       </c>
       <c r="Z130" s="38"/>
     </row>
@@ -11759,15 +11763,15 @@
       </c>
       <c r="R131" s="4">
         <f>R129-R130</f>
-        <v>1625868.4468447282</v>
+        <v>588667.09011575952</v>
       </c>
       <c r="U131" s="4">
         <f>U129-U130</f>
-        <v>24740307.591903027</v>
+        <v>24647611.295298129</v>
       </c>
       <c r="X131" s="4">
         <f>X129-X130</f>
-        <v>2428511.9872658299</v>
+        <v>2272569.4210975193</v>
       </c>
       <c r="Z131" s="38"/>
     </row>
@@ -11831,51 +11835,51 @@
       </c>
       <c r="I133" s="4">
         <f>I141*I130</f>
-        <v>80464.51997345034</v>
+        <v>80333.273414349693</v>
       </c>
       <c r="J133" s="4">
         <f>J141*I130</f>
-        <v>1957316.568097688</v>
+        <v>1957292.2795322149</v>
       </c>
       <c r="L133" s="4">
         <f>L141*L130</f>
-        <v>100241.7582597421</v>
+        <v>91806.708408756895</v>
       </c>
       <c r="M133" s="4">
         <f>M141*L130</f>
-        <v>1999762.5513110063</v>
+        <v>2007930.6408945527</v>
       </c>
       <c r="O133" s="4">
         <f>O141*O130</f>
-        <v>124509.76530548533</v>
+        <v>119687.89540326738</v>
       </c>
       <c r="P133" s="4">
         <f>P141*O130</f>
-        <v>2070986.9451807863</v>
+        <v>2075147.2382531904</v>
       </c>
       <c r="R133" s="4">
         <f>R141*R130</f>
-        <v>94293.001358187947</v>
+        <v>139940.26445123838</v>
       </c>
       <c r="S133" s="4">
         <f>S141*R130</f>
-        <v>1271229.3057861973</v>
+        <v>2262176.4917725199</v>
       </c>
       <c r="U133" s="4">
         <f>U141*U130</f>
-        <v>30365.318035164255</v>
+        <v>42505.359023831879</v>
       </c>
       <c r="V133" s="4">
         <f>V141*U130</f>
-        <v>219295.68831284312</v>
+        <v>299570.20959633822</v>
       </c>
       <c r="X133" s="4">
         <f>X141*X130</f>
-        <v>17535.251773675584</v>
+        <v>27081.188280169557</v>
       </c>
       <c r="Y133" s="4">
         <f>Y141*X130</f>
-        <v>63787.612791407948</v>
+        <v>209877.50332872596</v>
       </c>
       <c r="Z133" s="38"/>
     </row>
@@ -11899,51 +11903,51 @@
       </c>
       <c r="I134" s="4">
         <f>I133</f>
-        <v>80464.51997345034</v>
+        <v>80333.273414349693</v>
       </c>
       <c r="J134" s="4">
         <f>J133+I132</f>
-        <v>1957316.568097688</v>
+        <v>1957292.2795322149</v>
       </c>
       <c r="L134" s="4">
         <f>L133</f>
-        <v>100241.7582597421</v>
+        <v>91806.708408756895</v>
       </c>
       <c r="M134" s="4">
         <f>M133+L132</f>
-        <v>1999762.5513110063</v>
+        <v>2007930.6408945527</v>
       </c>
       <c r="O134" s="4">
         <f>O133</f>
-        <v>124509.76530548533</v>
+        <v>119687.89540326738</v>
       </c>
       <c r="P134" s="4">
         <f>P133+O132</f>
-        <v>2070986.9451807863</v>
+        <v>2075147.2382531904</v>
       </c>
       <c r="R134" s="4">
         <f>R133</f>
-        <v>94293.001358187947</v>
+        <v>139940.26445123838</v>
       </c>
       <c r="S134" s="4">
         <f>S133+R132</f>
-        <v>1271229.3057861973</v>
+        <v>2262176.4917725199</v>
       </c>
       <c r="U134" s="4">
         <f>U133</f>
-        <v>30365.318035164255</v>
+        <v>42505.359023831879</v>
       </c>
       <c r="V134" s="4">
         <f>V133+U132</f>
-        <v>219295.68831284312</v>
+        <v>299570.20959633822</v>
       </c>
       <c r="X134" s="4">
         <f>X133</f>
-        <v>17535.251773675584</v>
+        <v>27081.188280169557</v>
       </c>
       <c r="Y134" s="4">
         <f>Y133+X132</f>
-        <v>63787.612791407948</v>
+        <v>209877.50332872596</v>
       </c>
       <c r="Z134" s="38"/>
     </row>
@@ -11986,51 +11990,51 @@
       </c>
       <c r="I136" s="4">
         <f>I114/$F$23</f>
-        <v>0.90766274449544915</v>
+        <v>0.92425307697392622</v>
       </c>
       <c r="J136" s="4">
         <f>J114/$G$23</f>
-        <v>0.87205989585080868</v>
+        <v>0.8894392313816073</v>
       </c>
       <c r="L136" s="4">
         <f>L114/$F$23</f>
-        <v>0.81207998111883728</v>
+        <v>0.84423268422860009</v>
       </c>
       <c r="M136" s="4">
         <f>M114/$G$23</f>
-        <v>0.74289843043449877</v>
+        <v>0.77609913996359592</v>
       </c>
       <c r="O136" s="4">
         <f>O114/$F$23</f>
-        <v>0.69752387212354428</v>
+        <v>0.75225573758689401</v>
       </c>
       <c r="P136" s="4">
         <f>P114/$G$23</f>
-        <v>0.61270812108838446</v>
+        <v>0.65963426247132328</v>
       </c>
       <c r="R136" s="4">
         <f>R114/$F$23</f>
-        <v>0.55933619881349728</v>
+        <v>0.63135265926935324</v>
       </c>
       <c r="S136" s="4">
         <f>S114/$G$23</f>
-        <v>0.47961978548953171</v>
+        <v>0.5389284351854382</v>
       </c>
       <c r="U136" s="4">
         <f>U114/$F$23</f>
-        <v>0.45242326277638945</v>
+        <v>0.48853105467067059</v>
       </c>
       <c r="V136" s="4">
         <f>V114/$G$23</f>
-        <v>0.3991358105007784</v>
+        <v>0.4063565947756948</v>
       </c>
       <c r="X136" s="4">
         <f>X114/$F$23</f>
-        <v>0.41132157979844358</v>
+        <v>0.44566751325255183</v>
       </c>
       <c r="Y136" s="4">
         <f>Y114/$G$23</f>
-        <v>0.38439359803052098</v>
+        <v>0.39828350178087057</v>
       </c>
       <c r="Z136" s="38"/>
       <c r="AA136">
@@ -12076,39 +12080,39 @@
       </c>
       <c r="M137" s="4">
         <f>MAX(MIN((M136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.76335289475554091</v>
+        <v>0.8328091484893303</v>
       </c>
       <c r="O137" s="4">
         <f>MAX(MIN((O136-$F$17)/$F$18, 1), 0)</f>
-        <v>0.85222104179390024</v>
+        <v>0.97933386739236106</v>
       </c>
       <c r="P137" s="4">
         <f>MAX(MIN((P136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.49099331907540816</v>
+        <v>0.5891633289598236</v>
       </c>
       <c r="R137" s="4">
         <f>MAX(MIN((R136-$F$17)/$F$18, 1), 0)</f>
-        <v>0.53128504831712997</v>
+        <v>0.69854073566938424</v>
       </c>
       <c r="S137" s="4">
         <f>MAX(MIN((S136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.2125710402304235</v>
+        <v>0.33664539527627274</v>
       </c>
       <c r="U137" s="4">
         <f>MAX(MIN((U136-$F$17)/$F$18, 1), 0)</f>
-        <v>0.28298352821263806</v>
+        <v>0.36684260034451582</v>
       </c>
       <c r="V137" s="4">
         <f>MAX(MIN((V136-$G$17)/$G$18, 1), 0)</f>
-        <v>4.4197669070279458E-2</v>
+        <v>5.9303630113552025E-2</v>
       </c>
       <c r="X137" s="4">
         <f>MAX(MIN((X136-$F$17)/$F$18, 1), 0)</f>
-        <v>0.18752632031466515</v>
+        <v>0.26729353840979642</v>
       </c>
       <c r="Y137" s="4">
         <f>MAX(MIN((Y136-$G$17)/$G$18, 1), 0)</f>
-        <v>1.3356796557170923E-2</v>
+        <v>4.2414629745244618E-2</v>
       </c>
       <c r="Z137" s="38"/>
       <c r="AA137">
@@ -12156,58 +12160,58 @@
       </c>
       <c r="I139" s="4">
         <f>I126*I137</f>
-        <v>445499.85144890583</v>
+        <v>453642.73348242807</v>
       </c>
       <c r="J139" s="4">
         <f>J126*J137</f>
-        <v>10836878.67166445</v>
+        <v>11052847.496096702</v>
       </c>
       <c r="L139" s="4">
         <f>L126*L137</f>
-        <v>353084.4222994374</v>
+        <v>367064.10270879179</v>
       </c>
       <c r="M139" s="4">
         <f>M126*M137</f>
-        <v>7043821.0325094145</v>
+        <v>8028163.4291895209</v>
       </c>
       <c r="O139" s="4">
         <f>O126*O137</f>
-        <v>224435.22993197219</v>
+        <v>278148.02702330577</v>
       </c>
       <c r="P139" s="4">
         <f>P126*P137</f>
-        <v>3733060.054264558</v>
+        <v>4822527.024627001</v>
       </c>
       <c r="R139" s="4">
         <f>R126*R137</f>
-        <v>94293.001358187947</v>
+        <v>139940.26445123838</v>
       </c>
       <c r="S139" s="4">
         <f>S126*S137</f>
-        <v>1271229.3057861973</v>
+        <v>2262176.4917725199</v>
       </c>
       <c r="U139" s="4">
         <f>U126*U137</f>
-        <v>30365.318035164255</v>
+        <v>42505.359023831879</v>
       </c>
       <c r="V139" s="4">
         <f>V126*V137</f>
-        <v>219295.68831284312</v>
+        <v>299570.20959633822</v>
       </c>
       <c r="X139" s="4">
         <f>X126*X137</f>
-        <v>17535.251773675584</v>
+        <v>27081.188280169557</v>
       </c>
       <c r="Y139" s="4">
         <f>Y126*Y137</f>
-        <v>63787.612791407948</v>
+        <v>209877.50332872596</v>
       </c>
       <c r="Z139" s="38"/>
       <c r="AA139">
         <v>0.125</v>
       </c>
       <c r="AB139">
-        <f>SUM(AA$6:AA158)</f>
+        <f>SUM(AA$6:AA159)</f>
         <v>1.125</v>
       </c>
       <c r="AC139">
@@ -12234,51 +12238,51 @@
       </c>
       <c r="I140" s="4">
         <f>I139+J139</f>
-        <v>11282378.523113357</v>
+        <v>11506490.22957913</v>
       </c>
       <c r="J140" s="4">
         <f>I140</f>
-        <v>11282378.523113357</v>
+        <v>11506490.22957913</v>
       </c>
       <c r="L140" s="4">
         <f>L139+M139</f>
-        <v>7396905.4548088517</v>
+        <v>8395227.5318983123</v>
       </c>
       <c r="M140" s="4">
         <f>L140</f>
-        <v>7396905.4548088517</v>
+        <v>8395227.5318983123</v>
       </c>
       <c r="O140" s="4">
         <f>O139+P139</f>
-        <v>3957495.28419653</v>
+        <v>5100675.0516503071</v>
       </c>
       <c r="P140" s="4">
         <f>O140</f>
-        <v>3957495.28419653</v>
+        <v>5100675.0516503071</v>
       </c>
       <c r="R140" s="4">
         <f>R139+S139</f>
-        <v>1365522.3071443853</v>
+        <v>2402116.7562237582</v>
       </c>
       <c r="S140" s="4">
         <f>R140</f>
-        <v>1365522.3071443853</v>
+        <v>2402116.7562237582</v>
       </c>
       <c r="U140" s="4">
         <f>U139+V139</f>
-        <v>249661.00634800739</v>
+        <v>342075.56862017012</v>
       </c>
       <c r="V140" s="4">
         <f>U140</f>
-        <v>249661.00634800739</v>
+        <v>342075.56862017012</v>
       </c>
       <c r="X140" s="4">
         <f>X139+Y139</f>
-        <v>81322.864565083524</v>
+        <v>236958.69160889552</v>
       </c>
       <c r="Y140" s="4">
         <f>X140</f>
-        <v>81322.864565083524</v>
+        <v>236958.69160889552</v>
       </c>
       <c r="Z140" s="38"/>
     </row>
@@ -12302,51 +12306,51 @@
       </c>
       <c r="I141" s="4">
         <f>I139/I140</f>
-        <v>3.9486341513559745E-2</v>
+        <v>3.9424944047340565E-2</v>
       </c>
       <c r="J141" s="4">
         <f>J139/J140</f>
-        <v>0.96051365848644021</v>
+        <v>0.96057505595265946</v>
       </c>
       <c r="L141" s="4">
         <f>L139/L140</f>
-        <v>4.773407264113283E-2</v>
+        <v>4.3722948700806917E-2</v>
       </c>
       <c r="M141" s="4">
         <f>M139/M140</f>
-        <v>0.95226592735886717</v>
+        <v>0.95627705129919316</v>
       </c>
       <c r="O141" s="4">
         <f>O139/O140</f>
-        <v>5.6711433322033163E-2</v>
+        <v>5.4531610856745689E-2</v>
       </c>
       <c r="P141" s="4">
         <f>P139/P140</f>
-        <v>0.9432885666779669</v>
+        <v>0.94546838914325426</v>
       </c>
       <c r="R141" s="4">
         <f>R139/R140</f>
-        <v>6.9052699369939879E-2</v>
+        <v>5.8257061855407535E-2</v>
       </c>
       <c r="S141" s="4">
         <f>S139/S140</f>
-        <v>0.93094730063006004</v>
+        <v>0.94174293814459253</v>
       </c>
       <c r="U141" s="4">
         <f>U139/U140</f>
-        <v>0.12162619417161781</v>
+        <v>0.12425721952399496</v>
       </c>
       <c r="V141" s="4">
         <f>V139/V140</f>
-        <v>0.87837380582838209</v>
+        <v>0.87574278047600496</v>
       </c>
       <c r="X141" s="4">
         <f>X139/X140</f>
-        <v>0.21562511192214512</v>
+        <v>0.11428653701746266</v>
       </c>
       <c r="Y141" s="4">
         <f>Y139/Y140</f>
-        <v>0.78437488807785494</v>
+        <v>0.88571346298253728</v>
       </c>
       <c r="Z141" s="38"/>
     </row>
@@ -12381,478 +12385,531 @@
       </c>
       <c r="F144" s="4">
         <f>(F112 - F133 - F121)*$F$30</f>
-        <v>18798.841062135314</v>
+        <v>2223.2117181201452</v>
       </c>
       <c r="G144" s="4">
         <f>(G112 - G133 - G121)*$G$30+SUM(G91:G94)</f>
-        <v>306368.86168411467</v>
+        <v>36232.172031879854</v>
       </c>
       <c r="I144" s="4">
         <f>(I112 - I133 - I121)*$F$30</f>
-        <v>17404.870206432512</v>
+        <v>2084.4238554074132</v>
       </c>
       <c r="J144" s="4">
         <f>(J112 - J133 - J121)*$G$30+SUM(J91:J94)</f>
-        <v>279235.1009891578</v>
+        <v>33447.211823016281</v>
       </c>
       <c r="L144" s="4">
         <f>(L112 - L133 - L121)*$F$30</f>
-        <v>15781.46892166788</v>
+        <v>1929.437307269528</v>
       </c>
       <c r="M144" s="4">
         <f>(M112 - M133 - M121)*$G$30+SUM(M91:M94)</f>
-        <v>251926.30685617079</v>
+        <v>30590.343867813121</v>
       </c>
       <c r="O144" s="4">
         <f>(O112 - O133 - O121)*$F$30</f>
-        <v>13847.018578636153</v>
+        <v>1729.3769911958977</v>
       </c>
       <c r="P144" s="4">
         <f>(P112 - P133 - P121)*$G$30+SUM(P91:P94)</f>
-        <v>223944.76549977509</v>
+        <v>27621.242311606977</v>
       </c>
       <c r="R144" s="4">
         <f>(R112 - R133 - R121)*$F$30</f>
-        <v>12309.889569703864</v>
+        <v>1493.8143064538199</v>
       </c>
       <c r="S144" s="4">
         <f>(S112 - S133 - S121)*$G$30+SUM(S91:S94)</f>
-        <v>207108.11045742003</v>
+        <v>24382.300139165654</v>
       </c>
       <c r="U144" s="4">
         <f>(U112 - U133 - U121)*$F$30</f>
-        <v>11658.213086672471</v>
+        <v>1414.1084612152006</v>
       </c>
       <c r="V144" s="4">
         <f>(V112 - V133 - V121)*$G$30+SUM(V91:V94)</f>
-        <v>204407.342747824</v>
+        <v>24223.673488378809</v>
       </c>
       <c r="X144" s="4">
         <f>(X112 - X133 - X121)*$F$30</f>
-        <v>11186.390249970907</v>
+        <v>1359.1953827000175</v>
       </c>
       <c r="Y144" s="4">
         <f>(Y112 - Y133 - Y121)*$G$30+SUM(Y91:Y94)</f>
-        <v>203342.08674697479</v>
+        <v>24156.603765901902</v>
       </c>
       <c r="Z144" s="38"/>
     </row>
-    <row r="145" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A145" s="38" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="B145" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E145" s="14" t="s">
+      <c r="F145" s="4">
+        <f>F144*$F21</f>
+        <v>666.96351543604351</v>
+      </c>
+      <c r="G145" s="4">
+        <f>G144*$G21</f>
+        <v>9058.0430079699636</v>
+      </c>
+      <c r="I145" s="4">
+        <f>I144*$F21</f>
+        <v>625.32715662222392</v>
+      </c>
+      <c r="J145" s="4">
+        <f>J144*$G21</f>
+        <v>8361.8029557540704</v>
+      </c>
+      <c r="L145" s="4">
+        <f>L144*$F21</f>
+        <v>578.83119218085835</v>
+      </c>
+      <c r="M145" s="4">
+        <f>M144*$G21</f>
+        <v>7647.5859669532801</v>
+      </c>
+      <c r="O145" s="4">
+        <f>O144*$F21</f>
+        <v>518.81309735876926</v>
+      </c>
+      <c r="P145" s="4">
+        <f>P144*$G21</f>
+        <v>6905.3105779017442</v>
+      </c>
+      <c r="R145" s="4">
+        <f>R144*$F21</f>
+        <v>448.14429193614598</v>
+      </c>
+      <c r="S145" s="4">
+        <f>S144*$G21</f>
+        <v>6095.5750347914136</v>
+      </c>
+      <c r="U145" s="4">
+        <f>U144*$F21</f>
+        <v>424.23253836456018</v>
+      </c>
+      <c r="V145" s="4">
+        <f>V144*$G21</f>
+        <v>6055.9183720947021</v>
+      </c>
+      <c r="X145" s="4">
+        <f>X144*$F21</f>
+        <v>407.75861481000521</v>
+      </c>
+      <c r="Y145" s="4">
+        <f>Y144*$G21</f>
+        <v>6039.1509414754755</v>
+      </c>
+      <c r="Z145" s="38"/>
+    </row>
+    <row r="146" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A146" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="B146" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E146" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F146" s="4">
         <f>F133*$F21</f>
         <v>22932.474244558285</v>
       </c>
-      <c r="G145" s="4">
+      <c r="G146" s="4">
         <f>(G133+F132)*$G21</f>
         <v>478045.8547962014</v>
       </c>
-      <c r="I145" s="4">
+      <c r="I146" s="4">
         <f>I133*$F21</f>
-        <v>24139.3559920351</v>
-      </c>
-      <c r="J145" s="4">
+        <v>24099.982024304907</v>
+      </c>
+      <c r="J146" s="4">
         <f>(J133+I132)*$G21</f>
-        <v>489329.14202442201</v>
-      </c>
-      <c r="L145" s="4">
+        <v>489323.06988305371</v>
+      </c>
+      <c r="L146" s="4">
         <f>L133*$F21</f>
-        <v>30072.527477922627</v>
-      </c>
-      <c r="M145" s="4">
+        <v>27542.012522627068</v>
+      </c>
+      <c r="M146" s="4">
         <f>(M133+L132)*$G21</f>
-        <v>499940.63782775158</v>
-      </c>
-      <c r="O145" s="4">
+        <v>501982.66022363817</v>
+      </c>
+      <c r="O146" s="4">
         <f>O133*$F21</f>
-        <v>37352.929591645596</v>
-      </c>
-      <c r="P145" s="4">
+        <v>35906.368620980211</v>
+      </c>
+      <c r="P146" s="4">
         <f>(P133+O132)*$G21</f>
-        <v>517746.73629519658</v>
-      </c>
-      <c r="R145" s="4">
+        <v>518786.8095632976</v>
+      </c>
+      <c r="R146" s="4">
         <f>R133*$F21</f>
-        <v>28287.900407456382</v>
-      </c>
-      <c r="S145" s="4">
+        <v>41982.079335371513</v>
+      </c>
+      <c r="S146" s="4">
         <f>(S133+R132)*$G21</f>
-        <v>317807.32644654933</v>
-      </c>
-      <c r="U145" s="4">
+        <v>565544.12294312997</v>
+      </c>
+      <c r="U146" s="4">
         <f>U133*$F21</f>
-        <v>9109.5954105492765</v>
-      </c>
-      <c r="V145" s="4">
+        <v>12751.607707149564</v>
+      </c>
+      <c r="V146" s="4">
         <f>(V133+U132)*$G21</f>
-        <v>54823.92207821078</v>
-      </c>
-      <c r="X145" s="4">
+        <v>74892.552399084554</v>
+      </c>
+      <c r="X146" s="4">
         <f>X133*$F21</f>
-        <v>5260.5755321026745</v>
-      </c>
-      <c r="Y145" s="4">
+        <v>8124.356484050867</v>
+      </c>
+      <c r="Y146" s="4">
         <f>(Y133+X132)*$G21</f>
-        <v>15946.903197851987</v>
-      </c>
-      <c r="Z145" s="38"/>
-    </row>
-    <row r="146" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A146" s="38" t="s">
+        <v>52469.375832181489</v>
+      </c>
+      <c r="Z146" s="38"/>
+    </row>
+    <row r="147" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="B146" s="33" t="s">
+      <c r="B147" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E146" s="10" t="s">
+      <c r="E147" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F147" s="4">
         <f>F121-F124*F125-F122</f>
         <v>2175</v>
       </c>
-      <c r="G146" s="4">
+      <c r="G147" s="4">
         <f>G121-F124*G125-G122+G54</f>
         <v>2700</v>
       </c>
-      <c r="I146" s="4">
+      <c r="I147" s="4">
         <f>I121-I124*I125-I122</f>
-        <v>2522.6826284504195</v>
-      </c>
-      <c r="J146" s="4">
+        <v>2553.6682270231522</v>
+      </c>
+      <c r="J147" s="4">
         <f>J121-I124*J125-J122+J54</f>
-        <v>2713.9939124902994</v>
-      </c>
-      <c r="L146" s="4">
+        <v>2749.6662244491781</v>
+      </c>
+      <c r="L147" s="4">
         <f>L121-L124*L125-L122</f>
-        <v>2191.1872894169087</v>
-      </c>
-      <c r="M146" s="4">
+        <v>2247.3642961427208</v>
+      </c>
+      <c r="M147" s="4">
         <f>M121-L124*M125-M122+M54</f>
-        <v>2092.6800374053146</v>
-      </c>
-      <c r="O146" s="4">
+        <v>2150.9145738675443</v>
+      </c>
+      <c r="O147" s="4">
         <f>O121-O124*O125-O122</f>
-        <v>2413.4739452429521</v>
-      </c>
-      <c r="P146" s="4">
+        <v>2528.8860607810102</v>
+      </c>
+      <c r="P147" s="4">
         <f>P121-O124*P125-P122+P54</f>
-        <v>3802.2215606406944</v>
-      </c>
-      <c r="R146" s="4">
+        <v>3970.3423721656281</v>
+      </c>
+      <c r="R147" s="4">
         <f>R121-R124*R125-R122</f>
-        <v>3016.5429221318309</v>
-      </c>
-      <c r="S146" s="4">
+        <v>3233.485543462959</v>
+      </c>
+      <c r="S147" s="4">
         <f>S121-R124*S125-S122+S54</f>
-        <v>673.13393967667128</v>
-      </c>
-      <c r="U146" s="4">
+        <v>716.29459674366728</v>
+      </c>
+      <c r="U147" s="4">
         <f>U121-U124*U125-U122</f>
-        <v>2672.9284826043049</v>
-      </c>
-      <c r="V146" s="4">
+        <v>2779.5242885485477</v>
+      </c>
+      <c r="V147" s="4">
         <f>V121-U124*V125-V122+V54</f>
-        <v>1626.2436955233939</v>
-      </c>
-      <c r="X146" s="4">
+        <v>1640.3911750361863</v>
+      </c>
+      <c r="X147" s="4">
         <f>X121-X124*X125-X122</f>
-        <v>2522.1899350817448</v>
-      </c>
-      <c r="Y146" s="4">
+        <v>2623.5844614534308</v>
+      </c>
+      <c r="Y147" s="4">
         <f>Y121-X124*Y125-Y122+Y54</f>
-        <v>1834.3021373837346</v>
-      </c>
-      <c r="Z146" s="38"/>
-    </row>
-    <row r="147" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A147" s="38" t="s">
+        <v>1864.3672357973865</v>
+      </c>
+      <c r="Z147" s="38"/>
+    </row>
+    <row r="148" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A148" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="B147" s="33" t="s">
+      <c r="B148" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E147" s="10" t="s">
+      <c r="E148" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F148" s="4">
         <f>MAX((F121 - F122)*$F21-F16*F9,0)</f>
         <v>2128.25</v>
       </c>
-      <c r="G147" s="4">
+      <c r="G148" s="4">
         <f>MAX((G121-G122+G54)*$G21-G16*G9,0)</f>
         <v>2058</v>
       </c>
-      <c r="I147" s="4">
+      <c r="I148" s="4">
         <f>MAX((I121 - I122)*$F21-I16*I9,0)</f>
-        <v>2463.5532284504188</v>
-      </c>
-      <c r="J147" s="4">
+        <v>2494.538827023151</v>
+      </c>
+      <c r="J148" s="4">
         <f>MAX((J121-J122+J54)*$G21-J16*J9,0)</f>
-        <v>2054.6855937419159</v>
-      </c>
-      <c r="L147" s="4">
+        <v>2084.4125203743147</v>
+      </c>
+      <c r="L148" s="4">
         <f>MAX((L121 - L122)*$F21-L16*L9,0)</f>
-        <v>2134.788089416908</v>
-      </c>
-      <c r="M147" s="4">
+        <v>2190.9650961427201</v>
+      </c>
+      <c r="M148" s="4">
         <f>MAX((M121-M122+M54)*$G21-M16*M9,0)</f>
-        <v>1567.0296311710949</v>
-      </c>
-      <c r="O147" s="4">
+        <v>1615.5584115562865</v>
+      </c>
+      <c r="O148" s="4">
         <f>MAX((O121 - O122)*$F21-O16*O9,0)</f>
-        <v>2351.9509452429515</v>
-      </c>
-      <c r="P147" s="4">
+        <v>2467.3630607810096</v>
+      </c>
+      <c r="P148" s="4">
         <f>MAX((P121-P122+P54)*$G21-P16*P9,0)</f>
-        <v>2803.5643672005781</v>
-      </c>
-      <c r="R147" s="4">
+        <v>2943.6650434713565</v>
+      </c>
+      <c r="R148" s="4">
         <f>MAX((R121 - R122)*$F21-R16*R9,0)</f>
-        <v>2919.3029221318302</v>
-      </c>
-      <c r="S147" s="4">
+        <v>3136.2455434629583</v>
+      </c>
+      <c r="S148" s="4">
         <f>MAX((S121-S122+S54)*$G21-S16*S9,0)</f>
-        <v>485.31614973055918</v>
-      </c>
-      <c r="U147" s="4">
+        <v>521.28336395305598</v>
+      </c>
+      <c r="U148" s="4">
         <f>MAX((U121 - U122)*$F21-U16*U9,0)</f>
-        <v>2597.791882604306</v>
-      </c>
-      <c r="V147" s="4">
+        <v>2704.3876885485497</v>
+      </c>
+      <c r="V148" s="4">
         <f>MAX((V121-V122+V54)*$G21-V16*V9,0)</f>
-        <v>1133.443079602828</v>
-      </c>
-      <c r="X147" s="4">
+        <v>1145.2326458634884</v>
+      </c>
+      <c r="X148" s="4">
         <f>MAX((X121 - X122)*$F21-X16*X9,0)</f>
-        <v>2428.7273350817454</v>
-      </c>
-      <c r="Y147" s="4">
+        <v>2530.1218614534314</v>
+      </c>
+      <c r="Y148" s="4">
         <f>MAX((Y121-Y122+Y54)*$G21-Y16*Y9,0)</f>
-        <v>1328.1371144864454</v>
-      </c>
-      <c r="Z147" s="38"/>
-    </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A148" s="38" t="s">
+        <v>1353.1913631644886</v>
+      </c>
+      <c r="Z148" s="38"/>
+    </row>
+    <row r="149" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A149" s="38" t="s">
         <v>302</v>
       </c>
-      <c r="B148" s="33" t="s">
+      <c r="B149" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F149" s="4">
         <f>I111*I7*(1+$F21)</f>
         <v>3880.5</v>
       </c>
-      <c r="G148" s="4">
+      <c r="G149" s="4">
         <f>(J111*J7+SUMPRODUCT(G38:G41,G86:G89))*(1+$G21)</f>
         <v>287385</v>
       </c>
-      <c r="I148" s="4">
+      <c r="I149" s="4">
         <f>L111*L7*(1+$F21)</f>
         <v>3856.32</v>
       </c>
-      <c r="J148" s="4">
+      <c r="J149" s="4">
         <f>(M111*M7+SUMPRODUCT(J38:J41,J86:J89))*(1+$G21)</f>
         <v>287259.5625</v>
       </c>
-      <c r="L148" s="4">
+      <c r="L149" s="4">
         <f>O111*O7*(1+$F21)</f>
         <v>3833.7000000000003</v>
       </c>
-      <c r="M148" s="4">
+      <c r="M149" s="4">
         <f>(P111*P7+SUMPRODUCT(M38:M41,M86:M89))*(1+$G21)</f>
         <v>287156.71250000002</v>
       </c>
-      <c r="O148" s="4">
+      <c r="O149" s="4">
         <f>R111*R7*(1+$F21)</f>
         <v>3806.4</v>
       </c>
-      <c r="P148" s="4">
+      <c r="P149" s="4">
         <f>(S111*S7+SUMPRODUCT(P38:P41,P86:P89))*(1+$G21)</f>
         <v>286948.5</v>
       </c>
-      <c r="R148" s="4">
+      <c r="R149" s="4">
         <f>U111*U7*(1+$F21)</f>
         <v>3767.4</v>
       </c>
-      <c r="S148" s="4">
+      <c r="S149" s="4">
         <f>(V111*V7+SUMPRODUCT(S38:S41,S86:S89))*(1+$G21)</f>
         <v>286924.28750000003</v>
       </c>
-      <c r="U148" s="4">
+      <c r="U149" s="4">
         <f>X111*X7*(1+$F21)</f>
-        <v>3327.4969606347436</v>
-      </c>
-      <c r="V148" s="4">
+        <v>3593.0636935346747</v>
+      </c>
+      <c r="V149" s="4">
         <f>(Y111*Y7+SUMPRODUCT(V38:V41,V86:V89))*(1+$G21)</f>
-        <v>243889.44739455794</v>
-      </c>
-      <c r="X148" s="4">
+        <v>248300.31050651748</v>
+      </c>
+      <c r="X149" s="4">
         <f>AA111*AA7*(1+$F21)</f>
         <v>0</v>
       </c>
-      <c r="Y148" s="4">
+      <c r="Y149" s="4">
         <f>(AB111*AB7+SUMPRODUCT(Y38:Y41,Y86:Y89))*(1+$G21)</f>
         <v>129.19999999999999</v>
       </c>
-      <c r="Z148" s="38"/>
-    </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A151" s="24" t="s">
+      <c r="Z149" s="38"/>
+    </row>
+    <row r="152" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A152" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="F151" s="4">
-        <f>F146+F122</f>
+      <c r="F152" s="4">
+        <f>F147+F122</f>
         <v>2425</v>
       </c>
-      <c r="G151" s="4">
-        <f>G146+G122</f>
+      <c r="G152" s="4">
+        <f>G147+G122</f>
         <v>3700</v>
       </c>
-      <c r="I151" s="4">
-        <f>I146+I122</f>
-        <v>2838.8826284504194</v>
-      </c>
-      <c r="J151" s="4">
-        <f>J146+J122</f>
-        <v>3791.9939124902994</v>
-      </c>
-      <c r="L151" s="4">
-        <f>L146+L122</f>
-        <v>2492.7872894169086</v>
-      </c>
-      <c r="M151" s="4">
-        <f>M146+M122</f>
-        <v>3013.8800374053144</v>
-      </c>
-      <c r="O151" s="4">
-        <f>O146+O122</f>
-        <v>2742.4739452429521</v>
-      </c>
-      <c r="P151" s="4">
-        <f>P146+P122</f>
-        <v>5703.0215606406946</v>
-      </c>
-      <c r="R151" s="4">
-        <f>R146+R122</f>
-        <v>3536.5429221318309</v>
-      </c>
-      <c r="S151" s="4">
-        <f>S146+S122</f>
-        <v>1067.0339396766713</v>
-      </c>
-      <c r="U151" s="4">
-        <f>U146+U122</f>
-        <v>3074.7284826043051</v>
-      </c>
-      <c r="V151" s="4">
-        <f>V146+V122</f>
-        <v>2781.2436955233939</v>
-      </c>
-      <c r="X151" s="4">
-        <f>X146+X122</f>
-        <v>3021.989935081745</v>
-      </c>
-      <c r="Y151" s="4">
-        <f>Y146+Y122</f>
-        <v>2878.3021373837346</v>
-      </c>
-    </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A153" s="38" t="s">
+      <c r="I152" s="4">
+        <f>I147+I122</f>
+        <v>2869.868227023152</v>
+      </c>
+      <c r="J152" s="4">
+        <f>J147+J122</f>
+        <v>3827.6662244491781</v>
+      </c>
+      <c r="L152" s="4">
+        <f>L147+L122</f>
+        <v>2548.9642961427207</v>
+      </c>
+      <c r="M152" s="4">
+        <f>M147+M122</f>
+        <v>3072.1145738675441</v>
+      </c>
+      <c r="O152" s="4">
+        <f>O147+O122</f>
+        <v>2857.8860607810102</v>
+      </c>
+      <c r="P152" s="4">
+        <f>P147+P122</f>
+        <v>5871.1423721656283</v>
+      </c>
+      <c r="R152" s="4">
+        <f>R147+R122</f>
+        <v>3753.485543462959</v>
+      </c>
+      <c r="S152" s="4">
+        <f>S147+S122</f>
+        <v>1110.1945967436673</v>
+      </c>
+      <c r="U152" s="4">
+        <f>U147+U122</f>
+        <v>3181.3242885485479</v>
+      </c>
+      <c r="V152" s="4">
+        <f>V147+V122</f>
+        <v>2795.3911750361863</v>
+      </c>
+      <c r="X152" s="4">
+        <f>X147+X122</f>
+        <v>3123.384461453431</v>
+      </c>
+      <c r="Y152" s="4">
+        <f>Y147+Y122</f>
+        <v>2908.3672357973865</v>
+      </c>
+    </row>
+    <row r="154" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A154" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="B153" s="33" t="s">
+      <c r="B154" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F154" s="4">
         <f>F124+F133+G133+F132</f>
         <v>2000000</v>
       </c>
-      <c r="I153" s="4">
+      <c r="I154" s="4">
         <f>I124+I133+J133</f>
         <v>2050000</v>
       </c>
-      <c r="L153" s="4">
+      <c r="L154" s="4">
         <f>L124+L133+M133</f>
-        <v>2110000.0000000005</v>
-      </c>
-      <c r="O153" s="4">
+        <v>2110000</v>
+      </c>
+      <c r="O154" s="4">
         <f>O124+O133+P133</f>
         <v>2210000</v>
       </c>
-      <c r="R153" s="4">
+      <c r="R154" s="4">
         <f>R124+R133+S133</f>
-        <v>1374131.5531552718</v>
-      </c>
-      <c r="U153" s="4">
+        <v>2411332.9098842405</v>
+      </c>
+      <c r="U154" s="4">
         <f>U124+U133+V133</f>
-        <v>259692.40809697201</v>
-      </c>
-      <c r="X153" s="4">
+        <v>352388.70470186783</v>
+      </c>
+      <c r="X154" s="4">
         <f>X124+X133+Y133</f>
-        <v>91488.01273416965</v>
-      </c>
-      <c r="Z153" s="38"/>
-    </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F154" s="4">
-        <f>F153/F33</f>
+        <v>247430.57890248077</v>
+      </c>
+      <c r="Z154" s="38"/>
+    </row>
+    <row r="155" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F155" s="4">
+        <f>F154/F33</f>
         <v>1</v>
       </c>
-      <c r="I154" s="4">
-        <f>I153/I33</f>
+      <c r="I155" s="4">
+        <f>I154/I33</f>
         <v>1</v>
       </c>
-      <c r="L154" s="4">
-        <f>L153/L33</f>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="O154" s="4">
-        <f>O153/O33</f>
+      <c r="L155" s="4">
+        <f>L154/L33</f>
         <v>1</v>
       </c>
-      <c r="R154" s="4">
-        <f>R153/R33</f>
-        <v>0.45804385105175727</v>
-      </c>
-      <c r="U154" s="4">
-        <f>U153/U33</f>
-        <v>1.038769632387888E-2</v>
-      </c>
-      <c r="X154" s="4">
-        <f>X153/X33</f>
-        <v>3.6304766958003831E-2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="AA159">
-        <v>0.1225</v>
-      </c>
-      <c r="AB159">
-        <f>SUM(AA$6:AA159)</f>
-        <v>1.2475000000000001</v>
-      </c>
-      <c r="AC159">
-        <v>20</v>
+      <c r="O155" s="4">
+        <f>O154/O33</f>
+        <v>1</v>
+      </c>
+      <c r="R155" s="4">
+        <f>R154/R33</f>
+        <v>0.80377763662808011</v>
+      </c>
+      <c r="U155" s="4">
+        <f>U154/U33</f>
+        <v>1.4095548188074713E-2</v>
+      </c>
+      <c r="X155" s="4">
+        <f>X154/X33</f>
+        <v>9.8186737659714599E-2</v>
       </c>
     </row>
     <row r="160" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AA160">
-        <v>0.12239999999999999</v>
+        <v>0.1225</v>
       </c>
       <c r="AB160">
         <f>SUM(AA$6:AA160)</f>
-        <v>1.3699000000000001</v>
+        <v>1.2475000000000001</v>
       </c>
       <c r="AC160">
         <v>20</v>
@@ -12860,13 +12917,25 @@
     </row>
     <row r="161" spans="27:29" x14ac:dyDescent="0.2">
       <c r="AA161">
-        <v>0.12230000000000001</v>
+        <v>0.12239999999999999</v>
       </c>
       <c r="AB161">
         <f>SUM(AA$6:AA161)</f>
+        <v>1.3699000000000001</v>
+      </c>
+      <c r="AC161">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="27:29" x14ac:dyDescent="0.2">
+      <c r="AA162">
+        <v>0.12230000000000001</v>
+      </c>
+      <c r="AB162">
+        <f>SUM(AA$6:AA162)</f>
         <v>1.4922000000000002</v>
       </c>
-      <c r="AC161">
+      <c r="AC162">
         <v>20</v>
       </c>
     </row>
@@ -12916,4 +12985,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40B7113C-E57E-E340-957C-77A5927B4CD4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8405E880-F68F-1F45-BDD6-B68CBF1F15C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD70AD-11E1-2348-A77F-DE216AAD897E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="760" windowWidth="33780" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAD70AD-11E1-2348-A77F-DE216AAD897E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3312DB0-35BF-4B40-AD8A-44200E17485A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="760" windowWidth="33780" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3312DB0-35BF-4B40-AD8A-44200E17485A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2868BA-3FEB-C140-9630-268A0A3EB0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="760" windowWidth="33780" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="9040" yWindow="760" windowWidth="33780" windowHeight="19400" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6869E642-61B5-724A-9F9F-F3EAE8BE1752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36EE739-1C78-174B-BB96-7938DAAAF8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20080" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="420" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="325">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -902,9 +902,6 @@
     <t>latex variable</t>
   </si>
   <si>
-    <t>A_r(t)</t>
-  </si>
-  <si>
     <t>A(t)</t>
   </si>
   <si>
@@ -920,9 +917,6 @@
     <t>a^{(y)}_{out}(t)</t>
   </si>
   <si>
-    <t>A_r(t + 1)</t>
-  </si>
-  <si>
     <t>\chi_(t)</t>
   </si>
   <si>
@@ -935,12 +929,6 @@
     <t>\hat{\alpha}(t)</t>
   </si>
   <si>
-    <t>\bar{S}_{targ}(t)</t>
-  </si>
-  <si>
-    <t>k_0</t>
-  </si>
-  <si>
     <t>\gamma</t>
   </si>
   <si>
@@ -963,6 +951,75 @@
   </si>
   <si>
     <t>this has been modified to use a logistic ramp rather than alinear</t>
+  </si>
+  <si>
+    <t>\overline{B}_{targ}(t)</t>
+  </si>
+  <si>
+    <t>\underline{B}_{targ}(t)</t>
+  </si>
+  <si>
+    <t>\overline{B}_0</t>
+  </si>
+  <si>
+    <t>\Delta B_0</t>
+  </si>
+  <si>
+    <t>\delta(t)</t>
+  </si>
+  <si>
+    <t>A_{protected}(t)</t>
+  </si>
+  <si>
+    <t>a_{protected}(t)</t>
+  </si>
+  <si>
+    <t>A^*(t)</t>
+  </si>
+  <si>
+    <t>A^*_{protected}(t)</t>
+  </si>
+  <si>
+    <t>d(t)</t>
+  </si>
+  <si>
+    <t>A^*(t + 1)</t>
+  </si>
+  <si>
+    <t>A_{young}(t, u)</t>
+  </si>
+  <si>
+    <t>\hat{A}_{young}(t, u)</t>
+  </si>
+  <si>
+    <t>L_{young}(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{conv}(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{y}_{conv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{preserved\_in\_conv}(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{y}_{preserved\_in\_conv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{y}_{availble\_from\_conv}(t)</t>
+  </si>
+  <si>
+    <t>\underline{Y}_{conv}(t, u)</t>
+  </si>
+  <si>
+    <t>\underline{y}_{conv}(t)</t>
+  </si>
+  <si>
+    <t>Q_0(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{Y}^*(t, u)</t>
   </si>
 </sst>
 </file>
@@ -1230,11 +1287,20 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1242,17 +1308,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1826,12 +1883,12 @@
         <v>29</v>
       </c>
       <c r="M1" s="51"/>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
       <c r="R1" s="51" t="s">
         <v>48</v>
       </c>
@@ -6391,16 +6448,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="R1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6420,18 +6477,18 @@
     <col min="8" max="8" width="15.1640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
     <col min="10" max="11" width="13.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" style="5" customWidth="1"/>
-    <col min="13" max="14" width="13.33203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="21.1640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="21.1640625" style="4" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" style="5" customWidth="1"/>
-    <col min="19" max="20" width="13.33203125" style="4" customWidth="1"/>
-    <col min="21" max="21" width="9.1640625" style="5" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" style="4" customWidth="1"/>
-    <col min="23" max="23" width="12.5" style="4" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" style="5" customWidth="1"/>
-    <col min="25" max="26" width="13.33203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="21.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" style="4" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="4" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
     <col min="28" max="30" width="14.6640625" customWidth="1"/>
     <col min="31" max="33" width="14.1640625" customWidth="1"/>
@@ -6485,10 +6542,10 @@
       <c r="H2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="44">
+      <c r="I2" s="47">
         <v>150</v>
       </c>
-      <c r="J2" s="44"/>
+      <c r="J2" s="47"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -6519,10 +6576,10 @@
       <c r="H3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="47">
         <v>30</v>
       </c>
-      <c r="J3" s="44"/>
+      <c r="J3" s="47"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -6576,11 +6633,11 @@
         <v>6</v>
       </c>
       <c r="Z4" s="20"/>
-      <c r="AE4" s="43" t="s">
+      <c r="AE4" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="AF4" s="43"/>
-      <c r="AG4" s="43"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46"/>
       <c r="AL4" t="s">
         <v>94</v>
       </c>
@@ -6596,7 +6653,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -6610,35 +6667,35 @@
       <c r="F5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="42"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="17"/>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="42"/>
-      <c r="M5" s="42" t="s">
+      <c r="K5" s="48"/>
+      <c r="M5" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="42"/>
-      <c r="P5" s="42" t="s">
+      <c r="N5" s="48"/>
+      <c r="P5" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="42"/>
-      <c r="S5" s="42" t="s">
+      <c r="Q5" s="48"/>
+      <c r="S5" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="T5" s="42"/>
-      <c r="V5" s="42" t="s">
+      <c r="T5" s="48"/>
+      <c r="V5" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="W5" s="42"/>
-      <c r="Y5" s="42" t="s">
+      <c r="W5" s="48"/>
+      <c r="Y5" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="Z5" s="42"/>
+      <c r="Z5" s="48"/>
       <c r="AA5" s="24" t="s">
         <v>284</v>
       </c>
@@ -6799,7 +6856,7 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -6891,7 +6948,7 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -6969,7 +7026,7 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7033,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7085,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7130,7 +7187,7 @@
         <v>110</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7210,7 +7267,7 @@
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7248,7 +7305,7 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7317,7 +7374,7 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7325,7 +7382,7 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="38" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C16" s="31"/>
       <c r="G16" s="4">
@@ -7384,7 +7441,9 @@
         <f>Z15*0.192</f>
         <v>1.728</v>
       </c>
-      <c r="AA16" s="38"/>
+      <c r="AA16" s="38" t="s">
+        <v>303</v>
+      </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
       <c r="AG16" s="19"/>
@@ -7406,7 +7465,7 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -7426,7 +7485,7 @@
       <c r="C18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="44" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="10" t="s">
@@ -7439,7 +7498,7 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -7459,7 +7518,7 @@
       <c r="C19" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="41"/>
+      <c r="E19" s="44"/>
       <c r="F19" s="10" t="s">
         <v>138</v>
       </c>
@@ -7467,7 +7526,7 @@
         <v>0.67</v>
       </c>
       <c r="AA19" s="40" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -7497,7 +7556,7 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -7527,7 +7586,7 @@
         <v>0.25</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
@@ -7582,7 +7641,7 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -7659,7 +7718,9 @@
       <c r="Z25" s="4">
         <v>49500</v>
       </c>
-      <c r="AA25" s="38"/>
+      <c r="AA25" s="38" t="s">
+        <v>307</v>
+      </c>
       <c r="AE25" s="19">
         <v>10</v>
       </c>
@@ -7709,7 +7770,9 @@
         <f>MAX(Z$25-Z$13, 0)</f>
         <v>0</v>
       </c>
-      <c r="AA26" s="38"/>
+      <c r="AA26" s="38" t="s">
+        <v>308</v>
+      </c>
       <c r="AE26" s="19">
         <v>6</v>
       </c>
@@ -7787,7 +7850,9 @@
         <f>MIN(Z13,Z25)</f>
         <v>49500</v>
       </c>
-      <c r="AA27" s="38"/>
+      <c r="AA27" s="38" t="s">
+        <v>310</v>
+      </c>
       <c r="AE27" s="19">
         <v>3</v>
       </c>
@@ -7835,7 +7900,7 @@
       <c r="C29" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="44" t="s">
         <v>170</v>
       </c>
       <c r="F29" s="25" t="s">
@@ -7847,7 +7912,9 @@
       <c r="H29" s="4">
         <v>0.92</v>
       </c>
-      <c r="AA29" s="38"/>
+      <c r="AA29" s="38" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="30" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="38" t="s">
@@ -7856,7 +7923,7 @@
       <c r="C30" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="44"/>
       <c r="F30" s="25" t="s">
         <v>171</v>
       </c>
@@ -7872,7 +7939,9 @@
         <f>G29/G20</f>
         <v>2E-3</v>
       </c>
-      <c r="AA30" s="38"/>
+      <c r="AA30" s="38" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="31" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="26"/>
@@ -7927,7 +7996,9 @@
       <c r="Y33" s="4">
         <v>2520000</v>
       </c>
-      <c r="AA33" s="38"/>
+      <c r="AA33" s="38" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="35" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
@@ -8023,10 +8094,10 @@
       </c>
     </row>
     <row r="38" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="C38" s="45" t="s">
+      <c r="C38" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F38" s="14" t="s">
@@ -8114,8 +8185,8 @@
       <c r="AA38" s="37"/>
     </row>
     <row r="39" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="47"/>
-      <c r="C39" s="45"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="42"/>
       <c r="F39" s="14" t="s">
         <v>69</v>
       </c>
@@ -8197,11 +8268,13 @@
         <f>W39-Y39</f>
         <v>80</v>
       </c>
-      <c r="AA39" s="38"/>
+      <c r="AA39" s="38" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="40" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B40" s="47"/>
-      <c r="C40" s="45"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="42"/>
       <c r="F40" s="14" t="s">
         <v>79</v>
       </c>
@@ -8282,11 +8355,13 @@
         <f>W40-Y40</f>
         <v>92</v>
       </c>
-      <c r="AA40" s="38"/>
+      <c r="AA40" s="38" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="41" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="47"/>
-      <c r="C41" s="45"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="42"/>
       <c r="F41" s="14" t="s">
         <v>80</v>
       </c>
@@ -8366,7 +8441,9 @@
         <f>W41-Y41</f>
         <v>43</v>
       </c>
-      <c r="AA41" s="38"/>
+      <c r="AA41" s="38" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="42" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F42" s="14" t="s">
@@ -8377,10 +8454,10 @@
       </c>
     </row>
     <row r="43" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F43" s="14" t="s">
@@ -8416,8 +8493,8 @@
       <c r="AA43" s="38"/>
     </row>
     <row r="44" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="47"/>
-      <c r="C44" s="45"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="42"/>
       <c r="F44" s="14" t="s">
         <v>196</v>
       </c>
@@ -8448,11 +8525,13 @@
         <f>IF(W39=0, 0, W97*Y39/W39)</f>
         <v>0</v>
       </c>
-      <c r="AA44" s="38"/>
+      <c r="AA44" s="38" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="45" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B45" s="47"/>
-      <c r="C45" s="45"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="42"/>
       <c r="F45" s="14" t="s">
         <v>197</v>
       </c>
@@ -8486,8 +8565,8 @@
       <c r="AA45" s="38"/>
     </row>
     <row r="46" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="47"/>
-      <c r="C46" s="45"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="42"/>
       <c r="F46" s="14" t="s">
         <v>198</v>
       </c>
@@ -8556,7 +8635,9 @@
         <f>SUM(Z43:Z46)</f>
         <v>0</v>
       </c>
-      <c r="AA47" s="38"/>
+      <c r="AA47" s="38" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="48" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F48" s="14" t="s">
@@ -8567,13 +8648,13 @@
       </c>
     </row>
     <row r="49" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="C49" s="45" t="s">
+      <c r="C49" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="41" t="s">
+      <c r="E49" s="44" t="s">
         <v>251</v>
       </c>
       <c r="F49" s="14" t="s">
@@ -8607,12 +8688,14 @@
         <f>MIN(Z43,Z$15*Y38)</f>
         <v>0</v>
       </c>
-      <c r="AA49" s="38"/>
+      <c r="AA49" s="38" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="50" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B50" s="47"/>
-      <c r="C50" s="45"/>
-      <c r="E50" s="41"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="42"/>
+      <c r="E50" s="44"/>
       <c r="F50" s="14" t="s">
         <v>252</v>
       </c>
@@ -8647,9 +8730,9 @@
       <c r="AA50" s="38"/>
     </row>
     <row r="51" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="47"/>
-      <c r="C51" s="45"/>
-      <c r="E51" s="41"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="42"/>
+      <c r="E51" s="44"/>
       <c r="F51" s="14" t="s">
         <v>253</v>
       </c>
@@ -8684,9 +8767,9 @@
       <c r="AA51" s="38"/>
     </row>
     <row r="52" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="47"/>
-      <c r="C52" s="45"/>
-      <c r="E52" s="41"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="42"/>
+      <c r="E52" s="44"/>
       <c r="F52" s="14" t="s">
         <v>254</v>
       </c>
@@ -8756,7 +8839,9 @@
         <f>SUM(Z49:Z52)</f>
         <v>0</v>
       </c>
-      <c r="AA53" s="38"/>
+      <c r="AA53" s="38" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B54" s="38" t="s">
@@ -8792,16 +8877,18 @@
         <f>Z47-Z53</f>
         <v>0</v>
       </c>
-      <c r="AA54" s="38"/>
+      <c r="AA54" s="38" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.2">
       <c r="F55" s="14"/>
     </row>
     <row r="56" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="47" t="s">
+      <c r="B56" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="45" t="s">
+      <c r="C56" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F56" s="14" t="s">
@@ -8835,11 +8922,13 @@
         <f>Z43*$H$21</f>
         <v>0</v>
       </c>
-      <c r="AA56" s="38"/>
+      <c r="AA56" s="38" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="57" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B57" s="47"/>
-      <c r="C57" s="45"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="42"/>
       <c r="F57" s="14" t="s">
         <v>200</v>
       </c>
@@ -8874,8 +8963,8 @@
       <c r="AA57" s="38"/>
     </row>
     <row r="58" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="47"/>
-      <c r="C58" s="45"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="42"/>
       <c r="F58" s="14" t="s">
         <v>201</v>
       </c>
@@ -8910,8 +8999,8 @@
       <c r="AA58" s="38"/>
     </row>
     <row r="59" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="47"/>
-      <c r="C59" s="45"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="42"/>
       <c r="F59" s="14" t="s">
         <v>202</v>
       </c>
@@ -8981,16 +9070,18 @@
         <f>SUM(Z56:Z59)</f>
         <v>0</v>
       </c>
-      <c r="AA60" s="38"/>
+      <c r="AA60" s="38" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="61" spans="2:27" x14ac:dyDescent="0.2">
       <c r="F61" s="14"/>
     </row>
     <row r="62" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="45" t="s">
+      <c r="C62" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F62" s="14" t="s">
@@ -9024,11 +9115,13 @@
         <f>AE14</f>
         <v>0.6</v>
       </c>
-      <c r="AA62" s="38"/>
+      <c r="AA62" s="38" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="63" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B63" s="47"/>
-      <c r="C63" s="45"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="42"/>
       <c r="F63" s="14" t="s">
         <v>91</v>
       </c>
@@ -9061,8 +9154,8 @@
       <c r="AA63" s="38"/>
     </row>
     <row r="64" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B64" s="47"/>
-      <c r="C64" s="45"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="42"/>
       <c r="F64" s="14" t="s">
         <v>92</v>
       </c>
@@ -9094,8 +9187,8 @@
       <c r="AA64" s="38"/>
     </row>
     <row r="65" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="47"/>
-      <c r="C65" s="45"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="42"/>
       <c r="F65" s="14" t="s">
         <v>93</v>
       </c>
@@ -9134,10 +9227,10 @@
       <c r="F67" s="14"/>
     </row>
     <row r="68" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="45" t="s">
+      <c r="C68" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F68" s="14" t="s">
@@ -9171,11 +9264,13 @@
         <f>W68*(1- $G$30)+Z38*Z62</f>
         <v>113.71737449773644</v>
       </c>
-      <c r="AA68" s="38"/>
+      <c r="AA68" s="38" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="69" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="47"/>
-      <c r="C69" s="45"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="42"/>
       <c r="F69" s="14" t="s">
         <v>110</v>
       </c>
@@ -9206,9 +9301,9 @@
       <c r="AA69" s="38"/>
     </row>
     <row r="70" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="47"/>
-      <c r="C70" s="45"/>
-      <c r="E70" s="41"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="42"/>
+      <c r="E70" s="44"/>
       <c r="F70" s="14" t="s">
         <v>111</v>
       </c>
@@ -9235,9 +9330,9 @@
       <c r="AA70" s="38"/>
     </row>
     <row r="71" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="47"/>
-      <c r="C71" s="45"/>
-      <c r="E71" s="41"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="42"/>
+      <c r="E71" s="44"/>
       <c r="F71" s="14" t="s">
         <v>112</v>
       </c>
@@ -9264,14 +9359,14 @@
       <c r="AA71" s="38"/>
     </row>
     <row r="72" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="E72" s="41"/>
+      <c r="E72" s="44"/>
       <c r="F72" s="14"/>
     </row>
     <row r="73" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B73" s="47" t="s">
+      <c r="B73" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="C73" s="45" t="s">
+      <c r="C73" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F73" s="14" t="s">
@@ -9307,8 +9402,8 @@
       <c r="AA73" s="38"/>
     </row>
     <row r="74" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B74" s="47"/>
-      <c r="C74" s="45"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="42"/>
       <c r="F74" s="14" t="s">
         <v>128</v>
       </c>
@@ -9342,9 +9437,9 @@
       <c r="AA74" s="38"/>
     </row>
     <row r="75" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="47"/>
-      <c r="C75" s="45"/>
-      <c r="E75" s="41" t="s">
+      <c r="B75" s="43"/>
+      <c r="C75" s="42"/>
+      <c r="E75" s="44" t="s">
         <v>152</v>
       </c>
       <c r="F75" s="14" t="s">
@@ -9380,9 +9475,9 @@
       <c r="AA75" s="38"/>
     </row>
     <row r="76" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B76" s="47"/>
-      <c r="C76" s="45"/>
-      <c r="E76" s="41"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="42"/>
+      <c r="E76" s="44"/>
       <c r="F76" s="14" t="s">
         <v>130</v>
       </c>
@@ -9422,7 +9517,7 @@
       <c r="C77" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E77" s="41"/>
+      <c r="E77" s="44"/>
       <c r="F77" s="14" t="s">
         <v>147</v>
       </c>
@@ -9459,7 +9554,7 @@
       </c>
     </row>
     <row r="78" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="E78" s="41"/>
+      <c r="E78" s="44"/>
       <c r="F78" s="14"/>
       <c r="AD78" t="s">
         <v>85</v>
@@ -9469,10 +9564,10 @@
       </c>
     </row>
     <row r="79" spans="2:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="48" t="s">
+      <c r="B79" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="C79" s="45" t="s">
+      <c r="C79" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F79" s="14" t="s">
@@ -9505,8 +9600,8 @@
       </c>
     </row>
     <row r="80" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B80" s="48"/>
-      <c r="C80" s="45"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="42"/>
       <c r="F80" s="14" t="s">
         <v>148</v>
       </c>
@@ -9569,8 +9664,8 @@
       <c r="AA80" s="39"/>
     </row>
     <row r="81" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="48"/>
-      <c r="C81" s="45"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="42"/>
       <c r="E81" s="22">
         <v>0</v>
       </c>
@@ -9636,8 +9731,8 @@
       <c r="AA81" s="39"/>
     </row>
     <row r="82" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="48"/>
-      <c r="C82" s="45"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="42"/>
       <c r="E82" s="22">
         <v>1</v>
       </c>
@@ -9703,8 +9798,8 @@
       <c r="AA82" s="39"/>
     </row>
     <row r="83" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="48"/>
-      <c r="C83" s="45"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="42"/>
       <c r="E83" s="22">
         <v>2</v>
       </c>
@@ -9797,10 +9892,10 @@
       </c>
     </row>
     <row r="86" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B86" s="46" t="s">
+      <c r="B86" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="C86" s="45" t="s">
+      <c r="C86" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F86" s="14" t="s">
@@ -9861,8 +9956,8 @@
       <c r="AA86" s="37"/>
     </row>
     <row r="87" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B87" s="46"/>
-      <c r="C87" s="45"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="42"/>
       <c r="F87" s="14" t="s">
         <v>132</v>
       </c>
@@ -9921,8 +10016,8 @@
       <c r="AA87" s="37"/>
     </row>
     <row r="88" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B88" s="46"/>
-      <c r="C88" s="45"/>
+      <c r="B88" s="41"/>
+      <c r="C88" s="42"/>
       <c r="F88" s="14" t="s">
         <v>133</v>
       </c>
@@ -9981,8 +10076,8 @@
       <c r="AA88" s="37"/>
     </row>
     <row r="89" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B89" s="46"/>
-      <c r="C89" s="45"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="42"/>
       <c r="F89" s="14" t="s">
         <v>134</v>
       </c>
@@ -10044,10 +10139,10 @@
       <c r="F90" s="14"/>
     </row>
     <row r="91" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="46" t="s">
+      <c r="B91" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="45" t="s">
+      <c r="C91" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F91" s="14" t="s">
@@ -10084,8 +10179,8 @@
       <c r="AA91" s="37"/>
     </row>
     <row r="92" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="46"/>
-      <c r="C92" s="45"/>
+      <c r="B92" s="41"/>
+      <c r="C92" s="42"/>
       <c r="F92" s="14" t="s">
         <v>206</v>
       </c>
@@ -10120,8 +10215,8 @@
       <c r="AA92" s="37"/>
     </row>
     <row r="93" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="46"/>
-      <c r="C93" s="45"/>
+      <c r="B93" s="41"/>
+      <c r="C93" s="42"/>
       <c r="F93" s="14" t="s">
         <v>207</v>
       </c>
@@ -10156,8 +10251,8 @@
       <c r="AA93" s="37"/>
     </row>
     <row r="94" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="46"/>
-      <c r="C94" s="45"/>
+      <c r="B94" s="41"/>
+      <c r="C94" s="42"/>
       <c r="F94" s="14" t="s">
         <v>208</v>
       </c>
@@ -10195,10 +10290,10 @@
       <c r="F95" s="14"/>
     </row>
     <row r="96" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B96" s="46" t="s">
+      <c r="B96" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C96" s="45" t="s">
+      <c r="C96" s="42" t="s">
         <v>174</v>
       </c>
       <c r="F96" s="14" t="s">
@@ -10235,8 +10330,8 @@
       <c r="AA96" s="37"/>
     </row>
     <row r="97" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="46"/>
-      <c r="C97" s="45"/>
+      <c r="B97" s="41"/>
+      <c r="C97" s="42"/>
       <c r="F97" s="14" t="s">
         <v>71</v>
       </c>
@@ -10271,8 +10366,8 @@
       <c r="AA97" s="37"/>
     </row>
     <row r="98" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B98" s="46"/>
-      <c r="C98" s="45"/>
+      <c r="B98" s="41"/>
+      <c r="C98" s="42"/>
       <c r="F98" s="14" t="s">
         <v>72</v>
       </c>
@@ -10307,8 +10402,8 @@
       <c r="AA98" s="37"/>
     </row>
     <row r="99" spans="2:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="46"/>
-      <c r="C99" s="45"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="42"/>
       <c r="F99" s="14" t="s">
         <v>81</v>
       </c>
@@ -10347,10 +10442,10 @@
       <c r="F100" s="14"/>
     </row>
     <row r="101" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B101" s="46" t="s">
+      <c r="B101" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="C101" s="45" t="s">
+      <c r="C101" s="42" t="s">
         <v>174</v>
       </c>
       <c r="E101" s="26"/>
@@ -10388,8 +10483,8 @@
       <c r="AA101" s="37"/>
     </row>
     <row r="102" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="46"/>
-      <c r="C102" s="45"/>
+      <c r="B102" s="41"/>
+      <c r="C102" s="42"/>
       <c r="E102" s="26"/>
       <c r="F102" s="14" t="s">
         <v>212</v>
@@ -10425,8 +10520,8 @@
       <c r="AA102" s="37"/>
     </row>
     <row r="103" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="46"/>
-      <c r="C103" s="45"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="42"/>
       <c r="E103" s="26"/>
       <c r="F103" s="14" t="s">
         <v>213</v>
@@ -10462,8 +10557,8 @@
       <c r="AA103" s="37"/>
     </row>
     <row r="104" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="46"/>
-      <c r="C104" s="45"/>
+      <c r="B104" s="41"/>
+      <c r="C104" s="42"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
         <v>214</v>
@@ -10724,7 +10819,7 @@
         <v>0.86560925711218095</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="111" spans="2:27" ht="17" x14ac:dyDescent="0.2">
@@ -12059,7 +12154,7 @@
     </row>
     <row r="137" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B137" s="38" t="s">
         <v>186</v>
@@ -12455,7 +12550,7 @@
     </row>
     <row r="145" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B145" s="38" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>163</v>
@@ -12724,7 +12819,7 @@
     </row>
     <row r="149" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>163</v>
@@ -12953,6 +13048,30 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="E75:E78"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="C56:C59"/>
     <mergeCell ref="B101:B104"/>
     <mergeCell ref="C101:C104"/>
     <mergeCell ref="B49:B52"/>
@@ -12968,30 +13087,6 @@
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="C73:C76"/>
     <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="C56:C59"/>
-    <mergeCell ref="AE4:AG4"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="E75:E78"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36EE739-1C78-174B-BB96-7938DAAAF8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143413A2-A337-814F-8CE2-89532D7AB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="-3240" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="336">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -968,33 +968,15 @@
     <t>\delta(t)</t>
   </si>
   <si>
-    <t>A_{protected}(t)</t>
-  </si>
-  <si>
-    <t>a_{protected}(t)</t>
-  </si>
-  <si>
     <t>A^*(t)</t>
   </si>
   <si>
-    <t>A^*_{protected}(t)</t>
-  </si>
-  <si>
     <t>d(t)</t>
   </si>
   <si>
     <t>A^*(t + 1)</t>
   </si>
   <si>
-    <t>A_{young}(t, u)</t>
-  </si>
-  <si>
-    <t>\hat{A}_{young}(t, u)</t>
-  </si>
-  <si>
-    <t>L_{young}(t, u)</t>
-  </si>
-  <si>
     <t>\overline{Y}_{conv}(t, u)</t>
   </si>
   <si>
@@ -1020,6 +1002,57 @@
   </si>
   <si>
     <t>\overline{Y}^*(t, u)</t>
+  </si>
+  <si>
+    <t>A^{young}(t, u)</t>
+  </si>
+  <si>
+    <t>\hat{A}^{young}(t, u)</t>
+  </si>
+  <si>
+    <t>L^{young}(t, u)</t>
+  </si>
+  <si>
+    <t>A^{(protected)}(t)</t>
+  </si>
+  <si>
+    <t>a^{(protected)}(t)</t>
+  </si>
+  <si>
+    <t>A^{(*protected)}(t)</t>
+  </si>
+  <si>
+    <t>latex description</t>
+  </si>
+  <si>
+    <t>Area of land use at beginning of time $t$</t>
+  </si>
+  <si>
+    <t>Total of land converted away from type during time $t$</t>
+  </si>
+  <si>
+    <t>Area remaining from land use type at beginning of simulation at beginning of time $t$</t>
+  </si>
+  <si>
+    <t>Area of young forest converted away</t>
+  </si>
+  <si>
+    <t>Area of young forest that would be converted away assuming no protection (counterfactual)</t>
+  </si>
+  <si>
+    <t>Area of conversion into new forest land (planted or restored)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Fraction of biomass in each forest type that's converted to another land use class that is available for use to satisfy fuelwood and harvested wood product demands</t>
+  </si>
+  <si>
+    <t>Average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
+  </si>
+  <si>
+    <t>Average above ground stock contained In land use classes that forests transition into; used to estimate above-ground conversion losses of stock.</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1287,20 +1320,11 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1308,8 +1332,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1322,6 +1355,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1883,12 +1922,12 @@
         <v>29</v>
       </c>
       <c r="M1" s="51"/>
-      <c r="N1" s="47" t="s">
+      <c r="N1" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
       <c r="R1" s="51" t="s">
         <v>48</v>
       </c>
@@ -6448,16 +6487,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="U1:V1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6490,7 +6529,8 @@
     <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
     <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
-    <col min="28" max="30" width="14.6640625" customWidth="1"/>
+    <col min="28" max="28" width="48.33203125" style="53" customWidth="1"/>
+    <col min="29" max="30" width="14.6640625" customWidth="1"/>
     <col min="31" max="33" width="14.1640625" customWidth="1"/>
     <col min="34" max="34" width="4.1640625" customWidth="1"/>
     <col min="35" max="35" width="3.33203125" customWidth="1"/>
@@ -6529,6 +6569,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="24"/>
+      <c r="AB1" s="55"/>
     </row>
     <row r="2" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="24"/>
@@ -6542,10 +6583,10 @@
       <c r="H2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="47">
+      <c r="I2" s="44">
         <v>150</v>
       </c>
-      <c r="J2" s="47"/>
+      <c r="J2" s="44"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -6565,6 +6606,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="24"/>
+      <c r="AB2" s="55"/>
     </row>
     <row r="3" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="24"/>
@@ -6576,10 +6618,10 @@
       <c r="H3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="47">
+      <c r="I3" s="44">
         <v>30</v>
       </c>
-      <c r="J3" s="47"/>
+      <c r="J3" s="44"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -6597,6 +6639,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="24"/>
+      <c r="AB3" s="55"/>
     </row>
     <row r="4" spans="1:41" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G4" s="8">
@@ -6633,11 +6676,12 @@
         <v>6</v>
       </c>
       <c r="Z4" s="20"/>
-      <c r="AE4" s="46" t="s">
+      <c r="AB4" s="55"/>
+      <c r="AE4" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="46"/>
+      <c r="AF4" s="43"/>
+      <c r="AG4" s="43"/>
       <c r="AL4" t="s">
         <v>94</v>
       </c>
@@ -6667,37 +6711,40 @@
       <c r="F5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="48"/>
+      <c r="H5" s="42"/>
       <c r="I5" s="17"/>
-      <c r="J5" s="48" t="s">
+      <c r="J5" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="48"/>
-      <c r="M5" s="48" t="s">
+      <c r="K5" s="42"/>
+      <c r="M5" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="48"/>
-      <c r="P5" s="48" t="s">
+      <c r="N5" s="42"/>
+      <c r="P5" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="48"/>
-      <c r="S5" s="48" t="s">
+      <c r="Q5" s="42"/>
+      <c r="S5" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="T5" s="48"/>
-      <c r="V5" s="48" t="s">
+      <c r="T5" s="42"/>
+      <c r="V5" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="W5" s="48"/>
-      <c r="Y5" s="48" t="s">
+      <c r="W5" s="42"/>
+      <c r="Y5" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="Z5" s="48"/>
+      <c r="Z5" s="42"/>
       <c r="AA5" s="24" t="s">
         <v>284</v>
+      </c>
+      <c r="AB5" s="56" t="s">
+        <v>325</v>
       </c>
       <c r="AD5" s="36" t="s">
         <v>234</v>
@@ -6768,6 +6815,7 @@
       <c r="Z6" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="AB6" s="55"/>
       <c r="AE6" s="19">
         <v>0</v>
       </c>
@@ -6856,7 +6904,10 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>309</v>
+        <v>307</v>
+      </c>
+      <c r="AB7" s="54" t="s">
+        <v>328</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -6950,6 +7001,9 @@
       <c r="AA8" s="38" t="s">
         <v>285</v>
       </c>
+      <c r="AB8" s="54" t="s">
+        <v>326</v>
+      </c>
       <c r="AE8" s="19">
         <v>0.05</v>
       </c>
@@ -7028,6 +7082,9 @@
       <c r="AA9" s="38" t="s">
         <v>287</v>
       </c>
+      <c r="AB9" s="54" t="s">
+        <v>327</v>
+      </c>
       <c r="AE9" s="19">
         <v>0.12</v>
       </c>
@@ -7092,6 +7149,9 @@
       <c r="AA10" s="38" t="s">
         <v>288</v>
       </c>
+      <c r="AB10" s="54" t="s">
+        <v>330</v>
+      </c>
       <c r="AE10" s="19">
         <v>0.2</v>
       </c>
@@ -7144,6 +7204,9 @@
       <c r="AA11" s="38" t="s">
         <v>289</v>
       </c>
+      <c r="AB11" s="54" t="s">
+        <v>329</v>
+      </c>
       <c r="AE11" s="19">
         <v>0.2</v>
       </c>
@@ -7189,6 +7252,9 @@
       <c r="AA12" s="38" t="s">
         <v>286</v>
       </c>
+      <c r="AB12" s="54" t="s">
+        <v>331</v>
+      </c>
       <c r="AE12" s="19">
         <v>0.36</v>
       </c>
@@ -7267,7 +7333,10 @@
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>312</v>
+        <v>309</v>
+      </c>
+      <c r="AB13" s="54" t="s">
+        <v>332</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7307,6 +7376,9 @@
       <c r="AA14" s="38" t="s">
         <v>290</v>
       </c>
+      <c r="AB14" s="54" t="s">
+        <v>333</v>
+      </c>
       <c r="AE14" s="19">
         <v>0.6</v>
       </c>
@@ -7375,6 +7447,9 @@
       </c>
       <c r="AA15" s="38" t="s">
         <v>302</v>
+      </c>
+      <c r="AB15" s="54" t="s">
+        <v>335</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7444,6 +7519,9 @@
       <c r="AA16" s="38" t="s">
         <v>303</v>
       </c>
+      <c r="AB16" s="54" t="s">
+        <v>334</v>
+      </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
       <c r="AG16" s="19"/>
@@ -7467,6 +7545,7 @@
       <c r="AA17" s="38" t="s">
         <v>291</v>
       </c>
+      <c r="AB17" s="54"/>
       <c r="AE17" s="19">
         <v>1.8</v>
       </c>
@@ -7485,7 +7564,7 @@
       <c r="C18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="41" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="10" t="s">
@@ -7500,6 +7579,7 @@
       <c r="AA18" s="38" t="s">
         <v>292</v>
       </c>
+      <c r="AB18" s="54"/>
       <c r="AE18" s="19">
         <v>3</v>
       </c>
@@ -7518,7 +7598,7 @@
       <c r="C19" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="44"/>
+      <c r="E19" s="41"/>
       <c r="F19" s="10" t="s">
         <v>138</v>
       </c>
@@ -7528,6 +7608,7 @@
       <c r="AA19" s="40" t="s">
         <v>293</v>
       </c>
+      <c r="AB19" s="54"/>
       <c r="AE19" s="19">
         <v>6</v>
       </c>
@@ -7558,6 +7639,7 @@
       <c r="AA20" s="38" t="s">
         <v>304</v>
       </c>
+      <c r="AB20" s="54"/>
       <c r="AE20" s="19">
         <v>10</v>
       </c>
@@ -7588,6 +7670,7 @@
       <c r="AA21" s="38" t="s">
         <v>294</v>
       </c>
+      <c r="AB21" s="54"/>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
       <c r="AG21" s="19"/>
@@ -7611,6 +7694,7 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38"/>
+      <c r="AB22" s="54"/>
       <c r="AE22" s="19">
         <v>12</v>
       </c>
@@ -7643,6 +7727,7 @@
       <c r="AA23" s="38" t="s">
         <v>295</v>
       </c>
+      <c r="AB23" s="54"/>
       <c r="AE23" s="19">
         <v>13.5</v>
       </c>
@@ -7655,6 +7740,7 @@
       </c>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AB24" s="55"/>
       <c r="AE24" s="19">
         <v>12</v>
       </c>
@@ -7719,8 +7805,9 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>307</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="AB25" s="54"/>
       <c r="AE25" s="19">
         <v>10</v>
       </c>
@@ -7771,8 +7858,9 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>308</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="AB26" s="54"/>
       <c r="AE26" s="19">
         <v>6</v>
       </c>
@@ -7851,8 +7939,9 @@
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>310</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="AB27" s="54"/>
       <c r="AE27" s="19">
         <v>3</v>
       </c>
@@ -7882,6 +7971,7 @@
       <c r="W28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
+      <c r="AB28" s="55"/>
       <c r="AE28" s="19">
         <v>1.8</v>
       </c>
@@ -7900,7 +7990,7 @@
       <c r="C29" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="E29" s="41" t="s">
         <v>170</v>
       </c>
       <c r="F29" s="25" t="s">
@@ -7915,6 +8005,7 @@
       <c r="AA29" s="38" t="s">
         <v>305</v>
       </c>
+      <c r="AB29" s="54"/>
     </row>
     <row r="30" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="38" t="s">
@@ -7923,7 +8014,7 @@
       <c r="C30" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="44"/>
+      <c r="E30" s="41"/>
       <c r="F30" s="25" t="s">
         <v>171</v>
       </c>
@@ -7942,9 +8033,11 @@
       <c r="AA30" s="38" t="s">
         <v>306</v>
       </c>
+      <c r="AB30" s="54"/>
     </row>
     <row r="31" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="26"/>
+      <c r="AB31" s="54"/>
     </row>
     <row r="32" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="F32" s="15" t="s">
@@ -7964,6 +8057,7 @@
       <c r="W32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
+      <c r="AB32" s="54"/>
     </row>
     <row r="33" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="38" t="s">
@@ -7997,8 +8091,12 @@
         <v>2520000</v>
       </c>
       <c r="AA33" s="38" t="s">
-        <v>311</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="AB33" s="54"/>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB34" s="54"/>
     </row>
     <row r="35" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
@@ -8018,6 +8116,7 @@
       <c r="W35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
+      <c r="AB35" s="54"/>
     </row>
     <row r="36" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F36" s="15" t="s">
@@ -8039,6 +8138,7 @@
       <c r="P36" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="AB36" s="54"/>
     </row>
     <row r="37" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B37" s="24" t="s">
@@ -8092,12 +8192,13 @@
       <c r="Z37" s="4">
         <v>0</v>
       </c>
+      <c r="AB37" s="54"/>
     </row>
     <row r="38" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F38" s="14" t="s">
@@ -8183,10 +8284,11 @@
         <v>85</v>
       </c>
       <c r="AA38" s="37"/>
+      <c r="AB38" s="54"/>
     </row>
     <row r="39" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="43"/>
-      <c r="C39" s="42"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="45"/>
       <c r="F39" s="14" t="s">
         <v>69</v>
       </c>
@@ -8269,12 +8371,13 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
-        <v>313</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="AB39" s="54"/>
     </row>
     <row r="40" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B40" s="43"/>
-      <c r="C40" s="42"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="45"/>
       <c r="F40" s="14" t="s">
         <v>79</v>
       </c>
@@ -8356,12 +8459,13 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>314</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="AB40" s="54"/>
     </row>
     <row r="41" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="43"/>
-      <c r="C41" s="42"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="45"/>
       <c r="F41" s="14" t="s">
         <v>80</v>
       </c>
@@ -8442,22 +8546,23 @@
         <v>43</v>
       </c>
       <c r="AA41" s="38" t="s">
-        <v>315</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="AB41" s="54"/>
     </row>
     <row r="42" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AB42" s="54" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="43" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B43" s="43" t="s">
+      <c r="B43" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F43" s="14" t="s">
@@ -8491,10 +8596,11 @@
         <v>0</v>
       </c>
       <c r="AA43" s="38"/>
+      <c r="AB43" s="54"/>
     </row>
     <row r="44" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="43"/>
-      <c r="C44" s="42"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="45"/>
       <c r="F44" s="14" t="s">
         <v>196</v>
       </c>
@@ -8526,12 +8632,13 @@
         <v>0</v>
       </c>
       <c r="AA44" s="38" t="s">
-        <v>316</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="AB44" s="54"/>
     </row>
     <row r="45" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B45" s="43"/>
-      <c r="C45" s="42"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="45"/>
       <c r="F45" s="14" t="s">
         <v>197</v>
       </c>
@@ -8563,10 +8670,11 @@
         <v>0</v>
       </c>
       <c r="AA45" s="38"/>
+      <c r="AB45" s="54"/>
     </row>
     <row r="46" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="43"/>
-      <c r="C46" s="42"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="45"/>
       <c r="F46" s="14" t="s">
         <v>198</v>
       </c>
@@ -8598,6 +8706,7 @@
         <v>0</v>
       </c>
       <c r="AA46" s="38"/>
+      <c r="AB46" s="54"/>
     </row>
     <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B47" s="38" t="s">
@@ -8636,25 +8745,26 @@
         <v>0</v>
       </c>
       <c r="AA47" s="38" t="s">
-        <v>317</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="AB47" s="54"/>
     </row>
     <row r="48" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F48" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB48" t="s">
+      <c r="AB48" s="54" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="43" t="s">
+    <row r="49" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B49" s="47" t="s">
         <v>263</v>
       </c>
-      <c r="C49" s="42" t="s">
+      <c r="C49" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="44" t="s">
+      <c r="E49" s="41" t="s">
         <v>251</v>
       </c>
       <c r="F49" s="14" t="s">
@@ -8689,13 +8799,14 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="50" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B50" s="43"/>
-      <c r="C50" s="42"/>
-      <c r="E50" s="44"/>
+        <v>312</v>
+      </c>
+      <c r="AB49" s="54"/>
+    </row>
+    <row r="50" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B50" s="47"/>
+      <c r="C50" s="45"/>
+      <c r="E50" s="41"/>
       <c r="F50" s="14" t="s">
         <v>252</v>
       </c>
@@ -8728,11 +8839,12 @@
         <v>0</v>
       </c>
       <c r="AA50" s="38"/>
-    </row>
-    <row r="51" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="43"/>
-      <c r="C51" s="42"/>
-      <c r="E51" s="44"/>
+      <c r="AB50" s="54"/>
+    </row>
+    <row r="51" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B51" s="47"/>
+      <c r="C51" s="45"/>
+      <c r="E51" s="41"/>
       <c r="F51" s="14" t="s">
         <v>253</v>
       </c>
@@ -8765,11 +8877,12 @@
         <v>0</v>
       </c>
       <c r="AA51" s="38"/>
-    </row>
-    <row r="52" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="43"/>
-      <c r="C52" s="42"/>
-      <c r="E52" s="44"/>
+      <c r="AB51" s="54"/>
+    </row>
+    <row r="52" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B52" s="47"/>
+      <c r="C52" s="45"/>
+      <c r="E52" s="41"/>
       <c r="F52" s="14" t="s">
         <v>254</v>
       </c>
@@ -8802,8 +8915,9 @@
         <v>0</v>
       </c>
       <c r="AA52" s="38"/>
-    </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="54"/>
+    </row>
+    <row r="53" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B53" s="38" t="s">
         <v>264</v>
       </c>
@@ -8840,10 +8954,11 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+      <c r="AB53" s="54"/>
+    </row>
+    <row r="54" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B54" s="38" t="s">
         <v>266</v>
       </c>
@@ -8878,17 +8993,19 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+      <c r="AB54" s="54"/>
+    </row>
+    <row r="55" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F55" s="14"/>
-    </row>
-    <row r="56" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="43" t="s">
+      <c r="AB55" s="54"/>
+    </row>
+    <row r="56" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B56" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="42" t="s">
+      <c r="C56" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F56" s="14" t="s">
@@ -8923,12 +9040,13 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="57" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B57" s="43"/>
-      <c r="C57" s="42"/>
+        <v>315</v>
+      </c>
+      <c r="AB56" s="54"/>
+    </row>
+    <row r="57" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B57" s="47"/>
+      <c r="C57" s="45"/>
       <c r="F57" s="14" t="s">
         <v>200</v>
       </c>
@@ -8961,10 +9079,11 @@
         <v>0</v>
       </c>
       <c r="AA57" s="38"/>
-    </row>
-    <row r="58" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="43"/>
-      <c r="C58" s="42"/>
+      <c r="AB57" s="54"/>
+    </row>
+    <row r="58" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B58" s="47"/>
+      <c r="C58" s="45"/>
       <c r="F58" s="14" t="s">
         <v>201</v>
       </c>
@@ -8997,10 +9116,11 @@
         <v>0</v>
       </c>
       <c r="AA58" s="38"/>
-    </row>
-    <row r="59" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="43"/>
-      <c r="C59" s="42"/>
+      <c r="AB58" s="54"/>
+    </row>
+    <row r="59" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B59" s="47"/>
+      <c r="C59" s="45"/>
       <c r="F59" s="14" t="s">
         <v>202</v>
       </c>
@@ -9033,8 +9153,9 @@
         <v>0</v>
       </c>
       <c r="AA59" s="38"/>
-    </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="54"/>
+    </row>
+    <row r="60" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B60" s="38" t="s">
         <v>194</v>
       </c>
@@ -9071,17 +9192,19 @@
         <v>0</v>
       </c>
       <c r="AA60" s="38" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+      <c r="AB60" s="54"/>
+    </row>
+    <row r="61" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F61" s="14"/>
-    </row>
-    <row r="62" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B62" s="43" t="s">
+      <c r="AB61" s="54"/>
+    </row>
+    <row r="62" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B62" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="42" t="s">
+      <c r="C62" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F62" s="14" t="s">
@@ -9116,12 +9239,13 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="63" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B63" s="43"/>
-      <c r="C63" s="42"/>
+        <v>317</v>
+      </c>
+      <c r="AB62" s="54"/>
+    </row>
+    <row r="63" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B63" s="47"/>
+      <c r="C63" s="45"/>
       <c r="F63" s="14" t="s">
         <v>91</v>
       </c>
@@ -9152,10 +9276,11 @@
         <v>0.36</v>
       </c>
       <c r="AA63" s="38"/>
-    </row>
-    <row r="64" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B64" s="43"/>
-      <c r="C64" s="42"/>
+      <c r="AB63" s="54"/>
+    </row>
+    <row r="64" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B64" s="47"/>
+      <c r="C64" s="45"/>
       <c r="F64" s="14" t="s">
         <v>92</v>
       </c>
@@ -9185,10 +9310,11 @@
         <v>0.2</v>
       </c>
       <c r="AA64" s="38"/>
+      <c r="AB64" s="54"/>
     </row>
     <row r="65" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="43"/>
-      <c r="C65" s="42"/>
+      <c r="B65" s="47"/>
+      <c r="C65" s="45"/>
       <c r="F65" s="14" t="s">
         <v>93</v>
       </c>
@@ -9217,20 +9343,23 @@
         <v>0.12</v>
       </c>
       <c r="AA65" s="38"/>
+      <c r="AB65" s="54"/>
     </row>
     <row r="66" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="F66" s="14" t="s">
         <v>49</v>
       </c>
+      <c r="AB66" s="54"/>
     </row>
     <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="F67" s="14"/>
+      <c r="AB67" s="54"/>
     </row>
     <row r="68" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="43" t="s">
+      <c r="B68" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="42" t="s">
+      <c r="C68" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F68" s="14" t="s">
@@ -9265,12 +9394,13 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>324</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AB68" s="54"/>
     </row>
     <row r="69" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="43"/>
-      <c r="C69" s="42"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="45"/>
       <c r="F69" s="14" t="s">
         <v>110</v>
       </c>
@@ -9299,11 +9429,12 @@
         <v>59.120937045501634</v>
       </c>
       <c r="AA69" s="38"/>
+      <c r="AB69" s="54"/>
     </row>
     <row r="70" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="43"/>
-      <c r="C70" s="42"/>
-      <c r="E70" s="44"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="45"/>
+      <c r="E70" s="41"/>
       <c r="F70" s="14" t="s">
         <v>111</v>
       </c>
@@ -9328,11 +9459,12 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA70" s="38"/>
+      <c r="AB70" s="54"/>
     </row>
     <row r="71" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="43"/>
-      <c r="C71" s="42"/>
-      <c r="E71" s="44"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="45"/>
+      <c r="E71" s="41"/>
       <c r="F71" s="14" t="s">
         <v>112</v>
       </c>
@@ -9357,16 +9489,18 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA71" s="38"/>
+      <c r="AB71" s="54"/>
     </row>
     <row r="72" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="E72" s="44"/>
+      <c r="E72" s="41"/>
       <c r="F72" s="14"/>
+      <c r="AB72" s="54"/>
     </row>
     <row r="73" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B73" s="43" t="s">
+      <c r="B73" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C73" s="42" t="s">
+      <c r="C73" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F73" s="14" t="s">
@@ -9400,10 +9534,11 @@
         <v>0</v>
       </c>
       <c r="AA73" s="38"/>
+      <c r="AB73" s="54"/>
     </row>
     <row r="74" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B74" s="43"/>
-      <c r="C74" s="42"/>
+      <c r="B74" s="47"/>
+      <c r="C74" s="45"/>
       <c r="F74" s="14" t="s">
         <v>128</v>
       </c>
@@ -9435,11 +9570,12 @@
         <v>0</v>
       </c>
       <c r="AA74" s="38"/>
+      <c r="AB74" s="54"/>
     </row>
     <row r="75" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="43"/>
-      <c r="C75" s="42"/>
-      <c r="E75" s="44" t="s">
+      <c r="B75" s="47"/>
+      <c r="C75" s="45"/>
+      <c r="E75" s="41" t="s">
         <v>152</v>
       </c>
       <c r="F75" s="14" t="s">
@@ -9473,11 +9609,12 @@
         <v>0</v>
       </c>
       <c r="AA75" s="38"/>
+      <c r="AB75" s="54"/>
     </row>
     <row r="76" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B76" s="43"/>
-      <c r="C76" s="42"/>
-      <c r="E76" s="44"/>
+      <c r="B76" s="47"/>
+      <c r="C76" s="45"/>
+      <c r="E76" s="41"/>
       <c r="F76" s="14" t="s">
         <v>130</v>
       </c>
@@ -9509,6 +9646,7 @@
         <v>0</v>
       </c>
       <c r="AA76" s="38"/>
+      <c r="AB76" s="54"/>
     </row>
     <row r="77" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B77" s="38" t="s">
@@ -9517,7 +9655,7 @@
       <c r="C77" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E77" s="44"/>
+      <c r="E77" s="41"/>
       <c r="F77" s="14" t="s">
         <v>147</v>
       </c>
@@ -9549,13 +9687,15 @@
         <v>0</v>
       </c>
       <c r="AA77" s="38"/>
+      <c r="AB77" s="54"/>
       <c r="AF77" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="78" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="E78" s="44"/>
+      <c r="E78" s="41"/>
       <c r="F78" s="14"/>
+      <c r="AB78" s="54"/>
       <c r="AD78" t="s">
         <v>85</v>
       </c>
@@ -9564,10 +9704,10 @@
       </c>
     </row>
     <row r="79" spans="2:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="45" t="s">
+      <c r="B79" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="C79" s="42" t="s">
+      <c r="C79" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F79" s="14" t="s">
@@ -9595,13 +9735,14 @@
         <v>0</v>
       </c>
       <c r="AA79" s="39"/>
+      <c r="AB79" s="54"/>
       <c r="AD79" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="80" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B80" s="45"/>
-      <c r="C80" s="42"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="45"/>
       <c r="F80" s="14" t="s">
         <v>148</v>
       </c>
@@ -9662,10 +9803,11 @@
         <v>0</v>
       </c>
       <c r="AA80" s="39"/>
-    </row>
-    <row r="81" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="45"/>
-      <c r="C81" s="42"/>
+      <c r="AB80" s="54"/>
+    </row>
+    <row r="81" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B81" s="48"/>
+      <c r="C81" s="45"/>
       <c r="E81" s="22">
         <v>0</v>
       </c>
@@ -9729,10 +9871,11 @@
         <v>0</v>
       </c>
       <c r="AA81" s="39"/>
-    </row>
-    <row r="82" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="45"/>
-      <c r="C82" s="42"/>
+      <c r="AB81" s="54"/>
+    </row>
+    <row r="82" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B82" s="48"/>
+      <c r="C82" s="45"/>
       <c r="E82" s="22">
         <v>1</v>
       </c>
@@ -9796,10 +9939,11 @@
         <v>0</v>
       </c>
       <c r="AA82" s="39"/>
-    </row>
-    <row r="83" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="45"/>
-      <c r="C83" s="42"/>
+      <c r="AB82" s="54"/>
+    </row>
+    <row r="83" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B83" s="48"/>
+      <c r="C83" s="45"/>
       <c r="E83" s="22">
         <v>2</v>
       </c>
@@ -9863,14 +10007,16 @@
         <v>0</v>
       </c>
       <c r="AA83" s="39"/>
-    </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="54"/>
+    </row>
+    <row r="84" spans="2:28" x14ac:dyDescent="0.2">
       <c r="E84" s="22">
         <v>3</v>
       </c>
       <c r="F84" s="14"/>
-    </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="54"/>
+    </row>
+    <row r="85" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F85" s="14"/>
       <c r="J85" s="4" t="s">
         <v>136</v>
@@ -9890,12 +10036,13 @@
       <c r="Y85" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="86" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B86" s="41" t="s">
+      <c r="AB85" s="54"/>
+    </row>
+    <row r="86" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B86" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C86" s="42" t="s">
+      <c r="C86" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F86" s="14" t="s">
@@ -9954,10 +10101,11 @@
         <v>0.6</v>
       </c>
       <c r="AA86" s="37"/>
-    </row>
-    <row r="87" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B87" s="41"/>
-      <c r="C87" s="42"/>
+      <c r="AB86" s="54"/>
+    </row>
+    <row r="87" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B87" s="46"/>
+      <c r="C87" s="45"/>
       <c r="F87" s="14" t="s">
         <v>132</v>
       </c>
@@ -10014,10 +10162,11 @@
         <v>0.36</v>
       </c>
       <c r="AA87" s="37"/>
-    </row>
-    <row r="88" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B88" s="41"/>
-      <c r="C88" s="42"/>
+      <c r="AB87" s="54"/>
+    </row>
+    <row r="88" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B88" s="46"/>
+      <c r="C88" s="45"/>
       <c r="F88" s="14" t="s">
         <v>133</v>
       </c>
@@ -10074,10 +10223,11 @@
         <v>0.2</v>
       </c>
       <c r="AA88" s="37"/>
-    </row>
-    <row r="89" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B89" s="41"/>
-      <c r="C89" s="42"/>
+      <c r="AB88" s="54"/>
+    </row>
+    <row r="89" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B89" s="46"/>
+      <c r="C89" s="45"/>
       <c r="F89" s="14" t="s">
         <v>134</v>
       </c>
@@ -10134,15 +10284,17 @@
         <v>0.12</v>
       </c>
       <c r="AA89" s="37"/>
-    </row>
-    <row r="90" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="54"/>
+    </row>
+    <row r="90" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F90" s="14"/>
-    </row>
-    <row r="91" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="41" t="s">
+      <c r="AB90" s="54"/>
+    </row>
+    <row r="91" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B91" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="42" t="s">
+      <c r="C91" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F91" s="14" t="s">
@@ -10177,10 +10329,11 @@
         <v>9.8621113109027395E-2</v>
       </c>
       <c r="AA91" s="37"/>
-    </row>
-    <row r="92" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="41"/>
-      <c r="C92" s="42"/>
+      <c r="AB91" s="54"/>
+    </row>
+    <row r="92" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B92" s="46"/>
+      <c r="C92" s="45"/>
       <c r="F92" s="14" t="s">
         <v>206</v>
       </c>
@@ -10213,10 +10366,11 @@
         <v>4.7678726762454618E-2</v>
       </c>
       <c r="AA92" s="37"/>
-    </row>
-    <row r="93" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="41"/>
-      <c r="C93" s="42"/>
+      <c r="AB92" s="54"/>
+    </row>
+    <row r="93" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B93" s="46"/>
+      <c r="C93" s="45"/>
       <c r="F93" s="14" t="s">
         <v>207</v>
       </c>
@@ -10249,10 +10403,11 @@
         <v>2.5983329604301563E-2</v>
       </c>
       <c r="AA93" s="37"/>
-    </row>
-    <row r="94" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="41"/>
-      <c r="C94" s="42"/>
+      <c r="AB93" s="54"/>
+    </row>
+    <row r="94" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B94" s="46"/>
+      <c r="C94" s="45"/>
       <c r="F94" s="14" t="s">
         <v>208</v>
       </c>
@@ -10285,15 +10440,17 @@
         <v>4.049540093E-3</v>
       </c>
       <c r="AA94" s="37"/>
-    </row>
-    <row r="95" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="54"/>
+    </row>
+    <row r="95" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F95" s="14"/>
-    </row>
-    <row r="96" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B96" s="41" t="s">
+      <c r="AB95" s="54"/>
+    </row>
+    <row r="96" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B96" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="C96" s="42" t="s">
+      <c r="C96" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F96" s="14" t="s">
@@ -10328,10 +10485,11 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA96" s="37"/>
-    </row>
-    <row r="97" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="41"/>
-      <c r="C97" s="42"/>
+      <c r="AB96" s="54"/>
+    </row>
+    <row r="97" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B97" s="46"/>
+      <c r="C97" s="45"/>
       <c r="F97" s="14" t="s">
         <v>71</v>
       </c>
@@ -10364,10 +10522,11 @@
         <v>59.120937045501627</v>
       </c>
       <c r="AA97" s="37"/>
-    </row>
-    <row r="98" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B98" s="41"/>
-      <c r="C98" s="42"/>
+      <c r="AB97" s="54"/>
+    </row>
+    <row r="98" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B98" s="46"/>
+      <c r="C98" s="45"/>
       <c r="F98" s="14" t="s">
         <v>72</v>
       </c>
@@ -10400,10 +10559,11 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA98" s="37"/>
-    </row>
-    <row r="99" spans="2:27" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="41"/>
-      <c r="C99" s="42"/>
+      <c r="AB98" s="54"/>
+    </row>
+    <row r="99" spans="2:28" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="46"/>
+      <c r="C99" s="45"/>
       <c r="F99" s="14" t="s">
         <v>81</v>
       </c>
@@ -10436,16 +10596,18 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA99" s="37"/>
-    </row>
-    <row r="100" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="54"/>
+    </row>
+    <row r="100" spans="2:28" x14ac:dyDescent="0.2">
       <c r="E100" s="26"/>
       <c r="F100" s="14"/>
-    </row>
-    <row r="101" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B101" s="41" t="s">
+      <c r="AB100" s="54"/>
+    </row>
+    <row r="101" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B101" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="C101" s="42" t="s">
+      <c r="C101" s="45" t="s">
         <v>174</v>
       </c>
       <c r="E101" s="26"/>
@@ -10481,10 +10643,11 @@
         <v>28.429343624434111</v>
       </c>
       <c r="AA101" s="37"/>
-    </row>
-    <row r="102" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="41"/>
-      <c r="C102" s="42"/>
+      <c r="AB101" s="54"/>
+    </row>
+    <row r="102" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B102" s="46"/>
+      <c r="C102" s="45"/>
       <c r="E102" s="26"/>
       <c r="F102" s="14" t="s">
         <v>212</v>
@@ -10518,10 +10681,11 @@
         <v>14.780234261375407</v>
       </c>
       <c r="AA102" s="37"/>
-    </row>
-    <row r="103" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="41"/>
-      <c r="C103" s="42"/>
+      <c r="AB102" s="54"/>
+    </row>
+    <row r="103" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B103" s="46"/>
+      <c r="C103" s="45"/>
       <c r="E103" s="26"/>
       <c r="F103" s="14" t="s">
         <v>213</v>
@@ -10555,10 +10719,11 @@
         <v>8.7309770345259246</v>
       </c>
       <c r="AA103" s="37"/>
-    </row>
-    <row r="104" spans="2:27" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="41"/>
-      <c r="C104" s="42"/>
+      <c r="AB103" s="54"/>
+    </row>
+    <row r="104" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="B104" s="46"/>
+      <c r="C104" s="45"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
         <v>214</v>
@@ -10592,22 +10757,25 @@
         <v>1.93381883997675</v>
       </c>
       <c r="AA104" s="37"/>
-    </row>
-    <row r="105" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB104" s="54"/>
+    </row>
+    <row r="105" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B105" s="29"/>
       <c r="C105" s="35"/>
       <c r="E105" s="26"/>
       <c r="F105" s="14"/>
       <c r="AA105" s="29"/>
-    </row>
-    <row r="106" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB105" s="54"/>
+    </row>
+    <row r="106" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B106" s="29"/>
       <c r="C106" s="35"/>
       <c r="E106" s="26"/>
       <c r="F106" s="14"/>
       <c r="AA106" s="29"/>
-    </row>
-    <row r="107" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB106" s="54"/>
+    </row>
+    <row r="107" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="E107" s="26"/>
       <c r="F107" s="15" t="s">
         <v>140</v>
@@ -10616,8 +10784,9 @@
         <v>124</v>
       </c>
       <c r="H107" s="8"/>
-    </row>
-    <row r="108" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB107" s="54"/>
+    </row>
+    <row r="108" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="38" t="s">
         <v>239</v>
       </c>
@@ -10685,8 +10854,9 @@
         <v>0.92</v>
       </c>
       <c r="AA108" s="38"/>
-    </row>
-    <row r="109" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB108" s="54"/>
+    </row>
+    <row r="109" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="38" t="s">
         <v>240</v>
       </c>
@@ -10753,8 +10923,9 @@
         <v>24936000</v>
       </c>
       <c r="AA109" s="38"/>
-    </row>
-    <row r="110" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB109" s="54"/>
+    </row>
+    <row r="110" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="38" t="s">
         <v>183</v>
       </c>
@@ -10821,8 +10992,9 @@
       <c r="AA110" s="38" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="111" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB110" s="54"/>
+    </row>
+    <row r="111" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="38" t="s">
         <v>184</v>
       </c>
@@ -10889,8 +11061,9 @@
         <v>0.7963605165432065</v>
       </c>
       <c r="AA111" s="38"/>
-    </row>
-    <row r="112" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB111" s="54"/>
+    </row>
+    <row r="112" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B112" s="38" t="s">
         <v>241</v>
       </c>
@@ -10957,8 +11130,9 @@
         <v>15603395.572368858</v>
       </c>
       <c r="AA112" s="38"/>
-    </row>
-    <row r="113" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB112" s="54"/>
+    </row>
+    <row r="113" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B113" s="38" t="s">
         <v>244</v>
       </c>
@@ -11025,8 +11199,9 @@
         <v>62.573771143603061</v>
       </c>
       <c r="AA113" s="38"/>
-    </row>
-    <row r="114" spans="2:27" ht="34" x14ac:dyDescent="0.2">
+      <c r="AB113" s="54"/>
+    </row>
+    <row r="114" spans="2:28" ht="34" x14ac:dyDescent="0.2">
       <c r="B114" s="38" t="s">
         <v>282</v>
       </c>
@@ -11093,11 +11268,13 @@
         <v>24.772878143603059</v>
       </c>
       <c r="AA114" s="38"/>
-    </row>
-    <row r="115" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB114" s="54"/>
+    </row>
+    <row r="115" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F115" s="13"/>
-    </row>
-    <row r="116" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB115" s="54"/>
+    </row>
+    <row r="116" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F116" s="11" t="s">
         <v>58</v>
       </c>
@@ -11115,8 +11292,9 @@
       <c r="W116" s="12"/>
       <c r="Y116" s="12"/>
       <c r="Z116" s="12"/>
-    </row>
-    <row r="117" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB116" s="54"/>
+    </row>
+    <row r="117" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="38" t="s">
         <v>246</v>
       </c>
@@ -11183,8 +11361,9 @@
         <v>15603395.572368858</v>
       </c>
       <c r="AA117" s="38"/>
-    </row>
-    <row r="118" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB117" s="54"/>
+    </row>
+    <row r="118" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
         <v>245</v>
       </c>
@@ -11223,8 +11402,9 @@
         <v>215.49749504124878</v>
       </c>
       <c r="AA118" s="38"/>
-    </row>
-    <row r="119" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB118" s="54"/>
+    </row>
+    <row r="119" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="38" t="s">
         <v>242</v>
       </c>
@@ -11291,8 +11471,9 @@
         <v>15603611.069863901</v>
       </c>
       <c r="AA119" s="38"/>
-    </row>
-    <row r="120" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB119" s="54"/>
+    </row>
+    <row r="120" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B120" s="38" t="s">
         <v>243</v>
       </c>
@@ -11359,8 +11540,9 @@
         <v>3900902.7674659751</v>
       </c>
       <c r="AA120" s="38"/>
-    </row>
-    <row r="121" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB120" s="54"/>
+    </row>
+    <row r="121" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="38" t="s">
         <v>281</v>
       </c>
@@ -11427,8 +11609,9 @@
         <v>7258.5574526579549</v>
       </c>
       <c r="AA121" s="38"/>
-    </row>
-    <row r="122" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB121" s="54"/>
+    </row>
+    <row r="122" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B122" s="38" t="s">
         <v>265</v>
       </c>
@@ -11495,8 +11678,9 @@
         <v>1044</v>
       </c>
       <c r="AA122" s="38"/>
-    </row>
-    <row r="123" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB122" s="54"/>
+    </row>
+    <row r="123" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B123" s="38" t="s">
         <v>283</v>
       </c>
@@ -11563,8 +11747,9 @@
         <v>4350.1902168605684</v>
       </c>
       <c r="AA123" s="38"/>
-    </row>
-    <row r="124" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB123" s="54"/>
+    </row>
+    <row r="124" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="38" t="s">
         <v>258</v>
       </c>
@@ -11603,8 +11788,9 @@
         <v>10471.887293585241</v>
       </c>
       <c r="AA124" s="38"/>
-    </row>
-    <row r="125" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB124" s="54"/>
+    </row>
+    <row r="125" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="38" t="s">
         <v>259</v>
       </c>
@@ -11671,8 +11857,9 @@
         <v>0.41541606540450088</v>
       </c>
       <c r="AA125" s="38"/>
-    </row>
-    <row r="126" spans="2:27" ht="34" x14ac:dyDescent="0.2">
+      <c r="AB125" s="54"/>
+    </row>
+    <row r="126" spans="2:28" ht="34" x14ac:dyDescent="0.2">
       <c r="B126" s="38" t="s">
         <v>185</v>
       </c>
@@ -11739,8 +11926,12 @@
         <v>4948233.7719158493</v>
       </c>
       <c r="AA126" s="38"/>
-    </row>
-    <row r="128" spans="2:27" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB126" s="54"/>
+    </row>
+    <row r="127" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB127" s="54"/>
+    </row>
+    <row r="128" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F128" s="15" t="s">
         <v>73</v>
       </c>
@@ -11758,6 +11949,7 @@
       <c r="W128" s="8"/>
       <c r="Y128" s="8"/>
       <c r="Z128" s="8"/>
+      <c r="AB128" s="54"/>
     </row>
     <row r="129" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="38" t="s">
@@ -11798,6 +11990,7 @@
         <v>2509528.1127064149</v>
       </c>
       <c r="AA129" s="38"/>
+      <c r="AB129" s="54"/>
     </row>
     <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="38" t="s">
@@ -11838,6 +12031,7 @@
         <v>236958.69160889552</v>
       </c>
       <c r="AA130" s="38"/>
+      <c r="AB130" s="54"/>
     </row>
     <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="38" t="s">
@@ -11878,6 +12072,7 @@
         <v>2272569.4210975193</v>
       </c>
       <c r="AA131" s="38"/>
+      <c r="AB131" s="54"/>
     </row>
     <row r="132" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B132" s="38" t="s">
@@ -11918,6 +12113,7 @@
         <v>0</v>
       </c>
       <c r="AA132" s="38"/>
+      <c r="AB132" s="54"/>
     </row>
     <row r="133" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="38" t="s">
@@ -11986,6 +12182,7 @@
         <v>209877.50332872596</v>
       </c>
       <c r="AA133" s="38"/>
+      <c r="AB133" s="54"/>
     </row>
     <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B134" s="38" t="s">
@@ -12054,6 +12251,7 @@
         <v>209877.50332872596</v>
       </c>
       <c r="AA134" s="38"/>
+      <c r="AB134" s="54"/>
     </row>
     <row r="135" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F135" s="15" t="s">
@@ -12073,6 +12271,7 @@
       <c r="W135" s="8"/>
       <c r="Y135" s="8"/>
       <c r="Z135" s="8"/>
+      <c r="AB135" s="54"/>
     </row>
     <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B136" s="38" t="s">
@@ -12141,7 +12340,7 @@
         <v>0.39828350178087057</v>
       </c>
       <c r="AA136" s="38"/>
-      <c r="AB136">
+      <c r="AB136" s="54">
         <v>0.5</v>
       </c>
       <c r="AC136">
@@ -12222,7 +12421,7 @@
         <v>4.2414629745244618E-2</v>
       </c>
       <c r="AA137" s="38"/>
-      <c r="AB137">
+      <c r="AB137" s="54">
         <v>0.3</v>
       </c>
       <c r="AC137">
@@ -12236,7 +12435,7 @@
     <row r="138" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B138" s="38"/>
       <c r="AA138" s="38"/>
-      <c r="AB138">
+      <c r="AB138" s="54">
         <v>0.2</v>
       </c>
       <c r="AC138">
@@ -12314,7 +12513,7 @@
         <v>209877.50332872596</v>
       </c>
       <c r="AA139" s="38"/>
-      <c r="AB139">
+      <c r="AB139" s="54">
         <v>0.125</v>
       </c>
       <c r="AC139">
@@ -12392,6 +12591,7 @@
         <v>236958.69160889552</v>
       </c>
       <c r="AA140" s="38"/>
+      <c r="AB140" s="54"/>
     </row>
     <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B141" s="38" t="s">
@@ -12460,6 +12660,10 @@
         <v>0.88571346298253728</v>
       </c>
       <c r="AA141" s="38"/>
+      <c r="AB141" s="54"/>
+    </row>
+    <row r="142" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB142" s="54"/>
     </row>
     <row r="143" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F143" s="15" t="s">
@@ -12479,6 +12683,7 @@
       <c r="W143" s="8"/>
       <c r="Y143" s="8"/>
       <c r="Z143" s="8"/>
+      <c r="AB143" s="54"/>
     </row>
     <row r="144" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="38" t="s">
@@ -12547,6 +12752,7 @@
         <v>24156.603765901902</v>
       </c>
       <c r="AA144" s="38"/>
+      <c r="AB144" s="54"/>
     </row>
     <row r="145" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B145" s="38" t="s">
@@ -12612,6 +12818,7 @@
         <v>6039.1509414754755</v>
       </c>
       <c r="AA145" s="38"/>
+      <c r="AB145" s="54"/>
     </row>
     <row r="146" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B146" s="38" t="s">
@@ -12680,6 +12887,7 @@
         <v>52469.375832181489</v>
       </c>
       <c r="AA146" s="38"/>
+      <c r="AB146" s="54"/>
     </row>
     <row r="147" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B147" s="38" t="s">
@@ -12748,6 +12956,7 @@
         <v>1864.3672357973865</v>
       </c>
       <c r="AA147" s="38"/>
+      <c r="AB147" s="54"/>
     </row>
     <row r="148" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B148" s="38" t="s">
@@ -12816,6 +13025,7 @@
         <v>1353.1913631644886</v>
       </c>
       <c r="AA148" s="38"/>
+      <c r="AB148" s="54"/>
     </row>
     <row r="149" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
@@ -12872,15 +13082,22 @@
         <f>(Z111*Z7+SUMPRODUCT(W38:W41,W86:W89))*(1+$H21)</f>
         <v>248300.31050651748</v>
       </c>
-      <c r="Y149" s="4">
+      <c r="Y149" s="4" t="e">
         <f>AB111*AB7*(1+$G21)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z149" s="4">
         <f>(AC111*AC7+SUMPRODUCT(Z38:Z41,Z86:Z89))*(1+$H21)</f>
         <v>129.19999999999999</v>
       </c>
       <c r="AA149" s="38"/>
+      <c r="AB149" s="54"/>
+    </row>
+    <row r="150" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AB150" s="54"/>
+    </row>
+    <row r="151" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AB151" s="54"/>
     </row>
     <row r="152" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B152" s="24" t="s">
@@ -12942,6 +13159,10 @@
         <f>Z147+Z122</f>
         <v>2908.3672357973865</v>
       </c>
+      <c r="AB152" s="54"/>
+    </row>
+    <row r="153" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AB153" s="54"/>
     </row>
     <row r="154" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B154" s="38" t="s">
@@ -12979,6 +13200,7 @@
         <v>247430.57890248077</v>
       </c>
       <c r="AA154" s="38"/>
+      <c r="AB154" s="54"/>
     </row>
     <row r="155" spans="2:30" x14ac:dyDescent="0.2">
       <c r="G155" s="4">
@@ -13011,7 +13233,7 @@
       </c>
     </row>
     <row r="160" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB160">
+      <c r="AB160" s="53">
         <v>0.1225</v>
       </c>
       <c r="AC160">
@@ -13023,7 +13245,7 @@
       </c>
     </row>
     <row r="161" spans="28:30" x14ac:dyDescent="0.2">
-      <c r="AB161">
+      <c r="AB161" s="53">
         <v>0.12239999999999999</v>
       </c>
       <c r="AC161">
@@ -13035,7 +13257,7 @@
       </c>
     </row>
     <row r="162" spans="28:30" x14ac:dyDescent="0.2">
-      <c r="AB162">
+      <c r="AB162" s="53">
         <v>0.12230000000000001</v>
       </c>
       <c r="AC162">
@@ -13048,30 +13270,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="E75:E78"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="AE4:AG4"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="C56:C59"/>
     <mergeCell ref="B101:B104"/>
     <mergeCell ref="C101:C104"/>
     <mergeCell ref="B49:B52"/>
@@ -13087,6 +13285,30 @@
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="C73:C76"/>
     <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="C56:C59"/>
+    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="E75:E78"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143413A2-A337-814F-8CE2-89532D7AB636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADD75E4-B89C-564A-AF5D-2C1999A2946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3240" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="-320" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="358">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -583,11 +583,6 @@
     <t>T = number of time periods</t>
   </si>
   <si>
-    <t>arr_young_area_by_tp_planted (T x T)   [e.g., col J]
-arr_young_area_by_tp_planted_cumvals (T x T)   [e.g., col H]
-arr_young_area_by_tp_planted_drops (T x T)   [e.g., col I]</t>
-  </si>
-  <si>
     <t>arr_young_sf_adjusted_by_tp_planted (T x T)   [e.g., col J]
 arr_young_sf_adjustment_factor (T x T)   [e.g., col I]</t>
   </si>
@@ -899,9 +894,6 @@
     <t>arr_total_biomass_c_ag_available_from_conversion</t>
   </si>
   <si>
-    <t>latex variable</t>
-  </si>
-  <si>
     <t>A(t)</t>
   </si>
   <si>
@@ -1022,37 +1014,109 @@
     <t>A^{(*protected)}(t)</t>
   </si>
   <si>
-    <t>latex description</t>
-  </si>
-  <si>
-    <t>Area of land use at beginning of time $t$</t>
-  </si>
-  <si>
-    <t>Total of land converted away from type during time $t$</t>
-  </si>
-  <si>
-    <t>Area remaining from land use type at beginning of simulation at beginning of time $t$</t>
-  </si>
-  <si>
-    <t>Area of young forest converted away</t>
-  </si>
-  <si>
-    <t>Area of young forest that would be converted away assuming no protection (counterfactual)</t>
-  </si>
-  <si>
-    <t>Area of conversion into new forest land (planted or restored)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Fraction of biomass in each forest type that's converted to another land use class that is available for use to satisfy fuelwood and harvested wood product demands</t>
-  </si>
-  <si>
     <t>Average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
   </si>
   <si>
     <t>Average above ground stock contained In land use classes that forests transition into; used to estimate above-ground conversion losses of stock.</t>
+  </si>
+  <si>
+    <t>Fraction of biomass that represents dead storage. Is set in SISEPUEDE to be max of exogenous specification and amount implied by average stock in conversion targets (cannot have biomass below transition targets and remain forest).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraction of biomass in buffer zone; dead storage + buffer gives the fractional threshold for slowing removals. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fractional threshold for stock loss (compared to undisturbed forest levels) below which sequestration declines. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial steady-state storage in each class. Used in integration targets for NPP curve and as initial carbon storage condition. </t>
+  </si>
+  <si>
+    <t>Ratio of below-ground carbon stock to above-ground carbon stock in each forest type.</t>
+  </si>
+  <si>
+    <t>Area remaining from land use type at beginning of simulation at beginning of time $t$.</t>
+  </si>
+  <si>
+    <t>Area of land use at beginning of time $t$.</t>
+  </si>
+  <si>
+    <t>Total of land converted away from type during time $t$.</t>
+  </si>
+  <si>
+    <t>Area of young forest that would be converted away assuming no protection (counterfactual).</t>
+  </si>
+  <si>
+    <t>Area of young forest converted away.</t>
+  </si>
+  <si>
+    <t>Area of conversion into new forest land (planted or restored).</t>
+  </si>
+  <si>
+    <t>Fraction of biomass in each forest type that's converted to another land use class that is available for use to satisfy fuelwood and harvested wood product demands.</t>
+  </si>
+  <si>
+    <t>\overline{B}_0\check{\alpha}(t)</t>
+  </si>
+  <si>
+    <t>In healthy forest, available stock factor per unit area. Used to determine when average stocks fall below thresholds.</t>
+  </si>
+  <si>
+    <t>Total area of forest protected.</t>
+  </si>
+  <si>
+    <t>Area of young (newly planted) forest that is protected.</t>
+  </si>
+  <si>
+    <t>Area of remaining (from simulation initialization) forest that is protected.</t>
+  </si>
+  <si>
+    <t>Nominal sequestration factor (mass of biomass growth per time period) associated with forests. Used in NPP fit from integration target.</t>
+  </si>
+  <si>
+    <t>Fraction of biomass per time period lost to decomposition. This is estimated from the NPP fit funtion under the assumption that primary forests exist in steady state (i.e., that there is no net growth of biomass if left undistributed).</t>
+  </si>
+  <si>
+    <t>Total biomass (mass units) removals needed to satisfy fuelwood and harvested wood products demands.</t>
+  </si>
+  <si>
+    <t>Latex Variable</t>
+  </si>
+  <si>
+    <t>Variable Description</t>
+  </si>
+  <si>
+    <t>arr_young_area_by_tp_planted (T x T)   [e.g., col K]</t>
+  </si>
+  <si>
+    <t>arr_young_area_by_tp_planted_cumvals (T x T)   [e.g., col I]</t>
+  </si>
+  <si>
+    <t>arr_young_area_by_tp_planted_drops (T x T)   [e.g., col J]</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing how much area of young forest planted in time $t$ remains in time $u$</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing how much forest area in each time period (column $u$) has to be dropped due to conversion into young forests. Only applicable if all other secondary forest has been elimnated.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing cumulative area in young forests at time $t$. Used to determine how much area is removed from each young forest area if conversion is applicable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector ($T$) storing total mass of above-ground biomass in young forests converted in time $t$. </t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing total mass of biomass in young forests converted away in each time period by time period planted. Used to help ensure that earliest plantations are converted first.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing total above-ground mass of biomass preserved in each area of young forest planted by time period planted $u$.</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing total above-ground mass of biomass preserved in each time period.</t>
   </si>
 </sst>
 </file>
@@ -6697,7 +6761,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -6741,13 +6805,13 @@
       </c>
       <c r="Z5" s="42"/>
       <c r="AA5" s="24" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="AB5" s="56" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="AD5" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE5" s="21" t="s">
         <v>33</v>
@@ -6904,10 +6968,10 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AB7" s="54" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -6999,10 +7063,10 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AB8" s="54" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7029,7 +7093,7 @@
     </row>
     <row r="9" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>162</v>
@@ -7080,10 +7144,10 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AB9" s="54" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7110,7 +7174,7 @@
     </row>
     <row r="10" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="B10" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>174</v>
@@ -7147,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AB10" s="54" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7165,7 +7229,7 @@
     </row>
     <row r="11" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>174</v>
@@ -7202,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AB11" s="54" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7220,7 +7284,7 @@
     </row>
     <row r="12" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>162</v>
@@ -7250,10 +7314,10 @@
         <v>110</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AB12" s="54" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7333,10 +7397,10 @@
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AB13" s="54" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7344,7 +7408,7 @@
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>162</v>
@@ -7374,10 +7438,10 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AB14" s="54" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7392,16 +7456,16 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -7446,10 +7510,10 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AB15" s="54" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7457,7 +7521,7 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="38" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C16" s="31"/>
       <c r="G16" s="4">
@@ -7517,10 +7581,10 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AB16" s="54" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -7528,13 +7592,13 @@
     </row>
     <row r="17" spans="2:33" ht="51" x14ac:dyDescent="0.2">
       <c r="B17" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G17" s="4">
         <v>0.33057704999999998</v>
@@ -7543,9 +7607,11 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB17" s="54"/>
+        <v>289</v>
+      </c>
+      <c r="AB17" s="54" t="s">
+        <v>326</v>
+      </c>
       <c r="AE17" s="19">
         <v>1.8</v>
       </c>
@@ -7559,7 +7625,7 @@
     </row>
     <row r="18" spans="2:33" ht="34" x14ac:dyDescent="0.2">
       <c r="B18" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
@@ -7577,9 +7643,11 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB18" s="54"/>
+        <v>290</v>
+      </c>
+      <c r="AB18" s="54" t="s">
+        <v>327</v>
+      </c>
       <c r="AE18" s="19">
         <v>3</v>
       </c>
@@ -7593,7 +7661,7 @@
     </row>
     <row r="19" spans="2:33" ht="51" x14ac:dyDescent="0.2">
       <c r="B19" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>162</v>
@@ -7606,9 +7674,11 @@
         <v>0.67</v>
       </c>
       <c r="AA19" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="AB19" s="54"/>
+        <v>291</v>
+      </c>
+      <c r="AB19" s="54" t="s">
+        <v>328</v>
+      </c>
       <c r="AE19" s="19">
         <v>6</v>
       </c>
@@ -7622,7 +7692,7 @@
     </row>
     <row r="20" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>162</v>
@@ -7637,9 +7707,11 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="AB20" s="54"/>
+        <v>302</v>
+      </c>
+      <c r="AB20" s="54" t="s">
+        <v>329</v>
+      </c>
       <c r="AE20" s="19">
         <v>10</v>
       </c>
@@ -7653,7 +7725,7 @@
     </row>
     <row r="21" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>162</v>
@@ -7668,16 +7740,18 @@
         <v>0.25</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB21" s="54"/>
+        <v>292</v>
+      </c>
+      <c r="AB21" s="54" t="s">
+        <v>330</v>
+      </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
       <c r="AG21" s="19"/>
     </row>
     <row r="22" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B22" s="38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>174</v>
@@ -7693,7 +7767,9 @@
         <f>H$20*$H$17</f>
         <v>37.800893000000002</v>
       </c>
-      <c r="AA22" s="38"/>
+      <c r="AA22" s="38" t="s">
+        <v>338</v>
+      </c>
       <c r="AB22" s="54"/>
       <c r="AE22" s="19">
         <v>12</v>
@@ -7708,7 +7784,7 @@
     </row>
     <row r="23" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>174</v>
@@ -7725,9 +7801,11 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>295</v>
-      </c>
-      <c r="AB23" s="54"/>
+        <v>293</v>
+      </c>
+      <c r="AB23" s="54" t="s">
+        <v>339</v>
+      </c>
       <c r="AE23" s="19">
         <v>13.5</v>
       </c>
@@ -7805,9 +7883,11 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="AB25" s="54"/>
+        <v>320</v>
+      </c>
+      <c r="AB25" s="54" t="s">
+        <v>340</v>
+      </c>
       <c r="AE25" s="19">
         <v>10</v>
       </c>
@@ -7821,7 +7901,7 @@
     </row>
     <row r="26" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>163</v>
@@ -7858,9 +7938,11 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="AB26" s="54"/>
+        <v>321</v>
+      </c>
+      <c r="AB26" s="54" t="s">
+        <v>341</v>
+      </c>
       <c r="AE26" s="19">
         <v>6</v>
       </c>
@@ -7939,9 +8021,11 @@
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="AB27" s="54"/>
+        <v>322</v>
+      </c>
+      <c r="AB27" s="54" t="s">
+        <v>342</v>
+      </c>
       <c r="AE27" s="19">
         <v>3</v>
       </c>
@@ -7985,7 +8069,7 @@
     </row>
     <row r="29" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="38" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>162</v>
@@ -8003,13 +8087,15 @@
         <v>0.92</v>
       </c>
       <c r="AA29" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="AB29" s="54"/>
+        <v>303</v>
+      </c>
+      <c r="AB29" s="54" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="30" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>174</v>
@@ -8031,13 +8117,15 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB30" s="54"/>
+        <v>304</v>
+      </c>
+      <c r="AB30" s="54" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="31" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="26"/>
-      <c r="AB31" s="54"/>
+      <c r="AB31" s="55"/>
     </row>
     <row r="32" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="F32" s="15" t="s">
@@ -8057,9 +8145,9 @@
       <c r="W32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
-      <c r="AB32" s="54"/>
-    </row>
-    <row r="33" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB32" s="55"/>
+    </row>
+    <row r="33" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="38" t="s">
         <v>168</v>
       </c>
@@ -8091,14 +8179,16 @@
         <v>2520000</v>
       </c>
       <c r="AA33" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="AB33" s="54"/>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="AB34" s="54"/>
-    </row>
-    <row r="35" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+      <c r="AB33" s="54" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AB34" s="55"/>
+    </row>
+    <row r="35" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
         <v>57</v>
       </c>
@@ -8116,9 +8206,9 @@
       <c r="W35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
-      <c r="AB35" s="54"/>
-    </row>
-    <row r="36" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB35" s="55"/>
+    </row>
+    <row r="36" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F36" s="15" t="s">
         <v>139</v>
       </c>
@@ -8138,9 +8228,12 @@
       <c r="P36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB36" s="54"/>
-    </row>
-    <row r="37" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB36" s="55"/>
+      <c r="AD36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B37" s="24" t="s">
         <v>179</v>
       </c>
@@ -8192,11 +8285,11 @@
       <c r="Z37" s="4">
         <v>0</v>
       </c>
-      <c r="AB37" s="54"/>
-    </row>
-    <row r="38" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B38" s="46" t="s">
-        <v>180</v>
+      <c r="AB37" s="55"/>
+    </row>
+    <row r="38" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="B38" s="37" t="s">
+        <v>348</v>
       </c>
       <c r="C38" s="45" t="s">
         <v>174</v>
@@ -8283,11 +8376,17 @@
         <f>W38-Y38</f>
         <v>85</v>
       </c>
-      <c r="AA38" s="37"/>
-      <c r="AB38" s="54"/>
-    </row>
-    <row r="39" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B39" s="47"/>
+      <c r="AA38" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB38" s="54" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="B39" s="38" t="s">
+        <v>349</v>
+      </c>
       <c r="C39" s="45"/>
       <c r="F39" s="14" t="s">
         <v>69</v>
@@ -8371,12 +8470,16 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB39" s="54"/>
-    </row>
-    <row r="40" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B40" s="47"/>
+        <v>318</v>
+      </c>
+      <c r="AB39" s="54" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="40" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="B40" s="38" t="s">
+        <v>350</v>
+      </c>
       <c r="C40" s="45"/>
       <c r="F40" s="14" t="s">
         <v>79</v>
@@ -8459,12 +8562,14 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB40" s="54"/>
-    </row>
-    <row r="41" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="47"/>
+        <v>319</v>
+      </c>
+      <c r="AB40" s="54" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="41" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="B41" s="38"/>
       <c r="C41" s="45"/>
       <c r="F41" s="14" t="s">
         <v>80</v>
@@ -8545,28 +8650,24 @@
         <f>W41-Y41</f>
         <v>43</v>
       </c>
-      <c r="AA41" s="38" t="s">
-        <v>321</v>
-      </c>
+      <c r="AA41" s="38"/>
       <c r="AB41" s="54"/>
     </row>
-    <row r="42" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB42" s="54" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB42" s="55"/>
+    </row>
+    <row r="43" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B43" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C43" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H43" s="4">
         <v>0</v>
@@ -8595,14 +8696,18 @@
         <f>IF(W38=0, 0, W96*Y38/W38)</f>
         <v>0</v>
       </c>
-      <c r="AA43" s="38"/>
-      <c r="AB43" s="54"/>
-    </row>
-    <row r="44" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AA43" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="AB43" s="54" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="47"/>
       <c r="C44" s="45"/>
       <c r="F44" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H44" s="4">
         <v>0</v>
@@ -8631,16 +8736,14 @@
         <f>IF(W39=0, 0, W97*Y39/W39)</f>
         <v>0</v>
       </c>
-      <c r="AA44" s="38" t="s">
-        <v>310</v>
-      </c>
+      <c r="AA44" s="38"/>
       <c r="AB44" s="54"/>
     </row>
-    <row r="45" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B45" s="47"/>
       <c r="C45" s="45"/>
       <c r="F45" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -8672,11 +8775,11 @@
       <c r="AA45" s="38"/>
       <c r="AB45" s="54"/>
     </row>
-    <row r="46" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B46" s="47"/>
       <c r="C46" s="45"/>
       <c r="F46" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H46" s="4">
         <v>0</v>
@@ -8708,9 +8811,9 @@
       <c r="AA46" s="38"/>
       <c r="AB46" s="54"/>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B47" s="38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C47" s="28" t="s">
         <v>174</v>
@@ -8745,30 +8848,30 @@
         <v>0</v>
       </c>
       <c r="AA47" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB47" s="54"/>
-    </row>
-    <row r="48" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+      <c r="AB47" s="54" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F48" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB48" s="54" t="s">
-        <v>77</v>
-      </c>
+      <c r="AB48" s="55"/>
     </row>
     <row r="49" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B49" s="47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C49" s="45" t="s">
         <v>174</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H49" s="4">
         <f>MIN(H43,H$15*G38)</f>
@@ -8799,16 +8902,18 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="AB49" s="54"/>
+        <v>310</v>
+      </c>
+      <c r="AB49" s="54" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="50" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B50" s="47"/>
       <c r="C50" s="45"/>
       <c r="E50" s="41"/>
       <c r="F50" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H50" s="4">
         <f>MIN(H44,H$15*G39)</f>
@@ -8846,7 +8951,7 @@
       <c r="C51" s="45"/>
       <c r="E51" s="41"/>
       <c r="F51" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H51" s="4">
         <f>MIN(H45,H$15*G40)</f>
@@ -8884,7 +8989,7 @@
       <c r="C52" s="45"/>
       <c r="E52" s="41"/>
       <c r="F52" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H52" s="4">
         <f>MIN(H46,H$15*G41)</f>
@@ -8919,7 +9024,7 @@
     </row>
     <row r="53" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B53" s="38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C53" s="28" t="s">
         <v>174</v>
@@ -8954,13 +9059,15 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="AB53" s="54"/>
+        <v>311</v>
+      </c>
+      <c r="AB53" s="54" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="54" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B54" s="38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C54" s="28"/>
       <c r="F54" s="14"/>
@@ -8993,7 +9100,7 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AB54" s="54"/>
     </row>
@@ -9003,13 +9110,13 @@
     </row>
     <row r="56" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C56" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H56" s="4">
         <f>H43*$H$21</f>
@@ -9040,7 +9147,7 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AB56" s="54"/>
     </row>
@@ -9048,7 +9155,7 @@
       <c r="B57" s="47"/>
       <c r="C57" s="45"/>
       <c r="F57" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H57" s="4">
         <f>H44*$H$21</f>
@@ -9085,7 +9192,7 @@
       <c r="B58" s="47"/>
       <c r="C58" s="45"/>
       <c r="F58" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H58" s="4">
         <f>H45*$H$21</f>
@@ -9122,7 +9229,7 @@
       <c r="B59" s="47"/>
       <c r="C59" s="45"/>
       <c r="F59" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H59" s="4">
         <f>H46*$H$21</f>
@@ -9157,7 +9264,7 @@
     </row>
     <row r="60" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B60" s="38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C60" s="28" t="s">
         <v>174</v>
@@ -9192,7 +9299,7 @@
         <v>0</v>
       </c>
       <c r="AA60" s="38" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AB60" s="54"/>
     </row>
@@ -9239,7 +9346,7 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AB62" s="54"/>
     </row>
@@ -9357,7 +9464,7 @@
     </row>
     <row r="68" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B68" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C68" s="45" t="s">
         <v>174</v>
@@ -9394,7 +9501,7 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AB68" s="54"/>
     </row>
@@ -9498,7 +9605,7 @@
     </row>
     <row r="73" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B73" s="47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C73" s="45" t="s">
         <v>174</v>
@@ -9650,7 +9757,7 @@
     </row>
     <row r="77" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B77" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C77" s="28" t="s">
         <v>174</v>
@@ -9705,7 +9812,7 @@
     </row>
     <row r="79" spans="2:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="48" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C79" s="45" t="s">
         <v>174</v>
@@ -10040,7 +10147,7 @@
     </row>
     <row r="86" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B86" s="46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C86" s="45" t="s">
         <v>174</v>
@@ -10292,13 +10399,13 @@
     </row>
     <row r="91" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B91" s="46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C91" s="45" t="s">
         <v>174</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H91" s="4">
         <f>H57*H33</f>
@@ -10335,7 +10442,7 @@
       <c r="B92" s="46"/>
       <c r="C92" s="45"/>
       <c r="F92" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H92" s="4">
         <f>H58*H34</f>
@@ -10372,7 +10479,7 @@
       <c r="B93" s="46"/>
       <c r="C93" s="45"/>
       <c r="F93" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H93" s="4">
         <f>H59*H35</f>
@@ -10409,7 +10516,7 @@
       <c r="B94" s="46"/>
       <c r="C94" s="45"/>
       <c r="F94" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H94" s="4">
         <f>H60*H36</f>
@@ -10448,7 +10555,7 @@
     </row>
     <row r="96" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B96" s="46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C96" s="45" t="s">
         <v>174</v>
@@ -10605,14 +10712,14 @@
     </row>
     <row r="101" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B101" s="46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C101" s="45" t="s">
         <v>174</v>
       </c>
       <c r="E101" s="26"/>
       <c r="F101" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H101" s="4">
         <f>H96*$H$21</f>
@@ -10650,7 +10757,7 @@
       <c r="C102" s="45"/>
       <c r="E102" s="26"/>
       <c r="F102" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H102" s="4">
         <f t="shared" ref="H102:H104" si="9">H97*$H$21</f>
@@ -10688,7 +10795,7 @@
       <c r="C103" s="45"/>
       <c r="E103" s="26"/>
       <c r="F103" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H103" s="4">
         <f>H98*$H$21</f>
@@ -10726,7 +10833,7 @@
       <c r="C104" s="45"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H104" s="4">
         <f t="shared" si="9"/>
@@ -10788,10 +10895,10 @@
     </row>
     <row r="108" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E108" s="26"/>
       <c r="F108" s="14" t="s">
@@ -10858,7 +10965,7 @@
     </row>
     <row r="109" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C109" s="28" t="s">
         <v>174</v>
@@ -10927,7 +11034,7 @@
     </row>
     <row r="110" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C110" s="28" t="s">
         <v>174</v>
@@ -10990,13 +11097,13 @@
         <v>0.86560925711218095</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AB110" s="54"/>
     </row>
     <row r="111" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C111" s="33" t="s">
         <v>163</v>
@@ -11065,7 +11172,7 @@
     </row>
     <row r="112" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B112" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>163</v>
@@ -11134,7 +11241,7 @@
     </row>
     <row r="113" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B113" s="38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>163</v>
@@ -11203,7 +11310,7 @@
     </row>
     <row r="114" spans="2:28" ht="34" x14ac:dyDescent="0.2">
       <c r="B114" s="38" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C114" s="28" t="s">
         <v>174</v>
@@ -11296,13 +11403,13 @@
     </row>
     <row r="117" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G117" s="4">
         <f>G113*G7</f>
@@ -11365,13 +11472,13 @@
     </row>
     <row r="118" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C118" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H118" s="4">
         <f>SUM(H96:H99)</f>
@@ -11406,13 +11513,13 @@
     </row>
     <row r="119" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C119" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G119" s="4">
         <f>G117+G118</f>
@@ -11475,13 +11582,13 @@
     </row>
     <row r="120" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B120" s="38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C120" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G120" s="4">
         <f>G119*$G$21</f>
@@ -11544,13 +11651,13 @@
     </row>
     <row r="121" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C121" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G121" s="4">
         <f>G9*G113</f>
@@ -11613,13 +11720,13 @@
     </row>
     <row r="122" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B122" s="38" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C122" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G122" s="4">
         <f>MIN(G121,G9*G15)</f>
@@ -11682,13 +11789,13 @@
     </row>
     <row r="123" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B123" s="38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C123" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G123" s="4">
         <f>(G121-G122)*$G$14</f>
@@ -11751,13 +11858,13 @@
     </row>
     <row r="124" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C124" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G124" s="4">
         <f>MIN(G123+H123, G33)</f>
@@ -11792,13 +11899,13 @@
     </row>
     <row r="125" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C125" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G125" s="4">
         <f>G123/(G123+H123)</f>
@@ -11861,7 +11968,7 @@
     </row>
     <row r="126" spans="2:28" ht="34" x14ac:dyDescent="0.2">
       <c r="B126" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C126" s="28" t="s">
         <v>174</v>
@@ -11953,13 +12060,13 @@
     </row>
     <row r="129" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C129" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G129" s="4">
         <f>MAX(G33-G124,0)</f>
@@ -11994,7 +12101,7 @@
     </row>
     <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C130" s="28" t="s">
         <v>174</v>
@@ -12035,7 +12142,7 @@
     </row>
     <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="38" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C131" s="28" t="s">
         <v>174</v>
@@ -12076,7 +12183,7 @@
     </row>
     <row r="132" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B132" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C132" s="28" t="s">
         <v>174</v>
@@ -12117,7 +12224,7 @@
     </row>
     <row r="133" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>174</v>
@@ -12186,7 +12293,7 @@
     </row>
     <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B134" s="38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C134" s="33" t="s">
         <v>163</v>
@@ -12275,7 +12382,7 @@
     </row>
     <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B136" s="38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C136" s="28" t="s">
         <v>174</v>
@@ -12353,16 +12460,16 @@
     </row>
     <row r="137" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B137" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C137" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G137" s="4">
         <f>MAX(MIN((G136-$G$17)/$G$18, 1), 0)</f>
@@ -12448,7 +12555,7 @@
     </row>
     <row r="139" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B139" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C139" s="28" t="s">
         <v>174</v>
@@ -12526,7 +12633,7 @@
     </row>
     <row r="140" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B140" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C140" s="28" t="s">
         <v>174</v>
@@ -12595,7 +12702,7 @@
     </row>
     <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B141" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C141" s="28" t="s">
         <v>174</v>
@@ -12667,7 +12774,7 @@
     </row>
     <row r="143" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F143" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -12687,13 +12794,13 @@
     </row>
     <row r="144" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="38" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C144" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G144" s="4">
         <f>(G112 - G133 - G121)*$G$30</f>
@@ -12756,7 +12863,7 @@
     </row>
     <row r="145" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B145" s="38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>163</v>
@@ -12822,13 +12929,13 @@
     </row>
     <row r="146" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B146" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F146" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G146" s="4">
         <f>G133*$G21</f>
@@ -13029,7 +13136,7 @@
     </row>
     <row r="149" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>163</v>
@@ -13101,7 +13208,7 @@
     </row>
     <row r="152" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B152" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G152" s="4">
         <f>G147+G122</f>
@@ -13166,7 +13273,7 @@
     </row>
     <row r="154" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B154" s="38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C154" s="33" t="s">
         <v>163</v>
@@ -13269,7 +13376,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="38">
     <mergeCell ref="B101:B104"/>
     <mergeCell ref="C101:C104"/>
     <mergeCell ref="B49:B52"/>
@@ -13286,7 +13393,6 @@
     <mergeCell ref="C73:C76"/>
     <mergeCell ref="B86:B89"/>
     <mergeCell ref="C38:C41"/>
-    <mergeCell ref="B38:B41"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="B68:B71"/>
     <mergeCell ref="C68:C71"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADD75E4-B89C-564A-AF5D-2C1999A2946F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3412FEB-9A56-694D-B6C0-0872A89E70D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-320" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="2060" yWindow="500" windowWidth="34560" windowHeight="19560" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="432">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -583,10 +583,6 @@
     <t>T = number of time periods</t>
   </si>
   <si>
-    <t>arr_young_sf_adjusted_by_tp_planted (T x T)   [e.g., col J]
-arr_young_sf_adjustment_factor (T x T)   [e.g., col I]</t>
-  </si>
-  <si>
     <t>(ref to above)</t>
   </si>
   <si>
@@ -752,10 +748,6 @@
     <t>vec_young_biomass_c_available_for_removals_total</t>
   </si>
   <si>
-    <t>arr_young_biomass_c_stock_removal_allocation (T x T)   [e.g., col G]
-arr_young_biomass_c_stock_removal_allocation_aux (T x T)   [e.g., col F]</t>
-  </si>
-  <si>
     <t>arr_young_biomass_c_ag_stock_if_untouched (T x T)</t>
   </si>
   <si>
@@ -909,9 +901,6 @@
     <t>a^{(y)}_{out}(t)</t>
   </si>
   <si>
-    <t>\chi_(t)</t>
-  </si>
-  <si>
     <t>\check{\alpha}(t)</t>
   </si>
   <si>
@@ -927,9 +916,6 @@
     <t>k_{heav}</t>
   </si>
   <si>
-    <t>rrr</t>
-  </si>
-  <si>
     <t>arr_biomass_c_average_bg_stock_in_conversion_targets</t>
   </si>
   <si>
@@ -945,18 +931,9 @@
     <t>this has been modified to use a logistic ramp rather than alinear</t>
   </si>
   <si>
-    <t>\overline{B}_{targ}(t)</t>
-  </si>
-  <si>
-    <t>\underline{B}_{targ}(t)</t>
-  </si>
-  <si>
     <t>\overline{B}_0</t>
   </si>
   <si>
-    <t>\Delta B_0</t>
-  </si>
-  <si>
     <t>\delta(t)</t>
   </si>
   <si>
@@ -975,54 +952,24 @@
     <t>\overline{y}_{conv}(t)</t>
   </si>
   <si>
-    <t>\overline{Y}_{preserved\_in\_conv}(t, u)</t>
-  </si>
-  <si>
-    <t>\overline{y}_{preserved\_in\_conv}(t)</t>
-  </si>
-  <si>
-    <t>\overline{y}_{availble\_from\_conv}(t)</t>
-  </si>
-  <si>
     <t>\underline{Y}_{conv}(t, u)</t>
   </si>
   <si>
     <t>\underline{y}_{conv}(t)</t>
   </si>
   <si>
-    <t>Q_0(t, u)</t>
-  </si>
-  <si>
     <t>\overline{Y}^*(t, u)</t>
   </si>
   <si>
-    <t>A^{young}(t, u)</t>
-  </si>
-  <si>
-    <t>\hat{A}^{young}(t, u)</t>
-  </si>
-  <si>
-    <t>L^{young}(t, u)</t>
-  </si>
-  <si>
     <t>A^{(protected)}(t)</t>
   </si>
   <si>
     <t>a^{(protected)}(t)</t>
   </si>
   <si>
-    <t>A^{(*protected)}(t)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
-  </si>
-  <si>
-    <t>Average above ground stock contained In land use classes that forests transition into; used to estimate above-ground conversion losses of stock.</t>
-  </si>
-  <si>
     <t>Fraction of biomass that represents dead storage. Is set in SISEPUEDE to be max of exogenous specification and amount implied by average stock in conversion targets (cannot have biomass below transition targets and remain forest).</t>
   </si>
   <si>
@@ -1074,9 +1021,6 @@
     <t>Area of remaining (from simulation initialization) forest that is protected.</t>
   </si>
   <si>
-    <t>Nominal sequestration factor (mass of biomass growth per time period) associated with forests. Used in NPP fit from integration target.</t>
-  </si>
-  <si>
     <t>Fraction of biomass per time period lost to decomposition. This is estimated from the NPP fit funtion under the assumption that primary forests exist in steady state (i.e., that there is no net growth of biomass if left undistributed).</t>
   </si>
   <si>
@@ -1098,9 +1042,6 @@
     <t>arr_young_area_by_tp_planted_drops (T x T)   [e.g., col J]</t>
   </si>
   <si>
-    <t>Matrix ($T \times T$) storing how much area of young forest planted in time $t$ remains in time $u$</t>
-  </si>
-  <si>
     <t>Matrix ($T \times T$) storing how much forest area in each time period (column $u$) has to be dropped due to conversion into young forests. Only applicable if all other secondary forest has been elimnated.</t>
   </si>
   <si>
@@ -1117,6 +1058,285 @@
   </si>
   <si>
     <t>Vector ($T$) storing total above-ground mass of biomass preserved in each time period.</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing total biomass from conversion that is available to satisfy harvested wood product (HWP) and fuelwood (FW) demands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($T \times T$) storing total young biomass that is converted to other (non-forest) land use types by time period planted. </t>
+  </si>
+  <si>
+    <t>Vector ($T$)  storing total young biomass that is converted to other (non-forest) land use types at time $t$.</t>
+  </si>
+  <si>
+    <t>K_{avail}(t, u)</t>
+  </si>
+  <si>
+    <t>k_{avail}(T)</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing how much biomass is available at time $t$ from young forests.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) used to determine whether young biomass is available for harvest. Determined based on number of years of growth required to make biomass available.</t>
+  </si>
+  <si>
+    <t>arr_young_biomass_c_stock_removal_allocation_aux (T x T)   [e.g., col F]</t>
+  </si>
+  <si>
+    <t>arr_young_biomass_c_stock_removal_allocation (T x T)   [e.g., col G]</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing counterfactual for young biomass above-ground stock if untouched at time $t$ for biomass planted at time $u$.</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{alloc}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing total above-ground mass of biomas allocated for removal in time $t$ from biomass planted at time $u$.</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{alloc\_aux}(t, u)</t>
+  </si>
+  <si>
+    <t>arr_young_sf_adjusted_by_tp_planted (T x T)   [e.g., col J]</t>
+  </si>
+  <si>
+    <t>arr_young_sf_adjustment_factor (T x T)   [e.g., col I]</t>
+  </si>
+  <si>
+    <t>\Psi^{(y)}(t, u)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($T \times T$) storing the adjustment factor for young forest factors; applied to unadjusted yuong forest sequestration factor $R^{(y)}_0(t, u)$ based on depletion leevels. </t>
+  </si>
+  <si>
+    <t>\overline{Y}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing total above-ground biomass stock at time $t$ for young forests planted at time $u$.</t>
+  </si>
+  <si>
+    <t>\Delta_0\overline{Y}(t, u)</t>
+  </si>
+  <si>
+    <t>\Delta\overline{Y}(t, u)</t>
+  </si>
+  <si>
+    <t>\underline{Y}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing total below-ground biomass stock at time $t$ for young forests planted at time $u$.</t>
+  </si>
+  <si>
+    <t>D^{(y)}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing the loss of biomass in young forests due to decomposition. Decomposition rates are determined as a function of the NPP curve and an assumption that primary forests are in steady state.</t>
+  </si>
+  <si>
+    <t>A^{(y)}(t, u)</t>
+  </si>
+  <si>
+    <t>\hat{A}^{(y)}(t, u)</t>
+  </si>
+  <si>
+    <t>L^{(y)}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) used in auxialiary calculations for total above-ground mass of biomas allocated for removal in time $t$ from biomass planted at time $u$.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing the sequestration factors (which come from AFOLU NPP curve estimates) for unperturbed young forests by time period planted.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing the adjusted sequestration factors (which come from AFOLU NPP curve estimates) for forests by time period planted. Adjustments are based off of the level of average stock depletion.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times T$) storing how much area of young forest planted in time $t$ remains in time $u$.</t>
+  </si>
+  <si>
+    <t>\chi(t)</t>
+  </si>
+  <si>
+    <t>\overline{M}_0^*</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing initial (start of simulation) above ground biomass stock.</t>
+  </si>
+  <si>
+    <t>\Delta B</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing sequestration factor in original forests (as adjusted due to degradation).</t>
+  </si>
+  <si>
+    <t>\overline{M}_0</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing above ground biomass stock left from start of simulation if untouched (without degradation).</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing biomass stock remaining from forests present at the start of the simulation.</t>
+  </si>
+  <si>
+    <t>\overline{\overline{B}}</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing average (mass per unit area) biomass stock remaining from forests present at the start of the simulation.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing average (mass per unit area) biomass stock remaining from forests present at the start of the simulation \emph{excluding} dead storage.</t>
+  </si>
+  <si>
+    <t>\overline{y}(t)</t>
+  </si>
+  <si>
+    <t>\overline{m}(t)</t>
+  </si>
+  <si>
+    <t>\underline{m}(t)</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing total above-ground biomass stock in young forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing total above-ground biomass stock in all forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing total below-ground biomass stock in all forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing total mass of biomass from original forests converted away in each time period.</t>
+  </si>
+  <si>
+    <t>\Delta_0\overline{b}</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing average above ground stock contained In land use classes that forests transition into; used to estimate above-ground conversion losses of stock.</t>
+  </si>
+  <si>
+    <t>\overline{G}</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) soring average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
+  </si>
+  <si>
+    <t>\underline{G}</t>
+  </si>
+  <si>
+    <t>Vector (length 2) storing nominal sequestration factor (mass of biomass growth per time period) associated with forests. Used in NPP fit from integration target.</t>
+  </si>
+  <si>
+    <t>\overline{b}_{conv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{y}_{availconv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{y}_{presconv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{presconv}(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{b}_{presconv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{b}_{availconv}(t)</t>
+  </si>
+  <si>
+    <t>r_{conv}(t)</t>
+  </si>
+  <si>
+    <t>Mass of biomass removals from converted land at time $t$.</t>
+  </si>
+  <si>
+    <t>Row-stochastic matrix ($T \times 2$) storing allocation of removals by forest type (column) at time $t$ (row).</t>
+  </si>
+  <si>
+    <t>\Phi_{conv}</t>
+  </si>
+  <si>
+    <t>A^{(0)}_{avail}</t>
+  </si>
+  <si>
+    <t>Matrix storing total biomass available (i.e., excluding dead storage) in original forests by type (column) excluding land converted out at time period $t$. Excludes young forests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector ($T$) storing demand for removals from all forests, excluding those from conversions. </t>
+  </si>
+  <si>
+    <t>d_{rmv}</t>
+  </si>
+  <si>
+    <t>u^{(0)}_{rmv}</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing unmet demand for removals from original forests.</t>
+  </si>
+  <si>
+    <t>r^{(0)}_{rmv}</t>
+  </si>
+  <si>
+    <t>r^{(y)}_{rmv}</t>
+  </si>
+  <si>
+    <t>R^{(0)}_{rmv}</t>
+  </si>
+  <si>
+    <t>R_{rmv}</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing removals from original forests by type (columns), excluding conversions.</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing removals from young forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
+  </si>
+  <si>
+    <t>Vector ($T$) storing removals from original forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) storing removals from all forests byt ype (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
+  </si>
+  <si>
+    <t>\overline{\overline{B}}'</t>
+  </si>
+  <si>
+    <t>A^{(protected)*}(t)</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) giving fraction of original forest stock available when compared to healthy (unperturbed) baseline.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) giving fraction of removals satisfiable at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>\tilde{A}^{(0)}_{avail}</t>
+  </si>
+  <si>
+    <t>\tilde{a}^{(0)}</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) giving adjusted--based on availability in buffer zone--quantity of biomass available for removals by forest type.</t>
+  </si>
+  <si>
+    <t>Vector ($T $) giving adjusted--based on availability in buffer zone--total quantity of biomass available for removals.</t>
+  </si>
+  <si>
+    <t>Matrix ($T \times 2$) giving allocation of adjusted--based on availability in buffer zone--quantity of biomass available for removals by forest type.</t>
+  </si>
+  <si>
+    <t>\Phi_{avail}</t>
+  </si>
+  <si>
+    <t>\Psi^{(0)}_{seq}</t>
+  </si>
+  <si>
+    <t>\Psi^{(0)}_{rmvsat}</t>
+  </si>
+  <si>
+    <t>S^{(0)}(t, v)</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1378,9 +1598,6 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1405,9 +1622,6 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1425,6 +1639,15 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1961,60 +2184,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="50" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50" t="s">
+      <c r="G1" s="47"/>
+      <c r="H1" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="50"/>
-      <c r="J1" s="49" t="s">
+      <c r="I1" s="48"/>
+      <c r="J1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="51" t="s">
+      <c r="K1" s="47"/>
+      <c r="L1" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="51"/>
-      <c r="N1" s="44" t="s">
+      <c r="M1" s="49"/>
+      <c r="N1" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="51" t="s">
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52" t="s">
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="52"/>
+      <c r="V1" s="50"/>
       <c r="W1" s="4" t="s">
         <v>46</v>
       </c>
       <c r="X1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AC1" s="49" t="s">
+      <c r="AC1" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
       <c r="AI1" s="7" t="s">
         <v>37</v>
       </c>
@@ -6593,7 +6816,7 @@
     <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
     <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
-    <col min="28" max="28" width="48.33203125" style="53" customWidth="1"/>
+    <col min="28" max="28" width="64.5" style="51" customWidth="1"/>
     <col min="29" max="30" width="14.6640625" customWidth="1"/>
     <col min="31" max="33" width="14.1640625" customWidth="1"/>
     <col min="34" max="34" width="4.1640625" customWidth="1"/>
@@ -6633,7 +6856,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="24"/>
-      <c r="AB1" s="55"/>
+      <c r="AB1" s="53"/>
     </row>
     <row r="2" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="24"/>
@@ -6647,10 +6870,10 @@
       <c r="H2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="44">
+      <c r="I2" s="43">
         <v>150</v>
       </c>
-      <c r="J2" s="44"/>
+      <c r="J2" s="43"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -6670,7 +6893,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="24"/>
-      <c r="AB2" s="55"/>
+      <c r="AB2" s="53"/>
     </row>
     <row r="3" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="24"/>
@@ -6682,10 +6905,10 @@
       <c r="H3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="43">
         <v>30</v>
       </c>
-      <c r="J3" s="44"/>
+      <c r="J3" s="43"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -6703,7 +6926,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="24"/>
-      <c r="AB3" s="55"/>
+      <c r="AB3" s="53"/>
     </row>
     <row r="4" spans="1:41" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G4" s="8">
@@ -6740,12 +6963,12 @@
         <v>6</v>
       </c>
       <c r="Z4" s="20"/>
-      <c r="AB4" s="55"/>
-      <c r="AE4" s="43" t="s">
+      <c r="AB4" s="53"/>
+      <c r="AE4" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="AF4" s="43"/>
-      <c r="AG4" s="43"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="42"/>
       <c r="AL4" t="s">
         <v>94</v>
       </c>
@@ -6761,7 +6984,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -6775,43 +6998,43 @@
       <c r="F5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="42"/>
+      <c r="H5" s="41"/>
       <c r="I5" s="17"/>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="42"/>
-      <c r="M5" s="42" t="s">
+      <c r="K5" s="41"/>
+      <c r="M5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="42"/>
-      <c r="P5" s="42" t="s">
+      <c r="N5" s="41"/>
+      <c r="P5" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="42"/>
-      <c r="S5" s="42" t="s">
+      <c r="Q5" s="41"/>
+      <c r="S5" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="T5" s="42"/>
-      <c r="V5" s="42" t="s">
+      <c r="T5" s="41"/>
+      <c r="V5" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="W5" s="42"/>
-      <c r="Y5" s="42" t="s">
+      <c r="W5" s="41"/>
+      <c r="Y5" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="Z5" s="42"/>
+      <c r="Z5" s="41"/>
       <c r="AA5" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="AB5" s="56" t="s">
-        <v>347</v>
+        <v>328</v>
+      </c>
+      <c r="AB5" s="54" t="s">
+        <v>329</v>
       </c>
       <c r="AD5" s="36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AE5" s="21" t="s">
         <v>33</v>
@@ -6879,7 +7102,7 @@
       <c r="Z6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB6" s="55"/>
+      <c r="AB6" s="53"/>
       <c r="AE6" s="19">
         <v>0</v>
       </c>
@@ -6968,10 +7191,10 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="AB7" s="54" t="s">
-        <v>331</v>
+        <v>298</v>
+      </c>
+      <c r="AB7" s="52" t="s">
+        <v>314</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7063,10 +7286,10 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="AB8" s="54" t="s">
-        <v>332</v>
+        <v>281</v>
+      </c>
+      <c r="AB8" s="52" t="s">
+        <v>315</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7093,7 +7316,7 @@
     </row>
     <row r="9" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>162</v>
@@ -7144,10 +7367,10 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="AB9" s="54" t="s">
-        <v>333</v>
+        <v>283</v>
+      </c>
+      <c r="AB9" s="52" t="s">
+        <v>316</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7174,7 +7397,7 @@
     </row>
     <row r="10" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="B10" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>174</v>
@@ -7211,10 +7434,10 @@
         <v>0</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="AB10" s="54" t="s">
-        <v>334</v>
+        <v>284</v>
+      </c>
+      <c r="AB10" s="52" t="s">
+        <v>317</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7229,7 +7452,7 @@
     </row>
     <row r="11" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>174</v>
@@ -7266,10 +7489,10 @@
         <v>0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="AB11" s="54" t="s">
-        <v>335</v>
+        <v>285</v>
+      </c>
+      <c r="AB11" s="52" t="s">
+        <v>318</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7284,7 +7507,7 @@
     </row>
     <row r="12" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>162</v>
@@ -7314,10 +7537,10 @@
         <v>110</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB12" s="54" t="s">
-        <v>336</v>
+        <v>282</v>
+      </c>
+      <c r="AB12" s="52" t="s">
+        <v>319</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7397,10 +7620,10 @@
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="AB13" s="54" t="s">
-        <v>323</v>
+        <v>300</v>
+      </c>
+      <c r="AB13" s="52" t="s">
+        <v>308</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7408,7 +7631,7 @@
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>162</v>
@@ -7438,10 +7661,10 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB14" s="54" t="s">
-        <v>337</v>
+        <v>371</v>
+      </c>
+      <c r="AB14" s="52" t="s">
+        <v>320</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7456,16 +7679,16 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -7510,10 +7733,10 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="AB15" s="54" t="s">
-        <v>325</v>
+        <v>391</v>
+      </c>
+      <c r="AB15" s="52" t="s">
+        <v>390</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7521,7 +7744,7 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="38" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C16" s="31"/>
       <c r="G16" s="4">
@@ -7581,10 +7804,10 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB16" s="54" t="s">
-        <v>324</v>
+        <v>393</v>
+      </c>
+      <c r="AB16" s="52" t="s">
+        <v>392</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -7592,13 +7815,13 @@
     </row>
     <row r="17" spans="2:33" ht="51" x14ac:dyDescent="0.2">
       <c r="B17" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G17" s="4">
         <v>0.33057704999999998</v>
@@ -7607,10 +7830,10 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="AB17" s="54" t="s">
-        <v>326</v>
+        <v>286</v>
+      </c>
+      <c r="AB17" s="52" t="s">
+        <v>309</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -7625,12 +7848,12 @@
     </row>
     <row r="18" spans="2:33" ht="34" x14ac:dyDescent="0.2">
       <c r="B18" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="40" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="10" t="s">
@@ -7643,10 +7866,10 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="AB18" s="54" t="s">
-        <v>327</v>
+        <v>287</v>
+      </c>
+      <c r="AB18" s="52" t="s">
+        <v>310</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -7661,23 +7884,23 @@
     </row>
     <row r="19" spans="2:33" ht="51" x14ac:dyDescent="0.2">
       <c r="B19" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="41"/>
+      <c r="E19" s="40"/>
       <c r="F19" s="10" t="s">
         <v>138</v>
       </c>
       <c r="G19" s="4">
         <v>0.67</v>
       </c>
-      <c r="AA19" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB19" s="54" t="s">
-        <v>328</v>
+      <c r="AA19" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB19" s="52" t="s">
+        <v>311</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -7692,7 +7915,7 @@
     </row>
     <row r="20" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B20" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>162</v>
@@ -7707,10 +7930,10 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB20" s="54" t="s">
-        <v>329</v>
+        <v>296</v>
+      </c>
+      <c r="AB20" s="52" t="s">
+        <v>312</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -7725,7 +7948,7 @@
     </row>
     <row r="21" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>162</v>
@@ -7740,10 +7963,10 @@
         <v>0.25</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB21" s="54" t="s">
-        <v>330</v>
+        <v>289</v>
+      </c>
+      <c r="AB21" s="52" t="s">
+        <v>313</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
@@ -7751,7 +7974,7 @@
     </row>
     <row r="22" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B22" s="38" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>174</v>
@@ -7768,9 +7991,9 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="AB22" s="54"/>
+        <v>321</v>
+      </c>
+      <c r="AB22" s="52"/>
       <c r="AE22" s="19">
         <v>12</v>
       </c>
@@ -7784,7 +8007,7 @@
     </row>
     <row r="23" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>174</v>
@@ -7801,10 +8024,10 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="AB23" s="54" t="s">
-        <v>339</v>
+        <v>290</v>
+      </c>
+      <c r="AB23" s="52" t="s">
+        <v>322</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -7818,7 +8041,7 @@
       </c>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="AB24" s="55"/>
+      <c r="AB24" s="53"/>
       <c r="AE24" s="19">
         <v>12</v>
       </c>
@@ -7883,10 +8106,10 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB25" s="54" t="s">
-        <v>340</v>
+        <v>306</v>
+      </c>
+      <c r="AB25" s="52" t="s">
+        <v>323</v>
       </c>
       <c r="AE25" s="19">
         <v>10</v>
@@ -7901,7 +8124,7 @@
     </row>
     <row r="26" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>163</v>
@@ -7938,10 +8161,10 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="AB26" s="54" t="s">
-        <v>341</v>
+        <v>307</v>
+      </c>
+      <c r="AB26" s="52" t="s">
+        <v>324</v>
       </c>
       <c r="AE26" s="19">
         <v>6</v>
@@ -8021,10 +8244,10 @@
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="AB27" s="54" t="s">
-        <v>342</v>
+        <v>420</v>
+      </c>
+      <c r="AB27" s="52" t="s">
+        <v>325</v>
       </c>
       <c r="AE27" s="19">
         <v>3</v>
@@ -8055,7 +8278,7 @@
       <c r="W28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
-      <c r="AB28" s="55"/>
+      <c r="AB28" s="53"/>
       <c r="AE28" s="19">
         <v>1.8</v>
       </c>
@@ -8069,12 +8292,12 @@
     </row>
     <row r="29" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="38" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="40" t="s">
         <v>170</v>
       </c>
       <c r="F29" s="25" t="s">
@@ -8087,20 +8310,20 @@
         <v>0.92</v>
       </c>
       <c r="AA29" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB29" s="54" t="s">
-        <v>343</v>
+        <v>389</v>
+      </c>
+      <c r="AB29" s="52" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="25" t="s">
         <v>171</v>
       </c>
@@ -8117,15 +8340,15 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="AB30" s="54" t="s">
-        <v>344</v>
+        <v>297</v>
+      </c>
+      <c r="AB30" s="52" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="26"/>
-      <c r="AB31" s="55"/>
+      <c r="AB31" s="53"/>
     </row>
     <row r="32" spans="2:33" ht="17" x14ac:dyDescent="0.2">
       <c r="F32" s="15" t="s">
@@ -8145,7 +8368,7 @@
       <c r="W32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
-      <c r="AB32" s="55"/>
+      <c r="AB32" s="53"/>
     </row>
     <row r="33" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="38" t="s">
@@ -8179,14 +8402,14 @@
         <v>2520000</v>
       </c>
       <c r="AA33" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB33" s="54" t="s">
-        <v>345</v>
+        <v>299</v>
+      </c>
+      <c r="AB33" s="52" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB34" s="55"/>
+      <c r="AB34" s="53"/>
     </row>
     <row r="35" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
@@ -8206,7 +8429,7 @@
       <c r="W35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
-      <c r="AB35" s="55"/>
+      <c r="AB35" s="53"/>
     </row>
     <row r="36" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F36" s="15" t="s">
@@ -8228,7 +8451,7 @@
       <c r="P36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB36" s="55"/>
+      <c r="AB36" s="53"/>
       <c r="AD36" t="s">
         <v>77</v>
       </c>
@@ -8285,13 +8508,13 @@
       <c r="Z37" s="4">
         <v>0</v>
       </c>
-      <c r="AB37" s="55"/>
+      <c r="AB37" s="53"/>
     </row>
     <row r="38" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B38" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="C38" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="C38" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F38" s="14" t="s">
@@ -8377,17 +8600,17 @@
         <v>85</v>
       </c>
       <c r="AA38" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="AB38" s="54" t="s">
-        <v>353</v>
+        <v>364</v>
+      </c>
+      <c r="AB38" s="52" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="39" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B39" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="C39" s="45"/>
+        <v>331</v>
+      </c>
+      <c r="C39" s="44"/>
       <c r="F39" s="14" t="s">
         <v>69</v>
       </c>
@@ -8470,17 +8693,17 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="AB39" s="54" t="s">
-        <v>351</v>
+        <v>365</v>
+      </c>
+      <c r="AB39" s="52" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B40" s="38" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="45"/>
+        <v>332</v>
+      </c>
+      <c r="C40" s="44"/>
       <c r="F40" s="14" t="s">
         <v>79</v>
       </c>
@@ -8562,15 +8785,15 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB40" s="54" t="s">
-        <v>352</v>
+        <v>366</v>
+      </c>
+      <c r="AB40" s="52" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B41" s="38"/>
-      <c r="C41" s="45"/>
+      <c r="C41" s="44"/>
       <c r="F41" s="14" t="s">
         <v>80</v>
       </c>
@@ -8651,23 +8874,23 @@
         <v>43</v>
       </c>
       <c r="AA41" s="38"/>
-      <c r="AB41" s="54"/>
+      <c r="AB41" s="52"/>
     </row>
     <row r="42" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB42" s="55"/>
+      <c r="AB42" s="53"/>
     </row>
     <row r="43" spans="2:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B43" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="C43" s="45" t="s">
+      <c r="B43" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H43" s="4">
         <v>0</v>
@@ -8697,17 +8920,17 @@
         <v>0</v>
       </c>
       <c r="AA43" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="AB43" s="54" t="s">
-        <v>355</v>
+        <v>301</v>
+      </c>
+      <c r="AB43" s="52" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="2:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="47"/>
-      <c r="C44" s="45"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="44"/>
       <c r="F44" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H44" s="4">
         <v>0</v>
@@ -8737,13 +8960,13 @@
         <v>0</v>
       </c>
       <c r="AA44" s="38"/>
-      <c r="AB44" s="54"/>
+      <c r="AB44" s="52"/>
     </row>
     <row r="45" spans="2:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B45" s="47"/>
-      <c r="C45" s="45"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="44"/>
       <c r="F45" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -8773,13 +8996,13 @@
         <v>0</v>
       </c>
       <c r="AA45" s="38"/>
-      <c r="AB45" s="54"/>
+      <c r="AB45" s="52"/>
     </row>
     <row r="46" spans="2:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="47"/>
-      <c r="C46" s="45"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="44"/>
       <c r="F46" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H46" s="4">
         <v>0</v>
@@ -8809,11 +9032,11 @@
         <v>0</v>
       </c>
       <c r="AA46" s="38"/>
-      <c r="AB46" s="54"/>
+      <c r="AB46" s="52"/>
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B47" s="38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C47" s="28" t="s">
         <v>174</v>
@@ -8848,30 +9071,30 @@
         <v>0</v>
       </c>
       <c r="AA47" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB47" s="54" t="s">
-        <v>354</v>
+        <v>302</v>
+      </c>
+      <c r="AB47" s="52" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F48" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB48" s="55"/>
+      <c r="AB48" s="53"/>
     </row>
     <row r="49" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="C49" s="45" t="s">
+      <c r="B49" s="46" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="41" t="s">
-        <v>250</v>
+      <c r="E49" s="40" t="s">
+        <v>248</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H49" s="4">
         <f>MIN(H43,H$15*G38)</f>
@@ -8902,18 +9125,18 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="AB49" s="54" t="s">
-        <v>356</v>
+        <v>398</v>
+      </c>
+      <c r="AB49" s="52" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="50" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B50" s="47"/>
-      <c r="C50" s="45"/>
-      <c r="E50" s="41"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="44"/>
+      <c r="E50" s="40"/>
       <c r="F50" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H50" s="4">
         <f>MIN(H44,H$15*G39)</f>
@@ -8944,14 +9167,14 @@
         <v>0</v>
       </c>
       <c r="AA50" s="38"/>
-      <c r="AB50" s="54"/>
+      <c r="AB50" s="52"/>
     </row>
     <row r="51" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="47"/>
-      <c r="C51" s="45"/>
-      <c r="E51" s="41"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="44"/>
+      <c r="E51" s="40"/>
       <c r="F51" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H51" s="4">
         <f>MIN(H45,H$15*G40)</f>
@@ -8982,14 +9205,14 @@
         <v>0</v>
       </c>
       <c r="AA51" s="38"/>
-      <c r="AB51" s="54"/>
+      <c r="AB51" s="52"/>
     </row>
     <row r="52" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="47"/>
-      <c r="C52" s="45"/>
-      <c r="E52" s="41"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="44"/>
+      <c r="E52" s="40"/>
       <c r="F52" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H52" s="4">
         <f>MIN(H46,H$15*G41)</f>
@@ -9020,11 +9243,11 @@
         <v>0</v>
       </c>
       <c r="AA52" s="38"/>
-      <c r="AB52" s="54"/>
+      <c r="AB52" s="52"/>
     </row>
     <row r="53" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B53" s="38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C53" s="28" t="s">
         <v>174</v>
@@ -9059,15 +9282,15 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB53" s="54" t="s">
-        <v>357</v>
+        <v>397</v>
+      </c>
+      <c r="AB53" s="52" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B54" s="38" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C54" s="28"/>
       <c r="F54" s="14"/>
@@ -9100,23 +9323,25 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="AB54" s="54"/>
+        <v>396</v>
+      </c>
+      <c r="AB54" s="52" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="55" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F55" s="14"/>
-      <c r="AB55" s="54"/>
+      <c r="AB55" s="52"/>
     </row>
     <row r="56" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="47" t="s">
-        <v>192</v>
-      </c>
-      <c r="C56" s="45" t="s">
+      <c r="B56" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="C56" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H56" s="4">
         <f>H43*$H$21</f>
@@ -9147,15 +9372,17 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="AB56" s="54"/>
+        <v>303</v>
+      </c>
+      <c r="AB56" s="52" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="57" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B57" s="47"/>
-      <c r="C57" s="45"/>
+      <c r="B57" s="46"/>
+      <c r="C57" s="44"/>
       <c r="F57" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H57" s="4">
         <f>H44*$H$21</f>
@@ -9186,13 +9413,13 @@
         <v>0</v>
       </c>
       <c r="AA57" s="38"/>
-      <c r="AB57" s="54"/>
+      <c r="AB57" s="52"/>
     </row>
     <row r="58" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="47"/>
-      <c r="C58" s="45"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="44"/>
       <c r="F58" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H58" s="4">
         <f>H45*$H$21</f>
@@ -9223,13 +9450,13 @@
         <v>0</v>
       </c>
       <c r="AA58" s="38"/>
-      <c r="AB58" s="54"/>
+      <c r="AB58" s="52"/>
     </row>
     <row r="59" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="47"/>
-      <c r="C59" s="45"/>
+      <c r="B59" s="46"/>
+      <c r="C59" s="44"/>
       <c r="F59" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H59" s="4">
         <f>H46*$H$21</f>
@@ -9260,11 +9487,11 @@
         <v>0</v>
       </c>
       <c r="AA59" s="38"/>
-      <c r="AB59" s="54"/>
+      <c r="AB59" s="52"/>
     </row>
     <row r="60" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B60" s="38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C60" s="28" t="s">
         <v>174</v>
@@ -9299,19 +9526,21 @@
         <v>0</v>
       </c>
       <c r="AA60" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="AB60" s="54"/>
+        <v>304</v>
+      </c>
+      <c r="AB60" s="52" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="61" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F61" s="14"/>
-      <c r="AB61" s="54"/>
+      <c r="AB61" s="52"/>
     </row>
     <row r="62" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="45" t="s">
+      <c r="C62" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F62" s="14" t="s">
@@ -9346,13 +9575,15 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="AB62" s="54"/>
+        <v>358</v>
+      </c>
+      <c r="AB62" s="52" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="63" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B63" s="47"/>
-      <c r="C63" s="45"/>
+      <c r="B63" s="46"/>
+      <c r="C63" s="44"/>
       <c r="F63" s="14" t="s">
         <v>91</v>
       </c>
@@ -9383,11 +9614,11 @@
         <v>0.36</v>
       </c>
       <c r="AA63" s="38"/>
-      <c r="AB63" s="54"/>
+      <c r="AB63" s="52"/>
     </row>
     <row r="64" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B64" s="47"/>
-      <c r="C64" s="45"/>
+      <c r="B64" s="46"/>
+      <c r="C64" s="44"/>
       <c r="F64" s="14" t="s">
         <v>92</v>
       </c>
@@ -9417,11 +9648,11 @@
         <v>0.2</v>
       </c>
       <c r="AA64" s="38"/>
-      <c r="AB64" s="54"/>
+      <c r="AB64" s="52"/>
     </row>
     <row r="65" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="47"/>
-      <c r="C65" s="45"/>
+      <c r="B65" s="46"/>
+      <c r="C65" s="44"/>
       <c r="F65" s="14" t="s">
         <v>93</v>
       </c>
@@ -9450,23 +9681,23 @@
         <v>0.12</v>
       </c>
       <c r="AA65" s="38"/>
-      <c r="AB65" s="54"/>
+      <c r="AB65" s="52"/>
     </row>
     <row r="66" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="F66" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="AB66" s="54"/>
+      <c r="AB66" s="52"/>
     </row>
     <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="F67" s="14"/>
-      <c r="AB67" s="54"/>
+      <c r="AB67" s="52"/>
     </row>
     <row r="68" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="C68" s="45" t="s">
+      <c r="B68" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="C68" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F68" s="14" t="s">
@@ -9501,13 +9732,15 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="AB68" s="54"/>
+        <v>305</v>
+      </c>
+      <c r="AB68" s="52" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="69" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="47"/>
-      <c r="C69" s="45"/>
+      <c r="B69" s="46"/>
+      <c r="C69" s="44"/>
       <c r="F69" s="14" t="s">
         <v>110</v>
       </c>
@@ -9536,12 +9769,12 @@
         <v>59.120937045501634</v>
       </c>
       <c r="AA69" s="38"/>
-      <c r="AB69" s="54"/>
+      <c r="AB69" s="52"/>
     </row>
     <row r="70" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="47"/>
-      <c r="C70" s="45"/>
-      <c r="E70" s="41"/>
+      <c r="B70" s="46"/>
+      <c r="C70" s="44"/>
+      <c r="E70" s="40"/>
       <c r="F70" s="14" t="s">
         <v>111</v>
       </c>
@@ -9566,12 +9799,12 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA70" s="38"/>
-      <c r="AB70" s="54"/>
+      <c r="AB70" s="52"/>
     </row>
     <row r="71" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="47"/>
-      <c r="C71" s="45"/>
-      <c r="E71" s="41"/>
+      <c r="B71" s="46"/>
+      <c r="C71" s="44"/>
+      <c r="E71" s="40"/>
       <c r="F71" s="14" t="s">
         <v>112</v>
       </c>
@@ -9596,18 +9829,18 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA71" s="38"/>
-      <c r="AB71" s="54"/>
+      <c r="AB71" s="52"/>
     </row>
     <row r="72" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="E72" s="41"/>
+      <c r="E72" s="40"/>
       <c r="F72" s="14"/>
-      <c r="AB72" s="54"/>
+      <c r="AB72" s="52"/>
     </row>
     <row r="73" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B73" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C73" s="45" t="s">
+      <c r="B73" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F73" s="14" t="s">
@@ -9640,12 +9873,16 @@
         <f>INT(Y$4-$AG$6 &gt; $E81)*MAX(W96-$H$22*W38-Z43,0)</f>
         <v>0</v>
       </c>
-      <c r="AA73" s="38"/>
-      <c r="AB73" s="54"/>
+      <c r="AA73" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="AB73" s="52" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="74" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B74" s="47"/>
-      <c r="C74" s="45"/>
+      <c r="B74" s="46"/>
+      <c r="C74" s="44"/>
       <c r="F74" s="14" t="s">
         <v>128</v>
       </c>
@@ -9677,12 +9914,12 @@
         <v>0</v>
       </c>
       <c r="AA74" s="38"/>
-      <c r="AB74" s="54"/>
+      <c r="AB74" s="52"/>
     </row>
     <row r="75" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="47"/>
-      <c r="C75" s="45"/>
-      <c r="E75" s="41" t="s">
+      <c r="B75" s="46"/>
+      <c r="C75" s="44"/>
+      <c r="E75" s="40" t="s">
         <v>152</v>
       </c>
       <c r="F75" s="14" t="s">
@@ -9716,12 +9953,12 @@
         <v>0</v>
       </c>
       <c r="AA75" s="38"/>
-      <c r="AB75" s="54"/>
+      <c r="AB75" s="52"/>
     </row>
     <row r="76" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B76" s="47"/>
-      <c r="C76" s="45"/>
-      <c r="E76" s="41"/>
+      <c r="B76" s="46"/>
+      <c r="C76" s="44"/>
+      <c r="E76" s="40"/>
       <c r="F76" s="14" t="s">
         <v>130</v>
       </c>
@@ -9753,16 +9990,16 @@
         <v>0</v>
       </c>
       <c r="AA76" s="38"/>
-      <c r="AB76" s="54"/>
+      <c r="AB76" s="52"/>
     </row>
     <row r="77" spans="2:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B77" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C77" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E77" s="41"/>
+      <c r="E77" s="40"/>
       <c r="F77" s="14" t="s">
         <v>147</v>
       </c>
@@ -9793,16 +10030,20 @@
         <f>SUM(Z73:Z76)</f>
         <v>0</v>
       </c>
-      <c r="AA77" s="38"/>
-      <c r="AB77" s="54"/>
+      <c r="AA77" s="56" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB77" s="52" t="s">
+        <v>344</v>
+      </c>
       <c r="AF77" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="78" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="E78" s="41"/>
+      <c r="E78" s="40"/>
       <c r="F78" s="14"/>
-      <c r="AB78" s="54"/>
+      <c r="AB78" s="52"/>
       <c r="AD78" t="s">
         <v>85</v>
       </c>
@@ -9811,10 +10052,10 @@
       </c>
     </row>
     <row r="79" spans="2:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="48" t="s">
-        <v>236</v>
-      </c>
-      <c r="C79" s="45" t="s">
+      <c r="B79" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="C79" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F79" s="14" t="s">
@@ -9841,15 +10082,21 @@
       <c r="Y79" s="4">
         <v>0</v>
       </c>
-      <c r="AA79" s="39"/>
-      <c r="AB79" s="54"/>
+      <c r="AA79" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="AB79" s="52" t="s">
+        <v>350</v>
+      </c>
       <c r="AD79" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="80" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B80" s="48"/>
-      <c r="C80" s="45"/>
+      <c r="B80" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="C80" s="44"/>
       <c r="F80" s="14" t="s">
         <v>148</v>
       </c>
@@ -9909,12 +10156,16 @@
         <f>IF(Y80&gt;=Y$132, IF(Y79&lt;Y$132, Y$132-Y79, 0),Z73)</f>
         <v>0</v>
       </c>
-      <c r="AA80" s="39"/>
-      <c r="AB80" s="54"/>
+      <c r="AA80" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="AB80" s="52" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="81" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="48"/>
-      <c r="C81" s="45"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="44"/>
       <c r="E81" s="22">
         <v>0</v>
       </c>
@@ -9977,12 +10228,12 @@
         <f>IF(Y81&gt;=Y$132, IF(Y80&lt;Y$132, Y$132-Y80, 0),Z74)</f>
         <v>0</v>
       </c>
-      <c r="AA81" s="39"/>
-      <c r="AB81" s="54"/>
+      <c r="AA81" s="37"/>
+      <c r="AB81" s="52"/>
     </row>
     <row r="82" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="48"/>
-      <c r="C82" s="45"/>
+      <c r="B82" s="55"/>
+      <c r="C82" s="44"/>
       <c r="E82" s="22">
         <v>1</v>
       </c>
@@ -10045,12 +10296,12 @@
         <f>IF(Y82&gt;=Y$132, IF(Y81&lt;Y$132, Y$132-Y81, 0),Z75)</f>
         <v>0</v>
       </c>
-      <c r="AA82" s="39"/>
-      <c r="AB82" s="54"/>
+      <c r="AA82" s="37"/>
+      <c r="AB82" s="52"/>
     </row>
     <row r="83" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="48"/>
-      <c r="C83" s="45"/>
+      <c r="B83" s="55"/>
+      <c r="C83" s="44"/>
       <c r="E83" s="22">
         <v>2</v>
       </c>
@@ -10113,15 +10364,15 @@
         <f>IF(Y83&gt;=Y$132, IF(Y82&lt;Y$132, Y$132-Y82, 0),Z76)</f>
         <v>0</v>
       </c>
-      <c r="AA83" s="39"/>
-      <c r="AB83" s="54"/>
+      <c r="AA83" s="37"/>
+      <c r="AB83" s="52"/>
     </row>
     <row r="84" spans="2:28" x14ac:dyDescent="0.2">
       <c r="E84" s="22">
         <v>3</v>
       </c>
       <c r="F84" s="14"/>
-      <c r="AB84" s="54"/>
+      <c r="AB84" s="52"/>
     </row>
     <row r="85" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F85" s="14"/>
@@ -10143,13 +10394,13 @@
       <c r="Y85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="AB85" s="54"/>
+      <c r="AB85" s="52"/>
     </row>
     <row r="86" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B86" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="C86" s="45" t="s">
+      <c r="B86" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="C86" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F86" s="14" t="s">
@@ -10207,12 +10458,18 @@
         <f>Z62*Y86</f>
         <v>0.6</v>
       </c>
-      <c r="AA86" s="37"/>
-      <c r="AB86" s="54"/>
+      <c r="AA86" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB86" s="52" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="87" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B87" s="46"/>
-      <c r="C87" s="45"/>
+      <c r="B87" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="C87" s="44"/>
       <c r="F87" s="14" t="s">
         <v>132</v>
       </c>
@@ -10268,12 +10525,16 @@
         <f>Z63</f>
         <v>0.36</v>
       </c>
-      <c r="AA87" s="37"/>
-      <c r="AB87" s="54"/>
+      <c r="AA87" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="AB87" s="52" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="88" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B88" s="46"/>
-      <c r="C88" s="45"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="44"/>
       <c r="F88" s="14" t="s">
         <v>133</v>
       </c>
@@ -10330,11 +10591,11 @@
         <v>0.2</v>
       </c>
       <c r="AA88" s="37"/>
-      <c r="AB88" s="54"/>
+      <c r="AB88" s="52"/>
     </row>
     <row r="89" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B89" s="46"/>
-      <c r="C89" s="45"/>
+      <c r="B89" s="55"/>
+      <c r="C89" s="44"/>
       <c r="F89" s="14" t="s">
         <v>134</v>
       </c>
@@ -10391,21 +10652,21 @@
         <v>0.12</v>
       </c>
       <c r="AA89" s="37"/>
-      <c r="AB89" s="54"/>
+      <c r="AB89" s="52"/>
     </row>
     <row r="90" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F90" s="14"/>
-      <c r="AB90" s="54"/>
+      <c r="AB90" s="52"/>
     </row>
     <row r="91" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="46" t="s">
+      <c r="B91" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="C91" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="F91" s="14" t="s">
         <v>203</v>
-      </c>
-      <c r="C91" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="F91" s="14" t="s">
-        <v>204</v>
       </c>
       <c r="H91" s="4">
         <f>H57*H33</f>
@@ -10435,14 +10696,18 @@
         <f>(W96-Z80-Z43)*$G$30</f>
         <v>9.8621113109027395E-2</v>
       </c>
-      <c r="AA91" s="37"/>
-      <c r="AB91" s="54"/>
+      <c r="AA91" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB91" s="52" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="92" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="46"/>
-      <c r="C92" s="45"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="44"/>
       <c r="F92" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H92" s="4">
         <f>H58*H34</f>
@@ -10473,13 +10738,13 @@
         <v>4.7678726762454618E-2</v>
       </c>
       <c r="AA92" s="37"/>
-      <c r="AB92" s="54"/>
+      <c r="AB92" s="52"/>
     </row>
     <row r="93" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="46"/>
-      <c r="C93" s="45"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="44"/>
       <c r="F93" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H93" s="4">
         <f>H59*H35</f>
@@ -10510,13 +10775,13 @@
         <v>2.5983329604301563E-2</v>
       </c>
       <c r="AA93" s="37"/>
-      <c r="AB93" s="54"/>
+      <c r="AB93" s="52"/>
     </row>
     <row r="94" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="46"/>
-      <c r="C94" s="45"/>
+      <c r="B94" s="45"/>
+      <c r="C94" s="44"/>
       <c r="F94" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H94" s="4">
         <f>H60*H36</f>
@@ -10547,17 +10812,17 @@
         <v>4.049540093E-3</v>
       </c>
       <c r="AA94" s="37"/>
-      <c r="AB94" s="54"/>
+      <c r="AB94" s="52"/>
     </row>
     <row r="95" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F95" s="14"/>
-      <c r="AB95" s="54"/>
+      <c r="AB95" s="52"/>
     </row>
     <row r="96" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B96" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="C96" s="45" t="s">
+      <c r="B96" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="C96" s="44" t="s">
         <v>174</v>
       </c>
       <c r="F96" s="14" t="s">
@@ -10591,12 +10856,16 @@
         <f>W96 - Z80 - Z91 - Z43 + Z38*Z86</f>
         <v>113.71737449773644</v>
       </c>
-      <c r="AA96" s="37"/>
-      <c r="AB96" s="54"/>
+      <c r="AA96" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="AB96" s="52" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="97" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="46"/>
-      <c r="C97" s="45"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="44"/>
       <c r="F97" s="14" t="s">
         <v>71</v>
       </c>
@@ -10629,11 +10898,11 @@
         <v>59.120937045501627</v>
       </c>
       <c r="AA97" s="37"/>
-      <c r="AB97" s="54"/>
+      <c r="AB97" s="52"/>
     </row>
     <row r="98" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B98" s="46"/>
-      <c r="C98" s="45"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="44"/>
       <c r="F98" s="14" t="s">
         <v>72</v>
       </c>
@@ -10666,11 +10935,11 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA98" s="37"/>
-      <c r="AB98" s="54"/>
+      <c r="AB98" s="52"/>
     </row>
     <row r="99" spans="2:28" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="46"/>
-      <c r="C99" s="45"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="44"/>
       <c r="F99" s="14" t="s">
         <v>81</v>
       </c>
@@ -10703,23 +10972,23 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA99" s="37"/>
-      <c r="AB99" s="54"/>
+      <c r="AB99" s="52"/>
     </row>
     <row r="100" spans="2:28" x14ac:dyDescent="0.2">
       <c r="E100" s="26"/>
       <c r="F100" s="14"/>
-      <c r="AB100" s="54"/>
+      <c r="AB100" s="52"/>
     </row>
     <row r="101" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B101" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="C101" s="45" t="s">
+      <c r="B101" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C101" s="44" t="s">
         <v>174</v>
       </c>
       <c r="E101" s="26"/>
       <c r="F101" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H101" s="4">
         <f>H96*$H$21</f>
@@ -10749,15 +11018,19 @@
         <f>Z96*$H$21</f>
         <v>28.429343624434111</v>
       </c>
-      <c r="AA101" s="37"/>
-      <c r="AB101" s="54"/>
+      <c r="AA101" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB101" s="52" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="102" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="46"/>
-      <c r="C102" s="45"/>
+      <c r="B102" s="45"/>
+      <c r="C102" s="44"/>
       <c r="E102" s="26"/>
       <c r="F102" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H102" s="4">
         <f t="shared" ref="H102:H104" si="9">H97*$H$21</f>
@@ -10788,14 +11061,14 @@
         <v>14.780234261375407</v>
       </c>
       <c r="AA102" s="37"/>
-      <c r="AB102" s="54"/>
+      <c r="AB102" s="52"/>
     </row>
     <row r="103" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="46"/>
-      <c r="C103" s="45"/>
+      <c r="B103" s="45"/>
+      <c r="C103" s="44"/>
       <c r="E103" s="26"/>
       <c r="F103" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H103" s="4">
         <f>H98*$H$21</f>
@@ -10826,14 +11099,14 @@
         <v>8.7309770345259246</v>
       </c>
       <c r="AA103" s="37"/>
-      <c r="AB103" s="54"/>
+      <c r="AB103" s="52"/>
     </row>
     <row r="104" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="46"/>
-      <c r="C104" s="45"/>
+      <c r="B104" s="45"/>
+      <c r="C104" s="44"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H104" s="4">
         <f t="shared" si="9"/>
@@ -10864,7 +11137,7 @@
         <v>1.93381883997675</v>
       </c>
       <c r="AA104" s="37"/>
-      <c r="AB104" s="54"/>
+      <c r="AB104" s="52"/>
     </row>
     <row r="105" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B105" s="29"/>
@@ -10872,7 +11145,7 @@
       <c r="E105" s="26"/>
       <c r="F105" s="14"/>
       <c r="AA105" s="29"/>
-      <c r="AB105" s="54"/>
+      <c r="AB105" s="52"/>
     </row>
     <row r="106" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B106" s="29"/>
@@ -10880,7 +11153,7 @@
       <c r="E106" s="26"/>
       <c r="F106" s="14"/>
       <c r="AA106" s="29"/>
-      <c r="AB106" s="54"/>
+      <c r="AB106" s="52"/>
     </row>
     <row r="107" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="E107" s="26"/>
@@ -10891,14 +11164,14 @@
         <v>124</v>
       </c>
       <c r="H107" s="8"/>
-      <c r="AB107" s="54"/>
+      <c r="AB107" s="52"/>
     </row>
     <row r="108" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="38" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E108" s="26"/>
       <c r="F108" s="14" t="s">
@@ -10961,11 +11234,11 @@
         <v>0.92</v>
       </c>
       <c r="AA108" s="38"/>
-      <c r="AB108" s="54"/>
+      <c r="AB108" s="52"/>
     </row>
     <row r="109" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="38" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C109" s="28" t="s">
         <v>174</v>
@@ -11029,12 +11302,16 @@
         <f>Z7*$H$20</f>
         <v>24936000</v>
       </c>
-      <c r="AA109" s="38"/>
-      <c r="AB109" s="54"/>
+      <c r="AA109" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB109" s="52" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="110" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C110" s="28" t="s">
         <v>174</v>
@@ -11097,13 +11374,15 @@
         <v>0.86560925711218095</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB110" s="54"/>
+        <v>429</v>
+      </c>
+      <c r="AB110" s="52" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="111" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C111" s="33" t="s">
         <v>163</v>
@@ -11167,12 +11446,16 @@
         <f>Z108*Z110</f>
         <v>0.7963605165432065</v>
       </c>
-      <c r="AA111" s="38"/>
-      <c r="AB111" s="54"/>
+      <c r="AA111" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="AB111" s="52" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="112" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B112" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>163</v>
@@ -11236,12 +11519,16 @@
         <f>W112 - W133 - W121 - W144 + Z111*Z7</f>
         <v>15603395.572368858</v>
       </c>
-      <c r="AA112" s="38"/>
-      <c r="AB112" s="54"/>
+      <c r="AA112" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB112" s="52" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="113" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B113" s="38" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>163</v>
@@ -11305,12 +11592,16 @@
         <f>Z112/Z7</f>
         <v>62.573771143603061</v>
       </c>
-      <c r="AA113" s="38"/>
-      <c r="AB113" s="54"/>
+      <c r="AA113" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="AB113" s="52" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="114" spans="2:28" ht="34" x14ac:dyDescent="0.2">
       <c r="B114" s="38" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C114" s="28" t="s">
         <v>174</v>
@@ -11374,12 +11665,16 @@
         <f>MAX(Z113-$H22,0)</f>
         <v>24.772878143603059</v>
       </c>
-      <c r="AA114" s="38"/>
-      <c r="AB114" s="54"/>
+      <c r="AA114" s="38" t="s">
+        <v>419</v>
+      </c>
+      <c r="AB114" s="57" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="115" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F115" s="13"/>
-      <c r="AB115" s="54"/>
+      <c r="AB115" s="52"/>
     </row>
     <row r="116" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F116" s="11" t="s">
@@ -11399,17 +11694,17 @@
       <c r="W116" s="12"/>
       <c r="Y116" s="12"/>
       <c r="Z116" s="12"/>
-      <c r="AB116" s="54"/>
+      <c r="AB116" s="52"/>
     </row>
     <row r="117" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G117" s="4">
         <f>G113*G7</f>
@@ -11468,17 +11763,17 @@
         <v>15603395.572368858</v>
       </c>
       <c r="AA117" s="38"/>
-      <c r="AB117" s="54"/>
+      <c r="AB117" s="52"/>
     </row>
     <row r="118" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C118" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H118" s="4">
         <f>SUM(H96:H99)</f>
@@ -11508,18 +11803,22 @@
         <f>SUM(Z96:Z99)</f>
         <v>215.49749504124878</v>
       </c>
-      <c r="AA118" s="38"/>
-      <c r="AB118" s="54"/>
+      <c r="AA118" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB118" s="52" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="119" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="38" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C119" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G119" s="4">
         <f>G117+G118</f>
@@ -11577,18 +11876,22 @@
         <f>Z117+Z118</f>
         <v>15603611.069863901</v>
       </c>
-      <c r="AA119" s="38"/>
-      <c r="AB119" s="54"/>
+      <c r="AA119" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="AB119" s="52" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="120" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B120" s="38" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C120" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G120" s="4">
         <f>G119*$G$21</f>
@@ -11646,18 +11949,22 @@
         <f>Z119*$H$21</f>
         <v>3900902.7674659751</v>
       </c>
-      <c r="AA120" s="38"/>
-      <c r="AB120" s="54"/>
+      <c r="AA120" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="AB120" s="52" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="121" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C121" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G121" s="4">
         <f>G9*G113</f>
@@ -11715,18 +12022,22 @@
         <f>Z9*Z113</f>
         <v>7258.5574526579549</v>
       </c>
-      <c r="AA121" s="38"/>
-      <c r="AB121" s="54"/>
+      <c r="AA121" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="AB121" s="52" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="122" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B122" s="38" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C122" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G122" s="4">
         <f>MIN(G121,G9*G15)</f>
@@ -11784,18 +12095,22 @@
         <f>MIN(Z121,Z9*Z15)</f>
         <v>1044</v>
       </c>
-      <c r="AA122" s="38"/>
-      <c r="AB122" s="54"/>
+      <c r="AA122" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="AB122" s="52" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="123" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B123" s="38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C123" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G123" s="4">
         <f>(G121-G122)*$G$14</f>
@@ -11853,18 +12168,22 @@
         <f>(Z121-Z122+Z54)*$G$14</f>
         <v>4350.1902168605684</v>
       </c>
-      <c r="AA123" s="38"/>
-      <c r="AB123" s="54"/>
+      <c r="AA123" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="AB123" s="52" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="124" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C124" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G124" s="4">
         <f>MIN(G123+H123, G33)</f>
@@ -11894,18 +12213,22 @@
         <f>MIN(Y123+Z123, Y33)</f>
         <v>10471.887293585241</v>
       </c>
-      <c r="AA124" s="38"/>
-      <c r="AB124" s="54"/>
+      <c r="AA124" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="AB124" s="52" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="125" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C125" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G125" s="4">
         <f>G123/(G123+H123)</f>
@@ -11963,12 +12286,16 @@
         <f>Z123/(Y123+Z123)</f>
         <v>0.41541606540450088</v>
       </c>
-      <c r="AA125" s="38"/>
-      <c r="AB125" s="54"/>
+      <c r="AA125" s="38" t="s">
+        <v>404</v>
+      </c>
+      <c r="AB125" s="52" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="126" spans="2:28" ht="34" x14ac:dyDescent="0.2">
       <c r="B126" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C126" s="28" t="s">
         <v>174</v>
@@ -12032,11 +12359,15 @@
         <f>MAX(Z13-Z27, 0)*Z114</f>
         <v>4948233.7719158493</v>
       </c>
-      <c r="AA126" s="38"/>
-      <c r="AB126" s="54"/>
+      <c r="AA126" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="AB126" s="52" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="127" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="AB127" s="54"/>
+      <c r="AB127" s="52"/>
     </row>
     <row r="128" spans="2:28" ht="17" x14ac:dyDescent="0.2">
       <c r="F128" s="15" t="s">
@@ -12056,17 +12387,17 @@
       <c r="W128" s="8"/>
       <c r="Y128" s="8"/>
       <c r="Z128" s="8"/>
-      <c r="AB128" s="54"/>
+      <c r="AB128" s="52"/>
     </row>
     <row r="129" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="38" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C129" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G129" s="4">
         <f>MAX(G33-G124,0)</f>
@@ -12096,12 +12427,16 @@
         <f>MAX(Y33-Y124,0)</f>
         <v>2509528.1127064149</v>
       </c>
-      <c r="AA129" s="38"/>
-      <c r="AB129" s="54"/>
+      <c r="AA129" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB129" s="52" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="38" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C130" s="28" t="s">
         <v>174</v>
@@ -12137,12 +12472,16 @@
         <f>MIN(Y140,Y129)</f>
         <v>236958.69160889552</v>
       </c>
-      <c r="AA130" s="38"/>
-      <c r="AB130" s="54"/>
+      <c r="AA130" s="38" t="s">
+        <v>411</v>
+      </c>
+      <c r="AB130" s="52" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="38" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C131" s="28" t="s">
         <v>174</v>
@@ -12178,12 +12517,16 @@
         <f>Y129-Y130</f>
         <v>2272569.4210975193</v>
       </c>
-      <c r="AA131" s="38"/>
-      <c r="AB131" s="54"/>
+      <c r="AA131" s="38" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB131" s="52" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="132" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B132" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C132" s="28" t="s">
         <v>174</v>
@@ -12219,12 +12562,16 @@
         <f>MIN(Y131,Z77)</f>
         <v>0</v>
       </c>
-      <c r="AA132" s="38"/>
-      <c r="AB132" s="54"/>
+      <c r="AA132" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB132" s="52" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="133" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>174</v>
@@ -12288,12 +12635,16 @@
         <f>Z141*Y130</f>
         <v>209877.50332872596</v>
       </c>
-      <c r="AA133" s="38"/>
-      <c r="AB133" s="54"/>
+      <c r="AA133" s="38" t="s">
+        <v>413</v>
+      </c>
+      <c r="AB133" s="52" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B134" s="38" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C134" s="33" t="s">
         <v>163</v>
@@ -12357,8 +12708,12 @@
         <f>Z133+Y132</f>
         <v>209877.50332872596</v>
       </c>
-      <c r="AA134" s="38"/>
-      <c r="AB134" s="54"/>
+      <c r="AA134" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB134" s="52" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="135" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F135" s="15" t="s">
@@ -12378,11 +12733,11 @@
       <c r="W135" s="8"/>
       <c r="Y135" s="8"/>
       <c r="Z135" s="8"/>
-      <c r="AB135" s="54"/>
+      <c r="AB135" s="52"/>
     </row>
     <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B136" s="38" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C136" s="28" t="s">
         <v>174</v>
@@ -12446,13 +12801,15 @@
         <f>Z114/$H$23</f>
         <v>0.39828350178087057</v>
       </c>
-      <c r="AA136" s="38"/>
-      <c r="AB136" s="54">
-        <v>0.5</v>
+      <c r="AA136" s="38" t="s">
+        <v>431</v>
+      </c>
+      <c r="AB136" s="52" t="s">
+        <v>421</v>
       </c>
       <c r="AC136">
         <f>SUM(AB$6:AB136)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD136">
         <v>20</v>
@@ -12460,16 +12817,16 @@
     </row>
     <row r="137" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B137" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C137" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G137" s="4">
         <f>MAX(MIN((G136-$G$17)/$G$18, 1), 0)</f>
@@ -12527,13 +12884,15 @@
         <f>MAX(MIN((Z136-$H$17)/$H$18, 1), 0)</f>
         <v>4.2414629745244618E-2</v>
       </c>
-      <c r="AA137" s="38"/>
-      <c r="AB137" s="54">
-        <v>0.3</v>
+      <c r="AA137" s="39" t="s">
+        <v>430</v>
+      </c>
+      <c r="AB137" s="52" t="s">
+        <v>422</v>
       </c>
       <c r="AC137">
         <f>SUM(AB$6:AB137)</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AD137">
         <v>20</v>
@@ -12542,12 +12901,10 @@
     <row r="138" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B138" s="38"/>
       <c r="AA138" s="38"/>
-      <c r="AB138" s="54">
-        <v>0.2</v>
-      </c>
+      <c r="AB138" s="52"/>
       <c r="AC138">
         <f>SUM(AB$6:AB138)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD138">
         <v>20</v>
@@ -12555,7 +12912,7 @@
     </row>
     <row r="139" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B139" s="38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C139" s="28" t="s">
         <v>174</v>
@@ -12619,13 +12976,15 @@
         <f>Z126*Z137</f>
         <v>209877.50332872596</v>
       </c>
-      <c r="AA139" s="38"/>
-      <c r="AB139" s="54">
-        <v>0.125</v>
+      <c r="AA139" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="AB139" s="52" t="s">
+        <v>425</v>
       </c>
       <c r="AC139">
         <f>SUM(AB$6:AB159)</f>
-        <v>1.125</v>
+        <v>0</v>
       </c>
       <c r="AD139">
         <v>20</v>
@@ -12633,7 +12992,7 @@
     </row>
     <row r="140" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B140" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C140" s="28" t="s">
         <v>174</v>
@@ -12697,12 +13056,16 @@
         <f>Y140</f>
         <v>236958.69160889552</v>
       </c>
-      <c r="AA140" s="38"/>
-      <c r="AB140" s="54"/>
+      <c r="AA140" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="AB140" s="52" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B141" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C141" s="28" t="s">
         <v>174</v>
@@ -12766,15 +13129,19 @@
         <f>Z139/Z140</f>
         <v>0.88571346298253728</v>
       </c>
-      <c r="AA141" s="38"/>
-      <c r="AB141" s="54"/>
+      <c r="AA141" s="38" t="s">
+        <v>428</v>
+      </c>
+      <c r="AB141" s="52" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB142" s="54"/>
+      <c r="AB142" s="52"/>
     </row>
     <row r="143" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F143" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -12790,17 +13157,17 @@
       <c r="W143" s="8"/>
       <c r="Y143" s="8"/>
       <c r="Z143" s="8"/>
-      <c r="AB143" s="54"/>
+      <c r="AB143" s="52"/>
     </row>
     <row r="144" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C144" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G144" s="4">
         <f>(G112 - G133 - G121)*$G$30</f>
@@ -12859,11 +13226,11 @@
         <v>24156.603765901902</v>
       </c>
       <c r="AA144" s="38"/>
-      <c r="AB144" s="54"/>
+      <c r="AB144" s="52"/>
     </row>
     <row r="145" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B145" s="38" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>163</v>
@@ -12925,17 +13292,17 @@
         <v>6039.1509414754755</v>
       </c>
       <c r="AA145" s="38"/>
-      <c r="AB145" s="54"/>
+      <c r="AB145" s="52"/>
     </row>
     <row r="146" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B146" s="38" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F146" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G146" s="4">
         <f>G133*$G21</f>
@@ -12994,7 +13361,7 @@
         <v>52469.375832181489</v>
       </c>
       <c r="AA146" s="38"/>
-      <c r="AB146" s="54"/>
+      <c r="AB146" s="52"/>
     </row>
     <row r="147" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B147" s="38" t="s">
@@ -13063,7 +13430,7 @@
         <v>1864.3672357973865</v>
       </c>
       <c r="AA147" s="38"/>
-      <c r="AB147" s="54"/>
+      <c r="AB147" s="52"/>
     </row>
     <row r="148" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B148" s="38" t="s">
@@ -13132,11 +13499,11 @@
         <v>1353.1913631644886</v>
       </c>
       <c r="AA148" s="38"/>
-      <c r="AB148" s="54"/>
+      <c r="AB148" s="52"/>
     </row>
     <row r="149" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>163</v>
@@ -13198,17 +13565,17 @@
         <v>129.19999999999999</v>
       </c>
       <c r="AA149" s="38"/>
-      <c r="AB149" s="54"/>
+      <c r="AB149" s="52"/>
     </row>
     <row r="150" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB150" s="54"/>
+      <c r="AB150" s="52"/>
     </row>
     <row r="151" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB151" s="54"/>
+      <c r="AB151" s="52"/>
     </row>
     <row r="152" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B152" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G152" s="4">
         <f>G147+G122</f>
@@ -13266,14 +13633,14 @@
         <f>Z147+Z122</f>
         <v>2908.3672357973865</v>
       </c>
-      <c r="AB152" s="54"/>
+      <c r="AB152" s="52"/>
     </row>
     <row r="153" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB153" s="54"/>
+      <c r="AB153" s="52"/>
     </row>
     <row r="154" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B154" s="38" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C154" s="33" t="s">
         <v>163</v>
@@ -13307,7 +13674,7 @@
         <v>247430.57890248077</v>
       </c>
       <c r="AA154" s="38"/>
-      <c r="AB154" s="54"/>
+      <c r="AB154" s="52"/>
     </row>
     <row r="155" spans="2:30" x14ac:dyDescent="0.2">
       <c r="G155" s="4">
@@ -13340,49 +13707,48 @@
       </c>
     </row>
     <row r="160" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB160" s="53">
+      <c r="AB160" s="51">
         <v>0.1225</v>
       </c>
       <c r="AC160">
         <f>SUM(AB$6:AB160)</f>
-        <v>1.2475000000000001</v>
+        <v>0.1225</v>
       </c>
       <c r="AD160">
         <v>20</v>
       </c>
     </row>
     <row r="161" spans="28:30" x14ac:dyDescent="0.2">
-      <c r="AB161" s="53">
+      <c r="AB161" s="51">
         <v>0.12239999999999999</v>
       </c>
       <c r="AC161">
         <f>SUM(AB$6:AB161)</f>
-        <v>1.3699000000000001</v>
+        <v>0.24490000000000001</v>
       </c>
       <c r="AD161">
         <v>20</v>
       </c>
     </row>
     <row r="162" spans="28:30" x14ac:dyDescent="0.2">
-      <c r="AB162" s="53">
+      <c r="AB162" s="51">
         <v>0.12230000000000001</v>
       </c>
       <c r="AC162">
         <f>SUM(AB$6:AB162)</f>
-        <v>1.4922000000000002</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="AD162">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="36">
     <mergeCell ref="B101:B104"/>
     <mergeCell ref="C101:C104"/>
     <mergeCell ref="B49:B52"/>
     <mergeCell ref="C49:C52"/>
     <mergeCell ref="E49:E52"/>
-    <mergeCell ref="B79:B83"/>
     <mergeCell ref="C79:C83"/>
     <mergeCell ref="C86:C89"/>
     <mergeCell ref="B96:B99"/>
@@ -13391,7 +13757,6 @@
     <mergeCell ref="C91:C94"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="C73:C76"/>
-    <mergeCell ref="B86:B89"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="B68:B71"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3412FEB-9A56-694D-B6C0-0872A89E70D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07306AE-55B5-2F40-9E05-17D9F0059831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="500" windowWidth="34560" windowHeight="19560" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="8240" yWindow="760" windowWidth="34560" windowHeight="20060" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="480">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -715,12 +715,6 @@
     <t>vec_frac_biomass_from_conversion_available_for_use</t>
   </si>
   <si>
-    <t>vec_frac_biomass_dead_storage</t>
-  </si>
-  <si>
-    <t>vec_frac_biomass_buffer</t>
-  </si>
-  <si>
     <t>vec_frac_biomass_adjustment_threshold</t>
   </si>
   <si>
@@ -901,21 +895,12 @@
     <t>a^{(y)}_{out}(t)</t>
   </si>
   <si>
-    <t>\check{\alpha}(t)</t>
-  </si>
-  <si>
-    <t>\bar{\alpha}(t)</t>
-  </si>
-  <si>
     <t>\hat{\alpha}(t)</t>
   </si>
   <si>
     <t>\gamma</t>
   </si>
   <si>
-    <t>k_{heav}</t>
-  </si>
-  <si>
     <t>arr_biomass_c_average_bg_stock_in_conversion_targets</t>
   </si>
   <si>
@@ -925,18 +910,9 @@
     <t>arr_biomass_c_bg_lost_decomposition</t>
   </si>
   <si>
-    <t>modification notes</t>
-  </si>
-  <si>
     <t>this has been modified to use a logistic ramp rather than alinear</t>
   </si>
   <si>
-    <t>\overline{B}_0</t>
-  </si>
-  <si>
-    <t>\delta(t)</t>
-  </si>
-  <si>
     <t>A^*(t)</t>
   </si>
   <si>
@@ -961,21 +937,9 @@
     <t>\overline{Y}^*(t, u)</t>
   </si>
   <si>
-    <t>A^{(protected)}(t)</t>
-  </si>
-  <si>
-    <t>a^{(protected)}(t)</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Fraction of biomass that represents dead storage. Is set in SISEPUEDE to be max of exogenous specification and amount implied by average stock in conversion targets (cannot have biomass below transition targets and remain forest).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraction of biomass in buffer zone; dead storage + buffer gives the fractional threshold for slowing removals. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Fractional threshold for stock loss (compared to undisturbed forest levels) below which sequestration declines. </t>
   </si>
   <si>
@@ -985,15 +949,6 @@
     <t>Ratio of below-ground carbon stock to above-ground carbon stock in each forest type.</t>
   </si>
   <si>
-    <t>Area remaining from land use type at beginning of simulation at beginning of time $t$.</t>
-  </si>
-  <si>
-    <t>Area of land use at beginning of time $t$.</t>
-  </si>
-  <si>
-    <t>Total of land converted away from type during time $t$.</t>
-  </si>
-  <si>
     <t>Area of young forest that would be converted away assuming no protection (counterfactual).</t>
   </si>
   <si>
@@ -1006,9 +961,6 @@
     <t>Fraction of biomass in each forest type that's converted to another land use class that is available for use to satisfy fuelwood and harvested wood product demands.</t>
   </si>
   <si>
-    <t>\overline{B}_0\check{\alpha}(t)</t>
-  </si>
-  <si>
     <t>In healthy forest, available stock factor per unit area. Used to determine when average stocks fall below thresholds.</t>
   </si>
   <si>
@@ -1042,81 +994,18 @@
     <t>arr_young_area_by_tp_planted_drops (T x T)   [e.g., col J]</t>
   </si>
   <si>
-    <t>Matrix ($T \times T$) storing how much forest area in each time period (column $u$) has to be dropped due to conversion into young forests. Only applicable if all other secondary forest has been elimnated.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing cumulative area in young forests at time $t$. Used to determine how much area is removed from each young forest area if conversion is applicable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vector ($T$) storing total mass of above-ground biomass in young forests converted in time $t$. </t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing total mass of biomass in young forests converted away in each time period by time period planted. Used to help ensure that earliest plantations are converted first.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing total above-ground mass of biomass preserved in each area of young forest planted by time period planted $u$.</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing total above-ground mass of biomass preserved in each time period.</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing total biomass from conversion that is available to satisfy harvested wood product (HWP) and fuelwood (FW) demands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix ($T \times T$) storing total young biomass that is converted to other (non-forest) land use types by time period planted. </t>
-  </si>
-  <si>
-    <t>Vector ($T$)  storing total young biomass that is converted to other (non-forest) land use types at time $t$.</t>
-  </si>
-  <si>
-    <t>K_{avail}(t, u)</t>
-  </si>
-  <si>
-    <t>k_{avail}(T)</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing how much biomass is available at time $t$ from young forests.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) used to determine whether young biomass is available for harvest. Determined based on number of years of growth required to make biomass available.</t>
-  </si>
-  <si>
-    <t>arr_young_biomass_c_stock_removal_allocation_aux (T x T)   [e.g., col F]</t>
-  </si>
-  <si>
-    <t>arr_young_biomass_c_stock_removal_allocation (T x T)   [e.g., col G]</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing counterfactual for young biomass above-ground stock if untouched at time $t$ for biomass planted at time $u$.</t>
-  </si>
-  <si>
     <t>\overline{Y}_{alloc}(t, u)</t>
   </si>
   <si>
-    <t>Matrix ($T \times T$) storing total above-ground mass of biomas allocated for removal in time $t$ from biomass planted at time $u$.</t>
-  </si>
-  <si>
     <t>\overline{Y}_{alloc\_aux}(t, u)</t>
   </si>
   <si>
-    <t>arr_young_sf_adjusted_by_tp_planted (T x T)   [e.g., col J]</t>
-  </si>
-  <si>
-    <t>arr_young_sf_adjustment_factor (T x T)   [e.g., col I]</t>
-  </si>
-  <si>
     <t>\Psi^{(y)}(t, u)</t>
   </si>
   <si>
-    <t xml:space="preserve">Matrix ($T \times T$) storing the adjustment factor for young forest factors; applied to unadjusted yuong forest sequestration factor $R^{(y)}_0(t, u)$ based on depletion leevels. </t>
-  </si>
-  <si>
     <t>\overline{Y}(t, u)</t>
   </si>
   <si>
-    <t>Matrix ($T \times T$) storing total above-ground biomass stock at time $t$ for young forests planted at time $u$.</t>
-  </si>
-  <si>
     <t>\Delta_0\overline{Y}(t, u)</t>
   </si>
   <si>
@@ -1126,69 +1015,39 @@
     <t>\underline{Y}(t, u)</t>
   </si>
   <si>
-    <t>Matrix ($T \times T$) storing total below-ground biomass stock at time $t$ for young forests planted at time $u$.</t>
+    <t>L</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
   <si>
     <t>D^{(y)}(t, u)</t>
   </si>
   <si>
-    <t>Matrix ($T \times T$) storing the loss of biomass in young forests due to decomposition. Decomposition rates are determined as a function of the NPP curve and an assumption that primary forests are in steady state.</t>
-  </si>
-  <si>
     <t>A^{(y)}(t, u)</t>
   </si>
   <si>
     <t>\hat{A}^{(y)}(t, u)</t>
   </si>
   <si>
-    <t>L^{(y)}(t, u)</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) used in auxialiary calculations for total above-ground mass of biomas allocated for removal in time $t$ from biomass planted at time $u$.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing the sequestration factors (which come from AFOLU NPP curve estimates) for unperturbed young forests by time period planted.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing the adjusted sequestration factors (which come from AFOLU NPP curve estimates) for forests by time period planted. Adjustments are based off of the level of average stock depletion.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times T$) storing how much area of young forest planted in time $t$ remains in time $u$.</t>
-  </si>
-  <si>
     <t>\chi(t)</t>
   </si>
   <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>\overline{M}_0^*</t>
   </si>
   <si>
-    <t>Matrix ($T \times 2$) storing initial (start of simulation) above ground biomass stock.</t>
-  </si>
-  <si>
     <t>\Delta B</t>
   </si>
   <si>
-    <t>Matrix ($T \times 2$) storing sequestration factor in original forests (as adjusted due to degradation).</t>
-  </si>
-  <si>
     <t>\overline{M}_0</t>
   </si>
   <si>
-    <t>Matrix ($T \times 2$) storing above ground biomass stock left from start of simulation if untouched (without degradation).</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) storing biomass stock remaining from forests present at the start of the simulation.</t>
-  </si>
-  <si>
     <t>\overline{\overline{B}}</t>
   </si>
   <si>
-    <t>Matrix ($T \times 2$) storing average (mass per unit area) biomass stock remaining from forests present at the start of the simulation.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) storing average (mass per unit area) biomass stock remaining from forests present at the start of the simulation \emph{excluding} dead storage.</t>
-  </si>
-  <si>
     <t>\overline{y}(t)</t>
   </si>
   <si>
@@ -1198,33 +1057,9 @@
     <t>\underline{m}(t)</t>
   </si>
   <si>
-    <t>Vector ($T$) storing total above-ground biomass stock in young forests at the start of time period $t$.</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing total above-ground biomass stock in all forests at the start of time period $t$.</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing total below-ground biomass stock in all forests at the start of time period $t$.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) storing total mass of biomass from original forests converted away in each time period.</t>
-  </si>
-  <si>
     <t>\Delta_0\overline{b}</t>
   </si>
   <si>
-    <t>Matrix ($T \times 2$) storing average above ground stock contained In land use classes that forests transition into; used to estimate above-ground conversion losses of stock.</t>
-  </si>
-  <si>
-    <t>\overline{G}</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) soring average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
-  </si>
-  <si>
-    <t>\underline{G}</t>
-  </si>
-  <si>
     <t>Vector (length 2) storing nominal sequestration factor (mass of biomass growth per time period) associated with forests. Used in NPP fit from integration target.</t>
   </si>
   <si>
@@ -1246,87 +1081,30 @@
     <t>\overline{b}_{availconv}(t)</t>
   </si>
   <si>
+    <t>r</t>
+  </si>
+  <si>
     <t>r_{conv}(t)</t>
   </si>
   <si>
     <t>Mass of biomass removals from converted land at time $t$.</t>
   </si>
   <si>
-    <t>Row-stochastic matrix ($T \times 2$) storing allocation of removals by forest type (column) at time $t$ (row).</t>
-  </si>
-  <si>
     <t>\Phi_{conv}</t>
   </si>
   <si>
-    <t>A^{(0)}_{avail}</t>
-  </si>
-  <si>
     <t>Matrix storing total biomass available (i.e., excluding dead storage) in original forests by type (column) excluding land converted out at time period $t$. Excludes young forests.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vector ($T$) storing demand for removals from all forests, excluding those from conversions. </t>
-  </si>
-  <si>
-    <t>d_{rmv}</t>
-  </si>
-  <si>
-    <t>u^{(0)}_{rmv}</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing unmet demand for removals from original forests.</t>
-  </si>
-  <si>
-    <t>r^{(0)}_{rmv}</t>
-  </si>
-  <si>
-    <t>r^{(y)}_{rmv}</t>
-  </si>
-  <si>
-    <t>R^{(0)}_{rmv}</t>
-  </si>
-  <si>
-    <t>R_{rmv}</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) storing removals from original forests by type (columns), excluding conversions.</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing removals from young forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
-  </si>
-  <si>
-    <t>Vector ($T$) storing removals from original forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) storing removals from all forests byt ype (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
+    <t>u</t>
   </si>
   <si>
     <t>\overline{\overline{B}}'</t>
   </si>
   <si>
-    <t>A^{(protected)*}(t)</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) giving fraction of original forest stock available when compared to healthy (unperturbed) baseline.</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) giving fraction of removals satisfiable at time $t$ for forest type $v$.</t>
-  </si>
-  <si>
-    <t>\tilde{A}^{(0)}_{avail}</t>
-  </si>
-  <si>
-    <t>\tilde{a}^{(0)}</t>
-  </si>
-  <si>
-    <t>Matrix ($T \times 2$) giving adjusted--based on availability in buffer zone--quantity of biomass available for removals by forest type.</t>
-  </si>
-  <si>
     <t>Vector ($T $) giving adjusted--based on availability in buffer zone--total quantity of biomass available for removals.</t>
   </si>
   <si>
-    <t>Matrix ($T \times 2$) giving allocation of adjusted--based on availability in buffer zone--quantity of biomass available for removals by forest type.</t>
-  </si>
-  <si>
     <t>\Phi_{avail}</t>
   </si>
   <si>
@@ -1336,7 +1114,373 @@
     <t>\Psi^{(0)}_{rmvsat}</t>
   </si>
   <si>
-    <t>S^{(0)}(t, v)</t>
+    <t>\underline{L}_{conv}</t>
+  </si>
+  <si>
+    <t>\tilde{A}^{(y)}(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{L}_{decomp}(t, v)</t>
+  </si>
+  <si>
+    <t>\underline{L}_{decomp}(t, v)</t>
+  </si>
+  <si>
+    <t>\underline{L}_{rmv}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{L}_{conv}(t, v)</t>
+  </si>
+  <si>
+    <t>G(t, v)</t>
+  </si>
+  <si>
+    <t>s_{rmv}(t)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>\overline{\eta}</t>
+  </si>
+  <si>
+    <t>\underline{\eta}</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>\overline{B}^{(0)}</t>
+  </si>
+  <si>
+    <t>\overline{B_{avail}}</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Sort Class</t>
+  </si>
+  <si>
+    <t>z:\chi</t>
+  </si>
+  <si>
+    <t>z:\eta</t>
+  </si>
+  <si>
+    <t>z:\alpha</t>
+  </si>
+  <si>
+    <t>z:\gamma</t>
+  </si>
+  <si>
+    <t>z:\delta</t>
+  </si>
+  <si>
+    <t>z:\Psi</t>
+  </si>
+  <si>
+    <t>z:\Phi</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{avail}(t, u)</t>
+  </si>
+  <si>
+    <t>\overline{B}^{(0)}_{avail}</t>
+  </si>
+  <si>
+    <t>\tilde{\Psi}^{(0)}(t, v)</t>
+  </si>
+  <si>
+    <t>\tilde{b}^{(0)}</t>
+  </si>
+  <si>
+    <t>\tilde{B}^{(0)}_{avail}</t>
+  </si>
+  <si>
+    <t>n_tps_no_withdrawals_new_growth</t>
+  </si>
+  <si>
+    <t>n_{wait}</t>
+  </si>
+  <si>
+    <t>Number (integer) giving number of time periods that must pass after planting a forest to allow withdrawals.</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Total of land converted away from type during time $t$. $A(0)$ is an input vector.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($n_T \times 2$) storing area remaining from land use type at beginning of simulation at beginning of time $t$.  </t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing area of land use at beginning of time $t$. $A(0)$ is an input vector.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing average above ground stock contained In land use classes that forests transition into; used to estimate above-ground conversion losses of stock.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) soring average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing avrage biomass stock per unit area required to be considered forest.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing above ground biomass stock left from start of simulation if untouched (without degradation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($n_T \times 2$) storing adjustment factor for sequestration; responds to stock level compared to steady-state level. </t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing sequestration factor in original forests (as adjusted due to degradation).</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing biomass stock remaining from forests present at the start of the simulation.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing average (mass per unit area) biomass stock remaining from forests present at the start of the simulation.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing average (mass per unit area) biomass stock remaining from forests present at the start of the simulation \emph{excluding} dead storage.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing total mass of biomass from original forests converted away in each time period.</t>
+  </si>
+  <si>
+    <t>Row-stochastic matrix ($n_T \times 2$) storing allocation of removals by forest type (column) at time $t$ (row).</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing removals from original forests by type (columns), excluding conversions.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing removals from all forests byt ype (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving fraction of original forest stock available when compared to healthy (unperturbed) baseline.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving fraction of removals satisfiable at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving adjusted--based on availability in buffer zone--quantity of biomass available for removals by forest type.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving allocation of adjusted--based on availability in buffer zone--quantity of biomass available for removals by forest type.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving total loss of above-ground biomass stock due to decomposition at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving total loss of below-ground biomass stock due to decomposition at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving total loss of below-ground biomass stock due to above-ground removals at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving total loss of above-ground biomass stock due to land use conversion at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving total loss of below-ground biomass stock due to land use conversion at time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) giving total growth of above-ground biomass stock during time $t$ for forest type $v$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing cumulative area in young forests at time $t$. Used to determine how much area is removed from each young forest area if conversion is applicable.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing how much area of young forest planted in time $t$ remains in time $u$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing how much forest area in each time period (column $u$) has to be dropped due to conversion into young forests. Only applicable if all other secondary forest has been elimnated.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing total mass of biomass in young forests converted away in each time period by time period planted. Used to help ensure that earliest plantations are converted first.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing total above-ground mass of biomass preserved in each area of young forest planted by time period planted $u$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($n_T \times n_T$) storing total young biomass that is converted to other (non-forest) land use types by time period planted. </t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing the sequestration factors (which come from AFOLU NPP curve estimates) for unperturbed young forests by time period planted.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing counterfactual for young biomass above-ground stock if untouched at time $t$ for biomass planted at time $u$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) used to determine whether young biomass is available for harvest. Determined based on number of years of growth required to make biomass available.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing total above-ground mass of biomas allocated for removal in time $t$ from biomass planted at time $u$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) used in auxialiary calculations for total above-ground mass of biomas allocated for removal in time $t$ from biomass planted at time $u$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing the adjusted sequestration factors (which come from AFOLU NPP curve estimates) for forests by time period planted. Adjustments are based off of the level of average stock depletion.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing the loss of biomass in young forests due to decomposition. Decomposition rates are determined as a function of the NPP curve and an assumption that primary forests are in steady state.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing total above-ground biomass stock at time $t$ for young forests planted at time $u$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times n_T$) storing total below-ground biomass stock at time $t$ for young forests planted at time $u$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector ($n_T$) storing total mass of above-ground biomass in young forests converted in time $t$. </t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing total above-ground mass of biomass preserved in each time period.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing total biomass from conversion that is available to satisfy harvested wood product (HWP) and fuelwood (FW) demands.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$)  storing total young biomass that is converted to other (non-forest) land use types at time $t$.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing how much biomass is available at time $t$ from young forests.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing total above-ground biomass stock in young forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing total above-ground biomass stock in all forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing total below-ground biomass stock in all forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector ($n_T$) storing demand for removals from all forests, excluding those from conversions. </t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing removals from original forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing unmet demand for removals from original forests.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing removals from young forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) giving total removals supplied.</t>
+  </si>
+  <si>
+    <t>arr_frac_biomass_dead_storage</t>
+  </si>
+  <si>
+    <t>arr_frac_biomass_buffer</t>
+  </si>
+  <si>
+    <t>\check{\alpha}(t, v)</t>
+  </si>
+  <si>
+    <t>\bar{\alpha}(t, v)</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$)  storing fraction of biomass that represents dead storage. Is set in SISEPUEDE to be max of exogenous specification and amount implied by average stock in conversion targets (cannot have biomass below transition targets and remain forest).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($n_T \times 2$) storing fraction of biomass in buffer zone; dead storage + buffer gives the fractional threshold for slowing removals. </t>
+  </si>
+  <si>
+    <t>written</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>a^{(y)}_{prot}(t)</t>
+  </si>
+  <si>
+    <t>A_{prot}(t, v)</t>
+  </si>
+  <si>
+    <t>A_{prot}^*(t, v)</t>
+  </si>
+  <si>
+    <t>\Delta_0\overline{y}(u)</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing the sequestration factors for young forests $u$ time periods after planting.</t>
+  </si>
+  <si>
+    <t>vec_young_sf_curve_specification (T)</t>
+  </si>
+  <si>
+    <t>\tau</t>
+  </si>
+  <si>
+    <t>z:\tau</t>
+  </si>
+  <si>
+    <t>\delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix ($n_T \times n_T$) storing the adjustment factor for young forest factors; applied to unadjusted young forest sequestration factor $R^{(y)}_0(t, u)$ based on depletion levels. </t>
+  </si>
+  <si>
+    <t>arr_young_sf_adjustment_factor (T x T)   [e.g., col J]</t>
+  </si>
+  <si>
+    <t>arr_young_sf_adjusted_by_tp_planted (T x T)   [e.g., col K]</t>
+  </si>
+  <si>
+    <t>arr_young_biomass_c_stock_removal_allocation_aux (T x T)   [e.g., col G]</t>
+  </si>
+  <si>
+    <t>arr_young_biomass_c_stock_removal_allocation (T x T)   [e.g., col H]</t>
+  </si>
+  <si>
+    <t>\overline{y}_{avail}(t)</t>
+  </si>
+  <si>
+    <t>r^{(y)}_{rmv}(t)</t>
+  </si>
+  <si>
+    <t>R^{(0)}_{rmv}(t, v)</t>
+  </si>
+  <si>
+    <t>R_{rmv}(t, v)</t>
+  </si>
+  <si>
+    <t>u^{(0)}_{rmv}(t)</t>
+  </si>
+  <si>
+    <t>r^{(0)}_{rmv}(t)</t>
+  </si>
+  <si>
+    <t>d_{rmv}(t)</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1634,9 +1778,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1644,10 +1785,25 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6791,33 +6947,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F0562-A765-A442-B9DB-CF71D123E451}">
-  <dimension ref="A1:AO162"/>
+  <dimension ref="A1:AO164"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="62.1640625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="14" style="27" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="14" style="27" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" style="23" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="27" style="22" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="44" style="10" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="4" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
     <col min="10" max="11" width="13.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" style="5" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="21.1640625" style="5" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="21.1640625" style="4" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="20" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1640625" style="5" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="12.5" style="4" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
-    <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" style="5" customWidth="1"/>
+    <col min="13" max="14" width="13.33203125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="21.1640625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="13.33203125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" style="5" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="4" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="5" customWidth="1"/>
+    <col min="25" max="26" width="13.33203125" style="4" customWidth="1"/>
     <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
-    <col min="28" max="28" width="64.5" style="51" customWidth="1"/>
-    <col min="29" max="30" width="14.6640625" customWidth="1"/>
+    <col min="28" max="28" width="64.5" style="58" customWidth="1"/>
+    <col min="29" max="29" width="14.6640625" style="59" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" customWidth="1"/>
     <col min="31" max="33" width="14.1640625" customWidth="1"/>
     <col min="34" max="34" width="4.1640625" customWidth="1"/>
     <col min="35" max="35" width="3.33203125" customWidth="1"/>
@@ -6856,7 +7013,8 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="24"/>
-      <c r="AB1" s="53"/>
+      <c r="AB1" s="51"/>
+      <c r="AC1" s="27"/>
     </row>
     <row r="2" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="24"/>
@@ -6893,7 +7051,8 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="24"/>
-      <c r="AB2" s="53"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="24"/>
@@ -6926,7 +7085,8 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="24"/>
-      <c r="AB3" s="53"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="27"/>
     </row>
     <row r="4" spans="1:41" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G4" s="8">
@@ -6963,7 +7123,8 @@
         <v>6</v>
       </c>
       <c r="Z4" s="20"/>
-      <c r="AB4" s="53"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="27"/>
       <c r="AE4" s="42" t="s">
         <v>89</v>
       </c>
@@ -6984,7 +7145,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>457</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7028,13 +7189,16 @@
       </c>
       <c r="Z5" s="41"/>
       <c r="AA5" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB5" s="54" t="s">
-        <v>329</v>
+        <v>312</v>
+      </c>
+      <c r="AB5" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="AC5" s="27" t="s">
+        <v>380</v>
       </c>
       <c r="AD5" s="36" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AE5" s="21" t="s">
         <v>33</v>
@@ -7102,7 +7266,8 @@
       <c r="Z6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB6" s="53"/>
+      <c r="AB6" s="51"/>
+      <c r="AC6" s="27"/>
       <c r="AE6" s="19">
         <v>0</v>
       </c>
@@ -7127,6 +7292,9 @@
       </c>
     </row>
     <row r="7" spans="1:41" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
       </c>
@@ -7137,14 +7305,14 @@
         <v>67</v>
       </c>
       <c r="G7" s="4">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4">
         <v>250000</v>
       </c>
       <c r="J7" s="4">
         <f>G13</f>
-        <v>9950</v>
+        <v>0</v>
       </c>
       <c r="K7" s="4">
         <f>H13</f>
@@ -7152,7 +7320,7 @@
       </c>
       <c r="M7" s="4">
         <f>J13</f>
-        <v>9888</v>
+        <v>0</v>
       </c>
       <c r="N7" s="4">
         <f>K13</f>
@@ -7160,7 +7328,7 @@
       </c>
       <c r="P7" s="4">
         <f>M13</f>
-        <v>9830</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="4">
         <f>N13</f>
@@ -7168,7 +7336,7 @@
       </c>
       <c r="S7" s="4">
         <f>P13</f>
-        <v>9760</v>
+        <v>0</v>
       </c>
       <c r="T7" s="4">
         <f>Q13</f>
@@ -7176,7 +7344,7 @@
       </c>
       <c r="V7" s="4">
         <f>S13</f>
-        <v>9660</v>
+        <v>0</v>
       </c>
       <c r="W7" s="4">
         <f>T13</f>
@@ -7184,17 +7352,20 @@
       </c>
       <c r="Y7" s="4">
         <f>V7-V9</f>
-        <v>9562</v>
+        <v>-98</v>
       </c>
       <c r="Z7" s="4">
         <f>MAX(W7-W9,0)</f>
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="AB7" s="52" t="s">
-        <v>314</v>
+        <v>290</v>
+      </c>
+      <c r="AB7" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC7" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7220,6 +7391,9 @@
       </c>
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
       </c>
@@ -7231,7 +7405,7 @@
       </c>
       <c r="G8" s="4">
         <f>G7</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4">
         <f>H7</f>
@@ -7239,7 +7413,7 @@
       </c>
       <c r="J8" s="4">
         <f>J7</f>
-        <v>9950</v>
+        <v>0</v>
       </c>
       <c r="K8" s="4">
         <f>H8-H9+H12</f>
@@ -7247,7 +7421,7 @@
       </c>
       <c r="M8" s="4">
         <f>M7</f>
-        <v>9888</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4">
         <f>K8-K9+K12</f>
@@ -7255,7 +7429,7 @@
       </c>
       <c r="P8" s="4">
         <f>P7</f>
-        <v>9830</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="4">
         <f>N8-N9+N12</f>
@@ -7263,7 +7437,7 @@
       </c>
       <c r="S8" s="4">
         <f>S7</f>
-        <v>9760</v>
+        <v>0</v>
       </c>
       <c r="T8" s="4">
         <f>Q8-Q9+Q12</f>
@@ -7271,7 +7445,7 @@
       </c>
       <c r="V8" s="4">
         <f>V7</f>
-        <v>9660</v>
+        <v>0</v>
       </c>
       <c r="W8" s="4">
         <f>T8-T9+T12</f>
@@ -7279,17 +7453,20 @@
       </c>
       <c r="Y8" s="4">
         <f>Y7</f>
-        <v>9562</v>
+        <v>-98</v>
       </c>
       <c r="Z8" s="4">
         <f>W8-W9+W12</f>
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="AB8" s="52" t="s">
-        <v>315</v>
+        <v>279</v>
+      </c>
+      <c r="AB8" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC8" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7315,6 +7492,9 @@
       </c>
     </row>
     <row r="9" spans="1:41" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B9" s="38" t="s">
         <v>222</v>
       </c>
@@ -7367,10 +7547,13 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="AB9" s="52" t="s">
-        <v>316</v>
+        <v>281</v>
+      </c>
+      <c r="AB9" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="AC9" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7396,6 +7579,9 @@
       </c>
     </row>
     <row r="10" spans="1:41" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B10" s="38" t="s">
         <v>221</v>
       </c>
@@ -7434,10 +7620,13 @@
         <v>0</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB10" s="52" t="s">
-        <v>317</v>
+        <v>282</v>
+      </c>
+      <c r="AB10" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC10" s="54" t="s">
+        <v>366</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7451,6 +7640,9 @@
       </c>
     </row>
     <row r="11" spans="1:41" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B11" s="38" t="s">
         <v>219</v>
       </c>
@@ -7489,10 +7681,13 @@
         <v>0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="AB11" s="52" t="s">
-        <v>318</v>
+        <v>283</v>
+      </c>
+      <c r="AB11" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC11" s="54" t="s">
+        <v>366</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7506,6 +7701,9 @@
       </c>
     </row>
     <row r="12" spans="1:41" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B12" s="38" t="s">
         <v>220</v>
       </c>
@@ -7537,10 +7735,13 @@
         <v>110</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="AB12" s="52" t="s">
-        <v>319</v>
+        <v>280</v>
+      </c>
+      <c r="AB12" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="AC12" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7554,6 +7755,9 @@
       </c>
     </row>
     <row r="13" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B13" s="38" t="s">
         <v>158</v>
       </c>
@@ -7565,7 +7769,7 @@
       </c>
       <c r="G13" s="4">
         <f>MAX(G7-G9,0)</f>
-        <v>9950</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4">
         <f>MAX(H7-H9,0)</f>
@@ -7573,7 +7777,7 @@
       </c>
       <c r="J13" s="4">
         <f>MAX(J7-J9,0)</f>
-        <v>9888</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4">
         <f>MAX(K7-K9,0)</f>
@@ -7581,7 +7785,7 @@
       </c>
       <c r="M13" s="4">
         <f>MAX(M7-M9,0)</f>
-        <v>9830</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4">
         <f>MAX(N7-N9,0)</f>
@@ -7589,7 +7793,7 @@
       </c>
       <c r="P13" s="4">
         <f>MAX(P7-P9,0)</f>
-        <v>9760</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="4">
         <f>MAX(Q7-Q9,0)</f>
@@ -7597,7 +7801,7 @@
       </c>
       <c r="S13" s="4">
         <f>MAX(S7-S9,0)</f>
-        <v>9660</v>
+        <v>0</v>
       </c>
       <c r="T13" s="4">
         <f>MAX(T7-T9,0)</f>
@@ -7605,7 +7809,7 @@
       </c>
       <c r="V13" s="4">
         <f>MAX(V7-V9,0)</f>
-        <v>9562</v>
+        <v>0</v>
       </c>
       <c r="W13" s="4">
         <f>MAX(W7-W9,0)</f>
@@ -7613,23 +7817,29 @@
       </c>
       <c r="Y13" s="4">
         <f>MAX(Y7-Y9,0)</f>
-        <v>9464</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="4">
         <f>MAX(Z7-Z9,0)</f>
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="AB13" s="52" t="s">
-        <v>308</v>
+        <v>292</v>
+      </c>
+      <c r="AB13" s="53" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC13" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
       <c r="AG13" s="19"/>
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B14" s="38" t="s">
         <v>223</v>
       </c>
@@ -7661,10 +7871,13 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="AB14" s="52" t="s">
-        <v>320</v>
+        <v>329</v>
+      </c>
+      <c r="AB14" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="AC14" s="54" t="s">
+        <v>381</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7678,17 +7891,20 @@
       </c>
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B15" s="38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -7733,20 +7949,28 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="AB15" s="52" t="s">
-        <v>390</v>
+        <v>368</v>
+      </c>
+      <c r="AB15" s="53" t="s">
+        <v>400</v>
+      </c>
+      <c r="AC15" s="54" t="s">
+        <v>382</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
       <c r="AG15" s="19"/>
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B16" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="C16" s="31"/>
+        <v>286</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>162</v>
+      </c>
       <c r="G16" s="4">
         <f>G15*0.187</f>
         <v>0.93500000000000005</v>
@@ -7804,24 +8028,30 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="AB16" s="52" t="s">
-        <v>392</v>
+        <v>369</v>
+      </c>
+      <c r="AB16" s="53" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC16" s="54" t="s">
+        <v>382</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
       <c r="AG16" s="19"/>
     </row>
-    <row r="17" spans="2:33" ht="51" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="51" x14ac:dyDescent="0.2">
+      <c r="A17" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B17" s="38" t="s">
-        <v>224</v>
+        <v>451</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G17" s="4">
         <v>0.33057704999999998</v>
@@ -7830,10 +8060,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="AB17" s="52" t="s">
-        <v>309</v>
+        <v>453</v>
+      </c>
+      <c r="AB17" s="53" t="s">
+        <v>455</v>
+      </c>
+      <c r="AC17" s="54" t="s">
+        <v>383</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -7846,9 +8079,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:33" ht="34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B18" s="38" t="s">
-        <v>225</v>
+        <v>452</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
@@ -7866,10 +8102,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="AB18" s="52" t="s">
-        <v>310</v>
+        <v>454</v>
+      </c>
+      <c r="AB18" s="53" t="s">
+        <v>456</v>
+      </c>
+      <c r="AC18" s="54" t="s">
+        <v>383</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -7882,9 +8121,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:33" ht="51" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B19" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>162</v>
@@ -7897,10 +8139,13 @@
         <v>0.67</v>
       </c>
       <c r="AA19" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB19" s="52" t="s">
-        <v>311</v>
+        <v>284</v>
+      </c>
+      <c r="AB19" s="53" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC19" s="54" t="s">
+        <v>383</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -7913,9 +8158,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B20" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>162</v>
@@ -7930,10 +8178,13 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="AB20" s="52" t="s">
-        <v>312</v>
+        <v>371</v>
+      </c>
+      <c r="AB20" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC20" s="54" t="s">
+        <v>370</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -7946,9 +8197,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B21" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>162</v>
@@ -7963,18 +8217,24 @@
         <v>0.25</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="AB21" s="52" t="s">
-        <v>313</v>
+        <v>285</v>
+      </c>
+      <c r="AB21" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="AC21" s="55" t="s">
+        <v>384</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
       <c r="AG21" s="19"/>
     </row>
-    <row r="22" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B22" s="38" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>174</v>
@@ -7991,9 +8251,14 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="AB22" s="52"/>
+        <v>465</v>
+      </c>
+      <c r="AB22" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC22" s="54" t="s">
+        <v>466</v>
+      </c>
       <c r="AE22" s="19">
         <v>12</v>
       </c>
@@ -8005,9 +8270,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B23" s="38" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>174</v>
@@ -8024,10 +8292,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="AB23" s="52" t="s">
-        <v>322</v>
+        <v>372</v>
+      </c>
+      <c r="AB23" s="53" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC23" s="54" t="s">
+        <v>370</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -8040,8 +8311,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="AB24" s="53"/>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB24" s="51"/>
+      <c r="AC24" s="54"/>
       <c r="AE24" s="19">
         <v>12</v>
       </c>
@@ -8053,7 +8325,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B25" s="38" t="s">
         <v>159</v>
       </c>
@@ -8106,10 +8381,13 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="AB25" s="52" t="s">
-        <v>323</v>
+        <v>460</v>
+      </c>
+      <c r="AB25" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="AC25" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE25" s="19">
         <v>10</v>
@@ -8122,9 +8400,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B26" s="38" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>163</v>
@@ -8161,10 +8442,13 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="AB26" s="52" t="s">
-        <v>324</v>
+        <v>459</v>
+      </c>
+      <c r="AB26" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC26" s="54" t="s">
+        <v>366</v>
       </c>
       <c r="AE26" s="19">
         <v>6</v>
@@ -8177,7 +8461,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B27" s="38" t="s">
         <v>160</v>
       </c>
@@ -8189,7 +8476,7 @@
       </c>
       <c r="G27" s="4">
         <f>MIN(G13,G25)</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4">
         <f>MIN(H13,H25)</f>
@@ -8197,7 +8484,7 @@
       </c>
       <c r="J27" s="4">
         <f>MIN(J13,J25)</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4">
         <f>MIN(K13,K25)</f>
@@ -8205,7 +8492,7 @@
       </c>
       <c r="M27" s="4">
         <f>MIN(M13,M25)</f>
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="N27" s="4">
         <f>MIN(N13,N25)</f>
@@ -8213,7 +8500,7 @@
       </c>
       <c r="P27" s="4">
         <f>MIN(P13,P25)</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="4">
         <f>MIN(Q13,Q25)</f>
@@ -8221,7 +8508,7 @@
       </c>
       <c r="S27" s="4">
         <f>MIN(S13,S25)</f>
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="T27" s="4">
         <f>MIN(T13,T25)</f>
@@ -8229,7 +8516,7 @@
       </c>
       <c r="V27" s="4">
         <f>MIN(V13,V25)</f>
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="W27" s="4">
         <f>MIN(W13,W25)</f>
@@ -8237,17 +8524,20 @@
       </c>
       <c r="Y27" s="4">
         <f>MIN(Y13,Y25)</f>
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="4">
         <f>MIN(Z13,Z25)</f>
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>420</v>
-      </c>
-      <c r="AB27" s="52" t="s">
-        <v>325</v>
+        <v>461</v>
+      </c>
+      <c r="AB27" s="53" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC27" s="54" t="s">
+        <v>365</v>
       </c>
       <c r="AE27" s="19">
         <v>3</v>
@@ -8260,7 +8550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="F28" s="15" t="s">
         <v>169</v>
       </c>
@@ -8278,7 +8568,8 @@
       <c r="W28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
-      <c r="AB28" s="53"/>
+      <c r="AB28" s="51"/>
+      <c r="AC28" s="54"/>
       <c r="AE28" s="19">
         <v>1.8</v>
       </c>
@@ -8290,9 +8581,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B29" s="38" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>162</v>
@@ -8310,15 +8604,21 @@
         <v>0.92</v>
       </c>
       <c r="AA29" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="AB29" s="52" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="30" spans="2:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+      <c r="AB29" s="53" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC29" s="54" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B30" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>174</v>
@@ -8340,17 +8640,21 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="AB30" s="52" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="31" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+      <c r="AB30" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="AC30" s="54" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="26"/>
-      <c r="AB31" s="53"/>
-    </row>
-    <row r="32" spans="2:33" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="54"/>
+    </row>
+    <row r="32" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="F32" s="15" t="s">
         <v>56</v>
       </c>
@@ -8368,9 +8672,13 @@
       <c r="W32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
-      <c r="AB32" s="53"/>
-    </row>
-    <row r="33" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="54"/>
+    </row>
+    <row r="33" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B33" s="38" t="s">
         <v>168</v>
       </c>
@@ -8402,16 +8710,20 @@
         <v>2520000</v>
       </c>
       <c r="AA33" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="AB33" s="52" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB34" s="53"/>
-    </row>
-    <row r="35" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+      <c r="AB33" s="53" t="s">
+        <v>311</v>
+      </c>
+      <c r="AC33" s="54" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB34" s="51"/>
+      <c r="AC34" s="54"/>
+    </row>
+    <row r="35" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
         <v>57</v>
       </c>
@@ -8429,9 +8741,10 @@
       <c r="W35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
-      <c r="AB35" s="53"/>
-    </row>
-    <row r="36" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB35" s="51"/>
+      <c r="AC35" s="54"/>
+    </row>
+    <row r="36" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F36" s="15" t="s">
         <v>139</v>
       </c>
@@ -8451,12 +8764,13 @@
       <c r="P36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB36" s="53"/>
+      <c r="AB36" s="51"/>
+      <c r="AC36" s="54"/>
       <c r="AD36" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B37" s="24" t="s">
         <v>179</v>
       </c>
@@ -8508,11 +8822,15 @@
       <c r="Z37" s="4">
         <v>0</v>
       </c>
-      <c r="AB37" s="53"/>
-    </row>
-    <row r="38" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB37" s="51"/>
+      <c r="AC37" s="54"/>
+    </row>
+    <row r="38" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B38" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="C38" s="44" t="s">
         <v>174</v>
@@ -8600,15 +8918,21 @@
         <v>85</v>
       </c>
       <c r="AA38" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB38" s="52" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+      <c r="AB38" s="53" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC38" s="54" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B39" s="38" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="C39" s="44"/>
       <c r="F39" s="14" t="s">
@@ -8693,15 +9017,21 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB39" s="53" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC39" s="54" t="s">
         <v>365</v>
       </c>
-      <c r="AB39" s="52" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="40" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B40" s="38" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="C40" s="44"/>
       <c r="F40" s="14" t="s">
@@ -8785,13 +9115,16 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB40" s="52" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="41" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+      <c r="AB40" s="53" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC40" s="54" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B41" s="38"/>
       <c r="C41" s="44"/>
       <c r="F41" s="14" t="s">
@@ -8874,15 +9207,20 @@
         <v>43</v>
       </c>
       <c r="AA41" s="38"/>
-      <c r="AB41" s="52"/>
-    </row>
-    <row r="42" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB41" s="53"/>
+      <c r="AC41" s="54"/>
+    </row>
+    <row r="42" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB42" s="53"/>
-    </row>
-    <row r="43" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB42" s="51"/>
+      <c r="AC42" s="54"/>
+    </row>
+    <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A43" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B43" s="46" t="s">
         <v>189</v>
       </c>
@@ -8920,13 +9258,16 @@
         <v>0</v>
       </c>
       <c r="AA43" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="AB43" s="52" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="44" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+      <c r="AB43" s="53" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC43" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B44" s="46"/>
       <c r="C44" s="44"/>
       <c r="F44" s="14" t="s">
@@ -8960,9 +9301,10 @@
         <v>0</v>
       </c>
       <c r="AA44" s="38"/>
-      <c r="AB44" s="52"/>
-    </row>
-    <row r="45" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="54"/>
+    </row>
+    <row r="45" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B45" s="46"/>
       <c r="C45" s="44"/>
       <c r="F45" s="14" t="s">
@@ -8996,9 +9338,10 @@
         <v>0</v>
       </c>
       <c r="AA45" s="38"/>
-      <c r="AB45" s="52"/>
-    </row>
-    <row r="46" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB45" s="53"/>
+      <c r="AC45" s="54"/>
+    </row>
+    <row r="46" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B46" s="46"/>
       <c r="C46" s="44"/>
       <c r="F46" s="14" t="s">
@@ -9032,9 +9375,10 @@
         <v>0</v>
       </c>
       <c r="AA46" s="38"/>
-      <c r="AB46" s="52"/>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AB46" s="53"/>
+      <c r="AC46" s="54"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B47" s="38" t="s">
         <v>190</v>
       </c>
@@ -9071,30 +9415,34 @@
         <v>0</v>
       </c>
       <c r="AA47" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB47" s="52" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="48" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+      <c r="AB47" s="53" t="s">
+        <v>438</v>
+      </c>
+      <c r="AC47" s="54" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F48" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB48" s="53"/>
-    </row>
-    <row r="49" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB48" s="51"/>
+      <c r="AC48" s="54"/>
+    </row>
+    <row r="49" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B49" s="46" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>174</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H49" s="4">
         <f>MIN(H43,H$15*G38)</f>
@@ -9125,18 +9473,21 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="AB49" s="52" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="50" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+      <c r="AB49" s="53" t="s">
+        <v>427</v>
+      </c>
+      <c r="AC49" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B50" s="46"/>
       <c r="C50" s="44"/>
       <c r="E50" s="40"/>
       <c r="F50" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H50" s="4">
         <f>MIN(H44,H$15*G39)</f>
@@ -9167,14 +9518,15 @@
         <v>0</v>
       </c>
       <c r="AA50" s="38"/>
-      <c r="AB50" s="52"/>
-    </row>
-    <row r="51" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB50" s="53"/>
+      <c r="AC50" s="54"/>
+    </row>
+    <row r="51" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B51" s="46"/>
       <c r="C51" s="44"/>
       <c r="E51" s="40"/>
       <c r="F51" s="14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H51" s="4">
         <f>MIN(H45,H$15*G40)</f>
@@ -9205,14 +9557,15 @@
         <v>0</v>
       </c>
       <c r="AA51" s="38"/>
-      <c r="AB51" s="52"/>
-    </row>
-    <row r="52" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB51" s="53"/>
+      <c r="AC51" s="54"/>
+    </row>
+    <row r="52" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B52" s="46"/>
       <c r="C52" s="44"/>
       <c r="E52" s="40"/>
       <c r="F52" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H52" s="4">
         <f>MIN(H46,H$15*G41)</f>
@@ -9243,11 +9596,12 @@
         <v>0</v>
       </c>
       <c r="AA52" s="38"/>
-      <c r="AB52" s="52"/>
-    </row>
-    <row r="53" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB52" s="53"/>
+      <c r="AC52" s="54"/>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B53" s="38" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C53" s="28" t="s">
         <v>174</v>
@@ -9282,15 +9636,18 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>397</v>
-      </c>
-      <c r="AB53" s="52" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="54" spans="2:28" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+      <c r="AB53" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC53" s="54" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B54" s="38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C54" s="28"/>
       <c r="F54" s="14"/>
@@ -9323,17 +9680,21 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>396</v>
-      </c>
-      <c r="AB54" s="52" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="55" spans="2:28" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+      <c r="AB54" s="53" t="s">
+        <v>440</v>
+      </c>
+      <c r="AC54" s="54" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F55" s="14"/>
-      <c r="AB55" s="52"/>
-    </row>
-    <row r="56" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB55" s="53"/>
+      <c r="AC55" s="54"/>
+    </row>
+    <row r="56" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B56" s="46" t="s">
         <v>191</v>
       </c>
@@ -9372,13 +9733,16 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="AB56" s="52" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="57" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="AB56" s="53" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC56" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B57" s="46"/>
       <c r="C57" s="44"/>
       <c r="F57" s="14" t="s">
@@ -9413,9 +9777,10 @@
         <v>0</v>
       </c>
       <c r="AA57" s="38"/>
-      <c r="AB57" s="52"/>
-    </row>
-    <row r="58" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB57" s="53"/>
+      <c r="AC57" s="54"/>
+    </row>
+    <row r="58" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B58" s="46"/>
       <c r="C58" s="44"/>
       <c r="F58" s="14" t="s">
@@ -9450,9 +9815,10 @@
         <v>0</v>
       </c>
       <c r="AA58" s="38"/>
-      <c r="AB58" s="52"/>
-    </row>
-    <row r="59" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB58" s="53"/>
+      <c r="AC58" s="54"/>
+    </row>
+    <row r="59" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B59" s="46"/>
       <c r="C59" s="44"/>
       <c r="F59" s="14" t="s">
@@ -9487,9 +9853,10 @@
         <v>0</v>
       </c>
       <c r="AA59" s="38"/>
-      <c r="AB59" s="52"/>
-    </row>
-    <row r="60" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB59" s="53"/>
+      <c r="AC59" s="54"/>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B60" s="38" t="s">
         <v>192</v>
       </c>
@@ -9526,17 +9893,24 @@
         <v>0</v>
       </c>
       <c r="AA60" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="AB60" s="52" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="2:28" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+      <c r="AB60" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC60" s="54" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F61" s="14"/>
-      <c r="AB61" s="52"/>
-    </row>
-    <row r="62" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB61" s="53"/>
+      <c r="AC61" s="54"/>
+    </row>
+    <row r="62" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B62" s="46" t="s">
         <v>178</v>
       </c>
@@ -9575,13 +9949,16 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="AB62" s="52" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="63" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+      <c r="AB62" s="53" t="s">
+        <v>429</v>
+      </c>
+      <c r="AC62" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B63" s="46"/>
       <c r="C63" s="44"/>
       <c r="F63" s="14" t="s">
@@ -9614,9 +9991,10 @@
         <v>0.36</v>
       </c>
       <c r="AA63" s="38"/>
-      <c r="AB63" s="52"/>
-    </row>
-    <row r="64" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB63" s="53"/>
+      <c r="AC63" s="54"/>
+    </row>
+    <row r="64" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B64" s="46"/>
       <c r="C64" s="44"/>
       <c r="F64" s="14" t="s">
@@ -9648,9 +10026,10 @@
         <v>0.2</v>
       </c>
       <c r="AA64" s="38"/>
-      <c r="AB64" s="52"/>
-    </row>
-    <row r="65" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB64" s="53"/>
+      <c r="AC64" s="54"/>
+    </row>
+    <row r="65" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B65" s="46"/>
       <c r="C65" s="44"/>
       <c r="F65" s="14" t="s">
@@ -9681,21 +10060,40 @@
         <v>0.12</v>
       </c>
       <c r="AA65" s="38"/>
-      <c r="AB65" s="52"/>
-    </row>
-    <row r="66" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB65" s="53"/>
+      <c r="AC65" s="54"/>
+    </row>
+    <row r="66" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="A66" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="B66" s="38" t="s">
+        <v>464</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>162</v>
+      </c>
       <c r="F66" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="AB66" s="52"/>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AA66" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="AB66" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="AC66" s="54" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
       <c r="F67" s="14"/>
-      <c r="AB67" s="52"/>
-    </row>
-    <row r="68" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB67" s="53"/>
+      <c r="AC67" s="54"/>
+    </row>
+    <row r="68" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B68" s="46" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C68" s="44" t="s">
         <v>174</v>
@@ -9732,13 +10130,16 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="AB68" s="52" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="69" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+      <c r="AB68" s="53" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC68" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B69" s="46"/>
       <c r="C69" s="44"/>
       <c r="F69" s="14" t="s">
@@ -9769,9 +10170,10 @@
         <v>59.120937045501634</v>
       </c>
       <c r="AA69" s="38"/>
-      <c r="AB69" s="52"/>
-    </row>
-    <row r="70" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB69" s="53"/>
+      <c r="AC69" s="54"/>
+    </row>
+    <row r="70" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B70" s="46"/>
       <c r="C70" s="44"/>
       <c r="E70" s="40"/>
@@ -9799,9 +10201,10 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA70" s="38"/>
-      <c r="AB70" s="52"/>
-    </row>
-    <row r="71" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB70" s="53"/>
+      <c r="AC70" s="54"/>
+    </row>
+    <row r="71" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B71" s="46"/>
       <c r="C71" s="44"/>
       <c r="E71" s="40"/>
@@ -9829,16 +10232,21 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA71" s="38"/>
-      <c r="AB71" s="52"/>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AB71" s="53"/>
+      <c r="AC71" s="54"/>
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
       <c r="E72" s="40"/>
       <c r="F72" s="14"/>
-      <c r="AB72" s="52"/>
-    </row>
-    <row r="73" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB72" s="53"/>
+      <c r="AC72" s="54"/>
+    </row>
+    <row r="73" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B73" s="46" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C73" s="44" t="s">
         <v>174</v>
@@ -9874,13 +10282,16 @@
         <v>0</v>
       </c>
       <c r="AA73" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="AB73" s="52" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="74" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+      <c r="AB73" s="53" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC73" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B74" s="46"/>
       <c r="C74" s="44"/>
       <c r="F74" s="14" t="s">
@@ -9914,9 +10325,10 @@
         <v>0</v>
       </c>
       <c r="AA74" s="38"/>
-      <c r="AB74" s="52"/>
-    </row>
-    <row r="75" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB74" s="53"/>
+      <c r="AC74" s="54"/>
+    </row>
+    <row r="75" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B75" s="46"/>
       <c r="C75" s="44"/>
       <c r="E75" s="40" t="s">
@@ -9953,9 +10365,10 @@
         <v>0</v>
       </c>
       <c r="AA75" s="38"/>
-      <c r="AB75" s="52"/>
-    </row>
-    <row r="76" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB75" s="53"/>
+      <c r="AC75" s="54"/>
+    </row>
+    <row r="76" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="B76" s="46"/>
       <c r="C76" s="44"/>
       <c r="E76" s="40"/>
@@ -9990,11 +10403,15 @@
         <v>0</v>
       </c>
       <c r="AA76" s="38"/>
-      <c r="AB76" s="52"/>
-    </row>
-    <row r="77" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB76" s="53"/>
+      <c r="AC76" s="54"/>
+    </row>
+    <row r="77" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="A77" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B77" s="38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C77" s="28" t="s">
         <v>174</v>
@@ -10031,19 +10448,23 @@
         <v>0</v>
       </c>
       <c r="AA77" s="56" t="s">
-        <v>343</v>
-      </c>
-      <c r="AB77" s="52" t="s">
-        <v>344</v>
+        <v>473</v>
+      </c>
+      <c r="AB77" s="53" t="s">
+        <v>442</v>
+      </c>
+      <c r="AC77" s="54" t="s">
+        <v>376</v>
       </c>
       <c r="AF77" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="78" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="E78" s="40"/>
       <c r="F78" s="14"/>
-      <c r="AB78" s="52"/>
+      <c r="AB78" s="53"/>
+      <c r="AC78" s="54"/>
       <c r="AD78" t="s">
         <v>85</v>
       </c>
@@ -10051,9 +10472,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="79" spans="2:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B79" s="37" t="s">
-        <v>347</v>
+        <v>472</v>
       </c>
       <c r="C79" s="44" t="s">
         <v>174</v>
@@ -10083,18 +10507,24 @@
         <v>0</v>
       </c>
       <c r="AA79" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="AB79" s="52" t="s">
-        <v>350</v>
+        <v>317</v>
+      </c>
+      <c r="AB79" s="53" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC79" s="54" t="s">
+        <v>375</v>
       </c>
       <c r="AD79" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="A80" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B80" s="37" t="s">
-        <v>346</v>
+        <v>471</v>
       </c>
       <c r="C80" s="44"/>
       <c r="F80" s="14" t="s">
@@ -10157,14 +10587,17 @@
         <v>0</v>
       </c>
       <c r="AA80" s="38" t="s">
-        <v>351</v>
-      </c>
-      <c r="AB80" s="52" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="81" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="55"/>
+        <v>318</v>
+      </c>
+      <c r="AB80" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC80" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B81" s="52"/>
       <c r="C81" s="44"/>
       <c r="E81" s="22">
         <v>0</v>
@@ -10229,10 +10662,11 @@
         <v>0</v>
       </c>
       <c r="AA81" s="37"/>
-      <c r="AB81" s="52"/>
-    </row>
-    <row r="82" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="55"/>
+      <c r="AB81" s="53"/>
+      <c r="AC81" s="54"/>
+    </row>
+    <row r="82" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B82" s="52"/>
       <c r="C82" s="44"/>
       <c r="E82" s="22">
         <v>1</v>
@@ -10297,10 +10731,11 @@
         <v>0</v>
       </c>
       <c r="AA82" s="37"/>
-      <c r="AB82" s="52"/>
-    </row>
-    <row r="83" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="55"/>
+      <c r="AB82" s="53"/>
+      <c r="AC82" s="54"/>
+    </row>
+    <row r="83" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B83" s="52"/>
       <c r="C83" s="44"/>
       <c r="E83" s="22">
         <v>2</v>
@@ -10365,16 +10800,18 @@
         <v>0</v>
       </c>
       <c r="AA83" s="37"/>
-      <c r="AB83" s="52"/>
-    </row>
-    <row r="84" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB83" s="53"/>
+      <c r="AC83" s="54"/>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
       <c r="E84" s="22">
         <v>3</v>
       </c>
       <c r="F84" s="14"/>
-      <c r="AB84" s="52"/>
-    </row>
-    <row r="85" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB84" s="53"/>
+      <c r="AC84" s="54"/>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F85" s="14"/>
       <c r="J85" s="4" t="s">
         <v>136</v>
@@ -10394,11 +10831,15 @@
       <c r="Y85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="AB85" s="52"/>
-    </row>
-    <row r="86" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB85" s="53"/>
+      <c r="AC85" s="54"/>
+    </row>
+    <row r="86" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A86" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B86" s="37" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="C86" s="44" t="s">
         <v>174</v>
@@ -10459,15 +10900,21 @@
         <v>0.6</v>
       </c>
       <c r="AA86" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB86" s="52" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="87" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+      <c r="AB86" s="53" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC86" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A87" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B87" s="37" t="s">
-        <v>353</v>
+        <v>469</v>
       </c>
       <c r="C87" s="44"/>
       <c r="F87" s="14" t="s">
@@ -10526,13 +10973,16 @@
         <v>0.36</v>
       </c>
       <c r="AA87" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="AB87" s="52" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="88" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+      <c r="AB87" s="53" t="s">
+        <v>468</v>
+      </c>
+      <c r="AC87" s="54" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B88" s="37"/>
       <c r="C88" s="44"/>
       <c r="F88" s="14" t="s">
@@ -10591,10 +11041,11 @@
         <v>0.2</v>
       </c>
       <c r="AA88" s="37"/>
-      <c r="AB88" s="52"/>
-    </row>
-    <row r="89" spans="2:28" ht="17" x14ac:dyDescent="0.2">
-      <c r="B89" s="55"/>
+      <c r="AB88" s="53"/>
+      <c r="AC88" s="54"/>
+    </row>
+    <row r="89" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B89" s="52"/>
       <c r="C89" s="44"/>
       <c r="F89" s="14" t="s">
         <v>134</v>
@@ -10652,13 +11103,15 @@
         <v>0.12</v>
       </c>
       <c r="AA89" s="37"/>
-      <c r="AB89" s="52"/>
-    </row>
-    <row r="90" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB89" s="53"/>
+      <c r="AC89" s="54"/>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F90" s="14"/>
-      <c r="AB90" s="52"/>
-    </row>
-    <row r="91" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB90" s="53"/>
+      <c r="AC90" s="54"/>
+    </row>
+    <row r="91" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B91" s="45" t="s">
         <v>202</v>
       </c>
@@ -10697,13 +11150,16 @@
         <v>9.8621113109027395E-2</v>
       </c>
       <c r="AA91" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="AB91" s="52" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="92" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+      <c r="AB91" s="53" t="s">
+        <v>435</v>
+      </c>
+      <c r="AC91" s="54" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B92" s="45"/>
       <c r="C92" s="44"/>
       <c r="F92" s="14" t="s">
@@ -10738,9 +11194,10 @@
         <v>4.7678726762454618E-2</v>
       </c>
       <c r="AA92" s="37"/>
-      <c r="AB92" s="52"/>
-    </row>
-    <row r="93" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB92" s="53"/>
+      <c r="AC92" s="54"/>
+    </row>
+    <row r="93" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B93" s="45"/>
       <c r="C93" s="44"/>
       <c r="F93" s="14" t="s">
@@ -10775,9 +11232,10 @@
         <v>2.5983329604301563E-2</v>
       </c>
       <c r="AA93" s="37"/>
-      <c r="AB93" s="52"/>
-    </row>
-    <row r="94" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB93" s="53"/>
+      <c r="AC93" s="54"/>
+    </row>
+    <row r="94" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B94" s="45"/>
       <c r="C94" s="44"/>
       <c r="F94" s="14" t="s">
@@ -10812,13 +11270,18 @@
         <v>4.049540093E-3</v>
       </c>
       <c r="AA94" s="37"/>
-      <c r="AB94" s="52"/>
-    </row>
-    <row r="95" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB94" s="53"/>
+      <c r="AC94" s="54"/>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F95" s="14"/>
-      <c r="AB95" s="52"/>
-    </row>
-    <row r="96" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB95" s="53"/>
+      <c r="AC95" s="54"/>
+    </row>
+    <row r="96" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A96" s="19" t="s">
+        <v>458</v>
+      </c>
       <c r="B96" s="45" t="s">
         <v>207</v>
       </c>
@@ -10857,13 +11320,16 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA96" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="AB96" s="52" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="97" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+      <c r="AB96" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC96" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="97" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B97" s="45"/>
       <c r="C97" s="44"/>
       <c r="F97" s="14" t="s">
@@ -10898,9 +11364,10 @@
         <v>59.120937045501627</v>
       </c>
       <c r="AA97" s="37"/>
-      <c r="AB97" s="52"/>
-    </row>
-    <row r="98" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB97" s="53"/>
+      <c r="AC97" s="54"/>
+    </row>
+    <row r="98" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B98" s="45"/>
       <c r="C98" s="44"/>
       <c r="F98" s="14" t="s">
@@ -10935,9 +11402,10 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA98" s="37"/>
-      <c r="AB98" s="52"/>
-    </row>
-    <row r="99" spans="2:28" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB98" s="53"/>
+      <c r="AC98" s="54"/>
+    </row>
+    <row r="99" spans="2:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="45"/>
       <c r="C99" s="44"/>
       <c r="F99" s="14" t="s">
@@ -10972,14 +11440,16 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA99" s="37"/>
-      <c r="AB99" s="52"/>
-    </row>
-    <row r="100" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB99" s="53"/>
+      <c r="AC99" s="54"/>
+    </row>
+    <row r="100" spans="2:29" x14ac:dyDescent="0.2">
       <c r="E100" s="26"/>
       <c r="F100" s="14"/>
-      <c r="AB100" s="52"/>
-    </row>
-    <row r="101" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB100" s="53"/>
+      <c r="AC100" s="54"/>
+    </row>
+    <row r="101" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B101" s="45" t="s">
         <v>208</v>
       </c>
@@ -11019,13 +11489,16 @@
         <v>28.429343624434111</v>
       </c>
       <c r="AA101" s="38" t="s">
-        <v>360</v>
-      </c>
-      <c r="AB101" s="52" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="102" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+      <c r="AB101" s="53" t="s">
+        <v>437</v>
+      </c>
+      <c r="AC101" s="54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="102" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B102" s="45"/>
       <c r="C102" s="44"/>
       <c r="E102" s="26"/>
@@ -11061,9 +11534,10 @@
         <v>14.780234261375407</v>
       </c>
       <c r="AA102" s="37"/>
-      <c r="AB102" s="52"/>
-    </row>
-    <row r="103" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB102" s="53"/>
+      <c r="AC102" s="54"/>
+    </row>
+    <row r="103" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B103" s="45"/>
       <c r="C103" s="44"/>
       <c r="E103" s="26"/>
@@ -11099,9 +11573,10 @@
         <v>8.7309770345259246</v>
       </c>
       <c r="AA103" s="37"/>
-      <c r="AB103" s="52"/>
-    </row>
-    <row r="104" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB103" s="53"/>
+      <c r="AC103" s="54"/>
+    </row>
+    <row r="104" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B104" s="45"/>
       <c r="C104" s="44"/>
       <c r="E104" s="26"/>
@@ -11137,25 +11612,28 @@
         <v>1.93381883997675</v>
       </c>
       <c r="AA104" s="37"/>
-      <c r="AB104" s="52"/>
-    </row>
-    <row r="105" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB104" s="53"/>
+      <c r="AC104" s="54"/>
+    </row>
+    <row r="105" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B105" s="29"/>
       <c r="C105" s="35"/>
       <c r="E105" s="26"/>
       <c r="F105" s="14"/>
       <c r="AA105" s="29"/>
-      <c r="AB105" s="52"/>
-    </row>
-    <row r="106" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB105" s="53"/>
+      <c r="AC105" s="54"/>
+    </row>
+    <row r="106" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B106" s="29"/>
       <c r="C106" s="35"/>
       <c r="E106" s="26"/>
       <c r="F106" s="14"/>
       <c r="AA106" s="29"/>
-      <c r="AB106" s="52"/>
-    </row>
-    <row r="107" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB106" s="53"/>
+      <c r="AC106" s="54"/>
+    </row>
+    <row r="107" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="E107" s="26"/>
       <c r="F107" s="15" t="s">
         <v>140</v>
@@ -11164,11 +11642,12 @@
         <v>124</v>
       </c>
       <c r="H107" s="8"/>
-      <c r="AB107" s="52"/>
-    </row>
-    <row r="108" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB107" s="53"/>
+      <c r="AC107" s="54"/>
+    </row>
+    <row r="108" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C108" s="34" t="s">
         <v>180</v>
@@ -11234,11 +11713,12 @@
         <v>0.92</v>
       </c>
       <c r="AA108" s="38"/>
-      <c r="AB108" s="52"/>
-    </row>
-    <row r="109" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB108" s="53"/>
+      <c r="AC108" s="54"/>
+    </row>
+    <row r="109" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B109" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C109" s="28" t="s">
         <v>174</v>
@@ -11248,7 +11728,7 @@
       </c>
       <c r="G109" s="4">
         <f>G7*$G$20</f>
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="H109" s="4">
         <f>H7*$H$20</f>
@@ -11256,7 +11736,7 @@
       </c>
       <c r="J109" s="4">
         <f>J7*$G$20</f>
-        <v>1492500</v>
+        <v>0</v>
       </c>
       <c r="K109" s="4">
         <f>K7*$H$20</f>
@@ -11264,7 +11744,7 @@
       </c>
       <c r="M109" s="4">
         <f>M7*$G$20</f>
-        <v>1483200</v>
+        <v>0</v>
       </c>
       <c r="N109" s="4">
         <f>N7*$H$20</f>
@@ -11272,7 +11752,7 @@
       </c>
       <c r="P109" s="4">
         <f>P7*$G$20</f>
-        <v>1474500</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="4">
         <f>Q7*$H$20</f>
@@ -11280,7 +11760,7 @@
       </c>
       <c r="S109" s="4">
         <f>S7*$G$20</f>
-        <v>1464000</v>
+        <v>0</v>
       </c>
       <c r="T109" s="4">
         <f>T7*$H$20</f>
@@ -11288,7 +11768,7 @@
       </c>
       <c r="V109" s="4">
         <f>V7*$G$20</f>
-        <v>1449000</v>
+        <v>0</v>
       </c>
       <c r="W109" s="4">
         <f>W7*$H$20</f>
@@ -11296,20 +11776,23 @@
       </c>
       <c r="Y109" s="4">
         <f>Y7*$G$20</f>
-        <v>1434300</v>
+        <v>-14700</v>
       </c>
       <c r="Z109" s="4">
         <f>Z7*$H$20</f>
         <v>24936000</v>
       </c>
       <c r="AA109" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="AB109" s="52" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="110" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>331</v>
+      </c>
+      <c r="AB109" s="53" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC109" s="54" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="110" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="38" t="s">
         <v>181</v>
       </c>
@@ -11327,7 +11810,7 @@
       </c>
       <c r="J110" s="4">
         <f>IF(G112=0,0,MIN(MAX((G112/G109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" s="4">
         <f>IF(H112=0,0,MIN(MAX((H112/H109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11335,7 +11818,7 @@
       </c>
       <c r="M110" s="4">
         <f>IF(J112=0,0,MIN(MAX((J112/J109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" s="4">
         <f>IF(K112=0,0,MIN(MAX((K112/K109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11343,7 +11826,7 @@
       </c>
       <c r="P110" s="4">
         <f>IF(M112=0,0,MIN(MAX((M112/M109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="4">
         <f>IF(N112=0,0,MIN(MAX((N112/N109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11351,7 +11834,7 @@
       </c>
       <c r="S110" s="4">
         <f>IF(P112=0,0,MIN(MAX((P112/P109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" s="4">
         <f>IF(Q112=0,0,MIN(MAX((Q112/Q109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11359,7 +11842,7 @@
       </c>
       <c r="V110" s="4">
         <f>IF(S112=0,0,MIN(MAX((S112/S109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W110" s="4">
         <f>IF(T112=0,0,MIN(MAX((T112/T109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11367,20 +11850,23 @@
       </c>
       <c r="Y110" s="4">
         <f>IF(V112=0,0,MIN(MAX((V112/V109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0.96349966843506474</v>
+        <v>0</v>
       </c>
       <c r="Z110" s="4">
         <f>IF(W112=0,0,MIN(MAX((W112/W109-$H$17)/($G$19-$H$17), 0), 1))</f>
-        <v>0.86560925711218095</v>
+        <v>0.87277215440147748</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>429</v>
-      </c>
-      <c r="AB110" s="52" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="111" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+      <c r="AB110" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="AC110" s="54" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="111" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="38" t="s">
         <v>182</v>
       </c>
@@ -11400,7 +11886,7 @@
       </c>
       <c r="J111" s="4">
         <f xml:space="preserve"> J108*J110</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K111" s="4">
         <f>K108*K110</f>
@@ -11408,7 +11894,7 @@
       </c>
       <c r="M111" s="4">
         <f xml:space="preserve"> M108*M110</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N111" s="4">
         <f>N108*N110</f>
@@ -11416,7 +11902,7 @@
       </c>
       <c r="P111" s="4">
         <f xml:space="preserve"> P108*P110</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="4">
         <f>Q108*Q110</f>
@@ -11424,7 +11910,7 @@
       </c>
       <c r="S111" s="4">
         <f xml:space="preserve"> S108*S110</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T111" s="4">
         <f>T108*T110</f>
@@ -11432,7 +11918,7 @@
       </c>
       <c r="V111" s="4">
         <f xml:space="preserve"> V108*V110</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W111" s="4">
         <f>W108*W110</f>
@@ -11440,22 +11926,25 @@
       </c>
       <c r="Y111" s="4">
         <f xml:space="preserve"> Y108*Y110</f>
-        <v>0.28904990053051943</v>
+        <v>0</v>
       </c>
       <c r="Z111" s="4">
         <f>Z108*Z110</f>
-        <v>0.7963605165432065</v>
+        <v>0.80295038204935931</v>
       </c>
       <c r="AA111" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="AB111" s="52" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="112" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+      <c r="AB111" s="53" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC111" s="54" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="112" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B112" s="38" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>163</v>
@@ -11465,7 +11954,7 @@
       </c>
       <c r="G112" s="4">
         <f>G7*G20</f>
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="H112" s="4">
         <f>H7*H20</f>
@@ -11473,62 +11962,65 @@
       </c>
       <c r="J112" s="4">
         <f>G112 - G133 - G121 - G144+J111*J7</f>
-        <v>1416820.2074666857</v>
+        <v>0</v>
       </c>
       <c r="K112" s="4">
         <f>H112 - H133 - H121 - H144 + K111*K7</f>
-        <v>23271492.408783317</v>
+        <v>23190103.809</v>
       </c>
       <c r="M112" s="4">
         <f>J112 - J133 - J121 - J144+M111*M7</f>
-        <v>1328540.482773518</v>
+        <v>0</v>
       </c>
       <c r="N112" s="4">
         <f>K112 - K133 - K121 - K144 + N111*N7</f>
-        <v>21500316.163346589</v>
+        <v>21332909.719951883</v>
       </c>
       <c r="P112" s="4">
         <f>M112 - M133 - M121 - M144+P111*P7</f>
-        <v>1229960.5227370157</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="4">
         <f>N112 - N133 - N121 - N144 + Q111*Q7</f>
-        <v>19683424.583337996</v>
+        <v>19419401.648653384</v>
       </c>
       <c r="S112" s="4">
         <f>P112 - P133 - P121 - P144+S111*S7</f>
-        <v>1102712.6301399493</v>
+        <v>0</v>
       </c>
       <c r="T112" s="4">
         <f>Q112 - Q133 - Q121 - Q144 + T111*T7</f>
-        <v>17795064.508199312</v>
+        <v>17406125.443449255</v>
       </c>
       <c r="V112" s="4">
         <f>S112 - S133 - S121 - S144+V111*V7</f>
-        <v>952878.26623738057</v>
+        <v>0</v>
       </c>
       <c r="W112" s="4">
         <f>T112 - T133 - T121 - T144 + W111*W7</f>
-        <v>15735231.967631815</v>
+        <v>15787407.623367518</v>
       </c>
       <c r="Y112" s="4">
         <f>V112 - V133 - V121 - V144+Y111*Y7</f>
-        <v>902055.81293937785</v>
+        <v>0</v>
       </c>
       <c r="Z112" s="4">
         <f>W112 - W133 - W121 - W144 + Z111*Z7</f>
-        <v>15603395.572368858</v>
+        <v>15618862.859584641</v>
       </c>
       <c r="AA112" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="AB112" s="52" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="113" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>333</v>
+      </c>
+      <c r="AB112" s="53" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC112" s="54" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B113" s="38" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C113" s="33" t="s">
         <v>163</v>
@@ -11537,71 +12029,74 @@
         <v>142</v>
       </c>
       <c r="G113" s="4">
-        <f>G112/G7</f>
-        <v>150</v>
+        <f>IF(G7=0,0,G112/G7)</f>
+        <v>0</v>
       </c>
       <c r="H113" s="4">
-        <f>H112/H7</f>
+        <f>IF(H7=0,0,H112/H7)</f>
         <v>100</v>
       </c>
       <c r="J113" s="4">
-        <f>J112/J7</f>
-        <v>142.39399070016941</v>
+        <f>IF(J7=0,0,J112/J7)</f>
+        <v>0</v>
       </c>
       <c r="K113" s="4">
-        <f>K112/K7</f>
-        <v>93.12321892270235</v>
+        <f>IF(K7=0,0,K112/K7)</f>
+        <v>92.797534249699879</v>
       </c>
       <c r="M113" s="4">
-        <f>M112/M7</f>
-        <v>134.35886759440919</v>
+        <f>IF(M7=0,0,M112/M7)</f>
+        <v>0</v>
       </c>
       <c r="N113" s="4">
-        <f>N112/N7</f>
-        <v>86.073566449203682</v>
+        <f>IF(N7=0,0,N112/N7)</f>
+        <v>85.403377717089882</v>
       </c>
       <c r="P113" s="4">
-        <f>P112/P7</f>
-        <v>125.12314575147667</v>
+        <f>IF(P7=0,0,P112/P7)</f>
+        <v>0</v>
       </c>
       <c r="Q113" s="4">
-        <f>Q112/Q7</f>
-        <v>78.82955507231992</v>
+        <f>IF(Q7=0,0,Q112/Q7)</f>
+        <v>77.772177562529578</v>
       </c>
       <c r="S113" s="4">
-        <f>S112/S7</f>
-        <v>112.98285144876529</v>
+        <f>IF(S7=0,0,S112/S7)</f>
+        <v>0</v>
       </c>
       <c r="T113" s="4">
-        <f>T112/T7</f>
-        <v>71.321760405441637</v>
+        <f>IF(T7=0,0,T112/T7)</f>
+        <v>69.76291138999477</v>
       </c>
       <c r="V113" s="4">
-        <f>V112/V7</f>
-        <v>98.641642467637737</v>
+        <f>IF(V7=0,0,V112/V7)</f>
+        <v>0</v>
       </c>
       <c r="W113" s="4">
-        <f>W112/W7</f>
-        <v>63.075910318609083</v>
+        <f>IF(W7=0,0,W112/W7)</f>
+        <v>63.285060522989269</v>
       </c>
       <c r="Y113" s="4">
-        <f>Y112/Y7</f>
-        <v>94.337566716103098</v>
+        <f>IF(Y7=0,0,Y112/Y7)</f>
+        <v>0</v>
       </c>
       <c r="Z113" s="4">
-        <f>Z112/Z7</f>
-        <v>62.573771143603061</v>
+        <f>IF(Z7=0,0,Z112/Z7)</f>
+        <v>62.635799083993589</v>
       </c>
       <c r="AA113" s="38" t="s">
-        <v>379</v>
-      </c>
-      <c r="AB113" s="52" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="114" spans="2:28" ht="34" x14ac:dyDescent="0.2">
+        <v>334</v>
+      </c>
+      <c r="AB113" s="53" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC113" s="54" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="114" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B114" s="38" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C114" s="28" t="s">
         <v>174</v>
@@ -11611,7 +12106,7 @@
       </c>
       <c r="G114" s="4">
         <f>MAX(G113-$G22,0)</f>
-        <v>100.4134425</v>
+        <v>0</v>
       </c>
       <c r="H114" s="4">
         <f>MAX(H113-$H22,0)</f>
@@ -11619,64 +12114,68 @@
       </c>
       <c r="J114" s="4">
         <f>MAX(J113-$G22,0)</f>
-        <v>92.807433200169413</v>
+        <v>0</v>
       </c>
       <c r="K114" s="4">
         <f>MAX(K113-$H22,0)</f>
-        <v>55.322325922702348</v>
+        <v>54.996641249699877</v>
       </c>
       <c r="M114" s="4">
         <f>MAX(M113-$G22,0)</f>
-        <v>84.772310094409193</v>
+        <v>0</v>
       </c>
       <c r="N114" s="4">
         <f>MAX(N113-$H22,0)</f>
-        <v>48.27267344920368</v>
+        <v>47.602484717089879</v>
       </c>
       <c r="P114" s="4">
         <f>MAX(P113-$G22,0)</f>
-        <v>75.536588251476672</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="4">
         <f>MAX(Q113-$H22,0)</f>
-        <v>41.028662072319918</v>
+        <v>39.971284562529576</v>
       </c>
       <c r="S114" s="4">
         <f>MAX(S113-$G22,0)</f>
-        <v>63.39629394876529</v>
+        <v>0</v>
       </c>
       <c r="T114" s="4">
         <f>MAX(T113-$H22,0)</f>
-        <v>33.520867405441635</v>
+        <v>31.962018389994768</v>
       </c>
       <c r="V114" s="4">
         <f>MAX(V113-$G22,0)</f>
-        <v>49.05508496763774</v>
+        <v>0</v>
       </c>
       <c r="W114" s="4">
         <f>MAX(W113-$H22,0)</f>
-        <v>25.275017318609081</v>
+        <v>25.484167522989267</v>
       </c>
       <c r="Y114" s="4">
         <f>MAX(Y113-$G22,0)</f>
-        <v>44.7510092161031</v>
+        <v>0</v>
       </c>
       <c r="Z114" s="4">
         <f>MAX(Z113-$H22,0)</f>
-        <v>24.772878143603059</v>
+        <v>24.834906083993587</v>
       </c>
       <c r="AA114" s="38" t="s">
-        <v>419</v>
+        <v>352</v>
       </c>
       <c r="AB114" s="57" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="115" spans="2:28" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+      <c r="AC114" s="54" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="115" spans="2:29" x14ac:dyDescent="0.2">
       <c r="F115" s="13"/>
-      <c r="AB115" s="52"/>
-    </row>
-    <row r="116" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB115" s="53"/>
+      <c r="AC115" s="54"/>
+    </row>
+    <row r="116" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="F116" s="11" t="s">
         <v>58</v>
       </c>
@@ -11694,11 +12193,12 @@
       <c r="W116" s="12"/>
       <c r="Y116" s="12"/>
       <c r="Z116" s="12"/>
-      <c r="AB116" s="52"/>
-    </row>
-    <row r="117" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB116" s="53"/>
+      <c r="AC116" s="54"/>
+    </row>
+    <row r="117" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="38" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C117" s="34" t="s">
         <v>180</v>
@@ -11708,7 +12208,7 @@
       </c>
       <c r="G117" s="4">
         <f>G113*G7</f>
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="H117" s="4">
         <f>H113*H7</f>
@@ -11716,58 +12216,59 @@
       </c>
       <c r="J117" s="4">
         <f>J113*J7</f>
-        <v>1416820.2074666857</v>
+        <v>0</v>
       </c>
       <c r="K117" s="4">
         <f>K113*K7</f>
-        <v>23271492.408783317</v>
+        <v>23190103.809</v>
       </c>
       <c r="M117" s="4">
         <f>M113*M7</f>
-        <v>1328540.4827735182</v>
+        <v>0</v>
       </c>
       <c r="N117" s="4">
         <f>N113*N7</f>
-        <v>21500316.163346589</v>
+        <v>21332909.719951883</v>
       </c>
       <c r="P117" s="4">
         <f>P113*P7</f>
-        <v>1229960.5227370157</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="4">
         <f>Q113*Q7</f>
-        <v>19683424.583337996</v>
+        <v>19419401.648653384</v>
       </c>
       <c r="S117" s="4">
         <f>S113*S7</f>
-        <v>1102712.6301399493</v>
+        <v>0</v>
       </c>
       <c r="T117" s="4">
         <f>T113*T7</f>
-        <v>17795064.508199312</v>
+        <v>17406125.443449255</v>
       </c>
       <c r="V117" s="4">
         <f>V113*V7</f>
-        <v>952878.26623738057</v>
+        <v>0</v>
       </c>
       <c r="W117" s="4">
         <f>W113*W7</f>
-        <v>15735231.967631815</v>
+        <v>15787407.623367518</v>
       </c>
       <c r="Y117" s="4">
         <f>Y113*Y7</f>
-        <v>902055.81293937785</v>
+        <v>0</v>
       </c>
       <c r="Z117" s="4">
         <f>Z113*Z7</f>
-        <v>15603395.572368858</v>
+        <v>15618862.859584641</v>
       </c>
       <c r="AA117" s="38"/>
-      <c r="AB117" s="52"/>
-    </row>
-    <row r="118" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB117" s="53"/>
+      <c r="AC117" s="54"/>
+    </row>
+    <row r="118" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C118" s="33" t="s">
         <v>163</v>
@@ -11804,15 +12305,18 @@
         <v>215.49749504124878</v>
       </c>
       <c r="AA118" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="AB118" s="52" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="119" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+      <c r="AB118" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC118" s="54" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="119" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B119" s="38" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C119" s="33" t="s">
         <v>163</v>
@@ -11822,7 +12326,7 @@
       </c>
       <c r="G119" s="4">
         <f>G117+G118</f>
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="H119" s="4">
         <f>H117+H118</f>
@@ -11830,62 +12334,65 @@
       </c>
       <c r="J119" s="4">
         <f>J117+J118</f>
-        <v>1416820.2074666857</v>
+        <v>0</v>
       </c>
       <c r="K119" s="4">
         <f>K117+K118</f>
-        <v>23271493.258783318</v>
+        <v>23190104.659000002</v>
       </c>
       <c r="M119" s="4">
         <f>M117+M118</f>
-        <v>1328540.4827735182</v>
+        <v>0</v>
       </c>
       <c r="N119" s="4">
         <f>N117+N118</f>
-        <v>21500322.062012088</v>
+        <v>21332915.618617382</v>
       </c>
       <c r="P119" s="4">
         <f>P117+P118</f>
-        <v>1229960.5227370157</v>
+        <v>0</v>
       </c>
       <c r="Q119" s="4">
         <f>Q117+Q118</f>
-        <v>19683445.592742592</v>
+        <v>19419422.65805798</v>
       </c>
       <c r="S119" s="4">
         <f>S117+S118</f>
-        <v>1102712.6301399493</v>
+        <v>0</v>
       </c>
       <c r="T119" s="4">
         <f>T117+T118</f>
-        <v>17795117.114619143</v>
+        <v>17406178.049869087</v>
       </c>
       <c r="V119" s="4">
         <f>V117+V118</f>
-        <v>952878.26623738057</v>
+        <v>0</v>
       </c>
       <c r="W119" s="4">
         <f>W117+W118</f>
-        <v>15735344.281459566</v>
+        <v>15787519.937195269</v>
       </c>
       <c r="Y119" s="4">
         <f>Y117+Y118</f>
-        <v>902055.81293937785</v>
+        <v>0</v>
       </c>
       <c r="Z119" s="4">
         <f>Z117+Z118</f>
-        <v>15603611.069863901</v>
+        <v>15619078.357079683</v>
       </c>
       <c r="AA119" s="38" t="s">
-        <v>383</v>
-      </c>
-      <c r="AB119" s="52" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="120" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+      <c r="AB119" s="53" t="s">
+        <v>444</v>
+      </c>
+      <c r="AC119" s="54" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="120" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B120" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C120" s="33" t="s">
         <v>163</v>
@@ -11895,7 +12402,7 @@
       </c>
       <c r="G120" s="4">
         <f>G119*$G$21</f>
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="H120" s="4">
         <f>H119*$H$21</f>
@@ -11903,72 +12410,75 @@
       </c>
       <c r="J120" s="4">
         <f>J119*$G$21</f>
-        <v>425046.0622400057</v>
+        <v>0</v>
       </c>
       <c r="K120" s="4">
         <f>K119*$H$21</f>
-        <v>5817873.3146958295</v>
+        <v>5797526.1647500005</v>
       </c>
       <c r="M120" s="4">
         <f>M119*$G$21</f>
-        <v>398562.14483205543</v>
+        <v>0</v>
       </c>
       <c r="N120" s="4">
         <f>N119*$H$21</f>
-        <v>5375080.5155030219</v>
+        <v>5333228.9046543455</v>
       </c>
       <c r="P120" s="4">
         <f>P119*$G$21</f>
-        <v>368988.1568211047</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="4">
         <f>Q119*$H$21</f>
-        <v>4920861.398185648</v>
+        <v>4854855.6645144951</v>
       </c>
       <c r="S120" s="4">
         <f>S119*$G$21</f>
-        <v>330813.78904198477</v>
+        <v>0</v>
       </c>
       <c r="T120" s="4">
         <f>T119*$H$21</f>
-        <v>4448779.2786547858</v>
+        <v>4351544.5124672716</v>
       </c>
       <c r="V120" s="4">
         <f>V119*$G$21</f>
-        <v>285863.47987121413</v>
+        <v>0</v>
       </c>
       <c r="W120" s="4">
         <f>W119*$H$21</f>
-        <v>3933836.0703648916</v>
+        <v>3946879.9842988173</v>
       </c>
       <c r="Y120" s="4">
         <f>Y119*$G$21</f>
-        <v>270616.74388181337</v>
+        <v>0</v>
       </c>
       <c r="Z120" s="4">
         <f>Z119*$H$21</f>
-        <v>3900902.7674659751</v>
+        <v>3904769.5892699207</v>
       </c>
       <c r="AA120" s="38" t="s">
-        <v>384</v>
-      </c>
-      <c r="AB120" s="52" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="121" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+      <c r="AB120" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="AC120" s="54" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B121" s="38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C121" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G121" s="4">
         <f>G9*G113</f>
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="H121" s="4">
         <f>H9*H113</f>
@@ -11976,72 +12486,75 @@
       </c>
       <c r="J121" s="4">
         <f>J9*J113</f>
-        <v>8828.4274234105033</v>
+        <v>0</v>
       </c>
       <c r="K121" s="4">
         <f>K9*K113</f>
-        <v>10243.554081497259</v>
+        <v>10207.728767466986</v>
       </c>
       <c r="M121" s="4">
         <f>M9*M113</f>
-        <v>7792.8143204757334</v>
+        <v>0</v>
       </c>
       <c r="N121" s="4">
         <f>N9*N113</f>
-        <v>8090.9152462251459</v>
+        <v>8027.917505406449</v>
       </c>
       <c r="P121" s="4">
         <f>P9*P113</f>
-        <v>8758.6202026033661</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="4">
         <f>Q9*Q113</f>
-        <v>15135.274573885425</v>
+        <v>14932.258092005679</v>
       </c>
       <c r="S121" s="4">
         <f>S9*S113</f>
-        <v>11298.285144876529</v>
+        <v>0</v>
       </c>
       <c r="T121" s="4">
         <f>T9*T113</f>
-        <v>2781.5486558122238</v>
+        <v>2720.753544209796</v>
       </c>
       <c r="V121" s="4">
         <f>V9*V113</f>
-        <v>9666.8809618284977</v>
+        <v>0</v>
       </c>
       <c r="W121" s="4">
         <f>W9*W113</f>
-        <v>6622.9705834539536</v>
+        <v>6644.9313549138733</v>
       </c>
       <c r="Y121" s="4">
         <f>Y9*Y113</f>
-        <v>9245.0815381781031</v>
+        <v>0</v>
       </c>
       <c r="Z121" s="4">
         <f>Z9*Z113</f>
-        <v>7258.5574526579549</v>
+        <v>7265.7526937432567</v>
       </c>
       <c r="AA121" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="AB121" s="52" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="122" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+      <c r="AB121" s="53" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC121" s="54" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="122" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B122" s="38" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C122" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G122" s="4">
         <f>MIN(G121,G9*G15)</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H122" s="4">
         <f>MIN(H121,H9*H15)</f>
@@ -12049,7 +12562,7 @@
       </c>
       <c r="J122" s="4">
         <f>MIN(J121,J9*J15)</f>
-        <v>316.2</v>
+        <v>0</v>
       </c>
       <c r="K122" s="4">
         <f>MIN(K121,K9*K15)</f>
@@ -12057,7 +12570,7 @@
       </c>
       <c r="M122" s="4">
         <f>MIN(M121,M9*M15)</f>
-        <v>301.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="N122" s="4">
         <f>MIN(N121,N9*N15)</f>
@@ -12065,7 +12578,7 @@
       </c>
       <c r="P122" s="4">
         <f>MIN(P121,P9*P15)</f>
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="4">
         <f>MIN(Q121,Q9*Q15)</f>
@@ -12073,7 +12586,7 @@
       </c>
       <c r="S122" s="4">
         <f>MIN(S121,S9*S15)</f>
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="T122" s="4">
         <f>MIN(T121,T9*T15)</f>
@@ -12081,7 +12594,7 @@
       </c>
       <c r="V122" s="4">
         <f>MIN(V121,V9*V15)</f>
-        <v>401.79999999999995</v>
+        <v>0</v>
       </c>
       <c r="W122" s="4">
         <f>MIN(W121,W9*W15)</f>
@@ -12089,32 +12602,35 @@
       </c>
       <c r="Y122" s="4">
         <f>MIN(Y121,Y9*Y15)</f>
-        <v>499.79999999999995</v>
+        <v>0</v>
       </c>
       <c r="Z122" s="4">
         <f>MIN(Z121,Z9*Z15)</f>
         <v>1044</v>
       </c>
       <c r="AA122" s="38" t="s">
-        <v>399</v>
-      </c>
-      <c r="AB122" s="52" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="123" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+      <c r="AB122" s="53" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC122" s="54" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="123" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B123" s="38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C123" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G123" s="4">
         <f>(G121-G122)*$G$14</f>
-        <v>5075</v>
+        <v>0</v>
       </c>
       <c r="H123" s="4">
         <f>(H121-H122+H54)*$G$14</f>
@@ -12122,178 +12638,187 @@
       </c>
       <c r="J123" s="4">
         <f>(J121-J122)*$G$14</f>
-        <v>5958.5591963873512</v>
+        <v>0</v>
       </c>
       <c r="K123" s="4">
         <f>(K121-K122+K54)*$G$14</f>
-        <v>6415.8878570480811</v>
+        <v>6390.8101372268902</v>
       </c>
       <c r="M123" s="4">
         <f>(M121-M122)*$G$14</f>
-        <v>5243.8500243330127</v>
+        <v>0</v>
       </c>
       <c r="N123" s="4">
         <f>(N121-N122+N54)*$G$14</f>
-        <v>5018.8006723576018</v>
+        <v>4974.7022537845141</v>
       </c>
       <c r="P123" s="4">
         <f>(P121-P122)*$G$14</f>
-        <v>5900.7341418223559</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="4">
         <f>(Q121-Q122+Q54)*$G$14</f>
-        <v>9264.1322017197963</v>
+        <v>9122.0206644039754</v>
       </c>
       <c r="S123" s="4">
         <f>(S121-S122)*$G$14</f>
-        <v>7544.7996014135697</v>
+        <v>0</v>
       </c>
       <c r="T123" s="4">
         <f>(T121-T122+T54)*$G$14</f>
-        <v>1671.3540590685566</v>
+        <v>1628.7974809468571</v>
       </c>
       <c r="V123" s="4">
         <f>(V121-V122)*$G$14</f>
-        <v>6485.5566732799489</v>
+        <v>0</v>
       </c>
       <c r="W123" s="4">
         <f>(W121-W122+W54)*$G$14</f>
-        <v>3827.5794084177674</v>
+        <v>3842.951948439711</v>
       </c>
       <c r="Y123" s="4">
         <f>(Y121-Y122)*$G$14</f>
-        <v>6121.6970767246721</v>
+        <v>0</v>
       </c>
       <c r="Z123" s="4">
         <f>(Z121-Z122+Z54)*$G$14</f>
-        <v>4350.1902168605684</v>
+        <v>4355.2268856202791</v>
       </c>
       <c r="AA123" s="38" t="s">
-        <v>400</v>
-      </c>
-      <c r="AB123" s="52" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="124" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+      <c r="AB123" s="53" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC123" s="54" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B124" s="38" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C124" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G124" s="4">
         <f>MIN(G123+H123, G33)</f>
-        <v>11375</v>
+        <v>6300</v>
       </c>
       <c r="J124" s="4">
         <f>MIN(J123+K123, J33)</f>
-        <v>12374.447053435433</v>
+        <v>6390.8101372268902</v>
       </c>
       <c r="M124" s="4">
         <f>MIN(M123+N123, M33)</f>
-        <v>10262.650696690614</v>
+        <v>4974.7022537845141</v>
       </c>
       <c r="P124" s="4">
         <f>MIN(P123+Q123, P33)</f>
-        <v>15164.866343542151</v>
+        <v>9122.0206644039754</v>
       </c>
       <c r="S124" s="4">
         <f>MIN(S123+T123, S33)</f>
-        <v>9216.1536604821267</v>
+        <v>1628.7974809468571</v>
       </c>
       <c r="V124" s="4">
         <f>MIN(V123+W123, V33)</f>
-        <v>10313.136081697716</v>
+        <v>3842.951948439711</v>
       </c>
       <c r="Y124" s="4">
         <f>MIN(Y123+Z123, Y33)</f>
-        <v>10471.887293585241</v>
+        <v>4355.2268856202791</v>
       </c>
       <c r="AA124" s="38" t="s">
-        <v>401</v>
-      </c>
-      <c r="AB124" s="52" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="125" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+      <c r="AB124" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="AC124" s="54" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="125" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B125" s="38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C125" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G125" s="4">
         <f>G123/(G123+H123)</f>
-        <v>0.44615384615384618</v>
+        <v>0</v>
       </c>
       <c r="H125" s="4">
         <f>H123/(G123+H123)</f>
-        <v>0.55384615384615388</v>
+        <v>1</v>
       </c>
       <c r="J125" s="4">
         <f>J123/(J123+K123)</f>
-        <v>0.48152124863899409</v>
+        <v>0</v>
       </c>
       <c r="K125" s="4">
         <f>K123/(J123+K123)</f>
-        <v>0.51847875136100585</v>
+        <v>1</v>
       </c>
       <c r="M125" s="4">
         <f>M123/(M123+N123)</f>
-        <v>0.51096448464566679</v>
+        <v>0</v>
       </c>
       <c r="N125" s="4">
         <f>N123/(M123+N123)</f>
-        <v>0.48903551535433326</v>
+        <v>1</v>
       </c>
       <c r="P125" s="4">
         <f>P123/(P123+Q123)</f>
-        <v>0.38910558181972643</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="4">
         <f>Q123/(P123+Q123)</f>
-        <v>0.61089441818027368</v>
+        <v>1</v>
       </c>
       <c r="S125" s="4">
         <f>S123/(S123+T123)</f>
-        <v>0.81864950166411143</v>
+        <v>0</v>
       </c>
       <c r="T125" s="4">
         <f>T123/(S123+T123)</f>
-        <v>0.18135049833588848</v>
+        <v>1</v>
       </c>
       <c r="V125" s="4">
         <f>V123/(V123+W123)</f>
-        <v>0.62886367656775044</v>
+        <v>0</v>
       </c>
       <c r="W125" s="4">
         <f>W123/(V123+W123)</f>
-        <v>0.37113632343224967</v>
+        <v>1</v>
       </c>
       <c r="Y125" s="4">
         <f>Y123/(Y123+Z123)</f>
-        <v>0.58458393459549907</v>
+        <v>0</v>
       </c>
       <c r="Z125" s="4">
         <f>Z123/(Y123+Z123)</f>
-        <v>0.41541606540450088</v>
+        <v>1</v>
       </c>
       <c r="AA125" s="38" t="s">
-        <v>404</v>
-      </c>
-      <c r="AB125" s="52" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="126" spans="2:28" ht="34" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+      <c r="AB125" s="53" t="s">
+        <v>410</v>
+      </c>
+      <c r="AC125" s="54" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B126" s="38" t="s">
         <v>183</v>
       </c>
@@ -12305,7 +12830,7 @@
       </c>
       <c r="G126" s="4">
         <f>MAX(G13-G27, 0)*G114</f>
-        <v>497046.54037499998</v>
+        <v>0</v>
       </c>
       <c r="H126" s="4">
         <f>MAX(H13-H27, 0)*H114</f>
@@ -12313,63 +12838,67 @@
       </c>
       <c r="J126" s="4">
         <f>MAX(J13-J27, 0)*J114</f>
-        <v>453642.73348242807</v>
+        <v>0</v>
       </c>
       <c r="K126" s="4">
         <f>MAX(K13-K27, 0)*K114</f>
-        <v>11052847.496096702</v>
+        <v>10987778.955277538</v>
       </c>
       <c r="M126" s="4">
         <f>MAX(M13-M27, 0)*M114</f>
-        <v>367064.10270879179</v>
+        <v>0</v>
       </c>
       <c r="N126" s="4">
         <f>MAX(N13-N27, 0)*N114</f>
-        <v>9639859.7971121781</v>
+        <v>9506025.7880639806</v>
       </c>
       <c r="P126" s="4">
         <f>MAX(P13-P27, 0)*P114</f>
-        <v>284017.57182555227</v>
+        <v>0</v>
       </c>
       <c r="Q126" s="4">
         <f>MAX(Q13-Q27, 0)*Q114</f>
-        <v>8185382.1980761131</v>
+        <v>7974431.1553629003</v>
       </c>
       <c r="S126" s="4">
         <f>MAX(S13-S27, 0)*S114</f>
-        <v>200332.2888780983</v>
+        <v>0</v>
       </c>
       <c r="T126" s="4">
         <f>MAX(T13-T27, 0)*T114</f>
-        <v>6719760.6844318574</v>
+        <v>6407266.0165503006</v>
       </c>
       <c r="V126" s="4">
         <f>MAX(V13-V27, 0)*V114</f>
-        <v>115868.11069356035</v>
+        <v>0</v>
       </c>
       <c r="W126" s="4">
         <f>MAX(W13-W27, 0)*W114</f>
-        <v>5051464.9612972112</v>
+        <v>5093265.7211446352</v>
       </c>
       <c r="Y126" s="4">
         <f>MAX(Y13-Y27, 0)*Y114</f>
-        <v>101316.28486525742</v>
+        <v>0</v>
       </c>
       <c r="Z126" s="4">
         <f>MAX(Z13-Z27, 0)*Z114</f>
-        <v>4948233.7719158493</v>
+        <v>4960623.4808412148</v>
       </c>
       <c r="AA126" s="38" t="s">
-        <v>405</v>
-      </c>
-      <c r="AB126" s="52" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="127" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="AB127" s="52"/>
-    </row>
-    <row r="128" spans="2:28" ht="17" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+      <c r="AB126" s="53" t="s">
+        <v>350</v>
+      </c>
+      <c r="AC126" s="54" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="127" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AB127" s="53"/>
+      <c r="AC127" s="54"/>
+    </row>
+    <row r="128" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="F128" s="15" t="s">
         <v>73</v>
       </c>
@@ -12387,56 +12916,60 @@
       <c r="W128" s="8"/>
       <c r="Y128" s="8"/>
       <c r="Z128" s="8"/>
-      <c r="AB128" s="52"/>
+      <c r="AB128" s="53"/>
+      <c r="AC128" s="54"/>
     </row>
     <row r="129" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C129" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G129" s="4">
         <f>MAX(G33-G124,0)</f>
-        <v>1988625</v>
+        <v>1993700</v>
       </c>
       <c r="J129" s="4">
         <f>MAX(J33-J124,0)</f>
-        <v>2037625.5529465645</v>
+        <v>2043609.1898627731</v>
       </c>
       <c r="M129" s="4">
         <f>MAX(M33-M124,0)</f>
-        <v>2099737.3493033093</v>
+        <v>2105025.2977462155</v>
       </c>
       <c r="P129" s="4">
         <f>MAX(P33-P124,0)</f>
-        <v>2194835.133656458</v>
+        <v>2200877.9793355959</v>
       </c>
       <c r="S129" s="4">
         <f>MAX(S33-S124,0)</f>
-        <v>2990783.8463395177</v>
+        <v>2998371.2025190531</v>
       </c>
       <c r="V129" s="4">
         <f>MAX(V33-V124,0)</f>
-        <v>24989686.863918301</v>
+        <v>24996157.048051558</v>
       </c>
       <c r="Y129" s="4">
         <f>MAX(Y33-Y124,0)</f>
-        <v>2509528.1127064149</v>
+        <v>2515644.7731143795</v>
       </c>
       <c r="AA129" s="38" t="s">
-        <v>408</v>
-      </c>
-      <c r="AB129" s="52" t="s">
-        <v>407</v>
+        <v>479</v>
+      </c>
+      <c r="AB129" s="53" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC129" s="54" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B130" s="38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C130" s="28" t="s">
         <v>174</v>
@@ -12446,42 +12979,45 @@
       </c>
       <c r="G130" s="4">
         <f>MIN(G140,G129)</f>
-        <v>1988625</v>
+        <v>1993700</v>
       </c>
       <c r="J130" s="4">
         <f>MIN(J140,J129)</f>
-        <v>2037625.5529465645</v>
+        <v>2043609.1898627731</v>
       </c>
       <c r="M130" s="4">
         <f>MIN(M140,M129)</f>
-        <v>2099737.3493033093</v>
+        <v>2105025.2977462155</v>
       </c>
       <c r="P130" s="4">
         <f>MIN(P140,P129)</f>
-        <v>2194835.133656458</v>
+        <v>2200877.9793355959</v>
       </c>
       <c r="S130" s="4">
         <f>MIN(S140,S129)</f>
-        <v>2402116.7562237582</v>
+        <v>1821040.5218088522</v>
       </c>
       <c r="V130" s="4">
         <f>MIN(V140,V129)</f>
-        <v>342075.56862017012</v>
+        <v>337878.12833874481</v>
       </c>
       <c r="Y130" s="4">
         <f>MIN(Y140,Y129)</f>
-        <v>236958.69160889552</v>
+        <v>220752.12927619604</v>
       </c>
       <c r="AA130" s="38" t="s">
-        <v>411</v>
-      </c>
-      <c r="AB130" s="52" t="s">
-        <v>417</v>
+        <v>478</v>
+      </c>
+      <c r="AB130" s="53" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC130" s="54" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B131" s="38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C131" s="28" t="s">
         <v>174</v>
@@ -12507,21 +13043,24 @@
       </c>
       <c r="S131" s="4">
         <f>S129-S130</f>
-        <v>588667.09011575952</v>
+        <v>1177330.6807102009</v>
       </c>
       <c r="V131" s="4">
         <f>V129-V130</f>
-        <v>24647611.295298129</v>
+        <v>24658278.919712815</v>
       </c>
       <c r="Y131" s="4">
         <f>Y129-Y130</f>
-        <v>2272569.4210975193</v>
+        <v>2294892.6438381835</v>
       </c>
       <c r="AA131" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="AB131" s="52" t="s">
-        <v>410</v>
+        <v>477</v>
+      </c>
+      <c r="AB131" s="53" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC131" s="54" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="132" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -12563,15 +13102,18 @@
         <v>0</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB132" s="52" t="s">
-        <v>416</v>
+        <v>474</v>
+      </c>
+      <c r="AB132" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="AC132" s="54" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="133" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B133" s="38" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>174</v>
@@ -12581,70 +13123,73 @@
       </c>
       <c r="G133" s="4">
         <f>G141*G130</f>
-        <v>76441.580815194291</v>
+        <v>0</v>
       </c>
       <c r="H133" s="4">
         <f>H141*G130</f>
-        <v>1912183.4191848056</v>
+        <v>1993700</v>
       </c>
       <c r="J133" s="4">
         <f>J141*J130</f>
-        <v>80333.273414349693</v>
+        <v>0</v>
       </c>
       <c r="K133" s="4">
         <f>K141*J130</f>
-        <v>1957292.2795322149</v>
+        <v>2043609.1898627731</v>
       </c>
       <c r="M133" s="4">
         <f>M141*M130</f>
-        <v>91806.708408756895</v>
+        <v>0</v>
       </c>
       <c r="N133" s="4">
         <f>N141*M130</f>
-        <v>2007930.6408945527</v>
+        <v>2105025.2977462155</v>
       </c>
       <c r="P133" s="4">
         <f>P141*P130</f>
-        <v>119687.89540326738</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="4">
         <f>Q141*P130</f>
-        <v>2075147.2382531904</v>
+        <v>2200877.9793355959</v>
       </c>
       <c r="S133" s="4">
         <f>S141*S130</f>
-        <v>139940.26445123838</v>
+        <v>0</v>
       </c>
       <c r="T133" s="4">
         <f>T141*S130</f>
-        <v>2262176.4917725199</v>
+        <v>1821040.5218088522</v>
       </c>
       <c r="V133" s="4">
         <f>V141*V130</f>
-        <v>42505.359023831879</v>
+        <v>0</v>
       </c>
       <c r="W133" s="4">
         <f>W141*V130</f>
-        <v>299570.20959633822</v>
+        <v>337878.12833874481</v>
       </c>
       <c r="Y133" s="4">
         <f>Y141*Y130</f>
-        <v>27081.188280169557</v>
+        <v>0</v>
       </c>
       <c r="Z133" s="4">
         <f>Z141*Y130</f>
-        <v>209877.50332872596</v>
+        <v>220752.12927619604</v>
       </c>
       <c r="AA133" s="38" t="s">
-        <v>413</v>
-      </c>
-      <c r="AB133" s="52" t="s">
-        <v>415</v>
+        <v>475</v>
+      </c>
+      <c r="AB133" s="53" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC133" s="54" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B134" s="38" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C134" s="33" t="s">
         <v>163</v>
@@ -12654,65 +13199,68 @@
       </c>
       <c r="G134" s="4">
         <f>G133</f>
-        <v>76441.580815194291</v>
+        <v>0</v>
       </c>
       <c r="H134" s="4">
         <f>H133+G132</f>
-        <v>1912183.4191848056</v>
+        <v>1993700</v>
       </c>
       <c r="J134" s="4">
         <f>J133</f>
-        <v>80333.273414349693</v>
+        <v>0</v>
       </c>
       <c r="K134" s="4">
         <f>K133+J132</f>
-        <v>1957292.2795322149</v>
+        <v>2043609.1898627731</v>
       </c>
       <c r="M134" s="4">
         <f>M133</f>
-        <v>91806.708408756895</v>
+        <v>0</v>
       </c>
       <c r="N134" s="4">
         <f>N133+M132</f>
-        <v>2007930.6408945527</v>
+        <v>2105025.2977462155</v>
       </c>
       <c r="P134" s="4">
         <f>P133</f>
-        <v>119687.89540326738</v>
+        <v>0</v>
       </c>
       <c r="Q134" s="4">
         <f>Q133+P132</f>
-        <v>2075147.2382531904</v>
+        <v>2200877.9793355959</v>
       </c>
       <c r="S134" s="4">
         <f>S133</f>
-        <v>139940.26445123838</v>
+        <v>0</v>
       </c>
       <c r="T134" s="4">
         <f>T133+S132</f>
-        <v>2262176.4917725199</v>
+        <v>1821040.5218088522</v>
       </c>
       <c r="V134" s="4">
         <f>V133</f>
-        <v>42505.359023831879</v>
+        <v>0</v>
       </c>
       <c r="W134" s="4">
         <f>W133+V132</f>
-        <v>299570.20959633822</v>
+        <v>337878.12833874481</v>
       </c>
       <c r="Y134" s="4">
         <f>Y133</f>
-        <v>27081.188280169557</v>
+        <v>0</v>
       </c>
       <c r="Z134" s="4">
         <f>Z133+Y132</f>
-        <v>209877.50332872596</v>
+        <v>220752.12927619604</v>
       </c>
       <c r="AA134" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="AB134" s="52" t="s">
-        <v>418</v>
+        <v>476</v>
+      </c>
+      <c r="AB134" s="53" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC134" s="54" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -12733,11 +13281,12 @@
       <c r="W135" s="8"/>
       <c r="Y135" s="8"/>
       <c r="Z135" s="8"/>
-      <c r="AB135" s="52"/>
+      <c r="AB135" s="53"/>
+      <c r="AC135" s="54"/>
     </row>
     <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B136" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C136" s="28" t="s">
         <v>174</v>
@@ -12747,7 +13296,7 @@
       </c>
       <c r="G136" s="4">
         <f>G114/$G$23</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" s="4">
         <f>H114/$H$23</f>
@@ -12755,61 +13304,60 @@
       </c>
       <c r="J136" s="4">
         <f>J114/$G$23</f>
-        <v>0.92425307697392622</v>
+        <v>0</v>
       </c>
       <c r="K136" s="4">
         <f>K114/$H$23</f>
-        <v>0.8894392313816073</v>
+        <v>0.88420306821607386</v>
       </c>
       <c r="M136" s="4">
         <f>M114/$G$23</f>
-        <v>0.84423268422860009</v>
+        <v>0</v>
       </c>
       <c r="N136" s="4">
         <f>N114/$H$23</f>
-        <v>0.77609913996359592</v>
+        <v>0.76532424681096922</v>
       </c>
       <c r="P136" s="4">
         <f>P114/$G$23</f>
-        <v>0.75225573758689401</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="4">
         <f>Q114/$H$23</f>
-        <v>0.65963426247132328</v>
+        <v>0.64263437998441963</v>
       </c>
       <c r="S136" s="4">
         <f>S114/$G$23</f>
-        <v>0.63135265926935324</v>
+        <v>0</v>
       </c>
       <c r="T136" s="4">
         <f>T114/$H$23</f>
-        <v>0.5389284351854382</v>
+        <v>0.51386619409173784</v>
       </c>
       <c r="V136" s="4">
         <f>V114/$G$23</f>
-        <v>0.48853105467067059</v>
+        <v>0</v>
       </c>
       <c r="W136" s="4">
         <f>W114/$H$23</f>
-        <v>0.4063565947756948</v>
+        <v>0.40971918653091383</v>
       </c>
       <c r="Y136" s="4">
         <f>Y114/$G$23</f>
-        <v>0.44566751325255183</v>
+        <v>0</v>
       </c>
       <c r="Z136" s="4">
         <f>Z114/$H$23</f>
-        <v>0.39828350178087057</v>
+        <v>0.39928074986661122</v>
       </c>
       <c r="AA136" s="38" t="s">
-        <v>431</v>
-      </c>
-      <c r="AB136" s="52" t="s">
-        <v>421</v>
-      </c>
-      <c r="AC136">
-        <f>SUM(AB$6:AB136)</f>
-        <v>0</v>
+        <v>390</v>
+      </c>
+      <c r="AB136" s="53" t="s">
+        <v>413</v>
+      </c>
+      <c r="AC136" s="54" t="s">
+        <v>386</v>
       </c>
       <c r="AD136">
         <v>20</v>
@@ -12817,7 +13365,7 @@
     </row>
     <row r="137" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B137" s="38" t="s">
         <v>184</v>
@@ -12830,7 +13378,7 @@
       </c>
       <c r="G137" s="4">
         <f>MAX(MIN((G136-$G$17)/$G$18, 1), 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" s="4">
         <f>MAX(MIN((H136-$H$17)/$H$18, 1), 0)</f>
@@ -12838,7 +13386,7 @@
       </c>
       <c r="J137" s="4">
         <f>MAX(MIN((J136-$G$17)/$G$18, 1), 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" s="4">
         <f>MAX(MIN((K136-$H$17)/$H$18, 1), 0)</f>
@@ -12846,53 +13394,52 @@
       </c>
       <c r="M137" s="4">
         <f>MAX(MIN((M136-$G$17)/$G$18, 1), 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" s="4">
         <f>MAX(MIN((N136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.8328091484893303</v>
+        <v>0.81026795213003489</v>
       </c>
       <c r="P137" s="4">
         <f>MAX(MIN((P136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.97933386739236106</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="4">
         <f>MAX(MIN((Q136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.5891633289598236</v>
+        <v>0.55359938565252242</v>
       </c>
       <c r="S137" s="4">
         <f>MAX(MIN((S136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.69854073566938424</v>
+        <v>0</v>
       </c>
       <c r="T137" s="4">
         <f>MAX(MIN((T136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.33664539527627274</v>
+        <v>0.28421490805985111</v>
       </c>
       <c r="V137" s="4">
         <f>MAX(MIN((V136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.36684260034451582</v>
+        <v>0</v>
       </c>
       <c r="W137" s="4">
         <f>MAX(MIN((W136-$H$17)/$H$18, 1), 0)</f>
-        <v>5.9303630113552025E-2</v>
+        <v>6.6338209478458504E-2</v>
       </c>
       <c r="Y137" s="4">
         <f>MAX(MIN((Y136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.26729353840979642</v>
+        <v>0</v>
       </c>
       <c r="Z137" s="4">
         <f>MAX(MIN((Z136-$H$17)/$H$18, 1), 0)</f>
-        <v>4.2414629745244618E-2</v>
+        <v>4.4500883836231256E-2</v>
       </c>
       <c r="AA137" s="39" t="s">
-        <v>430</v>
-      </c>
-      <c r="AB137" s="52" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC137">
-        <f>SUM(AB$6:AB137)</f>
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="AB137" s="53" t="s">
+        <v>414</v>
+      </c>
+      <c r="AC137" s="54" t="s">
+        <v>386</v>
       </c>
       <c r="AD137">
         <v>20</v>
@@ -12901,11 +13448,8 @@
     <row r="138" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B138" s="38"/>
       <c r="AA138" s="38"/>
-      <c r="AB138" s="52"/>
-      <c r="AC138">
-        <f>SUM(AB$6:AB138)</f>
-        <v>0</v>
-      </c>
+      <c r="AB138" s="53"/>
+      <c r="AC138" s="54"/>
       <c r="AD138">
         <v>20</v>
       </c>
@@ -12922,7 +13466,7 @@
       </c>
       <c r="G139" s="4">
         <f>G126*G137</f>
-        <v>497046.54037499998</v>
+        <v>0</v>
       </c>
       <c r="H139" s="4">
         <f>H126*H137</f>
@@ -12930,61 +13474,60 @@
       </c>
       <c r="J139" s="4">
         <f>J126*J137</f>
-        <v>453642.73348242807</v>
+        <v>0</v>
       </c>
       <c r="K139" s="4">
         <f>K126*K137</f>
-        <v>11052847.496096702</v>
+        <v>10987778.955277538</v>
       </c>
       <c r="M139" s="4">
         <f>M126*M137</f>
-        <v>367064.10270879179</v>
+        <v>0</v>
       </c>
       <c r="N139" s="4">
         <f>N126*N137</f>
-        <v>8028163.4291895209</v>
+        <v>7702428.0481899027</v>
       </c>
       <c r="P139" s="4">
         <f>P126*P137</f>
-        <v>278148.02702330577</v>
+        <v>0</v>
       </c>
       <c r="Q139" s="4">
         <f>Q126*Q137</f>
-        <v>4822527.024627001</v>
+        <v>4414640.1885372363</v>
       </c>
       <c r="S139" s="4">
         <f>S126*S137</f>
-        <v>139940.26445123838</v>
+        <v>0</v>
       </c>
       <c r="T139" s="4">
         <f>T126*T137</f>
-        <v>2262176.4917725199</v>
+        <v>1821040.5218088522</v>
       </c>
       <c r="V139" s="4">
         <f>V126*V137</f>
-        <v>42505.359023831879</v>
+        <v>0</v>
       </c>
       <c r="W139" s="4">
         <f>W126*W137</f>
-        <v>299570.20959633822</v>
+        <v>337878.12833874481</v>
       </c>
       <c r="Y139" s="4">
         <f>Y126*Y137</f>
-        <v>27081.188280169557</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="4">
         <f>Z126*Z137</f>
-        <v>209877.50332872596</v>
+        <v>220752.12927619604</v>
       </c>
       <c r="AA139" s="38" t="s">
-        <v>423</v>
-      </c>
-      <c r="AB139" s="52" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC139">
-        <f>SUM(AB$6:AB159)</f>
-        <v>0</v>
+        <v>392</v>
+      </c>
+      <c r="AB139" s="53" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC139" s="54" t="s">
+        <v>370</v>
       </c>
       <c r="AD139">
         <v>20</v>
@@ -13002,65 +13545,68 @@
       </c>
       <c r="G140" s="4">
         <f>G139+H139</f>
-        <v>12930648.029674999</v>
+        <v>12433601.4893</v>
       </c>
       <c r="H140" s="4">
         <f>G140</f>
-        <v>12930648.029674999</v>
+        <v>12433601.4893</v>
       </c>
       <c r="J140" s="4">
         <f>J139+K139</f>
-        <v>11506490.22957913</v>
+        <v>10987778.955277538</v>
       </c>
       <c r="K140" s="4">
         <f>J140</f>
-        <v>11506490.22957913</v>
+        <v>10987778.955277538</v>
       </c>
       <c r="M140" s="4">
         <f>M139+N139</f>
-        <v>8395227.5318983123</v>
+        <v>7702428.0481899027</v>
       </c>
       <c r="N140" s="4">
         <f>M140</f>
-        <v>8395227.5318983123</v>
+        <v>7702428.0481899027</v>
       </c>
       <c r="P140" s="4">
         <f>P139+Q139</f>
-        <v>5100675.0516503071</v>
+        <v>4414640.1885372363</v>
       </c>
       <c r="Q140" s="4">
         <f>P140</f>
-        <v>5100675.0516503071</v>
+        <v>4414640.1885372363</v>
       </c>
       <c r="S140" s="4">
         <f>S139+T139</f>
-        <v>2402116.7562237582</v>
+        <v>1821040.5218088522</v>
       </c>
       <c r="T140" s="4">
         <f>S140</f>
-        <v>2402116.7562237582</v>
+        <v>1821040.5218088522</v>
       </c>
       <c r="V140" s="4">
         <f>V139+W139</f>
-        <v>342075.56862017012</v>
+        <v>337878.12833874481</v>
       </c>
       <c r="W140" s="4">
         <f>V140</f>
-        <v>342075.56862017012</v>
+        <v>337878.12833874481</v>
       </c>
       <c r="Y140" s="4">
         <f>Y139+Z139</f>
-        <v>236958.69160889552</v>
+        <v>220752.12927619604</v>
       </c>
       <c r="Z140" s="4">
         <f>Y140</f>
-        <v>236958.69160889552</v>
+        <v>220752.12927619604</v>
       </c>
       <c r="AA140" s="38" t="s">
-        <v>424</v>
-      </c>
-      <c r="AB140" s="52" t="s">
-        <v>426</v>
+        <v>391</v>
+      </c>
+      <c r="AB140" s="53" t="s">
+        <v>353</v>
+      </c>
+      <c r="AC140" s="54" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13075,73 +13621,77 @@
       </c>
       <c r="G141" s="4">
         <f>G139/G140</f>
-        <v>3.8439414578009576E-2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="4">
         <f>H139/H140</f>
-        <v>0.96156058542199041</v>
+        <v>1</v>
       </c>
       <c r="J141" s="4">
         <f>J139/J140</f>
-        <v>3.9424944047340565E-2</v>
+        <v>0</v>
       </c>
       <c r="K141" s="4">
         <f>K139/K140</f>
-        <v>0.96057505595265946</v>
+        <v>1</v>
       </c>
       <c r="M141" s="4">
         <f>M139/M140</f>
-        <v>4.3722948700806917E-2</v>
+        <v>0</v>
       </c>
       <c r="N141" s="4">
         <f>N139/N140</f>
-        <v>0.95627705129919316</v>
+        <v>1</v>
       </c>
       <c r="P141" s="4">
         <f>P139/P140</f>
-        <v>5.4531610856745689E-2</v>
+        <v>0</v>
       </c>
       <c r="Q141" s="4">
         <f>Q139/Q140</f>
-        <v>0.94546838914325426</v>
+        <v>1</v>
       </c>
       <c r="S141" s="4">
         <f>S139/S140</f>
-        <v>5.8257061855407535E-2</v>
+        <v>0</v>
       </c>
       <c r="T141" s="4">
         <f>T139/T140</f>
-        <v>0.94174293814459253</v>
+        <v>1</v>
       </c>
       <c r="V141" s="4">
         <f>V139/V140</f>
-        <v>0.12425721952399496</v>
+        <v>0</v>
       </c>
       <c r="W141" s="4">
         <f>W139/W140</f>
-        <v>0.87574278047600496</v>
+        <v>1</v>
       </c>
       <c r="Y141" s="4">
         <f>Y139/Y140</f>
-        <v>0.11428653701746266</v>
+        <v>0</v>
       </c>
       <c r="Z141" s="4">
         <f>Z139/Z140</f>
-        <v>0.88571346298253728</v>
+        <v>1</v>
       </c>
       <c r="AA141" s="38" t="s">
-        <v>428</v>
-      </c>
-      <c r="AB141" s="52" t="s">
-        <v>427</v>
+        <v>354</v>
+      </c>
+      <c r="AB141" s="53" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC141" s="54" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB142" s="52"/>
+      <c r="AB142" s="53"/>
+      <c r="AC142" s="54"/>
     </row>
     <row r="143" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F143" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -13157,11 +13707,12 @@
       <c r="W143" s="8"/>
       <c r="Y143" s="8"/>
       <c r="Z143" s="8"/>
-      <c r="AB143" s="52"/>
+      <c r="AB143" s="53"/>
+      <c r="AC143" s="54"/>
     </row>
     <row r="144" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="38" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C144" s="33" t="s">
         <v>163</v>
@@ -13171,132 +13722,146 @@
       </c>
       <c r="G144" s="4">
         <f>(G112 - G133 - G121)*$G$30</f>
-        <v>2223.2117181201452</v>
+        <v>0</v>
       </c>
       <c r="H144" s="4">
         <f>(H112 - H133 - H121)*$H$30+SUM(H91:H94)</f>
-        <v>36232.172031879854</v>
+        <v>36104.190999999999</v>
       </c>
       <c r="J144" s="4">
         <f>(J112 - J133 - J121)*$G$30</f>
-        <v>2084.4238554074132</v>
+        <v>0</v>
       </c>
       <c r="K144" s="4">
         <f>(K112 - K133 - K121)*$H$30+SUM(K91:K94)</f>
-        <v>33447.211823016281</v>
+        <v>33183.970417880526</v>
       </c>
       <c r="M144" s="4">
         <f>(M112 - M133 - M121)*$G$30</f>
-        <v>1929.437307269528</v>
+        <v>0</v>
       </c>
       <c r="N144" s="4">
         <f>(N112 - N133 - N121)*$H$30+SUM(N91:N94)</f>
-        <v>30590.343867813121</v>
+        <v>30175.176046879413</v>
       </c>
       <c r="P144" s="4">
         <f>(P112 - P133 - P121)*$G$30</f>
-        <v>1729.3769911958977</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="4">
         <f>(Q112 - Q133 - Q121)*$H$30+SUM(Q91:Q94)</f>
-        <v>27621.242311606977</v>
+        <v>27009.647776529317</v>
       </c>
       <c r="S144" s="4">
         <f>(S112 - S133 - S121)*$G$30</f>
-        <v>1493.8143064538199</v>
+        <v>0</v>
       </c>
       <c r="T144" s="4">
         <f>(T112 - T133 - T121)*$H$30+SUM(T91:T94)</f>
-        <v>24382.300139165654</v>
+        <v>24464.344728676238</v>
       </c>
       <c r="V144" s="4">
         <f>(V112 - V133 - V121)*$G$30</f>
-        <v>1414.1084612152006</v>
+        <v>0</v>
       </c>
       <c r="W144" s="4">
         <f>(W112 - W133 - W121)*$H$30+SUM(W91:W94)</f>
-        <v>24223.673488378809</v>
+        <v>24245.411357047091</v>
       </c>
       <c r="Y144" s="4">
         <f>(Y112 - Y133 - Y121)*$G$30</f>
-        <v>1359.1953827000175</v>
+        <v>0</v>
       </c>
       <c r="Z144" s="4">
         <f>(Z112 - Z133 - Z121)*$H$30+SUM(Z91:Z94)</f>
-        <v>24156.603765901902</v>
-      </c>
-      <c r="AA144" s="38"/>
-      <c r="AB144" s="52"/>
+        <v>24163.802947564651</v>
+      </c>
+      <c r="AA144" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB144" s="53" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC144" s="54" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="145" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B145" s="38" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>163</v>
       </c>
       <c r="G145" s="4">
         <f>G144*$G21</f>
-        <v>666.96351543604351</v>
+        <v>0</v>
       </c>
       <c r="H145" s="4">
         <f>H144*$H21</f>
-        <v>9058.0430079699636</v>
+        <v>9026.0477499999997</v>
       </c>
       <c r="J145" s="4">
         <f>J144*$G21</f>
-        <v>625.32715662222392</v>
+        <v>0</v>
       </c>
       <c r="K145" s="4">
         <f>K144*$H21</f>
-        <v>8361.8029557540704</v>
+        <v>8295.9926044701315</v>
       </c>
       <c r="M145" s="4">
         <f>M144*$G21</f>
-        <v>578.83119218085835</v>
+        <v>0</v>
       </c>
       <c r="N145" s="4">
         <f>N144*$H21</f>
-        <v>7647.5859669532801</v>
+        <v>7543.7940117198532</v>
       </c>
       <c r="P145" s="4">
         <f>P144*$G21</f>
-        <v>518.81309735876926</v>
+        <v>0</v>
       </c>
       <c r="Q145" s="4">
         <f>Q144*$H21</f>
-        <v>6905.3105779017442</v>
+        <v>6752.4119441323292</v>
       </c>
       <c r="S145" s="4">
         <f>S144*$G21</f>
-        <v>448.14429193614598</v>
+        <v>0</v>
       </c>
       <c r="T145" s="4">
         <f>T144*$H21</f>
-        <v>6095.5750347914136</v>
+        <v>6116.0861821690596</v>
       </c>
       <c r="V145" s="4">
         <f>V144*$G21</f>
-        <v>424.23253836456018</v>
+        <v>0</v>
       </c>
       <c r="W145" s="4">
         <f>W144*$H21</f>
-        <v>6055.9183720947021</v>
+        <v>6061.3528392617727</v>
       </c>
       <c r="Y145" s="4">
         <f>Y144*$G21</f>
-        <v>407.75861481000521</v>
+        <v>0</v>
       </c>
       <c r="Z145" s="4">
         <f>Z144*$H21</f>
-        <v>6039.1509414754755</v>
-      </c>
-      <c r="AA145" s="38"/>
-      <c r="AB145" s="52"/>
+        <v>6040.9507368911627</v>
+      </c>
+      <c r="AA145" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB145" s="53" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC145" s="54" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="146" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B146" s="38" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>163</v>
@@ -13306,62 +13871,69 @@
       </c>
       <c r="G146" s="4">
         <f>G133*$G21</f>
-        <v>22932.474244558285</v>
+        <v>0</v>
       </c>
       <c r="H146" s="4">
         <f>(H133+G132)*$H21</f>
-        <v>478045.8547962014</v>
+        <v>498425</v>
       </c>
       <c r="J146" s="4">
         <f>J133*$G21</f>
-        <v>24099.982024304907</v>
+        <v>0</v>
       </c>
       <c r="K146" s="4">
         <f>(K133+J132)*$H21</f>
-        <v>489323.06988305371</v>
+        <v>510902.29746569326</v>
       </c>
       <c r="M146" s="4">
         <f>M133*$G21</f>
-        <v>27542.012522627068</v>
+        <v>0</v>
       </c>
       <c r="N146" s="4">
         <f>(N133+M132)*$H21</f>
-        <v>501982.66022363817</v>
+        <v>526256.32443655387</v>
       </c>
       <c r="P146" s="4">
         <f>P133*$G21</f>
-        <v>35906.368620980211</v>
+        <v>0</v>
       </c>
       <c r="Q146" s="4">
         <f>(Q133+P132)*$H21</f>
-        <v>518786.8095632976</v>
+        <v>550219.49483389896</v>
       </c>
       <c r="S146" s="4">
         <f>S133*$G21</f>
-        <v>41982.079335371513</v>
+        <v>0</v>
       </c>
       <c r="T146" s="4">
         <f>(T133+S132)*$H21</f>
-        <v>565544.12294312997</v>
+        <v>455260.13045221305</v>
       </c>
       <c r="V146" s="4">
         <f>V133*$G21</f>
-        <v>12751.607707149564</v>
+        <v>0</v>
       </c>
       <c r="W146" s="4">
         <f>(W133+V132)*$H21</f>
-        <v>74892.552399084554</v>
+        <v>84469.532084686201</v>
       </c>
       <c r="Y146" s="4">
         <f>Y133*$G21</f>
-        <v>8124.356484050867</v>
+        <v>0</v>
       </c>
       <c r="Z146" s="4">
         <f>(Z133+Y132)*$H21</f>
-        <v>52469.375832181489</v>
-      </c>
-      <c r="AA146" s="38"/>
-      <c r="AB146" s="52"/>
+        <v>55188.032319049009</v>
+      </c>
+      <c r="AA146" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB146" s="53" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC146" s="54" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="147" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B147" s="38" t="s">
@@ -13375,7 +13947,7 @@
       </c>
       <c r="G147" s="4">
         <f>G121-G124*G125-G122</f>
-        <v>2175</v>
+        <v>0</v>
       </c>
       <c r="H147" s="4">
         <f>H121-G124*H125-H122+H54</f>
@@ -13383,54 +13955,61 @@
       </c>
       <c r="J147" s="4">
         <f>J121-J124*J125-J122</f>
-        <v>2553.6682270231522</v>
+        <v>0</v>
       </c>
       <c r="K147" s="4">
         <f>K121-J124*K125-K122+K54</f>
-        <v>2749.6662244491781</v>
+        <v>2738.9186302400958</v>
       </c>
       <c r="M147" s="4">
         <f>M121-M124*M125-M122</f>
-        <v>2247.3642961427208</v>
+        <v>0</v>
       </c>
       <c r="N147" s="4">
         <f>N121-M124*N125-N122+N54</f>
-        <v>2150.9145738675443</v>
+        <v>2132.015251621935</v>
       </c>
       <c r="P147" s="4">
         <f>P121-P124*P125-P122</f>
-        <v>2528.8860607810102</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="4">
         <f>Q121-P124*Q125-Q122+Q54</f>
-        <v>3970.3423721656281</v>
+        <v>3909.4374276017033</v>
       </c>
       <c r="S147" s="4">
         <f>S121-S124*S125-S122</f>
-        <v>3233.485543462959</v>
+        <v>0</v>
       </c>
       <c r="T147" s="4">
         <f>T121-S124*T125-T122+T54</f>
-        <v>716.29459674366728</v>
+        <v>698.05606326293889</v>
       </c>
       <c r="V147" s="4">
         <f>V121-V124*V125-V122</f>
-        <v>2779.5242885485477</v>
+        <v>0</v>
       </c>
       <c r="W147" s="4">
         <f>W121-V124*W125-W122+W54</f>
-        <v>1640.3911750361863</v>
+        <v>1646.9794064741623</v>
       </c>
       <c r="Y147" s="4">
         <f>Y121-Y124*Y125-Y122</f>
-        <v>2623.5844614534308</v>
+        <v>0</v>
       </c>
       <c r="Z147" s="4">
         <f>Z121-Y124*Z125-Z122+Z54</f>
-        <v>1864.3672357973865</v>
-      </c>
-      <c r="AA147" s="38"/>
-      <c r="AB147" s="52"/>
+        <v>1866.5258081229777</v>
+      </c>
+      <c r="AA147" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB147" s="53" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC147" s="54" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="148" spans="2:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B148" s="38" t="s">
@@ -13444,7 +14023,7 @@
       </c>
       <c r="G148" s="4">
         <f>MAX((G121 - G122)*$G21-G16*G9,0)</f>
-        <v>2128.25</v>
+        <v>0</v>
       </c>
       <c r="H148" s="4">
         <f>MAX((H121-H122+H54)*$H21-H16*H9,0)</f>
@@ -13452,65 +14031,72 @@
       </c>
       <c r="J148" s="4">
         <f>MAX((J121 - J122)*$G21-J16*J9,0)</f>
-        <v>2494.538827023151</v>
+        <v>0</v>
       </c>
       <c r="K148" s="4">
         <f>MAX((K121-K122+K54)*$H21-K16*K9,0)</f>
-        <v>2084.4125203743147</v>
+        <v>2075.4561918667464</v>
       </c>
       <c r="M148" s="4">
         <f>MAX((M121 - M122)*$G21-M16*M9,0)</f>
-        <v>2190.9650961427201</v>
+        <v>0</v>
       </c>
       <c r="N148" s="4">
         <f>MAX((N121-N122+N54)*$H21-N16*N9,0)</f>
-        <v>1615.5584115562865</v>
+        <v>1599.8089763516123</v>
       </c>
       <c r="P148" s="4">
         <f>MAX((P121 - P122)*$G21-P16*P9,0)</f>
-        <v>2467.3630607810096</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="4">
         <f>MAX((Q121-Q122+Q54)*$H21-Q16*Q9,0)</f>
-        <v>2943.6650434713565</v>
+        <v>2892.9109230014201</v>
       </c>
       <c r="S148" s="4">
         <f>MAX((S121 - S122)*$G21-S16*S9,0)</f>
-        <v>3136.2455434629583</v>
+        <v>0</v>
       </c>
       <c r="T148" s="4">
         <f>MAX((T121-T122+T54)*$H21-T16*T9,0)</f>
-        <v>521.28336395305598</v>
+        <v>506.08458605244897</v>
       </c>
       <c r="V148" s="4">
         <f>MAX((V121 - V122)*$G21-V16*V9,0)</f>
-        <v>2704.3876885485497</v>
+        <v>0</v>
       </c>
       <c r="W148" s="4">
         <f>MAX((W121-W122+W54)*$H21-W16*W9,0)</f>
-        <v>1145.2326458634884</v>
+        <v>1150.7228387284683</v>
       </c>
       <c r="Y148" s="4">
         <f>MAX((Y121 - Y122)*$G21-Y16*Y9,0)</f>
-        <v>2530.1218614534314</v>
+        <v>0</v>
       </c>
       <c r="Z148" s="4">
         <f>MAX((Z121-Z122+Z54)*$H21-Z16*Z9,0)</f>
-        <v>1353.1913631644886</v>
-      </c>
-      <c r="AA148" s="38"/>
-      <c r="AB148" s="52"/>
+        <v>1354.9901734358141</v>
+      </c>
+      <c r="AA148" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="AB148" s="53" t="s">
+        <v>421</v>
+      </c>
+      <c r="AC148" s="54" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="149" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>163</v>
       </c>
       <c r="G149" s="4">
         <f>J111*J7*(1+$G21)</f>
-        <v>3880.5</v>
+        <v>0</v>
       </c>
       <c r="H149" s="4">
         <f>(K111*K7+SUMPRODUCT(H38:H41,H86:H89))*(1+$H21)</f>
@@ -13518,7 +14104,7 @@
       </c>
       <c r="J149" s="4">
         <f>M111*M7*(1+$G21)</f>
-        <v>3856.32</v>
+        <v>0</v>
       </c>
       <c r="K149" s="4">
         <f>(N111*N7+SUMPRODUCT(K38:K41,K86:K89))*(1+$H21)</f>
@@ -13526,7 +14112,7 @@
       </c>
       <c r="M149" s="4">
         <f>P111*P7*(1+$G21)</f>
-        <v>3833.7000000000003</v>
+        <v>0</v>
       </c>
       <c r="N149" s="4">
         <f>(Q111*Q7+SUMPRODUCT(N38:N41,N86:N89))*(1+$H21)</f>
@@ -13534,7 +14120,7 @@
       </c>
       <c r="P149" s="4">
         <f>S111*S7*(1+$G21)</f>
-        <v>3806.4</v>
+        <v>0</v>
       </c>
       <c r="Q149" s="4">
         <f>(T111*T7+SUMPRODUCT(Q38:Q41,Q86:Q89))*(1+$H21)</f>
@@ -13542,7 +14128,7 @@
       </c>
       <c r="S149" s="4">
         <f>V111*V7*(1+$G21)</f>
-        <v>3767.4</v>
+        <v>0</v>
       </c>
       <c r="T149" s="4">
         <f>(W111*W7+SUMPRODUCT(T38:T41,T86:T89))*(1+$H21)</f>
@@ -13550,36 +14136,45 @@
       </c>
       <c r="V149" s="4">
         <f>Y111*Y7*(1+$G21)</f>
-        <v>3593.0636935346747</v>
+        <v>0</v>
       </c>
       <c r="W149" s="4">
         <f>(Z111*Z7+SUMPRODUCT(W38:W41,W86:W89))*(1+$H21)</f>
-        <v>248300.31050651748</v>
+        <v>250354.37158478529</v>
       </c>
       <c r="Y149" s="4" t="e">
         <f>AB111*AB7*(1+$G21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z149" s="4">
+      <c r="Z149" s="4" t="e">
         <f>(AC111*AC7+SUMPRODUCT(Z38:Z41,Z86:Z89))*(1+$H21)</f>
-        <v>129.19999999999999</v>
-      </c>
-      <c r="AA149" s="38"/>
-      <c r="AB149" s="52"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA149" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="AB149" s="53" t="s">
+        <v>422</v>
+      </c>
+      <c r="AC149" s="54" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="150" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB150" s="52"/>
+      <c r="AB150" s="53"/>
+      <c r="AC150" s="54"/>
     </row>
     <row r="151" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB151" s="52"/>
+      <c r="AB151" s="53"/>
+      <c r="AC151" s="54"/>
     </row>
     <row r="152" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B152" s="24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G152" s="4">
         <f>G147+G122</f>
-        <v>2425</v>
+        <v>0</v>
       </c>
       <c r="H152" s="4">
         <f>H147+H122</f>
@@ -13587,60 +14182,62 @@
       </c>
       <c r="J152" s="4">
         <f>J147+J122</f>
-        <v>2869.868227023152</v>
+        <v>0</v>
       </c>
       <c r="K152" s="4">
         <f>K147+K122</f>
-        <v>3827.6662244491781</v>
+        <v>3816.9186302400958</v>
       </c>
       <c r="M152" s="4">
         <f>M147+M122</f>
-        <v>2548.9642961427207</v>
+        <v>0</v>
       </c>
       <c r="N152" s="4">
         <f>N147+N122</f>
-        <v>3072.1145738675441</v>
+        <v>3053.2152516219348</v>
       </c>
       <c r="P152" s="4">
         <f>P147+P122</f>
-        <v>2857.8860607810102</v>
+        <v>0</v>
       </c>
       <c r="Q152" s="4">
         <f>Q147+Q122</f>
-        <v>5871.1423721656283</v>
+        <v>5810.2374276017035</v>
       </c>
       <c r="S152" s="4">
         <f>S147+S122</f>
-        <v>3753.485543462959</v>
+        <v>0</v>
       </c>
       <c r="T152" s="4">
         <f>T147+T122</f>
-        <v>1110.1945967436673</v>
+        <v>1091.9560632629389</v>
       </c>
       <c r="V152" s="4">
         <f>V147+V122</f>
-        <v>3181.3242885485479</v>
+        <v>0</v>
       </c>
       <c r="W152" s="4">
         <f>W147+W122</f>
-        <v>2795.3911750361863</v>
+        <v>2801.9794064741623</v>
       </c>
       <c r="Y152" s="4">
         <f>Y147+Y122</f>
-        <v>3123.384461453431</v>
+        <v>0</v>
       </c>
       <c r="Z152" s="4">
         <f>Z147+Z122</f>
-        <v>2908.3672357973865</v>
-      </c>
-      <c r="AB152" s="52"/>
+        <v>2910.5258081229777</v>
+      </c>
+      <c r="AB152" s="53"/>
+      <c r="AC152" s="54"/>
     </row>
     <row r="153" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB153" s="52"/>
+      <c r="AB153" s="53"/>
+      <c r="AC153" s="54"/>
     </row>
     <row r="154" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B154" s="38" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C154" s="33" t="s">
         <v>163</v>
@@ -13663,18 +14260,25 @@
       </c>
       <c r="S154" s="4">
         <f>S124+S133+T133</f>
-        <v>2411332.9098842405</v>
+        <v>1822669.3192897991</v>
       </c>
       <c r="V154" s="4">
         <f>V124+V133+W133</f>
-        <v>352388.70470186783</v>
+        <v>341721.08028718451</v>
       </c>
       <c r="Y154" s="4">
         <f>Y124+Y133+Z133</f>
-        <v>247430.57890248077</v>
-      </c>
-      <c r="AA154" s="38"/>
-      <c r="AB154" s="52"/>
+        <v>225107.35616181631</v>
+      </c>
+      <c r="AA154" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB154" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="AC154" s="54" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="155" spans="2:30" x14ac:dyDescent="0.2">
       <c r="G155" s="4">
@@ -13695,52 +14299,86 @@
       </c>
       <c r="S155" s="4">
         <f>S154/S33</f>
-        <v>0.80377763662808011</v>
+        <v>0.60755643976326634</v>
       </c>
       <c r="V155" s="4">
         <f>V154/V33</f>
-        <v>1.4095548188074713E-2</v>
+        <v>1.366884321148738E-2</v>
       </c>
       <c r="Y155" s="4">
         <f>Y154/Y33</f>
-        <v>9.8186737659714599E-2</v>
-      </c>
+        <v>8.9328315937228689E-2</v>
+      </c>
+      <c r="AA155" s="38"/>
+      <c r="AB155" s="53"/>
+      <c r="AC155" s="54"/>
+    </row>
+    <row r="156" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B156" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="C156" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA156" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="AB156" s="53" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC156" s="54" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="157" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B157" s="38"/>
+      <c r="AA157" s="38"/>
+      <c r="AB157" s="53"/>
+      <c r="AC157" s="54"/>
+    </row>
+    <row r="158" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AA158" s="38"/>
+      <c r="AB158" s="53"/>
+      <c r="AC158" s="54"/>
+    </row>
+    <row r="159" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AA159" s="38"/>
+      <c r="AB159" s="53"/>
+      <c r="AC159" s="54"/>
     </row>
     <row r="160" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB160" s="51">
-        <v>0.1225</v>
-      </c>
-      <c r="AC160">
-        <f>SUM(AB$6:AB160)</f>
-        <v>0.1225</v>
-      </c>
+      <c r="AA160" s="38"/>
+      <c r="AB160" s="53"/>
+      <c r="AC160" s="54"/>
       <c r="AD160">
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="28:30" x14ac:dyDescent="0.2">
-      <c r="AB161" s="51">
-        <v>0.12239999999999999</v>
-      </c>
-      <c r="AC161">
-        <f>SUM(AB$6:AB161)</f>
-        <v>0.24490000000000001</v>
-      </c>
+    <row r="161" spans="27:30" x14ac:dyDescent="0.2">
+      <c r="AA161" s="38"/>
+      <c r="AB161" s="53"/>
+      <c r="AC161" s="54"/>
       <c r="AD161">
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="28:30" x14ac:dyDescent="0.2">
-      <c r="AB162" s="51">
-        <v>0.12230000000000001</v>
-      </c>
-      <c r="AC162">
-        <f>SUM(AB$6:AB162)</f>
-        <v>0.36720000000000003</v>
-      </c>
+    <row r="162" spans="27:30" x14ac:dyDescent="0.2">
+      <c r="AA162" s="38"/>
+      <c r="AB162" s="53"/>
+      <c r="AC162" s="54"/>
       <c r="AD162">
         <v>20</v>
       </c>
+    </row>
+    <row r="163" spans="27:30" x14ac:dyDescent="0.2">
+      <c r="AA163" s="38"/>
+      <c r="AB163" s="53"/>
+      <c r="AC163" s="54"/>
+    </row>
+    <row r="164" spans="27:30" x14ac:dyDescent="0.2">
+      <c r="AA164" s="38"/>
+      <c r="AB164" s="53"/>
+      <c r="AC164" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="36">

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07306AE-55B5-2F40-9E05-17D9F0059831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DF1C0F-5C91-4848-9A35-540414953B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8240" yWindow="760" windowWidth="34560" windowHeight="20060" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="-3860" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="480">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -997,9 +997,6 @@
     <t>\overline{Y}_{alloc}(t, u)</t>
   </si>
   <si>
-    <t>\overline{Y}_{alloc\_aux}(t, u)</t>
-  </si>
-  <si>
     <t>\Psi^{(y)}(t, u)</t>
   </si>
   <si>
@@ -1279,9 +1276,6 @@
     <t>Matrix ($n_T \times 2$) storing removals from original forests by type (columns), excluding conversions.</t>
   </si>
   <si>
-    <t>Matrix ($n_T \times 2$) storing removals from all forests byt ype (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
-  </si>
-  <si>
     <t>Matrix ($n_T \times 2$) giving fraction of original forest stock available when compared to healthy (unperturbed) baseline.</t>
   </si>
   <si>
@@ -1481,6 +1475,12 @@
   </si>
   <si>
     <t>d_{rmv}(t)</t>
+  </si>
+  <si>
+    <t>\overline{Y}_{aux}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing removals from all forests by type (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
   </si>
 </sst>
 </file>
@@ -6961,16 +6961,16 @@
     <col min="10" max="11" width="13.33203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="11.83203125" style="5" customWidth="1"/>
     <col min="13" max="14" width="13.33203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="21.1640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="21.1640625" style="4" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" style="5" customWidth="1"/>
-    <col min="19" max="20" width="13.33203125" style="4" customWidth="1"/>
-    <col min="21" max="21" width="9.1640625" style="5" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" style="4" customWidth="1"/>
-    <col min="23" max="23" width="12.5" style="4" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" style="5" customWidth="1"/>
-    <col min="25" max="26" width="13.33203125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="21.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" style="4" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="4" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
     <col min="28" max="28" width="64.5" style="58" customWidth="1"/>
     <col min="29" max="29" width="14.6640625" style="59" customWidth="1"/>
@@ -7145,7 +7145,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7195,7 +7195,7 @@
         <v>313</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AD5" s="36" t="s">
         <v>230</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="7" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
@@ -7362,10 +7362,10 @@
         <v>290</v>
       </c>
       <c r="AB7" s="53" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AC7" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7392,7 +7392,7 @@
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
@@ -7463,10 +7463,10 @@
         <v>279</v>
       </c>
       <c r="AB8" s="53" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AC8" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="9" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>222</v>
@@ -7550,10 +7550,10 @@
         <v>281</v>
       </c>
       <c r="AB9" s="53" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC9" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7580,7 +7580,7 @@
     </row>
     <row r="10" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>221</v>
@@ -7626,7 +7626,7 @@
         <v>302</v>
       </c>
       <c r="AC10" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="11" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>219</v>
@@ -7687,7 +7687,7 @@
         <v>303</v>
       </c>
       <c r="AC11" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="12" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>220</v>
@@ -7741,7 +7741,7 @@
         <v>304</v>
       </c>
       <c r="AC12" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7756,7 +7756,7 @@
     </row>
     <row r="13" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>158</v>
@@ -7830,7 +7830,7 @@
         <v>298</v>
       </c>
       <c r="AC13" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7838,7 +7838,7 @@
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>223</v>
@@ -7871,13 +7871,13 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AB14" s="53" t="s">
         <v>305</v>
       </c>
       <c r="AC14" s="54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>244</v>
@@ -7949,13 +7949,13 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AB15" s="53" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AC15" s="54" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7963,7 +7963,7 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>286</v>
@@ -8028,13 +8028,13 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AB16" s="53" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AC16" s="54" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="17" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
@@ -8060,13 +8060,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="AB17" s="53" t="s">
         <v>453</v>
       </c>
-      <c r="AB17" s="53" t="s">
-        <v>455</v>
-      </c>
       <c r="AC17" s="54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -8081,10 +8081,10 @@
     </row>
     <row r="18" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
@@ -8102,13 +8102,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="AB18" s="53" t="s">
         <v>454</v>
       </c>
-      <c r="AB18" s="53" t="s">
-        <v>456</v>
-      </c>
       <c r="AC18" s="54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -8123,7 +8123,7 @@
     </row>
     <row r="19" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>224</v>
@@ -8145,7 +8145,7 @@
         <v>299</v>
       </c>
       <c r="AC19" s="54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="20" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>226</v>
@@ -8178,13 +8178,13 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AB20" s="53" t="s">
         <v>300</v>
       </c>
       <c r="AC20" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -8199,7 +8199,7 @@
     </row>
     <row r="21" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>228</v>
@@ -8223,7 +8223,7 @@
         <v>301</v>
       </c>
       <c r="AC21" s="55" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="22" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>275</v>
@@ -8251,13 +8251,13 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AB22" s="53" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AC22" s="54" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AE22" s="19">
         <v>12</v>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="23" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>227</v>
@@ -8292,13 +8292,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AB23" s="53" t="s">
         <v>306</v>
       </c>
       <c r="AC23" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -8327,7 +8327,7 @@
     </row>
     <row r="25" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>159</v>
@@ -8381,13 +8381,13 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AB25" s="53" t="s">
         <v>307</v>
       </c>
       <c r="AC25" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE25" s="19">
         <v>10</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="26" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>274</v>
@@ -8442,13 +8442,13 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AB26" s="53" t="s">
         <v>308</v>
       </c>
       <c r="AC26" s="54" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AE26" s="19">
         <v>6</v>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="27" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>160</v>
@@ -8531,13 +8531,13 @@
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AB27" s="53" t="s">
         <v>309</v>
       </c>
       <c r="AC27" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AE27" s="19">
         <v>3</v>
@@ -8583,7 +8583,7 @@
     </row>
     <row r="29" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>273</v>
@@ -8604,18 +8604,18 @@
         <v>0.92</v>
       </c>
       <c r="AA29" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB29" s="53" t="s">
         <v>338</v>
       </c>
-      <c r="AB29" s="53" t="s">
-        <v>339</v>
-      </c>
       <c r="AC29" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>229</v>
@@ -8640,13 +8640,13 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AB30" s="53" t="s">
         <v>310</v>
       </c>
       <c r="AC30" s="54" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -8677,7 +8677,7 @@
     </row>
     <row r="33" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B33" s="38" t="s">
         <v>168</v>
@@ -8716,7 +8716,7 @@
         <v>311</v>
       </c>
       <c r="AC33" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.2">
@@ -8827,7 +8827,7 @@
     </row>
     <row r="38" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B38" s="37" t="s">
         <v>314</v>
@@ -8918,18 +8918,18 @@
         <v>85</v>
       </c>
       <c r="AA38" s="38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AB38" s="53" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AC38" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B39" s="38" t="s">
         <v>315</v>
@@ -9017,18 +9017,18 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AB39" s="53" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AC39" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B40" s="38" t="s">
         <v>316</v>
@@ -9115,13 +9115,13 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AB40" s="53" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AC40" s="54" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9219,7 +9219,7 @@
     </row>
     <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B43" s="46" t="s">
         <v>189</v>
@@ -9261,10 +9261,10 @@
         <v>293</v>
       </c>
       <c r="AB43" s="53" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AC43" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9379,6 +9379,9 @@
       <c r="AC46" s="54"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A47" s="19" t="s">
+        <v>456</v>
+      </c>
       <c r="B47" s="38" t="s">
         <v>190</v>
       </c>
@@ -9418,10 +9421,10 @@
         <v>294</v>
       </c>
       <c r="AB47" s="53" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AC47" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9473,13 +9476,13 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB49" s="53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AC49" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -9636,13 +9639,13 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB53" s="53" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AC53" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
@@ -9680,13 +9683,13 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB54" s="53" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AC54" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
@@ -9736,10 +9739,10 @@
         <v>295</v>
       </c>
       <c r="AB56" s="53" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AC56" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -9896,10 +9899,10 @@
         <v>296</v>
       </c>
       <c r="AB60" s="53" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AC60" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
@@ -9909,7 +9912,7 @@
     </row>
     <row r="62" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B62" s="46" t="s">
         <v>178</v>
@@ -9949,13 +9952,13 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AB62" s="53" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AC62" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -10065,10 +10068,10 @@
     </row>
     <row r="66" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>162</v>
@@ -10077,13 +10080,13 @@
         <v>49</v>
       </c>
       <c r="AA66" s="38" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AB66" s="53" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AC66" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.2">
@@ -10133,10 +10136,10 @@
         <v>297</v>
       </c>
       <c r="AB68" s="53" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AC68" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" spans="1:32" ht="17" x14ac:dyDescent="0.2">
@@ -10243,7 +10246,7 @@
     </row>
     <row r="73" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B73" s="46" t="s">
         <v>231</v>
@@ -10282,13 +10285,13 @@
         <v>0</v>
       </c>
       <c r="AA73" s="38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AB73" s="53" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AC73" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="74" spans="1:32" ht="17" x14ac:dyDescent="0.2">
@@ -10408,7 +10411,7 @@
     </row>
     <row r="77" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A77" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>232</v>
@@ -10448,13 +10451,13 @@
         <v>0</v>
       </c>
       <c r="AA77" s="56" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="AB77" s="53" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AC77" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AF77" t="s">
         <v>106</v>
@@ -10474,10 +10477,10 @@
     </row>
     <row r="79" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C79" s="44" t="s">
         <v>174</v>
@@ -10510,10 +10513,10 @@
         <v>317</v>
       </c>
       <c r="AB79" s="53" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AC79" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AD79" t="s">
         <v>86</v>
@@ -10521,10 +10524,10 @@
     </row>
     <row r="80" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C80" s="44"/>
       <c r="F80" s="14" t="s">
@@ -10587,13 +10590,13 @@
         <v>0</v>
       </c>
       <c r="AA80" s="38" t="s">
-        <v>318</v>
+        <v>478</v>
       </c>
       <c r="AB80" s="53" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AC80" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -10836,10 +10839,10 @@
     </row>
     <row r="86" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C86" s="44" t="s">
         <v>174</v>
@@ -10900,21 +10903,21 @@
         <v>0.6</v>
       </c>
       <c r="AA86" s="37" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AB86" s="53" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AC86" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A87" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C87" s="44"/>
       <c r="F87" s="14" t="s">
@@ -10973,13 +10976,13 @@
         <v>0.36</v>
       </c>
       <c r="AA87" s="37" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AB87" s="53" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AC87" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -11150,13 +11153,13 @@
         <v>9.8621113109027395E-2</v>
       </c>
       <c r="AA91" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AB91" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AC91" s="54" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -11280,7 +11283,7 @@
     </row>
     <row r="96" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B96" s="45" t="s">
         <v>207</v>
@@ -11320,13 +11323,13 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA96" s="38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AB96" s="53" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AC96" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="97" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -11489,13 +11492,13 @@
         <v>28.429343624434111</v>
       </c>
       <c r="AA101" s="38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AB101" s="53" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AC101" s="54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="102" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -11783,13 +11786,13 @@
         <v>24936000</v>
       </c>
       <c r="AA109" s="38" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AB109" s="53" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AC109" s="54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -11857,13 +11860,13 @@
         <v>0.87277215440147748</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AB110" s="53" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AC110" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -11933,13 +11936,13 @@
         <v>0.80295038204935931</v>
       </c>
       <c r="AA111" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AB111" s="53" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AC111" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12009,13 +12012,13 @@
         <v>15618862.859584641</v>
       </c>
       <c r="AA112" s="38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AB112" s="53" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC112" s="54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="113" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12085,13 +12088,13 @@
         <v>62.635799083993589</v>
       </c>
       <c r="AA113" s="38" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AB113" s="53" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AC113" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="2:29" ht="34" x14ac:dyDescent="0.2">
@@ -12161,13 +12164,13 @@
         <v>24.834906083993587</v>
       </c>
       <c r="AA114" s="38" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AB114" s="57" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AC114" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="2:29" x14ac:dyDescent="0.2">
@@ -12305,13 +12308,13 @@
         <v>215.49749504124878</v>
       </c>
       <c r="AA118" s="38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AB118" s="53" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AC118" s="54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12381,13 +12384,13 @@
         <v>15619078.357079683</v>
       </c>
       <c r="AA119" s="38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AB119" s="53" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AC119" s="54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12457,13 +12460,13 @@
         <v>3904769.5892699207</v>
       </c>
       <c r="AA120" s="38" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AB120" s="53" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AC120" s="54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12533,13 +12536,13 @@
         <v>7265.7526937432567</v>
       </c>
       <c r="AA121" s="38" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB121" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC121" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12609,13 +12612,13 @@
         <v>1044</v>
       </c>
       <c r="AA122" s="38" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AB122" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC122" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12685,13 +12688,13 @@
         <v>4355.2268856202791</v>
       </c>
       <c r="AA123" s="38" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AB123" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC123" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12733,13 +12736,13 @@
         <v>4355.2268856202791</v>
       </c>
       <c r="AA124" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="AB124" s="53" t="s">
         <v>347</v>
       </c>
-      <c r="AB124" s="53" t="s">
-        <v>348</v>
-      </c>
       <c r="AC124" s="54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="125" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12809,13 +12812,13 @@
         <v>1</v>
       </c>
       <c r="AA125" s="38" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AB125" s="53" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AC125" s="54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="2:29" ht="34" x14ac:dyDescent="0.2">
@@ -12885,13 +12888,13 @@
         <v>4960623.4808412148</v>
       </c>
       <c r="AA126" s="38" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AB126" s="53" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AC126" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="127" spans="2:29" x14ac:dyDescent="0.2">
@@ -12958,13 +12961,13 @@
         <v>2515644.7731143795</v>
       </c>
       <c r="AA129" s="38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AB129" s="53" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AC129" s="54" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13006,13 +13009,13 @@
         <v>220752.12927619604</v>
       </c>
       <c r="AA130" s="38" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AB130" s="53" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AC130" s="54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13054,13 +13057,13 @@
         <v>2294892.6438381835</v>
       </c>
       <c r="AA131" s="38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AB131" s="53" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AC131" s="54" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13102,13 +13105,13 @@
         <v>0</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AB132" s="53" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AC132" s="54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="133" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13178,13 +13181,13 @@
         <v>220752.12927619604</v>
       </c>
       <c r="AA133" s="38" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AB133" s="53" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AC133" s="54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13254,13 +13257,13 @@
         <v>220752.12927619604</v>
       </c>
       <c r="AA134" s="38" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AB134" s="53" t="s">
-        <v>412</v>
+        <v>479</v>
       </c>
       <c r="AC134" s="54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13351,13 +13354,13 @@
         <v>0.39928074986661122</v>
       </c>
       <c r="AA136" s="38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AB136" s="53" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AC136" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD136">
         <v>20</v>
@@ -13433,13 +13436,13 @@
         <v>4.4500883836231256E-2</v>
       </c>
       <c r="AA137" s="39" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AB137" s="53" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AC137" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AD137">
         <v>20</v>
@@ -13521,13 +13524,13 @@
         <v>220752.12927619604</v>
       </c>
       <c r="AA139" s="38" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AB139" s="53" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AC139" s="54" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AD139">
         <v>20</v>
@@ -13600,13 +13603,13 @@
         <v>220752.12927619604</v>
       </c>
       <c r="AA140" s="38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AB140" s="53" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AC140" s="54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13676,13 +13679,13 @@
         <v>1</v>
       </c>
       <c r="AA141" s="38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AB141" s="53" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AC141" s="54" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.2">
@@ -13777,13 +13780,13 @@
         <v>24163.802947564651</v>
       </c>
       <c r="AA144" s="38" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AB144" s="53" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AC144" s="54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="145" spans="2:30" x14ac:dyDescent="0.2">
@@ -13850,13 +13853,13 @@
         <v>6040.9507368911627</v>
       </c>
       <c r="AA145" s="38" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB145" s="53" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AC145" s="54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="146" spans="2:30" ht="17" x14ac:dyDescent="0.2">
@@ -13926,13 +13929,13 @@
         <v>55188.032319049009</v>
       </c>
       <c r="AA146" s="38" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB146" s="53" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AC146" s="54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="147" spans="2:30" ht="17" x14ac:dyDescent="0.2">
@@ -14002,13 +14005,13 @@
         <v>1866.5258081229777</v>
       </c>
       <c r="AA147" s="38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AB147" s="53" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AC147" s="54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148" spans="2:30" ht="17" x14ac:dyDescent="0.2">
@@ -14078,13 +14081,13 @@
         <v>1354.9901734358141</v>
       </c>
       <c r="AA148" s="38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB148" s="53" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AC148" s="54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="149" spans="2:30" x14ac:dyDescent="0.2">
@@ -14151,13 +14154,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="AA149" s="38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AB149" s="53" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AC149" s="54" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="150" spans="2:30" x14ac:dyDescent="0.2">
@@ -14271,13 +14274,13 @@
         <v>225107.35616181631</v>
       </c>
       <c r="AA154" s="38" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AB154" s="53" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AC154" s="54" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="155" spans="2:30" x14ac:dyDescent="0.2">
@@ -14315,19 +14318,19 @@
     </row>
     <row r="156" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B156" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C156" s="31" t="s">
         <v>162</v>
       </c>
       <c r="AA156" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB156" s="53" t="s">
         <v>394</v>
       </c>
-      <c r="AB156" s="53" t="s">
+      <c r="AC156" s="54" t="s">
         <v>395</v>
-      </c>
-      <c r="AC156" s="54" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="157" spans="2:30" x14ac:dyDescent="0.2">

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DF1C0F-5C91-4848-9A35-540414953B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4510B7CF-81D4-9047-B8C9-3D7CF0029853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3860" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="7820" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="480">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -1105,9 +1105,6 @@
     <t>\Phi_{avail}</t>
   </si>
   <si>
-    <t>\Psi^{(0)}_{seq}</t>
-  </si>
-  <si>
     <t>\Psi^{(0)}_{rmvsat}</t>
   </si>
   <si>
@@ -1153,9 +1150,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>\overline{B}^{(0)}</t>
-  </si>
-  <si>
     <t>\overline{B_{avail}}</t>
   </si>
   <si>
@@ -1481,6 +1475,12 @@
   </si>
   <si>
     <t>Matrix ($n_T \times 2$) storing removals from all forests by type (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
+  </si>
+  <si>
+    <t>\overline{b}^{(0)}</t>
+  </si>
+  <si>
+    <t>xf</t>
   </si>
 </sst>
 </file>
@@ -1745,39 +1745,6 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1803,6 +1770,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2340,60 +2340,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48" t="s">
+      <c r="G1" s="56"/>
+      <c r="H1" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="48"/>
-      <c r="J1" s="47" t="s">
+      <c r="I1" s="57"/>
+      <c r="J1" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="47"/>
-      <c r="L1" s="49" t="s">
+      <c r="K1" s="56"/>
+      <c r="L1" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="49"/>
-      <c r="N1" s="43" t="s">
+      <c r="M1" s="58"/>
+      <c r="N1" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="49" t="s">
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="50" t="s">
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="V1" s="50"/>
+      <c r="V1" s="59"/>
       <c r="W1" s="4" t="s">
         <v>46</v>
       </c>
       <c r="X1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AC1" s="47" t="s">
+      <c r="AC1" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="56"/>
+      <c r="AG1" s="56"/>
+      <c r="AH1" s="56"/>
       <c r="AI1" s="7" t="s">
         <v>37</v>
       </c>
@@ -6930,16 +6930,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="R1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6959,8 +6959,8 @@
     <col min="8" max="8" width="15.1640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
     <col min="10" max="11" width="13.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" style="5" customWidth="1"/>
-    <col min="13" max="14" width="13.33203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="21.1640625" style="5" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="21.1640625" style="4" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="13.33203125" style="4" hidden="1" customWidth="1"/>
@@ -6972,8 +6972,8 @@
     <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
     <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
-    <col min="28" max="28" width="64.5" style="58" customWidth="1"/>
-    <col min="29" max="29" width="14.6640625" style="59" customWidth="1"/>
+    <col min="28" max="28" width="64.5" style="47" customWidth="1"/>
+    <col min="29" max="29" width="14.6640625" style="48" customWidth="1"/>
     <col min="30" max="30" width="14.6640625" customWidth="1"/>
     <col min="31" max="33" width="14.1640625" customWidth="1"/>
     <col min="34" max="34" width="4.1640625" customWidth="1"/>
@@ -7013,7 +7013,7 @@
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="24"/>
-      <c r="AB1" s="51"/>
+      <c r="AB1" s="40"/>
       <c r="AC1" s="27"/>
     </row>
     <row r="2" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -7028,10 +7028,10 @@
       <c r="H2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="54">
         <v>150</v>
       </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="54"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -7051,7 +7051,7 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="24"/>
-      <c r="AB2" s="51"/>
+      <c r="AB2" s="40"/>
       <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -7064,10 +7064,10 @@
       <c r="H3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="54">
         <v>30</v>
       </c>
-      <c r="J3" s="43"/>
+      <c r="J3" s="54"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -7085,7 +7085,7 @@
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="24"/>
-      <c r="AB3" s="51"/>
+      <c r="AB3" s="40"/>
       <c r="AC3" s="27"/>
     </row>
     <row r="4" spans="1:41" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -7123,13 +7123,13 @@
         <v>6</v>
       </c>
       <c r="Z4" s="20"/>
-      <c r="AB4" s="51"/>
+      <c r="AB4" s="40"/>
       <c r="AC4" s="27"/>
-      <c r="AE4" s="42" t="s">
+      <c r="AE4" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="42"/>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="53"/>
       <c r="AL4" t="s">
         <v>94</v>
       </c>
@@ -7145,7 +7145,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7159,43 +7159,43 @@
       <c r="F5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="55"/>
       <c r="I5" s="17"/>
-      <c r="J5" s="41" t="s">
+      <c r="J5" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="41"/>
-      <c r="M5" s="41" t="s">
+      <c r="K5" s="55"/>
+      <c r="M5" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="41"/>
-      <c r="P5" s="41" t="s">
+      <c r="N5" s="55"/>
+      <c r="P5" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="Q5" s="41"/>
-      <c r="S5" s="41" t="s">
+      <c r="Q5" s="55"/>
+      <c r="S5" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="T5" s="41"/>
-      <c r="V5" s="41" t="s">
+      <c r="T5" s="55"/>
+      <c r="V5" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="W5" s="41"/>
-      <c r="Y5" s="41" t="s">
+      <c r="W5" s="55"/>
+      <c r="Y5" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="Z5" s="41"/>
+      <c r="Z5" s="55"/>
       <c r="AA5" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="AB5" s="51" t="s">
+      <c r="AB5" s="40" t="s">
         <v>313</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AD5" s="36" t="s">
         <v>230</v>
@@ -7266,7 +7266,7 @@
       <c r="Z6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB6" s="51"/>
+      <c r="AB6" s="40"/>
       <c r="AC6" s="27"/>
       <c r="AE6" s="19">
         <v>0</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="7" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
@@ -7305,14 +7305,14 @@
         <v>67</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H7" s="4">
         <v>250000</v>
       </c>
       <c r="J7" s="4">
         <f>G13</f>
-        <v>0</v>
+        <v>49950</v>
       </c>
       <c r="K7" s="4">
         <f>H13</f>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="M7" s="4">
         <f>J13</f>
-        <v>0</v>
+        <v>49888</v>
       </c>
       <c r="N7" s="4">
         <f>K13</f>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="P7" s="4">
         <f>M13</f>
-        <v>0</v>
+        <v>49830</v>
       </c>
       <c r="Q7" s="4">
         <f>N13</f>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="S7" s="4">
         <f>P13</f>
-        <v>0</v>
+        <v>49760</v>
       </c>
       <c r="T7" s="4">
         <f>Q13</f>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="V7" s="4">
         <f>S13</f>
-        <v>0</v>
+        <v>49660</v>
       </c>
       <c r="W7" s="4">
         <f>T13</f>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="Y7" s="4">
         <f>V7-V9</f>
-        <v>-98</v>
+        <v>49562</v>
       </c>
       <c r="Z7" s="4">
         <f>MAX(W7-W9,0)</f>
@@ -7361,11 +7361,11 @@
       <c r="AA7" s="38" t="s">
         <v>290</v>
       </c>
-      <c r="AB7" s="53" t="s">
-        <v>397</v>
-      </c>
-      <c r="AC7" s="54" t="s">
-        <v>364</v>
+      <c r="AB7" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC7" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7392,7 +7392,7 @@
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G8" s="4">
         <f>G7</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H8" s="4">
         <f>H7</f>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="J8" s="4">
         <f>J7</f>
-        <v>0</v>
+        <v>49950</v>
       </c>
       <c r="K8" s="4">
         <f>H8-H9+H12</f>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="M8" s="4">
         <f>M7</f>
-        <v>0</v>
+        <v>49888</v>
       </c>
       <c r="N8" s="4">
         <f>K8-K9+K12</f>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P8" s="4">
         <f>P7</f>
-        <v>0</v>
+        <v>49830</v>
       </c>
       <c r="Q8" s="4">
         <f>N8-N9+N12</f>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="S8" s="4">
         <f>S7</f>
-        <v>0</v>
+        <v>49760</v>
       </c>
       <c r="T8" s="4">
         <f>Q8-Q9+Q12</f>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="V8" s="4">
         <f>V7</f>
-        <v>0</v>
+        <v>49660</v>
       </c>
       <c r="W8" s="4">
         <f>T8-T9+T12</f>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="Y8" s="4">
         <f>Y7</f>
-        <v>-98</v>
+        <v>49562</v>
       </c>
       <c r="Z8" s="4">
         <f>W8-W9+W12</f>
@@ -7462,11 +7462,11 @@
       <c r="AA8" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="AB8" s="53" t="s">
-        <v>398</v>
-      </c>
-      <c r="AC8" s="54" t="s">
-        <v>364</v>
+      <c r="AB8" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC8" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="9" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>222</v>
@@ -7549,11 +7549,11 @@
       <c r="AA9" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="AB9" s="53" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC9" s="54" t="s">
-        <v>364</v>
+      <c r="AB9" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC9" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7580,7 +7580,7 @@
     </row>
     <row r="10" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>221</v>
@@ -7622,11 +7622,11 @@
       <c r="AA10" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="AB10" s="53" t="s">
+      <c r="AB10" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="AC10" s="54" t="s">
-        <v>365</v>
+      <c r="AC10" s="43" t="s">
+        <v>364</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="11" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>219</v>
@@ -7683,11 +7683,11 @@
       <c r="AA11" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="AB11" s="53" t="s">
+      <c r="AB11" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="AC11" s="54" t="s">
-        <v>365</v>
+      <c r="AC11" s="43" t="s">
+        <v>364</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="12" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>220</v>
@@ -7737,11 +7737,11 @@
       <c r="AA12" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="AB12" s="53" t="s">
+      <c r="AB12" s="42" t="s">
         <v>304</v>
       </c>
-      <c r="AC12" s="54" t="s">
-        <v>364</v>
+      <c r="AC12" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7756,7 +7756,7 @@
     </row>
     <row r="13" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>158</v>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="G13" s="4">
         <f>MAX(G7-G9,0)</f>
-        <v>0</v>
+        <v>49950</v>
       </c>
       <c r="H13" s="4">
         <f>MAX(H7-H9,0)</f>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="J13" s="4">
         <f>MAX(J7-J9,0)</f>
-        <v>0</v>
+        <v>49888</v>
       </c>
       <c r="K13" s="4">
         <f>MAX(K7-K9,0)</f>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="M13" s="4">
         <f>MAX(M7-M9,0)</f>
-        <v>0</v>
+        <v>49830</v>
       </c>
       <c r="N13" s="4">
         <f>MAX(N7-N9,0)</f>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="P13" s="4">
         <f>MAX(P7-P9,0)</f>
-        <v>0</v>
+        <v>49760</v>
       </c>
       <c r="Q13" s="4">
         <f>MAX(Q7-Q9,0)</f>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="S13" s="4">
         <f>MAX(S7-S9,0)</f>
-        <v>0</v>
+        <v>49660</v>
       </c>
       <c r="T13" s="4">
         <f>MAX(T7-T9,0)</f>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="V13" s="4">
         <f>MAX(V7-V9,0)</f>
-        <v>0</v>
+        <v>49562</v>
       </c>
       <c r="W13" s="4">
         <f>MAX(W7-W9,0)</f>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Y13" s="4">
         <f>MAX(Y7-Y9,0)</f>
-        <v>0</v>
+        <v>49464</v>
       </c>
       <c r="Z13" s="4">
         <f>MAX(Z7-Z9,0)</f>
@@ -7826,11 +7826,11 @@
       <c r="AA13" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="AB13" s="53" t="s">
+      <c r="AB13" s="42" t="s">
         <v>298</v>
       </c>
-      <c r="AC13" s="54" t="s">
-        <v>364</v>
+      <c r="AC13" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7838,7 +7838,7 @@
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>223</v>
@@ -7873,11 +7873,11 @@
       <c r="AA14" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="AB14" s="53" t="s">
+      <c r="AB14" s="42" t="s">
         <v>305</v>
       </c>
-      <c r="AC14" s="54" t="s">
-        <v>380</v>
+      <c r="AC14" s="43" t="s">
+        <v>378</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>244</v>
@@ -7949,13 +7949,13 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>367</v>
-      </c>
-      <c r="AB15" s="53" t="s">
-        <v>399</v>
-      </c>
-      <c r="AC15" s="54" t="s">
-        <v>381</v>
+        <v>366</v>
+      </c>
+      <c r="AB15" s="42" t="s">
+        <v>397</v>
+      </c>
+      <c r="AC15" s="43" t="s">
+        <v>379</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7963,7 +7963,7 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>286</v>
@@ -8028,13 +8028,13 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="AB16" s="53" t="s">
-        <v>400</v>
-      </c>
-      <c r="AC16" s="54" t="s">
-        <v>381</v>
+        <v>367</v>
+      </c>
+      <c r="AB16" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC16" s="43" t="s">
+        <v>379</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="17" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
@@ -8060,13 +8060,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="AB17" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="AB17" s="53" t="s">
-        <v>453</v>
-      </c>
-      <c r="AC17" s="54" t="s">
-        <v>382</v>
+      <c r="AC17" s="43" t="s">
+        <v>380</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -8081,15 +8081,15 @@
     </row>
     <row r="18" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="52" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="10" t="s">
@@ -8102,13 +8102,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="AB18" s="42" t="s">
         <v>452</v>
       </c>
-      <c r="AB18" s="53" t="s">
-        <v>454</v>
-      </c>
-      <c r="AC18" s="54" t="s">
-        <v>382</v>
+      <c r="AC18" s="43" t="s">
+        <v>380</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -8123,7 +8123,7 @@
     </row>
     <row r="19" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>224</v>
@@ -8131,7 +8131,7 @@
       <c r="C19" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="40"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="10" t="s">
         <v>138</v>
       </c>
@@ -8141,11 +8141,11 @@
       <c r="AA19" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="AB19" s="53" t="s">
+      <c r="AB19" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="AC19" s="54" t="s">
-        <v>382</v>
+      <c r="AC19" s="43" t="s">
+        <v>380</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="20" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>226</v>
@@ -8178,13 +8178,13 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="AB20" s="53" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB20" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="AC20" s="54" t="s">
-        <v>369</v>
+      <c r="AC20" s="43" t="s">
+        <v>368</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -8199,7 +8199,7 @@
     </row>
     <row r="21" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>228</v>
@@ -8219,11 +8219,11 @@
       <c r="AA21" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="AB21" s="53" t="s">
+      <c r="AB21" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="AC21" s="55" t="s">
-        <v>383</v>
+      <c r="AC21" s="44" t="s">
+        <v>381</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="22" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>275</v>
@@ -8251,13 +8251,13 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="AB22" s="53" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC22" s="54" t="s">
-        <v>464</v>
+        <v>461</v>
+      </c>
+      <c r="AB22" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC22" s="43" t="s">
+        <v>462</v>
       </c>
       <c r="AE22" s="19">
         <v>12</v>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="23" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>227</v>
@@ -8292,13 +8292,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="AB23" s="53" t="s">
+        <v>369</v>
+      </c>
+      <c r="AB23" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="AC23" s="54" t="s">
-        <v>369</v>
+      <c r="AC23" s="43" t="s">
+        <v>368</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -8312,8 +8312,8 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="AB24" s="51"/>
-      <c r="AC24" s="54"/>
+      <c r="AB24" s="40"/>
+      <c r="AC24" s="43"/>
       <c r="AE24" s="19">
         <v>12</v>
       </c>
@@ -8327,7 +8327,7 @@
     </row>
     <row r="25" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>159</v>
@@ -8381,13 +8381,13 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>458</v>
-      </c>
-      <c r="AB25" s="53" t="s">
+        <v>456</v>
+      </c>
+      <c r="AB25" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="AC25" s="54" t="s">
-        <v>364</v>
+      <c r="AC25" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE25" s="19">
         <v>10</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="26" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>274</v>
@@ -8442,13 +8442,13 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>457</v>
-      </c>
-      <c r="AB26" s="53" t="s">
+        <v>455</v>
+      </c>
+      <c r="AB26" s="42" t="s">
         <v>308</v>
       </c>
-      <c r="AC26" s="54" t="s">
-        <v>365</v>
+      <c r="AC26" s="43" t="s">
+        <v>364</v>
       </c>
       <c r="AE26" s="19">
         <v>6</v>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="27" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>160</v>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="G27" s="4">
         <f>MIN(G13,G25)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H27" s="4">
         <f>MIN(H13,H25)</f>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="J27" s="4">
         <f>MIN(J13,J25)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K27" s="4">
         <f>MIN(K13,K25)</f>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="M27" s="4">
         <f>MIN(M13,M25)</f>
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="N27" s="4">
         <f>MIN(N13,N25)</f>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="P27" s="4">
         <f>MIN(P13,P25)</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="Q27" s="4">
         <f>MIN(Q13,Q25)</f>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="S27" s="4">
         <f>MIN(S13,S25)</f>
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="T27" s="4">
         <f>MIN(T13,T25)</f>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="V27" s="4">
         <f>MIN(V13,V25)</f>
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="W27" s="4">
         <f>MIN(W13,W25)</f>
@@ -8524,20 +8524,20 @@
       </c>
       <c r="Y27" s="4">
         <f>MIN(Y13,Y25)</f>
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="Z27" s="4">
         <f>MIN(Z13,Z25)</f>
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>459</v>
-      </c>
-      <c r="AB27" s="53" t="s">
+        <v>457</v>
+      </c>
+      <c r="AB27" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="AC27" s="54" t="s">
-        <v>364</v>
+      <c r="AC27" s="43" t="s">
+        <v>363</v>
       </c>
       <c r="AE27" s="19">
         <v>3</v>
@@ -8568,8 +8568,8 @@
       <c r="W28" s="8"/>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="54"/>
+      <c r="AB28" s="40"/>
+      <c r="AC28" s="43"/>
       <c r="AE28" s="19">
         <v>1.8</v>
       </c>
@@ -8583,7 +8583,7 @@
     </row>
     <row r="29" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>273</v>
@@ -8591,7 +8591,7 @@
       <c r="C29" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="52" t="s">
         <v>170</v>
       </c>
       <c r="F29" s="25" t="s">
@@ -8606,16 +8606,16 @@
       <c r="AA29" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="AB29" s="53" t="s">
+      <c r="AB29" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="AC29" s="54" t="s">
-        <v>372</v>
+      <c r="AC29" s="43" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>229</v>
@@ -8623,7 +8623,7 @@
       <c r="C30" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="40"/>
+      <c r="E30" s="52"/>
       <c r="F30" s="25" t="s">
         <v>171</v>
       </c>
@@ -8640,19 +8640,19 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="AB30" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB30" s="42" t="s">
         <v>310</v>
       </c>
-      <c r="AC30" s="54" t="s">
-        <v>384</v>
+      <c r="AC30" s="43" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E31" s="26"/>
-      <c r="AB31" s="51"/>
-      <c r="AC31" s="54"/>
+      <c r="AB31" s="40"/>
+      <c r="AC31" s="43"/>
     </row>
     <row r="32" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="F32" s="15" t="s">
@@ -8672,12 +8672,12 @@
       <c r="W32" s="8"/>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
-      <c r="AB32" s="51"/>
-      <c r="AC32" s="54"/>
+      <c r="AB32" s="40"/>
+      <c r="AC32" s="43"/>
     </row>
     <row r="33" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B33" s="38" t="s">
         <v>168</v>
@@ -8712,16 +8712,16 @@
       <c r="AA33" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="AB33" s="53" t="s">
+      <c r="AB33" s="42" t="s">
         <v>311</v>
       </c>
-      <c r="AC33" s="54" t="s">
-        <v>373</v>
+      <c r="AC33" s="43" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB34" s="51"/>
-      <c r="AC34" s="54"/>
+      <c r="AB34" s="40"/>
+      <c r="AC34" s="43"/>
     </row>
     <row r="35" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
@@ -8741,8 +8741,8 @@
       <c r="W35" s="12"/>
       <c r="Y35" s="12"/>
       <c r="Z35" s="12"/>
-      <c r="AB35" s="51"/>
-      <c r="AC35" s="54"/>
+      <c r="AB35" s="40"/>
+      <c r="AC35" s="43"/>
     </row>
     <row r="36" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F36" s="15" t="s">
@@ -8764,8 +8764,8 @@
       <c r="P36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB36" s="51"/>
-      <c r="AC36" s="54"/>
+      <c r="AB36" s="40"/>
+      <c r="AC36" s="43"/>
       <c r="AD36" t="s">
         <v>77</v>
       </c>
@@ -8822,17 +8822,17 @@
       <c r="Z37" s="4">
         <v>0</v>
       </c>
-      <c r="AB37" s="51"/>
-      <c r="AC37" s="54"/>
+      <c r="AB37" s="40"/>
+      <c r="AC37" s="43"/>
     </row>
     <row r="38" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B38" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="C38" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F38" s="14" t="s">
@@ -8920,21 +8920,21 @@
       <c r="AA38" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="AB38" s="53" t="s">
-        <v>421</v>
-      </c>
-      <c r="AC38" s="54" t="s">
-        <v>364</v>
+      <c r="AB38" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="AC38" s="43" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B39" s="38" t="s">
         <v>315</v>
       </c>
-      <c r="C39" s="44"/>
+      <c r="C39" s="50"/>
       <c r="F39" s="14" t="s">
         <v>69</v>
       </c>
@@ -9019,21 +9019,21 @@
       <c r="AA39" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="AB39" s="53" t="s">
-        <v>422</v>
-      </c>
-      <c r="AC39" s="54" t="s">
-        <v>364</v>
+      <c r="AB39" s="42" t="s">
+        <v>420</v>
+      </c>
+      <c r="AC39" s="43" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B40" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="C40" s="44"/>
+      <c r="C40" s="50"/>
       <c r="F40" s="14" t="s">
         <v>79</v>
       </c>
@@ -9115,18 +9115,18 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="AB40" s="53" t="s">
-        <v>423</v>
-      </c>
-      <c r="AC40" s="54" t="s">
-        <v>364</v>
+        <v>356</v>
+      </c>
+      <c r="AB40" s="42" t="s">
+        <v>421</v>
+      </c>
+      <c r="AC40" s="43" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B41" s="38"/>
-      <c r="C41" s="44"/>
+      <c r="C41" s="50"/>
       <c r="F41" s="14" t="s">
         <v>80</v>
       </c>
@@ -9207,24 +9207,24 @@
         <v>43</v>
       </c>
       <c r="AA41" s="38"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="54"/>
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="43"/>
     </row>
     <row r="42" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F42" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB42" s="51"/>
-      <c r="AC42" s="54"/>
+      <c r="AB42" s="40"/>
+      <c r="AC42" s="43"/>
     </row>
     <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B43" s="46" t="s">
+        <v>454</v>
+      </c>
+      <c r="B43" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="C43" s="44" t="s">
+      <c r="C43" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F43" s="14" t="s">
@@ -9260,16 +9260,16 @@
       <c r="AA43" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="AB43" s="53" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC43" s="54" t="s">
-        <v>374</v>
+      <c r="AB43" s="42" t="s">
+        <v>422</v>
+      </c>
+      <c r="AC43" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B44" s="46"/>
-      <c r="C44" s="44"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="50"/>
       <c r="F44" s="14" t="s">
         <v>194</v>
       </c>
@@ -9301,12 +9301,12 @@
         <v>0</v>
       </c>
       <c r="AA44" s="38"/>
-      <c r="AB44" s="53"/>
-      <c r="AC44" s="54"/>
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="43"/>
     </row>
     <row r="45" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B45" s="46"/>
-      <c r="C45" s="44"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="50"/>
       <c r="F45" s="14" t="s">
         <v>195</v>
       </c>
@@ -9338,12 +9338,12 @@
         <v>0</v>
       </c>
       <c r="AA45" s="38"/>
-      <c r="AB45" s="53"/>
-      <c r="AC45" s="54"/>
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="43"/>
     </row>
     <row r="46" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B46" s="46"/>
-      <c r="C46" s="44"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="50"/>
       <c r="F46" s="14" t="s">
         <v>196</v>
       </c>
@@ -9375,12 +9375,12 @@
         <v>0</v>
       </c>
       <c r="AA46" s="38"/>
-      <c r="AB46" s="53"/>
-      <c r="AC46" s="54"/>
+      <c r="AB46" s="42"/>
+      <c r="AC46" s="43"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B47" s="38" t="s">
         <v>190</v>
@@ -9420,28 +9420,31 @@
       <c r="AA47" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="AB47" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="AC47" s="54" t="s">
-        <v>375</v>
+      <c r="AB47" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC47" s="43" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F48" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB48" s="51"/>
-      <c r="AC48" s="54"/>
+      <c r="AB48" s="40"/>
+      <c r="AC48" s="43"/>
     </row>
     <row r="49" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="46" t="s">
+      <c r="A49" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B49" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="40" t="s">
+      <c r="E49" s="52" t="s">
         <v>246</v>
       </c>
       <c r="F49" s="14" t="s">
@@ -9478,17 +9481,17 @@
       <c r="AA49" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="AB49" s="53" t="s">
-        <v>425</v>
-      </c>
-      <c r="AC49" s="54" t="s">
-        <v>374</v>
+      <c r="AB49" s="42" t="s">
+        <v>423</v>
+      </c>
+      <c r="AC49" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B50" s="46"/>
-      <c r="C50" s="44"/>
-      <c r="E50" s="40"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="50"/>
+      <c r="E50" s="52"/>
       <c r="F50" s="14" t="s">
         <v>247</v>
       </c>
@@ -9521,13 +9524,13 @@
         <v>0</v>
       </c>
       <c r="AA50" s="38"/>
-      <c r="AB50" s="53"/>
-      <c r="AC50" s="54"/>
+      <c r="AB50" s="42"/>
+      <c r="AC50" s="43"/>
     </row>
     <row r="51" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B51" s="46"/>
-      <c r="C51" s="44"/>
-      <c r="E51" s="40"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="50"/>
+      <c r="E51" s="52"/>
       <c r="F51" s="14" t="s">
         <v>248</v>
       </c>
@@ -9560,13 +9563,13 @@
         <v>0</v>
       </c>
       <c r="AA51" s="38"/>
-      <c r="AB51" s="53"/>
-      <c r="AC51" s="54"/>
+      <c r="AB51" s="42"/>
+      <c r="AC51" s="43"/>
     </row>
     <row r="52" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B52" s="46"/>
-      <c r="C52" s="44"/>
-      <c r="E52" s="40"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="50"/>
+      <c r="E52" s="52"/>
       <c r="F52" s="14" t="s">
         <v>249</v>
       </c>
@@ -9599,10 +9602,13 @@
         <v>0</v>
       </c>
       <c r="AA52" s="38"/>
-      <c r="AB52" s="53"/>
-      <c r="AC52" s="54"/>
+      <c r="AB52" s="42"/>
+      <c r="AC52" s="43"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A53" s="19" t="s">
+        <v>454</v>
+      </c>
       <c r="B53" s="38" t="s">
         <v>259</v>
       </c>
@@ -9641,14 +9647,17 @@
       <c r="AA53" s="38" t="s">
         <v>341</v>
       </c>
-      <c r="AB53" s="53" t="s">
-        <v>437</v>
-      </c>
-      <c r="AC53" s="54" t="s">
-        <v>375</v>
+      <c r="AB53" s="42" t="s">
+        <v>435</v>
+      </c>
+      <c r="AC53" s="43" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A54" s="19" t="s">
+        <v>454</v>
+      </c>
       <c r="B54" s="38" t="s">
         <v>261</v>
       </c>
@@ -9685,23 +9694,26 @@
       <c r="AA54" s="38" t="s">
         <v>340</v>
       </c>
-      <c r="AB54" s="53" t="s">
-        <v>438</v>
-      </c>
-      <c r="AC54" s="54" t="s">
-        <v>375</v>
+      <c r="AB54" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC54" s="43" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F55" s="14"/>
-      <c r="AB55" s="53"/>
-      <c r="AC55" s="54"/>
+      <c r="AB55" s="42"/>
+      <c r="AC55" s="43"/>
     </row>
     <row r="56" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="46" t="s">
+      <c r="A56" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B56" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="C56" s="44" t="s">
+      <c r="C56" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F56" s="14" t="s">
@@ -9738,16 +9750,16 @@
       <c r="AA56" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="AB56" s="53" t="s">
-        <v>426</v>
-      </c>
-      <c r="AC56" s="54" t="s">
-        <v>374</v>
+      <c r="AB56" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC56" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="57" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B57" s="46"/>
-      <c r="C57" s="44"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="50"/>
       <c r="F57" s="14" t="s">
         <v>198</v>
       </c>
@@ -9780,12 +9792,12 @@
         <v>0</v>
       </c>
       <c r="AA57" s="38"/>
-      <c r="AB57" s="53"/>
-      <c r="AC57" s="54"/>
+      <c r="AB57" s="42"/>
+      <c r="AC57" s="43"/>
     </row>
     <row r="58" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B58" s="46"/>
-      <c r="C58" s="44"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="50"/>
       <c r="F58" s="14" t="s">
         <v>199</v>
       </c>
@@ -9818,12 +9830,12 @@
         <v>0</v>
       </c>
       <c r="AA58" s="38"/>
-      <c r="AB58" s="53"/>
-      <c r="AC58" s="54"/>
+      <c r="AB58" s="42"/>
+      <c r="AC58" s="43"/>
     </row>
     <row r="59" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="46"/>
-      <c r="C59" s="44"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="50"/>
       <c r="F59" s="14" t="s">
         <v>200</v>
       </c>
@@ -9856,10 +9868,13 @@
         <v>0</v>
       </c>
       <c r="AA59" s="38"/>
-      <c r="AB59" s="53"/>
-      <c r="AC59" s="54"/>
+      <c r="AB59" s="42"/>
+      <c r="AC59" s="43"/>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A60" s="19" t="s">
+        <v>454</v>
+      </c>
       <c r="B60" s="38" t="s">
         <v>192</v>
       </c>
@@ -9898,26 +9913,26 @@
       <c r="AA60" s="38" t="s">
         <v>296</v>
       </c>
-      <c r="AB60" s="53" t="s">
-        <v>439</v>
-      </c>
-      <c r="AC60" s="54" t="s">
-        <v>375</v>
+      <c r="AB60" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="AC60" s="43" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F61" s="14"/>
-      <c r="AB61" s="53"/>
-      <c r="AC61" s="54"/>
+      <c r="AB61" s="42"/>
+      <c r="AC61" s="43"/>
     </row>
     <row r="62" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B62" s="46" t="s">
+        <v>454</v>
+      </c>
+      <c r="B62" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="44" t="s">
+      <c r="C62" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F62" s="14" t="s">
@@ -9954,16 +9969,16 @@
       <c r="AA62" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="AB62" s="53" t="s">
-        <v>427</v>
-      </c>
-      <c r="AC62" s="54" t="s">
-        <v>374</v>
+      <c r="AB62" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC62" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="63" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B63" s="46"/>
-      <c r="C63" s="44"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="50"/>
       <c r="F63" s="14" t="s">
         <v>91</v>
       </c>
@@ -9994,12 +10009,12 @@
         <v>0.36</v>
       </c>
       <c r="AA63" s="38"/>
-      <c r="AB63" s="53"/>
-      <c r="AC63" s="54"/>
+      <c r="AB63" s="42"/>
+      <c r="AC63" s="43"/>
     </row>
     <row r="64" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B64" s="46"/>
-      <c r="C64" s="44"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="50"/>
       <c r="F64" s="14" t="s">
         <v>92</v>
       </c>
@@ -10029,12 +10044,12 @@
         <v>0.2</v>
       </c>
       <c r="AA64" s="38"/>
-      <c r="AB64" s="53"/>
-      <c r="AC64" s="54"/>
+      <c r="AB64" s="42"/>
+      <c r="AC64" s="43"/>
     </row>
     <row r="65" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B65" s="46"/>
-      <c r="C65" s="44"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="50"/>
       <c r="F65" s="14" t="s">
         <v>93</v>
       </c>
@@ -10063,15 +10078,15 @@
         <v>0.12</v>
       </c>
       <c r="AA65" s="38"/>
-      <c r="AB65" s="53"/>
-      <c r="AC65" s="54"/>
+      <c r="AB65" s="42"/>
+      <c r="AC65" s="43"/>
     </row>
     <row r="66" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>162</v>
@@ -10080,25 +10095,28 @@
         <v>49</v>
       </c>
       <c r="AA66" s="38" t="s">
-        <v>460</v>
-      </c>
-      <c r="AB66" s="53" t="s">
-        <v>461</v>
-      </c>
-      <c r="AC66" s="54" t="s">
-        <v>375</v>
+        <v>458</v>
+      </c>
+      <c r="AB66" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="AC66" s="43" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.2">
       <c r="F67" s="14"/>
-      <c r="AB67" s="53"/>
-      <c r="AC67" s="54"/>
+      <c r="AB67" s="42"/>
+      <c r="AC67" s="43"/>
     </row>
     <row r="68" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B68" s="46" t="s">
+      <c r="A68" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B68" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="C68" s="44" t="s">
+      <c r="C68" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F68" s="14" t="s">
@@ -10113,38 +10131,38 @@
         <v>0.85</v>
       </c>
       <c r="N68" s="4">
-        <f>K68*(1- $G$30)+N38*N62</f>
+        <f>K68*(1- $G$30)*N38/K38+N38*N62</f>
         <v>5.0986655000000001</v>
       </c>
       <c r="Q68" s="4">
-        <f>N68*(1- $G$30)+Q38*Q62</f>
+        <f>N68*(1- $G$30)*Q38/N38+Q38*Q62</f>
         <v>15.290660595165001</v>
       </c>
       <c r="T68" s="4">
-        <f>Q68*(1- $G$30)+T38*T62</f>
+        <f>Q68*(1- $G$30)*T38/Q38+T38*T62</f>
         <v>32.266654258030592</v>
       </c>
       <c r="W68" s="4">
-        <f>T68*(1- $G$30)+W38*W62</f>
+        <f>T68*(1- $G$30)*W38/T38+W38*W62</f>
         <v>62.815995610845476</v>
       </c>
       <c r="Z68" s="4">
-        <f>W68*(1- $G$30)+Z38*Z62</f>
-        <v>113.71737449773644</v>
+        <f>W68*(1- $G$30)*Z38/W38+Z38*Z62</f>
+        <v>113.71737449773646</v>
       </c>
       <c r="AA68" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="AB68" s="53" t="s">
-        <v>428</v>
-      </c>
-      <c r="AC68" s="54" t="s">
-        <v>374</v>
+      <c r="AB68" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC68" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="69" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B69" s="46"/>
-      <c r="C69" s="44"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="50"/>
       <c r="F69" s="14" t="s">
         <v>110</v>
       </c>
@@ -10153,33 +10171,33 @@
         <v>0</v>
       </c>
       <c r="N69" s="4">
-        <f>K69*(1- $G$30)+N39*N63</f>
+        <f>K69*(1- $G$30)*N39/K39+N39*N63</f>
         <v>0.8</v>
       </c>
       <c r="Q69" s="4">
-        <f>N69*(1- $G$30)+Q39*Q63</f>
+        <f>N69*(1- $G$30)*Q39/N39+Q39*Q63</f>
         <v>4.7987440000000001</v>
       </c>
       <c r="T69" s="4">
-        <f>Q69*(1- $G$30)+T39*T63</f>
+        <f>Q69*(1- $G$30)*T39/Q39+T39*T63</f>
         <v>14.39120997192</v>
       </c>
       <c r="W69" s="4">
-        <f>T69*(1- $G$30)+W39*W63</f>
+        <f>T69*(1- $G$30)*W39/T39+W39*W63</f>
         <v>30.368615772264086</v>
       </c>
       <c r="Z69" s="4">
-        <f>W69*(1- $G$30)+Z39*Z63</f>
-        <v>59.120937045501634</v>
+        <f>W69*(1- $G$30)*Z39/W39+Z39*Z63</f>
+        <v>59.120937045501627</v>
       </c>
       <c r="AA69" s="38"/>
-      <c r="AB69" s="53"/>
-      <c r="AC69" s="54"/>
+      <c r="AB69" s="42"/>
+      <c r="AC69" s="43"/>
     </row>
     <row r="70" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B70" s="46"/>
-      <c r="C70" s="44"/>
-      <c r="E70" s="40"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="50"/>
+      <c r="E70" s="52"/>
       <c r="F70" s="14" t="s">
         <v>111</v>
       </c>
@@ -10188,29 +10206,29 @@
         <v>0</v>
       </c>
       <c r="Q70" s="4">
-        <f>N70*(1- $G$30)+Q40*Q64</f>
+        <f>N70*(1- $G$30)*Q40/N40+Q40*Q64</f>
         <v>0.92</v>
       </c>
       <c r="T70" s="4">
-        <f>Q70*(1- $G$30)+T40*T64</f>
+        <f>Q70*(1- $G$30)*T40/Q40+T40*T64</f>
         <v>5.5185556000000009</v>
       </c>
       <c r="W70" s="4">
-        <f>T70*(1- $G$30)+W40*W64</f>
+        <f>T70*(1- $G$30)*W40/T40+W40*W64</f>
         <v>16.549891467708001</v>
       </c>
       <c r="Z70" s="4">
-        <f>W70*(1- $G$30)+Z40*Z64</f>
+        <f>W70*(1- $G$30)*Z40/W40+Z40*Z64</f>
         <v>34.923908138103698</v>
       </c>
       <c r="AA70" s="38"/>
-      <c r="AB70" s="53"/>
-      <c r="AC70" s="54"/>
+      <c r="AB70" s="42"/>
+      <c r="AC70" s="43"/>
     </row>
     <row r="71" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B71" s="46"/>
-      <c r="C71" s="44"/>
-      <c r="E71" s="40"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="50"/>
+      <c r="E71" s="52"/>
       <c r="F71" s="14" t="s">
         <v>112</v>
       </c>
@@ -10223,35 +10241,35 @@
         <v>0</v>
       </c>
       <c r="T71" s="4">
-        <f>Q71*(1- $G$30)+T41*T65</f>
+        <f>Q71*(1- $G$30)*T41/Q41+T41*T65</f>
         <v>0.43</v>
       </c>
       <c r="W71" s="4">
-        <f>T71*(1- $G$30)+W41*W65</f>
+        <f>T71*(1- $G$30)*W41/T41+W41*W65</f>
         <v>2.5793249</v>
       </c>
       <c r="Z71" s="4">
-        <f>W71*(1- $G$30)+Z41*Z65</f>
+        <f>W71*(1- $G$30)*Z41/W41+Z41*Z65</f>
         <v>7.7352753599069999</v>
       </c>
       <c r="AA71" s="38"/>
-      <c r="AB71" s="53"/>
-      <c r="AC71" s="54"/>
+      <c r="AB71" s="42"/>
+      <c r="AC71" s="43"/>
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="E72" s="40"/>
+      <c r="E72" s="52"/>
       <c r="F72" s="14"/>
-      <c r="AB72" s="53"/>
-      <c r="AC72" s="54"/>
+      <c r="AB72" s="42"/>
+      <c r="AC72" s="43"/>
     </row>
     <row r="73" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B73" s="46" t="s">
+        <v>454</v>
+      </c>
+      <c r="B73" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="44" t="s">
+      <c r="C73" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F73" s="14" t="s">
@@ -10285,18 +10303,18 @@
         <v>0</v>
       </c>
       <c r="AA73" s="38" t="s">
-        <v>387</v>
-      </c>
-      <c r="AB73" s="53" t="s">
-        <v>429</v>
-      </c>
-      <c r="AC73" s="54" t="s">
-        <v>374</v>
+        <v>385</v>
+      </c>
+      <c r="AB73" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="AC73" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="74" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B74" s="46"/>
-      <c r="C74" s="44"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="50"/>
       <c r="F74" s="14" t="s">
         <v>128</v>
       </c>
@@ -10328,13 +10346,13 @@
         <v>0</v>
       </c>
       <c r="AA74" s="38"/>
-      <c r="AB74" s="53"/>
-      <c r="AC74" s="54"/>
+      <c r="AB74" s="42"/>
+      <c r="AC74" s="43"/>
     </row>
     <row r="75" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B75" s="46"/>
-      <c r="C75" s="44"/>
-      <c r="E75" s="40" t="s">
+      <c r="B75" s="51"/>
+      <c r="C75" s="50"/>
+      <c r="E75" s="52" t="s">
         <v>152</v>
       </c>
       <c r="F75" s="14" t="s">
@@ -10368,13 +10386,13 @@
         <v>0</v>
       </c>
       <c r="AA75" s="38"/>
-      <c r="AB75" s="53"/>
-      <c r="AC75" s="54"/>
+      <c r="AB75" s="42"/>
+      <c r="AC75" s="43"/>
     </row>
     <row r="76" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B76" s="46"/>
-      <c r="C76" s="44"/>
-      <c r="E76" s="40"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="50"/>
+      <c r="E76" s="52"/>
       <c r="F76" s="14" t="s">
         <v>130</v>
       </c>
@@ -10406,12 +10424,12 @@
         <v>0</v>
       </c>
       <c r="AA76" s="38"/>
-      <c r="AB76" s="53"/>
-      <c r="AC76" s="54"/>
+      <c r="AB76" s="42"/>
+      <c r="AC76" s="43"/>
     </row>
     <row r="77" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A77" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>232</v>
@@ -10419,7 +10437,7 @@
       <c r="C77" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E77" s="40"/>
+      <c r="E77" s="52"/>
       <c r="F77" s="14" t="s">
         <v>147</v>
       </c>
@@ -10450,24 +10468,24 @@
         <f>SUM(Z73:Z76)</f>
         <v>0</v>
       </c>
-      <c r="AA77" s="56" t="s">
-        <v>471</v>
-      </c>
-      <c r="AB77" s="53" t="s">
-        <v>440</v>
-      </c>
-      <c r="AC77" s="54" t="s">
-        <v>375</v>
+      <c r="AA77" s="45" t="s">
+        <v>469</v>
+      </c>
+      <c r="AB77" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="AC77" s="43" t="s">
+        <v>373</v>
       </c>
       <c r="AF77" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="E78" s="40"/>
+      <c r="E78" s="52"/>
       <c r="F78" s="14"/>
-      <c r="AB78" s="53"/>
-      <c r="AC78" s="54"/>
+      <c r="AB78" s="42"/>
+      <c r="AC78" s="43"/>
       <c r="AD78" t="s">
         <v>85</v>
       </c>
@@ -10477,12 +10495,12 @@
     </row>
     <row r="79" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>470</v>
-      </c>
-      <c r="C79" s="44" t="s">
+        <v>468</v>
+      </c>
+      <c r="C79" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F79" s="14" t="s">
@@ -10512,11 +10530,11 @@
       <c r="AA79" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="AB79" s="53" t="s">
-        <v>430</v>
-      </c>
-      <c r="AC79" s="54" t="s">
-        <v>374</v>
+      <c r="AB79" s="42" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC79" s="43" t="s">
+        <v>372</v>
       </c>
       <c r="AD79" t="s">
         <v>86</v>
@@ -10524,12 +10542,12 @@
     </row>
     <row r="80" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>469</v>
-      </c>
-      <c r="C80" s="44"/>
+        <v>467</v>
+      </c>
+      <c r="C80" s="50"/>
       <c r="F80" s="14" t="s">
         <v>148</v>
       </c>
@@ -10590,18 +10608,18 @@
         <v>0</v>
       </c>
       <c r="AA80" s="38" t="s">
-        <v>478</v>
-      </c>
-      <c r="AB80" s="53" t="s">
-        <v>431</v>
-      </c>
-      <c r="AC80" s="54" t="s">
-        <v>374</v>
+        <v>476</v>
+      </c>
+      <c r="AB80" s="42" t="s">
+        <v>429</v>
+      </c>
+      <c r="AC80" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B81" s="52"/>
-      <c r="C81" s="44"/>
+      <c r="B81" s="41"/>
+      <c r="C81" s="50"/>
       <c r="E81" s="22">
         <v>0</v>
       </c>
@@ -10665,12 +10683,12 @@
         <v>0</v>
       </c>
       <c r="AA81" s="37"/>
-      <c r="AB81" s="53"/>
-      <c r="AC81" s="54"/>
+      <c r="AB81" s="42"/>
+      <c r="AC81" s="43"/>
     </row>
     <row r="82" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B82" s="52"/>
-      <c r="C82" s="44"/>
+      <c r="B82" s="41"/>
+      <c r="C82" s="50"/>
       <c r="E82" s="22">
         <v>1</v>
       </c>
@@ -10734,12 +10752,12 @@
         <v>0</v>
       </c>
       <c r="AA82" s="37"/>
-      <c r="AB82" s="53"/>
-      <c r="AC82" s="54"/>
+      <c r="AB82" s="42"/>
+      <c r="AC82" s="43"/>
     </row>
     <row r="83" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B83" s="52"/>
-      <c r="C83" s="44"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="50"/>
       <c r="E83" s="22">
         <v>2</v>
       </c>
@@ -10803,16 +10821,16 @@
         <v>0</v>
       </c>
       <c r="AA83" s="37"/>
-      <c r="AB83" s="53"/>
-      <c r="AC83" s="54"/>
+      <c r="AB83" s="42"/>
+      <c r="AC83" s="43"/>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.2">
       <c r="E84" s="22">
         <v>3</v>
       </c>
       <c r="F84" s="14"/>
-      <c r="AB84" s="53"/>
-      <c r="AC84" s="54"/>
+      <c r="AB84" s="42"/>
+      <c r="AC84" s="43"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F85" s="14"/>
@@ -10834,17 +10852,17 @@
       <c r="Y85" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="AB85" s="53"/>
-      <c r="AC85" s="54"/>
+      <c r="AB85" s="42"/>
+      <c r="AC85" s="43"/>
     </row>
     <row r="86" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>468</v>
-      </c>
-      <c r="C86" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="C86" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F86" s="14" t="s">
@@ -10905,21 +10923,21 @@
       <c r="AA86" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="AB86" s="53" t="s">
-        <v>432</v>
-      </c>
-      <c r="AC86" s="54" t="s">
-        <v>374</v>
+      <c r="AB86" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC86" s="43" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A87" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>467</v>
-      </c>
-      <c r="C87" s="44"/>
+        <v>465</v>
+      </c>
+      <c r="C87" s="50"/>
       <c r="F87" s="14" t="s">
         <v>132</v>
       </c>
@@ -10978,16 +10996,16 @@
       <c r="AA87" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="AB87" s="53" t="s">
-        <v>466</v>
-      </c>
-      <c r="AC87" s="54" t="s">
-        <v>385</v>
+      <c r="AB87" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="AC87" s="43" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B88" s="37"/>
-      <c r="C88" s="44"/>
+      <c r="C88" s="50"/>
       <c r="F88" s="14" t="s">
         <v>133</v>
       </c>
@@ -11044,12 +11062,12 @@
         <v>0.2</v>
       </c>
       <c r="AA88" s="37"/>
-      <c r="AB88" s="53"/>
-      <c r="AC88" s="54"/>
+      <c r="AB88" s="42"/>
+      <c r="AC88" s="43"/>
     </row>
     <row r="89" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B89" s="52"/>
-      <c r="C89" s="44"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="50"/>
       <c r="F89" s="14" t="s">
         <v>134</v>
       </c>
@@ -11106,19 +11124,22 @@
         <v>0.12</v>
       </c>
       <c r="AA89" s="37"/>
-      <c r="AB89" s="53"/>
-      <c r="AC89" s="54"/>
+      <c r="AB89" s="42"/>
+      <c r="AC89" s="43"/>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F90" s="14"/>
-      <c r="AB90" s="53"/>
-      <c r="AC90" s="54"/>
+      <c r="AB90" s="42"/>
+      <c r="AC90" s="43"/>
     </row>
     <row r="91" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B91" s="45" t="s">
+      <c r="A91" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B91" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="C91" s="44" t="s">
+      <c r="C91" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F91" s="14" t="s">
@@ -11155,16 +11176,16 @@
       <c r="AA91" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="AB91" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="AC91" s="54" t="s">
+      <c r="AB91" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="AC91" s="43" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B92" s="45"/>
-      <c r="C92" s="44"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="50"/>
       <c r="F92" s="14" t="s">
         <v>204</v>
       </c>
@@ -11197,12 +11218,12 @@
         <v>4.7678726762454618E-2</v>
       </c>
       <c r="AA92" s="37"/>
-      <c r="AB92" s="53"/>
-      <c r="AC92" s="54"/>
+      <c r="AB92" s="42"/>
+      <c r="AC92" s="43"/>
     </row>
     <row r="93" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B93" s="45"/>
-      <c r="C93" s="44"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="50"/>
       <c r="F93" s="14" t="s">
         <v>205</v>
       </c>
@@ -11235,12 +11256,12 @@
         <v>2.5983329604301563E-2</v>
       </c>
       <c r="AA93" s="37"/>
-      <c r="AB93" s="53"/>
-      <c r="AC93" s="54"/>
+      <c r="AB93" s="42"/>
+      <c r="AC93" s="43"/>
     </row>
     <row r="94" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B94" s="45"/>
-      <c r="C94" s="44"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="50"/>
       <c r="F94" s="14" t="s">
         <v>206</v>
       </c>
@@ -11273,22 +11294,22 @@
         <v>4.049540093E-3</v>
       </c>
       <c r="AA94" s="37"/>
-      <c r="AB94" s="53"/>
-      <c r="AC94" s="54"/>
+      <c r="AB94" s="42"/>
+      <c r="AC94" s="43"/>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F95" s="14"/>
-      <c r="AB95" s="53"/>
-      <c r="AC95" s="54"/>
+      <c r="AB95" s="42"/>
+      <c r="AC95" s="43"/>
     </row>
     <row r="96" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B96" s="45" t="s">
+        <v>454</v>
+      </c>
+      <c r="B96" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="C96" s="44" t="s">
+      <c r="C96" s="50" t="s">
         <v>174</v>
       </c>
       <c r="F96" s="14" t="s">
@@ -11325,16 +11346,16 @@
       <c r="AA96" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="AB96" s="53" t="s">
-        <v>434</v>
-      </c>
-      <c r="AC96" s="54" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="97" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="45"/>
-      <c r="C97" s="44"/>
+      <c r="AB96" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC96" s="43" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B97" s="49"/>
+      <c r="C97" s="50"/>
       <c r="F97" s="14" t="s">
         <v>71</v>
       </c>
@@ -11367,12 +11388,12 @@
         <v>59.120937045501627</v>
       </c>
       <c r="AA97" s="37"/>
-      <c r="AB97" s="53"/>
-      <c r="AC97" s="54"/>
-    </row>
-    <row r="98" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B98" s="45"/>
-      <c r="C98" s="44"/>
+      <c r="AB97" s="42"/>
+      <c r="AC97" s="43"/>
+    </row>
+    <row r="98" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B98" s="49"/>
+      <c r="C98" s="50"/>
       <c r="F98" s="14" t="s">
         <v>72</v>
       </c>
@@ -11405,12 +11426,12 @@
         <v>34.923908138103698</v>
       </c>
       <c r="AA98" s="37"/>
-      <c r="AB98" s="53"/>
-      <c r="AC98" s="54"/>
-    </row>
-    <row r="99" spans="2:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="45"/>
-      <c r="C99" s="44"/>
+      <c r="AB98" s="42"/>
+      <c r="AC98" s="43"/>
+    </row>
+    <row r="99" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="49"/>
+      <c r="C99" s="50"/>
       <c r="F99" s="14" t="s">
         <v>81</v>
       </c>
@@ -11443,20 +11464,23 @@
         <v>7.7352753599069999</v>
       </c>
       <c r="AA99" s="37"/>
-      <c r="AB99" s="53"/>
-      <c r="AC99" s="54"/>
-    </row>
-    <row r="100" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AB99" s="42"/>
+      <c r="AC99" s="43"/>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
       <c r="E100" s="26"/>
       <c r="F100" s="14"/>
-      <c r="AB100" s="53"/>
-      <c r="AC100" s="54"/>
-    </row>
-    <row r="101" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B101" s="45" t="s">
+      <c r="AB100" s="42"/>
+      <c r="AC100" s="43"/>
+    </row>
+    <row r="101" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A101" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B101" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="44" t="s">
+      <c r="C101" s="50" t="s">
         <v>174</v>
       </c>
       <c r="E101" s="26"/>
@@ -11494,16 +11518,16 @@
       <c r="AA101" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="AB101" s="53" t="s">
-        <v>435</v>
-      </c>
-      <c r="AC101" s="54" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="102" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="45"/>
-      <c r="C102" s="44"/>
+      <c r="AB101" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC101" s="43" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="102" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B102" s="49"/>
+      <c r="C102" s="50"/>
       <c r="E102" s="26"/>
       <c r="F102" s="14" t="s">
         <v>210</v>
@@ -11537,12 +11561,12 @@
         <v>14.780234261375407</v>
       </c>
       <c r="AA102" s="37"/>
-      <c r="AB102" s="53"/>
-      <c r="AC102" s="54"/>
-    </row>
-    <row r="103" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B103" s="45"/>
-      <c r="C103" s="44"/>
+      <c r="AB102" s="42"/>
+      <c r="AC102" s="43"/>
+    </row>
+    <row r="103" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B103" s="49"/>
+      <c r="C103" s="50"/>
       <c r="E103" s="26"/>
       <c r="F103" s="14" t="s">
         <v>211</v>
@@ -11576,12 +11600,12 @@
         <v>8.7309770345259246</v>
       </c>
       <c r="AA103" s="37"/>
-      <c r="AB103" s="53"/>
-      <c r="AC103" s="54"/>
-    </row>
-    <row r="104" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="45"/>
-      <c r="C104" s="44"/>
+      <c r="AB103" s="42"/>
+      <c r="AC103" s="43"/>
+    </row>
+    <row r="104" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B104" s="49"/>
+      <c r="C104" s="50"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
         <v>212</v>
@@ -11615,28 +11639,28 @@
         <v>1.93381883997675</v>
       </c>
       <c r="AA104" s="37"/>
-      <c r="AB104" s="53"/>
-      <c r="AC104" s="54"/>
-    </row>
-    <row r="105" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AB104" s="42"/>
+      <c r="AC104" s="43"/>
+    </row>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B105" s="29"/>
       <c r="C105" s="35"/>
       <c r="E105" s="26"/>
       <c r="F105" s="14"/>
       <c r="AA105" s="29"/>
-      <c r="AB105" s="53"/>
-      <c r="AC105" s="54"/>
-    </row>
-    <row r="106" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AB105" s="42"/>
+      <c r="AC105" s="43"/>
+    </row>
+    <row r="106" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B106" s="29"/>
       <c r="C106" s="35"/>
       <c r="E106" s="26"/>
       <c r="F106" s="14"/>
       <c r="AA106" s="29"/>
-      <c r="AB106" s="53"/>
-      <c r="AC106" s="54"/>
-    </row>
-    <row r="107" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB106" s="42"/>
+      <c r="AC106" s="43"/>
+    </row>
+    <row r="107" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="E107" s="26"/>
       <c r="F107" s="15" t="s">
         <v>140</v>
@@ -11645,10 +11669,10 @@
         <v>124</v>
       </c>
       <c r="H107" s="8"/>
-      <c r="AB107" s="53"/>
-      <c r="AC107" s="54"/>
-    </row>
-    <row r="108" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB107" s="42"/>
+      <c r="AC107" s="43"/>
+    </row>
+    <row r="108" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B108" s="38" t="s">
         <v>234</v>
       </c>
@@ -11716,10 +11740,13 @@
         <v>0.92</v>
       </c>
       <c r="AA108" s="38"/>
-      <c r="AB108" s="53"/>
-      <c r="AC108" s="54"/>
-    </row>
-    <row r="109" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB108" s="42"/>
+      <c r="AC108" s="43"/>
+    </row>
+    <row r="109" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A109" s="19" t="s">
+        <v>454</v>
+      </c>
       <c r="B109" s="38" t="s">
         <v>235</v>
       </c>
@@ -11731,7 +11758,7 @@
       </c>
       <c r="G109" s="4">
         <f>G7*$G$20</f>
-        <v>0</v>
+        <v>7500000</v>
       </c>
       <c r="H109" s="4">
         <f>H7*$H$20</f>
@@ -11739,7 +11766,7 @@
       </c>
       <c r="J109" s="4">
         <f>J7*$G$20</f>
-        <v>0</v>
+        <v>7492500</v>
       </c>
       <c r="K109" s="4">
         <f>K7*$H$20</f>
@@ -11747,7 +11774,7 @@
       </c>
       <c r="M109" s="4">
         <f>M7*$G$20</f>
-        <v>0</v>
+        <v>7483200</v>
       </c>
       <c r="N109" s="4">
         <f>N7*$H$20</f>
@@ -11755,7 +11782,7 @@
       </c>
       <c r="P109" s="4">
         <f>P7*$G$20</f>
-        <v>0</v>
+        <v>7474500</v>
       </c>
       <c r="Q109" s="4">
         <f>Q7*$H$20</f>
@@ -11763,7 +11790,7 @@
       </c>
       <c r="S109" s="4">
         <f>S7*$G$20</f>
-        <v>0</v>
+        <v>7464000</v>
       </c>
       <c r="T109" s="4">
         <f>T7*$H$20</f>
@@ -11771,7 +11798,7 @@
       </c>
       <c r="V109" s="4">
         <f>V7*$G$20</f>
-        <v>0</v>
+        <v>7449000</v>
       </c>
       <c r="W109" s="4">
         <f>W7*$H$20</f>
@@ -11779,7 +11806,7 @@
       </c>
       <c r="Y109" s="4">
         <f>Y7*$G$20</f>
-        <v>-14700</v>
+        <v>7434300</v>
       </c>
       <c r="Z109" s="4">
         <f>Z7*$H$20</f>
@@ -11788,14 +11815,14 @@
       <c r="AA109" s="38" t="s">
         <v>330</v>
       </c>
-      <c r="AB109" s="53" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC109" s="54" t="s">
+      <c r="AB109" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="AC109" s="43" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="110" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B110" s="38" t="s">
         <v>181</v>
       </c>
@@ -11813,7 +11840,7 @@
       </c>
       <c r="J110" s="4">
         <f>IF(G112=0,0,MIN(MAX((G112/G109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" s="4">
         <f>IF(H112=0,0,MIN(MAX((H112/H109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11821,7 +11848,7 @@
       </c>
       <c r="M110" s="4">
         <f>IF(J112=0,0,MIN(MAX((J112/J109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N110" s="4">
         <f>IF(K112=0,0,MIN(MAX((K112/K109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11829,7 +11856,7 @@
       </c>
       <c r="P110" s="4">
         <f>IF(M112=0,0,MIN(MAX((M112/M109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="4">
         <f>IF(N112=0,0,MIN(MAX((N112/N109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11837,7 +11864,7 @@
       </c>
       <c r="S110" s="4">
         <f>IF(P112=0,0,MIN(MAX((P112/P109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" s="4">
         <f>IF(Q112=0,0,MIN(MAX((Q112/Q109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11845,7 +11872,7 @@
       </c>
       <c r="V110" s="4">
         <f>IF(S112=0,0,MIN(MAX((S112/S109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="4">
         <f>IF(T112=0,0,MIN(MAX((T112/T109-$H$17)/($G$19-$H$17), 0), 1))</f>
@@ -11853,23 +11880,23 @@
       </c>
       <c r="Y110" s="4">
         <f>IF(V112=0,0,MIN(MAX((V112/V109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0</v>
+        <v>0.86115188084024752</v>
       </c>
       <c r="Z110" s="4">
         <f>IF(W112=0,0,MIN(MAX((W112/W109-$H$17)/($G$19-$H$17), 0), 1))</f>
-        <v>0.87277215440147748</v>
+        <v>1</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>354</v>
-      </c>
-      <c r="AB110" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC110" s="54" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="111" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+      <c r="AB110" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC110" s="43" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B111" s="38" t="s">
         <v>182</v>
       </c>
@@ -11889,7 +11916,7 @@
       </c>
       <c r="J111" s="4">
         <f xml:space="preserve"> J108*J110</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K111" s="4">
         <f>K108*K110</f>
@@ -11897,7 +11924,7 @@
       </c>
       <c r="M111" s="4">
         <f xml:space="preserve"> M108*M110</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N111" s="4">
         <f>N108*N110</f>
@@ -11905,7 +11932,7 @@
       </c>
       <c r="P111" s="4">
         <f xml:space="preserve"> P108*P110</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q111" s="4">
         <f>Q108*Q110</f>
@@ -11913,7 +11940,7 @@
       </c>
       <c r="S111" s="4">
         <f xml:space="preserve"> S108*S110</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="T111" s="4">
         <f>T108*T110</f>
@@ -11921,7 +11948,7 @@
       </c>
       <c r="V111" s="4">
         <f xml:space="preserve"> V108*V110</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W111" s="4">
         <f>W108*W110</f>
@@ -11929,23 +11956,23 @@
       </c>
       <c r="Y111" s="4">
         <f xml:space="preserve"> Y108*Y110</f>
-        <v>0</v>
+        <v>0.25834556425207422</v>
       </c>
       <c r="Z111" s="4">
         <f>Z108*Z110</f>
-        <v>0.80295038204935931</v>
+        <v>0.92</v>
       </c>
       <c r="AA111" s="38" t="s">
         <v>331</v>
       </c>
-      <c r="AB111" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="AC111" s="54" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="112" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="AB111" s="42" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC111" s="43" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="112" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B112" s="38" t="s">
         <v>236</v>
       </c>
@@ -11957,7 +11984,7 @@
       </c>
       <c r="G112" s="4">
         <f>G7*G20</f>
-        <v>0</v>
+        <v>7500000</v>
       </c>
       <c r="H112" s="4">
         <f>H7*H20</f>
@@ -11965,59 +11992,59 @@
       </c>
       <c r="J112" s="4">
         <f>G112 - G133 - G121 - G144+J111*J7</f>
-        <v>0</v>
+        <v>6966918.08125271</v>
       </c>
       <c r="K112" s="4">
         <f>H112 - H133 - H121 - H144 + K111*K7</f>
-        <v>23190103.809</v>
+        <v>23723974.534997292</v>
       </c>
       <c r="M112" s="4">
         <f>J112 - J133 - J121 - J144+M111*M7</f>
-        <v>0</v>
+        <v>6430976.9232831635</v>
       </c>
       <c r="N112" s="4">
         <f>K112 - K133 - K121 - K144 + N111*N7</f>
-        <v>21332909.719951883</v>
+        <v>22403030.169761121</v>
       </c>
       <c r="P112" s="4">
         <f>M112 - M133 - M121 - M144+P111*P7</f>
-        <v>0</v>
+        <v>5878439.281534086</v>
       </c>
       <c r="Q112" s="4">
         <f>N112 - N133 - N121 - N144 + Q111*Q7</f>
-        <v>19419401.648653384</v>
+        <v>21042661.124617502</v>
       </c>
       <c r="S112" s="4">
         <f>P112 - P133 - P121 - P144+S111*S7</f>
-        <v>0</v>
+        <v>5319767.3068811921</v>
       </c>
       <c r="T112" s="4">
         <f>Q112 - Q133 - Q121 - Q144 + T111*T7</f>
-        <v>17406125.443449255</v>
+        <v>19588129.944080703</v>
       </c>
       <c r="V112" s="4">
         <f>S112 - S133 - S121 - S144+V111*V7</f>
-        <v>0</v>
+        <v>4639771.7535949051</v>
       </c>
       <c r="W112" s="4">
         <f>T112 - T133 - T121 - T144 + W111*W7</f>
-        <v>15787407.623367518</v>
+        <v>17473377.815496068</v>
       </c>
       <c r="Y112" s="4">
         <f>V112 - V133 - V121 - V144+Y111*Y7</f>
-        <v>0</v>
+        <v>4179370.6046086708</v>
       </c>
       <c r="Z112" s="4">
         <f>W112 - W133 - W121 - W144 + Z111*Z7</f>
-        <v>15618862.859584641</v>
+        <v>15778712.676320704</v>
       </c>
       <c r="AA112" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="AB112" s="53" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC112" s="54" t="s">
+      <c r="AB112" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC112" s="43" t="s">
         <v>329</v>
       </c>
     </row>
@@ -12033,7 +12060,7 @@
       </c>
       <c r="G113" s="4">
         <f>IF(G7=0,0,G112/G7)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H113" s="4">
         <f>IF(H7=0,0,H112/H7)</f>
@@ -12041,60 +12068,60 @@
       </c>
       <c r="J113" s="4">
         <f>IF(J7=0,0,J112/J7)</f>
-        <v>0</v>
+        <v>139.47783946451872</v>
       </c>
       <c r="K113" s="4">
         <f>IF(K7=0,0,K112/K7)</f>
-        <v>92.797534249699879</v>
+        <v>94.933871688664638</v>
       </c>
       <c r="M113" s="4">
         <f>IF(M7=0,0,M112/M7)</f>
-        <v>0</v>
+        <v>128.90829304207753</v>
       </c>
       <c r="N113" s="4">
         <f>IF(N7=0,0,N112/N7)</f>
-        <v>85.403377717089882</v>
+        <v>89.687458143885351</v>
       </c>
       <c r="P113" s="4">
         <f>IF(P7=0,0,P112/P7)</f>
-        <v>0</v>
+        <v>117.96988323367621</v>
       </c>
       <c r="Q113" s="4">
         <f>IF(Q7=0,0,Q112/Q7)</f>
-        <v>77.772177562529578</v>
+        <v>84.273120613135575</v>
       </c>
       <c r="S113" s="4">
         <f>IF(S7=0,0,S112/S7)</f>
-        <v>0</v>
+        <v>106.90850697108505</v>
       </c>
       <c r="T113" s="4">
         <f>IF(T7=0,0,T112/T7)</f>
-        <v>69.76291138999477</v>
+        <v>78.508280204248038</v>
       </c>
       <c r="V113" s="4">
         <f>IF(V7=0,0,V112/V7)</f>
-        <v>0</v>
+        <v>93.430764268926808</v>
       </c>
       <c r="W113" s="4">
         <f>IF(W7=0,0,W112/W7)</f>
-        <v>63.285060522989269</v>
+        <v>70.043404146858549</v>
       </c>
       <c r="Y113" s="4">
         <f>IF(Y7=0,0,Y112/Y7)</f>
-        <v>0</v>
+        <v>84.326108805307911</v>
       </c>
       <c r="Z113" s="4">
         <f>IF(Z7=0,0,Z112/Z7)</f>
-        <v>62.635799083993589</v>
+        <v>63.276839414183122</v>
       </c>
       <c r="AA113" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="AB113" s="53" t="s">
-        <v>406</v>
-      </c>
-      <c r="AC113" s="54" t="s">
-        <v>369</v>
+      <c r="AB113" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="AC113" s="43" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="2:29" ht="34" x14ac:dyDescent="0.2">
@@ -12109,7 +12136,7 @@
       </c>
       <c r="G114" s="4">
         <f>MAX(G113-$G22,0)</f>
-        <v>0</v>
+        <v>100.4134425</v>
       </c>
       <c r="H114" s="4">
         <f>MAX(H113-$H22,0)</f>
@@ -12117,66 +12144,66 @@
       </c>
       <c r="J114" s="4">
         <f>MAX(J113-$G22,0)</f>
-        <v>0</v>
+        <v>89.891281964518726</v>
       </c>
       <c r="K114" s="4">
         <f>MAX(K113-$H22,0)</f>
-        <v>54.996641249699877</v>
+        <v>57.132978688664636</v>
       </c>
       <c r="M114" s="4">
         <f>MAX(M113-$G22,0)</f>
-        <v>0</v>
+        <v>79.321735542077533</v>
       </c>
       <c r="N114" s="4">
         <f>MAX(N113-$H22,0)</f>
-        <v>47.602484717089879</v>
+        <v>51.886565143885349</v>
       </c>
       <c r="P114" s="4">
         <f>MAX(P113-$G22,0)</f>
-        <v>0</v>
+        <v>68.383325733676216</v>
       </c>
       <c r="Q114" s="4">
         <f>MAX(Q113-$H22,0)</f>
-        <v>39.971284562529576</v>
+        <v>46.472227613135573</v>
       </c>
       <c r="S114" s="4">
         <f>MAX(S113-$G22,0)</f>
-        <v>0</v>
+        <v>57.321949471085048</v>
       </c>
       <c r="T114" s="4">
         <f>MAX(T113-$H22,0)</f>
-        <v>31.962018389994768</v>
+        <v>40.707387204248036</v>
       </c>
       <c r="V114" s="4">
         <f>MAX(V113-$G22,0)</f>
-        <v>0</v>
+        <v>43.84420676892681</v>
       </c>
       <c r="W114" s="4">
         <f>MAX(W113-$H22,0)</f>
-        <v>25.484167522989267</v>
+        <v>32.242511146858547</v>
       </c>
       <c r="Y114" s="4">
         <f>MAX(Y113-$G22,0)</f>
-        <v>0</v>
+        <v>34.739551305307913</v>
       </c>
       <c r="Z114" s="4">
         <f>MAX(Z113-$H22,0)</f>
-        <v>24.834906083993587</v>
+        <v>25.47594641418312</v>
       </c>
       <c r="AA114" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="AB114" s="57" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC114" s="54" t="s">
-        <v>369</v>
+      <c r="AB114" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC114" s="43" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="2:29" x14ac:dyDescent="0.2">
       <c r="F115" s="13"/>
-      <c r="AB115" s="53"/>
-      <c r="AC115" s="54"/>
+      <c r="AB115" s="42"/>
+      <c r="AC115" s="43"/>
     </row>
     <row r="116" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="F116" s="11" t="s">
@@ -12196,8 +12223,8 @@
       <c r="W116" s="12"/>
       <c r="Y116" s="12"/>
       <c r="Z116" s="12"/>
-      <c r="AB116" s="53"/>
-      <c r="AC116" s="54"/>
+      <c r="AB116" s="42"/>
+      <c r="AC116" s="43"/>
     </row>
     <row r="117" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B117" s="38" t="s">
@@ -12211,7 +12238,7 @@
       </c>
       <c r="G117" s="4">
         <f>G113*G7</f>
-        <v>0</v>
+        <v>7500000</v>
       </c>
       <c r="H117" s="4">
         <f>H113*H7</f>
@@ -12219,55 +12246,55 @@
       </c>
       <c r="J117" s="4">
         <f>J113*J7</f>
-        <v>0</v>
+        <v>6966918.08125271</v>
       </c>
       <c r="K117" s="4">
         <f>K113*K7</f>
-        <v>23190103.809</v>
+        <v>23723974.534997292</v>
       </c>
       <c r="M117" s="4">
         <f>M113*M7</f>
-        <v>0</v>
+        <v>6430976.9232831635</v>
       </c>
       <c r="N117" s="4">
         <f>N113*N7</f>
-        <v>21332909.719951883</v>
+        <v>22403030.169761121</v>
       </c>
       <c r="P117" s="4">
         <f>P113*P7</f>
-        <v>0</v>
+        <v>5878439.281534086</v>
       </c>
       <c r="Q117" s="4">
         <f>Q113*Q7</f>
-        <v>19419401.648653384</v>
+        <v>21042661.124617502</v>
       </c>
       <c r="S117" s="4">
         <f>S113*S7</f>
-        <v>0</v>
+        <v>5319767.3068811921</v>
       </c>
       <c r="T117" s="4">
         <f>T113*T7</f>
-        <v>17406125.443449255</v>
+        <v>19588129.944080703</v>
       </c>
       <c r="V117" s="4">
         <f>V113*V7</f>
-        <v>0</v>
+        <v>4639771.7535949051</v>
       </c>
       <c r="W117" s="4">
         <f>W113*W7</f>
-        <v>15787407.623367518</v>
+        <v>17473377.815496068</v>
       </c>
       <c r="Y117" s="4">
         <f>Y113*Y7</f>
-        <v>0</v>
+        <v>4179370.6046086708</v>
       </c>
       <c r="Z117" s="4">
         <f>Z113*Z7</f>
-        <v>15618862.859584641</v>
+        <v>15778712.676320704</v>
       </c>
       <c r="AA117" s="38"/>
-      <c r="AB117" s="53"/>
-      <c r="AC117" s="54"/>
+      <c r="AB117" s="42"/>
+      <c r="AC117" s="43"/>
     </row>
     <row r="118" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
@@ -12310,11 +12337,11 @@
       <c r="AA118" s="38" t="s">
         <v>334</v>
       </c>
-      <c r="AB118" s="53" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC118" s="54" t="s">
-        <v>375</v>
+      <c r="AB118" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC118" s="43" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12329,7 +12356,7 @@
       </c>
       <c r="G119" s="4">
         <f>G117+G118</f>
-        <v>0</v>
+        <v>7500000</v>
       </c>
       <c r="H119" s="4">
         <f>H117+H118</f>
@@ -12337,60 +12364,60 @@
       </c>
       <c r="J119" s="4">
         <f>J117+J118</f>
-        <v>0</v>
+        <v>6966918.08125271</v>
       </c>
       <c r="K119" s="4">
         <f>K117+K118</f>
-        <v>23190104.659000002</v>
+        <v>23723975.384997293</v>
       </c>
       <c r="M119" s="4">
         <f>M117+M118</f>
-        <v>0</v>
+        <v>6430976.9232831635</v>
       </c>
       <c r="N119" s="4">
         <f>N117+N118</f>
-        <v>21332915.618617382</v>
+        <v>22403036.06842662</v>
       </c>
       <c r="P119" s="4">
         <f>P117+P118</f>
-        <v>0</v>
+        <v>5878439.281534086</v>
       </c>
       <c r="Q119" s="4">
         <f>Q117+Q118</f>
-        <v>19419422.65805798</v>
+        <v>21042682.134022098</v>
       </c>
       <c r="S119" s="4">
         <f>S117+S118</f>
-        <v>0</v>
+        <v>5319767.3068811921</v>
       </c>
       <c r="T119" s="4">
         <f>T117+T118</f>
-        <v>17406178.049869087</v>
+        <v>19588182.550500534</v>
       </c>
       <c r="V119" s="4">
         <f>V117+V118</f>
-        <v>0</v>
+        <v>4639771.7535949051</v>
       </c>
       <c r="W119" s="4">
         <f>W117+W118</f>
-        <v>15787519.937195269</v>
+        <v>17473490.129323818</v>
       </c>
       <c r="Y119" s="4">
         <f>Y117+Y118</f>
-        <v>0</v>
+        <v>4179370.6046086708</v>
       </c>
       <c r="Z119" s="4">
         <f>Z117+Z118</f>
-        <v>15619078.357079683</v>
+        <v>15778928.173815746</v>
       </c>
       <c r="AA119" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="AB119" s="53" t="s">
-        <v>442</v>
-      </c>
-      <c r="AC119" s="54" t="s">
-        <v>376</v>
+      <c r="AB119" s="42" t="s">
+        <v>440</v>
+      </c>
+      <c r="AC119" s="43" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12405,7 +12432,7 @@
       </c>
       <c r="G120" s="4">
         <f>G119*$G$21</f>
-        <v>0</v>
+        <v>2250000</v>
       </c>
       <c r="H120" s="4">
         <f>H119*$H$21</f>
@@ -12413,60 +12440,60 @@
       </c>
       <c r="J120" s="4">
         <f>J119*$G$21</f>
-        <v>0</v>
+        <v>2090075.424375813</v>
       </c>
       <c r="K120" s="4">
         <f>K119*$H$21</f>
-        <v>5797526.1647500005</v>
+        <v>5930993.8462493233</v>
       </c>
       <c r="M120" s="4">
         <f>M119*$G$21</f>
-        <v>0</v>
+        <v>1929293.0769849489</v>
       </c>
       <c r="N120" s="4">
         <f>N119*$H$21</f>
-        <v>5333228.9046543455</v>
+        <v>5600759.0171066551</v>
       </c>
       <c r="P120" s="4">
         <f>P119*$G$21</f>
-        <v>0</v>
+        <v>1763531.7844602258</v>
       </c>
       <c r="Q120" s="4">
         <f>Q119*$H$21</f>
-        <v>4854855.6645144951</v>
+        <v>5260670.5335055245</v>
       </c>
       <c r="S120" s="4">
         <f>S119*$G$21</f>
-        <v>0</v>
+        <v>1595930.1920643577</v>
       </c>
       <c r="T120" s="4">
         <f>T119*$H$21</f>
-        <v>4351544.5124672716</v>
+        <v>4897045.6376251336</v>
       </c>
       <c r="V120" s="4">
         <f>V119*$G$21</f>
-        <v>0</v>
+        <v>1391931.5260784714</v>
       </c>
       <c r="W120" s="4">
         <f>W119*$H$21</f>
-        <v>3946879.9842988173</v>
+        <v>4368372.5323309544</v>
       </c>
       <c r="Y120" s="4">
         <f>Y119*$G$21</f>
-        <v>0</v>
+        <v>1253811.1813826011</v>
       </c>
       <c r="Z120" s="4">
         <f>Z119*$H$21</f>
-        <v>3904769.5892699207</v>
+        <v>3944732.0434539365</v>
       </c>
       <c r="AA120" s="38" t="s">
         <v>336</v>
       </c>
-      <c r="AB120" s="53" t="s">
-        <v>443</v>
-      </c>
-      <c r="AC120" s="54" t="s">
-        <v>376</v>
+      <c r="AB120" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC120" s="43" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12481,7 +12508,7 @@
       </c>
       <c r="G121" s="4">
         <f>G9*G113</f>
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="H121" s="4">
         <f>H9*H113</f>
@@ -12489,60 +12516,60 @@
       </c>
       <c r="J121" s="4">
         <f>J9*J113</f>
-        <v>0</v>
+        <v>8647.6260468001601</v>
       </c>
       <c r="K121" s="4">
         <f>K9*K113</f>
-        <v>10207.728767466986</v>
+        <v>10442.725885753111</v>
       </c>
       <c r="M121" s="4">
         <f>M9*M113</f>
-        <v>0</v>
+        <v>7476.6809964404965</v>
       </c>
       <c r="N121" s="4">
         <f>N9*N113</f>
-        <v>8027.917505406449</v>
+        <v>8430.6210655252235</v>
       </c>
       <c r="P121" s="4">
         <f>P9*P113</f>
-        <v>0</v>
+        <v>8257.8918263573341</v>
       </c>
       <c r="Q121" s="4">
         <f>Q9*Q113</f>
-        <v>14932.258092005679</v>
+        <v>16180.43915772203</v>
       </c>
       <c r="S121" s="4">
         <f>S9*S113</f>
-        <v>0</v>
+        <v>10690.850697108504</v>
       </c>
       <c r="T121" s="4">
         <f>T9*T113</f>
-        <v>2720.753544209796</v>
+        <v>3061.8229279656734</v>
       </c>
       <c r="V121" s="4">
         <f>V9*V113</f>
-        <v>0</v>
+        <v>9156.2148983548268</v>
       </c>
       <c r="W121" s="4">
         <f>W9*W113</f>
-        <v>6644.9313549138733</v>
+        <v>7354.5574354201481</v>
       </c>
       <c r="Y121" s="4">
         <f>Y9*Y113</f>
-        <v>0</v>
+        <v>8263.9586629201749</v>
       </c>
       <c r="Z121" s="4">
         <f>Z9*Z113</f>
-        <v>7265.7526937432567</v>
+        <v>7340.1133720452426</v>
       </c>
       <c r="AA121" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="AB121" s="53" t="s">
-        <v>408</v>
-      </c>
-      <c r="AC121" s="54" t="s">
-        <v>372</v>
+      <c r="AB121" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC121" s="43" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12557,7 +12584,7 @@
       </c>
       <c r="G122" s="4">
         <f>MIN(G121,G9*G15)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H122" s="4">
         <f>MIN(H121,H9*H15)</f>
@@ -12565,7 +12592,7 @@
       </c>
       <c r="J122" s="4">
         <f>MIN(J121,J9*J15)</f>
-        <v>0</v>
+        <v>316.2</v>
       </c>
       <c r="K122" s="4">
         <f>MIN(K121,K9*K15)</f>
@@ -12573,7 +12600,7 @@
       </c>
       <c r="M122" s="4">
         <f>MIN(M121,M9*M15)</f>
-        <v>0</v>
+        <v>301.60000000000002</v>
       </c>
       <c r="N122" s="4">
         <f>MIN(N121,N9*N15)</f>
@@ -12581,7 +12608,7 @@
       </c>
       <c r="P122" s="4">
         <f>MIN(P121,P9*P15)</f>
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="Q122" s="4">
         <f>MIN(Q121,Q9*Q15)</f>
@@ -12589,7 +12616,7 @@
       </c>
       <c r="S122" s="4">
         <f>MIN(S121,S9*S15)</f>
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="T122" s="4">
         <f>MIN(T121,T9*T15)</f>
@@ -12597,7 +12624,7 @@
       </c>
       <c r="V122" s="4">
         <f>MIN(V121,V9*V15)</f>
-        <v>0</v>
+        <v>401.79999999999995</v>
       </c>
       <c r="W122" s="4">
         <f>MIN(W121,W9*W15)</f>
@@ -12605,7 +12632,7 @@
       </c>
       <c r="Y122" s="4">
         <f>MIN(Y121,Y9*Y15)</f>
-        <v>0</v>
+        <v>499.79999999999995</v>
       </c>
       <c r="Z122" s="4">
         <f>MIN(Z121,Z9*Z15)</f>
@@ -12614,11 +12641,11 @@
       <c r="AA122" s="38" t="s">
         <v>343</v>
       </c>
-      <c r="AB122" s="53" t="s">
-        <v>408</v>
-      </c>
-      <c r="AC122" s="54" t="s">
-        <v>372</v>
+      <c r="AB122" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC122" s="43" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12633,7 +12660,7 @@
       </c>
       <c r="G123" s="4">
         <f>(G121-G122)*$G$14</f>
-        <v>0</v>
+        <v>5075</v>
       </c>
       <c r="H123" s="4">
         <f>(H121-H122+H54)*$G$14</f>
@@ -12641,60 +12668,60 @@
       </c>
       <c r="J123" s="4">
         <f>(J121-J122)*$G$14</f>
-        <v>0</v>
+        <v>5831.998232760111</v>
       </c>
       <c r="K123" s="4">
         <f>(K121-K122+K54)*$G$14</f>
-        <v>6390.8101372268902</v>
+        <v>6555.3081200271772</v>
       </c>
       <c r="M123" s="4">
         <f>(M121-M122)*$G$14</f>
-        <v>0</v>
+        <v>5022.5566975083466</v>
       </c>
       <c r="N123" s="4">
         <f>(N121-N122+N54)*$G$14</f>
-        <v>4974.7022537845141</v>
+        <v>5256.5947458676565</v>
       </c>
       <c r="P123" s="4">
         <f>(P121-P122)*$G$14</f>
-        <v>0</v>
+        <v>5550.2242784501332</v>
       </c>
       <c r="Q123" s="4">
         <f>(Q121-Q122+Q54)*$G$14</f>
-        <v>9122.0206644039754</v>
+        <v>9995.7474104054218</v>
       </c>
       <c r="S123" s="4">
         <f>(S121-S122)*$G$14</f>
-        <v>0</v>
+        <v>7119.5954879759529</v>
       </c>
       <c r="T123" s="4">
         <f>(T121-T122+T54)*$G$14</f>
-        <v>1628.7974809468571</v>
+        <v>1867.5460495759712</v>
       </c>
       <c r="V123" s="4">
         <f>(V121-V122)*$G$14</f>
-        <v>0</v>
+        <v>6128.0904288483789</v>
       </c>
       <c r="W123" s="4">
         <f>(W121-W122+W54)*$G$14</f>
-        <v>3842.951948439711</v>
+        <v>4339.690204794103</v>
       </c>
       <c r="Y123" s="4">
         <f>(Y121-Y122)*$G$14</f>
-        <v>0</v>
+        <v>5434.9110640441222</v>
       </c>
       <c r="Z123" s="4">
         <f>(Z121-Z122+Z54)*$G$14</f>
-        <v>4355.2268856202791</v>
+        <v>4407.2793604316694</v>
       </c>
       <c r="AA123" s="38" t="s">
         <v>344</v>
       </c>
-      <c r="AB123" s="53" t="s">
-        <v>408</v>
-      </c>
-      <c r="AC123" s="54" t="s">
-        <v>372</v>
+      <c r="AB123" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC123" s="43" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="17" x14ac:dyDescent="0.2">
@@ -12709,39 +12736,39 @@
       </c>
       <c r="G124" s="4">
         <f>MIN(G123+H123, G33)</f>
-        <v>6300</v>
+        <v>11375</v>
       </c>
       <c r="J124" s="4">
         <f>MIN(J123+K123, J33)</f>
-        <v>6390.8101372268902</v>
+        <v>12387.306352787287</v>
       </c>
       <c r="M124" s="4">
         <f>MIN(M123+N123, M33)</f>
-        <v>4974.7022537845141</v>
+        <v>10279.151443376002</v>
       </c>
       <c r="P124" s="4">
         <f>MIN(P123+Q123, P33)</f>
-        <v>9122.0206644039754</v>
+        <v>15545.971688855556</v>
       </c>
       <c r="S124" s="4">
         <f>MIN(S123+T123, S33)</f>
-        <v>1628.7974809468571</v>
+        <v>8987.1415375519246</v>
       </c>
       <c r="V124" s="4">
         <f>MIN(V123+W123, V33)</f>
-        <v>3842.951948439711</v>
+        <v>10467.780633642482</v>
       </c>
       <c r="Y124" s="4">
         <f>MIN(Y123+Z123, Y33)</f>
-        <v>4355.2268856202791</v>
+        <v>9842.1904244757916</v>
       </c>
       <c r="AA124" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="AB124" s="53" t="s">
+      <c r="AB124" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="AC124" s="54" t="s">
+      <c r="AC124" s="43" t="s">
         <v>345</v>
       </c>
     </row>
@@ -12757,68 +12784,68 @@
       </c>
       <c r="G125" s="4">
         <f>G123/(G123+H123)</f>
-        <v>0</v>
+        <v>0.44615384615384618</v>
       </c>
       <c r="H125" s="4">
         <f>H123/(G123+H123)</f>
-        <v>1</v>
+        <v>0.55384615384615388</v>
       </c>
       <c r="J125" s="4">
         <f>J123/(J123+K123)</f>
-        <v>0</v>
+        <v>0.47080439174315275</v>
       </c>
       <c r="K125" s="4">
         <f>K123/(J123+K123)</f>
-        <v>1</v>
+        <v>0.52919560825684731</v>
       </c>
       <c r="M125" s="4">
         <f>M123/(M123+N123)</f>
-        <v>0</v>
+        <v>0.48861588674665718</v>
       </c>
       <c r="N125" s="4">
         <f>N123/(M123+N123)</f>
-        <v>1</v>
+        <v>0.51138411325334288</v>
       </c>
       <c r="P125" s="4">
         <f>P123/(P123+Q123)</f>
-        <v>0</v>
+        <v>0.35702009430706244</v>
       </c>
       <c r="Q125" s="4">
         <f>Q123/(P123+Q123)</f>
-        <v>1</v>
+        <v>0.6429799056929375</v>
       </c>
       <c r="S125" s="4">
         <f>S123/(S123+T123)</f>
-        <v>0</v>
+        <v>0.79219799290212511</v>
       </c>
       <c r="T125" s="4">
         <f>T123/(S123+T123)</f>
-        <v>1</v>
+        <v>0.20780200709787489</v>
       </c>
       <c r="V125" s="4">
         <f>V123/(V123+W123)</f>
-        <v>0</v>
+        <v>0.58542404004467397</v>
       </c>
       <c r="W125" s="4">
         <f>W123/(V123+W123)</f>
-        <v>1</v>
+        <v>0.41457595995532603</v>
       </c>
       <c r="Y125" s="4">
         <f>Y123/(Y123+Z123)</f>
-        <v>0</v>
+        <v>0.55220543696537883</v>
       </c>
       <c r="Z125" s="4">
         <f>Z123/(Y123+Z123)</f>
-        <v>1</v>
+        <v>0.44779456303462112</v>
       </c>
       <c r="AA125" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="AB125" s="53" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC125" s="54" t="s">
-        <v>386</v>
+      <c r="AB125" s="42" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC125" s="43" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="126" spans="2:29" ht="34" x14ac:dyDescent="0.2">
@@ -12833,7 +12860,7 @@
       </c>
       <c r="G126" s="4">
         <f>MAX(G13-G27, 0)*G114</f>
-        <v>0</v>
+        <v>4513584.2403750001</v>
       </c>
       <c r="H126" s="4">
         <f>MAX(H13-H27, 0)*H114</f>
@@ -12841,65 +12868,65 @@
       </c>
       <c r="J126" s="4">
         <f>MAX(J13-J27, 0)*J114</f>
-        <v>0</v>
+        <v>4035039.8648233167</v>
       </c>
       <c r="K126" s="4">
         <f>MAX(K13-K27, 0)*K114</f>
-        <v>10987778.955277538</v>
+        <v>11414597.812208308</v>
       </c>
       <c r="M126" s="4">
         <f>MAX(M13-M27, 0)*M114</f>
-        <v>0</v>
+        <v>3516332.5365802972</v>
       </c>
       <c r="N126" s="4">
         <f>MAX(N13-N27, 0)*N114</f>
-        <v>9506025.7880639806</v>
+        <v>10361539.512973329</v>
       </c>
       <c r="P126" s="4">
         <f>MAX(P13-P27, 0)*P114</f>
-        <v>0</v>
+        <v>2992454.3341056714</v>
       </c>
       <c r="Q126" s="4">
         <f>MAX(Q13-Q27, 0)*Q114</f>
-        <v>7974431.1553629003</v>
+        <v>9271395.2977309991</v>
       </c>
       <c r="S126" s="4">
         <f>MAX(S13-S27, 0)*S114</f>
-        <v>0</v>
+        <v>2474015.3391720308</v>
       </c>
       <c r="T126" s="4">
         <f>MAX(T13-T27, 0)*T114</f>
-        <v>6407266.0165503006</v>
+        <v>8160406.3758995822</v>
       </c>
       <c r="V126" s="4">
         <f>MAX(V13-V27, 0)*V114</f>
-        <v>0</v>
+        <v>1857328.2871452775</v>
       </c>
       <c r="W126" s="4">
         <f>MAX(W13-W27, 0)*W114</f>
-        <v>5093265.7211446352</v>
+        <v>6443988.2778111491</v>
       </c>
       <c r="Y126" s="4">
         <f>MAX(Y13-Y27, 0)*Y114</f>
-        <v>0</v>
+        <v>1468232.3963675336</v>
       </c>
       <c r="Z126" s="4">
         <f>MAX(Z13-Z27, 0)*Z114</f>
-        <v>4960623.4808412148</v>
+        <v>5088667.4405545928</v>
       </c>
       <c r="AA126" s="38" t="s">
-        <v>388</v>
-      </c>
-      <c r="AB126" s="53" t="s">
+        <v>386</v>
+      </c>
+      <c r="AB126" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="AC126" s="54" t="s">
-        <v>369</v>
+      <c r="AC126" s="43" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="127" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB127" s="53"/>
-      <c r="AC127" s="54"/>
+      <c r="AB127" s="42"/>
+      <c r="AC127" s="43"/>
     </row>
     <row r="128" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="F128" s="15" t="s">
@@ -12919,8 +12946,8 @@
       <c r="W128" s="8"/>
       <c r="Y128" s="8"/>
       <c r="Z128" s="8"/>
-      <c r="AB128" s="53"/>
-      <c r="AC128" s="54"/>
+      <c r="AB128" s="42"/>
+      <c r="AC128" s="43"/>
     </row>
     <row r="129" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B129" s="38" t="s">
@@ -12934,40 +12961,40 @@
       </c>
       <c r="G129" s="4">
         <f>MAX(G33-G124,0)</f>
-        <v>1993700</v>
+        <v>1988625</v>
       </c>
       <c r="J129" s="4">
         <f>MAX(J33-J124,0)</f>
-        <v>2043609.1898627731</v>
+        <v>2037612.6936472128</v>
       </c>
       <c r="M129" s="4">
         <f>MAX(M33-M124,0)</f>
-        <v>2105025.2977462155</v>
+        <v>2099720.8485566238</v>
       </c>
       <c r="P129" s="4">
         <f>MAX(P33-P124,0)</f>
-        <v>2200877.9793355959</v>
+        <v>2194454.0283111446</v>
       </c>
       <c r="S129" s="4">
         <f>MAX(S33-S124,0)</f>
-        <v>2998371.2025190531</v>
+        <v>2991012.8584624482</v>
       </c>
       <c r="V129" s="4">
         <f>MAX(V33-V124,0)</f>
-        <v>24996157.048051558</v>
+        <v>24989532.219366357</v>
       </c>
       <c r="Y129" s="4">
         <f>MAX(Y33-Y124,0)</f>
-        <v>2515644.7731143795</v>
+        <v>2510157.8095755242</v>
       </c>
       <c r="AA129" s="38" t="s">
-        <v>477</v>
-      </c>
-      <c r="AB129" s="53" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC129" s="54" t="s">
-        <v>373</v>
+        <v>475</v>
+      </c>
+      <c r="AB129" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="AC129" s="43" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -12982,39 +13009,39 @@
       </c>
       <c r="G130" s="4">
         <f>MIN(G140,G129)</f>
-        <v>1993700</v>
+        <v>1988625</v>
       </c>
       <c r="J130" s="4">
         <f>MIN(J140,J129)</f>
-        <v>2043609.1898627731</v>
+        <v>2037612.6936472128</v>
       </c>
       <c r="M130" s="4">
         <f>MIN(M140,M129)</f>
-        <v>2105025.2977462155</v>
+        <v>2099720.8485566238</v>
       </c>
       <c r="P130" s="4">
         <f>MIN(P140,P129)</f>
-        <v>2200877.9793355959</v>
+        <v>2194454.0283111446</v>
       </c>
       <c r="S130" s="4">
         <f>MIN(S140,S129)</f>
-        <v>1821040.5218088522</v>
+        <v>2991012.8584624482</v>
       </c>
       <c r="V130" s="4">
         <f>MIN(V140,V129)</f>
-        <v>337878.12833874481</v>
+        <v>2349768.169205951</v>
       </c>
       <c r="Y130" s="4">
         <f>MIN(Y140,Y129)</f>
-        <v>220752.12927619604</v>
+        <v>388638.16574066621</v>
       </c>
       <c r="AA130" s="38" t="s">
-        <v>476</v>
-      </c>
-      <c r="AB130" s="53" t="s">
-        <v>445</v>
-      </c>
-      <c r="AC130" s="54" t="s">
+        <v>474</v>
+      </c>
+      <c r="AB130" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="AC130" s="43" t="s">
         <v>345</v>
       </c>
     </row>
@@ -13046,23 +13073,23 @@
       </c>
       <c r="S131" s="4">
         <f>S129-S130</f>
-        <v>1177330.6807102009</v>
+        <v>0</v>
       </c>
       <c r="V131" s="4">
         <f>V129-V130</f>
-        <v>24658278.919712815</v>
+        <v>22639764.050160404</v>
       </c>
       <c r="Y131" s="4">
         <f>Y129-Y130</f>
-        <v>2294892.6438381835</v>
+        <v>2121519.6438348582</v>
       </c>
       <c r="AA131" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="AB131" s="53" t="s">
-        <v>446</v>
-      </c>
-      <c r="AC131" s="54" t="s">
+        <v>473</v>
+      </c>
+      <c r="AB131" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="AC131" s="43" t="s">
         <v>350</v>
       </c>
     </row>
@@ -13105,12 +13132,12 @@
         <v>0</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="AB132" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="AC132" s="54" t="s">
+        <v>470</v>
+      </c>
+      <c r="AB132" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="AC132" s="43" t="s">
         <v>345</v>
       </c>
     </row>
@@ -13126,68 +13153,68 @@
       </c>
       <c r="G133" s="4">
         <f>G141*G130</f>
-        <v>0</v>
+        <v>529635.22104433016</v>
       </c>
       <c r="H133" s="4">
         <f>H141*G130</f>
-        <v>1993700</v>
+        <v>1458989.7789556701</v>
       </c>
       <c r="J133" s="4">
         <f>J141*J130</f>
-        <v>0</v>
+        <v>532170.95570853585</v>
       </c>
       <c r="K133" s="4">
         <f>K141*J130</f>
-        <v>2043609.1898627731</v>
+        <v>1505441.737938677</v>
       </c>
       <c r="M133" s="4">
         <f>M141*M130</f>
-        <v>0</v>
+        <v>550789.80536667234</v>
       </c>
       <c r="N133" s="4">
         <f>N141*M130</f>
-        <v>2105025.2977462155</v>
+        <v>1548931.0431899517</v>
       </c>
       <c r="P133" s="4">
         <f>P141*P130</f>
-        <v>0</v>
+        <v>557000.38865488267</v>
       </c>
       <c r="Q133" s="4">
         <f>Q141*P130</f>
-        <v>2200877.9793355959</v>
+        <v>1637453.639656262</v>
       </c>
       <c r="S133" s="4">
         <f>S141*S130</f>
-        <v>0</v>
+        <v>676930.23301880853</v>
       </c>
       <c r="T133" s="4">
         <f>T141*S130</f>
-        <v>1821040.5218088522</v>
+        <v>2314082.6254436397</v>
       </c>
       <c r="V133" s="4">
         <f>V141*V130</f>
-        <v>0</v>
+        <v>457497.26124774636</v>
       </c>
       <c r="W133" s="4">
         <f>W141*V130</f>
-        <v>337878.12833874481</v>
+        <v>1892270.9079582046</v>
       </c>
       <c r="Y133" s="4">
         <f>Y141*Y130</f>
-        <v>0</v>
+        <v>52472.144574730177</v>
       </c>
       <c r="Z133" s="4">
         <f>Z141*Y130</f>
-        <v>220752.12927619604</v>
+        <v>336166.02116593602</v>
       </c>
       <c r="AA133" s="38" t="s">
-        <v>473</v>
-      </c>
-      <c r="AB133" s="53" t="s">
-        <v>410</v>
-      </c>
-      <c r="AC133" s="54" t="s">
-        <v>377</v>
+        <v>471</v>
+      </c>
+      <c r="AB133" s="42" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC133" s="43" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13202,68 +13229,68 @@
       </c>
       <c r="G134" s="4">
         <f>G133</f>
-        <v>0</v>
+        <v>529635.22104433016</v>
       </c>
       <c r="H134" s="4">
         <f>H133+G132</f>
-        <v>1993700</v>
+        <v>1458989.7789556701</v>
       </c>
       <c r="J134" s="4">
         <f>J133</f>
-        <v>0</v>
+        <v>532170.95570853585</v>
       </c>
       <c r="K134" s="4">
         <f>K133+J132</f>
-        <v>2043609.1898627731</v>
+        <v>1505441.737938677</v>
       </c>
       <c r="M134" s="4">
         <f>M133</f>
-        <v>0</v>
+        <v>550789.80536667234</v>
       </c>
       <c r="N134" s="4">
         <f>N133+M132</f>
-        <v>2105025.2977462155</v>
+        <v>1548931.0431899517</v>
       </c>
       <c r="P134" s="4">
         <f>P133</f>
-        <v>0</v>
+        <v>557000.38865488267</v>
       </c>
       <c r="Q134" s="4">
         <f>Q133+P132</f>
-        <v>2200877.9793355959</v>
+        <v>1637453.639656262</v>
       </c>
       <c r="S134" s="4">
         <f>S133</f>
-        <v>0</v>
+        <v>676930.23301880853</v>
       </c>
       <c r="T134" s="4">
         <f>T133+S132</f>
-        <v>1821040.5218088522</v>
+        <v>2314082.6254436397</v>
       </c>
       <c r="V134" s="4">
         <f>V133</f>
-        <v>0</v>
+        <v>457497.26124774636</v>
       </c>
       <c r="W134" s="4">
         <f>W133+V132</f>
-        <v>337878.12833874481</v>
+        <v>1892270.9079582046</v>
       </c>
       <c r="Y134" s="4">
         <f>Y133</f>
-        <v>0</v>
+        <v>52472.144574730177</v>
       </c>
       <c r="Z134" s="4">
         <f>Z133+Y132</f>
-        <v>220752.12927619604</v>
+        <v>336166.02116593602</v>
       </c>
       <c r="AA134" s="38" t="s">
-        <v>474</v>
-      </c>
-      <c r="AB134" s="53" t="s">
-        <v>479</v>
-      </c>
-      <c r="AC134" s="54" t="s">
-        <v>377</v>
+        <v>472</v>
+      </c>
+      <c r="AB134" s="42" t="s">
+        <v>477</v>
+      </c>
+      <c r="AC134" s="43" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="135" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13284,8 +13311,8 @@
       <c r="W135" s="8"/>
       <c r="Y135" s="8"/>
       <c r="Z135" s="8"/>
-      <c r="AB135" s="53"/>
-      <c r="AC135" s="54"/>
+      <c r="AB135" s="42"/>
+      <c r="AC135" s="43"/>
     </row>
     <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B136" s="38" t="s">
@@ -13299,7 +13326,7 @@
       </c>
       <c r="G136" s="4">
         <f>G114/$G$23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" s="4">
         <f>H114/$H$23</f>
@@ -13307,60 +13334,60 @@
       </c>
       <c r="J136" s="4">
         <f>J114/$G$23</f>
-        <v>0</v>
+        <v>0.8952116342841121</v>
       </c>
       <c r="K136" s="4">
         <f>K114/$H$23</f>
-        <v>0.88420306821607386</v>
+        <v>0.91854982240604577</v>
       </c>
       <c r="M136" s="4">
         <f>M114/$G$23</f>
-        <v>0</v>
+        <v>0.78995136076604022</v>
       </c>
       <c r="N136" s="4">
         <f>N114/$H$23</f>
-        <v>0.76532424681096922</v>
+        <v>0.83420112677639169</v>
       </c>
       <c r="P136" s="4">
         <f>P114/$G$23</f>
-        <v>0</v>
+        <v>0.681017640976468</v>
       </c>
       <c r="Q136" s="4">
         <f>Q114/$H$23</f>
-        <v>0.64263437998441963</v>
+        <v>0.74715264984649332</v>
       </c>
       <c r="S136" s="4">
         <f>S114/$G$23</f>
-        <v>0</v>
+        <v>0.57085931966813153</v>
       </c>
       <c r="T136" s="4">
         <f>T114/$H$23</f>
-        <v>0.51386619409173784</v>
+        <v>0.65446899750904841</v>
       </c>
       <c r="V136" s="4">
         <f>V114/$G$23</f>
-        <v>0</v>
+        <v>0.43663682548207439</v>
       </c>
       <c r="W136" s="4">
         <f>W114/$H$23</f>
-        <v>0.40971918653091383</v>
+        <v>0.51837578868871137</v>
       </c>
       <c r="Y136" s="4">
         <f>Y114/$G$23</f>
-        <v>0</v>
+        <v>0.3459651461038985</v>
       </c>
       <c r="Z136" s="4">
         <f>Z114/$H$23</f>
-        <v>0.39928074986661122</v>
+        <v>0.40958701246600088</v>
       </c>
       <c r="AA136" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="AB136" s="53" t="s">
-        <v>411</v>
-      </c>
-      <c r="AC136" s="54" t="s">
-        <v>385</v>
+        <v>387</v>
+      </c>
+      <c r="AB136" s="42" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC136" s="43" t="s">
+        <v>383</v>
       </c>
       <c r="AD136">
         <v>20</v>
@@ -13381,7 +13408,7 @@
       </c>
       <c r="G137" s="4">
         <f>MAX(MIN((G136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="4">
         <f>MAX(MIN((H136-$H$17)/$H$18, 1), 0)</f>
@@ -13389,7 +13416,7 @@
       </c>
       <c r="J137" s="4">
         <f>MAX(MIN((J136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" s="4">
         <f>MAX(MIN((K136-$H$17)/$H$18, 1), 0)</f>
@@ -13397,52 +13424,52 @@
       </c>
       <c r="M137" s="4">
         <f>MAX(MIN((M136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" s="4">
         <f>MAX(MIN((N136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.81026795213003489</v>
+        <v>0.95435915135809635</v>
       </c>
       <c r="P137" s="4">
         <f>MAX(MIN((P136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>0.81388590259622062</v>
       </c>
       <c r="Q137" s="4">
         <f>MAX(MIN((Q136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.55359938565252242</v>
+        <v>0.7722527690988813</v>
       </c>
       <c r="S137" s="4">
         <f>MAX(MIN((S136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>0.55804708975578599</v>
       </c>
       <c r="T137" s="4">
         <f>MAX(MIN((T136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.28421490805985111</v>
+        <v>0.57835753718878935</v>
       </c>
       <c r="V137" s="4">
         <f>MAX(MIN((V136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>0.24632008483051848</v>
       </c>
       <c r="W137" s="4">
         <f>MAX(MIN((W136-$H$17)/$H$18, 1), 0)</f>
-        <v>6.6338209478458504E-2</v>
+        <v>0.29364903013153193</v>
       </c>
       <c r="Y137" s="4">
         <f>MAX(MIN((Y136-$G$17)/$G$18, 1), 0)</f>
-        <v>0</v>
+        <v>3.5738310028132055E-2</v>
       </c>
       <c r="Z137" s="4">
         <f>MAX(MIN((Z136-$H$17)/$H$18, 1), 0)</f>
-        <v>4.4500883836231256E-2</v>
+        <v>6.6061699864060811E-2</v>
       </c>
       <c r="AA137" s="39" t="s">
-        <v>355</v>
-      </c>
-      <c r="AB137" s="53" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC137" s="54" t="s">
-        <v>385</v>
+        <v>354</v>
+      </c>
+      <c r="AB137" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="AC137" s="43" t="s">
+        <v>383</v>
       </c>
       <c r="AD137">
         <v>20</v>
@@ -13451,8 +13478,8 @@
     <row r="138" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B138" s="38"/>
       <c r="AA138" s="38"/>
-      <c r="AB138" s="53"/>
-      <c r="AC138" s="54"/>
+      <c r="AB138" s="42"/>
+      <c r="AC138" s="43"/>
       <c r="AD138">
         <v>20</v>
       </c>
@@ -13469,7 +13496,7 @@
       </c>
       <c r="G139" s="4">
         <f>G126*G137</f>
-        <v>0</v>
+        <v>4513584.2403750001</v>
       </c>
       <c r="H139" s="4">
         <f>H126*H137</f>
@@ -13477,60 +13504,60 @@
       </c>
       <c r="J139" s="4">
         <f>J126*J137</f>
-        <v>0</v>
+        <v>4035039.8648233167</v>
       </c>
       <c r="K139" s="4">
         <f>K126*K137</f>
-        <v>10987778.955277538</v>
+        <v>11414597.812208308</v>
       </c>
       <c r="M139" s="4">
         <f>M126*M137</f>
-        <v>0</v>
+        <v>3516332.5365802972</v>
       </c>
       <c r="N139" s="4">
         <f>N126*N137</f>
-        <v>7702428.0481899027</v>
+        <v>9888630.0563646089</v>
       </c>
       <c r="P139" s="4">
         <f>P126*P137</f>
-        <v>0</v>
+        <v>2435516.3966915668</v>
       </c>
       <c r="Q139" s="4">
         <f>Q126*Q137</f>
-        <v>4414640.1885372363</v>
+        <v>7159860.692083111</v>
       </c>
       <c r="S139" s="4">
         <f>S126*S137</f>
-        <v>0</v>
+        <v>1380617.0600361256</v>
       </c>
       <c r="T139" s="4">
         <f>T126*T137</f>
-        <v>1821040.5218088522</v>
+        <v>4719632.5340249762</v>
       </c>
       <c r="V139" s="4">
         <f>V126*V137</f>
-        <v>0</v>
+        <v>457497.26124774636</v>
       </c>
       <c r="W139" s="4">
         <f>W126*W137</f>
-        <v>337878.12833874481</v>
+        <v>1892270.9079582046</v>
       </c>
       <c r="Y139" s="4">
         <f>Y126*Y137</f>
-        <v>0</v>
+        <v>52472.144574730184</v>
       </c>
       <c r="Z139" s="4">
         <f>Z126*Z137</f>
-        <v>220752.12927619604</v>
+        <v>336166.02116593602</v>
       </c>
       <c r="AA139" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="AB139" s="53" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC139" s="54" t="s">
-        <v>369</v>
+        <v>389</v>
+      </c>
+      <c r="AB139" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC139" s="43" t="s">
+        <v>368</v>
       </c>
       <c r="AD139">
         <v>20</v>
@@ -13548,68 +13575,68 @@
       </c>
       <c r="G140" s="4">
         <f>G139+H139</f>
-        <v>12433601.4893</v>
+        <v>16947185.729674999</v>
       </c>
       <c r="H140" s="4">
         <f>G140</f>
-        <v>12433601.4893</v>
+        <v>16947185.729674999</v>
       </c>
       <c r="J140" s="4">
         <f>J139+K139</f>
-        <v>10987778.955277538</v>
+        <v>15449637.677031625</v>
       </c>
       <c r="K140" s="4">
         <f>J140</f>
-        <v>10987778.955277538</v>
+        <v>15449637.677031625</v>
       </c>
       <c r="M140" s="4">
         <f>M139+N139</f>
-        <v>7702428.0481899027</v>
+        <v>13404962.592944905</v>
       </c>
       <c r="N140" s="4">
         <f>M140</f>
-        <v>7702428.0481899027</v>
+        <v>13404962.592944905</v>
       </c>
       <c r="P140" s="4">
         <f>P139+Q139</f>
-        <v>4414640.1885372363</v>
+        <v>9595377.0887746774</v>
       </c>
       <c r="Q140" s="4">
         <f>P140</f>
-        <v>4414640.1885372363</v>
+        <v>9595377.0887746774</v>
       </c>
       <c r="S140" s="4">
         <f>S139+T139</f>
-        <v>1821040.5218088522</v>
+        <v>6100249.5940611018</v>
       </c>
       <c r="T140" s="4">
         <f>S140</f>
-        <v>1821040.5218088522</v>
+        <v>6100249.5940611018</v>
       </c>
       <c r="V140" s="4">
         <f>V139+W139</f>
-        <v>337878.12833874481</v>
+        <v>2349768.169205951</v>
       </c>
       <c r="W140" s="4">
         <f>V140</f>
-        <v>337878.12833874481</v>
+        <v>2349768.169205951</v>
       </c>
       <c r="Y140" s="4">
         <f>Y139+Z139</f>
-        <v>220752.12927619604</v>
+        <v>388638.16574066621</v>
       </c>
       <c r="Z140" s="4">
         <f>Y140</f>
-        <v>220752.12927619604</v>
+        <v>388638.16574066621</v>
       </c>
       <c r="AA140" s="38" t="s">
-        <v>390</v>
-      </c>
-      <c r="AB140" s="53" t="s">
+        <v>388</v>
+      </c>
+      <c r="AB140" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="AC140" s="54" t="s">
-        <v>372</v>
+      <c r="AC140" s="43" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13624,73 +13651,73 @@
       </c>
       <c r="G141" s="4">
         <f>G139/G140</f>
-        <v>0</v>
+        <v>0.26633237591015407</v>
       </c>
       <c r="H141" s="4">
         <f>H139/H140</f>
-        <v>1</v>
+        <v>0.73366762408984598</v>
       </c>
       <c r="J141" s="4">
         <f>J139/J140</f>
-        <v>0</v>
+        <v>0.26117375366168316</v>
       </c>
       <c r="K141" s="4">
         <f>K139/K140</f>
-        <v>1</v>
+        <v>0.73882624633831684</v>
       </c>
       <c r="M141" s="4">
         <f>M139/M140</f>
-        <v>0</v>
+        <v>0.26231572913384776</v>
       </c>
       <c r="N141" s="4">
         <f>N139/N140</f>
-        <v>1</v>
+        <v>0.73768427086615229</v>
       </c>
       <c r="P141" s="4">
         <f>P139/P140</f>
-        <v>0</v>
+        <v>0.25382185339446417</v>
       </c>
       <c r="Q141" s="4">
         <f>Q139/Q140</f>
-        <v>1</v>
+        <v>0.74617814660553583</v>
       </c>
       <c r="S141" s="4">
         <f>S139/S140</f>
-        <v>0</v>
+        <v>0.22632140517335969</v>
       </c>
       <c r="T141" s="4">
         <f>T139/T140</f>
-        <v>1</v>
+        <v>0.77367859482664036</v>
       </c>
       <c r="V141" s="4">
         <f>V139/V140</f>
-        <v>0</v>
+        <v>0.1946988929560429</v>
       </c>
       <c r="W141" s="4">
         <f>W139/W140</f>
-        <v>1</v>
+        <v>0.80530110704395708</v>
       </c>
       <c r="Y141" s="4">
         <f>Y139/Y140</f>
-        <v>0</v>
+        <v>0.13501541845415213</v>
       </c>
       <c r="Z141" s="4">
         <f>Z139/Z140</f>
-        <v>1</v>
+        <v>0.86498458154584779</v>
       </c>
       <c r="AA141" s="38" t="s">
         <v>353</v>
       </c>
-      <c r="AB141" s="53" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC141" s="54" t="s">
-        <v>386</v>
+      <c r="AB141" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC141" s="43" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB142" s="53"/>
-      <c r="AC142" s="54"/>
+      <c r="AB142" s="42"/>
+      <c r="AC142" s="43"/>
     </row>
     <row r="143" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="F143" s="15" t="s">
@@ -13710,8 +13737,8 @@
       <c r="W143" s="8"/>
       <c r="Y143" s="8"/>
       <c r="Z143" s="8"/>
-      <c r="AB143" s="53"/>
-      <c r="AC143" s="54"/>
+      <c r="AB143" s="42"/>
+      <c r="AC143" s="43"/>
     </row>
     <row r="144" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="B144" s="38" t="s">
@@ -13725,67 +13752,67 @@
       </c>
       <c r="G144" s="4">
         <f>(G112 - G133 - G121)*$G$30</f>
-        <v>0</v>
+        <v>10931.697702960402</v>
       </c>
       <c r="H144" s="4">
         <f>(H112 - H133 - H121)*$H$30+SUM(H91:H94)</f>
-        <v>36104.190999999999</v>
+        <v>36943.686047039599</v>
       </c>
       <c r="J144" s="4">
         <f>(J112 - J133 - J121)*$G$30</f>
-        <v>0</v>
+        <v>10088.976214210876</v>
       </c>
       <c r="K144" s="4">
         <f>(K112 - K133 - K121)*$H$30+SUM(K91:K94)</f>
-        <v>33183.970417880526</v>
+        <v>34866.701411741393</v>
       </c>
       <c r="M144" s="4">
         <f>(M112 - M133 - M121)*$G$30</f>
-        <v>0</v>
+        <v>9220.1553859644791</v>
       </c>
       <c r="N144" s="4">
         <f>(N112 - N133 - N121)*$H$30+SUM(N91:N94)</f>
-        <v>30175.176046879413</v>
+        <v>32727.700888143867</v>
       </c>
       <c r="P144" s="4">
         <f>(P112 - P133 - P121)*$G$30</f>
-        <v>0</v>
+        <v>8341.6941716529673</v>
       </c>
       <c r="Q144" s="4">
         <f>(Q112 - Q133 - Q121)*$H$30+SUM(Q91:Q94)</f>
-        <v>27009.647776529317</v>
+        <v>30440.781722816362</v>
       </c>
       <c r="S144" s="4">
         <f>(S112 - S133 - S121)*$G$30</f>
-        <v>0</v>
+        <v>7272.4695703694815</v>
       </c>
       <c r="T144" s="4">
         <f>(T112 - T133 - T121)*$H$30+SUM(T91:T94)</f>
-        <v>24464.344728676238</v>
+        <v>27115.480213028492</v>
       </c>
       <c r="V144" s="4">
         <f>(V112 - V133 - V121)*$G$30</f>
-        <v>0</v>
+        <v>6551.7956955946229</v>
       </c>
       <c r="W144" s="4">
         <f>(W112 - W133 - W121)*$H$30+SUM(W91:W94)</f>
-        <v>24245.411357047091</v>
+        <v>24450.873781739971</v>
       </c>
       <c r="Y144" s="4">
         <f>(Y112 - Y133 - Y121)*$G$30</f>
-        <v>0</v>
+        <v>6466.2561671525018</v>
       </c>
       <c r="Z144" s="4">
         <f>(Z112 - Z133 - Z121)*$H$30+SUM(Z91:Z94)</f>
-        <v>24163.802947564651</v>
+        <v>24233.450603308444</v>
       </c>
       <c r="AA144" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="AB144" s="53" t="s">
-        <v>415</v>
-      </c>
-      <c r="AC144" s="54" t="s">
+        <v>357</v>
+      </c>
+      <c r="AB144" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="AC144" s="43" t="s">
         <v>323</v>
       </c>
     </row>
@@ -13798,67 +13825,67 @@
       </c>
       <c r="G145" s="4">
         <f>G144*$G21</f>
-        <v>0</v>
+        <v>3279.5093108881206</v>
       </c>
       <c r="H145" s="4">
         <f>H144*$H21</f>
-        <v>9026.0477499999997</v>
+        <v>9235.9215117598997</v>
       </c>
       <c r="J145" s="4">
         <f>J144*$G21</f>
-        <v>0</v>
+        <v>3026.6928642632624</v>
       </c>
       <c r="K145" s="4">
         <f>K144*$H21</f>
-        <v>8295.9926044701315</v>
+        <v>8716.6753529353482</v>
       </c>
       <c r="M145" s="4">
         <f>M144*$G21</f>
-        <v>0</v>
+        <v>2766.0466157893438</v>
       </c>
       <c r="N145" s="4">
         <f>N144*$H21</f>
-        <v>7543.7940117198532</v>
+        <v>8181.9252220359667</v>
       </c>
       <c r="P145" s="4">
         <f>P144*$G21</f>
-        <v>0</v>
+        <v>2502.5082514958899</v>
       </c>
       <c r="Q145" s="4">
         <f>Q144*$H21</f>
-        <v>6752.4119441323292</v>
+        <v>7610.1954307040905</v>
       </c>
       <c r="S145" s="4">
         <f>S144*$G21</f>
-        <v>0</v>
+        <v>2181.7408711108442</v>
       </c>
       <c r="T145" s="4">
         <f>T144*$H21</f>
-        <v>6116.0861821690596</v>
+        <v>6778.8700532571229</v>
       </c>
       <c r="V145" s="4">
         <f>V144*$G21</f>
-        <v>0</v>
+        <v>1965.5387086783867</v>
       </c>
       <c r="W145" s="4">
         <f>W144*$H21</f>
-        <v>6061.3528392617727</v>
+        <v>6112.7184454349926</v>
       </c>
       <c r="Y145" s="4">
         <f>Y144*$G21</f>
-        <v>0</v>
+        <v>1939.8768501457505</v>
       </c>
       <c r="Z145" s="4">
         <f>Z144*$H21</f>
-        <v>6040.9507368911627</v>
+        <v>6058.3626508271109</v>
       </c>
       <c r="AA145" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB145" s="53" t="s">
-        <v>416</v>
-      </c>
-      <c r="AC145" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB145" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="AC145" s="43" t="s">
         <v>323</v>
       </c>
     </row>
@@ -13874,67 +13901,67 @@
       </c>
       <c r="G146" s="4">
         <f>G133*$G21</f>
-        <v>0</v>
+        <v>158890.56631329903</v>
       </c>
       <c r="H146" s="4">
         <f>(H133+G132)*$H21</f>
-        <v>498425</v>
+        <v>364747.44473891752</v>
       </c>
       <c r="J146" s="4">
         <f>J133*$G21</f>
-        <v>0</v>
+        <v>159651.28671256074</v>
       </c>
       <c r="K146" s="4">
         <f>(K133+J132)*$H21</f>
-        <v>510902.29746569326</v>
+        <v>376360.43448466924</v>
       </c>
       <c r="M146" s="4">
         <f>M133*$G21</f>
-        <v>0</v>
+        <v>165236.9416100017</v>
       </c>
       <c r="N146" s="4">
         <f>(N133+M132)*$H21</f>
-        <v>526256.32443655387</v>
+        <v>387232.76079748792</v>
       </c>
       <c r="P146" s="4">
         <f>P133*$G21</f>
-        <v>0</v>
+        <v>167100.1165964648</v>
       </c>
       <c r="Q146" s="4">
         <f>(Q133+P132)*$H21</f>
-        <v>550219.49483389896</v>
+        <v>409363.4099140655</v>
       </c>
       <c r="S146" s="4">
         <f>S133*$G21</f>
-        <v>0</v>
+        <v>203079.06990564257</v>
       </c>
       <c r="T146" s="4">
         <f>(T133+S132)*$H21</f>
-        <v>455260.13045221305</v>
+        <v>578520.65636090992</v>
       </c>
       <c r="V146" s="4">
         <f>V133*$G21</f>
-        <v>0</v>
+        <v>137249.17837432391</v>
       </c>
       <c r="W146" s="4">
         <f>(W133+V132)*$H21</f>
-        <v>84469.532084686201</v>
+        <v>473067.72698955116</v>
       </c>
       <c r="Y146" s="4">
         <f>Y133*$G21</f>
-        <v>0</v>
+        <v>15741.643372419052</v>
       </c>
       <c r="Z146" s="4">
         <f>(Z133+Y132)*$H21</f>
-        <v>55188.032319049009</v>
+        <v>84041.505291484005</v>
       </c>
       <c r="AA146" s="38" t="s">
-        <v>360</v>
-      </c>
-      <c r="AB146" s="53" t="s">
-        <v>417</v>
-      </c>
-      <c r="AC146" s="54" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB146" s="42" t="s">
+        <v>415</v>
+      </c>
+      <c r="AC146" s="43" t="s">
         <v>323</v>
       </c>
     </row>
@@ -13950,7 +13977,7 @@
       </c>
       <c r="G147" s="4">
         <f>G121-G124*G125-G122</f>
-        <v>0</v>
+        <v>2175</v>
       </c>
       <c r="H147" s="4">
         <f>H121-G124*H125-H122+H54</f>
@@ -13958,59 +13985,59 @@
       </c>
       <c r="J147" s="4">
         <f>J121-J124*J125-J122</f>
-        <v>0</v>
+        <v>2499.4278140400493</v>
       </c>
       <c r="K147" s="4">
         <f>K121-J124*K125-K122+K54</f>
-        <v>2738.9186302400958</v>
+        <v>2809.4177657259334</v>
       </c>
       <c r="M147" s="4">
         <f>M121-M124*M125-M122</f>
-        <v>0</v>
+        <v>2152.52429893215</v>
       </c>
       <c r="N147" s="4">
         <f>N121-M124*N125-N122+N54</f>
-        <v>2132.015251621935</v>
+        <v>2252.8263196575672</v>
       </c>
       <c r="P147" s="4">
         <f>P121-P124*P125-P122</f>
-        <v>0</v>
+        <v>2378.667547907201</v>
       </c>
       <c r="Q147" s="4">
         <f>Q121-P124*Q125-Q122+Q54</f>
-        <v>3909.4374276017033</v>
+        <v>4283.8917473166084</v>
       </c>
       <c r="S147" s="4">
         <f>S121-S124*S125-S122</f>
-        <v>0</v>
+        <v>3051.2552091325515</v>
       </c>
       <c r="T147" s="4">
         <f>T121-S124*T125-T122+T54</f>
-        <v>698.05606326293889</v>
+        <v>800.37687838970226</v>
       </c>
       <c r="V147" s="4">
         <f>V121-V124*V125-V122</f>
-        <v>0</v>
+        <v>2626.3244695064477</v>
       </c>
       <c r="W147" s="4">
         <f>W121-V124*W125-W122+W54</f>
-        <v>1646.9794064741623</v>
+        <v>1859.8672306260451</v>
       </c>
       <c r="Y147" s="4">
         <f>Y121-Y124*Y125-Y122</f>
-        <v>0</v>
+        <v>2329.2475988760525</v>
       </c>
       <c r="Z147" s="4">
         <f>Z121-Y124*Z125-Z122+Z54</f>
-        <v>1866.5258081229777</v>
+        <v>1888.8340116135732</v>
       </c>
       <c r="AA147" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="AB147" s="53" t="s">
-        <v>418</v>
-      </c>
-      <c r="AC147" s="54" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB147" s="42" t="s">
+        <v>416</v>
+      </c>
+      <c r="AC147" s="43" t="s">
         <v>323</v>
       </c>
     </row>
@@ -14026,7 +14053,7 @@
       </c>
       <c r="G148" s="4">
         <f>MAX((G121 - G122)*$G21-G16*G9,0)</f>
-        <v>0</v>
+        <v>2128.25</v>
       </c>
       <c r="H148" s="4">
         <f>MAX((H121-H122+H54)*$H21-H16*H9,0)</f>
@@ -14034,59 +14061,59 @@
       </c>
       <c r="J148" s="4">
         <f>MAX((J121 - J122)*$G21-J16*J9,0)</f>
-        <v>0</v>
+        <v>2440.2984140400481</v>
       </c>
       <c r="K148" s="4">
         <f>MAX((K121-K122+K54)*$H21-K16*K9,0)</f>
-        <v>2075.4561918667464</v>
+        <v>2134.2054714382775</v>
       </c>
       <c r="M148" s="4">
         <f>MAX((M121 - M122)*$G21-M16*M9,0)</f>
-        <v>0</v>
+        <v>2096.1250989321488</v>
       </c>
       <c r="N148" s="4">
         <f>MAX((N121-N122+N54)*$H21-N16*N9,0)</f>
-        <v>1599.8089763516123</v>
+        <v>1700.4848663813059</v>
       </c>
       <c r="P148" s="4">
         <f>MAX((P121 - P122)*$G21-P16*P9,0)</f>
-        <v>0</v>
+        <v>2317.1445479071999</v>
       </c>
       <c r="Q148" s="4">
         <f>MAX((Q121-Q122+Q54)*$H21-Q16*Q9,0)</f>
-        <v>2892.9109230014201</v>
+        <v>3204.9561894305079</v>
       </c>
       <c r="S148" s="4">
         <f>MAX((S121 - S122)*$G21-S16*S9,0)</f>
-        <v>0</v>
+        <v>2954.0152091325508</v>
       </c>
       <c r="T148" s="4">
         <f>MAX((T121-T122+T54)*$H21-T16*T9,0)</f>
-        <v>506.08458605244897</v>
+        <v>591.35193199141838</v>
       </c>
       <c r="V148" s="4">
         <f>MAX((V121 - V122)*$G21-V16*V9,0)</f>
-        <v>0</v>
+        <v>2551.1878695064484</v>
       </c>
       <c r="W148" s="4">
         <f>MAX((W121-W122+W54)*$H21-W16*W9,0)</f>
-        <v>1150.7228387284683</v>
+        <v>1328.129358855037</v>
       </c>
       <c r="Y148" s="4">
         <f>MAX((Y121 - Y122)*$G21-Y16*Y9,0)</f>
-        <v>0</v>
+        <v>2235.7849988760527</v>
       </c>
       <c r="Z148" s="4">
         <f>MAX((Z121-Z122+Z54)*$H21-Z16*Z9,0)</f>
-        <v>1354.9901734358141</v>
+        <v>1373.5803430113106</v>
       </c>
       <c r="AA148" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="AB148" s="53" t="s">
-        <v>419</v>
-      </c>
-      <c r="AC148" s="54" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB148" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC148" s="43" t="s">
         <v>323</v>
       </c>
     </row>
@@ -14099,7 +14126,7 @@
       </c>
       <c r="G149" s="4">
         <f>J111*J7*(1+$G21)</f>
-        <v>0</v>
+        <v>19480.5</v>
       </c>
       <c r="H149" s="4">
         <f>(K111*K7+SUMPRODUCT(H38:H41,H86:H89))*(1+$H21)</f>
@@ -14107,7 +14134,7 @@
       </c>
       <c r="J149" s="4">
         <f>M111*M7*(1+$G21)</f>
-        <v>0</v>
+        <v>19456.32</v>
       </c>
       <c r="K149" s="4">
         <f>(N111*N7+SUMPRODUCT(K38:K41,K86:K89))*(1+$H21)</f>
@@ -14115,7 +14142,7 @@
       </c>
       <c r="M149" s="4">
         <f>P111*P7*(1+$G21)</f>
-        <v>0</v>
+        <v>19433.7</v>
       </c>
       <c r="N149" s="4">
         <f>(Q111*Q7+SUMPRODUCT(N38:N41,N86:N89))*(1+$H21)</f>
@@ -14123,7 +14150,7 @@
       </c>
       <c r="P149" s="4">
         <f>S111*S7*(1+$G21)</f>
-        <v>0</v>
+        <v>19406.400000000001</v>
       </c>
       <c r="Q149" s="4">
         <f>(T111*T7+SUMPRODUCT(Q38:Q41,Q86:Q89))*(1+$H21)</f>
@@ -14131,7 +14158,7 @@
       </c>
       <c r="S149" s="4">
         <f>V111*V7*(1+$G21)</f>
-        <v>0</v>
+        <v>19367.400000000001</v>
       </c>
       <c r="T149" s="4">
         <f>(W111*W7+SUMPRODUCT(T38:T41,T86:T89))*(1+$H21)</f>
@@ -14139,11 +14166,11 @@
       </c>
       <c r="V149" s="4">
         <f>Y111*Y7*(1+$G21)</f>
-        <v>0</v>
+        <v>16645.359712099693</v>
       </c>
       <c r="W149" s="4">
         <f>(Z111*Z7+SUMPRODUCT(W38:W41,W86:W89))*(1+$H21)</f>
-        <v>250354.37158478529</v>
+        <v>286838.73750000005</v>
       </c>
       <c r="Y149" s="4" t="e">
         <f>AB111*AB7*(1+$G21)</f>
@@ -14154,22 +14181,22 @@
         <v>#VALUE!</v>
       </c>
       <c r="AA149" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="AB149" s="53" t="s">
-        <v>420</v>
-      </c>
-      <c r="AC149" s="54" t="s">
-        <v>366</v>
+        <v>361</v>
+      </c>
+      <c r="AB149" s="42" t="s">
+        <v>418</v>
+      </c>
+      <c r="AC149" s="43" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="150" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB150" s="53"/>
-      <c r="AC150" s="54"/>
+      <c r="AB150" s="42"/>
+      <c r="AC150" s="43"/>
     </row>
     <row r="151" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB151" s="53"/>
-      <c r="AC151" s="54"/>
+      <c r="AB151" s="42"/>
+      <c r="AC151" s="43"/>
     </row>
     <row r="152" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B152" s="24" t="s">
@@ -14177,7 +14204,7 @@
       </c>
       <c r="G152" s="4">
         <f>G147+G122</f>
-        <v>0</v>
+        <v>2425</v>
       </c>
       <c r="H152" s="4">
         <f>H147+H122</f>
@@ -14185,58 +14212,58 @@
       </c>
       <c r="J152" s="4">
         <f>J147+J122</f>
-        <v>0</v>
+        <v>2815.6278140400491</v>
       </c>
       <c r="K152" s="4">
         <f>K147+K122</f>
-        <v>3816.9186302400958</v>
+        <v>3887.4177657259334</v>
       </c>
       <c r="M152" s="4">
         <f>M147+M122</f>
-        <v>0</v>
+        <v>2454.1242989321499</v>
       </c>
       <c r="N152" s="4">
         <f>N147+N122</f>
-        <v>3053.2152516219348</v>
+        <v>3174.026319657567</v>
       </c>
       <c r="P152" s="4">
         <f>P147+P122</f>
-        <v>0</v>
+        <v>2707.667547907201</v>
       </c>
       <c r="Q152" s="4">
         <f>Q147+Q122</f>
-        <v>5810.2374276017035</v>
+        <v>6184.6917473166086</v>
       </c>
       <c r="S152" s="4">
         <f>S147+S122</f>
-        <v>0</v>
+        <v>3571.2552091325515</v>
       </c>
       <c r="T152" s="4">
         <f>T147+T122</f>
-        <v>1091.9560632629389</v>
+        <v>1194.2768783897022</v>
       </c>
       <c r="V152" s="4">
         <f>V147+V122</f>
-        <v>0</v>
+        <v>3028.1244695064479</v>
       </c>
       <c r="W152" s="4">
         <f>W147+W122</f>
-        <v>2801.9794064741623</v>
+        <v>3014.8672306260451</v>
       </c>
       <c r="Y152" s="4">
         <f>Y147+Y122</f>
-        <v>0</v>
+        <v>2829.0475988760527</v>
       </c>
       <c r="Z152" s="4">
         <f>Z147+Z122</f>
-        <v>2910.5258081229777</v>
-      </c>
-      <c r="AB152" s="53"/>
-      <c r="AC152" s="54"/>
+        <v>2932.8340116135732</v>
+      </c>
+      <c r="AB152" s="42"/>
+      <c r="AC152" s="43"/>
     </row>
     <row r="153" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB153" s="53"/>
-      <c r="AC153" s="54"/>
+      <c r="AB153" s="42"/>
+      <c r="AC153" s="43"/>
     </row>
     <row r="154" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B154" s="38" t="s">
@@ -14247,7 +14274,7 @@
       </c>
       <c r="G154" s="4">
         <f>G124+G133+H133+G132</f>
-        <v>2000000</v>
+        <v>2000000.0000000002</v>
       </c>
       <c r="J154" s="4">
         <f>J124+J133+K133</f>
@@ -14263,30 +14290,30 @@
       </c>
       <c r="S154" s="4">
         <f>S124+S133+T133</f>
-        <v>1822669.3192897991</v>
+        <v>3000000</v>
       </c>
       <c r="V154" s="4">
         <f>V124+V133+W133</f>
-        <v>341721.08028718451</v>
+        <v>2360235.9498395934</v>
       </c>
       <c r="Y154" s="4">
         <f>Y124+Y133+Z133</f>
-        <v>225107.35616181631</v>
+        <v>398480.35616514197</v>
       </c>
       <c r="AA154" s="38" t="s">
-        <v>363</v>
-      </c>
-      <c r="AB154" s="53" t="s">
-        <v>448</v>
-      </c>
-      <c r="AC154" s="54" t="s">
-        <v>378</v>
+        <v>362</v>
+      </c>
+      <c r="AB154" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC154" s="43" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="155" spans="2:30" x14ac:dyDescent="0.2">
       <c r="G155" s="4">
         <f>G154/G33</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J155" s="4">
         <f>J154/J33</f>
@@ -14302,89 +14329,112 @@
       </c>
       <c r="S155" s="4">
         <f>S154/S33</f>
-        <v>0.60755643976326634</v>
+        <v>1</v>
       </c>
       <c r="V155" s="4">
         <f>V154/V33</f>
-        <v>1.366884321148738E-2</v>
+        <v>9.4409437993583742E-2</v>
       </c>
       <c r="Y155" s="4">
         <f>Y154/Y33</f>
-        <v>8.9328315937228689E-2</v>
+        <v>0.15812712546235794</v>
       </c>
       <c r="AA155" s="38"/>
-      <c r="AB155" s="53"/>
-      <c r="AC155" s="54"/>
+      <c r="AB155" s="42"/>
+      <c r="AC155" s="43"/>
     </row>
     <row r="156" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B156" s="38" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C156" s="31" t="s">
         <v>162</v>
       </c>
       <c r="AA156" s="38" t="s">
+        <v>391</v>
+      </c>
+      <c r="AB156" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC156" s="43" t="s">
         <v>393</v>
-      </c>
-      <c r="AB156" s="53" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC156" s="54" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="157" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B157" s="38"/>
       <c r="AA157" s="38"/>
-      <c r="AB157" s="53"/>
-      <c r="AC157" s="54"/>
+      <c r="AB157" s="42"/>
+      <c r="AC157" s="43"/>
     </row>
     <row r="158" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA158" s="38"/>
-      <c r="AB158" s="53"/>
-      <c r="AC158" s="54"/>
+      <c r="AB158" s="42"/>
+      <c r="AC158" s="43"/>
     </row>
     <row r="159" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA159" s="38"/>
-      <c r="AB159" s="53"/>
-      <c r="AC159" s="54"/>
+      <c r="AB159" s="42"/>
+      <c r="AC159" s="43"/>
     </row>
     <row r="160" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA160" s="38"/>
-      <c r="AB160" s="53"/>
-      <c r="AC160" s="54"/>
+      <c r="AB160" s="42"/>
+      <c r="AC160" s="43"/>
       <c r="AD160">
         <v>20</v>
       </c>
     </row>
     <row r="161" spans="27:30" x14ac:dyDescent="0.2">
       <c r="AA161" s="38"/>
-      <c r="AB161" s="53"/>
-      <c r="AC161" s="54"/>
+      <c r="AB161" s="42"/>
+      <c r="AC161" s="43"/>
       <c r="AD161">
         <v>20</v>
       </c>
     </row>
     <row r="162" spans="27:30" x14ac:dyDescent="0.2">
       <c r="AA162" s="38"/>
-      <c r="AB162" s="53"/>
-      <c r="AC162" s="54"/>
+      <c r="AB162" s="42"/>
+      <c r="AC162" s="43"/>
       <c r="AD162">
         <v>20</v>
       </c>
     </row>
     <row r="163" spans="27:30" x14ac:dyDescent="0.2">
       <c r="AA163" s="38"/>
-      <c r="AB163" s="53"/>
-      <c r="AC163" s="54"/>
+      <c r="AB163" s="42"/>
+      <c r="AC163" s="43"/>
     </row>
     <row r="164" spans="27:30" x14ac:dyDescent="0.2">
       <c r="AA164" s="38"/>
-      <c r="AB164" s="53"/>
-      <c r="AC164" s="54"/>
+      <c r="AB164" s="42"/>
+      <c r="AC164" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E70:E72"/>
+    <mergeCell ref="E75:E78"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="C56:C59"/>
     <mergeCell ref="B101:B104"/>
     <mergeCell ref="C101:C104"/>
     <mergeCell ref="B49:B52"/>
@@ -14398,29 +14448,6 @@
     <mergeCell ref="C91:C94"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="C73:C76"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="C56:C59"/>
-    <mergeCell ref="AE4:AG4"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E70:E72"/>
-    <mergeCell ref="E75:E78"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4510B7CF-81D4-9047-B8C9-3D7CF0029853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A037414-49F1-A147-8E76-3E5546D626CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7820" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="14800" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="482">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -880,15 +880,9 @@
     <t>arr_total_biomass_c_ag_available_from_conversion</t>
   </si>
   <si>
-    <t>A(t)</t>
-  </si>
-  <si>
     <t>A_{in}(t)</t>
   </si>
   <si>
-    <t>A_{out}(t)</t>
-  </si>
-  <si>
     <t>\hat{a}^{(y)}_{out}(t)</t>
   </si>
   <si>
@@ -913,15 +907,9 @@
     <t>this has been modified to use a logistic ramp rather than alinear</t>
   </si>
   <si>
-    <t>A^*(t)</t>
-  </si>
-  <si>
     <t>d(t)</t>
   </si>
   <si>
-    <t>A^*(t + 1)</t>
-  </si>
-  <si>
     <t>\overline{Y}_{conv}(t, u)</t>
   </si>
   <si>
@@ -1015,12 +1003,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>D^{(y)}(t, u)</t>
-  </si>
-  <si>
     <t>A^{(y)}(t, u)</t>
   </si>
   <si>
@@ -1033,36 +1015,15 @@
     <t>M</t>
   </si>
   <si>
-    <t>\overline{M}_0^*</t>
-  </si>
-  <si>
-    <t>\Delta B</t>
-  </si>
-  <si>
-    <t>\overline{M}_0</t>
-  </si>
-  <si>
-    <t>\overline{\overline{B}}</t>
-  </si>
-  <si>
     <t>\overline{y}(t)</t>
   </si>
   <si>
-    <t>\overline{m}(t)</t>
-  </si>
-  <si>
-    <t>\underline{m}(t)</t>
-  </si>
-  <si>
     <t>\Delta_0\overline{b}</t>
   </si>
   <si>
     <t>Vector (length 2) storing nominal sequestration factor (mass of biomass growth per time period) associated with forests. Used in NPP fit from integration target.</t>
   </si>
   <si>
-    <t>\overline{b}_{conv}(t)</t>
-  </si>
-  <si>
     <t>\overline{y}_{availconv}(t)</t>
   </si>
   <si>
@@ -1072,12 +1033,6 @@
     <t>\overline{Y}_{presconv}(t, u)</t>
   </si>
   <si>
-    <t>\overline{b}_{presconv}(t)</t>
-  </si>
-  <si>
-    <t>\overline{b}_{availconv}(t)</t>
-  </si>
-  <si>
     <t>r</t>
   </si>
   <si>
@@ -1096,9 +1051,6 @@
     <t>u</t>
   </si>
   <si>
-    <t>\overline{\overline{B}}'</t>
-  </si>
-  <si>
     <t>Vector ($T $) giving adjusted--based on availability in buffer zone--total quantity of biomass available for removals.</t>
   </si>
   <si>
@@ -1114,12 +1066,6 @@
     <t>\tilde{A}^{(y)}(t, u)</t>
   </si>
   <si>
-    <t>\overline{L}_{decomp}(t, v)</t>
-  </si>
-  <si>
-    <t>\underline{L}_{decomp}(t, v)</t>
-  </si>
-  <si>
     <t>\underline{L}_{rmv}(t, v)</t>
   </si>
   <si>
@@ -1141,12 +1087,6 @@
     <t>G</t>
   </si>
   <si>
-    <t>\overline{\eta}</t>
-  </si>
-  <si>
-    <t>\underline{\eta}</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -1165,9 +1105,6 @@
     <t>y</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
@@ -1201,9 +1138,6 @@
     <t>\overline{Y}_{avail}(t, u)</t>
   </si>
   <si>
-    <t>\overline{B}^{(0)}_{avail}</t>
-  </si>
-  <si>
     <t>\tilde{\Psi}^{(0)}(t, v)</t>
   </si>
   <si>
@@ -1363,12 +1297,6 @@
     <t>Vector ($n_T$) storing total above-ground biomass stock in young forests at the start of time period $t$.</t>
   </si>
   <si>
-    <t>Vector ($n_T$) storing total above-ground biomass stock in all forests at the start of time period $t$.</t>
-  </si>
-  <si>
-    <t>Vector ($n_T$) storing total below-ground biomass stock in all forests at the start of time period $t$.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vector ($n_T$) storing demand for removals from all forests, excluding those from conversions. </t>
   </si>
   <si>
@@ -1477,10 +1405,88 @@
     <t>Matrix ($n_T \times 2$) storing removals from all forests by type (columns), excluding conversions. Removals from young secondary forests are added to those removals from original secondary forests.</t>
   </si>
   <si>
-    <t>\overline{b}^{(0)}</t>
-  </si>
-  <si>
-    <t>xf</t>
+    <t>\Psi^{(0)}(t, v)</t>
+  </si>
+  <si>
+    <t>A^*(t, v)</t>
+  </si>
+  <si>
+    <t>A(t, v)</t>
+  </si>
+  <si>
+    <t>A_{out}(t, v)</t>
+  </si>
+  <si>
+    <t>A^*(t + 1, v)</t>
+  </si>
+  <si>
+    <t>\overline{\eta}(t, v)</t>
+  </si>
+  <si>
+    <t>\underline{\eta}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{b}^{(0)}(v)</t>
+  </si>
+  <si>
+    <t>\overline{L}_{dcmp}(t, v)</t>
+  </si>
+  <si>
+    <t>\underline{L}_{dcmp}(t, v)</t>
+  </si>
+  <si>
+    <t>vec_young_biomass_c_loss_from_decomposition (T)</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing the total loss of biomass in young forests due to decomposition.</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>\overline{l}^{(y)}_{dcmp}(t)</t>
+  </si>
+  <si>
+    <t>\overline{L}^{(y)}_{dcmp}(t, u)</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing total above-ground biomass stock in all forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>Matrix ($n_T \times 2$) storing total below-ground biomass stock in all forests at the start of time period $t$.</t>
+  </si>
+  <si>
+    <t>\overline{B}_{conv}(t, v)</t>
+  </si>
+  <si>
+    <t>\underline{M}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{M}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{B}_{presconv}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{B}_{availconv}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{B}^{(0)}_{avail}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{\overline{B}}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{\overline{B}}'(t, v)</t>
+  </si>
+  <si>
+    <t>\Delta\overline{B}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{M}_0^*(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{M}_0(t, v)</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1542,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1621,6 +1627,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1634,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1803,6 +1815,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6947,14 +6965,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F0562-A765-A442-B9DB-CF71D123E451}">
-  <dimension ref="A1:AO164"/>
+  <dimension ref="A1:AO165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="6.5" style="48" customWidth="1"/>
     <col min="2" max="2" width="62.1640625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="14" style="27" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="2" style="27" customWidth="1"/>
     <col min="4" max="4" width="4.1640625" style="23" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="27" style="22" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="44" style="10" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="10" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="4" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
@@ -6971,7 +6990,7 @@
     <col min="23" max="23" width="12.5" style="4" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
     <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="62.1640625" style="24" customWidth="1"/>
+    <col min="27" max="27" width="24" style="24" customWidth="1"/>
     <col min="28" max="28" width="64.5" style="47" customWidth="1"/>
     <col min="29" max="29" width="14.6640625" style="48" customWidth="1"/>
     <col min="30" max="30" width="14.6640625" customWidth="1"/>
@@ -6981,6 +7000,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60"/>
       <c r="B1" s="24"/>
       <c r="C1" s="27"/>
       <c r="D1" s="23"/>
@@ -7017,6 +7037,7 @@
       <c r="AC1" s="27"/>
     </row>
     <row r="2" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60"/>
       <c r="B2" s="24"/>
       <c r="C2" s="27"/>
       <c r="D2" s="23"/>
@@ -7055,6 +7076,7 @@
       <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="1:41" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="60"/>
       <c r="B3" s="24"/>
       <c r="C3" s="27"/>
       <c r="D3" s="23"/>
@@ -7144,8 +7166,8 @@
       </c>
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>453</v>
+      <c r="A5" s="61" t="s">
+        <v>429</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7189,13 +7211,13 @@
       </c>
       <c r="Z5" s="55"/>
       <c r="AA5" s="24" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AB5" s="40" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="AD5" s="36" t="s">
         <v>230</v>
@@ -7291,9 +7313,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
-        <v>454</v>
+    <row r="7" spans="1:41" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
@@ -7359,13 +7381,13 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>290</v>
+        <v>455</v>
       </c>
       <c r="AB7" s="42" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="AC7" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7391,8 +7413,8 @@
       </c>
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
-        <v>454</v>
+      <c r="A8" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
@@ -7460,13 +7482,13 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>279</v>
+        <v>456</v>
       </c>
       <c r="AB8" s="42" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="AC8" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7491,9 +7513,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
-        <v>454</v>
+    <row r="9" spans="1:41" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>222</v>
@@ -7547,13 +7569,13 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>281</v>
+        <v>457</v>
       </c>
       <c r="AB9" s="42" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="AC9" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7578,9 +7600,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
-        <v>454</v>
+    <row r="10" spans="1:41" ht="85" x14ac:dyDescent="0.2">
+      <c r="A10" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>221</v>
@@ -7620,13 +7642,13 @@
         <v>0</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AC10" s="43" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7639,9 +7661,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
-        <v>454</v>
+    <row r="11" spans="1:41" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>219</v>
@@ -7681,13 +7703,13 @@
         <v>0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AB11" s="42" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AC11" s="43" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7700,9 +7722,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
-        <v>454</v>
+    <row r="12" spans="1:41" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>220</v>
@@ -7735,13 +7757,13 @@
         <v>110</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AB12" s="42" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7755,8 +7777,8 @@
       </c>
     </row>
     <row r="13" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
-        <v>454</v>
+      <c r="A13" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>158</v>
@@ -7824,21 +7846,21 @@
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>292</v>
+        <v>458</v>
       </c>
       <c r="AB13" s="42" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AC13" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
       <c r="AG13" s="19"/>
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
-        <v>454</v>
+      <c r="A14" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>223</v>
@@ -7871,13 +7893,13 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AB14" s="42" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AC14" s="43" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7891,8 +7913,8 @@
       </c>
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
-        <v>454</v>
+      <c r="A15" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>244</v>
@@ -7949,24 +7971,24 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>366</v>
+        <v>459</v>
       </c>
       <c r="AB15" s="42" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="AC15" s="43" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
       <c r="AG15" s="19"/>
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>454</v>
+      <c r="A16" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>162</v>
@@ -8028,24 +8050,24 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
       <c r="AB16" s="42" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="AC16" s="43" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
       <c r="AG16" s="19"/>
     </row>
-    <row r="17" spans="1:33" ht="51" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
-        <v>454</v>
+    <row r="17" spans="1:33" ht="136" x14ac:dyDescent="0.2">
+      <c r="A17" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
@@ -8060,13 +8082,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="AB17" s="42" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="AC17" s="43" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -8079,12 +8101,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
-        <v>454</v>
+    <row r="18" spans="1:33" ht="102" x14ac:dyDescent="0.2">
+      <c r="A18" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
@@ -8102,13 +8124,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="AB18" s="42" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="AC18" s="43" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -8121,9 +8143,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="51" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>454</v>
+    <row r="19" spans="1:33" ht="136" x14ac:dyDescent="0.2">
+      <c r="A19" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>224</v>
@@ -8139,13 +8161,13 @@
         <v>0.67</v>
       </c>
       <c r="AA19" s="39" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AB19" s="42" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AC19" s="43" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -8158,9 +8180,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>454</v>
+    <row r="20" spans="1:33" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>226</v>
@@ -8178,13 +8200,13 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="AB20" s="42" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AC20" s="43" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -8197,9 +8219,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
-        <v>454</v>
+    <row r="21" spans="1:33" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>228</v>
@@ -8217,21 +8239,21 @@
         <v>0.25</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AB21" s="42" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AC21" s="44" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
       <c r="AG21" s="19"/>
     </row>
-    <row r="22" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
-        <v>454</v>
+    <row r="22" spans="1:33" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>275</v>
@@ -8251,13 +8273,13 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="AB22" s="42" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="AC22" s="43" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="AE22" s="19">
         <v>12</v>
@@ -8270,9 +8292,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
-        <v>454</v>
+    <row r="23" spans="1:33" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>227</v>
@@ -8292,13 +8314,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="AB23" s="42" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AC23" s="43" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -8326,8 +8348,8 @@
       </c>
     </row>
     <row r="25" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
-        <v>454</v>
+      <c r="A25" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>159</v>
@@ -8381,13 +8403,13 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="AB25" s="42" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AC25" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE25" s="19">
         <v>10</v>
@@ -8400,9 +8422,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
-        <v>454</v>
+    <row r="26" spans="1:33" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>274</v>
@@ -8442,13 +8464,13 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="AB26" s="42" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AC26" s="43" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="AE26" s="19">
         <v>6</v>
@@ -8461,9 +8483,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="19" t="s">
-        <v>454</v>
+    <row r="27" spans="1:33" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>160</v>
@@ -8531,13 +8553,13 @@
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="AB27" s="42" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AC27" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AE27" s="19">
         <v>3</v>
@@ -8550,7 +8572,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="F28" s="15" t="s">
         <v>169</v>
       </c>
@@ -8582,8 +8604,8 @@
       </c>
     </row>
     <row r="29" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
-        <v>454</v>
+      <c r="A29" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>273</v>
@@ -8604,18 +8626,18 @@
         <v>0.92</v>
       </c>
       <c r="AA29" s="38" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="AB29" s="42" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="AC29" s="43" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
-        <v>454</v>
+      <c r="A30" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>229</v>
@@ -8640,13 +8662,13 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="AB30" s="42" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AC30" s="43" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -8675,9 +8697,9 @@
       <c r="AB32" s="40"/>
       <c r="AC32" s="43"/>
     </row>
-    <row r="33" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
-        <v>454</v>
+    <row r="33" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+      <c r="A33" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B33" s="38" t="s">
         <v>168</v>
@@ -8710,20 +8732,20 @@
         <v>2520000</v>
       </c>
       <c r="AA33" s="38" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AB33" s="42" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AC33" s="43" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.2">
       <c r="AB34" s="40"/>
       <c r="AC34" s="43"/>
     </row>
-    <row r="35" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="F35" s="11" t="s">
         <v>57</v>
       </c>
@@ -8744,7 +8766,7 @@
       <c r="AB35" s="40"/>
       <c r="AC35" s="43"/>
     </row>
-    <row r="36" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="F36" s="15" t="s">
         <v>139</v>
       </c>
@@ -8826,11 +8848,11 @@
       <c r="AC37" s="43"/>
     </row>
     <row r="38" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="19" t="s">
-        <v>454</v>
+      <c r="A38" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C38" s="50" t="s">
         <v>174</v>
@@ -8918,21 +8940,21 @@
         <v>85</v>
       </c>
       <c r="AA38" s="38" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AB38" s="42" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="AC38" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="19" t="s">
-        <v>454</v>
+      <c r="A39" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C39" s="50"/>
       <c r="F39" s="14" t="s">
@@ -9017,21 +9039,21 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AB39" s="42" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="AC39" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="19" t="s">
-        <v>454</v>
+      <c r="A40" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C40" s="50"/>
       <c r="F40" s="14" t="s">
@@ -9115,13 +9137,13 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="AB40" s="42" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="AC40" s="43" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9217,9 +9239,9 @@
       <c r="AB42" s="40"/>
       <c r="AC42" s="43"/>
     </row>
-    <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="19" t="s">
-        <v>454</v>
+    <row r="43" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A43" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B43" s="51" t="s">
         <v>189</v>
@@ -9234,40 +9256,40 @@
         <v>0</v>
       </c>
       <c r="K43" s="4">
-        <f>IF(H38=0, 0, H96*J38/H38)</f>
+        <f>IF(H38=0, 0, H97*J38/H38)</f>
         <v>0</v>
       </c>
       <c r="N43" s="4">
-        <f>IF(K38=0, 0, K96*M38/K38)</f>
+        <f>IF(K38=0, 0, K97*M38/K38)</f>
         <v>0</v>
       </c>
       <c r="Q43" s="4">
-        <f>IF(N38=0, 0, N96*P38/N38)</f>
+        <f>IF(N38=0, 0, N97*P38/N38)</f>
         <v>0</v>
       </c>
       <c r="T43" s="4">
-        <f>IF(Q38=0, 0, Q96*S38/Q38)</f>
+        <f>IF(Q38=0, 0, Q97*S38/Q38)</f>
         <v>0</v>
       </c>
       <c r="W43" s="4">
-        <f>IF(T38=0, 0, T96*V38/T38)</f>
+        <f>IF(T38=0, 0, T97*V38/T38)</f>
         <v>0</v>
       </c>
       <c r="Z43" s="4">
-        <f>IF(W38=0, 0, W96*Y38/W38)</f>
+        <f>IF(W38=0, 0, W97*Y38/W38)</f>
         <v>0</v>
       </c>
       <c r="AA43" s="38" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AB43" s="42" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="AC43" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B44" s="51"/>
       <c r="C44" s="50"/>
       <c r="F44" s="14" t="s">
@@ -9277,34 +9299,34 @@
         <v>0</v>
       </c>
       <c r="K44" s="4">
-        <f>IF(H39=0, 0, H97*J39/H39)</f>
+        <f>IF(H39=0, 0, H98*J39/H39)</f>
         <v>0</v>
       </c>
       <c r="N44" s="4">
-        <f>IF(K39=0, 0, K97*M39/K39)</f>
+        <f>IF(K39=0, 0, K98*M39/K39)</f>
         <v>0</v>
       </c>
       <c r="Q44" s="4">
-        <f>IF(N39=0, 0, N97*P39/N39)</f>
+        <f>IF(N39=0, 0, N98*P39/N39)</f>
         <v>0</v>
       </c>
       <c r="T44" s="4">
-        <f>IF(Q39=0, 0, Q97*S39/Q39)</f>
+        <f>IF(Q39=0, 0, Q98*S39/Q39)</f>
         <v>0</v>
       </c>
       <c r="W44" s="4">
-        <f>IF(T39=0, 0, T97*V39/T39)</f>
+        <f>IF(T39=0, 0, T98*V39/T39)</f>
         <v>0</v>
       </c>
       <c r="Z44" s="4">
-        <f>IF(W39=0, 0, W97*Y39/W39)</f>
+        <f>IF(W39=0, 0, W98*Y39/W39)</f>
         <v>0</v>
       </c>
       <c r="AA44" s="38"/>
       <c r="AB44" s="42"/>
       <c r="AC44" s="43"/>
     </row>
-    <row r="45" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B45" s="51"/>
       <c r="C45" s="50"/>
       <c r="F45" s="14" t="s">
@@ -9314,34 +9336,34 @@
         <v>0</v>
       </c>
       <c r="K45" s="4">
-        <f>IF(H40=0, 0, H98*J40/H40)</f>
+        <f>IF(H40=0, 0, H99*J40/H40)</f>
         <v>0</v>
       </c>
       <c r="N45" s="4">
-        <f>IF(K40=0, 0, K98*M40/K40)</f>
+        <f>IF(K40=0, 0, K99*M40/K40)</f>
         <v>0</v>
       </c>
       <c r="Q45" s="4">
-        <f>IF(N40=0, 0, N98*P40/N40)</f>
+        <f>IF(N40=0, 0, N99*P40/N40)</f>
         <v>0</v>
       </c>
       <c r="T45" s="4">
-        <f>IF(Q40=0, 0, Q98*S40/Q40)</f>
+        <f>IF(Q40=0, 0, Q99*S40/Q40)</f>
         <v>0</v>
       </c>
       <c r="W45" s="4">
-        <f>IF(T40=0, 0, T98*V40/T40)</f>
+        <f>IF(T40=0, 0, T99*V40/T40)</f>
         <v>0</v>
       </c>
       <c r="Z45" s="4">
-        <f>IF(W40=0, 0, W98*Y40/W40)</f>
+        <f>IF(W40=0, 0, W99*Y40/W40)</f>
         <v>0</v>
       </c>
       <c r="AA45" s="38"/>
       <c r="AB45" s="42"/>
       <c r="AC45" s="43"/>
     </row>
-    <row r="46" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B46" s="51"/>
       <c r="C46" s="50"/>
       <c r="F46" s="14" t="s">
@@ -9351,27 +9373,27 @@
         <v>0</v>
       </c>
       <c r="K46" s="4">
-        <f>IF(H41=0, 0, H99*J41/H41)</f>
+        <f>IF(H41=0, 0, H100*J41/H41)</f>
         <v>0</v>
       </c>
       <c r="N46" s="4">
-        <f>IF(K41=0, 0, K99*M41/K41)</f>
+        <f>IF(K41=0, 0, K100*M41/K41)</f>
         <v>0</v>
       </c>
       <c r="Q46" s="4">
-        <f>IF(N41=0, 0, N99*P41/N41)</f>
+        <f>IF(N41=0, 0, N100*P41/N41)</f>
         <v>0</v>
       </c>
       <c r="T46" s="4">
-        <f>IF(Q41=0, 0, Q99*S41/Q41)</f>
+        <f>IF(Q41=0, 0, Q100*S41/Q41)</f>
         <v>0</v>
       </c>
       <c r="W46" s="4">
-        <f>IF(T41=0, 0, T99*V41/T41)</f>
+        <f>IF(T41=0, 0, T100*V41/T41)</f>
         <v>0</v>
       </c>
       <c r="Z46" s="4">
-        <f>IF(W41=0, 0, W99*Y41/W41)</f>
+        <f>IF(W41=0, 0, W100*Y41/W41)</f>
         <v>0</v>
       </c>
       <c r="AA46" s="38"/>
@@ -9379,8 +9401,8 @@
       <c r="AC46" s="43"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A47" s="19" t="s">
-        <v>454</v>
+      <c r="A47" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B47" s="38" t="s">
         <v>190</v>
@@ -9418,13 +9440,13 @@
         <v>0</v>
       </c>
       <c r="AA47" s="38" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AB47" s="42" t="s">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="AC47" s="43" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9434,9 +9456,9 @@
       <c r="AB48" s="40"/>
       <c r="AC48" s="43"/>
     </row>
-    <row r="49" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="19" t="s">
-        <v>454</v>
+    <row r="49" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="A49" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B49" s="51" t="s">
         <v>258</v>
@@ -9479,16 +9501,16 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="AB49" s="42" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="AC49" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B50" s="51"/>
       <c r="C50" s="50"/>
       <c r="E50" s="52"/>
@@ -9527,7 +9549,7 @@
       <c r="AB50" s="42"/>
       <c r="AC50" s="43"/>
     </row>
-    <row r="51" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B51" s="51"/>
       <c r="C51" s="50"/>
       <c r="E51" s="52"/>
@@ -9566,7 +9588,7 @@
       <c r="AB51" s="42"/>
       <c r="AC51" s="43"/>
     </row>
-    <row r="52" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B52" s="51"/>
       <c r="C52" s="50"/>
       <c r="E52" s="52"/>
@@ -9606,8 +9628,8 @@
       <c r="AC52" s="43"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A53" s="19" t="s">
-        <v>454</v>
+      <c r="A53" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B53" s="38" t="s">
         <v>259</v>
@@ -9645,18 +9667,18 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="AB53" s="42" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="AC53" s="43" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A54" s="19" t="s">
-        <v>454</v>
+      <c r="A54" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B54" s="38" t="s">
         <v>261</v>
@@ -9692,13 +9714,13 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="AB54" s="42" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="AC54" s="43" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
@@ -9706,9 +9728,9 @@
       <c r="AB55" s="42"/>
       <c r="AC55" s="43"/>
     </row>
-    <row r="56" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A56" s="19" t="s">
-        <v>454</v>
+    <row r="56" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A56" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B56" s="51" t="s">
         <v>191</v>
@@ -9748,16 +9770,16 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AB56" s="42" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="AC56" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B57" s="51"/>
       <c r="C57" s="50"/>
       <c r="F57" s="14" t="s">
@@ -9795,7 +9817,7 @@
       <c r="AB57" s="42"/>
       <c r="AC57" s="43"/>
     </row>
-    <row r="58" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B58" s="51"/>
       <c r="C58" s="50"/>
       <c r="F58" s="14" t="s">
@@ -9833,7 +9855,7 @@
       <c r="AB58" s="42"/>
       <c r="AC58" s="43"/>
     </row>
-    <row r="59" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B59" s="51"/>
       <c r="C59" s="50"/>
       <c r="F59" s="14" t="s">
@@ -9872,8 +9894,8 @@
       <c r="AC59" s="43"/>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A60" s="19" t="s">
-        <v>454</v>
+      <c r="A60" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B60" s="38" t="s">
         <v>192</v>
@@ -9911,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="AA60" s="38" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AB60" s="42" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="AC60" s="43" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
@@ -9925,9 +9947,9 @@
       <c r="AB61" s="42"/>
       <c r="AC61" s="43"/>
     </row>
-    <row r="62" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="19" t="s">
-        <v>454</v>
+    <row r="62" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A62" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B62" s="51" t="s">
         <v>178</v>
@@ -9967,16 +9989,16 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AB62" s="42" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="AC62" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="63" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B63" s="51"/>
       <c r="C63" s="50"/>
       <c r="F63" s="14" t="s">
@@ -10012,7 +10034,7 @@
       <c r="AB63" s="42"/>
       <c r="AC63" s="43"/>
     </row>
-    <row r="64" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B64" s="51"/>
       <c r="C64" s="50"/>
       <c r="F64" s="14" t="s">
@@ -10047,7 +10069,7 @@
       <c r="AB64" s="42"/>
       <c r="AC64" s="43"/>
     </row>
-    <row r="65" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B65" s="51"/>
       <c r="C65" s="50"/>
       <c r="F65" s="14" t="s">
@@ -10082,11 +10104,11 @@
       <c r="AC65" s="43"/>
     </row>
     <row r="66" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A66" s="19" t="s">
-        <v>454</v>
+      <c r="A66" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>162</v>
@@ -10095,13 +10117,13 @@
         <v>49</v>
       </c>
       <c r="AA66" s="38" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="AB66" s="42" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="AC66" s="43" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.2">
@@ -10109,9 +10131,9 @@
       <c r="AB67" s="42"/>
       <c r="AC67" s="43"/>
     </row>
-    <row r="68" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A68" s="19" t="s">
-        <v>454</v>
+    <row r="68" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A68" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B68" s="51" t="s">
         <v>233</v>
@@ -10151,16 +10173,16 @@
         <v>113.71737449773646</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AB68" s="42" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="AC68" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="69" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B69" s="51"/>
       <c r="C69" s="50"/>
       <c r="F69" s="14" t="s">
@@ -10194,7 +10216,7 @@
       <c r="AB69" s="42"/>
       <c r="AC69" s="43"/>
     </row>
-    <row r="70" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B70" s="51"/>
       <c r="C70" s="50"/>
       <c r="E70" s="52"/>
@@ -10225,7 +10247,7 @@
       <c r="AB70" s="42"/>
       <c r="AC70" s="43"/>
     </row>
-    <row r="71" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B71" s="51"/>
       <c r="C71" s="50"/>
       <c r="E71" s="52"/>
@@ -10262,9 +10284,9 @@
       <c r="AB72" s="42"/>
       <c r="AC72" s="43"/>
     </row>
-    <row r="73" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" s="19" t="s">
-        <v>454</v>
+    <row r="73" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A73" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B73" s="51" t="s">
         <v>231</v>
@@ -10279,40 +10301,40 @@
         <v>0</v>
       </c>
       <c r="K73" s="4">
-        <f>INT(J$4-$AG$6 &gt; $E81)*MAX(H96-$H$22*H38-K43,0)</f>
+        <f>INT(J$4-$AG$6 &gt; $E81)*MAX(H97-$H$22*H38-K43,0)</f>
         <v>0</v>
       </c>
       <c r="N73" s="4">
-        <f>INT(M$4-$AG$6 &gt; $E81)*MAX(K96-$H$22*K38-N43,0)</f>
+        <f>INT(M$4-$AG$6 &gt; $E81)*MAX(K97-$H$22*K38-N43,0)</f>
         <v>0</v>
       </c>
       <c r="Q73" s="4">
-        <f>INT(P$4-$AG$6 &gt; $E81)*MAX(N96-$H$22*N38-Q43,0)</f>
+        <f>INT(P$4-$AG$6 &gt; $E81)*MAX(N97-$H$22*N38-Q43,0)</f>
         <v>0</v>
       </c>
       <c r="T73" s="4">
-        <f>INT(S$4-$AG$6 &gt; $E81)*MAX(Q96-$H$22*Q38-T43,0)</f>
+        <f>INT(S$4-$AG$6 &gt; $E81)*MAX(Q97-$H$22*Q38-T43,0)</f>
         <v>0</v>
       </c>
       <c r="W73" s="4">
-        <f>INT(V$4-$AG$6 &gt; $E81)*MAX(T96-$H$22*T38-W43,0)</f>
+        <f>INT(V$4-$AG$6 &gt; $E81)*MAX(T97-$H$22*T38-W43,0)</f>
         <v>0</v>
       </c>
       <c r="Z73" s="4">
-        <f>INT(Y$4-$AG$6 &gt; $E81)*MAX(W96-$H$22*W38-Z43,0)</f>
+        <f>INT(Y$4-$AG$6 &gt; $E81)*MAX(W97-$H$22*W38-Z43,0)</f>
         <v>0</v>
       </c>
       <c r="AA73" s="38" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="AB73" s="42" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="AC73" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="74" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B74" s="51"/>
       <c r="C74" s="50"/>
       <c r="F74" s="14" t="s">
@@ -10322,34 +10344,34 @@
         <v>0</v>
       </c>
       <c r="K74" s="4">
-        <f>INT(J$4-$AG$6 &gt; $E82)*MAX(H97-$H$22*H39-K44,0)</f>
+        <f>INT(J$4-$AG$6 &gt; $E82)*MAX(H98-$H$22*H39-K44,0)</f>
         <v>0</v>
       </c>
       <c r="N74" s="4">
-        <f>INT(M$4-$AG$6 &gt; $E82)*MAX(K97-$H$22*K39-N44,0)</f>
+        <f>INT(M$4-$AG$6 &gt; $E82)*MAX(K98-$H$22*K39-N44,0)</f>
         <v>0</v>
       </c>
       <c r="Q74" s="4">
-        <f>INT(P$4-$AG$6 &gt; $E82)*MAX(N97-$H$22*N39-Q44,0)</f>
+        <f>INT(P$4-$AG$6 &gt; $E82)*MAX(N98-$H$22*N39-Q44,0)</f>
         <v>0</v>
       </c>
       <c r="T74" s="4">
-        <f>INT(S$4-$AG$6 &gt; $E82)*MAX(Q97-$H$22*Q39-T44,0)</f>
+        <f>INT(S$4-$AG$6 &gt; $E82)*MAX(Q98-$H$22*Q39-T44,0)</f>
         <v>0</v>
       </c>
       <c r="W74" s="4">
-        <f>INT(V$4-$AG$6 &gt; $E82)*MAX(T97-$H$22*T39-W44,0)</f>
+        <f>INT(V$4-$AG$6 &gt; $E82)*MAX(T98-$H$22*T39-W44,0)</f>
         <v>0</v>
       </c>
       <c r="Z74" s="4">
-        <f>INT(Y$4-$AG$6 &gt; $E82)*MAX(W97-$H$22*W39-Z44,0)</f>
+        <f>INT(Y$4-$AG$6 &gt; $E82)*MAX(W98-$H$22*W39-Z44,0)</f>
         <v>0</v>
       </c>
       <c r="AA74" s="38"/>
       <c r="AB74" s="42"/>
       <c r="AC74" s="43"/>
     </row>
-    <row r="75" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B75" s="51"/>
       <c r="C75" s="50"/>
       <c r="E75" s="52" t="s">
@@ -10362,34 +10384,34 @@
         <v>0</v>
       </c>
       <c r="K75" s="4">
-        <f>INT(J$4-$AG$6 &gt; $E83)*MAX(H98-$H$22*H40-K45,0)</f>
+        <f>INT(J$4-$AG$6 &gt; $E83)*MAX(H99-$H$22*H40-K45,0)</f>
         <v>0</v>
       </c>
       <c r="N75" s="4">
-        <f>INT(M$4-$AG$6 &gt; $E83)*MAX(K98-$H$22*K40-N45,0)</f>
+        <f>INT(M$4-$AG$6 &gt; $E83)*MAX(K99-$H$22*K40-N45,0)</f>
         <v>0</v>
       </c>
       <c r="Q75" s="4">
-        <f>INT(P$4-$AG$6 &gt; $E83)*MAX(N98-$H$22*N40-Q45,0)</f>
+        <f>INT(P$4-$AG$6 &gt; $E83)*MAX(N99-$H$22*N40-Q45,0)</f>
         <v>0</v>
       </c>
       <c r="T75" s="4">
-        <f>INT(S$4-$AG$6 &gt; $E83)*MAX(Q98-$H$22*Q40-T45,0)</f>
+        <f>INT(S$4-$AG$6 &gt; $E83)*MAX(Q99-$H$22*Q40-T45,0)</f>
         <v>0</v>
       </c>
       <c r="W75" s="4">
-        <f>INT(V$4-$AG$6 &gt; $E83)*MAX(T98-$H$22*T40-W45,0)</f>
+        <f>INT(V$4-$AG$6 &gt; $E83)*MAX(T99-$H$22*T40-W45,0)</f>
         <v>0</v>
       </c>
       <c r="Z75" s="4">
-        <f>INT(Y$4-$AG$6 &gt; $E83)*MAX(W98-$H$22*W40-Z45,0)</f>
+        <f>INT(Y$4-$AG$6 &gt; $E83)*MAX(W99-$H$22*W40-Z45,0)</f>
         <v>0</v>
       </c>
       <c r="AA75" s="38"/>
       <c r="AB75" s="42"/>
       <c r="AC75" s="43"/>
     </row>
-    <row r="76" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B76" s="51"/>
       <c r="C76" s="50"/>
       <c r="E76" s="52"/>
@@ -10400,36 +10422,36 @@
         <v>0</v>
       </c>
       <c r="K76" s="4">
-        <f>INT(J$4-$AG$6 &gt; $E84)*MAX(H99-$H$22*H41-K46,0)</f>
+        <f>INT(J$4-$AG$6 &gt; $E84)*MAX(H100-$H$22*H41-K46,0)</f>
         <v>0</v>
       </c>
       <c r="N76" s="4">
-        <f>INT(M$4-$AG$6 &gt; $E84)*MAX(K99-$H$22*K41-N46,0)</f>
+        <f>INT(M$4-$AG$6 &gt; $E84)*MAX(K100-$H$22*K41-N46,0)</f>
         <v>0</v>
       </c>
       <c r="Q76" s="4">
-        <f>INT(P$4-$AG$6 &gt; $E84)*MAX(N99-$H$22*N41-Q46,0)</f>
+        <f>INT(P$4-$AG$6 &gt; $E84)*MAX(N100-$H$22*N41-Q46,0)</f>
         <v>0</v>
       </c>
       <c r="T76" s="4">
-        <f>INT(S$4-$AG$6 &gt; $E84)*MAX(Q99-$H$22*Q41-T46,0)</f>
+        <f>INT(S$4-$AG$6 &gt; $E84)*MAX(Q100-$H$22*Q41-T46,0)</f>
         <v>0</v>
       </c>
       <c r="W76" s="4">
-        <f>INT(V$4-$AG$6 &gt; $E84)*MAX(T99-$H$22*T41-W46,0)</f>
+        <f>INT(V$4-$AG$6 &gt; $E84)*MAX(T100-$H$22*T41-W46,0)</f>
         <v>0</v>
       </c>
       <c r="Z76" s="4">
-        <f>INT(Y$4-$AG$6 &gt; $E84)*MAX(W99-$H$22*W41-Z46,0)</f>
+        <f>INT(Y$4-$AG$6 &gt; $E84)*MAX(W100-$H$22*W41-Z46,0)</f>
         <v>0</v>
       </c>
       <c r="AA76" s="38"/>
       <c r="AB76" s="42"/>
       <c r="AC76" s="43"/>
     </row>
-    <row r="77" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A77" s="19" t="s">
-        <v>454</v>
+    <row r="77" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A77" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>232</v>
@@ -10469,13 +10491,13 @@
         <v>0</v>
       </c>
       <c r="AA77" s="45" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="AB77" s="42" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="AC77" s="43" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="AF77" t="s">
         <v>106</v>
@@ -10494,11 +10516,11 @@
       </c>
     </row>
     <row r="79" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="19" t="s">
-        <v>454</v>
+      <c r="A79" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C79" s="50" t="s">
         <v>174</v>
@@ -10528,24 +10550,24 @@
         <v>0</v>
       </c>
       <c r="AA79" s="38" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AB79" s="42" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="AC79" s="43" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="AD79" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A80" s="19" t="s">
-        <v>454</v>
+    <row r="80" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A80" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C80" s="50"/>
       <c r="F80" s="14" t="s">
@@ -10556,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="4">
-        <f>IF(G80&gt;=G$132, IF(G79&lt;G$132, G$132-G79, 0),H73)</f>
+        <f>IF(G80&gt;=G$133, IF(G79&lt;G$133, G$133-G79, 0),H73)</f>
         <v>0</v>
       </c>
       <c r="J80" s="4">
@@ -10564,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="4">
-        <f>IF(J80&gt;=J$132, IF(J79&lt;J$132, J$132-J79, 0),K73)</f>
+        <f>IF(J80&gt;=J$133, IF(J79&lt;J$133, J$133-J79, 0),K73)</f>
         <v>0</v>
       </c>
       <c r="M80" s="4">
@@ -10572,7 +10594,7 @@
         <v>0</v>
       </c>
       <c r="N80" s="4">
-        <f>IF(M80&gt;=M$132, IF(M79&lt;M$132, M$132-M79, 0),N73)</f>
+        <f>IF(M80&gt;=M$133, IF(M79&lt;M$133, M$133-M79, 0),N73)</f>
         <v>0</v>
       </c>
       <c r="P80" s="4">
@@ -10580,7 +10602,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="4">
-        <f>IF(P80&gt;=P$132, IF(P79&lt;P$132, P$132-P79, 0),Q73)</f>
+        <f>IF(P80&gt;=P$133, IF(P79&lt;P$133, P$133-P79, 0),Q73)</f>
         <v>0</v>
       </c>
       <c r="S80" s="4">
@@ -10588,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="4">
-        <f>IF(S80&gt;=S$132, IF(S79&lt;S$132, S$132-S79, 0),T73)</f>
+        <f>IF(S80&gt;=S$133, IF(S79&lt;S$133, S$133-S79, 0),T73)</f>
         <v>0</v>
       </c>
       <c r="V80" s="4">
@@ -10596,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="W80" s="4">
-        <f>IF(V80&gt;=V$132, IF(V79&lt;V$132, V$132-V79, 0),W73)</f>
+        <f>IF(V80&gt;=V$133, IF(V79&lt;V$133, V$133-V79, 0),W73)</f>
         <v>0</v>
       </c>
       <c r="Y80" s="4">
@@ -10604,20 +10626,20 @@
         <v>0</v>
       </c>
       <c r="Z80" s="4">
-        <f>IF(Y80&gt;=Y$132, IF(Y79&lt;Y$132, Y$132-Y79, 0),Z73)</f>
+        <f>IF(Y80&gt;=Y$133, IF(Y79&lt;Y$133, Y$133-Y79, 0),Z73)</f>
         <v>0</v>
       </c>
       <c r="AA80" s="38" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="AB80" s="42" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="AC80" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B81" s="41"/>
       <c r="C81" s="50"/>
       <c r="E81" s="22">
@@ -10631,7 +10653,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="4">
-        <f>IF(G81&gt;=G$132, IF(G80&lt;G$132, G$132-G80, 0),H74)</f>
+        <f>IF(G81&gt;=G$133, IF(G80&lt;G$133, G$133-G80, 0),H74)</f>
         <v>0</v>
       </c>
       <c r="J81" s="4">
@@ -10639,7 +10661,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="4">
-        <f>IF(J81&gt;=J$132, IF(J80&lt;J$132, J$132-J80, 0),K74)</f>
+        <f>IF(J81&gt;=J$133, IF(J80&lt;J$133, J$133-J80, 0),K74)</f>
         <v>0</v>
       </c>
       <c r="M81" s="4">
@@ -10647,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="4">
-        <f>IF(M81&gt;=M$132, IF(M80&lt;M$132, M$132-M80, 0),N74)</f>
+        <f>IF(M81&gt;=M$133, IF(M80&lt;M$133, M$133-M80, 0),N74)</f>
         <v>0</v>
       </c>
       <c r="P81" s="4">
@@ -10655,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="4">
-        <f>IF(P81&gt;=P$132, IF(P80&lt;P$132, P$132-P80, 0),Q74)</f>
+        <f>IF(P81&gt;=P$133, IF(P80&lt;P$133, P$133-P80, 0),Q74)</f>
         <v>0</v>
       </c>
       <c r="S81" s="4">
@@ -10663,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="4">
-        <f>IF(S81&gt;=S$132, IF(S80&lt;S$132, S$132-S80, 0),T74)</f>
+        <f>IF(S81&gt;=S$133, IF(S80&lt;S$133, S$133-S80, 0),T74)</f>
         <v>0</v>
       </c>
       <c r="V81" s="4">
@@ -10671,7 +10693,7 @@
         <v>0</v>
       </c>
       <c r="W81" s="4">
-        <f>IF(V81&gt;=V$132, IF(V80&lt;V$132, V$132-V80, 0),W74)</f>
+        <f>IF(V81&gt;=V$133, IF(V80&lt;V$133, V$133-V80, 0),W74)</f>
         <v>0</v>
       </c>
       <c r="Y81" s="4">
@@ -10679,14 +10701,14 @@
         <v>0</v>
       </c>
       <c r="Z81" s="4">
-        <f>IF(Y81&gt;=Y$132, IF(Y80&lt;Y$132, Y$132-Y80, 0),Z74)</f>
+        <f>IF(Y81&gt;=Y$133, IF(Y80&lt;Y$133, Y$133-Y80, 0),Z74)</f>
         <v>0</v>
       </c>
       <c r="AA81" s="37"/>
       <c r="AB81" s="42"/>
       <c r="AC81" s="43"/>
     </row>
-    <row r="82" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B82" s="41"/>
       <c r="C82" s="50"/>
       <c r="E82" s="22">
@@ -10700,7 +10722,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="4">
-        <f>IF(G82&gt;=G$132, IF(G81&lt;G$132, G$132-G81, 0),H75)</f>
+        <f>IF(G82&gt;=G$133, IF(G81&lt;G$133, G$133-G81, 0),H75)</f>
         <v>0</v>
       </c>
       <c r="J82" s="4">
@@ -10708,7 +10730,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="4">
-        <f>IF(J82&gt;=J$132, IF(J81&lt;J$132, J$132-J81, 0),K75)</f>
+        <f>IF(J82&gt;=J$133, IF(J81&lt;J$133, J$133-J81, 0),K75)</f>
         <v>0</v>
       </c>
       <c r="M82" s="4">
@@ -10716,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="4">
-        <f>IF(M82&gt;=M$132, IF(M81&lt;M$132, M$132-M81, 0),N75)</f>
+        <f>IF(M82&gt;=M$133, IF(M81&lt;M$133, M$133-M81, 0),N75)</f>
         <v>0</v>
       </c>
       <c r="P82" s="4">
@@ -10724,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="4">
-        <f>IF(P82&gt;=P$132, IF(P81&lt;P$132, P$132-P81, 0),Q75)</f>
+        <f>IF(P82&gt;=P$133, IF(P81&lt;P$133, P$133-P81, 0),Q75)</f>
         <v>0</v>
       </c>
       <c r="S82" s="4">
@@ -10732,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="T82" s="4">
-        <f>IF(S82&gt;=S$132, IF(S81&lt;S$132, S$132-S81, 0),T75)</f>
+        <f>IF(S82&gt;=S$133, IF(S81&lt;S$133, S$133-S81, 0),T75)</f>
         <v>0</v>
       </c>
       <c r="V82" s="4">
@@ -10740,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="W82" s="4">
-        <f>IF(V82&gt;=V$132, IF(V81&lt;V$132, V$132-V81, 0),W75)</f>
+        <f>IF(V82&gt;=V$133, IF(V81&lt;V$133, V$133-V81, 0),W75)</f>
         <v>0</v>
       </c>
       <c r="Y82" s="4">
@@ -10748,14 +10770,14 @@
         <v>0</v>
       </c>
       <c r="Z82" s="4">
-        <f>IF(Y82&gt;=Y$132, IF(Y81&lt;Y$132, Y$132-Y81, 0),Z75)</f>
+        <f>IF(Y82&gt;=Y$133, IF(Y81&lt;Y$133, Y$133-Y81, 0),Z75)</f>
         <v>0</v>
       </c>
       <c r="AA82" s="37"/>
       <c r="AB82" s="42"/>
       <c r="AC82" s="43"/>
     </row>
-    <row r="83" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B83" s="41"/>
       <c r="C83" s="50"/>
       <c r="E83" s="22">
@@ -10769,7 +10791,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="4">
-        <f>IF(G83&gt;=G$132, IF(G82&lt;G$132, G$132-G82, 0),H76)</f>
+        <f>IF(G83&gt;=G$133, IF(G82&lt;G$133, G$133-G82, 0),H76)</f>
         <v>0</v>
       </c>
       <c r="J83" s="4">
@@ -10777,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="4">
-        <f>IF(J83&gt;=J$132, IF(J82&lt;J$132, J$132-J82, 0),K76)</f>
+        <f>IF(J83&gt;=J$133, IF(J82&lt;J$133, J$133-J82, 0),K76)</f>
         <v>0</v>
       </c>
       <c r="M83" s="4">
@@ -10785,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="4">
-        <f>IF(M83&gt;=M$132, IF(M82&lt;M$132, M$132-M82, 0),N76)</f>
+        <f>IF(M83&gt;=M$133, IF(M82&lt;M$133, M$133-M82, 0),N76)</f>
         <v>0</v>
       </c>
       <c r="P83" s="4">
@@ -10793,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="4">
-        <f>IF(P83&gt;=P$132, IF(P82&lt;P$132, P$132-P82, 0),Q76)</f>
+        <f>IF(P83&gt;=P$133, IF(P82&lt;P$133, P$133-P82, 0),Q76)</f>
         <v>0</v>
       </c>
       <c r="S83" s="4">
@@ -10801,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="4">
-        <f>IF(S83&gt;=S$132, IF(S82&lt;S$132, S$132-S82, 0),T76)</f>
+        <f>IF(S83&gt;=S$133, IF(S82&lt;S$133, S$133-S82, 0),T76)</f>
         <v>0</v>
       </c>
       <c r="V83" s="4">
@@ -10809,7 +10831,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="4">
-        <f>IF(V83&gt;=V$132, IF(V82&lt;V$132, V$132-V82, 0),W76)</f>
+        <f>IF(V83&gt;=V$133, IF(V82&lt;V$133, V$133-V82, 0),W76)</f>
         <v>0</v>
       </c>
       <c r="Y83" s="4">
@@ -10817,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="4">
-        <f>IF(Y83&gt;=Y$132, IF(Y82&lt;Y$132, Y$132-Y82, 0),Z76)</f>
+        <f>IF(Y83&gt;=Y$133, IF(Y82&lt;Y$133, Y$133-Y82, 0),Z76)</f>
         <v>0</v>
       </c>
       <c r="AA83" s="37"/>
@@ -10855,12 +10877,12 @@
       <c r="AB85" s="42"/>
       <c r="AC85" s="43"/>
     </row>
-    <row r="86" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="19" t="s">
-        <v>454</v>
+    <row r="86" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A86" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C86" s="50" t="s">
         <v>174</v>
@@ -10873,7 +10895,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="4">
-        <f>IF(H96=0,1,MIN(MAX((H96/H68-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(H97=0,1,MIN(MAX((H97/H68-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="K86" s="4">
@@ -10881,7 +10903,7 @@
         <v>0.01</v>
       </c>
       <c r="M86" s="4">
-        <f>IF(K96=0,1,MIN(MAX((K96/K68-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(K97=0,1,MIN(MAX((K97/K68-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="N86" s="4">
@@ -10889,7 +10911,7 @@
         <v>0.05</v>
       </c>
       <c r="P86" s="4">
-        <f>IF(N96=0,1,MIN(MAX((N96/N68-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(N97=0,1,MIN(MAX((N97/N68-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Q86" s="4">
@@ -10897,7 +10919,7 @@
         <v>0.12</v>
       </c>
       <c r="S86" s="4">
-        <f>IF(Q96=0,1,MIN(MAX((Q96/Q68-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(Q97=0,1,MIN(MAX((Q97/Q68-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="T86" s="4">
@@ -10905,7 +10927,7 @@
         <v>0.2</v>
       </c>
       <c r="V86" s="4">
-        <f>IF(T96=0,1,MIN(MAX((T96/T68-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(T97=0,1,MIN(MAX((T97/T68-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="W86" s="4">
@@ -10913,7 +10935,7 @@
         <v>0.36</v>
       </c>
       <c r="Y86" s="4">
-        <f>IF(W96=0,1,MIN(MAX((W96/W68-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(W97=0,1,MIN(MAX((W97/W68-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Z86" s="4">
@@ -10921,21 +10943,21 @@
         <v>0.6</v>
       </c>
       <c r="AA86" s="37" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AB86" s="42" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC86" s="43" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="61" t="s">
         <v>430</v>
       </c>
-      <c r="AC86" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="87" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="19" t="s">
-        <v>454</v>
-      </c>
       <c r="B87" s="37" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C87" s="50"/>
       <c r="F87" s="14" t="s">
@@ -10946,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="4">
-        <f>IF(H97=0,1,MIN(MAX((H97/H69-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(H98=0,1,MIN(MAX((H98/H69-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="K87" s="4">
@@ -10954,7 +10976,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="4">
-        <f>IF(K97=0,1,MIN(MAX((K97/K69-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(K98=0,1,MIN(MAX((K98/K69-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="N87" s="4">
@@ -10962,7 +10984,7 @@
         <v>0.01</v>
       </c>
       <c r="P87" s="4">
-        <f>IF(N97=0,1,MIN(MAX((N97/N69-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(N98=0,1,MIN(MAX((N98/N69-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Q87" s="4">
@@ -10970,7 +10992,7 @@
         <v>0.05</v>
       </c>
       <c r="S87" s="4">
-        <f>IF(Q97=0,1,MIN(MAX((Q97/Q69-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(Q98=0,1,MIN(MAX((Q98/Q69-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="T87" s="4">
@@ -10978,7 +11000,7 @@
         <v>0.12</v>
       </c>
       <c r="V87" s="4">
-        <f>IF(T97=0,1,MIN(MAX((T97/T69-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(T98=0,1,MIN(MAX((T98/T69-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="W87" s="4">
@@ -10986,7 +11008,7 @@
         <v>0.2</v>
       </c>
       <c r="Y87" s="4">
-        <f>IF(W97=0,1,MIN(MAX((W97/W69-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(W98=0,1,MIN(MAX((W98/W69-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Z87" s="4">
@@ -10994,16 +11016,16 @@
         <v>0.36</v>
       </c>
       <c r="AA87" s="37" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AB87" s="42" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="AC87" s="43" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B88" s="37"/>
       <c r="C88" s="50"/>
       <c r="F88" s="14" t="s">
@@ -11014,7 +11036,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="4">
-        <f>IF(H98=0,1,MIN(MAX((H98/H70-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(H99=0,1,MIN(MAX((H99/H70-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="K88" s="4">
@@ -11022,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="4">
-        <f>IF(K98=0,1,MIN(MAX((K98/K70-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(K99=0,1,MIN(MAX((K99/K70-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="N88" s="4">
@@ -11030,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="P88" s="4">
-        <f>IF(N98=0,1,MIN(MAX((N98/N70-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(N99=0,1,MIN(MAX((N99/N70-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Q88" s="4">
@@ -11038,7 +11060,7 @@
         <v>0.01</v>
       </c>
       <c r="S88" s="4">
-        <f>IF(Q98=0,1,MIN(MAX((Q98/Q70-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(Q99=0,1,MIN(MAX((Q99/Q70-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="T88" s="4">
@@ -11046,7 +11068,7 @@
         <v>0.05</v>
       </c>
       <c r="V88" s="4">
-        <f>IF(T98=0,1,MIN(MAX((T98/T70-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(T99=0,1,MIN(MAX((T99/T70-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="W88" s="4">
@@ -11054,7 +11076,7 @@
         <v>0.12</v>
       </c>
       <c r="Y88" s="4">
-        <f>IF(W98=0,1,MIN(MAX((W98/W70-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(W99=0,1,MIN(MAX((W99/W70-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Z88" s="4">
@@ -11065,7 +11087,7 @@
       <c r="AB88" s="42"/>
       <c r="AC88" s="43"/>
     </row>
-    <row r="89" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B89" s="41"/>
       <c r="C89" s="50"/>
       <c r="F89" s="14" t="s">
@@ -11076,7 +11098,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="4">
-        <f>IF(H99=0,1,MIN(MAX((H99/H71-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(H100=0,1,MIN(MAX((H100/H71-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="K89" s="4">
@@ -11084,7 +11106,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="4">
-        <f>IF(K99=0,1,MIN(MAX((K99/K71-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(K100=0,1,MIN(MAX((K100/K71-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="N89" s="4">
@@ -11092,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="4">
-        <f>IF(N99=0,1,MIN(MAX((N99/N71-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(N100=0,1,MIN(MAX((N100/N71-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Q89" s="4">
@@ -11100,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="4">
-        <f>IF(Q99=0,1,MIN(MAX((Q99/Q71-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(Q100=0,1,MIN(MAX((Q100/Q71-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="T89" s="4">
@@ -11108,7 +11130,7 @@
         <v>0.01</v>
       </c>
       <c r="V89" s="4">
-        <f>IF(T99=0,1,MIN(MAX((T99/T71-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(T100=0,1,MIN(MAX((T100/T71-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="W89" s="4">
@@ -11116,7 +11138,7 @@
         <v>0.05</v>
       </c>
       <c r="Y89" s="4">
-        <f>IF(W99=0,1,MIN(MAX((W99/W71-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <f>IF(W100=0,1,MIN(MAX((W100/W71-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Z89" s="4">
@@ -11132,9 +11154,9 @@
       <c r="AB90" s="42"/>
       <c r="AC90" s="43"/>
     </row>
-    <row r="91" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="19" t="s">
-        <v>454</v>
+    <row r="91" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="A91" s="61" t="s">
+        <v>430</v>
       </c>
       <c r="B91" s="49" t="s">
         <v>202</v>
@@ -11150,40 +11172,40 @@
         <v>0</v>
       </c>
       <c r="K91" s="4">
-        <f>(H96-K80-K43)*$G$30</f>
+        <f>(H97-K80-K43)*$G$30</f>
         <v>0</v>
       </c>
       <c r="N91" s="4">
-        <f>(K96-N80-N43)*$G$30</f>
+        <f>(K97-N80-N43)*$G$30</f>
         <v>1.3345E-3</v>
       </c>
       <c r="Q91" s="4">
-        <f>(N96-Q80-Q43)*$G$30</f>
+        <f>(N97-Q80-Q43)*$G$30</f>
         <v>8.0049048349999999E-3</v>
       </c>
       <c r="T91" s="4">
-        <f>(Q96-T80-T43)*$G$30</f>
+        <f>(Q97-T80-T43)*$G$30</f>
         <v>2.4006337134409049E-2</v>
       </c>
       <c r="W91" s="4">
-        <f>(T96-W80-W43)*$G$30</f>
+        <f>(T97-W80-W43)*$G$30</f>
         <v>5.0658647185108027E-2</v>
       </c>
       <c r="Z91" s="4">
-        <f>(W96-Z80-Z43)*$G$30</f>
+        <f>(W97-Z80-Z43)*$G$30</f>
         <v>9.8621113109027395E-2</v>
       </c>
       <c r="AA91" s="37" t="s">
-        <v>325</v>
+        <v>468</v>
       </c>
       <c r="AB91" s="42" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="AC91" s="43" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B92" s="49"/>
       <c r="C92" s="50"/>
       <c r="F92" s="14" t="s">
@@ -11194,34 +11216,34 @@
         <v>0</v>
       </c>
       <c r="K92" s="4">
-        <f>(H97-K81-K44)*$G$30</f>
+        <f>(H98-K81-K44)*$G$30</f>
         <v>0</v>
       </c>
       <c r="N92" s="4">
-        <f>(K97-N81-N44)*$G$30</f>
+        <f>(K98-N81-N44)*$G$30</f>
         <v>0</v>
       </c>
       <c r="Q92" s="4">
-        <f>(N97-Q81-Q44)*$G$30</f>
+        <f>(N98-Q81-Q44)*$G$30</f>
         <v>1.2560000000000002E-3</v>
       </c>
       <c r="T92" s="4">
-        <f>(Q97-T81-T44)*$G$30</f>
+        <f>(Q98-T81-T44)*$G$30</f>
         <v>7.5340280800000005E-3</v>
       </c>
       <c r="W92" s="4">
-        <f>(T97-W81-W44)*$G$30</f>
+        <f>(T98-W81-W44)*$G$30</f>
         <v>2.2594199655914398E-2</v>
       </c>
       <c r="Z92" s="4">
-        <f>(W97-Z81-Z44)*$G$30</f>
+        <f>(W98-Z81-Z44)*$G$30</f>
         <v>4.7678726762454618E-2</v>
       </c>
       <c r="AA92" s="37"/>
       <c r="AB92" s="42"/>
       <c r="AC92" s="43"/>
     </row>
-    <row r="93" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B93" s="49"/>
       <c r="C93" s="50"/>
       <c r="F93" s="14" t="s">
@@ -11232,34 +11254,34 @@
         <v>0</v>
       </c>
       <c r="K93" s="4">
-        <f>(H98-K82-K45)*$G$30</f>
+        <f>(H99-K82-K45)*$G$30</f>
         <v>0</v>
       </c>
       <c r="N93" s="4">
-        <f>(K98-N82-N45)*$G$30</f>
+        <f>(K99-N82-N45)*$G$30</f>
         <v>0</v>
       </c>
       <c r="Q93" s="4">
-        <f>(N98-Q82-Q45)*$G$30</f>
+        <f>(N99-Q82-Q45)*$G$30</f>
         <v>0</v>
       </c>
       <c r="T93" s="4">
-        <f>(Q98-T82-T45)*$G$30</f>
+        <f>(Q99-T82-T45)*$G$30</f>
         <v>1.4444E-3</v>
       </c>
       <c r="W93" s="4">
-        <f>(T98-W82-W45)*$G$30</f>
+        <f>(T99-W82-W45)*$G$30</f>
         <v>8.664132292000002E-3</v>
       </c>
       <c r="Z93" s="4">
-        <f>(W98-Z82-Z45)*$G$30</f>
+        <f>(W99-Z82-Z45)*$G$30</f>
         <v>2.5983329604301563E-2</v>
       </c>
       <c r="AA93" s="37"/>
       <c r="AB93" s="42"/>
       <c r="AC93" s="43"/>
     </row>
-    <row r="94" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B94" s="49"/>
       <c r="C94" s="50"/>
       <c r="F94" s="14" t="s">
@@ -11270,334 +11292,342 @@
         <v>0</v>
       </c>
       <c r="K94" s="4">
-        <f>(H99-K83-K46)*$G$30</f>
+        <f>(H100-K83-K46)*$G$30</f>
         <v>0</v>
       </c>
       <c r="N94" s="4">
-        <f>(K99-N83-N46)*$G$30</f>
+        <f>(K100-N83-N46)*$G$30</f>
         <v>0</v>
       </c>
       <c r="Q94" s="4">
-        <f>(N99-Q83-Q46)*$G$30</f>
+        <f>(N100-Q83-Q46)*$G$30</f>
         <v>0</v>
       </c>
       <c r="T94" s="4">
-        <f>(Q99-T83-T46)*$G$30</f>
+        <f>(Q100-T83-T46)*$G$30</f>
         <v>0</v>
       </c>
       <c r="W94" s="4">
-        <f>(T99-W83-W46)*$G$30</f>
+        <f>(T100-W83-W46)*$G$30</f>
         <v>6.7509999999999998E-4</v>
       </c>
       <c r="Z94" s="4">
-        <f>(W99-Z83-Z46)*$G$30</f>
+        <f>(W100-Z83-Z46)*$G$30</f>
         <v>4.049540093E-3</v>
       </c>
       <c r="AA94" s="37"/>
       <c r="AB94" s="42"/>
       <c r="AC94" s="43"/>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A95" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="B95" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="C95" s="28"/>
       <c r="F95" s="14"/>
-      <c r="AB95" s="42"/>
-      <c r="AC95" s="43"/>
-    </row>
-    <row r="96" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="B96" s="49" t="s">
+      <c r="H95" s="4">
+        <f>SUM(H91:H94)</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="4">
+        <f>SUM(K91:K94)</f>
+        <v>0</v>
+      </c>
+      <c r="N95" s="4">
+        <f>SUM(N91:N94)</f>
+        <v>1.3345E-3</v>
+      </c>
+      <c r="Q95" s="4">
+        <f>SUM(Q91:Q94)</f>
+        <v>9.2609048350000001E-3</v>
+      </c>
+      <c r="T95" s="4">
+        <f>SUM(T91:T94)</f>
+        <v>3.2984765214409045E-2</v>
+      </c>
+      <c r="W95" s="4">
+        <f>SUM(W91:W94)</f>
+        <v>8.2592079133022425E-2</v>
+      </c>
+      <c r="Z95" s="4">
+        <f>SUM(Z91:Z94)</f>
+        <v>0.17633270956878355</v>
+      </c>
+      <c r="AA95" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="AB95" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="AC95" s="43" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F96" s="14"/>
+      <c r="AB96" s="42"/>
+      <c r="AC96" s="43"/>
+    </row>
+    <row r="97" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="B97" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="C96" s="50" t="s">
+      <c r="C97" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="F96" s="14" t="s">
+      <c r="F97" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="H96" s="4">
+      <c r="H97" s="4">
         <f>H62*H38</f>
         <v>0</v>
       </c>
-      <c r="K96" s="4">
-        <f>H96 - K80 - K91 - K43 + K38*K86</f>
+      <c r="K97" s="4">
+        <f>H97 - K80 - K91 - K43 + K38*K86</f>
         <v>0.85</v>
       </c>
-      <c r="N96" s="4">
-        <f>K96 - N80 - N91 - N43 + N38*N86</f>
+      <c r="N97" s="4">
+        <f>K97 - N80 - N91 - N43 + N38*N86</f>
         <v>5.0986655000000001</v>
       </c>
-      <c r="Q96" s="4">
-        <f>N96 - Q80 - Q91 - Q43 + Q38*Q86</f>
+      <c r="Q97" s="4">
+        <f>N97 - Q80 - Q91 - Q43 + Q38*Q86</f>
         <v>15.290660595164999</v>
       </c>
-      <c r="T96" s="4">
-        <f>Q96 - T80 - T91 - T43 + T38*T86</f>
+      <c r="T97" s="4">
+        <f>Q97 - T80 - T91 - T43 + T38*T86</f>
         <v>32.266654258030592</v>
       </c>
-      <c r="W96" s="4">
-        <f>T96 - W80 - W91 - W43 + W38*W86</f>
+      <c r="W97" s="4">
+        <f>T97 - W80 - W91 - W43 + W38*W86</f>
         <v>62.815995610845476</v>
       </c>
-      <c r="Z96" s="4">
-        <f>W96 - Z80 - Z91 - Z43 + Z38*Z86</f>
+      <c r="Z97" s="4">
+        <f>W97 - Z80 - Z91 - Z43 + Z38*Z86</f>
         <v>113.71737449773644</v>
       </c>
-      <c r="AA96" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="AB96" s="42" t="s">
-        <v>432</v>
-      </c>
-      <c r="AC96" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B97" s="49"/>
-      <c r="C97" s="50"/>
-      <c r="F97" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H97" s="4">
-        <f>H63*H39</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="4">
-        <f>H97 - K81 - K92 - K44 + K39*K87</f>
-        <v>0</v>
-      </c>
-      <c r="N97" s="4">
-        <f>K97 - N81 - N92 - N44 + N39*N87</f>
-        <v>0.8</v>
-      </c>
-      <c r="Q97" s="4">
-        <f>N97 - Q81 - Q92 - Q44 + Q39*Q87</f>
-        <v>4.7987440000000001</v>
-      </c>
-      <c r="T97" s="4">
-        <f>Q97 - T81 - T92 - T44 + T39*T87</f>
-        <v>14.391209971919999</v>
-      </c>
-      <c r="W97" s="4">
-        <f>T97 - W81 - W92 - W44 + W39*W87</f>
-        <v>30.368615772264086</v>
-      </c>
-      <c r="Z97" s="4">
-        <f>W97 - Z81 - Z92 - Z44 + Z39*Z87</f>
-        <v>59.120937045501627</v>
-      </c>
-      <c r="AA97" s="37"/>
-      <c r="AB97" s="42"/>
-      <c r="AC97" s="43"/>
+      <c r="AA97" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="AB97" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="AC97" s="43" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="98" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B98" s="49"/>
       <c r="C98" s="50"/>
       <c r="F98" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H98" s="4">
-        <f>H64*H40</f>
+        <f>H63*H39</f>
         <v>0</v>
       </c>
       <c r="K98" s="4">
-        <f>H98 - K82 - K93 - K45 + K40*K88</f>
+        <f>H98 - K81 - K92 - K44 + K39*K87</f>
         <v>0</v>
       </c>
       <c r="N98" s="4">
-        <f>K98 - N82 - N93 - N45 + N40*N88</f>
-        <v>0</v>
+        <f>K98 - N81 - N92 - N44 + N39*N87</f>
+        <v>0.8</v>
       </c>
       <c r="Q98" s="4">
-        <f>N98 - Q82 - Q93 - Q45 + Q40*Q88</f>
-        <v>0.92</v>
+        <f>N98 - Q81 - Q92 - Q44 + Q39*Q87</f>
+        <v>4.7987440000000001</v>
       </c>
       <c r="T98" s="4">
-        <f>Q98 - T82 - T93 - T45 + T40*T88</f>
-        <v>5.5185556000000009</v>
+        <f>Q98 - T81 - T92 - T44 + T39*T87</f>
+        <v>14.391209971919999</v>
       </c>
       <c r="W98" s="4">
-        <f>T98 - W82 - W93 - W45 + W40*W88</f>
-        <v>16.549891467708001</v>
+        <f>T98 - W81 - W92 - W44 + W39*W87</f>
+        <v>30.368615772264086</v>
       </c>
       <c r="Z98" s="4">
-        <f>W98 - Z82 - Z93 - Z45 + Z40*Z88</f>
-        <v>34.923908138103698</v>
+        <f>W98 - Z81 - Z92 - Z44 + Z39*Z87</f>
+        <v>59.120937045501627</v>
       </c>
       <c r="AA98" s="37"/>
       <c r="AB98" s="42"/>
       <c r="AC98" s="43"/>
     </row>
-    <row r="99" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B99" s="49"/>
       <c r="C99" s="50"/>
       <c r="F99" s="14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H99" s="4">
-        <f>H65*H41</f>
+        <f>H64*H40</f>
         <v>0</v>
       </c>
       <c r="K99" s="4">
-        <f>H99 - K83 - K94 - K46 + K41*K89</f>
+        <f>H99 - K82 - K93 - K45 + K40*K88</f>
         <v>0</v>
       </c>
       <c r="N99" s="4">
-        <f>K99 - N83 - N94 - N46 + N41*N89</f>
+        <f>K99 - N82 - N93 - N45 + N40*N88</f>
         <v>0</v>
       </c>
       <c r="Q99" s="4">
-        <f>N99 - Q83 - Q94 - Q46 + Q41*Q89</f>
-        <v>0</v>
+        <f>N99 - Q82 - Q93 - Q45 + Q40*Q88</f>
+        <v>0.92</v>
       </c>
       <c r="T99" s="4">
-        <f>Q99 - T83 - T94 - T46 + T41*T89</f>
-        <v>0.43</v>
+        <f>Q99 - T82 - T93 - T45 + T40*T88</f>
+        <v>5.5185556000000009</v>
       </c>
       <c r="W99" s="4">
-        <f>T99 - W83 - W94 - W46 + W41*W89</f>
-        <v>2.5793249</v>
+        <f>T99 - W82 - W93 - W45 + W40*W88</f>
+        <v>16.549891467708001</v>
       </c>
       <c r="Z99" s="4">
-        <f>W99 - Z83 - Z94 - Z46 + Z41*Z89</f>
-        <v>7.7352753599069999</v>
+        <f>W99 - Z82 - Z93 - Z45 + Z40*Z88</f>
+        <v>34.923908138103698</v>
       </c>
       <c r="AA99" s="37"/>
       <c r="AB99" s="42"/>
       <c r="AC99" s="43"/>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="E100" s="26"/>
-      <c r="F100" s="14"/>
+    <row r="100" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="49"/>
+      <c r="C100" s="50"/>
+      <c r="F100" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H100" s="4">
+        <f>H65*H41</f>
+        <v>0</v>
+      </c>
+      <c r="K100" s="4">
+        <f>H100 - K83 - K94 - K46 + K41*K89</f>
+        <v>0</v>
+      </c>
+      <c r="N100" s="4">
+        <f>K100 - N83 - N94 - N46 + N41*N89</f>
+        <v>0</v>
+      </c>
+      <c r="Q100" s="4">
+        <f>N100 - Q83 - Q94 - Q46 + Q41*Q89</f>
+        <v>0</v>
+      </c>
+      <c r="T100" s="4">
+        <f>Q100 - T83 - T94 - T46 + T41*T89</f>
+        <v>0.43</v>
+      </c>
+      <c r="W100" s="4">
+        <f>T100 - W83 - W94 - W46 + W41*W89</f>
+        <v>2.5793249</v>
+      </c>
+      <c r="Z100" s="4">
+        <f>W100 - Z83 - Z94 - Z46 + Z41*Z89</f>
+        <v>7.7352753599069999</v>
+      </c>
+      <c r="AA100" s="37"/>
       <c r="AB100" s="42"/>
       <c r="AC100" s="43"/>
     </row>
-    <row r="101" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="B101" s="49" t="s">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="E101" s="26"/>
+      <c r="F101" s="14"/>
+      <c r="AB101" s="42"/>
+      <c r="AC101" s="43"/>
+    </row>
+    <row r="102" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A102" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="B102" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="50" t="s">
+      <c r="C102" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E101" s="26"/>
-      <c r="F101" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H101" s="4">
-        <f>H96*$H$21</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="4">
-        <f>K96*$H$21</f>
-        <v>0.21249999999999999</v>
-      </c>
-      <c r="N101" s="4">
-        <f>N96*$H$21</f>
-        <v>1.274666375</v>
-      </c>
-      <c r="Q101" s="4">
-        <f>Q96*$H$21</f>
-        <v>3.8226651487912497</v>
-      </c>
-      <c r="T101" s="4">
-        <f>T96*$H$21</f>
-        <v>8.0666635645076479</v>
-      </c>
-      <c r="W101" s="4">
-        <f>W96*$H$21</f>
-        <v>15.703998902711369</v>
-      </c>
-      <c r="Z101" s="4">
-        <f>Z96*$H$21</f>
-        <v>28.429343624434111</v>
-      </c>
-      <c r="AA101" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="AB101" s="42" t="s">
-        <v>433</v>
-      </c>
-      <c r="AC101" s="43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="102" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B102" s="49"/>
-      <c r="C102" s="50"/>
       <c r="E102" s="26"/>
       <c r="F102" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H102" s="4">
-        <f t="shared" ref="H102:H104" si="9">H97*$H$21</f>
+        <f>H97*$H$21</f>
         <v>0</v>
       </c>
       <c r="K102" s="4">
-        <f t="shared" ref="K102:K104" si="10">K97*$H$21</f>
-        <v>0</v>
+        <f>K97*$H$21</f>
+        <v>0.21249999999999999</v>
       </c>
       <c r="N102" s="4">
-        <f t="shared" ref="N102:N104" si="11">N97*$H$21</f>
-        <v>0.2</v>
+        <f>N97*$H$21</f>
+        <v>1.274666375</v>
       </c>
       <c r="Q102" s="4">
-        <f t="shared" ref="Q102:Q104" si="12">Q97*$H$21</f>
-        <v>1.199686</v>
+        <f>Q97*$H$21</f>
+        <v>3.8226651487912497</v>
       </c>
       <c r="T102" s="4">
-        <f t="shared" ref="T102:T104" si="13">T97*$H$21</f>
-        <v>3.5978024929799997</v>
+        <f>T97*$H$21</f>
+        <v>8.0666635645076479</v>
       </c>
       <c r="W102" s="4">
-        <f t="shared" ref="W102:W104" si="14">W97*$H$21</f>
-        <v>7.5921539430660214</v>
+        <f>W97*$H$21</f>
+        <v>15.703998902711369</v>
       </c>
       <c r="Z102" s="4">
-        <f t="shared" ref="Z102:Z104" si="15">Z97*$H$21</f>
-        <v>14.780234261375407</v>
-      </c>
-      <c r="AA102" s="37"/>
-      <c r="AB102" s="42"/>
-      <c r="AC102" s="43"/>
+        <f>Z97*$H$21</f>
+        <v>28.429343624434111</v>
+      </c>
+      <c r="AA102" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB102" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="AC102" s="43" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="103" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B103" s="49"/>
       <c r="C103" s="50"/>
       <c r="E103" s="26"/>
       <c r="F103" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H103" s="4">
-        <f>H98*$H$21</f>
+        <f t="shared" ref="H103:H105" si="9">H98*$H$21</f>
         <v>0</v>
       </c>
       <c r="K103" s="4">
-        <f>K98*$H$21</f>
+        <f t="shared" ref="K103:K105" si="10">K98*$H$21</f>
         <v>0</v>
       </c>
       <c r="N103" s="4">
-        <f>N98*$H$21</f>
-        <v>0</v>
+        <f t="shared" ref="N103:N105" si="11">N98*$H$21</f>
+        <v>0.2</v>
       </c>
       <c r="Q103" s="4">
-        <f>Q98*$H$21</f>
-        <v>0.23</v>
+        <f t="shared" ref="Q103:Q105" si="12">Q98*$H$21</f>
+        <v>1.199686</v>
       </c>
       <c r="T103" s="4">
-        <f>T98*$H$21</f>
-        <v>1.3796389000000002</v>
+        <f t="shared" ref="T103:T105" si="13">T98*$H$21</f>
+        <v>3.5978024929799997</v>
       </c>
       <c r="W103" s="4">
-        <f>W98*$H$21</f>
-        <v>4.1374728669270002</v>
+        <f t="shared" ref="W103:W105" si="14">W98*$H$21</f>
+        <v>7.5921539430660214</v>
       </c>
       <c r="Z103" s="4">
-        <f>Z98*$H$21</f>
-        <v>8.7309770345259246</v>
+        <f t="shared" ref="Z103:Z105" si="15">Z98*$H$21</f>
+        <v>14.780234261375407</v>
       </c>
       <c r="AA103" s="37"/>
       <c r="AB103" s="42"/>
@@ -11608,46 +11638,76 @@
       <c r="C104" s="50"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H104" s="4">
-        <f t="shared" si="9"/>
+        <f>H99*$H$21</f>
         <v>0</v>
       </c>
       <c r="K104" s="4">
-        <f t="shared" si="10"/>
+        <f>K99*$H$21</f>
         <v>0</v>
       </c>
       <c r="N104" s="4">
-        <f t="shared" si="11"/>
+        <f>N99*$H$21</f>
         <v>0</v>
       </c>
       <c r="Q104" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>Q99*$H$21</f>
+        <v>0.23</v>
       </c>
       <c r="T104" s="4">
-        <f t="shared" si="13"/>
-        <v>0.1075</v>
+        <f>T99*$H$21</f>
+        <v>1.3796389000000002</v>
       </c>
       <c r="W104" s="4">
-        <f t="shared" si="14"/>
-        <v>0.64483122500000001</v>
+        <f>W99*$H$21</f>
+        <v>4.1374728669270002</v>
       </c>
       <c r="Z104" s="4">
-        <f t="shared" si="15"/>
-        <v>1.93381883997675</v>
+        <f>Z99*$H$21</f>
+        <v>8.7309770345259246</v>
       </c>
       <c r="AA104" s="37"/>
       <c r="AB104" s="42"/>
       <c r="AC104" s="43"/>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B105" s="29"/>
-      <c r="C105" s="35"/>
+    <row r="105" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B105" s="49"/>
+      <c r="C105" s="50"/>
       <c r="E105" s="26"/>
-      <c r="F105" s="14"/>
-      <c r="AA105" s="29"/>
+      <c r="F105" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H105" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="4">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N105" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q105" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T105" s="4">
+        <f t="shared" si="13"/>
+        <v>0.1075</v>
+      </c>
+      <c r="W105" s="4">
+        <f t="shared" si="14"/>
+        <v>0.64483122500000001</v>
+      </c>
+      <c r="Z105" s="4">
+        <f t="shared" si="15"/>
+        <v>1.93381883997675</v>
+      </c>
+      <c r="AA105" s="37"/>
       <c r="AB105" s="42"/>
       <c r="AC105" s="43"/>
     </row>
@@ -11660,2729 +11720,2736 @@
       <c r="AB106" s="42"/>
       <c r="AC106" s="43"/>
     </row>
-    <row r="107" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B107" s="29"/>
+      <c r="C107" s="35"/>
       <c r="E107" s="26"/>
-      <c r="F107" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="H107" s="8"/>
+      <c r="F107" s="14"/>
+      <c r="AA107" s="29"/>
       <c r="AB107" s="42"/>
       <c r="AC107" s="43"/>
     </row>
-    <row r="108" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B108" s="38" t="s">
+    <row r="108" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="E108" s="26"/>
+      <c r="F108" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H108" s="8"/>
+      <c r="AB108" s="42"/>
+      <c r="AC108" s="43"/>
+    </row>
+    <row r="109" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B109" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="C108" s="34" t="s">
+      <c r="C109" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="E108" s="26"/>
-      <c r="F108" s="14" t="s">
+      <c r="E109" s="26"/>
+      <c r="F109" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G108" s="4">
+      <c r="G109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="H108" s="4">
+      <c r="H109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="J108" s="4">
+      <c r="J109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="K108" s="4">
+      <c r="K109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="M108" s="4">
+      <c r="M109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="N108" s="4">
+      <c r="N109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="P108" s="4">
+      <c r="P109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="Q108" s="4">
+      <c r="Q109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="S108" s="4">
+      <c r="S109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="T108" s="4">
+      <c r="T109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="V108" s="4">
+      <c r="V109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="W108" s="4">
+      <c r="W109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="Y108" s="4">
+      <c r="Y109" s="4">
         <f>$G$29</f>
         <v>0.3</v>
       </c>
-      <c r="Z108" s="4">
+      <c r="Z109" s="4">
         <f>$H$29</f>
         <v>0.92</v>
       </c>
-      <c r="AA108" s="38"/>
-      <c r="AB108" s="42"/>
-      <c r="AC108" s="43"/>
-    </row>
-    <row r="109" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="B109" s="38" t="s">
+      <c r="AA109" s="38"/>
+      <c r="AB109" s="42"/>
+      <c r="AC109" s="43"/>
+    </row>
+    <row r="110" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A110" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="B110" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="C109" s="28" t="s">
+      <c r="C110" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F109" s="14" t="s">
+      <c r="F110" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G109" s="4">
+      <c r="G110" s="4">
         <f>G7*$G$20</f>
         <v>7500000</v>
       </c>
-      <c r="H109" s="4">
+      <c r="H110" s="4">
         <f>H7*$H$20</f>
         <v>25000000</v>
       </c>
-      <c r="J109" s="4">
+      <c r="J110" s="4">
         <f>J7*$G$20</f>
         <v>7492500</v>
       </c>
-      <c r="K109" s="4">
+      <c r="K110" s="4">
         <f>K7*$H$20</f>
         <v>24990000</v>
       </c>
-      <c r="M109" s="4">
+      <c r="M110" s="4">
         <f>M7*$G$20</f>
         <v>7483200</v>
       </c>
-      <c r="N109" s="4">
+      <c r="N110" s="4">
         <f>N7*$H$20</f>
         <v>24979000</v>
       </c>
-      <c r="P109" s="4">
+      <c r="P110" s="4">
         <f>P7*$G$20</f>
         <v>7474500</v>
       </c>
-      <c r="Q109" s="4">
+      <c r="Q110" s="4">
         <f>Q7*$H$20</f>
         <v>24969600</v>
       </c>
-      <c r="S109" s="4">
+      <c r="S110" s="4">
         <f>S7*$G$20</f>
         <v>7464000</v>
       </c>
-      <c r="T109" s="4">
+      <c r="T110" s="4">
         <f>T7*$H$20</f>
         <v>24950400</v>
       </c>
-      <c r="V109" s="4">
+      <c r="V110" s="4">
         <f>V7*$G$20</f>
         <v>7449000</v>
       </c>
-      <c r="W109" s="4">
+      <c r="W110" s="4">
         <f>W7*$H$20</f>
         <v>24946500</v>
       </c>
-      <c r="Y109" s="4">
+      <c r="Y110" s="4">
         <f>Y7*$G$20</f>
         <v>7434300</v>
       </c>
-      <c r="Z109" s="4">
+      <c r="Z110" s="4">
         <f>Z7*$H$20</f>
         <v>24936000</v>
       </c>
-      <c r="AA109" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="AB109" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="AC109" s="43" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="110" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B110" s="38" t="s">
+      <c r="AA110" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="AB110" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="AC110" s="43" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="111" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A111" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="B111" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="C110" s="28" t="s">
+      <c r="C111" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F110" s="14" t="s">
+      <c r="F111" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G111" s="4">
         <v>1</v>
       </c>
-      <c r="H110" s="4">
+      <c r="H111" s="4">
         <v>1</v>
       </c>
-      <c r="J110" s="4">
-        <f>IF(G112=0,0,MIN(MAX((G112/G109-$G$17)/($G$19-$G$17), 0), 1))</f>
+      <c r="J111" s="4">
+        <f>IF(G113=0,0,MIN(MAX((G113/G110-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="K110" s="4">
-        <f>IF(H112=0,0,MIN(MAX((H112/H109-$H$17)/($G$19-$H$17), 0), 1))</f>
+      <c r="K111" s="4">
+        <f>IF(H113=0,0,MIN(MAX((H113/H110-$H$17)/($G$19-$H$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="M110" s="4">
-        <f>IF(J112=0,0,MIN(MAX((J112/J109-$G$17)/($G$19-$G$17), 0), 1))</f>
+      <c r="M111" s="4">
+        <f>IF(J113=0,0,MIN(MAX((J113/J110-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="N110" s="4">
-        <f>IF(K112=0,0,MIN(MAX((K112/K109-$H$17)/($G$19-$H$17), 0), 1))</f>
+      <c r="N111" s="4">
+        <f>IF(K113=0,0,MIN(MAX((K113/K110-$H$17)/($G$19-$H$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="P110" s="4">
-        <f>IF(M112=0,0,MIN(MAX((M112/M109-$G$17)/($G$19-$G$17), 0), 1))</f>
+      <c r="P111" s="4">
+        <f>IF(M113=0,0,MIN(MAX((M113/M110-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="Q110" s="4">
-        <f>IF(N112=0,0,MIN(MAX((N112/N109-$H$17)/($G$19-$H$17), 0), 1))</f>
+      <c r="Q111" s="4">
+        <f>IF(N113=0,0,MIN(MAX((N113/N110-$H$17)/($G$19-$H$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="S110" s="4">
-        <f>IF(P112=0,0,MIN(MAX((P112/P109-$G$17)/($G$19-$G$17), 0), 1))</f>
+      <c r="S111" s="4">
+        <f>IF(P113=0,0,MIN(MAX((P113/P110-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="T110" s="4">
-        <f>IF(Q112=0,0,MIN(MAX((Q112/Q109-$H$17)/($G$19-$H$17), 0), 1))</f>
+      <c r="T111" s="4">
+        <f>IF(Q113=0,0,MIN(MAX((Q113/Q110-$H$17)/($G$19-$H$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="V110" s="4">
-        <f>IF(S112=0,0,MIN(MAX((S112/S109-$G$17)/($G$19-$G$17), 0), 1))</f>
+      <c r="V111" s="4">
+        <f>IF(S113=0,0,MIN(MAX((S113/S110-$G$17)/($G$19-$G$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="W110" s="4">
-        <f>IF(T112=0,0,MIN(MAX((T112/T109-$H$17)/($G$19-$H$17), 0), 1))</f>
+      <c r="W111" s="4">
+        <f>IF(T113=0,0,MIN(MAX((T113/T110-$H$17)/($G$19-$H$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="Y110" s="4">
-        <f>IF(V112=0,0,MIN(MAX((V112/V109-$G$17)/($G$19-$G$17), 0), 1))</f>
-        <v>0.86115188084024752</v>
-      </c>
-      <c r="Z110" s="4">
-        <f>IF(W112=0,0,MIN(MAX((W112/W109-$H$17)/($G$19-$H$17), 0), 1))</f>
+      <c r="Y111" s="4">
+        <f>IF(V113=0,0,MIN(MAX((V113/V110-$G$17)/($G$19-$G$17), 0), 1))</f>
+        <v>0.8611518815783703</v>
+      </c>
+      <c r="Z111" s="4">
+        <f>IF(W113=0,0,MIN(MAX((W113/W110-$H$17)/($G$19-$H$17), 0), 1))</f>
         <v>1</v>
       </c>
-      <c r="AA110" s="38" t="s">
-        <v>479</v>
-      </c>
-      <c r="AB110" s="42" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC110" s="43" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="111" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B111" s="38" t="s">
+      <c r="AA111" s="38" t="s">
+        <v>454</v>
+      </c>
+      <c r="AB111" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="AC111" s="43" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="112" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A112" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="B112" s="38" t="s">
         <v>182</v>
-      </c>
-      <c r="C111" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F111" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="G111" s="4">
-        <f>G108</f>
-        <v>0.3</v>
-      </c>
-      <c r="H111" s="4">
-        <f>H108</f>
-        <v>0.92</v>
-      </c>
-      <c r="J111" s="4">
-        <f xml:space="preserve"> J108*J110</f>
-        <v>0.3</v>
-      </c>
-      <c r="K111" s="4">
-        <f>K108*K110</f>
-        <v>0.92</v>
-      </c>
-      <c r="M111" s="4">
-        <f xml:space="preserve"> M108*M110</f>
-        <v>0.3</v>
-      </c>
-      <c r="N111" s="4">
-        <f>N108*N110</f>
-        <v>0.92</v>
-      </c>
-      <c r="P111" s="4">
-        <f xml:space="preserve"> P108*P110</f>
-        <v>0.3</v>
-      </c>
-      <c r="Q111" s="4">
-        <f>Q108*Q110</f>
-        <v>0.92</v>
-      </c>
-      <c r="S111" s="4">
-        <f xml:space="preserve"> S108*S110</f>
-        <v>0.3</v>
-      </c>
-      <c r="T111" s="4">
-        <f>T108*T110</f>
-        <v>0.92</v>
-      </c>
-      <c r="V111" s="4">
-        <f xml:space="preserve"> V108*V110</f>
-        <v>0.3</v>
-      </c>
-      <c r="W111" s="4">
-        <f>W108*W110</f>
-        <v>0.92</v>
-      </c>
-      <c r="Y111" s="4">
-        <f xml:space="preserve"> Y108*Y110</f>
-        <v>0.25834556425207422</v>
-      </c>
-      <c r="Z111" s="4">
-        <f>Z108*Z110</f>
-        <v>0.92</v>
-      </c>
-      <c r="AA111" s="38" t="s">
-        <v>331</v>
-      </c>
-      <c r="AB111" s="42" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC111" s="43" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="112" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B112" s="38" t="s">
-        <v>236</v>
       </c>
       <c r="C112" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F112" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="G112" s="4">
+        <f>G109</f>
+        <v>0.3</v>
+      </c>
+      <c r="H112" s="4">
+        <f>H109</f>
+        <v>0.92</v>
+      </c>
+      <c r="J112" s="4">
+        <f xml:space="preserve"> J109*J111</f>
+        <v>0.3</v>
+      </c>
+      <c r="K112" s="4">
+        <f>K109*K111</f>
+        <v>0.92</v>
+      </c>
+      <c r="M112" s="4">
+        <f xml:space="preserve"> M109*M111</f>
+        <v>0.3</v>
+      </c>
+      <c r="N112" s="4">
+        <f>N109*N111</f>
+        <v>0.92</v>
+      </c>
+      <c r="P112" s="4">
+        <f xml:space="preserve"> P109*P111</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q112" s="4">
+        <f>Q109*Q111</f>
+        <v>0.92</v>
+      </c>
+      <c r="S112" s="4">
+        <f xml:space="preserve"> S109*S111</f>
+        <v>0.3</v>
+      </c>
+      <c r="T112" s="4">
+        <f>T109*T111</f>
+        <v>0.92</v>
+      </c>
+      <c r="V112" s="4">
+        <f xml:space="preserve"> V109*V111</f>
+        <v>0.3</v>
+      </c>
+      <c r="W112" s="4">
+        <f>W109*W111</f>
+        <v>0.92</v>
+      </c>
+      <c r="Y112" s="4">
+        <f xml:space="preserve"> Y109*Y111</f>
+        <v>0.25834556447351109</v>
+      </c>
+      <c r="Z112" s="4">
+        <f>Z109*Z111</f>
+        <v>0.92</v>
+      </c>
+      <c r="AA112" s="38" t="s">
+        <v>479</v>
+      </c>
+      <c r="AB112" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="AC112" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B113" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F113" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G113" s="4">
         <f>G7*G20</f>
         <v>7500000</v>
       </c>
-      <c r="H112" s="4">
+      <c r="H113" s="4">
         <f>H7*H20</f>
         <v>25000000</v>
       </c>
-      <c r="J112" s="4">
-        <f>G112 - G133 - G121 - G144+J111*J7</f>
+      <c r="J113" s="4">
+        <f>G113 - G134 - G122 - G145+J112*J7</f>
         <v>6966918.08125271</v>
       </c>
-      <c r="K112" s="4">
-        <f>H112 - H133 - H121 - H144 + K111*K7</f>
+      <c r="K113" s="4">
+        <f>H113 - H134 - H122 - (H145 - H95)+ K112*K7</f>
         <v>23723974.534997292</v>
       </c>
-      <c r="M112" s="4">
-        <f>J112 - J133 - J121 - J144+M111*M7</f>
+      <c r="M113" s="4">
+        <f>J113 - J134 - J122 - J145+M112*M7</f>
         <v>6430976.9232831635</v>
       </c>
-      <c r="N112" s="4">
-        <f>K112 - K133 - K121 - K144 + N111*N7</f>
+      <c r="N113" s="4">
+        <f>K113 - K134 - K122 - (K145 - K95)+ N112*N7</f>
         <v>22403030.169761121</v>
       </c>
-      <c r="P112" s="4">
-        <f>M112 - M133 - M121 - M144+P111*P7</f>
+      <c r="P113" s="4">
+        <f>M113 - M134 - M122 - M145+P112*P7</f>
         <v>5878439.281534086</v>
       </c>
-      <c r="Q112" s="4">
-        <f>N112 - N133 - N121 - N144 + Q111*Q7</f>
-        <v>21042661.124617502</v>
-      </c>
-      <c r="S112" s="4">
-        <f>P112 - P133 - P121 - P144+S111*S7</f>
-        <v>5319767.3068811921</v>
-      </c>
-      <c r="T112" s="4">
-        <f>Q112 - Q133 - Q121 - Q144 + T111*T7</f>
-        <v>19588129.944080703</v>
-      </c>
-      <c r="V112" s="4">
-        <f>S112 - S133 - S121 - S144+V111*V7</f>
-        <v>4639771.7535949051</v>
-      </c>
-      <c r="W112" s="4">
-        <f>T112 - T133 - T121 - T144 + W111*W7</f>
-        <v>17473377.815496068</v>
-      </c>
-      <c r="Y112" s="4">
-        <f>V112 - V133 - V121 - V144+Y111*Y7</f>
-        <v>4179370.6046086708</v>
-      </c>
-      <c r="Z112" s="4">
-        <f>W112 - W133 - W121 - W144 + Z111*Z7</f>
-        <v>15778712.676320704</v>
-      </c>
-      <c r="AA112" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB112" s="42" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC112" s="43" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="113" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B113" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="C113" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F113" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G113" s="4">
-        <f>IF(G7=0,0,G112/G7)</f>
-        <v>150</v>
-      </c>
-      <c r="H113" s="4">
-        <f>IF(H7=0,0,H112/H7)</f>
-        <v>100</v>
-      </c>
-      <c r="J113" s="4">
-        <f>IF(J7=0,0,J112/J7)</f>
-        <v>139.47783946451872</v>
-      </c>
-      <c r="K113" s="4">
-        <f>IF(K7=0,0,K112/K7)</f>
-        <v>94.933871688664638</v>
-      </c>
-      <c r="M113" s="4">
-        <f>IF(M7=0,0,M112/M7)</f>
-        <v>128.90829304207753</v>
-      </c>
-      <c r="N113" s="4">
-        <f>IF(N7=0,0,N112/N7)</f>
-        <v>89.687458143885351</v>
-      </c>
-      <c r="P113" s="4">
-        <f>IF(P7=0,0,P112/P7)</f>
-        <v>117.96988323367621</v>
-      </c>
       <c r="Q113" s="4">
-        <f>IF(Q7=0,0,Q112/Q7)</f>
-        <v>84.273120613135575</v>
+        <f>N113 - N134 - N122 - (N145 - N95)+ Q112*Q7</f>
+        <v>21042661.125952005</v>
       </c>
       <c r="S113" s="4">
-        <f>IF(S7=0,0,S112/S7)</f>
-        <v>106.90850697108505</v>
+        <f>P113 - P134 - P122 - P145+S112*S7</f>
+        <v>5319767.3070256906</v>
       </c>
       <c r="T113" s="4">
-        <f>IF(T7=0,0,T112/T7)</f>
-        <v>78.508280204248038</v>
+        <f>Q113 - Q134 - Q122 - (Q145 - Q95)+ T112*T7</f>
+        <v>19588129.954529207</v>
       </c>
       <c r="V113" s="4">
-        <f>IF(V7=0,0,V112/V7)</f>
-        <v>93.430764268926808</v>
+        <f>S113 - S134 - S122 - S145+V112*V7</f>
+        <v>4639771.7554611461</v>
       </c>
       <c r="W113" s="4">
-        <f>IF(W7=0,0,W112/W7)</f>
-        <v>70.043404146858549</v>
+        <f>T113 - T134 - T122 - (T145 - T95)+ W112*W7</f>
+        <v>17473377.857190389</v>
       </c>
       <c r="Y113" s="4">
-        <f>IF(Y7=0,0,Y112/Y7)</f>
-        <v>84.326108805307911</v>
+        <f>V113 - V134 - V122 - V145+Y112*Y7</f>
+        <v>4179370.6044759089</v>
       </c>
       <c r="Z113" s="4">
-        <f>IF(Z7=0,0,Z112/Z7)</f>
-        <v>63.276839414183122</v>
+        <f>W113 - W134 - W122 - (W145 - W95)+ Z112*Z7</f>
+        <v>15778712.754563004</v>
       </c>
       <c r="AA113" s="38" t="s">
-        <v>333</v>
+        <v>481</v>
       </c>
       <c r="AB113" s="42" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="AC113" s="43" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
     </row>
     <row r="114" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B114" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G114" s="4">
+        <f>IF(G7=0,0,G113/G7)</f>
+        <v>150</v>
+      </c>
+      <c r="H114" s="4">
+        <f>IF(H7=0,0,H113/H7)</f>
+        <v>100</v>
+      </c>
+      <c r="J114" s="4">
+        <f>IF(J7=0,0,J113/J7)</f>
+        <v>139.47783946451872</v>
+      </c>
+      <c r="K114" s="4">
+        <f>IF(K7=0,0,K113/K7)</f>
+        <v>94.933871688664638</v>
+      </c>
+      <c r="M114" s="4">
+        <f>IF(M7=0,0,M113/M7)</f>
+        <v>128.90829304207753</v>
+      </c>
+      <c r="N114" s="4">
+        <f>IF(N7=0,0,N113/N7)</f>
+        <v>89.687458143885351</v>
+      </c>
+      <c r="P114" s="4">
+        <f>IF(P7=0,0,P113/P7)</f>
+        <v>117.96988323367621</v>
+      </c>
+      <c r="Q114" s="4">
+        <f>IF(Q7=0,0,Q113/Q7)</f>
+        <v>84.273120618480093</v>
+      </c>
+      <c r="S114" s="4">
+        <f>IF(S7=0,0,S113/S7)</f>
+        <v>106.90850697398896</v>
+      </c>
+      <c r="T114" s="4">
+        <f>IF(T7=0,0,T113/T7)</f>
+        <v>78.508280246125139</v>
+      </c>
+      <c r="V114" s="4">
+        <f>IF(V7=0,0,V113/V7)</f>
+        <v>93.430764306507172</v>
+      </c>
+      <c r="W114" s="4">
+        <f>IF(W7=0,0,W113/W7)</f>
+        <v>70.043404313993506</v>
+      </c>
+      <c r="Y114" s="4">
+        <f>IF(Y7=0,0,Y113/Y7)</f>
+        <v>84.326108802629207</v>
+      </c>
+      <c r="Z114" s="4">
+        <f>IF(Z7=0,0,Z113/Z7)</f>
+        <v>63.276839727955583</v>
+      </c>
+      <c r="AA114" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="AB114" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="AC114" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="115" spans="2:29" ht="68" x14ac:dyDescent="0.2">
+      <c r="B115" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="C114" s="28" t="s">
+      <c r="C115" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F114" s="10" t="s">
+      <c r="F115" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G114" s="4">
-        <f>MAX(G113-$G22,0)</f>
+      <c r="G115" s="4">
+        <f>MAX(G114-$G22,0)</f>
         <v>100.4134425</v>
       </c>
-      <c r="H114" s="4">
-        <f>MAX(H113-$H22,0)</f>
+      <c r="H115" s="4">
+        <f>MAX(H114-$H22,0)</f>
         <v>62.199106999999998</v>
       </c>
-      <c r="J114" s="4">
-        <f>MAX(J113-$G22,0)</f>
+      <c r="J115" s="4">
+        <f>MAX(J114-$G22,0)</f>
         <v>89.891281964518726</v>
       </c>
-      <c r="K114" s="4">
-        <f>MAX(K113-$H22,0)</f>
+      <c r="K115" s="4">
+        <f>MAX(K114-$H22,0)</f>
         <v>57.132978688664636</v>
       </c>
-      <c r="M114" s="4">
-        <f>MAX(M113-$G22,0)</f>
+      <c r="M115" s="4">
+        <f>MAX(M114-$G22,0)</f>
         <v>79.321735542077533</v>
       </c>
-      <c r="N114" s="4">
-        <f>MAX(N113-$H22,0)</f>
+      <c r="N115" s="4">
+        <f>MAX(N114-$H22,0)</f>
         <v>51.886565143885349</v>
       </c>
-      <c r="P114" s="4">
-        <f>MAX(P113-$G22,0)</f>
+      <c r="P115" s="4">
+        <f>MAX(P114-$G22,0)</f>
         <v>68.383325733676216</v>
       </c>
-      <c r="Q114" s="4">
-        <f>MAX(Q113-$H22,0)</f>
-        <v>46.472227613135573</v>
-      </c>
-      <c r="S114" s="4">
-        <f>MAX(S113-$G22,0)</f>
-        <v>57.321949471085048</v>
-      </c>
-      <c r="T114" s="4">
-        <f>MAX(T113-$H22,0)</f>
-        <v>40.707387204248036</v>
-      </c>
-      <c r="V114" s="4">
-        <f>MAX(V113-$G22,0)</f>
-        <v>43.84420676892681</v>
-      </c>
-      <c r="W114" s="4">
-        <f>MAX(W113-$H22,0)</f>
-        <v>32.242511146858547</v>
-      </c>
-      <c r="Y114" s="4">
-        <f>MAX(Y113-$G22,0)</f>
-        <v>34.739551305307913</v>
-      </c>
-      <c r="Z114" s="4">
-        <f>MAX(Z113-$H22,0)</f>
-        <v>25.47594641418312</v>
-      </c>
-      <c r="AA114" s="38" t="s">
-        <v>351</v>
-      </c>
-      <c r="AB114" s="46" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC114" s="43" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="F115" s="13"/>
-      <c r="AB115" s="42"/>
-      <c r="AC115" s="43"/>
-    </row>
-    <row r="116" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="F116" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G116" s="12"/>
-      <c r="H116" s="12"/>
-      <c r="J116" s="12"/>
-      <c r="K116" s="12"/>
-      <c r="M116" s="12"/>
-      <c r="N116" s="12"/>
-      <c r="P116" s="12"/>
-      <c r="Q116" s="12"/>
-      <c r="S116" s="12"/>
-      <c r="T116" s="12"/>
-      <c r="V116" s="12"/>
-      <c r="W116" s="12"/>
-      <c r="Y116" s="12"/>
-      <c r="Z116" s="12"/>
+      <c r="Q115" s="4">
+        <f>MAX(Q114-$H22,0)</f>
+        <v>46.47222761848009</v>
+      </c>
+      <c r="S115" s="4">
+        <f>MAX(S114-$G22,0)</f>
+        <v>57.321949473988965</v>
+      </c>
+      <c r="T115" s="4">
+        <f>MAX(T114-$H22,0)</f>
+        <v>40.707387246125137</v>
+      </c>
+      <c r="V115" s="4">
+        <f>MAX(V114-$G22,0)</f>
+        <v>43.844206806507174</v>
+      </c>
+      <c r="W115" s="4">
+        <f>MAX(W114-$H22,0)</f>
+        <v>32.242511313993504</v>
+      </c>
+      <c r="Y115" s="4">
+        <f>MAX(Y114-$G22,0)</f>
+        <v>34.739551302629209</v>
+      </c>
+      <c r="Z115" s="4">
+        <f>MAX(Z114-$H22,0)</f>
+        <v>25.475946727955581</v>
+      </c>
+      <c r="AA115" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB115" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC115" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="116" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="F116" s="13"/>
       <c r="AB116" s="42"/>
       <c r="AC116" s="43"/>
     </row>
     <row r="117" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B117" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="C117" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F117" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G117" s="4">
-        <f>G113*G7</f>
-        <v>7500000</v>
-      </c>
-      <c r="H117" s="4">
-        <f>H113*H7</f>
-        <v>25000000</v>
-      </c>
-      <c r="J117" s="4">
-        <f>J113*J7</f>
-        <v>6966918.08125271</v>
-      </c>
-      <c r="K117" s="4">
-        <f>K113*K7</f>
-        <v>23723974.534997292</v>
-      </c>
-      <c r="M117" s="4">
-        <f>M113*M7</f>
-        <v>6430976.9232831635</v>
-      </c>
-      <c r="N117" s="4">
-        <f>N113*N7</f>
-        <v>22403030.169761121</v>
-      </c>
-      <c r="P117" s="4">
-        <f>P113*P7</f>
-        <v>5878439.281534086</v>
-      </c>
-      <c r="Q117" s="4">
-        <f>Q113*Q7</f>
-        <v>21042661.124617502</v>
-      </c>
-      <c r="S117" s="4">
-        <f>S113*S7</f>
-        <v>5319767.3068811921</v>
-      </c>
-      <c r="T117" s="4">
-        <f>T113*T7</f>
-        <v>19588129.944080703</v>
-      </c>
-      <c r="V117" s="4">
-        <f>V113*V7</f>
-        <v>4639771.7535949051</v>
-      </c>
-      <c r="W117" s="4">
-        <f>W113*W7</f>
-        <v>17473377.815496068</v>
-      </c>
-      <c r="Y117" s="4">
-        <f>Y113*Y7</f>
-        <v>4179370.6046086708</v>
-      </c>
-      <c r="Z117" s="4">
-        <f>Z113*Z7</f>
-        <v>15778712.676320704</v>
-      </c>
-      <c r="AA117" s="38"/>
+      <c r="F117" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+      <c r="M117" s="12"/>
+      <c r="N117" s="12"/>
+      <c r="P117" s="12"/>
+      <c r="Q117" s="12"/>
+      <c r="S117" s="12"/>
+      <c r="T117" s="12"/>
+      <c r="V117" s="12"/>
+      <c r="W117" s="12"/>
+      <c r="Y117" s="12"/>
+      <c r="Z117" s="12"/>
       <c r="AB117" s="42"/>
       <c r="AC117" s="43"/>
     </row>
-    <row r="118" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="C118" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G118" s="4">
+        <f>G114*G7</f>
+        <v>7500000</v>
+      </c>
+      <c r="H118" s="4">
+        <f>H114*H7</f>
+        <v>25000000</v>
+      </c>
+      <c r="J118" s="4">
+        <f>J114*J7</f>
+        <v>6966918.08125271</v>
+      </c>
+      <c r="K118" s="4">
+        <f>K114*K7</f>
+        <v>23723974.534997292</v>
+      </c>
+      <c r="M118" s="4">
+        <f>M114*M7</f>
+        <v>6430976.9232831635</v>
+      </c>
+      <c r="N118" s="4">
+        <f>N114*N7</f>
+        <v>22403030.169761121</v>
+      </c>
+      <c r="P118" s="4">
+        <f>P114*P7</f>
+        <v>5878439.281534086</v>
+      </c>
+      <c r="Q118" s="4">
+        <f>Q114*Q7</f>
+        <v>21042661.125952005</v>
+      </c>
+      <c r="S118" s="4">
+        <f>S114*S7</f>
+        <v>5319767.3070256906</v>
+      </c>
+      <c r="T118" s="4">
+        <f>T114*T7</f>
+        <v>19588129.954529207</v>
+      </c>
+      <c r="V118" s="4">
+        <f>V114*V7</f>
+        <v>4639771.7554611461</v>
+      </c>
+      <c r="W118" s="4">
+        <f>W114*W7</f>
+        <v>17473377.857190389</v>
+      </c>
+      <c r="Y118" s="4">
+        <f>Y114*Y7</f>
+        <v>4179370.6044759089</v>
+      </c>
+      <c r="Z118" s="4">
+        <f>Z114*Z7</f>
+        <v>15778712.754563004</v>
+      </c>
+      <c r="AA118" s="38"/>
+      <c r="AB118" s="42"/>
+      <c r="AC118" s="43"/>
+    </row>
+    <row r="119" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B119" s="38" t="s">
         <v>240</v>
-      </c>
-      <c r="C118" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F118" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="H118" s="4">
-        <f>SUM(H96:H99)</f>
-        <v>0</v>
-      </c>
-      <c r="K118" s="4">
-        <f>SUM(K96:K99)</f>
-        <v>0.85</v>
-      </c>
-      <c r="N118" s="4">
-        <f>SUM(N96:N99)</f>
-        <v>5.8986654999999999</v>
-      </c>
-      <c r="Q118" s="4">
-        <f>SUM(Q96:Q99)</f>
-        <v>21.009404595165002</v>
-      </c>
-      <c r="T118" s="4">
-        <f>SUM(T96:T99)</f>
-        <v>52.606419829950589</v>
-      </c>
-      <c r="W118" s="4">
-        <f>SUM(W96:W99)</f>
-        <v>112.31382775081757</v>
-      </c>
-      <c r="Z118" s="4">
-        <f>SUM(Z96:Z99)</f>
-        <v>215.49749504124878</v>
-      </c>
-      <c r="AA118" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="AB118" s="42" t="s">
-        <v>439</v>
-      </c>
-      <c r="AC118" s="43" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="119" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B119" s="38" t="s">
-        <v>237</v>
       </c>
       <c r="C119" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="G119" s="4">
-        <f>G117+G118</f>
-        <v>7500000</v>
+        <v>216</v>
       </c>
       <c r="H119" s="4">
-        <f>H117+H118</f>
-        <v>25000000</v>
-      </c>
-      <c r="J119" s="4">
-        <f>J117+J118</f>
-        <v>6966918.08125271</v>
+        <f>SUM(H97:H100)</f>
+        <v>0</v>
       </c>
       <c r="K119" s="4">
-        <f>K117+K118</f>
-        <v>23723975.384997293</v>
-      </c>
-      <c r="M119" s="4">
-        <f>M117+M118</f>
-        <v>6430976.9232831635</v>
+        <f>SUM(K97:K100)</f>
+        <v>0.85</v>
       </c>
       <c r="N119" s="4">
-        <f>N117+N118</f>
-        <v>22403036.06842662</v>
-      </c>
-      <c r="P119" s="4">
-        <f>P117+P118</f>
-        <v>5878439.281534086</v>
+        <f>SUM(N97:N100)</f>
+        <v>5.8986654999999999</v>
       </c>
       <c r="Q119" s="4">
-        <f>Q117+Q118</f>
-        <v>21042682.134022098</v>
-      </c>
-      <c r="S119" s="4">
-        <f>S117+S118</f>
-        <v>5319767.3068811921</v>
+        <f>SUM(Q97:Q100)</f>
+        <v>21.009404595165002</v>
       </c>
       <c r="T119" s="4">
-        <f>T117+T118</f>
-        <v>19588182.550500534</v>
-      </c>
-      <c r="V119" s="4">
-        <f>V117+V118</f>
-        <v>4639771.7535949051</v>
+        <f>SUM(T97:T100)</f>
+        <v>52.606419829950589</v>
       </c>
       <c r="W119" s="4">
-        <f>W117+W118</f>
-        <v>17473490.129323818</v>
-      </c>
-      <c r="Y119" s="4">
-        <f>Y117+Y118</f>
-        <v>4179370.6046086708</v>
+        <f>SUM(W97:W100)</f>
+        <v>112.31382775081757</v>
       </c>
       <c r="Z119" s="4">
-        <f>Z117+Z118</f>
-        <v>15778928.173815746</v>
+        <f>SUM(Z97:Z100)</f>
+        <v>215.49749504124878</v>
       </c>
       <c r="AA119" s="38" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="AB119" s="42" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="AC119" s="43" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="120" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="120" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B120" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C120" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F120" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G120" s="4">
+        <f>G118+G119</f>
+        <v>7500000</v>
+      </c>
+      <c r="H120" s="4">
+        <f>H118+H119</f>
+        <v>25000000</v>
+      </c>
+      <c r="J120" s="4">
+        <f>J118+J119</f>
+        <v>6966918.08125271</v>
+      </c>
+      <c r="K120" s="4">
+        <f>K118+K119</f>
+        <v>23723975.384997293</v>
+      </c>
+      <c r="M120" s="4">
+        <f>M118+M119</f>
+        <v>6430976.9232831635</v>
+      </c>
+      <c r="N120" s="4">
+        <f>N118+N119</f>
+        <v>22403036.06842662</v>
+      </c>
+      <c r="P120" s="4">
+        <f>P118+P119</f>
+        <v>5878439.281534086</v>
+      </c>
+      <c r="Q120" s="4">
+        <f>Q118+Q119</f>
+        <v>21042682.135356601</v>
+      </c>
+      <c r="S120" s="4">
+        <f>S118+S119</f>
+        <v>5319767.3070256906</v>
+      </c>
+      <c r="T120" s="4">
+        <f>T118+T119</f>
+        <v>19588182.560949039</v>
+      </c>
+      <c r="V120" s="4">
+        <f>V118+V119</f>
+        <v>4639771.7554611461</v>
+      </c>
+      <c r="W120" s="4">
+        <f>W118+W119</f>
+        <v>17473490.171018139</v>
+      </c>
+      <c r="Y120" s="4">
+        <f>Y118+Y119</f>
+        <v>4179370.6044759089</v>
+      </c>
+      <c r="Z120" s="4">
+        <f>Z118+Z119</f>
+        <v>15778928.252058046</v>
+      </c>
+      <c r="AA120" s="38" t="s">
+        <v>473</v>
+      </c>
+      <c r="AB120" s="42" t="s">
+        <v>469</v>
+      </c>
+      <c r="AC120" s="43" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="121" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B121" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="C121" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F121" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G120" s="4">
-        <f>G119*$G$21</f>
+      <c r="G121" s="4">
+        <f>G120*$G$21</f>
         <v>2250000</v>
       </c>
-      <c r="H120" s="4">
-        <f>H119*$H$21</f>
+      <c r="H121" s="4">
+        <f>H120*$H$21</f>
         <v>6250000</v>
       </c>
-      <c r="J120" s="4">
-        <f>J119*$G$21</f>
+      <c r="J121" s="4">
+        <f>J120*$G$21</f>
         <v>2090075.424375813</v>
       </c>
-      <c r="K120" s="4">
-        <f>K119*$H$21</f>
+      <c r="K121" s="4">
+        <f>K120*$H$21</f>
         <v>5930993.8462493233</v>
       </c>
-      <c r="M120" s="4">
-        <f>M119*$G$21</f>
+      <c r="M121" s="4">
+        <f>M120*$G$21</f>
         <v>1929293.0769849489</v>
       </c>
-      <c r="N120" s="4">
-        <f>N119*$H$21</f>
+      <c r="N121" s="4">
+        <f>N120*$H$21</f>
         <v>5600759.0171066551</v>
       </c>
-      <c r="P120" s="4">
-        <f>P119*$G$21</f>
+      <c r="P121" s="4">
+        <f>P120*$G$21</f>
         <v>1763531.7844602258</v>
       </c>
-      <c r="Q120" s="4">
-        <f>Q119*$H$21</f>
-        <v>5260670.5335055245</v>
-      </c>
-      <c r="S120" s="4">
-        <f>S119*$G$21</f>
-        <v>1595930.1920643577</v>
-      </c>
-      <c r="T120" s="4">
-        <f>T119*$H$21</f>
-        <v>4897045.6376251336</v>
-      </c>
-      <c r="V120" s="4">
-        <f>V119*$G$21</f>
-        <v>1391931.5260784714</v>
-      </c>
-      <c r="W120" s="4">
-        <f>W119*$H$21</f>
-        <v>4368372.5323309544</v>
-      </c>
-      <c r="Y120" s="4">
-        <f>Y119*$G$21</f>
-        <v>1253811.1813826011</v>
-      </c>
-      <c r="Z120" s="4">
-        <f>Z119*$H$21</f>
-        <v>3944732.0434539365</v>
-      </c>
-      <c r="AA120" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="AB120" s="42" t="s">
-        <v>441</v>
-      </c>
-      <c r="AC120" s="43" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="121" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B121" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="C121" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="G121" s="4">
-        <f>G9*G113</f>
-        <v>7500</v>
-      </c>
-      <c r="H121" s="4">
-        <f>H9*H113</f>
-        <v>10000</v>
-      </c>
-      <c r="J121" s="4">
-        <f>J9*J113</f>
-        <v>8647.6260468001601</v>
-      </c>
-      <c r="K121" s="4">
-        <f>K9*K113</f>
-        <v>10442.725885753111</v>
-      </c>
-      <c r="M121" s="4">
-        <f>M9*M113</f>
-        <v>7476.6809964404965</v>
-      </c>
-      <c r="N121" s="4">
-        <f>N9*N113</f>
-        <v>8430.6210655252235</v>
-      </c>
-      <c r="P121" s="4">
-        <f>P9*P113</f>
-        <v>8257.8918263573341</v>
-      </c>
       <c r="Q121" s="4">
-        <f>Q9*Q113</f>
-        <v>16180.43915772203</v>
+        <f>Q120*$H$21</f>
+        <v>5260670.5338391503</v>
       </c>
       <c r="S121" s="4">
-        <f>S9*S113</f>
-        <v>10690.850697108504</v>
+        <f>S120*$G$21</f>
+        <v>1595930.192107707</v>
       </c>
       <c r="T121" s="4">
-        <f>T9*T113</f>
-        <v>3061.8229279656734</v>
+        <f>T120*$H$21</f>
+        <v>4897045.6402372597</v>
       </c>
       <c r="V121" s="4">
-        <f>V9*V113</f>
-        <v>9156.2148983548268</v>
+        <f>V120*$G$21</f>
+        <v>1391931.5266383437</v>
       </c>
       <c r="W121" s="4">
-        <f>W9*W113</f>
-        <v>7354.5574354201481</v>
+        <f>W120*$H$21</f>
+        <v>4368372.5427545346</v>
       </c>
       <c r="Y121" s="4">
-        <f>Y9*Y113</f>
-        <v>8263.9586629201749</v>
+        <f>Y120*$G$21</f>
+        <v>1253811.1813427727</v>
       </c>
       <c r="Z121" s="4">
-        <f>Z9*Z113</f>
-        <v>7340.1133720452426</v>
+        <f>Z120*$H$21</f>
+        <v>3944732.0630145115</v>
       </c>
       <c r="AA121" s="38" t="s">
-        <v>339</v>
+        <v>472</v>
       </c>
       <c r="AB121" s="42" t="s">
-        <v>406</v>
+        <v>470</v>
       </c>
       <c r="AC121" s="43" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
     </row>
     <row r="122" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B122" s="38" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="C122" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G122" s="4">
-        <f>MIN(G121,G9*G15)</f>
-        <v>250</v>
+        <f>G9*G114</f>
+        <v>7500</v>
       </c>
       <c r="H122" s="4">
-        <f>MIN(H121,H9*H15)</f>
-        <v>1000</v>
+        <f>H9*H114</f>
+        <v>10000</v>
       </c>
       <c r="J122" s="4">
-        <f>MIN(J121,J9*J15)</f>
-        <v>316.2</v>
+        <f>J9*J114</f>
+        <v>8647.6260468001601</v>
       </c>
       <c r="K122" s="4">
-        <f>MIN(K121,K9*K15)</f>
-        <v>1078</v>
+        <f>K9*K114</f>
+        <v>10442.725885753111</v>
       </c>
       <c r="M122" s="4">
-        <f>MIN(M121,M9*M15)</f>
-        <v>301.60000000000002</v>
+        <f>M9*M114</f>
+        <v>7476.6809964404965</v>
       </c>
       <c r="N122" s="4">
-        <f>MIN(N121,N9*N15)</f>
-        <v>921.2</v>
+        <f>N9*N114</f>
+        <v>8430.6210655252235</v>
       </c>
       <c r="P122" s="4">
-        <f>MIN(P121,P9*P15)</f>
-        <v>329</v>
+        <f>P9*P114</f>
+        <v>8257.8918263573341</v>
       </c>
       <c r="Q122" s="4">
-        <f>MIN(Q121,Q9*Q15)</f>
-        <v>1900.8000000000002</v>
+        <f>Q9*Q114</f>
+        <v>16180.439158748177</v>
       </c>
       <c r="S122" s="4">
-        <f>MIN(S121,S9*S15)</f>
-        <v>520</v>
+        <f>S9*S114</f>
+        <v>10690.850697398897</v>
       </c>
       <c r="T122" s="4">
-        <f>MIN(T121,T9*T15)</f>
-        <v>393.9</v>
+        <f>T9*T114</f>
+        <v>3061.8229295988804</v>
       </c>
       <c r="V122" s="4">
-        <f>MIN(V121,V9*V15)</f>
-        <v>401.79999999999995</v>
+        <f>V9*V114</f>
+        <v>9156.2149020377037</v>
       </c>
       <c r="W122" s="4">
-        <f>MIN(W121,W9*W15)</f>
-        <v>1155</v>
+        <f>W9*W114</f>
+        <v>7354.5574529693185</v>
       </c>
       <c r="Y122" s="4">
-        <f>MIN(Y121,Y9*Y15)</f>
-        <v>499.79999999999995</v>
+        <f>Y9*Y114</f>
+        <v>8263.958662657662</v>
       </c>
       <c r="Z122" s="4">
-        <f>MIN(Z121,Z9*Z15)</f>
-        <v>1044</v>
+        <f>Z9*Z114</f>
+        <v>7340.1134084428477</v>
       </c>
       <c r="AA122" s="38" t="s">
-        <v>343</v>
+        <v>471</v>
       </c>
       <c r="AB122" s="42" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="AC122" s="43" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="123" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="123" spans="2:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B123" s="38" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="C123" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F123" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G123" s="4">
+        <f>MIN(G122,G9*G15)</f>
+        <v>250</v>
+      </c>
+      <c r="H123" s="4">
+        <f>MIN(H122,H9*H15)</f>
+        <v>1000</v>
+      </c>
+      <c r="J123" s="4">
+        <f>MIN(J122,J9*J15)</f>
+        <v>316.2</v>
+      </c>
+      <c r="K123" s="4">
+        <f>MIN(K122,K9*K15)</f>
+        <v>1078</v>
+      </c>
+      <c r="M123" s="4">
+        <f>MIN(M122,M9*M15)</f>
+        <v>301.60000000000002</v>
+      </c>
+      <c r="N123" s="4">
+        <f>MIN(N122,N9*N15)</f>
+        <v>921.2</v>
+      </c>
+      <c r="P123" s="4">
+        <f>MIN(P122,P9*P15)</f>
+        <v>329</v>
+      </c>
+      <c r="Q123" s="4">
+        <f>MIN(Q122,Q9*Q15)</f>
+        <v>1900.8000000000002</v>
+      </c>
+      <c r="S123" s="4">
+        <f>MIN(S122,S9*S15)</f>
+        <v>520</v>
+      </c>
+      <c r="T123" s="4">
+        <f>MIN(T122,T9*T15)</f>
+        <v>393.9</v>
+      </c>
+      <c r="V123" s="4">
+        <f>MIN(V122,V9*V15)</f>
+        <v>401.79999999999995</v>
+      </c>
+      <c r="W123" s="4">
+        <f>MIN(W122,W9*W15)</f>
+        <v>1155</v>
+      </c>
+      <c r="Y123" s="4">
+        <f>MIN(Y122,Y9*Y15)</f>
+        <v>499.79999999999995</v>
+      </c>
+      <c r="Z123" s="4">
+        <f>MIN(Z122,Z9*Z15)</f>
+        <v>1044</v>
+      </c>
+      <c r="AA123" s="38" t="s">
+        <v>474</v>
+      </c>
+      <c r="AB123" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC123" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B124" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="C124" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F124" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="G123" s="4">
-        <f>(G121-G122)*$G$14</f>
+      <c r="G124" s="4">
+        <f>(G122-G123)*$G$14</f>
         <v>5075</v>
       </c>
-      <c r="H123" s="4">
-        <f>(H121-H122+H54)*$G$14</f>
+      <c r="H124" s="4">
+        <f>(H122-H123+H54)*$G$14</f>
         <v>6300</v>
       </c>
-      <c r="J123" s="4">
-        <f>(J121-J122)*$G$14</f>
+      <c r="J124" s="4">
+        <f>(J122-J123)*$G$14</f>
         <v>5831.998232760111</v>
       </c>
-      <c r="K123" s="4">
-        <f>(K121-K122+K54)*$G$14</f>
+      <c r="K124" s="4">
+        <f>(K122-K123+K54)*$G$14</f>
         <v>6555.3081200271772</v>
       </c>
-      <c r="M123" s="4">
-        <f>(M121-M122)*$G$14</f>
+      <c r="M124" s="4">
+        <f>(M122-M123)*$G$14</f>
         <v>5022.5566975083466</v>
       </c>
-      <c r="N123" s="4">
-        <f>(N121-N122+N54)*$G$14</f>
+      <c r="N124" s="4">
+        <f>(N122-N123+N54)*$G$14</f>
         <v>5256.5947458676565</v>
       </c>
-      <c r="P123" s="4">
-        <f>(P121-P122)*$G$14</f>
+      <c r="P124" s="4">
+        <f>(P122-P123)*$G$14</f>
         <v>5550.2242784501332</v>
       </c>
-      <c r="Q123" s="4">
-        <f>(Q121-Q122+Q54)*$G$14</f>
-        <v>9995.7474104054218</v>
-      </c>
-      <c r="S123" s="4">
-        <f>(S121-S122)*$G$14</f>
-        <v>7119.5954879759529</v>
-      </c>
-      <c r="T123" s="4">
-        <f>(T121-T122+T54)*$G$14</f>
-        <v>1867.5460495759712</v>
-      </c>
-      <c r="V123" s="4">
-        <f>(V121-V122)*$G$14</f>
-        <v>6128.0904288483789</v>
-      </c>
-      <c r="W123" s="4">
-        <f>(W121-W122+W54)*$G$14</f>
-        <v>4339.690204794103</v>
-      </c>
-      <c r="Y123" s="4">
-        <f>(Y121-Y122)*$G$14</f>
-        <v>5434.9110640441222</v>
-      </c>
-      <c r="Z123" s="4">
-        <f>(Z121-Z122+Z54)*$G$14</f>
-        <v>4407.2793604316694</v>
-      </c>
-      <c r="AA123" s="38" t="s">
-        <v>344</v>
-      </c>
-      <c r="AB123" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="AC123" s="43" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="124" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B124" s="38" t="s">
+      <c r="Q124" s="4">
+        <f>(Q122-Q123+Q54)*$G$14</f>
+        <v>9995.7474111237243</v>
+      </c>
+      <c r="S124" s="4">
+        <f>(S122-S123)*$G$14</f>
+        <v>7119.5954881792277</v>
+      </c>
+      <c r="T124" s="4">
+        <f>(T122-T123+T54)*$G$14</f>
+        <v>1867.5460507192161</v>
+      </c>
+      <c r="V124" s="4">
+        <f>(V122-V123)*$G$14</f>
+        <v>6128.0904314263926</v>
+      </c>
+      <c r="W124" s="4">
+        <f>(W122-W123+W54)*$G$14</f>
+        <v>4339.6902170785224</v>
+      </c>
+      <c r="Y124" s="4">
+        <f>(Y122-Y123)*$G$14</f>
+        <v>5434.9110638603634</v>
+      </c>
+      <c r="Z124" s="4">
+        <f>(Z122-Z123+Z54)*$G$14</f>
+        <v>4407.2793859099929</v>
+      </c>
+      <c r="AA124" s="38" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB124" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC124" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="125" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B125" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="33" t="s">
+      <c r="C125" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F124" s="14" t="s">
+      <c r="F125" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="G124" s="4">
-        <f>MIN(G123+H123, G33)</f>
+      <c r="G125" s="4">
+        <f>MIN(G124+H124, G33)</f>
         <v>11375</v>
       </c>
-      <c r="J124" s="4">
-        <f>MIN(J123+K123, J33)</f>
+      <c r="J125" s="4">
+        <f>MIN(J124+K124, J33)</f>
         <v>12387.306352787287</v>
       </c>
-      <c r="M124" s="4">
-        <f>MIN(M123+N123, M33)</f>
+      <c r="M125" s="4">
+        <f>MIN(M124+N124, M33)</f>
         <v>10279.151443376002</v>
       </c>
-      <c r="P124" s="4">
-        <f>MIN(P123+Q123, P33)</f>
-        <v>15545.971688855556</v>
-      </c>
-      <c r="S124" s="4">
-        <f>MIN(S123+T123, S33)</f>
-        <v>8987.1415375519246</v>
-      </c>
-      <c r="V124" s="4">
-        <f>MIN(V123+W123, V33)</f>
-        <v>10467.780633642482</v>
-      </c>
-      <c r="Y124" s="4">
-        <f>MIN(Y123+Z123, Y33)</f>
-        <v>9842.1904244757916</v>
-      </c>
-      <c r="AA124" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="AB124" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="AC124" s="43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="125" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B125" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="C125" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="G125" s="4">
-        <f>G123/(G123+H123)</f>
-        <v>0.44615384615384618</v>
-      </c>
-      <c r="H125" s="4">
-        <f>H123/(G123+H123)</f>
-        <v>0.55384615384615388</v>
-      </c>
-      <c r="J125" s="4">
-        <f>J123/(J123+K123)</f>
-        <v>0.47080439174315275</v>
-      </c>
-      <c r="K125" s="4">
-        <f>K123/(J123+K123)</f>
-        <v>0.52919560825684731</v>
-      </c>
-      <c r="M125" s="4">
-        <f>M123/(M123+N123)</f>
-        <v>0.48861588674665718</v>
-      </c>
-      <c r="N125" s="4">
-        <f>N123/(M123+N123)</f>
-        <v>0.51138411325334288</v>
-      </c>
       <c r="P125" s="4">
-        <f>P123/(P123+Q123)</f>
-        <v>0.35702009430706244</v>
-      </c>
-      <c r="Q125" s="4">
-        <f>Q123/(P123+Q123)</f>
-        <v>0.6429799056929375</v>
+        <f>MIN(P124+Q124, P33)</f>
+        <v>15545.971689573857</v>
       </c>
       <c r="S125" s="4">
-        <f>S123/(S123+T123)</f>
-        <v>0.79219799290212511</v>
-      </c>
-      <c r="T125" s="4">
-        <f>T123/(S123+T123)</f>
-        <v>0.20780200709787489</v>
+        <f>MIN(S124+T124, S33)</f>
+        <v>8987.1415388984442</v>
       </c>
       <c r="V125" s="4">
-        <f>V123/(V123+W123)</f>
-        <v>0.58542404004467397</v>
-      </c>
-      <c r="W125" s="4">
-        <f>W123/(V123+W123)</f>
-        <v>0.41457595995532603</v>
+        <f>MIN(V124+W124, V33)</f>
+        <v>10467.780648504915</v>
       </c>
       <c r="Y125" s="4">
-        <f>Y123/(Y123+Z123)</f>
-        <v>0.55220543696537883</v>
-      </c>
-      <c r="Z125" s="4">
-        <f>Z123/(Y123+Z123)</f>
-        <v>0.44779456303462112</v>
+        <f>MIN(Y124+Z124, Y33)</f>
+        <v>9842.1904497703563</v>
       </c>
       <c r="AA125" s="38" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="AB125" s="42" t="s">
-        <v>407</v>
+        <v>332</v>
       </c>
       <c r="AC125" s="43" t="s">
-        <v>384</v>
+        <v>330</v>
       </c>
     </row>
     <row r="126" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B126" s="38" t="s">
-        <v>183</v>
+        <v>254</v>
       </c>
       <c r="C126" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F126" s="10" t="s">
+      <c r="F126" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="G126" s="4">
+        <f>G124/(G124+H124)</f>
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="H126" s="4">
+        <f>H124/(G124+H124)</f>
+        <v>0.55384615384615388</v>
+      </c>
+      <c r="J126" s="4">
+        <f>J124/(J124+K124)</f>
+        <v>0.47080439174315275</v>
+      </c>
+      <c r="K126" s="4">
+        <f>K124/(J124+K124)</f>
+        <v>0.52919560825684731</v>
+      </c>
+      <c r="M126" s="4">
+        <f>M124/(M124+N124)</f>
+        <v>0.48861588674665718</v>
+      </c>
+      <c r="N126" s="4">
+        <f>N124/(M124+N124)</f>
+        <v>0.51138411325334288</v>
+      </c>
+      <c r="P126" s="4">
+        <f>P124/(P124+Q124)</f>
+        <v>0.35702009429056636</v>
+      </c>
+      <c r="Q126" s="4">
+        <f>Q124/(P124+Q124)</f>
+        <v>0.64297990570943375</v>
+      </c>
+      <c r="S126" s="4">
+        <f>S124/(S124+T124)</f>
+        <v>0.79219799280605052</v>
+      </c>
+      <c r="T126" s="4">
+        <f>T124/(S124+T124)</f>
+        <v>0.2078020071939494</v>
+      </c>
+      <c r="V126" s="4">
+        <f>V124/(V124+W124)</f>
+        <v>0.58542403945975419</v>
+      </c>
+      <c r="W126" s="4">
+        <f>W124/(V124+W124)</f>
+        <v>0.41457596054024581</v>
+      </c>
+      <c r="Y126" s="4">
+        <f>Y124/(Y124+Z124)</f>
+        <v>0.55220543552753276</v>
+      </c>
+      <c r="Z126" s="4">
+        <f>Z124/(Y124+Z124)</f>
+        <v>0.44779456447246724</v>
+      </c>
+      <c r="AA126" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="AB126" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC126" s="43" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="127" spans="2:29" ht="68" x14ac:dyDescent="0.2">
+      <c r="B127" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="C127" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F127" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G126" s="4">
-        <f>MAX(G13-G27, 0)*G114</f>
+      <c r="G127" s="4">
+        <f>MAX(G13-G27, 0)*G115</f>
         <v>4513584.2403750001</v>
       </c>
-      <c r="H126" s="4">
-        <f>MAX(H13-H27, 0)*H114</f>
+      <c r="H127" s="4">
+        <f>MAX(H13-H27, 0)*H115</f>
         <v>12433601.4893</v>
       </c>
-      <c r="J126" s="4">
-        <f>MAX(J13-J27, 0)*J114</f>
+      <c r="J127" s="4">
+        <f>MAX(J13-J27, 0)*J115</f>
         <v>4035039.8648233167</v>
       </c>
-      <c r="K126" s="4">
-        <f>MAX(K13-K27, 0)*K114</f>
+      <c r="K127" s="4">
+        <f>MAX(K13-K27, 0)*K115</f>
         <v>11414597.812208308</v>
       </c>
-      <c r="M126" s="4">
-        <f>MAX(M13-M27, 0)*M114</f>
+      <c r="M127" s="4">
+        <f>MAX(M13-M27, 0)*M115</f>
         <v>3516332.5365802972</v>
       </c>
-      <c r="N126" s="4">
-        <f>MAX(N13-N27, 0)*N114</f>
+      <c r="N127" s="4">
+        <f>MAX(N13-N27, 0)*N115</f>
         <v>10361539.512973329</v>
       </c>
-      <c r="P126" s="4">
-        <f>MAX(P13-P27, 0)*P114</f>
+      <c r="P127" s="4">
+        <f>MAX(P13-P27, 0)*P115</f>
         <v>2992454.3341056714</v>
       </c>
-      <c r="Q126" s="4">
-        <f>MAX(Q13-Q27, 0)*Q114</f>
-        <v>9271395.2977309991</v>
-      </c>
-      <c r="S126" s="4">
-        <f>MAX(S13-S27, 0)*S114</f>
-        <v>2474015.3391720308</v>
-      </c>
-      <c r="T126" s="4">
-        <f>MAX(T13-T27, 0)*T114</f>
-        <v>8160406.3758995822</v>
-      </c>
-      <c r="V126" s="4">
-        <f>MAX(V13-V27, 0)*V114</f>
-        <v>1857328.2871452775</v>
-      </c>
-      <c r="W126" s="4">
-        <f>MAX(W13-W27, 0)*W114</f>
-        <v>6443988.2778111491</v>
-      </c>
-      <c r="Y126" s="4">
-        <f>MAX(Y13-Y27, 0)*Y114</f>
-        <v>1468232.3963675336</v>
-      </c>
-      <c r="Z126" s="4">
-        <f>MAX(Z13-Z27, 0)*Z114</f>
-        <v>5088667.4405545928</v>
-      </c>
-      <c r="AA126" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="AB126" s="42" t="s">
-        <v>349</v>
-      </c>
-      <c r="AC126" s="43" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="127" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB127" s="42"/>
-      <c r="AC127" s="43"/>
-    </row>
-    <row r="128" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="F128" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G128" s="8"/>
-      <c r="H128" s="8"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="8"/>
-      <c r="M128" s="8"/>
-      <c r="N128" s="8"/>
-      <c r="P128" s="8"/>
-      <c r="Q128" s="8"/>
-      <c r="S128" s="8"/>
-      <c r="T128" s="8"/>
-      <c r="V128" s="8"/>
-      <c r="W128" s="8"/>
-      <c r="Y128" s="8"/>
-      <c r="Z128" s="8"/>
+      <c r="Q127" s="4">
+        <f>MAX(Q13-Q27, 0)*Q115</f>
+        <v>9271395.2987972517</v>
+      </c>
+      <c r="S127" s="4">
+        <f>MAX(S13-S27, 0)*S115</f>
+        <v>2474015.3392973635</v>
+      </c>
+      <c r="T127" s="4">
+        <f>MAX(T13-T27, 0)*T115</f>
+        <v>8160406.3842944754</v>
+      </c>
+      <c r="V127" s="4">
+        <f>MAX(V13-V27, 0)*V115</f>
+        <v>1857328.2887372568</v>
+      </c>
+      <c r="W127" s="4">
+        <f>MAX(W13-W27, 0)*W115</f>
+        <v>6443988.3112147413</v>
+      </c>
+      <c r="Y127" s="4">
+        <f>MAX(Y13-Y27, 0)*Y115</f>
+        <v>1468232.3962543209</v>
+      </c>
+      <c r="Z127" s="4">
+        <f>MAX(Z13-Z27, 0)*Z115</f>
+        <v>5088667.5032287594</v>
+      </c>
+      <c r="AA127" s="38" t="s">
+        <v>476</v>
+      </c>
+      <c r="AB127" s="42" t="s">
+        <v>334</v>
+      </c>
+      <c r="AC127" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="128" spans="2:29" x14ac:dyDescent="0.2">
       <c r="AB128" s="42"/>
       <c r="AC128" s="43"/>
     </row>
     <row r="129" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B129" s="38" t="s">
+      <c r="F129" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="8"/>
+      <c r="M129" s="8"/>
+      <c r="N129" s="8"/>
+      <c r="P129" s="8"/>
+      <c r="Q129" s="8"/>
+      <c r="S129" s="8"/>
+      <c r="T129" s="8"/>
+      <c r="V129" s="8"/>
+      <c r="W129" s="8"/>
+      <c r="Y129" s="8"/>
+      <c r="Z129" s="8"/>
+      <c r="AB129" s="42"/>
+      <c r="AC129" s="43"/>
+    </row>
+    <row r="130" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+      <c r="B130" s="38" t="s">
         <v>255</v>
-      </c>
-      <c r="C129" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="G129" s="4">
-        <f>MAX(G33-G124,0)</f>
-        <v>1988625</v>
-      </c>
-      <c r="J129" s="4">
-        <f>MAX(J33-J124,0)</f>
-        <v>2037612.6936472128</v>
-      </c>
-      <c r="M129" s="4">
-        <f>MAX(M33-M124,0)</f>
-        <v>2099720.8485566238</v>
-      </c>
-      <c r="P129" s="4">
-        <f>MAX(P33-P124,0)</f>
-        <v>2194454.0283111446</v>
-      </c>
-      <c r="S129" s="4">
-        <f>MAX(S33-S124,0)</f>
-        <v>2991012.8584624482</v>
-      </c>
-      <c r="V129" s="4">
-        <f>MAX(V33-V124,0)</f>
-        <v>24989532.219366357</v>
-      </c>
-      <c r="Y129" s="4">
-        <f>MAX(Y33-Y124,0)</f>
-        <v>2510157.8095755242</v>
-      </c>
-      <c r="AA129" s="38" t="s">
-        <v>475</v>
-      </c>
-      <c r="AB129" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="AC129" s="43" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B130" s="38" t="s">
-        <v>256</v>
       </c>
       <c r="C130" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F130" s="10" t="s">
-        <v>165</v>
+      <c r="F130" s="14" t="s">
+        <v>257</v>
       </c>
       <c r="G130" s="4">
-        <f>MIN(G140,G129)</f>
+        <f>MAX(G33-G125,0)</f>
         <v>1988625</v>
       </c>
       <c r="J130" s="4">
-        <f>MIN(J140,J129)</f>
+        <f>MAX(J33-J125,0)</f>
         <v>2037612.6936472128</v>
       </c>
       <c r="M130" s="4">
-        <f>MIN(M140,M129)</f>
+        <f>MAX(M33-M125,0)</f>
         <v>2099720.8485566238</v>
       </c>
       <c r="P130" s="4">
-        <f>MIN(P140,P129)</f>
-        <v>2194454.0283111446</v>
+        <f>MAX(P33-P125,0)</f>
+        <v>2194454.028310426</v>
       </c>
       <c r="S130" s="4">
-        <f>MIN(S140,S129)</f>
-        <v>2991012.8584624482</v>
+        <f>MAX(S33-S125,0)</f>
+        <v>2991012.8584611015</v>
       </c>
       <c r="V130" s="4">
-        <f>MIN(V140,V129)</f>
-        <v>2349768.169205951</v>
+        <f>MAX(V33-V125,0)</f>
+        <v>24989532.219351497</v>
       </c>
       <c r="Y130" s="4">
-        <f>MIN(Y140,Y129)</f>
-        <v>388638.16574066621</v>
+        <f>MAX(Y33-Y125,0)</f>
+        <v>2510157.8095502295</v>
       </c>
       <c r="AA130" s="38" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="AB130" s="42" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="AC130" s="43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="131" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B131" s="38" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C131" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="G131" s="4">
-        <f>G129-G130</f>
-        <v>0</v>
+        <f>MIN(G141,G130)</f>
+        <v>1988625</v>
       </c>
       <c r="J131" s="4">
-        <f>J129-J130</f>
-        <v>0</v>
+        <f>MIN(J141,J130)</f>
+        <v>2037612.6936472128</v>
       </c>
       <c r="M131" s="4">
-        <f>M129-M130</f>
-        <v>0</v>
+        <f>MIN(M141,M130)</f>
+        <v>2099720.8485566238</v>
       </c>
       <c r="P131" s="4">
-        <f>P129-P130</f>
-        <v>0</v>
+        <f>MIN(P141,P130)</f>
+        <v>2194454.028310426</v>
       </c>
       <c r="S131" s="4">
-        <f>S129-S130</f>
-        <v>0</v>
+        <f>MIN(S141,S130)</f>
+        <v>2991012.8584611015</v>
       </c>
       <c r="V131" s="4">
-        <f>V129-V130</f>
-        <v>22639764.050160404</v>
+        <f>MIN(V141,V130)</f>
+        <v>2349768.217245861</v>
       </c>
       <c r="Y131" s="4">
-        <f>Y129-Y130</f>
-        <v>2121519.6438348582</v>
+        <f>MIN(Y141,Y130)</f>
+        <v>388638.22348903998</v>
       </c>
       <c r="AA131" s="38" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="AB131" s="42" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="AC131" s="43" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="132" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="132" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B132" s="38" t="s">
-        <v>214</v>
+        <v>267</v>
       </c>
       <c r="C132" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="G132" s="4">
-        <f>MIN(G131,H77)</f>
+        <f>G130-G131</f>
         <v>0</v>
       </c>
       <c r="J132" s="4">
-        <f>MIN(J131,K77)</f>
+        <f>J130-J131</f>
         <v>0</v>
       </c>
       <c r="M132" s="4">
-        <f>MIN(M131,N77)</f>
+        <f>M130-M131</f>
         <v>0</v>
       </c>
       <c r="P132" s="4">
-        <f>MIN(P131,Q77)</f>
+        <f>P130-P131</f>
         <v>0</v>
       </c>
       <c r="S132" s="4">
-        <f>MIN(S131,T77)</f>
+        <f>S130-S131</f>
         <v>0</v>
       </c>
       <c r="V132" s="4">
-        <f>MIN(V131,W77)</f>
-        <v>0</v>
+        <f>V130-V131</f>
+        <v>22639764.002105635</v>
       </c>
       <c r="Y132" s="4">
-        <f>MIN(Y131,Z77)</f>
-        <v>0</v>
+        <f>Y130-Y131</f>
+        <v>2121519.5860611894</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="AB132" s="42" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="AC132" s="43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="133" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="133" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B133" s="38" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F133" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G133" s="4">
+        <f>MIN(G132,H77)</f>
+        <v>0</v>
+      </c>
+      <c r="J133" s="4">
+        <f>MIN(J132,K77)</f>
+        <v>0</v>
+      </c>
+      <c r="M133" s="4">
+        <f>MIN(M132,N77)</f>
+        <v>0</v>
+      </c>
+      <c r="P133" s="4">
+        <f>MIN(P132,Q77)</f>
+        <v>0</v>
+      </c>
+      <c r="S133" s="4">
+        <f>MIN(S132,T77)</f>
+        <v>0</v>
+      </c>
+      <c r="V133" s="4">
+        <f>MIN(V132,W77)</f>
+        <v>0</v>
+      </c>
+      <c r="Y133" s="4">
+        <f>MIN(Y132,Z77)</f>
+        <v>0</v>
+      </c>
+      <c r="AA133" s="38" t="s">
+        <v>446</v>
+      </c>
+      <c r="AB133" s="42" t="s">
+        <v>421</v>
+      </c>
+      <c r="AC133" s="43" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="134" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B134" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="C134" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F134" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G133" s="4">
-        <f>G141*G130</f>
+      <c r="G134" s="4">
+        <f>G142*G131</f>
         <v>529635.22104433016</v>
       </c>
-      <c r="H133" s="4">
-        <f>H141*G130</f>
+      <c r="H134" s="4">
+        <f>H142*G131</f>
         <v>1458989.7789556701</v>
       </c>
-      <c r="J133" s="4">
-        <f>J141*J130</f>
+      <c r="J134" s="4">
+        <f>J142*J131</f>
         <v>532170.95570853585</v>
       </c>
-      <c r="K133" s="4">
-        <f>K141*J130</f>
+      <c r="K134" s="4">
+        <f>K142*J131</f>
         <v>1505441.737938677</v>
       </c>
-      <c r="M133" s="4">
-        <f>M141*M130</f>
+      <c r="M134" s="4">
+        <f>M142*M131</f>
         <v>550789.80536667234</v>
       </c>
-      <c r="N133" s="4">
-        <f>N141*M130</f>
+      <c r="N134" s="4">
+        <f>N142*M131</f>
         <v>1548931.0431899517</v>
       </c>
-      <c r="P133" s="4">
-        <f>P141*P130</f>
-        <v>557000.38865488267</v>
-      </c>
-      <c r="Q133" s="4">
-        <f>Q141*P130</f>
-        <v>1637453.639656262</v>
-      </c>
-      <c r="S133" s="4">
-        <f>S141*S130</f>
-        <v>676930.23301880853</v>
-      </c>
-      <c r="T133" s="4">
-        <f>T141*S130</f>
-        <v>2314082.6254436397</v>
-      </c>
-      <c r="V133" s="4">
-        <f>V141*V130</f>
-        <v>457497.26124774636</v>
-      </c>
-      <c r="W133" s="4">
-        <f>W141*V130</f>
-        <v>1892270.9079582046</v>
-      </c>
-      <c r="Y133" s="4">
-        <f>Y141*Y130</f>
-        <v>52472.144574730177</v>
-      </c>
-      <c r="Z133" s="4">
-        <f>Z141*Y130</f>
-        <v>336166.02116593602</v>
-      </c>
-      <c r="AA133" s="38" t="s">
-        <v>471</v>
-      </c>
-      <c r="AB133" s="42" t="s">
-        <v>408</v>
-      </c>
-      <c r="AC133" s="43" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="134" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B134" s="38" t="s">
+      <c r="P134" s="4">
+        <f>P142*P131</f>
+        <v>557000.38851015724</v>
+      </c>
+      <c r="Q134" s="4">
+        <f>Q142*P131</f>
+        <v>1637453.6398002687</v>
+      </c>
+      <c r="S134" s="4">
+        <f>S142*S131</f>
+        <v>676930.2312938408</v>
+      </c>
+      <c r="T134" s="4">
+        <f>T142*S131</f>
+        <v>2314082.6271672607</v>
+      </c>
+      <c r="V134" s="4">
+        <f>V142*V131</f>
+        <v>457497.26325426705</v>
+      </c>
+      <c r="W134" s="4">
+        <f>W142*V131</f>
+        <v>1892270.9539915938</v>
+      </c>
+      <c r="Y134" s="4">
+        <f>Y142*Y131</f>
+        <v>52472.144479718736</v>
+      </c>
+      <c r="Z134" s="4">
+        <f>Z142*Y131</f>
+        <v>336166.07900932123</v>
+      </c>
+      <c r="AA134" s="38" t="s">
+        <v>447</v>
+      </c>
+      <c r="AB134" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="AC134" s="43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="135" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B135" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="C134" s="33" t="s">
+      <c r="C135" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F134" s="10" t="s">
+      <c r="F135" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="G134" s="4">
-        <f>G133</f>
+      <c r="G135" s="4">
+        <f>G134</f>
         <v>529635.22104433016</v>
       </c>
-      <c r="H134" s="4">
-        <f>H133+G132</f>
+      <c r="H135" s="4">
+        <f>H134+G133</f>
         <v>1458989.7789556701</v>
       </c>
-      <c r="J134" s="4">
-        <f>J133</f>
+      <c r="J135" s="4">
+        <f>J134</f>
         <v>532170.95570853585</v>
       </c>
-      <c r="K134" s="4">
-        <f>K133+J132</f>
+      <c r="K135" s="4">
+        <f>K134+J133</f>
         <v>1505441.737938677</v>
       </c>
-      <c r="M134" s="4">
-        <f>M133</f>
+      <c r="M135" s="4">
+        <f>M134</f>
         <v>550789.80536667234</v>
       </c>
-      <c r="N134" s="4">
-        <f>N133+M132</f>
+      <c r="N135" s="4">
+        <f>N134+M133</f>
         <v>1548931.0431899517</v>
       </c>
-      <c r="P134" s="4">
-        <f>P133</f>
-        <v>557000.38865488267</v>
-      </c>
-      <c r="Q134" s="4">
-        <f>Q133+P132</f>
-        <v>1637453.639656262</v>
-      </c>
-      <c r="S134" s="4">
-        <f>S133</f>
-        <v>676930.23301880853</v>
-      </c>
-      <c r="T134" s="4">
-        <f>T133+S132</f>
-        <v>2314082.6254436397</v>
-      </c>
-      <c r="V134" s="4">
-        <f>V133</f>
-        <v>457497.26124774636</v>
-      </c>
-      <c r="W134" s="4">
-        <f>W133+V132</f>
-        <v>1892270.9079582046</v>
-      </c>
-      <c r="Y134" s="4">
-        <f>Y133</f>
-        <v>52472.144574730177</v>
-      </c>
-      <c r="Z134" s="4">
-        <f>Z133+Y132</f>
-        <v>336166.02116593602</v>
-      </c>
-      <c r="AA134" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="AB134" s="42" t="s">
-        <v>477</v>
-      </c>
-      <c r="AC134" s="43" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="135" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="F135" s="15" t="s">
+      <c r="P135" s="4">
+        <f>P134</f>
+        <v>557000.38851015724</v>
+      </c>
+      <c r="Q135" s="4">
+        <f>Q134+P133</f>
+        <v>1637453.6398002687</v>
+      </c>
+      <c r="S135" s="4">
+        <f>S134</f>
+        <v>676930.2312938408</v>
+      </c>
+      <c r="T135" s="4">
+        <f>T134+S133</f>
+        <v>2314082.6271672607</v>
+      </c>
+      <c r="V135" s="4">
+        <f>V134</f>
+        <v>457497.26325426705</v>
+      </c>
+      <c r="W135" s="4">
+        <f>W134+V133</f>
+        <v>1892270.9539915938</v>
+      </c>
+      <c r="Y135" s="4">
+        <f>Y134</f>
+        <v>52472.144479718736</v>
+      </c>
+      <c r="Z135" s="4">
+        <f>Z134+Y133</f>
+        <v>336166.07900932123</v>
+      </c>
+      <c r="AA135" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="AB135" s="42" t="s">
+        <v>453</v>
+      </c>
+      <c r="AC135" s="43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="136" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="F136" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="8"/>
-      <c r="M135" s="8"/>
-      <c r="N135" s="8"/>
-      <c r="P135" s="8"/>
-      <c r="Q135" s="8"/>
-      <c r="S135" s="8"/>
-      <c r="T135" s="8"/>
-      <c r="V135" s="8"/>
-      <c r="W135" s="8"/>
-      <c r="Y135" s="8"/>
-      <c r="Z135" s="8"/>
-      <c r="AB135" s="42"/>
-      <c r="AC135" s="43"/>
-    </row>
-    <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="B136" s="38" t="s">
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="8"/>
+      <c r="M136" s="8"/>
+      <c r="N136" s="8"/>
+      <c r="P136" s="8"/>
+      <c r="Q136" s="8"/>
+      <c r="S136" s="8"/>
+      <c r="T136" s="8"/>
+      <c r="V136" s="8"/>
+      <c r="W136" s="8"/>
+      <c r="Y136" s="8"/>
+      <c r="Z136" s="8"/>
+      <c r="AB136" s="42"/>
+      <c r="AC136" s="43"/>
+    </row>
+    <row r="137" spans="1:30" ht="119" x14ac:dyDescent="0.2">
+      <c r="B137" s="38" t="s">
         <v>271</v>
-      </c>
-      <c r="C136" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F136" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="G136" s="4">
-        <f>G114/$G$23</f>
-        <v>1</v>
-      </c>
-      <c r="H136" s="4">
-        <f>H114/$H$23</f>
-        <v>1</v>
-      </c>
-      <c r="J136" s="4">
-        <f>J114/$G$23</f>
-        <v>0.8952116342841121</v>
-      </c>
-      <c r="K136" s="4">
-        <f>K114/$H$23</f>
-        <v>0.91854982240604577</v>
-      </c>
-      <c r="M136" s="4">
-        <f>M114/$G$23</f>
-        <v>0.78995136076604022</v>
-      </c>
-      <c r="N136" s="4">
-        <f>N114/$H$23</f>
-        <v>0.83420112677639169</v>
-      </c>
-      <c r="P136" s="4">
-        <f>P114/$G$23</f>
-        <v>0.681017640976468</v>
-      </c>
-      <c r="Q136" s="4">
-        <f>Q114/$H$23</f>
-        <v>0.74715264984649332</v>
-      </c>
-      <c r="S136" s="4">
-        <f>S114/$G$23</f>
-        <v>0.57085931966813153</v>
-      </c>
-      <c r="T136" s="4">
-        <f>T114/$H$23</f>
-        <v>0.65446899750904841</v>
-      </c>
-      <c r="V136" s="4">
-        <f>V114/$G$23</f>
-        <v>0.43663682548207439</v>
-      </c>
-      <c r="W136" s="4">
-        <f>W114/$H$23</f>
-        <v>0.51837578868871137</v>
-      </c>
-      <c r="Y136" s="4">
-        <f>Y114/$G$23</f>
-        <v>0.3459651461038985</v>
-      </c>
-      <c r="Z136" s="4">
-        <f>Z114/$H$23</f>
-        <v>0.40958701246600088</v>
-      </c>
-      <c r="AA136" s="38" t="s">
-        <v>387</v>
-      </c>
-      <c r="AB136" s="42" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC136" s="43" t="s">
-        <v>383</v>
-      </c>
-      <c r="AD136">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="137" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>289</v>
-      </c>
-      <c r="B137" s="38" t="s">
-        <v>184</v>
       </c>
       <c r="C137" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="G137" s="4">
-        <f>MAX(MIN((G136-$G$17)/$G$18, 1), 0)</f>
+        <f>G115/$G$23</f>
         <v>1</v>
       </c>
       <c r="H137" s="4">
-        <f>MAX(MIN((H136-$H$17)/$H$18, 1), 0)</f>
+        <f>H115/$H$23</f>
         <v>1</v>
       </c>
       <c r="J137" s="4">
-        <f>MAX(MIN((J136-$G$17)/$G$18, 1), 0)</f>
-        <v>1</v>
+        <f>J115/$G$23</f>
+        <v>0.8952116342841121</v>
       </c>
       <c r="K137" s="4">
-        <f>MAX(MIN((K136-$H$17)/$H$18, 1), 0)</f>
-        <v>1</v>
+        <f>K115/$H$23</f>
+        <v>0.91854982240604577</v>
       </c>
       <c r="M137" s="4">
-        <f>MAX(MIN((M136-$G$17)/$G$18, 1), 0)</f>
-        <v>1</v>
+        <f>M115/$G$23</f>
+        <v>0.78995136076604022</v>
       </c>
       <c r="N137" s="4">
-        <f>MAX(MIN((N136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.95435915135809635</v>
+        <f>N115/$H$23</f>
+        <v>0.83420112677639169</v>
       </c>
       <c r="P137" s="4">
-        <f>MAX(MIN((P136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.81388590259622062</v>
+        <f>P115/$G$23</f>
+        <v>0.681017640976468</v>
       </c>
       <c r="Q137" s="4">
-        <f>MAX(MIN((Q136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.7722527690988813</v>
+        <f>Q115/$H$23</f>
+        <v>0.74715264993241937</v>
       </c>
       <c r="S137" s="4">
-        <f>MAX(MIN((S136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.55804708975578599</v>
+        <f>S115/$G$23</f>
+        <v>0.57085931969705117</v>
       </c>
       <c r="T137" s="4">
-        <f>MAX(MIN((T136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.57835753718878935</v>
+        <f>T115/$H$23</f>
+        <v>0.6544689981823234</v>
       </c>
       <c r="V137" s="4">
-        <f>MAX(MIN((V136-$G$17)/$G$18, 1), 0)</f>
-        <v>0.24632008483051848</v>
+        <f>V115/$G$23</f>
+        <v>0.43663682585633068</v>
       </c>
       <c r="W137" s="4">
-        <f>MAX(MIN((W136-$H$17)/$H$18, 1), 0)</f>
-        <v>0.29364903013153193</v>
+        <f>W115/$H$23</f>
+        <v>0.51837579137580714</v>
       </c>
       <c r="Y137" s="4">
-        <f>MAX(MIN((Y136-$G$17)/$G$18, 1), 0)</f>
-        <v>3.5738310028132055E-2</v>
+        <f>Y115/$G$23</f>
+        <v>0.34596514607722179</v>
       </c>
       <c r="Z137" s="4">
-        <f>MAX(MIN((Z136-$H$17)/$H$18, 1), 0)</f>
-        <v>6.6061699864060811E-2</v>
-      </c>
-      <c r="AA137" s="39" t="s">
-        <v>354</v>
+        <f>Z115/$H$23</f>
+        <v>0.40958701751064658</v>
+      </c>
+      <c r="AA137" s="38" t="s">
+        <v>365</v>
       </c>
       <c r="AB137" s="42" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="AC137" s="43" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="AD137">
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="B138" s="38"/>
-      <c r="AA138" s="38"/>
-      <c r="AB138" s="42"/>
-      <c r="AC138" s="43"/>
+    <row r="138" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A138" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="B138" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C138" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="G138" s="4">
+        <f>MAX(MIN((G137-$G$17)/$G$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H138" s="4">
+        <f>MAX(MIN((H137-$H$17)/$H$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J138" s="4">
+        <f>MAX(MIN((J137-$G$17)/$G$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="K138" s="4">
+        <f>MAX(MIN((K137-$H$17)/$H$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="M138" s="4">
+        <f>MAX(MIN((M137-$G$17)/$G$18, 1), 0)</f>
+        <v>1</v>
+      </c>
+      <c r="N138" s="4">
+        <f>MAX(MIN((N137-$H$17)/$H$18, 1), 0)</f>
+        <v>0.95435915135809635</v>
+      </c>
+      <c r="P138" s="4">
+        <f>MAX(MIN((P137-$G$17)/$G$18, 1), 0)</f>
+        <v>0.81388590259622062</v>
+      </c>
+      <c r="Q138" s="4">
+        <f>MAX(MIN((Q137-$H$17)/$H$18, 1), 0)</f>
+        <v>0.77225276927863951</v>
+      </c>
+      <c r="S138" s="4">
+        <f>MAX(MIN((S137-$G$17)/$G$18, 1), 0)</f>
+        <v>0.55804708982295081</v>
+      </c>
+      <c r="T138" s="4">
+        <f>MAX(MIN((T137-$H$17)/$H$18, 1), 0)</f>
+        <v>0.57835753859728811</v>
+      </c>
+      <c r="V138" s="4">
+        <f>MAX(MIN((V137-$G$17)/$G$18, 1), 0)</f>
+        <v>0.2463200856997155</v>
+      </c>
+      <c r="W138" s="4">
+        <f>MAX(MIN((W137-$H$17)/$H$18, 1), 0)</f>
+        <v>0.29364903575296619</v>
+      </c>
+      <c r="Y138" s="4">
+        <f>MAX(MIN((Y137-$G$17)/$G$18, 1), 0)</f>
+        <v>3.5738309966176322E-2</v>
+      </c>
+      <c r="Z138" s="4">
+        <f>MAX(MIN((Z137-$H$17)/$H$18, 1), 0)</f>
+        <v>6.6061710417515754E-2</v>
+      </c>
+      <c r="AA138" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="AB138" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC138" s="43" t="s">
+        <v>362</v>
+      </c>
       <c r="AD138">
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B139" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="C139" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G139" s="4">
-        <f>G126*G137</f>
-        <v>4513584.2403750001</v>
-      </c>
-      <c r="H139" s="4">
-        <f>H126*H137</f>
-        <v>12433601.4893</v>
-      </c>
-      <c r="J139" s="4">
-        <f>J126*J137</f>
-        <v>4035039.8648233167</v>
-      </c>
-      <c r="K139" s="4">
-        <f>K126*K137</f>
-        <v>11414597.812208308</v>
-      </c>
-      <c r="M139" s="4">
-        <f>M126*M137</f>
-        <v>3516332.5365802972</v>
-      </c>
-      <c r="N139" s="4">
-        <f>N126*N137</f>
-        <v>9888630.0563646089</v>
-      </c>
-      <c r="P139" s="4">
-        <f>P126*P137</f>
-        <v>2435516.3966915668</v>
-      </c>
-      <c r="Q139" s="4">
-        <f>Q126*Q137</f>
-        <v>7159860.692083111</v>
-      </c>
-      <c r="S139" s="4">
-        <f>S126*S137</f>
-        <v>1380617.0600361256</v>
-      </c>
-      <c r="T139" s="4">
-        <f>T126*T137</f>
-        <v>4719632.5340249762</v>
-      </c>
-      <c r="V139" s="4">
-        <f>V126*V137</f>
-        <v>457497.26124774636</v>
-      </c>
-      <c r="W139" s="4">
-        <f>W126*W137</f>
-        <v>1892270.9079582046</v>
-      </c>
-      <c r="Y139" s="4">
-        <f>Y126*Y137</f>
-        <v>52472.144574730184</v>
-      </c>
-      <c r="Z139" s="4">
-        <f>Z126*Z137</f>
-        <v>336166.02116593602</v>
-      </c>
-      <c r="AA139" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="AB139" s="42" t="s">
-        <v>411</v>
-      </c>
-      <c r="AC139" s="43" t="s">
-        <v>368</v>
-      </c>
+    <row r="139" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="B139" s="38"/>
+      <c r="AA139" s="38"/>
+      <c r="AB139" s="42"/>
+      <c r="AC139" s="43"/>
       <c r="AD139">
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="B140" s="38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C140" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="G140" s="4">
-        <f>G139+H139</f>
-        <v>16947185.729674999</v>
+        <f>G127*G138</f>
+        <v>4513584.2403750001</v>
       </c>
       <c r="H140" s="4">
-        <f>G140</f>
-        <v>16947185.729674999</v>
+        <f>H127*H138</f>
+        <v>12433601.4893</v>
       </c>
       <c r="J140" s="4">
-        <f>J139+K139</f>
-        <v>15449637.677031625</v>
+        <f>J127*J138</f>
+        <v>4035039.8648233167</v>
       </c>
       <c r="K140" s="4">
-        <f>J140</f>
-        <v>15449637.677031625</v>
+        <f>K127*K138</f>
+        <v>11414597.812208308</v>
       </c>
       <c r="M140" s="4">
-        <f>M139+N139</f>
-        <v>13404962.592944905</v>
+        <f>M127*M138</f>
+        <v>3516332.5365802972</v>
       </c>
       <c r="N140" s="4">
-        <f>M140</f>
-        <v>13404962.592944905</v>
+        <f>N127*N138</f>
+        <v>9888630.0563646089</v>
       </c>
       <c r="P140" s="4">
-        <f>P139+Q139</f>
-        <v>9595377.0887746774</v>
+        <f>P127*P138</f>
+        <v>2435516.3966915668</v>
       </c>
       <c r="Q140" s="4">
-        <f>P140</f>
-        <v>9595377.0887746774</v>
+        <f>Q127*Q138</f>
+        <v>7159860.694573137</v>
       </c>
       <c r="S140" s="4">
-        <f>S139+T139</f>
-        <v>6100249.5940611018</v>
+        <f>S127*S138</f>
+        <v>1380617.060272234</v>
       </c>
       <c r="T140" s="4">
-        <f>S140</f>
-        <v>6100249.5940611018</v>
+        <f>T127*T138</f>
+        <v>4719632.5503741484</v>
       </c>
       <c r="V140" s="4">
-        <f>V139+W139</f>
-        <v>2349768.169205951</v>
+        <f>V127*V138</f>
+        <v>457497.26325426705</v>
       </c>
       <c r="W140" s="4">
-        <f>V140</f>
-        <v>2349768.169205951</v>
+        <f>W127*W138</f>
+        <v>1892270.9539915938</v>
       </c>
       <c r="Y140" s="4">
-        <f>Y139+Z139</f>
-        <v>388638.16574066621</v>
+        <f>Y127*Y138</f>
+        <v>52472.144479718736</v>
       </c>
       <c r="Z140" s="4">
-        <f>Y140</f>
-        <v>388638.16574066621</v>
+        <f>Z127*Z138</f>
+        <v>336166.07900932123</v>
       </c>
       <c r="AA140" s="38" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="AB140" s="42" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="AC140" s="43" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="141" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+      <c r="AD140">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B141" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C141" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F141" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G141" s="4">
+        <f>G140+H140</f>
+        <v>16947185.729674999</v>
+      </c>
+      <c r="H141" s="4">
+        <f>G141</f>
+        <v>16947185.729674999</v>
+      </c>
+      <c r="J141" s="4">
+        <f>J140+K140</f>
+        <v>15449637.677031625</v>
+      </c>
+      <c r="K141" s="4">
+        <f>J141</f>
+        <v>15449637.677031625</v>
+      </c>
+      <c r="M141" s="4">
+        <f>M140+N140</f>
+        <v>13404962.592944905</v>
+      </c>
+      <c r="N141" s="4">
+        <f>M141</f>
+        <v>13404962.592944905</v>
+      </c>
+      <c r="P141" s="4">
+        <f>P140+Q140</f>
+        <v>9595377.0912647042</v>
+      </c>
+      <c r="Q141" s="4">
+        <f>P141</f>
+        <v>9595377.0912647042</v>
+      </c>
+      <c r="S141" s="4">
+        <f>S140+T140</f>
+        <v>6100249.610646382</v>
+      </c>
+      <c r="T141" s="4">
+        <f>S141</f>
+        <v>6100249.610646382</v>
+      </c>
+      <c r="V141" s="4">
+        <f>V140+W140</f>
+        <v>2349768.217245861</v>
+      </c>
+      <c r="W141" s="4">
+        <f>V141</f>
+        <v>2349768.217245861</v>
+      </c>
+      <c r="Y141" s="4">
+        <f>Y140+Z140</f>
+        <v>388638.22348903998</v>
+      </c>
+      <c r="Z141" s="4">
+        <f>Y141</f>
+        <v>388638.22348903998</v>
+      </c>
+      <c r="AA141" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="AB141" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="AC141" s="43" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="142" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B142" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C142" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F142" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="G141" s="4">
-        <f>G139/G140</f>
+      <c r="G142" s="4">
+        <f>G140/G141</f>
         <v>0.26633237591015407</v>
       </c>
-      <c r="H141" s="4">
-        <f>H139/H140</f>
+      <c r="H142" s="4">
+        <f>H140/H141</f>
         <v>0.73366762408984598</v>
       </c>
-      <c r="J141" s="4">
-        <f>J139/J140</f>
+      <c r="J142" s="4">
+        <f>J140/J141</f>
         <v>0.26117375366168316</v>
       </c>
-      <c r="K141" s="4">
-        <f>K139/K140</f>
+      <c r="K142" s="4">
+        <f>K140/K141</f>
         <v>0.73882624633831684</v>
       </c>
-      <c r="M141" s="4">
-        <f>M139/M140</f>
+      <c r="M142" s="4">
+        <f>M140/M141</f>
         <v>0.26231572913384776</v>
       </c>
-      <c r="N141" s="4">
-        <f>N139/N140</f>
+      <c r="N142" s="4">
+        <f>N140/N141</f>
         <v>0.73768427086615229</v>
       </c>
-      <c r="P141" s="4">
-        <f>P139/P140</f>
-        <v>0.25382185339446417</v>
-      </c>
-      <c r="Q141" s="4">
-        <f>Q139/Q140</f>
-        <v>0.74617814660553583</v>
-      </c>
-      <c r="S141" s="4">
-        <f>S139/S140</f>
-        <v>0.22632140517335969</v>
-      </c>
-      <c r="T141" s="4">
-        <f>T139/T140</f>
-        <v>0.77367859482664036</v>
-      </c>
-      <c r="V141" s="4">
-        <f>V139/V140</f>
-        <v>0.1946988929560429</v>
-      </c>
-      <c r="W141" s="4">
-        <f>W139/W140</f>
-        <v>0.80530110704395708</v>
-      </c>
-      <c r="Y141" s="4">
-        <f>Y139/Y140</f>
-        <v>0.13501541845415213</v>
-      </c>
-      <c r="Z141" s="4">
-        <f>Z139/Z140</f>
-        <v>0.86498458154584779</v>
-      </c>
-      <c r="AA141" s="38" t="s">
-        <v>353</v>
-      </c>
-      <c r="AB141" s="42" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC141" s="43" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB142" s="42"/>
-      <c r="AC142" s="43"/>
-    </row>
-    <row r="143" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="F143" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="8"/>
-      <c r="M143" s="8"/>
-      <c r="N143" s="8"/>
-      <c r="P143" s="8"/>
-      <c r="Q143" s="8"/>
-      <c r="S143" s="8"/>
-      <c r="T143" s="8"/>
-      <c r="V143" s="8"/>
-      <c r="W143" s="8"/>
-      <c r="Y143" s="8"/>
-      <c r="Z143" s="8"/>
+      <c r="P142" s="4">
+        <f>P140/P141</f>
+        <v>0.25382185332859675</v>
+      </c>
+      <c r="Q142" s="4">
+        <f>Q140/Q141</f>
+        <v>0.74617814667140325</v>
+      </c>
+      <c r="S142" s="4">
+        <f>S140/S141</f>
+        <v>0.22632140459674469</v>
+      </c>
+      <c r="T142" s="4">
+        <f>T140/T141</f>
+        <v>0.77367859540325534</v>
+      </c>
+      <c r="V142" s="4">
+        <f>V140/V141</f>
+        <v>0.19469888982943809</v>
+      </c>
+      <c r="W142" s="4">
+        <f>W140/W141</f>
+        <v>0.80530111017056183</v>
+      </c>
+      <c r="Y142" s="4">
+        <f>Y140/Y141</f>
+        <v>0.13501539814752295</v>
+      </c>
+      <c r="Z142" s="4">
+        <f>Z140/Z141</f>
+        <v>0.86498460185247705</v>
+      </c>
+      <c r="AA142" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB142" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC142" s="43" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="143" spans="1:30" x14ac:dyDescent="0.2">
       <c r="AB143" s="42"/>
       <c r="AC143" s="43"/>
     </row>
     <row r="144" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B144" s="38" t="s">
+      <c r="F144" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="J144" s="8"/>
+      <c r="K144" s="8"/>
+      <c r="M144" s="8"/>
+      <c r="N144" s="8"/>
+      <c r="P144" s="8"/>
+      <c r="Q144" s="8"/>
+      <c r="S144" s="8"/>
+      <c r="T144" s="8"/>
+      <c r="V144" s="8"/>
+      <c r="W144" s="8"/>
+      <c r="Y144" s="8"/>
+      <c r="Z144" s="8"/>
+      <c r="AB144" s="42"/>
+      <c r="AC144" s="43"/>
+    </row>
+    <row r="145" spans="2:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="B145" s="38" t="s">
         <v>269</v>
-      </c>
-      <c r="C144" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F144" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="G144" s="4">
-        <f>(G112 - G133 - G121)*$G$30</f>
-        <v>10931.697702960402</v>
-      </c>
-      <c r="H144" s="4">
-        <f>(H112 - H133 - H121)*$H$30+SUM(H91:H94)</f>
-        <v>36943.686047039599</v>
-      </c>
-      <c r="J144" s="4">
-        <f>(J112 - J133 - J121)*$G$30</f>
-        <v>10088.976214210876</v>
-      </c>
-      <c r="K144" s="4">
-        <f>(K112 - K133 - K121)*$H$30+SUM(K91:K94)</f>
-        <v>34866.701411741393</v>
-      </c>
-      <c r="M144" s="4">
-        <f>(M112 - M133 - M121)*$G$30</f>
-        <v>9220.1553859644791</v>
-      </c>
-      <c r="N144" s="4">
-        <f>(N112 - N133 - N121)*$H$30+SUM(N91:N94)</f>
-        <v>32727.700888143867</v>
-      </c>
-      <c r="P144" s="4">
-        <f>(P112 - P133 - P121)*$G$30</f>
-        <v>8341.6941716529673</v>
-      </c>
-      <c r="Q144" s="4">
-        <f>(Q112 - Q133 - Q121)*$H$30+SUM(Q91:Q94)</f>
-        <v>30440.781722816362</v>
-      </c>
-      <c r="S144" s="4">
-        <f>(S112 - S133 - S121)*$G$30</f>
-        <v>7272.4695703694815</v>
-      </c>
-      <c r="T144" s="4">
-        <f>(T112 - T133 - T121)*$H$30+SUM(T91:T94)</f>
-        <v>27115.480213028492</v>
-      </c>
-      <c r="V144" s="4">
-        <f>(V112 - V133 - V121)*$G$30</f>
-        <v>6551.7956955946229</v>
-      </c>
-      <c r="W144" s="4">
-        <f>(W112 - W133 - W121)*$H$30+SUM(W91:W94)</f>
-        <v>24450.873781739971</v>
-      </c>
-      <c r="Y144" s="4">
-        <f>(Y112 - Y133 - Y121)*$G$30</f>
-        <v>6466.2561671525018</v>
-      </c>
-      <c r="Z144" s="4">
-        <f>(Z112 - Z133 - Z121)*$H$30+SUM(Z91:Z94)</f>
-        <v>24233.450603308444</v>
-      </c>
-      <c r="AA144" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="AB144" s="42" t="s">
-        <v>413</v>
-      </c>
-      <c r="AC144" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="145" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B145" s="38" t="s">
-        <v>288</v>
       </c>
       <c r="C145" s="33" t="s">
         <v>163</v>
       </c>
+      <c r="F145" s="10" t="s">
+        <v>201</v>
+      </c>
       <c r="G145" s="4">
-        <f>G144*$G21</f>
-        <v>3279.5093108881206</v>
+        <f>(G113 - G134 - G122)*$G$30</f>
+        <v>10931.697702960402</v>
       </c>
       <c r="H145" s="4">
-        <f>H144*$H21</f>
-        <v>9235.9215117598997</v>
+        <f>(H113 - H134 - H122)*$H$30+H95</f>
+        <v>36943.686047039599</v>
       </c>
       <c r="J145" s="4">
-        <f>J144*$G21</f>
-        <v>3026.6928642632624</v>
+        <f>(J113 - J134 - J122)*$G$30</f>
+        <v>10088.976214210876</v>
       </c>
       <c r="K145" s="4">
-        <f>K144*$H21</f>
-        <v>8716.6753529353482</v>
+        <f>(K113 - K134 - K122)*$H$30+K95</f>
+        <v>34866.701411741393</v>
       </c>
       <c r="M145" s="4">
-        <f>M144*$G21</f>
-        <v>2766.0466157893438</v>
+        <f>(M113 - M134 - M122)*$G$30</f>
+        <v>9220.1553859644791</v>
       </c>
       <c r="N145" s="4">
-        <f>N144*$H21</f>
-        <v>8181.9252220359667</v>
+        <f>(N113 - N134 - N122)*$H$30+N95</f>
+        <v>32727.700888143867</v>
       </c>
       <c r="P145" s="4">
-        <f>P144*$G21</f>
-        <v>2502.5082514958899</v>
+        <f>(P113 - P134 - P122)*$G$30</f>
+        <v>8341.6941718801863</v>
       </c>
       <c r="Q145" s="4">
-        <f>Q144*$H21</f>
-        <v>7610.1954307040905</v>
+        <f>(Q113 - Q134 - Q122)*$H$30+Q95</f>
+        <v>30440.781724683824</v>
       </c>
       <c r="S145" s="4">
-        <f>S144*$G21</f>
-        <v>2181.7408711108442</v>
+        <f>(S113 - S134 - S122)*$G$30</f>
+        <v>7272.4695733040871</v>
       </c>
       <c r="T145" s="4">
-        <f>T144*$H21</f>
-        <v>6778.8700532571229</v>
+        <f>(T113 - T134 - T122)*$H$30+T95</f>
+        <v>27115.480226723997</v>
       </c>
       <c r="V145" s="4">
-        <f>V144*$G21</f>
-        <v>1965.5387086783867</v>
+        <f>(V113 - V134 - V122)*$G$30</f>
+        <v>6551.7956953686007</v>
       </c>
       <c r="W145" s="4">
-        <f>W144*$H21</f>
-        <v>6112.7184454349926</v>
+        <f>(W113 - W134 - W122)*$H$30+W95</f>
+        <v>24450.873774900079</v>
       </c>
       <c r="Y145" s="4">
-        <f>Y144*$G21</f>
-        <v>1939.8768501457505</v>
+        <f>(Y113 - Y134 - Y122)*$G$30</f>
+        <v>6466.2561670936466</v>
       </c>
       <c r="Z145" s="4">
-        <f>Z144*$H21</f>
-        <v>6058.3626508271109</v>
+        <f>(Z113 - Z134 - Z122)*$H$30+Z95</f>
+        <v>24233.450635277597</v>
       </c>
       <c r="AA145" s="38" t="s">
-        <v>358</v>
+        <v>462</v>
       </c>
       <c r="AB145" s="42" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="AC145" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="146" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="38" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F146" s="14" t="s">
-        <v>213</v>
-      </c>
       <c r="G146" s="4">
-        <f>G133*$G21</f>
-        <v>158890.56631329903</v>
+        <f>G145*$G21</f>
+        <v>3279.5093108881206</v>
       </c>
       <c r="H146" s="4">
-        <f>(H133+G132)*$H21</f>
-        <v>364747.44473891752</v>
+        <f>H145*$H21</f>
+        <v>9235.9215117598997</v>
       </c>
       <c r="J146" s="4">
-        <f>J133*$G21</f>
-        <v>159651.28671256074</v>
+        <f>J145*$G21</f>
+        <v>3026.6928642632624</v>
       </c>
       <c r="K146" s="4">
-        <f>(K133+J132)*$H21</f>
-        <v>376360.43448466924</v>
+        <f>K145*$H21</f>
+        <v>8716.6753529353482</v>
       </c>
       <c r="M146" s="4">
-        <f>M133*$G21</f>
-        <v>165236.9416100017</v>
+        <f>M145*$G21</f>
+        <v>2766.0466157893438</v>
       </c>
       <c r="N146" s="4">
-        <f>(N133+M132)*$H21</f>
-        <v>387232.76079748792</v>
+        <f>N145*$H21</f>
+        <v>8181.9252220359667</v>
       </c>
       <c r="P146" s="4">
-        <f>P133*$G21</f>
-        <v>167100.1165964648</v>
+        <f>P145*$G21</f>
+        <v>2502.5082515640556</v>
       </c>
       <c r="Q146" s="4">
-        <f>(Q133+P132)*$H21</f>
-        <v>409363.4099140655</v>
+        <f>Q145*$H21</f>
+        <v>7610.195431170956</v>
       </c>
       <c r="S146" s="4">
-        <f>S133*$G21</f>
-        <v>203079.06990564257</v>
+        <f>S145*$G21</f>
+        <v>2181.740871991226</v>
       </c>
       <c r="T146" s="4">
-        <f>(T133+S132)*$H21</f>
-        <v>578520.65636090992</v>
+        <f>T145*$H21</f>
+        <v>6778.8700566809994</v>
       </c>
       <c r="V146" s="4">
-        <f>V133*$G21</f>
-        <v>137249.17837432391</v>
+        <f>V145*$G21</f>
+        <v>1965.5387086105802</v>
       </c>
       <c r="W146" s="4">
-        <f>(W133+V132)*$H21</f>
-        <v>473067.72698955116</v>
+        <f>W145*$H21</f>
+        <v>6112.7184437250198</v>
       </c>
       <c r="Y146" s="4">
-        <f>Y133*$G21</f>
-        <v>15741.643372419052</v>
+        <f>Y145*$G21</f>
+        <v>1939.8768501280938</v>
       </c>
       <c r="Z146" s="4">
-        <f>(Z133+Y132)*$H21</f>
-        <v>84041.505291484005</v>
+        <f>Z145*$H21</f>
+        <v>6058.3626588193993</v>
       </c>
       <c r="AA146" s="38" t="s">
-        <v>359</v>
+        <v>463</v>
       </c>
       <c r="AB146" s="42" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="AC146" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="147" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="147" spans="2:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B147" s="38" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="C147" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F147" s="10" t="s">
-        <v>166</v>
+      <c r="F147" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="G147" s="4">
-        <f>G121-G124*G125-G122</f>
-        <v>2175</v>
+        <f>G134*$G21</f>
+        <v>158890.56631329903</v>
       </c>
       <c r="H147" s="4">
-        <f>H121-G124*H125-H122+H54</f>
-        <v>2700</v>
+        <f>(H134+G133)*$H21</f>
+        <v>364747.44473891752</v>
       </c>
       <c r="J147" s="4">
-        <f>J121-J124*J125-J122</f>
-        <v>2499.4278140400493</v>
+        <f>J134*$G21</f>
+        <v>159651.28671256074</v>
       </c>
       <c r="K147" s="4">
-        <f>K121-J124*K125-K122+K54</f>
-        <v>2809.4177657259334</v>
+        <f>(K134+J133)*$H21</f>
+        <v>376360.43448466924</v>
       </c>
       <c r="M147" s="4">
-        <f>M121-M124*M125-M122</f>
-        <v>2152.52429893215</v>
+        <f>M134*$G21</f>
+        <v>165236.9416100017</v>
       </c>
       <c r="N147" s="4">
-        <f>N121-M124*N125-N122+N54</f>
-        <v>2252.8263196575672</v>
+        <f>(N134+M133)*$H21</f>
+        <v>387232.76079748792</v>
       </c>
       <c r="P147" s="4">
-        <f>P121-P124*P125-P122</f>
-        <v>2378.667547907201</v>
+        <f>P134*$G21</f>
+        <v>167100.11655304718</v>
       </c>
       <c r="Q147" s="4">
-        <f>Q121-P124*Q125-Q122+Q54</f>
-        <v>4283.8917473166084</v>
+        <f>(Q134+P133)*$H21</f>
+        <v>409363.40995006717</v>
       </c>
       <c r="S147" s="4">
-        <f>S121-S124*S125-S122</f>
-        <v>3051.2552091325515</v>
+        <f>S134*$G21</f>
+        <v>203079.06938815225</v>
       </c>
       <c r="T147" s="4">
-        <f>T121-S124*T125-T122+T54</f>
-        <v>800.37687838970226</v>
+        <f>(T134+S133)*$H21</f>
+        <v>578520.65679181518</v>
       </c>
       <c r="V147" s="4">
-        <f>V121-V124*V125-V122</f>
-        <v>2626.3244695064477</v>
+        <f>V134*$G21</f>
+        <v>137249.17897628012</v>
       </c>
       <c r="W147" s="4">
-        <f>W121-V124*W125-W122+W54</f>
-        <v>1859.8672306260451</v>
+        <f>(W134+V133)*$H21</f>
+        <v>473067.73849789845</v>
       </c>
       <c r="Y147" s="4">
-        <f>Y121-Y124*Y125-Y122</f>
-        <v>2329.2475988760525</v>
+        <f>Y134*$G21</f>
+        <v>15741.643343915621</v>
       </c>
       <c r="Z147" s="4">
-        <f>Z121-Y124*Z125-Z122+Z54</f>
-        <v>1888.8340116135732</v>
+        <f>(Z134+Y133)*$H21</f>
+        <v>84041.519752330307</v>
       </c>
       <c r="AA147" s="38" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="AB147" s="42" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="AC147" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="148" spans="2:30" ht="17" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="148" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B148" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C148" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G148" s="4">
-        <f>MAX((G121 - G122)*$G21-G16*G9,0)</f>
-        <v>2128.25</v>
+        <f>G122-G125*G126-G123</f>
+        <v>2175</v>
       </c>
       <c r="H148" s="4">
-        <f>MAX((H121-H122+H54)*$H21-H16*H9,0)</f>
-        <v>2058</v>
+        <f>H122-G125*H126-H123+H54</f>
+        <v>2700</v>
       </c>
       <c r="J148" s="4">
-        <f>MAX((J121 - J122)*$G21-J16*J9,0)</f>
-        <v>2440.2984140400481</v>
+        <f>J122-J125*J126-J123</f>
+        <v>2499.4278140400493</v>
       </c>
       <c r="K148" s="4">
-        <f>MAX((K121-K122+K54)*$H21-K16*K9,0)</f>
-        <v>2134.2054714382775</v>
+        <f>K122-J125*K126-K123+K54</f>
+        <v>2809.4177657259334</v>
       </c>
       <c r="M148" s="4">
-        <f>MAX((M121 - M122)*$G21-M16*M9,0)</f>
-        <v>2096.1250989321488</v>
+        <f>M122-M125*M126-M123</f>
+        <v>2152.52429893215</v>
       </c>
       <c r="N148" s="4">
-        <f>MAX((N121-N122+N54)*$H21-N16*N9,0)</f>
-        <v>1700.4848663813059</v>
+        <f>N122-M125*N126-N123+N54</f>
+        <v>2252.8263196575672</v>
       </c>
       <c r="P148" s="4">
-        <f>MAX((P121 - P122)*$G21-P16*P9,0)</f>
-        <v>2317.1445479071999</v>
+        <f>P122-P125*P126-P123</f>
+        <v>2378.667547907201</v>
       </c>
       <c r="Q148" s="4">
-        <f>MAX((Q121-Q122+Q54)*$H21-Q16*Q9,0)</f>
-        <v>3204.9561894305079</v>
+        <f>Q122-P125*Q126-Q123+Q54</f>
+        <v>4283.8917476244524</v>
       </c>
       <c r="S148" s="4">
-        <f>MAX((S121 - S122)*$G21-S16*S9,0)</f>
-        <v>2954.0152091325508</v>
+        <f>S122-S125*S126-S123</f>
+        <v>3051.2552092196693</v>
       </c>
       <c r="T148" s="4">
-        <f>MAX((T121-T122+T54)*$H21-T16*T9,0)</f>
-        <v>591.35193199141838</v>
+        <f>T122-S125*T126-T123+T54</f>
+        <v>800.37687887966456</v>
       </c>
       <c r="V148" s="4">
-        <f>MAX((V121 - V122)*$G21-V16*V9,0)</f>
-        <v>2551.1878695064484</v>
+        <f>V122-V125*V126-V123</f>
+        <v>2626.324470611311</v>
       </c>
       <c r="W148" s="4">
-        <f>MAX((W121-W122+W54)*$H21-W16*W9,0)</f>
-        <v>1328.129358855037</v>
+        <f>W122-V125*W126-W123+W54</f>
+        <v>1859.8672358907961</v>
       </c>
       <c r="Y148" s="4">
-        <f>MAX((Y121 - Y122)*$G21-Y16*Y9,0)</f>
-        <v>2235.7849988760527</v>
+        <f>Y122-Y125*Y126-Y123</f>
+        <v>2329.2475987972985</v>
       </c>
       <c r="Z148" s="4">
-        <f>MAX((Z121-Z122+Z54)*$H21-Z16*Z9,0)</f>
-        <v>1373.5803430113106</v>
+        <f>Z122-Y125*Z126-Z123+Z54</f>
+        <v>1888.8340225328548</v>
       </c>
       <c r="AA148" s="38" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="AB148" s="42" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="AC148" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="149" spans="2:30" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="149" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
-        <v>287</v>
+        <v>177</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>163</v>
       </c>
+      <c r="F149" s="10" t="s">
+        <v>167</v>
+      </c>
       <c r="G149" s="4">
-        <f>J111*J7*(1+$G21)</f>
+        <f>MAX((G122 - G123)*$G21-G16*G9,0)</f>
+        <v>2128.25</v>
+      </c>
+      <c r="H149" s="4">
+        <f>MAX((H122-H123+H54)*$H21-H16*H9,0)</f>
+        <v>2058</v>
+      </c>
+      <c r="J149" s="4">
+        <f>MAX((J122 - J123)*$G21-J16*J9,0)</f>
+        <v>2440.2984140400481</v>
+      </c>
+      <c r="K149" s="4">
+        <f>MAX((K122-K123+K54)*$H21-K16*K9,0)</f>
+        <v>2134.2054714382775</v>
+      </c>
+      <c r="M149" s="4">
+        <f>MAX((M122 - M123)*$G21-M16*M9,0)</f>
+        <v>2096.1250989321488</v>
+      </c>
+      <c r="N149" s="4">
+        <f>MAX((N122-N123+N54)*$H21-N16*N9,0)</f>
+        <v>1700.4848663813059</v>
+      </c>
+      <c r="P149" s="4">
+        <f>MAX((P122 - P123)*$G21-P16*P9,0)</f>
+        <v>2317.1445479071999</v>
+      </c>
+      <c r="Q149" s="4">
+        <f>MAX((Q122-Q123+Q54)*$H21-Q16*Q9,0)</f>
+        <v>3204.9561896870446</v>
+      </c>
+      <c r="S149" s="4">
+        <f>MAX((S122 - S123)*$G21-S16*S9,0)</f>
+        <v>2954.0152092196686</v>
+      </c>
+      <c r="T149" s="4">
+        <f>MAX((T122-T123+T54)*$H21-T16*T9,0)</f>
+        <v>591.35193239972011</v>
+      </c>
+      <c r="V149" s="4">
+        <f>MAX((V122 - V123)*$G21-V16*V9,0)</f>
+        <v>2551.1878706113116</v>
+      </c>
+      <c r="W149" s="4">
+        <f>MAX((W122-W123+W54)*$H21-W16*W9,0)</f>
+        <v>1328.1293632423296</v>
+      </c>
+      <c r="Y149" s="4">
+        <f>MAX((Y122 - Y123)*$G21-Y16*Y9,0)</f>
+        <v>2235.7849987972986</v>
+      </c>
+      <c r="Z149" s="4">
+        <f>MAX((Z122-Z123+Z54)*$H21-Z16*Z9,0)</f>
+        <v>1373.5803521107118</v>
+      </c>
+      <c r="AA149" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="AB149" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC149" s="43" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="150" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B150" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="C150" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="G150" s="4">
+        <f>J112*J7*(1+$G21)</f>
         <v>19480.5</v>
       </c>
-      <c r="H149" s="4">
-        <f>(K111*K7+SUMPRODUCT(H38:H41,H86:H89))*(1+$H21)</f>
+      <c r="H150" s="4">
+        <f>(K112*K7+SUMPRODUCT(H38:H41,H86:H89))*(1+$H21)</f>
         <v>287385</v>
       </c>
-      <c r="J149" s="4">
-        <f>M111*M7*(1+$G21)</f>
+      <c r="J150" s="4">
+        <f>M112*M7*(1+$G21)</f>
         <v>19456.32</v>
       </c>
-      <c r="K149" s="4">
-        <f>(N111*N7+SUMPRODUCT(K38:K41,K86:K89))*(1+$H21)</f>
+      <c r="K150" s="4">
+        <f>(N112*N7+SUMPRODUCT(K38:K41,K86:K89))*(1+$H21)</f>
         <v>287259.5625</v>
       </c>
-      <c r="M149" s="4">
-        <f>P111*P7*(1+$G21)</f>
+      <c r="M150" s="4">
+        <f>P112*P7*(1+$G21)</f>
         <v>19433.7</v>
       </c>
-      <c r="N149" s="4">
-        <f>(Q111*Q7+SUMPRODUCT(N38:N41,N86:N89))*(1+$H21)</f>
+      <c r="N150" s="4">
+        <f>(Q112*Q7+SUMPRODUCT(N38:N41,N86:N89))*(1+$H21)</f>
         <v>287156.71250000002</v>
       </c>
-      <c r="P149" s="4">
-        <f>S111*S7*(1+$G21)</f>
+      <c r="P150" s="4">
+        <f>S112*S7*(1+$G21)</f>
         <v>19406.400000000001</v>
       </c>
-      <c r="Q149" s="4">
-        <f>(T111*T7+SUMPRODUCT(Q38:Q41,Q86:Q89))*(1+$H21)</f>
+      <c r="Q150" s="4">
+        <f>(T112*T7+SUMPRODUCT(Q38:Q41,Q86:Q89))*(1+$H21)</f>
         <v>286948.5</v>
       </c>
-      <c r="S149" s="4">
-        <f>V111*V7*(1+$G21)</f>
+      <c r="S150" s="4">
+        <f>V112*V7*(1+$G21)</f>
         <v>19367.400000000001</v>
       </c>
-      <c r="T149" s="4">
-        <f>(W111*W7+SUMPRODUCT(T38:T41,T86:T89))*(1+$H21)</f>
+      <c r="T150" s="4">
+        <f>(W112*W7+SUMPRODUCT(T38:T41,T86:T89))*(1+$H21)</f>
         <v>286924.28750000003</v>
       </c>
-      <c r="V149" s="4">
-        <f>Y111*Y7*(1+$G21)</f>
-        <v>16645.359712099693</v>
-      </c>
-      <c r="W149" s="4">
-        <f>(Z111*Z7+SUMPRODUCT(W38:W41,W86:W89))*(1+$H21)</f>
+      <c r="V150" s="4">
+        <f>Y112*Y7*(1+$G21)</f>
+        <v>16645.359726367005</v>
+      </c>
+      <c r="W150" s="4">
+        <f>(Z112*Z7+SUMPRODUCT(W38:W41,W86:W89))*(1+$H21)</f>
         <v>286838.73750000005</v>
       </c>
-      <c r="Y149" s="4" t="e">
-        <f>AB111*AB7*(1+$G21)</f>
+      <c r="Y150" s="4" t="e">
+        <f>AB112*AB7*(1+$G21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z149" s="4" t="e">
-        <f>(AC111*AC7+SUMPRODUCT(Z38:Z41,Z86:Z89))*(1+$H21)</f>
+      <c r="Z150" s="4" t="e">
+        <f>(AC112*AC7+SUMPRODUCT(Z38:Z41,Z86:Z89))*(1+$H21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA149" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="AB149" s="42" t="s">
-        <v>418</v>
-      </c>
-      <c r="AC149" s="43" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="150" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AB150" s="42"/>
-      <c r="AC150" s="43"/>
-    </row>
-    <row r="151" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AA150" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB150" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC150" s="43" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="151" spans="2:29" x14ac:dyDescent="0.2">
       <c r="AB151" s="42"/>
       <c r="AC151" s="43"/>
     </row>
-    <row r="152" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B152" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="G152" s="4">
-        <f>G147+G122</f>
-        <v>2425</v>
-      </c>
-      <c r="H152" s="4">
-        <f>H147+H122</f>
-        <v>3700</v>
-      </c>
-      <c r="J152" s="4">
-        <f>J147+J122</f>
-        <v>2815.6278140400491</v>
-      </c>
-      <c r="K152" s="4">
-        <f>K147+K122</f>
-        <v>3887.4177657259334</v>
-      </c>
-      <c r="M152" s="4">
-        <f>M147+M122</f>
-        <v>2454.1242989321499</v>
-      </c>
-      <c r="N152" s="4">
-        <f>N147+N122</f>
-        <v>3174.026319657567</v>
-      </c>
-      <c r="P152" s="4">
-        <f>P147+P122</f>
-        <v>2707.667547907201</v>
-      </c>
-      <c r="Q152" s="4">
-        <f>Q147+Q122</f>
-        <v>6184.6917473166086</v>
-      </c>
-      <c r="S152" s="4">
-        <f>S147+S122</f>
-        <v>3571.2552091325515</v>
-      </c>
-      <c r="T152" s="4">
-        <f>T147+T122</f>
-        <v>1194.2768783897022</v>
-      </c>
-      <c r="V152" s="4">
-        <f>V147+V122</f>
-        <v>3028.1244695064479</v>
-      </c>
-      <c r="W152" s="4">
-        <f>W147+W122</f>
-        <v>3014.8672306260451</v>
-      </c>
-      <c r="Y152" s="4">
-        <f>Y147+Y122</f>
-        <v>2829.0475988760527</v>
-      </c>
-      <c r="Z152" s="4">
-        <f>Z147+Z122</f>
-        <v>2932.8340116135732</v>
-      </c>
+    <row r="152" spans="2:29" x14ac:dyDescent="0.2">
       <c r="AB152" s="42"/>
       <c r="AC152" s="43"/>
     </row>
-    <row r="153" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B153" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="G153" s="4">
+        <f>G148+G123</f>
+        <v>2425</v>
+      </c>
+      <c r="H153" s="4">
+        <f>H148+H123</f>
+        <v>3700</v>
+      </c>
+      <c r="J153" s="4">
+        <f>J148+J123</f>
+        <v>2815.6278140400491</v>
+      </c>
+      <c r="K153" s="4">
+        <f>K148+K123</f>
+        <v>3887.4177657259334</v>
+      </c>
+      <c r="M153" s="4">
+        <f>M148+M123</f>
+        <v>2454.1242989321499</v>
+      </c>
+      <c r="N153" s="4">
+        <f>N148+N123</f>
+        <v>3174.026319657567</v>
+      </c>
+      <c r="P153" s="4">
+        <f>P148+P123</f>
+        <v>2707.667547907201</v>
+      </c>
+      <c r="Q153" s="4">
+        <f>Q148+Q123</f>
+        <v>6184.6917476244525</v>
+      </c>
+      <c r="S153" s="4">
+        <f>S148+S123</f>
+        <v>3571.2552092196693</v>
+      </c>
+      <c r="T153" s="4">
+        <f>T148+T123</f>
+        <v>1194.2768788796645</v>
+      </c>
+      <c r="V153" s="4">
+        <f>V148+V123</f>
+        <v>3028.1244706113112</v>
+      </c>
+      <c r="W153" s="4">
+        <f>W148+W123</f>
+        <v>3014.8672358907961</v>
+      </c>
+      <c r="Y153" s="4">
+        <f>Y148+Y123</f>
+        <v>2829.0475987972986</v>
+      </c>
+      <c r="Z153" s="4">
+        <f>Z148+Z123</f>
+        <v>2932.8340225328548</v>
+      </c>
       <c r="AB153" s="42"/>
       <c r="AC153" s="43"/>
     </row>
-    <row r="154" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B154" s="38" t="s">
+    <row r="154" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AB154" s="42"/>
+      <c r="AC154" s="43"/>
+    </row>
+    <row r="155" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B155" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="C154" s="33" t="s">
+      <c r="C155" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="G154" s="4">
-        <f>G124+G133+H133+G132</f>
+      <c r="G155" s="4">
+        <f>G125+G134+H134+G133</f>
         <v>2000000.0000000002</v>
       </c>
-      <c r="J154" s="4">
-        <f>J124+J133+K133</f>
+      <c r="J155" s="4">
+        <f>J125+J134+K134</f>
         <v>2050000</v>
       </c>
-      <c r="M154" s="4">
-        <f>M124+M133+N133</f>
+      <c r="M155" s="4">
+        <f>M125+M134+N134</f>
         <v>2110000</v>
       </c>
-      <c r="P154" s="4">
-        <f>P124+P133+Q133</f>
+      <c r="P155" s="4">
+        <f>P125+P134+Q134</f>
         <v>2210000</v>
       </c>
-      <c r="S154" s="4">
-        <f>S124+S133+T133</f>
+      <c r="S155" s="4">
+        <f>S125+S134+T134</f>
         <v>3000000</v>
       </c>
-      <c r="V154" s="4">
-        <f>V124+V133+W133</f>
-        <v>2360235.9498395934</v>
-      </c>
-      <c r="Y154" s="4">
-        <f>Y124+Y133+Z133</f>
-        <v>398480.35616514197</v>
-      </c>
-      <c r="AA154" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="AB154" s="42" t="s">
-        <v>446</v>
-      </c>
-      <c r="AC154" s="43" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="155" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="G155" s="4">
-        <f>G154/G33</f>
+      <c r="V155" s="4">
+        <f>V125+V134+W134</f>
+        <v>2360235.9978943658</v>
+      </c>
+      <c r="Y155" s="4">
+        <f>Y125+Y134+Z134</f>
+        <v>398480.41393881035</v>
+      </c>
+      <c r="AA155" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="AB155" s="42" t="s">
+        <v>422</v>
+      </c>
+      <c r="AC155" s="43" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="156" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="G156" s="4">
+        <f>G155/G33</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="J155" s="4">
-        <f>J154/J33</f>
+      <c r="J156" s="4">
+        <f>J155/J33</f>
         <v>1</v>
       </c>
-      <c r="M155" s="4">
-        <f>M154/M33</f>
+      <c r="M156" s="4">
+        <f>M155/M33</f>
         <v>1</v>
       </c>
-      <c r="P155" s="4">
-        <f>P154/P33</f>
+      <c r="P156" s="4">
+        <f>P155/P33</f>
         <v>1</v>
       </c>
-      <c r="S155" s="4">
-        <f>S154/S33</f>
+      <c r="S156" s="4">
+        <f>S155/S33</f>
         <v>1</v>
       </c>
-      <c r="V155" s="4">
-        <f>V154/V33</f>
-        <v>9.4409437993583742E-2</v>
-      </c>
-      <c r="Y155" s="4">
-        <f>Y154/Y33</f>
-        <v>0.15812712546235794</v>
-      </c>
-      <c r="AA155" s="38"/>
-      <c r="AB155" s="42"/>
-      <c r="AC155" s="43"/>
-    </row>
-    <row r="156" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B156" s="38" t="s">
-        <v>390</v>
-      </c>
-      <c r="C156" s="31" t="s">
+      <c r="V156" s="4">
+        <f>V155/V33</f>
+        <v>9.4409439915774634E-2</v>
+      </c>
+      <c r="Y156" s="4">
+        <f>Y155/Y33</f>
+        <v>0.15812714838841679</v>
+      </c>
+      <c r="AA156" s="38"/>
+      <c r="AB156" s="42"/>
+      <c r="AC156" s="43"/>
+    </row>
+    <row r="157" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B157" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="C157" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="AA156" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="AB156" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="AC156" s="43" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="157" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B157" s="38"/>
-      <c r="AA157" s="38"/>
-      <c r="AB157" s="42"/>
-      <c r="AC157" s="43"/>
-    </row>
-    <row r="158" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AA157" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="AB157" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="AC157" s="43" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="158" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B158" s="38"/>
       <c r="AA158" s="38"/>
       <c r="AB158" s="42"/>
       <c r="AC158" s="43"/>
     </row>
-    <row r="159" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:29" x14ac:dyDescent="0.2">
       <c r="AA159" s="38"/>
       <c r="AB159" s="42"/>
       <c r="AC159" s="43"/>
     </row>
-    <row r="160" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:29" x14ac:dyDescent="0.2">
       <c r="AA160" s="38"/>
       <c r="AB160" s="42"/>
       <c r="AC160" s="43"/>
-      <c r="AD160">
-        <v>20</v>
-      </c>
     </row>
     <row r="161" spans="27:30" x14ac:dyDescent="0.2">
       <c r="AA161" s="38"/>
@@ -14404,11 +14471,19 @@
       <c r="AA163" s="38"/>
       <c r="AB163" s="42"/>
       <c r="AC163" s="43"/>
+      <c r="AD163">
+        <v>20</v>
+      </c>
     </row>
     <row r="164" spans="27:30" x14ac:dyDescent="0.2">
       <c r="AA164" s="38"/>
       <c r="AB164" s="42"/>
       <c r="AC164" s="43"/>
+    </row>
+    <row r="165" spans="27:30" x14ac:dyDescent="0.2">
+      <c r="AA165" s="38"/>
+      <c r="AB165" s="42"/>
+      <c r="AC165" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -14435,15 +14510,15 @@
     <mergeCell ref="B62:B65"/>
     <mergeCell ref="B56:B59"/>
     <mergeCell ref="C56:C59"/>
-    <mergeCell ref="B101:B104"/>
-    <mergeCell ref="C101:C104"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="C102:C105"/>
     <mergeCell ref="B49:B52"/>
     <mergeCell ref="C49:C52"/>
     <mergeCell ref="E49:E52"/>
     <mergeCell ref="C79:C83"/>
     <mergeCell ref="C86:C89"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="C97:C100"/>
     <mergeCell ref="B91:B94"/>
     <mergeCell ref="C91:C94"/>
     <mergeCell ref="B73:B76"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A037414-49F1-A147-8E76-3E5546D626CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29F1DFB-7242-B94B-ADE9-ABFF08AE6623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14800" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="5380" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="482">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -892,9 +892,6 @@
     <t>\hat{\alpha}(t)</t>
   </si>
   <si>
-    <t>\gamma</t>
-  </si>
-  <si>
     <t>arr_biomass_c_average_bg_stock_in_conversion_targets</t>
   </si>
   <si>
@@ -931,12 +928,6 @@
     <t xml:space="preserve">Fractional threshold for stock loss (compared to undisturbed forest levels) below which sequestration declines. </t>
   </si>
   <si>
-    <t xml:space="preserve">Initial steady-state storage in each class. Used in integration targets for NPP curve and as initial carbon storage condition. </t>
-  </si>
-  <si>
-    <t>Ratio of below-ground carbon stock to above-ground carbon stock in each forest type.</t>
-  </si>
-  <si>
     <t>Area of young forest that would be converted away assuming no protection (counterfactual).</t>
   </si>
   <si>
@@ -949,9 +940,6 @@
     <t>Fraction of biomass in each forest type that's converted to another land use class that is available for use to satisfy fuelwood and harvested wood product demands.</t>
   </si>
   <si>
-    <t>In healthy forest, available stock factor per unit area. Used to determine when average stocks fall below thresholds.</t>
-  </si>
-  <si>
     <t>Total area of forest protected.</t>
   </si>
   <si>
@@ -1090,9 +1078,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>\overline{B_{avail}}</t>
-  </si>
-  <si>
     <t>b</t>
   </si>
   <si>
@@ -1174,9 +1159,6 @@
     <t>Matrix ($n_T \times 2$) soring average below ground stock contained In land use classes that forests transition into; used to estimate below-ground conversion losses of stock.</t>
   </si>
   <si>
-    <t>Matrix ($n_T \times 2$) storing avrage biomass stock per unit area required to be considered forest.</t>
-  </si>
-  <si>
     <t>Matrix ($n_T \times 2$) storing above ground biomass stock left from start of simulation if untouched (without degradation).</t>
   </si>
   <si>
@@ -1354,9 +1336,6 @@
     <t>vec_young_sf_curve_specification (T)</t>
   </si>
   <si>
-    <t>\tau</t>
-  </si>
-  <si>
     <t>z:\tau</t>
   </si>
   <si>
@@ -1487,6 +1466,27 @@
   </si>
   <si>
     <t>\overline{M}_0(t, v)</t>
+  </si>
+  <si>
+    <t>\tau(v)</t>
+  </si>
+  <si>
+    <t>Vector (dim $2$) storing avrage biomass stock per unit area required to be considered forest.</t>
+  </si>
+  <si>
+    <t>\overline{B_{avail}}(v)</t>
+  </si>
+  <si>
+    <t>\gamma(v)</t>
+  </si>
+  <si>
+    <t>Vector (dim $2$) storing available stock factor per unit area in healthy forest. Used to determine when average stocks fall below thresholds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector (dim $2$) storing initial steady-state storage in each class. Used in integration targets for NPP curve and as initial carbon storage condition. </t>
+  </si>
+  <si>
+    <t>Vector (dim $2$) storing ratio of below-ground carbon stock to above-ground carbon stock in each forest type.</t>
   </si>
 </sst>
 </file>
@@ -7167,7 +7167,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7211,13 +7211,13 @@
       </c>
       <c r="Z5" s="55"/>
       <c r="AA5" s="24" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AB5" s="40" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AD5" s="36" t="s">
         <v>230</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="7" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
@@ -7381,13 +7381,13 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="AB7" s="42" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AC7" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
@@ -7482,13 +7482,13 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="AB8" s="42" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AC8" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="9" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>222</v>
@@ -7569,13 +7569,13 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AB9" s="42" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AC9" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="10" spans="1:41" ht="85" x14ac:dyDescent="0.2">
       <c r="A10" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>221</v>
@@ -7645,10 +7645,10 @@
         <v>280</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AC10" s="43" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7663,7 +7663,7 @@
     </row>
     <row r="11" spans="1:41" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>219</v>
@@ -7706,10 +7706,10 @@
         <v>281</v>
       </c>
       <c r="AB11" s="42" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AC11" s="43" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="12" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>220</v>
@@ -7760,10 +7760,10 @@
         <v>279</v>
       </c>
       <c r="AB12" s="42" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE12" s="19">
         <v>0.36</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="13" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>158</v>
@@ -7846,13 +7846,13 @@
         <v>249244</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AB13" s="42" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AC13" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE13" s="19"/>
       <c r="AF13" s="19"/>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="14" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>223</v>
@@ -7893,13 +7893,13 @@
         <v>0.7</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AB14" s="42" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AC14" s="43" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AE14" s="19">
         <v>0.6</v>
@@ -7914,7 +7914,7 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>244</v>
@@ -7971,13 +7971,13 @@
         <v>9</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="AB15" s="42" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AC15" s="43" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
@@ -7985,10 +7985,10 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>162</v>
@@ -8050,13 +8050,13 @@
         <v>1.728</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="AB16" s="42" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AC16" s="43" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -8064,10 +8064,10 @@
     </row>
     <row r="17" spans="1:33" ht="136" x14ac:dyDescent="0.2">
       <c r="A17" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
@@ -8082,13 +8082,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AB17" s="42" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AC17" s="43" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AE17" s="19">
         <v>1.8</v>
@@ -8103,10 +8103,10 @@
     </row>
     <row r="18" spans="1:33" ht="102" x14ac:dyDescent="0.2">
       <c r="A18" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
@@ -8124,13 +8124,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AB18" s="42" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AC18" s="43" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AE18" s="19">
         <v>3</v>
@@ -8145,7 +8145,7 @@
     </row>
     <row r="19" spans="1:33" ht="136" x14ac:dyDescent="0.2">
       <c r="A19" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>224</v>
@@ -8164,10 +8164,10 @@
         <v>282</v>
       </c>
       <c r="AB19" s="42" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AC19" s="43" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AE19" s="19">
         <v>6</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="20" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>226</v>
@@ -8200,13 +8200,13 @@
         <v>100</v>
       </c>
       <c r="AA20" s="38" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="AB20" s="42" t="s">
-        <v>296</v>
+        <v>480</v>
       </c>
       <c r="AC20" s="43" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AE20" s="19">
         <v>10</v>
@@ -8221,7 +8221,7 @@
     </row>
     <row r="21" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>228</v>
@@ -8239,13 +8239,13 @@
         <v>0.25</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>283</v>
+        <v>478</v>
       </c>
       <c r="AB21" s="42" t="s">
-        <v>297</v>
+        <v>481</v>
       </c>
       <c r="AC21" s="44" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="22" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>275</v>
@@ -8273,13 +8273,13 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="AB22" s="42" t="s">
-        <v>377</v>
+        <v>476</v>
       </c>
       <c r="AC22" s="43" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="AE22" s="19">
         <v>12</v>
@@ -8294,7 +8294,7 @@
     </row>
     <row r="23" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>227</v>
@@ -8314,13 +8314,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>349</v>
+        <v>477</v>
       </c>
       <c r="AB23" s="42" t="s">
-        <v>302</v>
+        <v>479</v>
       </c>
       <c r="AC23" s="43" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AE23" s="19">
         <v>13.5</v>
@@ -8349,7 +8349,7 @@
     </row>
     <row r="25" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B25" s="38" t="s">
         <v>159</v>
@@ -8403,13 +8403,13 @@
         <v>49500</v>
       </c>
       <c r="AA25" s="38" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AB25" s="42" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AC25" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE25" s="19">
         <v>10</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="26" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>274</v>
@@ -8464,13 +8464,13 @@
         <v>0</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AB26" s="42" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AC26" s="43" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AE26" s="19">
         <v>6</v>
@@ -8485,7 +8485,7 @@
     </row>
     <row r="27" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>160</v>
@@ -8553,13 +8553,13 @@
         <v>49500</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="AB27" s="42" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AC27" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AE27" s="19">
         <v>3</v>
@@ -8605,7 +8605,7 @@
     </row>
     <row r="29" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B29" s="38" t="s">
         <v>273</v>
@@ -8626,18 +8626,18 @@
         <v>0.92</v>
       </c>
       <c r="AA29" s="38" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AB29" s="42" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AC29" s="43" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>229</v>
@@ -8662,13 +8662,13 @@
         <v>2E-3</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AB30" s="42" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AC30" s="43" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -8699,7 +8699,7 @@
     </row>
     <row r="33" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B33" s="38" t="s">
         <v>168</v>
@@ -8732,13 +8732,13 @@
         <v>2520000</v>
       </c>
       <c r="AA33" s="38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AB33" s="42" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AC33" s="43" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.2">
@@ -8849,10 +8849,10 @@
     </row>
     <row r="38" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C38" s="50" t="s">
         <v>174</v>
@@ -8940,21 +8940,21 @@
         <v>85</v>
       </c>
       <c r="AA38" s="38" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AB38" s="42" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AC38" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C39" s="50"/>
       <c r="F39" s="14" t="s">
@@ -9039,21 +9039,21 @@
         <v>80</v>
       </c>
       <c r="AA39" s="38" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AB39" s="42" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AC39" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C40" s="50"/>
       <c r="F40" s="14" t="s">
@@ -9137,13 +9137,13 @@
         <v>92</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AB40" s="42" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AC40" s="43" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9241,7 +9241,7 @@
     </row>
     <row r="43" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B43" s="51" t="s">
         <v>189</v>
@@ -9280,13 +9280,13 @@
         <v>0</v>
       </c>
       <c r="AA43" s="38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AB43" s="42" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AC43" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -9402,7 +9402,7 @@
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B47" s="38" t="s">
         <v>190</v>
@@ -9440,13 +9440,13 @@
         <v>0</v>
       </c>
       <c r="AA47" s="38" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AB47" s="42" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AC47" s="43" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="49" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B49" s="51" t="s">
         <v>258</v>
@@ -9501,13 +9501,13 @@
         <v>0</v>
       </c>
       <c r="AA49" s="38" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AB49" s="42" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AC49" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="51" x14ac:dyDescent="0.2">
@@ -9629,7 +9629,7 @@
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B53" s="38" t="s">
         <v>259</v>
@@ -9667,18 +9667,18 @@
         <v>0</v>
       </c>
       <c r="AA53" s="38" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AB53" s="42" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AC53" s="43" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B54" s="38" t="s">
         <v>261</v>
@@ -9714,13 +9714,13 @@
         <v>0</v>
       </c>
       <c r="AA54" s="38" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AB54" s="42" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="AC54" s="43" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
@@ -9730,7 +9730,7 @@
     </row>
     <row r="56" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A56" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B56" s="51" t="s">
         <v>191</v>
@@ -9770,13 +9770,13 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB56" s="42" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AC56" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -9895,7 +9895,7 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B60" s="38" t="s">
         <v>192</v>
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="AA60" s="38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB60" s="42" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="AC60" s="43" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
@@ -9949,7 +9949,7 @@
     </row>
     <row r="62" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A62" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B62" s="51" t="s">
         <v>178</v>
@@ -9989,13 +9989,13 @@
         <v>0.6</v>
       </c>
       <c r="AA62" s="38" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AB62" s="42" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AC62" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -10105,10 +10105,10 @@
     </row>
     <row r="66" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="B66" s="38" t="s">
         <v>430</v>
-      </c>
-      <c r="B66" s="38" t="s">
-        <v>436</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>162</v>
@@ -10117,13 +10117,13 @@
         <v>49</v>
       </c>
       <c r="AA66" s="38" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="AB66" s="42" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AC66" s="43" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.2">
@@ -10133,7 +10133,7 @@
     </row>
     <row r="68" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A68" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B68" s="51" t="s">
         <v>233</v>
@@ -10173,13 +10173,13 @@
         <v>113.71737449773646</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AB68" s="42" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AC68" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -10286,7 +10286,7 @@
     </row>
     <row r="73" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A73" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B73" s="51" t="s">
         <v>231</v>
@@ -10325,13 +10325,13 @@
         <v>0</v>
       </c>
       <c r="AA73" s="38" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AB73" s="42" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="AC73" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="74" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -10451,7 +10451,7 @@
     </row>
     <row r="77" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A77" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>232</v>
@@ -10491,13 +10491,13 @@
         <v>0</v>
       </c>
       <c r="AA77" s="45" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="AB77" s="42" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AC77" s="43" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AF77" t="s">
         <v>106</v>
@@ -10517,10 +10517,10 @@
     </row>
     <row r="79" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C79" s="50" t="s">
         <v>174</v>
@@ -10550,13 +10550,13 @@
         <v>0</v>
       </c>
       <c r="AA79" s="38" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AB79" s="42" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="AC79" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AD79" t="s">
         <v>86</v>
@@ -10564,10 +10564,10 @@
     </row>
     <row r="80" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A80" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C80" s="50"/>
       <c r="F80" s="14" t="s">
@@ -10630,13 +10630,13 @@
         <v>0</v>
       </c>
       <c r="AA80" s="38" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="AB80" s="42" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AC80" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -10879,10 +10879,10 @@
     </row>
     <row r="86" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A86" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C86" s="50" t="s">
         <v>174</v>
@@ -10943,21 +10943,21 @@
         <v>0.6</v>
       </c>
       <c r="AA86" s="37" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AB86" s="42" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AC86" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A87" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C87" s="50"/>
       <c r="F87" s="14" t="s">
@@ -11016,13 +11016,13 @@
         <v>0.36</v>
       </c>
       <c r="AA87" s="37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AB87" s="42" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AC87" s="43" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -11156,7 +11156,7 @@
     </row>
     <row r="91" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A91" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B91" s="49" t="s">
         <v>202</v>
@@ -11196,13 +11196,13 @@
         <v>9.8621113109027395E-2</v>
       </c>
       <c r="AA91" s="37" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AB91" s="42" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AC91" s="43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="51" x14ac:dyDescent="0.2">
@@ -11321,10 +11321,10 @@
     </row>
     <row r="95" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A95" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B95" s="37" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C95" s="28"/>
       <c r="F95" s="14"/>
@@ -11357,13 +11357,13 @@
         <v>0.17633270956878355</v>
       </c>
       <c r="AA95" s="37" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AB95" s="42" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AC95" s="43" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.2">
@@ -11373,7 +11373,7 @@
     </row>
     <row r="97" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A97" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B97" s="49" t="s">
         <v>207</v>
@@ -11413,13 +11413,13 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA97" s="38" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AB97" s="42" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AC97" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -11544,7 +11544,7 @@
     </row>
     <row r="102" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B102" s="49" t="s">
         <v>208</v>
@@ -11585,13 +11585,13 @@
         <v>28.429343624434111</v>
       </c>
       <c r="AA102" s="38" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AB102" s="42" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AC102" s="43" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="103" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -11814,7 +11814,7 @@
     </row>
     <row r="110" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A110" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B110" s="38" t="s">
         <v>235</v>
@@ -11882,18 +11882,18 @@
         <v>24936000</v>
       </c>
       <c r="AA110" s="38" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="AB110" s="42" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="AC110" s="43" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="111" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A111" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B111" s="38" t="s">
         <v>181</v>
@@ -11959,18 +11959,18 @@
         <v>1</v>
       </c>
       <c r="AA111" s="38" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="AB111" s="42" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AC111" s="43" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="112" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="61" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B112" s="38" t="s">
         <v>182</v>
@@ -12038,16 +12038,19 @@
         <v>0.92</v>
       </c>
       <c r="AA112" s="38" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="AB112" s="42" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AC112" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="113" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="113" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A113" s="61" t="s">
+        <v>424</v>
+      </c>
       <c r="B113" s="38" t="s">
         <v>236</v>
       </c>
@@ -12114,16 +12117,19 @@
         <v>15778712.754563004</v>
       </c>
       <c r="AA113" s="38" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="AB113" s="42" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AC113" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="114" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="114" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A114" s="61" t="s">
+        <v>424</v>
+      </c>
       <c r="B114" s="38" t="s">
         <v>239</v>
       </c>
@@ -12190,16 +12196,19 @@
         <v>63.276839727955583</v>
       </c>
       <c r="AA114" s="38" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="AB114" s="42" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="AC114" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="115" spans="2:29" ht="68" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="115" spans="1:29" ht="68" x14ac:dyDescent="0.2">
+      <c r="A115" s="61" t="s">
+        <v>424</v>
+      </c>
       <c r="B115" s="38" t="s">
         <v>277</v>
       </c>
@@ -12266,21 +12275,21 @@
         <v>25.475946727955581</v>
       </c>
       <c r="AA115" s="38" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="AB115" s="46" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AC115" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="116" spans="2:29" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F116" s="13"/>
       <c r="AB116" s="42"/>
       <c r="AC116" s="43"/>
     </row>
-    <row r="117" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="F117" s="11" t="s">
         <v>58</v>
       </c>
@@ -12301,7 +12310,7 @@
       <c r="AB117" s="42"/>
       <c r="AC117" s="43"/>
     </row>
-    <row r="118" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B118" s="38" t="s">
         <v>241</v>
       </c>
@@ -12371,7 +12380,7 @@
       <c r="AB118" s="42"/>
       <c r="AC118" s="43"/>
     </row>
-    <row r="119" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B119" s="38" t="s">
         <v>240</v>
       </c>
@@ -12410,16 +12419,16 @@
         <v>215.49749504124878</v>
       </c>
       <c r="AA119" s="38" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AB119" s="42" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="AC119" s="43" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="120" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B120" s="38" t="s">
         <v>237</v>
       </c>
@@ -12486,16 +12495,16 @@
         <v>15778928.252058046</v>
       </c>
       <c r="AA120" s="38" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="AB120" s="42" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="AC120" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="121" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B121" s="38" t="s">
         <v>238</v>
       </c>
@@ -12562,16 +12571,16 @@
         <v>3944732.0630145115</v>
       </c>
       <c r="AA121" s="38" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="AB121" s="42" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="AC121" s="43" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="122" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="122" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B122" s="38" t="s">
         <v>276</v>
       </c>
@@ -12638,16 +12647,16 @@
         <v>7340.1134084428477</v>
       </c>
       <c r="AA122" s="38" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="AB122" s="42" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AC122" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="123" spans="2:29" ht="51" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B123" s="38" t="s">
         <v>260</v>
       </c>
@@ -12714,16 +12723,16 @@
         <v>1044</v>
       </c>
       <c r="AA123" s="38" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="AB123" s="42" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AC123" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="124" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B124" s="38" t="s">
         <v>278</v>
       </c>
@@ -12790,16 +12799,16 @@
         <v>4407.2793859099929</v>
       </c>
       <c r="AA124" s="38" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AB124" s="42" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AC124" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="125" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B125" s="38" t="s">
         <v>253</v>
       </c>
@@ -12838,16 +12847,16 @@
         <v>9842.1904497703563</v>
       </c>
       <c r="AA125" s="38" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AB125" s="42" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AC125" s="43" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="126" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="126" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B126" s="38" t="s">
         <v>254</v>
       </c>
@@ -12914,16 +12923,16 @@
         <v>0.44779456447246724</v>
       </c>
       <c r="AA126" s="38" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AB126" s="42" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AC126" s="43" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="127" spans="2:29" ht="68" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="127" spans="1:29" ht="68" x14ac:dyDescent="0.2">
       <c r="B127" s="38" t="s">
         <v>183</v>
       </c>
@@ -12990,16 +12999,16 @@
         <v>5088667.5032287594</v>
       </c>
       <c r="AA127" s="38" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="AB127" s="42" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AC127" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="128" spans="2:29" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="128" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AB128" s="42"/>
       <c r="AC128" s="43"/>
     </row>
@@ -13063,13 +13072,13 @@
         <v>2510157.8095502295</v>
       </c>
       <c r="AA130" s="38" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="AB130" s="42" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AC130" s="43" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="131" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -13111,13 +13120,13 @@
         <v>388638.22348903998</v>
       </c>
       <c r="AA131" s="38" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="AB131" s="42" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AC131" s="43" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -13159,13 +13168,13 @@
         <v>2121519.5860611894</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="AB132" s="42" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AC132" s="43" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="133" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -13207,13 +13216,13 @@
         <v>0</v>
       </c>
       <c r="AA133" s="38" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="AB133" s="42" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AC133" s="43" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="134" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -13283,13 +13292,13 @@
         <v>336166.07900932123</v>
       </c>
       <c r="AA134" s="38" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="AB134" s="42" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="AC134" s="43" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="135" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -13359,13 +13368,13 @@
         <v>336166.07900932123</v>
       </c>
       <c r="AA135" s="38" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="AB135" s="42" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="AC135" s="43" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="136" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13456,13 +13465,13 @@
         <v>0.40958701751064658</v>
       </c>
       <c r="AA137" s="38" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AB137" s="42" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="AC137" s="43" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AD137">
         <v>20</v>
@@ -13470,7 +13479,7 @@
     </row>
     <row r="138" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A138" s="48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B138" s="38" t="s">
         <v>184</v>
@@ -13538,13 +13547,13 @@
         <v>6.6061710417515754E-2</v>
       </c>
       <c r="AA138" s="39" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AB138" s="42" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AC138" s="43" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AD138">
         <v>20</v>
@@ -13626,13 +13635,13 @@
         <v>336166.07900932123</v>
       </c>
       <c r="AA140" s="38" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AB140" s="42" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="AC140" s="43" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AD140">
         <v>20</v>
@@ -13705,13 +13714,13 @@
         <v>388638.22348903998</v>
       </c>
       <c r="AA141" s="38" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AB141" s="42" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AC141" s="43" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="142" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -13781,13 +13790,13 @@
         <v>0.86498460185247705</v>
       </c>
       <c r="AA142" s="38" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AB142" s="42" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="AC142" s="43" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="143" spans="1:30" x14ac:dyDescent="0.2">
@@ -13882,18 +13891,18 @@
         <v>24233.450635277597</v>
       </c>
       <c r="AA145" s="38" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AB145" s="42" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AC145" s="43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="146" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B146" s="38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C146" s="33" t="s">
         <v>163</v>
@@ -13955,13 +13964,13 @@
         <v>6058.3626588193993</v>
       </c>
       <c r="AA146" s="38" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="AB146" s="42" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AC146" s="43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="147" spans="2:29" ht="51" x14ac:dyDescent="0.2">
@@ -14031,13 +14040,13 @@
         <v>84041.519752330307</v>
       </c>
       <c r="AA147" s="38" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AB147" s="42" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AC147" s="43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="148" spans="2:29" ht="34" x14ac:dyDescent="0.2">
@@ -14107,13 +14116,13 @@
         <v>1888.8340225328548</v>
       </c>
       <c r="AA148" s="38" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AB148" s="42" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AC148" s="43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="149" spans="2:29" ht="34" x14ac:dyDescent="0.2">
@@ -14183,18 +14192,18 @@
         <v>1373.5803521107118</v>
       </c>
       <c r="AA149" s="38" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AB149" s="42" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AC149" s="43" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B150" s="38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C150" s="33" t="s">
         <v>163</v>
@@ -14256,13 +14265,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="AA150" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="AB150" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC150" s="43" t="s">
         <v>343</v>
-      </c>
-      <c r="AB150" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC150" s="43" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -14376,13 +14385,13 @@
         <v>398480.41393881035</v>
       </c>
       <c r="AA155" s="38" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AB155" s="42" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="AC155" s="43" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -14420,19 +14429,19 @@
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B157" s="38" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C157" s="31" t="s">
         <v>162</v>
       </c>
       <c r="AA157" s="38" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AB157" s="42" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AC157" s="43" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933D6FC4-B532-B64C-88AC-08906FECE688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5603A1-8EBF-334C-9F4E-C5B2926DDFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6160" yWindow="760" windowWidth="34560" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25580" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="491">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -685,9 +685,6 @@
     <t>bg biomass loss from stock removals</t>
   </si>
   <si>
-    <t>vec_biomass_c_removed_from_young</t>
-  </si>
-  <si>
     <t>total starting ag stock</t>
   </si>
   <si>
@@ -901,9 +898,6 @@
     <t>arr_biomass_c_bg_lost_decomposition</t>
   </si>
   <si>
-    <t>this has been modified to use a logistic ramp rather than alinear</t>
-  </si>
-  <si>
     <t>d(t)</t>
   </si>
   <si>
@@ -1123,9 +1117,6 @@
     <t>\tilde{\Psi}^{(0)}(t, v)</t>
   </si>
   <si>
-    <t>\tilde{b}^{(0)}</t>
-  </si>
-  <si>
     <t>n_tps_no_withdrawals_new_growth</t>
   </si>
   <si>
@@ -1456,9 +1447,6 @@
     <t>Vector (dim $2$) storing avrage biomass stock per unit area required to be considered forest.</t>
   </si>
   <si>
-    <t>\overline{B_{avail}}(v)</t>
-  </si>
-  <si>
     <t>\gamma(v)</t>
   </si>
   <si>
@@ -1502,6 +1490,30 @@
   </si>
   <si>
     <t>\Phi_{conv}(t, v)</t>
+  </si>
+  <si>
+    <t>\overline{B}_{avail}(v)</t>
+  </si>
+  <si>
+    <t>\tilde{m}^{(0)}</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>\psi^{(y)}(t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector ($n_T$) storing fraction of young removals that are available that are taken to satisfy removals _before_ original forests. If $&lt; 1$, does not negate the possibility that young forests will face removals after removals are taken from mature forests. </t>
+  </si>
+  <si>
+    <t>vec_biomass_c_removed_from_young_pre_orig</t>
+  </si>
+  <si>
+    <t>vec_biomass_c_removed_from_young_post_orig</t>
+  </si>
+  <si>
+    <t>vec_biomass_c_removals_young_priority_frac</t>
   </si>
 </sst>
 </file>
@@ -6980,31 +6992,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40F0562-A765-A442-B9DB-CF71D123E451}">
-  <dimension ref="A1:AO166"/>
+  <dimension ref="A1:AO168"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" style="48" customWidth="1"/>
-    <col min="2" max="2" width="62.1640625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="2" style="27" customWidth="1"/>
+    <col min="2" max="2" width="58.33203125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="27" customWidth="1"/>
     <col min="4" max="4" width="4.1640625" style="23" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="27" style="22" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="10" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="10" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="4" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
     <col min="10" max="11" width="13.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" style="5" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="21.1640625" style="5" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="21.1640625" style="4" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" style="5" hidden="1" customWidth="1"/>
-    <col min="19" max="20" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="9.1640625" style="5" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" style="4" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="12.5" style="4" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
-    <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" style="5" customWidth="1"/>
+    <col min="13" max="14" width="13.33203125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="21.1640625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="13.33203125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" style="5" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="4" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="5" customWidth="1"/>
+    <col min="25" max="26" width="13.33203125" style="4" customWidth="1"/>
     <col min="27" max="27" width="24" style="24" customWidth="1"/>
     <col min="28" max="28" width="64.5" style="47" customWidth="1"/>
     <col min="29" max="29" width="14.6640625" style="48" customWidth="1"/>
@@ -7182,7 +7194,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7226,16 +7238,16 @@
       </c>
       <c r="Z5" s="52"/>
       <c r="AA5" s="24" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AB5" s="40" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AD5" s="36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AE5" s="21" t="s">
         <v>33</v>
@@ -7330,7 +7342,7 @@
     </row>
     <row r="7" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
@@ -7396,13 +7408,13 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AB7" s="42" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AC7" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7429,7 +7441,7 @@
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
@@ -7497,13 +7509,13 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AB8" s="42" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AC8" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7530,10 +7542,10 @@
     </row>
     <row r="9" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>162</v>
@@ -7584,13 +7596,13 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AB9" s="42" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AC9" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7617,10 +7629,10 @@
     </row>
     <row r="10" spans="1:41" ht="85" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>174</v>
@@ -7657,13 +7669,13 @@
         <v>0</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AC10" s="43" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7678,10 +7690,10 @@
     </row>
     <row r="11" spans="1:41" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>174</v>
@@ -7718,13 +7730,13 @@
         <v>0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AB11" s="42" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AC11" s="43" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7739,10 +7751,10 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C12" s="28"/>
       <c r="G12" s="4">
@@ -7802,10 +7814,10 @@
         <v>116</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AB12" s="42" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="AC12" s="43"/>
       <c r="AE12" s="19"/>
@@ -7814,10 +7826,10 @@
     </row>
     <row r="13" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>162</v>
@@ -7847,13 +7859,13 @@
         <v>110</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AB13" s="42" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AC13" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE13" s="19">
         <v>0.36</v>
@@ -7868,7 +7880,7 @@
     </row>
     <row r="14" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>158</v>
@@ -7936,13 +7948,13 @@
         <v>249244</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AB14" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC14" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE14" s="19"/>
       <c r="AF14" s="19"/>
@@ -7950,10 +7962,10 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>162</v>
@@ -7983,13 +7995,13 @@
         <v>0.7</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AB15" s="42" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AC15" s="43" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AE15" s="19">
         <v>0.6</v>
@@ -8004,19 +8016,19 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>162</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G16" s="4">
         <v>5</v>
@@ -8061,13 +8073,13 @@
         <v>9</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AB16" s="42" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AC16" s="43" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -8075,10 +8087,10 @@
     </row>
     <row r="17" spans="1:33" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>162</v>
@@ -8140,13 +8152,13 @@
         <v>1.728</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AB17" s="42" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AC17" s="43" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AE17" s="19"/>
       <c r="AF17" s="19"/>
@@ -8154,16 +8166,16 @@
     </row>
     <row r="18" spans="1:33" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G18" s="4">
         <v>0.33057704999999998</v>
@@ -8172,13 +8184,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA18" s="38" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AB18" s="42" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AC18" s="43" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AE18" s="19">
         <v>1.8</v>
@@ -8193,10 +8205,10 @@
     </row>
     <row r="19" spans="1:33" ht="102" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>162</v>
@@ -8214,13 +8226,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA19" s="38" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AB19" s="42" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AC19" s="43" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AE19" s="19">
         <v>3</v>
@@ -8235,10 +8247,10 @@
     </row>
     <row r="20" spans="1:33" ht="136" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>162</v>
@@ -8251,13 +8263,13 @@
         <v>0.67</v>
       </c>
       <c r="AA20" s="39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AB20" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC20" s="43" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AE20" s="19">
         <v>6</v>
@@ -8272,10 +8284,10 @@
     </row>
     <row r="21" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>162</v>
@@ -8290,13 +8302,13 @@
         <v>100</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AB21" s="42" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AC21" s="43" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AE21" s="19">
         <v>10</v>
@@ -8311,10 +8323,10 @@
     </row>
     <row r="22" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>162</v>
@@ -8329,13 +8341,13 @@
         <v>0.25</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AB22" s="42" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AC22" s="44" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AE22" s="19"/>
       <c r="AF22" s="19"/>
@@ -8343,10 +8355,10 @@
     </row>
     <row r="23" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C23" s="32" t="s">
         <v>174</v>
@@ -8363,13 +8375,13 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AB23" s="42" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AC23" s="43" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AE23" s="19">
         <v>12</v>
@@ -8384,10 +8396,10 @@
     </row>
     <row r="24" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C24" s="32" t="s">
         <v>174</v>
@@ -8404,13 +8416,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA24" s="38" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="AB24" s="42" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="AC24" s="43" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AE24" s="19">
         <v>13.5</v>
@@ -8439,7 +8451,7 @@
     </row>
     <row r="26" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>159</v>
@@ -8493,13 +8505,13 @@
         <v>49500</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AB26" s="42" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AC26" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE26" s="19">
         <v>10</v>
@@ -8514,10 +8526,10 @@
     </row>
     <row r="27" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C27" s="33" t="s">
         <v>163</v>
@@ -8554,13 +8566,13 @@
         <v>0</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AB27" s="42" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AC27" s="43" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AE27" s="19">
         <v>6</v>
@@ -8575,7 +8587,7 @@
     </row>
     <row r="28" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B28" s="38" t="s">
         <v>160</v>
@@ -8643,13 +8655,13 @@
         <v>49500</v>
       </c>
       <c r="AA28" s="38" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AB28" s="42" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AC28" s="43" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AE28" s="19">
         <v>3</v>
@@ -8695,10 +8707,10 @@
     </row>
     <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>162</v>
@@ -8716,21 +8728,21 @@
         <v>0.92</v>
       </c>
       <c r="AA30" s="38" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AB30" s="42" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AC30" s="43" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>174</v>
@@ -8752,13 +8764,13 @@
         <v>2E-3</v>
       </c>
       <c r="AA31" s="38" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AB31" s="42" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AC31" s="43" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -8789,7 +8801,7 @@
     </row>
     <row r="34" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B34" s="38" t="s">
         <v>168</v>
@@ -8822,242 +8834,180 @@
         <v>2520000</v>
       </c>
       <c r="AA34" s="38" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AB34" s="42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AC34" s="43" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB35" s="40"/>
+      <c r="B35" s="38" t="s">
+        <v>490</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="P35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="V35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="AA35" s="38" t="s">
+        <v>486</v>
+      </c>
+      <c r="AB35" s="42" t="s">
+        <v>487</v>
+      </c>
       <c r="AC35" s="43"/>
     </row>
-    <row r="36" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="F36" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
       <c r="AB36" s="40"/>
       <c r="AC36" s="43"/>
     </row>
-    <row r="37" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="F37" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="H37" s="8"/>
-      <c r="J37" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>126</v>
-      </c>
+    <row r="37" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="F37" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="12"/>
+      <c r="S37" s="12"/>
+      <c r="T37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="12"/>
       <c r="AB37" s="40"/>
       <c r="AC37" s="43"/>
-      <c r="AD37" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B38" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="H38" s="4">
-        <v>0</v>
-      </c>
-      <c r="I38" s="5">
-        <f>SUM(K$38:K38)</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="4">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5">
-        <f>SUM(N$38:N38)</f>
-        <v>0</v>
-      </c>
-      <c r="N38" s="4">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5">
-        <f>SUM(Q$38:Q38)</f>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="4">
-        <v>0</v>
-      </c>
-      <c r="R38" s="5">
-        <f>SUM(T$38:T38)</f>
-        <v>0</v>
-      </c>
-      <c r="T38" s="4">
-        <v>0</v>
-      </c>
-      <c r="U38" s="5">
-        <f>SUM(W$38:W38)</f>
-        <v>0</v>
-      </c>
-      <c r="W38" s="4">
-        <v>0</v>
-      </c>
-      <c r="X38" s="5">
-        <f>SUM(Z$38:Z38)</f>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="4">
-        <v>0</v>
+    </row>
+    <row r="38" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+      <c r="F38" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" s="8"/>
+      <c r="J38" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="AB38" s="40"/>
       <c r="AC38" s="43"/>
+      <c r="AD38" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="39" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B39" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="C39" s="55" t="s">
+      <c r="B39" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5">
+        <f>SUM(K$39:K39)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <f>SUM(N$39:N39)</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="4">
+        <v>0</v>
+      </c>
+      <c r="O39" s="5">
+        <f>SUM(Q$39:Q39)</f>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>0</v>
+      </c>
+      <c r="R39" s="5">
+        <f>SUM(T$39:T39)</f>
+        <v>0</v>
+      </c>
+      <c r="T39" s="4">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5">
+        <f>SUM(W$39:W39)</f>
+        <v>0</v>
+      </c>
+      <c r="W39" s="4">
+        <v>0</v>
+      </c>
+      <c r="X39" s="5">
+        <f>SUM(Z$39:Z39)</f>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="40"/>
+      <c r="AC39" s="43"/>
+    </row>
+    <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="C40" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F40" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="4">
-        <v>0</v>
-      </c>
-      <c r="H39" s="4">
+      <c r="G40" s="4">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4">
         <f>H13</f>
         <v>85</v>
       </c>
-      <c r="I39" s="5">
-        <f>SUM(H$38:H39)</f>
-        <v>85</v>
-      </c>
-      <c r="J39" s="4">
-        <f>IF(I39&gt;=K$11, IF(I38&lt;K$11, K$11-I38, 0),H39)</f>
-        <v>0</v>
-      </c>
-      <c r="K39" s="4">
-        <f>H39-J39</f>
-        <v>85</v>
-      </c>
-      <c r="L39" s="5">
-        <f>SUM(K$38:K39)</f>
-        <v>85</v>
-      </c>
-      <c r="M39" s="4">
-        <f>IF(L39&gt;=N$11, IF(L38&lt;N$11, N$11-L38, 0),K39)</f>
-        <v>0</v>
-      </c>
-      <c r="N39" s="4">
-        <f>K39-M39</f>
-        <v>85</v>
-      </c>
-      <c r="O39" s="5">
-        <f>SUM(N$38:N39)</f>
-        <v>85</v>
-      </c>
-      <c r="P39" s="4">
-        <f>IF(O39&gt;=Q$11, IF(O38&lt;Q$11, Q$11-O38, 0),N39)</f>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="4">
-        <f>N39-P39</f>
-        <v>85</v>
-      </c>
-      <c r="R39" s="5">
-        <f>SUM(Q$38:Q39)</f>
-        <v>85</v>
-      </c>
-      <c r="S39" s="4">
-        <f>IF(R39&gt;=T$11, IF(R38&lt;T$11, T$11-R38, 0),Q39)</f>
-        <v>0</v>
-      </c>
-      <c r="T39" s="4">
-        <f>Q39-S39</f>
-        <v>85</v>
-      </c>
-      <c r="U39" s="5">
-        <f>SUM(T$38:T39)</f>
-        <v>85</v>
-      </c>
-      <c r="V39" s="4">
-        <f>IF(U39&gt;=W$11, IF(U38&lt;W$11, W$11-U38, 0),T39)</f>
-        <v>0</v>
-      </c>
-      <c r="W39" s="4">
-        <f>T39-V39</f>
-        <v>85</v>
-      </c>
-      <c r="X39" s="5">
-        <f>SUM(W$38:W39)</f>
-        <v>85</v>
-      </c>
-      <c r="Y39" s="4">
-        <f>IF(X39&gt;=Z$11, IF(X38&lt;Z$11, Z$11-X38, 0),W39)</f>
-        <v>0</v>
-      </c>
-      <c r="Z39" s="4">
-        <f>W39-Y39</f>
-        <v>85</v>
-      </c>
-      <c r="AA39" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="AB39" s="42" t="s">
-        <v>389</v>
-      </c>
-      <c r="AC39" s="43" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="C40" s="55"/>
-      <c r="F40" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G40" s="4">
-        <v>0</v>
-      </c>
-      <c r="H40" s="4">
-        <v>0</v>
-      </c>
       <c r="I40" s="5">
-        <f>SUM(H$38:H40)</f>
+        <f>SUM(H$39:H40)</f>
         <v>85</v>
       </c>
       <c r="J40" s="4">
@@ -9065,213 +9015,220 @@
         <v>0</v>
       </c>
       <c r="K40" s="4">
+        <f>H40-J40</f>
+        <v>85</v>
+      </c>
+      <c r="L40" s="5">
+        <f>SUM(K$39:K40)</f>
+        <v>85</v>
+      </c>
+      <c r="M40" s="4">
+        <f>IF(L40&gt;=N$11, IF(L39&lt;N$11, N$11-L39, 0),K40)</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="4">
+        <f>K40-M40</f>
+        <v>85</v>
+      </c>
+      <c r="O40" s="5">
+        <f>SUM(N$39:N40)</f>
+        <v>85</v>
+      </c>
+      <c r="P40" s="4">
+        <f>IF(O40&gt;=Q$11, IF(O39&lt;Q$11, Q$11-O39, 0),N40)</f>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4">
+        <f>N40-P40</f>
+        <v>85</v>
+      </c>
+      <c r="R40" s="5">
+        <f>SUM(Q$39:Q40)</f>
+        <v>85</v>
+      </c>
+      <c r="S40" s="4">
+        <f>IF(R40&gt;=T$11, IF(R39&lt;T$11, T$11-R39, 0),Q40)</f>
+        <v>0</v>
+      </c>
+      <c r="T40" s="4">
+        <f>Q40-S40</f>
+        <v>85</v>
+      </c>
+      <c r="U40" s="5">
+        <f>SUM(T$39:T40)</f>
+        <v>85</v>
+      </c>
+      <c r="V40" s="4">
+        <f>IF(U40&gt;=W$11, IF(U39&lt;W$11, W$11-U39, 0),T40)</f>
+        <v>0</v>
+      </c>
+      <c r="W40" s="4">
+        <f>T40-V40</f>
+        <v>85</v>
+      </c>
+      <c r="X40" s="5">
+        <f>SUM(W$39:W40)</f>
+        <v>85</v>
+      </c>
+      <c r="Y40" s="4">
+        <f>IF(X40&gt;=Z$11, IF(X39&lt;Z$11, Z$11-X39, 0),W40)</f>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="4">
+        <f>W40-Y40</f>
+        <v>85</v>
+      </c>
+      <c r="AA40" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB40" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="AC40" s="43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A41" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="C41" s="55"/>
+      <c r="F41" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5">
+        <f>SUM(H$39:H41)</f>
+        <v>85</v>
+      </c>
+      <c r="J41" s="4">
+        <f>IF(I41&gt;=K$11, IF(I40&lt;K$11, K$11-I40, 0),H41)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="4">
         <f>K13</f>
         <v>80</v>
       </c>
-      <c r="L40" s="5">
-        <f>SUM(K$38:K40)</f>
+      <c r="L41" s="5">
+        <f>SUM(K$39:K41)</f>
         <v>165</v>
       </c>
-      <c r="M40" s="4">
-        <f>IF(L40&gt;=N$11, IF(L39&lt;N$11, N$11-L39, 0),K40)</f>
-        <v>0</v>
-      </c>
-      <c r="N40" s="4">
-        <f>K40-M40</f>
+      <c r="M41" s="4">
+        <f>IF(L41&gt;=N$11, IF(L40&lt;N$11, N$11-L40, 0),K41)</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="4">
+        <f>K41-M41</f>
         <v>80</v>
       </c>
-      <c r="O40" s="5">
-        <f>SUM(N$38:N40)</f>
+      <c r="O41" s="5">
+        <f>SUM(N$39:N41)</f>
         <v>165</v>
       </c>
-      <c r="P40" s="4">
-        <f t="shared" ref="P40:P42" si="0">IF(O40&gt;=Q$11, IF(O39&lt;Q$11, Q$11-O39, 0),N40)</f>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="4">
-        <f>N40-P40</f>
+      <c r="P41" s="4">
+        <f t="shared" ref="P41:P43" si="0">IF(O41&gt;=Q$11, IF(O40&lt;Q$11, Q$11-O40, 0),N41)</f>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="4">
+        <f>N41-P41</f>
         <v>80</v>
       </c>
-      <c r="R40" s="5">
-        <f>SUM(Q$38:Q40)</f>
+      <c r="R41" s="5">
+        <f>SUM(Q$39:Q41)</f>
         <v>165</v>
       </c>
-      <c r="S40" s="4">
-        <f t="shared" ref="S40:S42" si="1">IF(R40&gt;=T$11, IF(R39&lt;T$11, T$11-R39, 0),Q40)</f>
-        <v>0</v>
-      </c>
-      <c r="T40" s="4">
-        <f>Q40-S40</f>
+      <c r="S41" s="4">
+        <f t="shared" ref="S41:S43" si="1">IF(R41&gt;=T$11, IF(R40&lt;T$11, T$11-R40, 0),Q41)</f>
+        <v>0</v>
+      </c>
+      <c r="T41" s="4">
+        <f>Q41-S41</f>
         <v>80</v>
       </c>
-      <c r="U40" s="5">
-        <f>SUM(T$38:T40)</f>
+      <c r="U41" s="5">
+        <f>SUM(T$39:T41)</f>
         <v>165</v>
       </c>
-      <c r="V40" s="4">
-        <f t="shared" ref="V40:V42" si="2">IF(U40&gt;=W$11, IF(U39&lt;W$11, W$11-U39, 0),T40)</f>
-        <v>0</v>
-      </c>
-      <c r="W40" s="4">
-        <f>T40-V40</f>
+      <c r="V41" s="4">
+        <f t="shared" ref="V41:V43" si="2">IF(U41&gt;=W$11, IF(U40&lt;W$11, W$11-U40, 0),T41)</f>
+        <v>0</v>
+      </c>
+      <c r="W41" s="4">
+        <f>T41-V41</f>
         <v>80</v>
       </c>
-      <c r="X40" s="5">
-        <f>SUM(W$38:W40)</f>
+      <c r="X41" s="5">
+        <f>SUM(W$39:W41)</f>
         <v>165</v>
       </c>
-      <c r="Y40" s="4">
-        <f t="shared" ref="Y40:Y42" si="3">IF(X40&gt;=Z$11, IF(X39&lt;Z$11, Z$11-X39, 0),W40)</f>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="4">
-        <f>W40-Y40</f>
+      <c r="Y41" s="4">
+        <f t="shared" ref="Y41:Y43" si="3">IF(X41&gt;=Z$11, IF(X40&lt;Z$11, Z$11-X40, 0),W41)</f>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="4">
+        <f>W41-Y41</f>
         <v>80</v>
       </c>
-      <c r="AA40" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="AB40" s="42" t="s">
-        <v>390</v>
-      </c>
-      <c r="AC40" s="43" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B41" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="C41" s="55"/>
-      <c r="F41" s="14" t="s">
+      <c r="AA41" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="AB41" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="AC41" s="43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="A42" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="C42" s="55"/>
+      <c r="F42" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G41" s="4">
-        <v>0</v>
-      </c>
-      <c r="H41" s="4">
-        <v>0</v>
-      </c>
-      <c r="I41" s="5">
-        <f>SUM(H$38:H41)</f>
+      <c r="G42" s="4">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <f>SUM(H$39:H42)</f>
         <v>85</v>
       </c>
-      <c r="J41" s="4">
-        <f>IF(I41&gt;=K$11, IF(I40&lt;K$11, K$11-I40, 0),H41)</f>
-        <v>0</v>
-      </c>
-      <c r="K41" s="4">
-        <v>0</v>
-      </c>
-      <c r="L41" s="5">
-        <f>SUM(K$38:K41)</f>
+      <c r="J42" s="4">
+        <f>IF(I42&gt;=K$11, IF(I41&lt;K$11, K$11-I41, 0),H42)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5">
+        <f>SUM(K$39:K42)</f>
         <v>165</v>
       </c>
-      <c r="M41" s="4">
-        <f t="shared" ref="M41:M42" si="4">IF(L41&gt;=N$11, IF(L40&lt;N$11, N$11-L40, 0),K41)</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="4">
+      <c r="M42" s="4">
+        <f t="shared" ref="M42:M43" si="4">IF(L42&gt;=N$11, IF(L41&lt;N$11, N$11-L41, 0),K42)</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="4">
         <f>N13</f>
         <v>92</v>
       </c>
-      <c r="O41" s="5">
-        <f>SUM(N$38:N41)</f>
-        <v>257</v>
-      </c>
-      <c r="P41" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="4">
-        <f>N41-P41</f>
-        <v>92</v>
-      </c>
-      <c r="R41" s="5">
-        <f>SUM(Q$38:Q41)</f>
-        <v>257</v>
-      </c>
-      <c r="S41" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T41" s="4">
-        <f>Q41-S41</f>
-        <v>92</v>
-      </c>
-      <c r="U41" s="5">
-        <f>SUM(T$38:T41)</f>
-        <v>257</v>
-      </c>
-      <c r="V41" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W41" s="4">
-        <f>T41-V41</f>
-        <v>92</v>
-      </c>
-      <c r="X41" s="5">
-        <f>SUM(W$38:W41)</f>
-        <v>257</v>
-      </c>
-      <c r="Y41" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="4">
-        <f>W41-Y41</f>
-        <v>92</v>
-      </c>
-      <c r="AA41" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="AB41" s="42" t="s">
-        <v>391</v>
-      </c>
-      <c r="AC41" s="43" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="B42" s="38"/>
-      <c r="C42" s="55"/>
-      <c r="F42" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G42" s="4">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4">
-        <v>0</v>
-      </c>
-      <c r="I42" s="5">
-        <f>SUM(H$38:H42)</f>
-        <v>85</v>
-      </c>
-      <c r="J42" s="4">
-        <f>IF(I42&gt;=K$11, IF(I41&lt;K$11, K$11-I41, 0),H42)</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="4">
-        <v>0</v>
-      </c>
-      <c r="L42" s="5">
-        <f>SUM(K$38:K42)</f>
-        <v>165</v>
-      </c>
-      <c r="M42" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N42" s="4">
-        <v>0</v>
-      </c>
       <c r="O42" s="5">
-        <f>SUM(N$38:N42)</f>
+        <f>SUM(N$39:N42)</f>
         <v>257</v>
       </c>
       <c r="P42" s="4">
@@ -9279,111 +9236,160 @@
         <v>0</v>
       </c>
       <c r="Q42" s="4">
+        <f>N42-P42</f>
+        <v>92</v>
+      </c>
+      <c r="R42" s="5">
+        <f>SUM(Q$39:Q42)</f>
+        <v>257</v>
+      </c>
+      <c r="S42" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="4">
+        <f>Q42-S42</f>
+        <v>92</v>
+      </c>
+      <c r="U42" s="5">
+        <f>SUM(T$39:T42)</f>
+        <v>257</v>
+      </c>
+      <c r="V42" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="4">
+        <f>T42-V42</f>
+        <v>92</v>
+      </c>
+      <c r="X42" s="5">
+        <f>SUM(W$39:W42)</f>
+        <v>257</v>
+      </c>
+      <c r="Y42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="4">
+        <f>W42-Y42</f>
+        <v>92</v>
+      </c>
+      <c r="AA42" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="AB42" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC42" s="43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="B43" s="38"/>
+      <c r="C43" s="55"/>
+      <c r="F43" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G43" s="4">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5">
+        <f>SUM(H$39:H43)</f>
+        <v>85</v>
+      </c>
+      <c r="J43" s="4">
+        <f>IF(I43&gt;=K$11, IF(I42&lt;K$11, K$11-I42, 0),H43)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <f>SUM(K$39:K43)</f>
+        <v>165</v>
+      </c>
+      <c r="M43" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="4">
+        <v>0</v>
+      </c>
+      <c r="O43" s="5">
+        <f>SUM(N$39:N43)</f>
+        <v>257</v>
+      </c>
+      <c r="P43" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="4">
         <f>Q13</f>
         <v>43</v>
       </c>
-      <c r="R42" s="5">
-        <f>SUM(Q$38:Q42)</f>
+      <c r="R43" s="5">
+        <f>SUM(Q$39:Q43)</f>
         <v>300</v>
       </c>
-      <c r="S42" s="4">
+      <c r="S43" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T42" s="4">
-        <f>Q42-S42</f>
+      <c r="T43" s="4">
+        <f>Q43-S43</f>
         <v>43</v>
       </c>
-      <c r="U42" s="5">
-        <f>SUM(T$38:T42)</f>
+      <c r="U43" s="5">
+        <f>SUM(T$39:T43)</f>
         <v>300</v>
       </c>
-      <c r="V42" s="4">
+      <c r="V43" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W42" s="4">
-        <f>T42-V42</f>
+      <c r="W43" s="4">
+        <f>T43-V43</f>
         <v>43</v>
       </c>
-      <c r="X42" s="5">
-        <f>SUM(W$38:W42)</f>
+      <c r="X43" s="5">
+        <f>SUM(W$39:W43)</f>
         <v>300</v>
       </c>
-      <c r="Y42" s="4">
+      <c r="Y43" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z42" s="4">
-        <f>W42-Y42</f>
+      <c r="Z43" s="4">
+        <f>W43-Y43</f>
         <v>43</v>
       </c>
-      <c r="AA42" s="38"/>
-      <c r="AB42" s="42"/>
-      <c r="AC42" s="43"/>
-    </row>
-    <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="F43" s="14" t="s">
+      <c r="AA43" s="38"/>
+      <c r="AB43" s="42"/>
+      <c r="AC43" s="43"/>
+    </row>
+    <row r="44" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="F44" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB43" s="40"/>
-      <c r="AC43" s="43"/>
-    </row>
-    <row r="44" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="A44" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B44" s="56" t="s">
+      <c r="AB44" s="40"/>
+      <c r="AC44" s="43"/>
+    </row>
+    <row r="45" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B45" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="C44" s="55" t="s">
+      <c r="C45" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F45" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="H44" s="4">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4">
-        <f>IF(H39=0, 0, H98*J39/H39)</f>
-        <v>0</v>
-      </c>
-      <c r="N44" s="4">
-        <f>IF(K39=0, 0, K98*M39/K39)</f>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="4">
-        <f>IF(N39=0, 0, N98*P39/N39)</f>
-        <v>0</v>
-      </c>
-      <c r="T44" s="4">
-        <f>IF(Q39=0, 0, Q98*S39/Q39)</f>
-        <v>0</v>
-      </c>
-      <c r="W44" s="4">
-        <f>IF(T39=0, 0, T98*V39/T39)</f>
-        <v>0</v>
-      </c>
-      <c r="Z44" s="4">
-        <f>IF(W39=0, 0, W98*Y39/W39)</f>
-        <v>0</v>
-      </c>
-      <c r="AA44" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB44" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="AC44" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="B45" s="56"/>
-      <c r="C45" s="55"/>
-      <c r="F45" s="14" t="s">
-        <v>194</v>
       </c>
       <c r="H45" s="4">
         <v>0</v>
@@ -9412,15 +9418,21 @@
         <f>IF(W40=0, 0, W99*Y40/W40)</f>
         <v>0</v>
       </c>
-      <c r="AA45" s="38"/>
-      <c r="AB45" s="42"/>
-      <c r="AC45" s="43"/>
+      <c r="AA45" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="AB45" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="AC45" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="46" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B46" s="56"/>
       <c r="C46" s="55"/>
       <c r="F46" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H46" s="4">
         <v>0</v>
@@ -9457,7 +9469,7 @@
       <c r="B47" s="56"/>
       <c r="C47" s="55"/>
       <c r="F47" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H47" s="4">
         <v>0</v>
@@ -9490,122 +9502,114 @@
       <c r="AB47" s="42"/>
       <c r="AC47" s="43"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A48" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B48" s="38" t="s">
+    <row r="48" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B48" s="56"/>
+      <c r="C48" s="55"/>
+      <c r="F48" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <f>IF(H43=0, 0, H102*J43/H43)</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4">
+        <f>IF(K43=0, 0, K102*M43/K43)</f>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4">
+        <f>IF(N43=0, 0, N102*P43/N43)</f>
+        <v>0</v>
+      </c>
+      <c r="T48" s="4">
+        <f>IF(Q43=0, 0, Q102*S43/Q43)</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="4">
+        <f>IF(T43=0, 0, T102*V43/T43)</f>
+        <v>0</v>
+      </c>
+      <c r="Z48" s="4">
+        <f>IF(W43=0, 0, W102*Y43/W43)</f>
+        <v>0</v>
+      </c>
+      <c r="AA48" s="38"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="43"/>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A49" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B49" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C49" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F48" s="14"/>
-      <c r="H48" s="4">
-        <f>SUM(H44:H47)</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
-        <f>SUM(K44:K47)</f>
-        <v>0</v>
-      </c>
-      <c r="N48" s="4">
-        <f>SUM(N44:N47)</f>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4">
-        <f>SUM(Q44:Q47)</f>
-        <v>0</v>
-      </c>
-      <c r="T48" s="4">
-        <f>SUM(T44:T47)</f>
-        <v>0</v>
-      </c>
-      <c r="W48" s="4">
-        <f>SUM(W44:W47)</f>
-        <v>0</v>
-      </c>
-      <c r="Z48" s="4">
-        <f>SUM(Z44:Z47)</f>
-        <v>0</v>
-      </c>
-      <c r="AA48" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="AB48" s="42" t="s">
-        <v>404</v>
-      </c>
-      <c r="AC48" s="43" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="14"/>
+      <c r="H49" s="4">
+        <f>SUM(H45:H48)</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <f>SUM(K45:K48)</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4">
+        <f>SUM(N45:N48)</f>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4">
+        <f>SUM(Q45:Q48)</f>
+        <v>0</v>
+      </c>
+      <c r="T49" s="4">
+        <f>SUM(T45:T48)</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="4">
+        <f>SUM(W45:W48)</f>
+        <v>0</v>
+      </c>
+      <c r="Z49" s="4">
+        <f>SUM(Z45:Z48)</f>
+        <v>0</v>
+      </c>
+      <c r="AA49" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB49" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC49" s="43" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="F50" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AB49" s="40"/>
-      <c r="AC49" s="43"/>
-    </row>
-    <row r="50" spans="1:29" ht="51" x14ac:dyDescent="0.2">
-      <c r="A50" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B50" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="C50" s="55" t="s">
+      <c r="AB50" s="40"/>
+      <c r="AC50" s="43"/>
+    </row>
+    <row r="51" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="A51" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B51" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="C51" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="E50" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="F50" s="14" t="s">
+      <c r="E51" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="H50" s="4">
-        <f>MIN(H44,H$16*G39)</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="4">
-        <f>MIN(K44,K$16*J39)</f>
-        <v>0</v>
-      </c>
-      <c r="N50" s="4">
-        <f>MIN(N44,N$16*M39)</f>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4">
-        <f>MIN(Q44,Q$16*P39)</f>
-        <v>0</v>
-      </c>
-      <c r="T50" s="4">
-        <f>MIN(T44,T$16*S39)</f>
-        <v>0</v>
-      </c>
-      <c r="W50" s="4">
-        <f>MIN(W44,W$16*V39)</f>
-        <v>0</v>
-      </c>
-      <c r="Z50" s="4">
-        <f>MIN(Z44,Z$16*Y39)</f>
-        <v>0</v>
-      </c>
-      <c r="AA50" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="AB50" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="AC50" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="51" spans="1:29" ht="51" x14ac:dyDescent="0.2">
-      <c r="B51" s="56"/>
-      <c r="C51" s="55"/>
-      <c r="E51" s="51"/>
       <c r="F51" s="14" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H51" s="4">
         <f>MIN(H45,H$16*G40)</f>
@@ -9620,31 +9624,37 @@
         <v>0</v>
       </c>
       <c r="Q51" s="4">
-        <f t="shared" ref="Q51" si="5">MIN(Q45,Q$16*P40)</f>
+        <f>MIN(Q45,Q$16*P40)</f>
         <v>0</v>
       </c>
       <c r="T51" s="4">
-        <f t="shared" ref="T51" si="6">MIN(T45,T$16*S40)</f>
+        <f>MIN(T45,T$16*S40)</f>
         <v>0</v>
       </c>
       <c r="W51" s="4">
-        <f t="shared" ref="W51" si="7">MIN(W45,W$16*V40)</f>
+        <f>MIN(W45,W$16*V40)</f>
         <v>0</v>
       </c>
       <c r="Z51" s="4">
-        <f t="shared" ref="Z51" si="8">MIN(Z45,Z$16*Y40)</f>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="38"/>
-      <c r="AB51" s="42"/>
-      <c r="AC51" s="43"/>
+        <f>MIN(Z45,Z$16*Y40)</f>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB51" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC51" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="52" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B52" s="56"/>
       <c r="C52" s="55"/>
       <c r="E52" s="51"/>
       <c r="F52" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H52" s="4">
         <f>MIN(H46,H$16*G41)</f>
@@ -9659,19 +9669,19 @@
         <v>0</v>
       </c>
       <c r="Q52" s="4">
-        <f>MIN(Q46,Q$16*P41)</f>
+        <f t="shared" ref="Q52" si="5">MIN(Q46,Q$16*P41)</f>
         <v>0</v>
       </c>
       <c r="T52" s="4">
-        <f>MIN(T46,T$16*S41)</f>
+        <f t="shared" ref="T52" si="6">MIN(T46,T$16*S41)</f>
         <v>0</v>
       </c>
       <c r="W52" s="4">
-        <f>MIN(W46,W$16*V41)</f>
+        <f t="shared" ref="W52" si="7">MIN(W46,W$16*V41)</f>
         <v>0</v>
       </c>
       <c r="Z52" s="4">
-        <f>MIN(Z46,Z$16*Y41)</f>
+        <f t="shared" ref="Z52" si="8">MIN(Z46,Z$16*Y41)</f>
         <v>0</v>
       </c>
       <c r="AA52" s="38"/>
@@ -9683,7 +9693,7 @@
       <c r="C53" s="55"/>
       <c r="E53" s="51"/>
       <c r="F53" s="14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H53" s="4">
         <f>MIN(H47,H$16*G42)</f>
@@ -9717,163 +9727,158 @@
       <c r="AB53" s="42"/>
       <c r="AC53" s="43"/>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A54" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B54" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="C54" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F54" s="14"/>
+    <row r="54" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="B54" s="56"/>
+      <c r="C54" s="55"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="14" t="s">
+        <v>248</v>
+      </c>
       <c r="H54" s="4">
-        <f>SUM(H50:H53)</f>
+        <f>MIN(H48,H$16*G43)</f>
         <v>0</v>
       </c>
       <c r="K54" s="4">
-        <f>SUM(K50:K53)</f>
+        <f>MIN(K48,K$16*J43)</f>
         <v>0</v>
       </c>
       <c r="N54" s="4">
-        <f>SUM(N50:N53)</f>
+        <f>MIN(N48,N$16*M43)</f>
         <v>0</v>
       </c>
       <c r="Q54" s="4">
-        <f>SUM(Q50:Q53)</f>
+        <f>MIN(Q48,Q$16*P43)</f>
         <v>0</v>
       </c>
       <c r="T54" s="4">
-        <f>SUM(T50:T53)</f>
+        <f>MIN(T48,T$16*S43)</f>
         <v>0</v>
       </c>
       <c r="W54" s="4">
-        <f>SUM(W50:W53)</f>
+        <f>MIN(W48,W$16*V43)</f>
         <v>0</v>
       </c>
       <c r="Z54" s="4">
-        <f>SUM(Z50:Z53)</f>
-        <v>0</v>
-      </c>
-      <c r="AA54" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="AB54" s="42" t="s">
-        <v>405</v>
-      </c>
-      <c r="AC54" s="43" t="s">
-        <v>347</v>
-      </c>
+        <f>MIN(Z48,Z$16*Y43)</f>
+        <v>0</v>
+      </c>
+      <c r="AA54" s="38"/>
+      <c r="AB54" s="42"/>
+      <c r="AC54" s="43"/>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A55" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="C55" s="28"/>
+        <v>258</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>174</v>
+      </c>
       <c r="F55" s="14"/>
       <c r="H55" s="4">
-        <f>H48-H54</f>
+        <f>SUM(H51:H54)</f>
         <v>0</v>
       </c>
       <c r="K55" s="4">
-        <f>K48-K54</f>
+        <f>SUM(K51:K54)</f>
         <v>0</v>
       </c>
       <c r="N55" s="4">
-        <f>N48-N54</f>
+        <f>SUM(N51:N54)</f>
         <v>0</v>
       </c>
       <c r="Q55" s="4">
-        <f>Q48-Q54</f>
+        <f>SUM(Q51:Q54)</f>
         <v>0</v>
       </c>
       <c r="T55" s="4">
-        <f>T48-T54</f>
+        <f>SUM(T51:T54)</f>
         <v>0</v>
       </c>
       <c r="W55" s="4">
-        <f>W48-W54</f>
+        <f>SUM(W51:W54)</f>
         <v>0</v>
       </c>
       <c r="Z55" s="4">
-        <f>Z48-Z54</f>
+        <f>SUM(Z51:Z54)</f>
         <v>0</v>
       </c>
       <c r="AA55" s="38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AB55" s="42" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="AC55" s="43" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A56" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" s="28"/>
       <c r="F56" s="14"/>
-      <c r="AB56" s="42"/>
-      <c r="AC56" s="43"/>
-    </row>
-    <row r="57" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A57" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B57" s="56" t="s">
+      <c r="H56" s="4">
+        <f>H49-H55</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="4">
+        <f>K49-K55</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="4">
+        <f>N49-N55</f>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="4">
+        <f>Q49-Q55</f>
+        <v>0</v>
+      </c>
+      <c r="T56" s="4">
+        <f>T49-T55</f>
+        <v>0</v>
+      </c>
+      <c r="W56" s="4">
+        <f>W49-W55</f>
+        <v>0</v>
+      </c>
+      <c r="Z56" s="4">
+        <f>Z49-Z55</f>
+        <v>0</v>
+      </c>
+      <c r="AA56" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="AB56" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="AC56" s="43" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F57" s="14"/>
+      <c r="AB57" s="42"/>
+      <c r="AC57" s="43"/>
+    </row>
+    <row r="58" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A58" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B58" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="C57" s="55" t="s">
+      <c r="C58" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F58" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="H57" s="4">
-        <f>H44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="4">
-        <f>K44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="N57" s="4">
-        <f>N44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="4">
-        <f>Q44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="T57" s="4">
-        <f>T44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="W57" s="4">
-        <f>W44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="Z57" s="4">
-        <f>Z44*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="AA57" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="AB57" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="AC57" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="B58" s="56"/>
-      <c r="C58" s="55"/>
-      <c r="F58" s="14" t="s">
-        <v>198</v>
       </c>
       <c r="H58" s="4">
         <f>H45*$H$22</f>
@@ -9903,15 +9908,21 @@
         <f>Z45*$H$22</f>
         <v>0</v>
       </c>
-      <c r="AA58" s="38"/>
-      <c r="AB58" s="42"/>
-      <c r="AC58" s="43"/>
+      <c r="AA58" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB58" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="AC58" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="59" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B59" s="56"/>
       <c r="C59" s="55"/>
       <c r="F59" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H59" s="4">
         <f>H46*$H$22</f>
@@ -9949,7 +9960,7 @@
       <c r="B60" s="56"/>
       <c r="C60" s="55"/>
       <c r="F60" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H60" s="4">
         <f>H47*$H$22</f>
@@ -9983,152 +9994,154 @@
       <c r="AB60" s="42"/>
       <c r="AC60" s="43"/>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A61" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B61" s="38" t="s">
+    <row r="61" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B61" s="56"/>
+      <c r="C61" s="55"/>
+      <c r="F61" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" s="4">
+        <f>H48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="4">
+        <f>K48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="N61" s="4">
+        <f>N48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4">
+        <f>Q48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="4">
+        <f>T48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="W61" s="4">
+        <f>W48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="Z61" s="4">
+        <f>Z48*$H$22</f>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="38"/>
+      <c r="AB61" s="42"/>
+      <c r="AC61" s="43"/>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A62" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B62" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="C62" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F61" s="14"/>
-      <c r="H61" s="4">
-        <f>SUM(H57:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="K61" s="4">
-        <f>SUM(K57:K60)</f>
-        <v>0</v>
-      </c>
-      <c r="N61" s="4">
-        <f>SUM(N57:N60)</f>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="4">
-        <f>SUM(Q57:Q60)</f>
-        <v>0</v>
-      </c>
-      <c r="T61" s="4">
-        <f>SUM(T57:T60)</f>
-        <v>0</v>
-      </c>
-      <c r="W61" s="4">
-        <f>SUM(W57:W60)</f>
-        <v>0</v>
-      </c>
-      <c r="Z61" s="4">
-        <f>SUM(Z57:Z60)</f>
-        <v>0</v>
-      </c>
-      <c r="AA61" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB61" s="42" t="s">
-        <v>407</v>
-      </c>
-      <c r="AC61" s="43" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="F62" s="14"/>
-      <c r="AB62" s="42"/>
-      <c r="AC62" s="43"/>
-    </row>
-    <row r="63" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A63" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B63" s="56" t="s">
+      <c r="H62" s="4">
+        <f>SUM(H58:H61)</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="4">
+        <f>SUM(K58:K61)</f>
+        <v>0</v>
+      </c>
+      <c r="N62" s="4">
+        <f>SUM(N58:N61)</f>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4">
+        <f>SUM(Q58:Q61)</f>
+        <v>0</v>
+      </c>
+      <c r="T62" s="4">
+        <f>SUM(T58:T61)</f>
+        <v>0</v>
+      </c>
+      <c r="W62" s="4">
+        <f>SUM(W58:W61)</f>
+        <v>0</v>
+      </c>
+      <c r="Z62" s="4">
+        <f>SUM(Z58:Z61)</f>
+        <v>0</v>
+      </c>
+      <c r="AA62" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB62" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="AC62" s="43" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F63" s="14"/>
+      <c r="AB63" s="42"/>
+      <c r="AC63" s="43"/>
+    </row>
+    <row r="64" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A64" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B64" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="C63" s="55" t="s">
+      <c r="C64" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F64" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H63" s="4">
+      <c r="H64" s="4">
         <f>AE6</f>
         <v>0</v>
       </c>
-      <c r="K63" s="4">
+      <c r="K64" s="4">
         <f>AE7</f>
         <v>0.01</v>
       </c>
-      <c r="N63" s="4">
+      <c r="N64" s="4">
         <f>AE8</f>
         <v>0.05</v>
       </c>
-      <c r="Q63" s="4">
+      <c r="Q64" s="4">
         <f>AE9</f>
         <v>0.12</v>
       </c>
-      <c r="T63" s="4">
+      <c r="T64" s="4">
         <f>AE11</f>
         <v>0.2</v>
       </c>
-      <c r="W63" s="4">
+      <c r="W64" s="4">
         <f>AE13</f>
         <v>0.36</v>
       </c>
-      <c r="Z63" s="4">
+      <c r="Z64" s="4">
         <f>AE15</f>
         <v>0.6</v>
       </c>
-      <c r="AA63" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="AB63" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="AC63" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="64" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="B64" s="56"/>
-      <c r="C64" s="55"/>
-      <c r="F64" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H64" s="4">
-        <v>0</v>
-      </c>
-      <c r="K64" s="4">
-        <v>0</v>
-      </c>
-      <c r="N64" s="4">
-        <f>AE7</f>
-        <v>0.01</v>
-      </c>
-      <c r="Q64" s="4">
-        <f>AE8</f>
-        <v>0.05</v>
-      </c>
-      <c r="T64" s="4">
-        <f>AE9</f>
-        <v>0.12</v>
-      </c>
-      <c r="W64" s="4">
-        <f>AE11</f>
-        <v>0.2</v>
-      </c>
-      <c r="Z64" s="4">
-        <f>AE13</f>
-        <v>0.36</v>
-      </c>
-      <c r="AA64" s="38"/>
-      <c r="AB64" s="42"/>
-      <c r="AC64" s="43"/>
+      <c r="AA64" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB64" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="AC64" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="65" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B65" s="56"/>
       <c r="C65" s="55"/>
       <c r="F65" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H65" s="4">
         <v>0</v>
@@ -10137,23 +10150,24 @@
         <v>0</v>
       </c>
       <c r="N65" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="4">
         <f>AE7</f>
         <v>0.01</v>
       </c>
-      <c r="T65" s="4">
+      <c r="Q65" s="4">
         <f>AE8</f>
         <v>0.05</v>
       </c>
-      <c r="W65" s="4">
+      <c r="T65" s="4">
         <f>AE9</f>
         <v>0.12</v>
       </c>
-      <c r="Z65" s="4">
+      <c r="W65" s="4">
         <f>AE11</f>
         <v>0.2</v>
+      </c>
+      <c r="Z65" s="4">
+        <f>AE13</f>
+        <v>0.36</v>
       </c>
       <c r="AA65" s="38"/>
       <c r="AB65" s="42"/>
@@ -10163,7 +10177,7 @@
       <c r="B66" s="56"/>
       <c r="C66" s="55"/>
       <c r="F66" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H66" s="4">
         <v>0</v>
@@ -10175,163 +10189,167 @@
         <v>0</v>
       </c>
       <c r="Q66" s="4">
-        <v>0</v>
-      </c>
-      <c r="T66" s="4">
         <f>AE7</f>
         <v>0.01</v>
       </c>
-      <c r="W66" s="4">
+      <c r="T66" s="4">
         <f>AE8</f>
         <v>0.05</v>
       </c>
-      <c r="Z66" s="4">
+      <c r="W66" s="4">
         <f>AE9</f>
         <v>0.12</v>
+      </c>
+      <c r="Z66" s="4">
+        <f>AE11</f>
+        <v>0.2</v>
       </c>
       <c r="AA66" s="38"/>
       <c r="AB66" s="42"/>
       <c r="AC66" s="43"/>
     </row>
-    <row r="67" spans="1:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B67" s="38" t="s">
-        <v>428</v>
-      </c>
-      <c r="C67" s="31" t="s">
+    <row r="67" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="B67" s="56"/>
+      <c r="C67" s="55"/>
+      <c r="F67" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H67" s="4">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4">
+        <v>0</v>
+      </c>
+      <c r="N67" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>0</v>
+      </c>
+      <c r="T67" s="4">
+        <f>AE7</f>
+        <v>0.01</v>
+      </c>
+      <c r="W67" s="4">
+        <f>AE8</f>
+        <v>0.05</v>
+      </c>
+      <c r="Z67" s="4">
+        <f>AE9</f>
+        <v>0.12</v>
+      </c>
+      <c r="AA67" s="38"/>
+      <c r="AB67" s="42"/>
+      <c r="AC67" s="43"/>
+    </row>
+    <row r="68" spans="1:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="A68" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B68" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="C68" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="F68" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="AA67" s="38" t="s">
-        <v>426</v>
-      </c>
-      <c r="AB67" s="42" t="s">
-        <v>427</v>
-      </c>
-      <c r="AC67" s="43" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="F68" s="14"/>
-      <c r="AB68" s="42"/>
-      <c r="AC68" s="43"/>
-    </row>
-    <row r="69" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="A69" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B69" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="C69" s="55" t="s">
+      <c r="AA68" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="AB68" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC68" s="43" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="F69" s="14"/>
+      <c r="AB69" s="42"/>
+      <c r="AC69" s="43"/>
+    </row>
+    <row r="70" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A70" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B70" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C70" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F70" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="H69" s="4">
-        <f>H39*H63</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="4">
-        <f>K39*K63</f>
-        <v>0.85</v>
-      </c>
-      <c r="N69" s="4">
-        <f>K69*(1- $G$31)*N39/K39+N39*N63</f>
-        <v>5.0986655000000001</v>
-      </c>
-      <c r="Q69" s="4">
-        <f>N69*(1- $G$31)*Q39/N39+Q39*Q63</f>
-        <v>15.290660595165001</v>
-      </c>
-      <c r="T69" s="4">
-        <f>Q69*(1- $G$31)*T39/Q39+T39*T63</f>
-        <v>32.266654258030592</v>
-      </c>
-      <c r="W69" s="4">
-        <f>T69*(1- $G$31)*W39/T39+W39*W63</f>
-        <v>62.815995610845476</v>
-      </c>
-      <c r="Z69" s="4">
-        <f>W69*(1- $G$31)*Z39/W39+Z39*Z63</f>
-        <v>113.71737449773646</v>
-      </c>
-      <c r="AA69" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB69" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="AC69" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="70" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="B70" s="56"/>
-      <c r="C70" s="55"/>
-      <c r="F70" s="14" t="s">
-        <v>110</v>
+      <c r="H70" s="4">
+        <f>H40*H64</f>
+        <v>0</v>
       </c>
       <c r="K70" s="4">
         <f>K40*K64</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="N70" s="4">
         <f>K70*(1- $G$31)*N40/K40+N40*N64</f>
-        <v>0.8</v>
+        <v>5.0986655000000001</v>
       </c>
       <c r="Q70" s="4">
         <f>N70*(1- $G$31)*Q40/N40+Q40*Q64</f>
-        <v>4.7987440000000001</v>
+        <v>15.290660595165001</v>
       </c>
       <c r="T70" s="4">
         <f>Q70*(1- $G$31)*T40/Q40+T40*T64</f>
-        <v>14.39120997192</v>
+        <v>32.266654258030592</v>
       </c>
       <c r="W70" s="4">
         <f>T70*(1- $G$31)*W40/T40+W40*W64</f>
-        <v>30.368615772264086</v>
+        <v>62.815995610845476</v>
       </c>
       <c r="Z70" s="4">
         <f>W70*(1- $G$31)*Z40/W40+Z40*Z64</f>
-        <v>59.120937045501627</v>
-      </c>
-      <c r="AA70" s="38"/>
-      <c r="AB70" s="42"/>
-      <c r="AC70" s="43"/>
+        <v>113.71737449773646</v>
+      </c>
+      <c r="AA70" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="AB70" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="AC70" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="71" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B71" s="56"/>
       <c r="C71" s="55"/>
-      <c r="E71" s="51"/>
       <c r="F71" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="K71" s="4">
+        <f>K41*K65</f>
+        <v>0</v>
       </c>
       <c r="N71" s="4">
-        <f>K71*(1- $G$31)+N41*N65</f>
-        <v>0</v>
+        <f>K71*(1- $G$31)*N41/K41+N41*N65</f>
+        <v>0.8</v>
       </c>
       <c r="Q71" s="4">
         <f>N71*(1- $G$31)*Q41/N41+Q41*Q65</f>
-        <v>0.92</v>
+        <v>4.7987440000000001</v>
       </c>
       <c r="T71" s="4">
         <f>Q71*(1- $G$31)*T41/Q41+T41*T65</f>
-        <v>5.5185556000000009</v>
+        <v>14.39120997192</v>
       </c>
       <c r="W71" s="4">
         <f>T71*(1- $G$31)*W41/T41+W41*W65</f>
-        <v>16.549891467708001</v>
+        <v>30.368615772264086</v>
       </c>
       <c r="Z71" s="4">
         <f>W71*(1- $G$31)*Z41/W41+Z41*Z65</f>
-        <v>34.923908138103698</v>
+        <v>59.120937045501627</v>
       </c>
       <c r="AA71" s="38"/>
       <c r="AB71" s="42"/>
@@ -10342,93 +10360,81 @@
       <c r="C72" s="55"/>
       <c r="E72" s="51"/>
       <c r="F72" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N72" s="4">
         <f>K72*(1- $G$31)+N42*N66</f>
         <v>0</v>
       </c>
       <c r="Q72" s="4">
-        <f>N72*(1- $G$31)+Q42*Q66</f>
-        <v>0</v>
+        <f>N72*(1- $G$31)*Q42/N42+Q42*Q66</f>
+        <v>0.92</v>
       </c>
       <c r="T72" s="4">
         <f>Q72*(1- $G$31)*T42/Q42+T42*T66</f>
-        <v>0.43</v>
+        <v>5.5185556000000009</v>
       </c>
       <c r="W72" s="4">
         <f>T72*(1- $G$31)*W42/T42+W42*W66</f>
-        <v>2.5793249</v>
+        <v>16.549891467708001</v>
       </c>
       <c r="Z72" s="4">
         <f>W72*(1- $G$31)*Z42/W42+Z42*Z66</f>
-        <v>7.7352753599069999</v>
+        <v>34.923908138103698</v>
       </c>
       <c r="AA72" s="38"/>
       <c r="AB72" s="42"/>
       <c r="AC72" s="43"/>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="B73" s="56"/>
+      <c r="C73" s="55"/>
       <c r="E73" s="51"/>
-      <c r="F73" s="14"/>
+      <c r="F73" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="N73" s="4">
+        <f>K73*(1- $G$31)+N43*N67</f>
+        <v>0</v>
+      </c>
+      <c r="Q73" s="4">
+        <f>N73*(1- $G$31)+Q43*Q67</f>
+        <v>0</v>
+      </c>
+      <c r="T73" s="4">
+        <f>Q73*(1- $G$31)*T43/Q43+T43*T67</f>
+        <v>0.43</v>
+      </c>
+      <c r="W73" s="4">
+        <f>T73*(1- $G$31)*W43/T43+W43*W67</f>
+        <v>2.5793249</v>
+      </c>
+      <c r="Z73" s="4">
+        <f>W73*(1- $G$31)*Z43/W43+Z43*Z67</f>
+        <v>7.7352753599069999</v>
+      </c>
+      <c r="AA73" s="38"/>
       <c r="AB73" s="42"/>
       <c r="AC73" s="43"/>
     </row>
-    <row r="74" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="A74" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B74" s="56" t="s">
-        <v>231</v>
-      </c>
-      <c r="C74" s="55" t="s">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="E74" s="51"/>
+      <c r="F74" s="14"/>
+      <c r="AB74" s="42"/>
+      <c r="AC74" s="43"/>
+    </row>
+    <row r="75" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A75" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F74" s="14" t="s">
+      <c r="F75" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="H74" s="4">
-        <v>0</v>
-      </c>
-      <c r="K74" s="4">
-        <f>INT(J$4-$AG$6 &gt; $E82)*MAX(H98-$H$23*H39-K44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N74" s="4">
-        <f>INT(M$4-$AG$6 &gt; $E82)*MAX(K98-$H$23*K39-N44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="4">
-        <f>INT(P$4-$AG$6 &gt; $E82)*MAX(N98-$H$23*N39-Q44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T74" s="4">
-        <f>INT(S$4-$AG$6 &gt; $E82)*MAX(Q98-$H$23*Q39-T44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="4">
-        <f>INT(V$4-$AG$6 &gt; $E82)*MAX(T98-$H$23*T39-W44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z74" s="4">
-        <f>INT(Y$4-$AG$6 &gt; $E82)*MAX(W98-$H$23*W39-Z44,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="AB74" s="42" t="s">
-        <v>397</v>
-      </c>
-      <c r="AC74" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="75" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="B75" s="56"/>
-      <c r="C75" s="55"/>
-      <c r="F75" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="H75" s="4">
         <v>0</v>
@@ -10457,18 +10463,21 @@
         <f>INT(Y$4-$AG$6 &gt; $E83)*MAX(W99-$H$23*W40-Z45,0)</f>
         <v>0</v>
       </c>
-      <c r="AA75" s="38"/>
-      <c r="AB75" s="42"/>
-      <c r="AC75" s="43"/>
+      <c r="AA75" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="AB75" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="AC75" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="76" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B76" s="56"/>
       <c r="C76" s="55"/>
-      <c r="E76" s="51" t="s">
-        <v>152</v>
-      </c>
       <c r="F76" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H76" s="4">
         <v>0</v>
@@ -10504,9 +10513,11 @@
     <row r="77" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="B77" s="56"/>
       <c r="C77" s="55"/>
-      <c r="E77" s="51"/>
+      <c r="E77" s="51" t="s">
+        <v>152</v>
+      </c>
       <c r="F77" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H77" s="4">
         <v>0</v>
@@ -10540,518 +10551,483 @@
       <c r="AC77" s="43"/>
     </row>
     <row r="78" spans="1:32" ht="34" x14ac:dyDescent="0.2">
-      <c r="A78" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B78" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="C78" s="28" t="s">
-        <v>174</v>
-      </c>
+      <c r="B78" s="56"/>
+      <c r="C78" s="55"/>
       <c r="E78" s="51"/>
       <c r="F78" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H78" s="4">
+        <v>0</v>
+      </c>
+      <c r="K78" s="4">
+        <f>INT(J$4-$AG$6 &gt; $E86)*MAX(H102-$H$23*H43-K48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N78" s="4">
+        <f>INT(M$4-$AG$6 &gt; $E86)*MAX(K102-$H$23*K43-N48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q78" s="4">
+        <f>INT(P$4-$AG$6 &gt; $E86)*MAX(N102-$H$23*N43-Q48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T78" s="4">
+        <f>INT(S$4-$AG$6 &gt; $E86)*MAX(Q102-$H$23*Q43-T48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W78" s="4">
+        <f>INT(V$4-$AG$6 &gt; $E86)*MAX(T102-$H$23*T43-W48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="4">
+        <f>INT(Y$4-$AG$6 &gt; $E86)*MAX(W102-$H$23*W43-Z48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA78" s="38"/>
+      <c r="AB78" s="42"/>
+      <c r="AC78" s="43"/>
+    </row>
+    <row r="79" spans="1:32" ht="34" x14ac:dyDescent="0.2">
+      <c r="A79" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B79" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E79" s="51"/>
+      <c r="F79" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="H78" s="4">
-        <v>0</v>
-      </c>
-      <c r="K78" s="4">
-        <f>SUM(K74:K77)</f>
-        <v>0</v>
-      </c>
-      <c r="N78" s="4">
-        <f>SUM(N74:N77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q78" s="4">
-        <f>SUM(Q74:Q77)</f>
-        <v>0</v>
-      </c>
-      <c r="T78" s="4">
-        <f>SUM(T74:T77)</f>
-        <v>0</v>
-      </c>
-      <c r="W78" s="4">
-        <f>SUM(W74:W77)</f>
-        <v>0</v>
-      </c>
-      <c r="Z78" s="4">
-        <f>SUM(Z74:Z77)</f>
-        <v>0</v>
-      </c>
-      <c r="AA78" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="AB78" s="42" t="s">
-        <v>408</v>
-      </c>
-      <c r="AC78" s="43" t="s">
-        <v>347</v>
-      </c>
-      <c r="AF78" t="s">
+      <c r="H79" s="4">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4">
+        <f>SUM(K75:K78)</f>
+        <v>0</v>
+      </c>
+      <c r="N79" s="4">
+        <f>SUM(N75:N78)</f>
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4">
+        <f>SUM(Q75:Q78)</f>
+        <v>0</v>
+      </c>
+      <c r="T79" s="4">
+        <f>SUM(T75:T78)</f>
+        <v>0</v>
+      </c>
+      <c r="W79" s="4">
+        <f>SUM(W75:W78)</f>
+        <v>0</v>
+      </c>
+      <c r="Z79" s="4">
+        <f>SUM(Z75:Z78)</f>
+        <v>0</v>
+      </c>
+      <c r="AA79" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="AB79" s="42" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC79" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF79" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="E79" s="51"/>
-      <c r="F79" s="14"/>
-      <c r="AB79" s="42"/>
-      <c r="AC79" s="43"/>
-      <c r="AD79" t="s">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="E80" s="51"/>
+      <c r="F80" s="14"/>
+      <c r="AB80" s="42"/>
+      <c r="AC80" s="43"/>
+      <c r="AD80" t="s">
         <v>85</v>
       </c>
-      <c r="AF79" t="s">
+      <c r="AF80" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B80" s="37" t="s">
-        <v>435</v>
-      </c>
-      <c r="C80" s="55" t="s">
+    <row r="81" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B81" s="37" t="s">
+        <v>432</v>
+      </c>
+      <c r="C81" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F81" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G80" s="4">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4">
-        <v>0</v>
-      </c>
-      <c r="M80" s="4">
-        <v>0</v>
-      </c>
-      <c r="P80" s="4">
-        <v>0</v>
-      </c>
-      <c r="S80" s="4">
-        <v>0</v>
-      </c>
-      <c r="V80" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="AB80" s="42" t="s">
-        <v>398</v>
-      </c>
-      <c r="AC80" s="43" t="s">
-        <v>346</v>
-      </c>
-      <c r="AD80" t="s">
+      <c r="G81" s="4">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0</v>
+      </c>
+      <c r="M81" s="4">
+        <v>0</v>
+      </c>
+      <c r="P81" s="4">
+        <v>0</v>
+      </c>
+      <c r="S81" s="4">
+        <v>0</v>
+      </c>
+      <c r="V81" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB81" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC81" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="AD81" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A81" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B81" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="C81" s="55"/>
-      <c r="F81" s="14" t="s">
+    <row r="82" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A82" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B82" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="C82" s="55"/>
+      <c r="F82" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G81" s="4">
-        <f>SUM(H$74:H74)</f>
-        <v>0</v>
-      </c>
-      <c r="H81" s="4">
-        <f>IF(G81&gt;=G$134, IF(G80&lt;G$134, G$134-G80, 0),H74)</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="4">
-        <f>SUM(K$74:K74)</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="4">
-        <f>IF(J81&gt;=J$134, IF(J80&lt;J$134, J$134-J80, 0),K74)</f>
-        <v>0</v>
-      </c>
-      <c r="M81" s="4">
-        <f>SUM(N$74:N74)</f>
-        <v>0</v>
-      </c>
-      <c r="N81" s="4">
-        <f>IF(M81&gt;=M$134, IF(M80&lt;M$134, M$134-M80, 0),N74)</f>
-        <v>0</v>
-      </c>
-      <c r="P81" s="4">
-        <f>SUM(Q$74:Q74)</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="4">
-        <f>IF(P81&gt;=P$134, IF(P80&lt;P$134, P$134-P80, 0),Q74)</f>
-        <v>0</v>
-      </c>
-      <c r="S81" s="4">
-        <f>SUM(T$74:T74)</f>
-        <v>0</v>
-      </c>
-      <c r="T81" s="4">
-        <f>IF(S81&gt;=S$134, IF(S80&lt;S$134, S$134-S80, 0),T74)</f>
-        <v>0</v>
-      </c>
-      <c r="V81" s="4">
-        <f>SUM(W$74:W74)</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="4">
-        <f>IF(V81&gt;=V$134, IF(V80&lt;V$134, V$134-V80, 0),W74)</f>
-        <v>0</v>
-      </c>
-      <c r="Y81" s="4">
-        <f>SUM(Z$74:Z74)</f>
-        <v>0</v>
-      </c>
-      <c r="Z81" s="4">
-        <f>IF(Y81&gt;=Y$134, IF(Y80&lt;Y$134, Y$134-Y80, 0),Z74)</f>
-        <v>0</v>
-      </c>
-      <c r="AA81" s="38" t="s">
-        <v>443</v>
-      </c>
-      <c r="AB81" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="AC81" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="82" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="B82" s="41"/>
-      <c r="C82" s="55"/>
-      <c r="E82" s="22">
-        <v>0</v>
-      </c>
-      <c r="F82" s="14" t="s">
-        <v>149</v>
-      </c>
       <c r="G82" s="4">
-        <f>SUM(H$74:H75)</f>
+        <f>SUM(H$75:H75)</f>
         <v>0</v>
       </c>
       <c r="H82" s="4">
-        <f>IF(G82&gt;=G$134, IF(G81&lt;G$134, G$134-G81, 0),H75)</f>
+        <f>IF(G82&gt;=G$136, IF(G81&lt;G$136, G$136-G81, 0),H75)</f>
         <v>0</v>
       </c>
       <c r="J82" s="4">
-        <f>SUM(K$74:K75)</f>
+        <f>SUM(K$75:K75)</f>
         <v>0</v>
       </c>
       <c r="K82" s="4">
-        <f>IF(J82&gt;=J$134, IF(J81&lt;J$134, J$134-J81, 0),K75)</f>
+        <f>IF(J82&gt;=J$136, IF(J81&lt;J$136, J$136-J81, 0),K75)</f>
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <f>SUM(N$74:N75)</f>
+        <f>SUM(N$75:N75)</f>
         <v>0</v>
       </c>
       <c r="N82" s="4">
-        <f>IF(M82&gt;=M$134, IF(M81&lt;M$134, M$134-M81, 0),N75)</f>
+        <f>IF(M82&gt;=M$136, IF(M81&lt;M$136, M$136-M81, 0),N75)</f>
         <v>0</v>
       </c>
       <c r="P82" s="4">
-        <f>SUM(Q$74:Q75)</f>
+        <f>SUM(Q$75:Q75)</f>
         <v>0</v>
       </c>
       <c r="Q82" s="4">
-        <f>IF(P82&gt;=P$134, IF(P81&lt;P$134, P$134-P81, 0),Q75)</f>
+        <f>IF(P82&gt;=P$136, IF(P81&lt;P$136, P$136-P81, 0),Q75)</f>
         <v>0</v>
       </c>
       <c r="S82" s="4">
-        <f>SUM(T$74:T75)</f>
+        <f>SUM(T$75:T75)</f>
         <v>0</v>
       </c>
       <c r="T82" s="4">
-        <f>IF(S82&gt;=S$134, IF(S81&lt;S$134, S$134-S81, 0),T75)</f>
+        <f>IF(S82&gt;=S$136, IF(S81&lt;S$136, S$136-S81, 0),T75)</f>
         <v>0</v>
       </c>
       <c r="V82" s="4">
-        <f>SUM(W$74:W75)</f>
+        <f>SUM(W$75:W75)</f>
         <v>0</v>
       </c>
       <c r="W82" s="4">
-        <f>IF(V82&gt;=V$134, IF(V81&lt;V$134, V$134-V81, 0),W75)</f>
+        <f>IF(V82&gt;=V$136, IF(V81&lt;V$136, V$136-V81, 0),W75)</f>
         <v>0</v>
       </c>
       <c r="Y82" s="4">
-        <f>SUM(Z$74:Z75)</f>
+        <f>SUM(Z$75:Z75)</f>
         <v>0</v>
       </c>
       <c r="Z82" s="4">
-        <f>IF(Y82&gt;=Y$134, IF(Y81&lt;Y$134, Y$134-Y81, 0),Z75)</f>
-        <v>0</v>
-      </c>
-      <c r="AA82" s="37"/>
-      <c r="AB82" s="42"/>
-      <c r="AC82" s="43"/>
-    </row>
-    <row r="83" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+        <f>IF(Y82&gt;=Y$136, IF(Y81&lt;Y$136, Y$136-Y81, 0),Z75)</f>
+        <v>0</v>
+      </c>
+      <c r="AA82" s="38" t="s">
+        <v>440</v>
+      </c>
+      <c r="AB82" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="AC82" s="43" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B83" s="41"/>
       <c r="C83" s="55"/>
       <c r="E83" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G83" s="4">
-        <f>SUM(H$74:H76)</f>
+        <f>SUM(H$75:H76)</f>
         <v>0</v>
       </c>
       <c r="H83" s="4">
-        <f>IF(G83&gt;=G$134, IF(G82&lt;G$134, G$134-G82, 0),H76)</f>
+        <f>IF(G83&gt;=G$136, IF(G82&lt;G$136, G$136-G82, 0),H76)</f>
         <v>0</v>
       </c>
       <c r="J83" s="4">
-        <f>SUM(K$74:K76)</f>
+        <f>SUM(K$75:K76)</f>
         <v>0</v>
       </c>
       <c r="K83" s="4">
-        <f>IF(J83&gt;=J$134, IF(J82&lt;J$134, J$134-J82, 0),K76)</f>
+        <f>IF(J83&gt;=J$136, IF(J82&lt;J$136, J$136-J82, 0),K76)</f>
         <v>0</v>
       </c>
       <c r="M83" s="4">
-        <f>SUM(N$74:N76)</f>
+        <f>SUM(N$75:N76)</f>
         <v>0</v>
       </c>
       <c r="N83" s="4">
-        <f>IF(M83&gt;=M$134, IF(M82&lt;M$134, M$134-M82, 0),N76)</f>
+        <f>IF(M83&gt;=M$136, IF(M82&lt;M$136, M$136-M82, 0),N76)</f>
         <v>0</v>
       </c>
       <c r="P83" s="4">
-        <f>SUM(Q$74:Q76)</f>
+        <f>SUM(Q$75:Q76)</f>
         <v>0</v>
       </c>
       <c r="Q83" s="4">
-        <f>IF(P83&gt;=P$134, IF(P82&lt;P$134, P$134-P82, 0),Q76)</f>
+        <f>IF(P83&gt;=P$136, IF(P82&lt;P$136, P$136-P82, 0),Q76)</f>
         <v>0</v>
       </c>
       <c r="S83" s="4">
-        <f>SUM(T$74:T76)</f>
+        <f>SUM(T$75:T76)</f>
         <v>0</v>
       </c>
       <c r="T83" s="4">
-        <f>IF(S83&gt;=S$134, IF(S82&lt;S$134, S$134-S82, 0),T76)</f>
+        <f>IF(S83&gt;=S$136, IF(S82&lt;S$136, S$136-S82, 0),T76)</f>
         <v>0</v>
       </c>
       <c r="V83" s="4">
-        <f>SUM(W$74:W76)</f>
+        <f>SUM(W$75:W76)</f>
         <v>0</v>
       </c>
       <c r="W83" s="4">
-        <f>IF(V83&gt;=V$134, IF(V82&lt;V$134, V$134-V82, 0),W76)</f>
+        <f>IF(V83&gt;=V$136, IF(V82&lt;V$136, V$136-V82, 0),W76)</f>
         <v>0</v>
       </c>
       <c r="Y83" s="4">
-        <f>SUM(Z$74:Z76)</f>
+        <f>SUM(Z$75:Z76)</f>
         <v>0</v>
       </c>
       <c r="Z83" s="4">
-        <f>IF(Y83&gt;=Y$134, IF(Y82&lt;Y$134, Y$134-Y82, 0),Z76)</f>
+        <f>IF(Y83&gt;=Y$136, IF(Y82&lt;Y$136, Y$136-Y82, 0),Z76)</f>
         <v>0</v>
       </c>
       <c r="AA83" s="37"/>
       <c r="AB83" s="42"/>
       <c r="AC83" s="43"/>
     </row>
-    <row r="84" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="B84" s="41"/>
       <c r="C84" s="55"/>
       <c r="E84" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G84" s="4">
-        <f>SUM(H$74:H77)</f>
+        <f>SUM(H$75:H77)</f>
         <v>0</v>
       </c>
       <c r="H84" s="4">
-        <f>IF(G84&gt;=G$134, IF(G83&lt;G$134, G$134-G83, 0),H77)</f>
+        <f>IF(G84&gt;=G$136, IF(G83&lt;G$136, G$136-G83, 0),H77)</f>
         <v>0</v>
       </c>
       <c r="J84" s="4">
-        <f>SUM(K$74:K77)</f>
+        <f>SUM(K$75:K77)</f>
         <v>0</v>
       </c>
       <c r="K84" s="4">
-        <f>IF(J84&gt;=J$134, IF(J83&lt;J$134, J$134-J83, 0),K77)</f>
+        <f>IF(J84&gt;=J$136, IF(J83&lt;J$136, J$136-J83, 0),K77)</f>
         <v>0</v>
       </c>
       <c r="M84" s="4">
-        <f>SUM(N$74:N77)</f>
+        <f>SUM(N$75:N77)</f>
         <v>0</v>
       </c>
       <c r="N84" s="4">
-        <f>IF(M84&gt;=M$134, IF(M83&lt;M$134, M$134-M83, 0),N77)</f>
+        <f>IF(M84&gt;=M$136, IF(M83&lt;M$136, M$136-M83, 0),N77)</f>
         <v>0</v>
       </c>
       <c r="P84" s="4">
-        <f>SUM(Q$74:Q77)</f>
+        <f>SUM(Q$75:Q77)</f>
         <v>0</v>
       </c>
       <c r="Q84" s="4">
-        <f>IF(P84&gt;=P$134, IF(P83&lt;P$134, P$134-P83, 0),Q77)</f>
+        <f>IF(P84&gt;=P$136, IF(P83&lt;P$136, P$136-P83, 0),Q77)</f>
         <v>0</v>
       </c>
       <c r="S84" s="4">
-        <f>SUM(T$74:T77)</f>
+        <f>SUM(T$75:T77)</f>
         <v>0</v>
       </c>
       <c r="T84" s="4">
-        <f>IF(S84&gt;=S$134, IF(S83&lt;S$134, S$134-S83, 0),T77)</f>
+        <f>IF(S84&gt;=S$136, IF(S83&lt;S$136, S$136-S83, 0),T77)</f>
         <v>0</v>
       </c>
       <c r="V84" s="4">
-        <f>SUM(W$74:W77)</f>
+        <f>SUM(W$75:W77)</f>
         <v>0</v>
       </c>
       <c r="W84" s="4">
-        <f>IF(V84&gt;=V$134, IF(V83&lt;V$134, V$134-V83, 0),W77)</f>
+        <f>IF(V84&gt;=V$136, IF(V83&lt;V$136, V$136-V83, 0),W77)</f>
         <v>0</v>
       </c>
       <c r="Y84" s="4">
-        <f>SUM(Z$74:Z77)</f>
+        <f>SUM(Z$75:Z77)</f>
         <v>0</v>
       </c>
       <c r="Z84" s="4">
-        <f>IF(Y84&gt;=Y$134, IF(Y83&lt;Y$134, Y$134-Y83, 0),Z77)</f>
+        <f>IF(Y84&gt;=Y$136, IF(Y83&lt;Y$136, Y$136-Y83, 0),Z77)</f>
         <v>0</v>
       </c>
       <c r="AA84" s="37"/>
       <c r="AB84" s="42"/>
       <c r="AC84" s="43"/>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B85" s="41"/>
+      <c r="C85" s="55"/>
       <c r="E85" s="22">
-        <v>3</v>
-      </c>
-      <c r="F85" s="14"/>
+        <v>2</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G85" s="4">
+        <f>SUM(H$75:H78)</f>
+        <v>0</v>
+      </c>
+      <c r="H85" s="4">
+        <f>IF(G85&gt;=G$136, IF(G84&lt;G$136, G$136-G84, 0),H78)</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="4">
+        <f>SUM(K$75:K78)</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="4">
+        <f>IF(J85&gt;=J$136, IF(J84&lt;J$136, J$136-J84, 0),K78)</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="4">
+        <f>SUM(N$75:N78)</f>
+        <v>0</v>
+      </c>
+      <c r="N85" s="4">
+        <f>IF(M85&gt;=M$136, IF(M84&lt;M$136, M$136-M84, 0),N78)</f>
+        <v>0</v>
+      </c>
+      <c r="P85" s="4">
+        <f>SUM(Q$75:Q78)</f>
+        <v>0</v>
+      </c>
+      <c r="Q85" s="4">
+        <f>IF(P85&gt;=P$136, IF(P84&lt;P$136, P$136-P84, 0),Q78)</f>
+        <v>0</v>
+      </c>
+      <c r="S85" s="4">
+        <f>SUM(T$75:T78)</f>
+        <v>0</v>
+      </c>
+      <c r="T85" s="4">
+        <f>IF(S85&gt;=S$136, IF(S84&lt;S$136, S$136-S84, 0),T78)</f>
+        <v>0</v>
+      </c>
+      <c r="V85" s="4">
+        <f>SUM(W$75:W78)</f>
+        <v>0</v>
+      </c>
+      <c r="W85" s="4">
+        <f>IF(V85&gt;=V$136, IF(V84&lt;V$136, V$136-V84, 0),W78)</f>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="4">
+        <f>SUM(Z$75:Z78)</f>
+        <v>0</v>
+      </c>
+      <c r="Z85" s="4">
+        <f>IF(Y85&gt;=Y$136, IF(Y84&lt;Y$136, Y$136-Y84, 0),Z78)</f>
+        <v>0</v>
+      </c>
+      <c r="AA85" s="37"/>
       <c r="AB85" s="42"/>
       <c r="AC85" s="43"/>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="E86" s="22">
+        <v>3</v>
+      </c>
       <c r="F86" s="14"/>
-      <c r="J86" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="M86" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="S86" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="V86" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y86" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="AB86" s="42"/>
       <c r="AC86" s="43"/>
     </row>
-    <row r="87" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A87" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B87" s="37" t="s">
-        <v>433</v>
-      </c>
-      <c r="C87" s="55" t="s">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="F87" s="14"/>
+      <c r="J87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="S87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="V87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y87" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB87" s="42"/>
+      <c r="AC87" s="43"/>
+    </row>
+    <row r="88" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A88" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B88" s="37" t="s">
+        <v>430</v>
+      </c>
+      <c r="C88" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F87" s="14" t="s">
+      <c r="F88" s="14" t="s">
         <v>131</v>
-      </c>
-      <c r="H87" s="4">
-        <f>H63</f>
-        <v>0</v>
-      </c>
-      <c r="J87" s="4">
-        <f>IF(H98=0,1,MIN(MAX((H98/H69-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="K87" s="4">
-        <f>K63*J87</f>
-        <v>0.01</v>
-      </c>
-      <c r="M87" s="4">
-        <f>IF(K98=0,1,MIN(MAX((K98/K69-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="N87" s="4">
-        <f>N63*M87</f>
-        <v>0.05</v>
-      </c>
-      <c r="P87" s="4">
-        <f>IF(N98=0,1,MIN(MAX((N98/N69-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="Q87" s="4">
-        <f>Q63*P87</f>
-        <v>0.12</v>
-      </c>
-      <c r="S87" s="4">
-        <f>IF(Q98=0,1,MIN(MAX((Q98/Q69-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="T87" s="4">
-        <f>T63*S87</f>
-        <v>0.2</v>
-      </c>
-      <c r="V87" s="4">
-        <f>IF(T98=0,1,MIN(MAX((T98/T69-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="W87" s="4">
-        <f>W63*V87</f>
-        <v>0.36</v>
-      </c>
-      <c r="Y87" s="4">
-        <f>IF(W98=0,1,MIN(MAX((W98/W69-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="Z87" s="4">
-        <f>Z63*Y87</f>
-        <v>0.6</v>
-      </c>
-      <c r="AA87" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="AB87" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="AC87" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A88" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B88" s="37" t="s">
-        <v>432</v>
-      </c>
-      <c r="C88" s="55"/>
-      <c r="F88" s="14" t="s">
-        <v>132</v>
       </c>
       <c r="H88" s="4">
         <f>H64</f>
@@ -11062,64 +11038,69 @@
         <v>1</v>
       </c>
       <c r="K88" s="4">
-        <f>K64</f>
-        <v>0</v>
+        <f>K64*J88</f>
+        <v>0.01</v>
       </c>
       <c r="M88" s="4">
         <f>IF(K99=0,1,MIN(MAX((K99/K70-$G$18)/($G$20-$G$18), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="N88" s="4">
-        <f>N64</f>
-        <v>0.01</v>
+        <f>N64*M88</f>
+        <v>0.05</v>
       </c>
       <c r="P88" s="4">
         <f>IF(N99=0,1,MIN(MAX((N99/N70-$G$18)/($G$20-$G$18), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Q88" s="4">
-        <f>Q64</f>
-        <v>0.05</v>
+        <f>Q64*P88</f>
+        <v>0.12</v>
       </c>
       <c r="S88" s="4">
         <f>IF(Q99=0,1,MIN(MAX((Q99/Q70-$G$18)/($G$20-$G$18), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="T88" s="4">
-        <f>T64</f>
-        <v>0.12</v>
+        <f>T64*S88</f>
+        <v>0.2</v>
       </c>
       <c r="V88" s="4">
         <f>IF(T99=0,1,MIN(MAX((T99/T70-$G$18)/($G$20-$G$18), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="W88" s="4">
-        <f>W64</f>
-        <v>0.2</v>
+        <f>W64*V88</f>
+        <v>0.36</v>
       </c>
       <c r="Y88" s="4">
         <f>IF(W99=0,1,MIN(MAX((W99/W70-$G$18)/($G$20-$G$18), 0), 1))</f>
         <v>1</v>
       </c>
       <c r="Z88" s="4">
-        <f>Z64</f>
-        <v>0.36</v>
+        <f>Z64*Y88</f>
+        <v>0.6</v>
       </c>
       <c r="AA88" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AB88" s="42" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="AC88" s="43" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="89" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="B89" s="37"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A89" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B89" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="C89" s="55"/>
       <c r="F89" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H89" s="4">
         <f>H65</f>
@@ -11139,7 +11120,7 @@
       </c>
       <c r="N89" s="4">
         <f>N65</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P89" s="4">
         <f>IF(N100=0,1,MIN(MAX((N100/N71-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11147,7 +11128,7 @@
       </c>
       <c r="Q89" s="4">
         <f>Q65</f>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="S89" s="4">
         <f>IF(Q100=0,1,MIN(MAX((Q100/Q71-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11155,7 +11136,7 @@
       </c>
       <c r="T89" s="4">
         <f>T65</f>
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="V89" s="4">
         <f>IF(T100=0,1,MIN(MAX((T100/T71-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11163,7 +11144,7 @@
       </c>
       <c r="W89" s="4">
         <f>W65</f>
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="Y89" s="4">
         <f>IF(W100=0,1,MIN(MAX((W100/W71-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11171,17 +11152,23 @@
       </c>
       <c r="Z89" s="4">
         <f>Z65</f>
-        <v>0.2</v>
-      </c>
-      <c r="AA89" s="37"/>
-      <c r="AB89" s="42"/>
-      <c r="AC89" s="43"/>
-    </row>
-    <row r="90" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="B90" s="41"/>
+        <v>0.36</v>
+      </c>
+      <c r="AA89" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="AB89" s="42" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC89" s="43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B90" s="37"/>
       <c r="C90" s="55"/>
       <c r="F90" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H90" s="4">
         <f>H66</f>
@@ -11209,7 +11196,7 @@
       </c>
       <c r="Q90" s="4">
         <f>Q66</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S90" s="4">
         <f>IF(Q101=0,1,MIN(MAX((Q101/Q72-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11217,7 +11204,7 @@
       </c>
       <c r="T90" s="4">
         <f>T66</f>
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="V90" s="4">
         <f>IF(T101=0,1,MIN(MAX((T101/T72-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11225,7 +11212,7 @@
       </c>
       <c r="W90" s="4">
         <f>W66</f>
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="Y90" s="4">
         <f>IF(W101=0,1,MIN(MAX((W101/W72-$G$18)/($G$20-$G$18), 0), 1))</f>
@@ -11233,76 +11220,94 @@
       </c>
       <c r="Z90" s="4">
         <f>Z66</f>
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="AA90" s="37"/>
       <c r="AB90" s="42"/>
       <c r="AC90" s="43"/>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F91" s="14"/>
+    <row r="91" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B91" s="41"/>
+      <c r="C91" s="55"/>
+      <c r="F91" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H91" s="4">
+        <f>H67</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="4">
+        <f>IF(H102=0,1,MIN(MAX((H102/H73-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="K91" s="4">
+        <f>K67</f>
+        <v>0</v>
+      </c>
+      <c r="M91" s="4">
+        <f>IF(K102=0,1,MIN(MAX((K102/K73-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="N91" s="4">
+        <f>N67</f>
+        <v>0</v>
+      </c>
+      <c r="P91" s="4">
+        <f>IF(N102=0,1,MIN(MAX((N102/N73-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="Q91" s="4">
+        <f>Q67</f>
+        <v>0</v>
+      </c>
+      <c r="S91" s="4">
+        <f>IF(Q102=0,1,MIN(MAX((Q102/Q73-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="T91" s="4">
+        <f>T67</f>
+        <v>0.01</v>
+      </c>
+      <c r="V91" s="4">
+        <f>IF(T102=0,1,MIN(MAX((T102/T73-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="W91" s="4">
+        <f>W67</f>
+        <v>0.05</v>
+      </c>
+      <c r="Y91" s="4">
+        <f>IF(W102=0,1,MIN(MAX((W102/W73-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
+      </c>
+      <c r="Z91" s="4">
+        <f>Z67</f>
+        <v>0.12</v>
+      </c>
+      <c r="AA91" s="37"/>
       <c r="AB91" s="42"/>
       <c r="AC91" s="43"/>
     </row>
-    <row r="92" spans="1:29" ht="51" x14ac:dyDescent="0.2">
-      <c r="A92" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B92" s="57" t="s">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="F92" s="14"/>
+      <c r="AB92" s="42"/>
+      <c r="AC92" s="43"/>
+    </row>
+    <row r="93" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+      <c r="A93" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B93" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="C92" s="55" t="s">
+      <c r="C93" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F92" s="14" t="s">
+      <c r="F93" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="H92" s="4">
-        <f>H58*H34</f>
-        <v>0</v>
-      </c>
-      <c r="K92" s="4">
-        <f>(H98-K81-K44)*$G$31</f>
-        <v>0</v>
-      </c>
-      <c r="N92" s="4">
-        <f>(K98-N81-N44)*$G$31</f>
-        <v>1.3345E-3</v>
-      </c>
-      <c r="Q92" s="4">
-        <f>(N98-Q81-Q44)*$G$31</f>
-        <v>8.0049048349999999E-3</v>
-      </c>
-      <c r="T92" s="4">
-        <f>(Q98-T81-T44)*$G$31</f>
-        <v>2.4006337134409049E-2</v>
-      </c>
-      <c r="W92" s="4">
-        <f>(T98-W81-W44)*$G$31</f>
-        <v>5.0658647185108027E-2</v>
-      </c>
-      <c r="Z92" s="4">
-        <f>(W98-Z81-Z44)*$G$31</f>
-        <v>9.8621113109027395E-2</v>
-      </c>
-      <c r="AA92" s="37" t="s">
-        <v>459</v>
-      </c>
-      <c r="AB92" s="42" t="s">
-        <v>401</v>
-      </c>
-      <c r="AC92" s="43" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="93" spans="1:29" ht="51" x14ac:dyDescent="0.2">
-      <c r="B93" s="57"/>
-      <c r="C93" s="55"/>
-      <c r="F93" s="14" t="s">
-        <v>204</v>
-      </c>
       <c r="H93" s="4">
-        <f>H59*H35</f>
+        <f>H59*H34</f>
         <v>0</v>
       </c>
       <c r="K93" s="4">
@@ -11311,33 +11316,39 @@
       </c>
       <c r="N93" s="4">
         <f>(K99-N82-N45)*$G$31</f>
-        <v>0</v>
+        <v>1.3345E-3</v>
       </c>
       <c r="Q93" s="4">
         <f>(N99-Q82-Q45)*$G$31</f>
-        <v>1.2560000000000002E-3</v>
+        <v>8.0049048349999999E-3</v>
       </c>
       <c r="T93" s="4">
         <f>(Q99-T82-T45)*$G$31</f>
-        <v>7.5340280800000005E-3</v>
+        <v>2.4006337134409049E-2</v>
       </c>
       <c r="W93" s="4">
         <f>(T99-W82-W45)*$G$31</f>
-        <v>2.2594199655914398E-2</v>
+        <v>5.0658647185108027E-2</v>
       </c>
       <c r="Z93" s="4">
         <f>(W99-Z82-Z45)*$G$31</f>
-        <v>4.7678726762454618E-2</v>
-      </c>
-      <c r="AA93" s="37"/>
-      <c r="AB93" s="42"/>
-      <c r="AC93" s="43"/>
-    </row>
-    <row r="94" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+        <v>9.8621113109027395E-2</v>
+      </c>
+      <c r="AA93" s="37" t="s">
+        <v>456</v>
+      </c>
+      <c r="AB93" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="AC93" s="43" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="B94" s="57"/>
       <c r="C94" s="55"/>
       <c r="F94" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H94" s="4">
         <f>H60*H36</f>
@@ -11353,29 +11364,29 @@
       </c>
       <c r="Q94" s="4">
         <f>(N100-Q83-Q46)*$G$31</f>
-        <v>0</v>
+        <v>1.2560000000000002E-3</v>
       </c>
       <c r="T94" s="4">
         <f>(Q100-T83-T46)*$G$31</f>
-        <v>1.4444E-3</v>
+        <v>7.5340280800000005E-3</v>
       </c>
       <c r="W94" s="4">
         <f>(T100-W83-W46)*$G$31</f>
-        <v>8.664132292000002E-3</v>
+        <v>2.2594199655914398E-2</v>
       </c>
       <c r="Z94" s="4">
         <f>(W100-Z83-Z46)*$G$31</f>
-        <v>2.5983329604301563E-2</v>
+        <v>4.7678726762454618E-2</v>
       </c>
       <c r="AA94" s="37"/>
       <c r="AB94" s="42"/>
       <c r="AC94" s="43"/>
     </row>
-    <row r="95" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="B95" s="57"/>
       <c r="C95" s="55"/>
       <c r="F95" s="14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H95" s="4">
         <f>H61*H37</f>
@@ -11395,128 +11406,122 @@
       </c>
       <c r="T95" s="4">
         <f>(Q101-T84-T47)*$G$31</f>
-        <v>0</v>
+        <v>1.4444E-3</v>
       </c>
       <c r="W95" s="4">
         <f>(T101-W84-W47)*$G$31</f>
-        <v>6.7509999999999998E-4</v>
+        <v>8.664132292000002E-3</v>
       </c>
       <c r="Z95" s="4">
         <f>(W101-Z84-Z47)*$G$31</f>
-        <v>4.049540093E-3</v>
+        <v>2.5983329604301563E-2</v>
       </c>
       <c r="AA95" s="37"/>
       <c r="AB95" s="42"/>
       <c r="AC95" s="43"/>
     </row>
-    <row r="96" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B96" s="37" t="s">
+    <row r="96" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+      <c r="B96" s="57"/>
+      <c r="C96" s="55"/>
+      <c r="F96" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H96" s="4">
+        <f>H62*H38</f>
+        <v>0</v>
+      </c>
+      <c r="K96" s="4">
+        <f>(H102-K85-K48)*$G$31</f>
+        <v>0</v>
+      </c>
+      <c r="N96" s="4">
+        <f>(K102-N85-N48)*$G$31</f>
+        <v>0</v>
+      </c>
+      <c r="Q96" s="4">
+        <f>(N102-Q85-Q48)*$G$31</f>
+        <v>0</v>
+      </c>
+      <c r="T96" s="4">
+        <f>(Q102-T85-T48)*$G$31</f>
+        <v>0</v>
+      </c>
+      <c r="W96" s="4">
+        <f>(T102-W85-W48)*$G$31</f>
+        <v>6.7509999999999998E-4</v>
+      </c>
+      <c r="Z96" s="4">
+        <f>(W102-Z85-Z48)*$G$31</f>
+        <v>4.049540093E-3</v>
+      </c>
+      <c r="AA96" s="37"/>
+      <c r="AB96" s="42"/>
+      <c r="AC96" s="43"/>
+    </row>
+    <row r="97" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B97" s="37" t="s">
+        <v>452</v>
+      </c>
+      <c r="C97" s="28"/>
+      <c r="F97" s="14"/>
+      <c r="H97" s="4">
+        <f>SUM(H93:H96)</f>
+        <v>0</v>
+      </c>
+      <c r="K97" s="4">
+        <f>SUM(K93:K96)</f>
+        <v>0</v>
+      </c>
+      <c r="N97" s="4">
+        <f>SUM(N93:N96)</f>
+        <v>1.3345E-3</v>
+      </c>
+      <c r="Q97" s="4">
+        <f>SUM(Q93:Q96)</f>
+        <v>9.2609048350000001E-3</v>
+      </c>
+      <c r="T97" s="4">
+        <f>SUM(T93:T96)</f>
+        <v>3.2984765214409045E-2</v>
+      </c>
+      <c r="W97" s="4">
+        <f>SUM(W93:W96)</f>
+        <v>8.2592079133022425E-2</v>
+      </c>
+      <c r="Z97" s="4">
+        <f>SUM(Z93:Z96)</f>
+        <v>0.17633270956878355</v>
+      </c>
+      <c r="AA97" s="37" t="s">
         <v>455</v>
       </c>
-      <c r="C96" s="28"/>
-      <c r="F96" s="14"/>
-      <c r="H96" s="4">
-        <f>SUM(H92:H95)</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="4">
-        <f>SUM(K92:K95)</f>
-        <v>0</v>
-      </c>
-      <c r="N96" s="4">
-        <f>SUM(N92:N95)</f>
-        <v>1.3345E-3</v>
-      </c>
-      <c r="Q96" s="4">
-        <f>SUM(Q92:Q95)</f>
-        <v>9.2609048350000001E-3</v>
-      </c>
-      <c r="T96" s="4">
-        <f>SUM(T92:T95)</f>
-        <v>3.2984765214409045E-2</v>
-      </c>
-      <c r="W96" s="4">
-        <f>SUM(W92:W95)</f>
-        <v>8.2592079133022425E-2</v>
-      </c>
-      <c r="Z96" s="4">
-        <f>SUM(Z92:Z95)</f>
-        <v>0.17633270956878355</v>
-      </c>
-      <c r="AA96" s="37" t="s">
-        <v>458</v>
-      </c>
-      <c r="AB96" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="AC96" s="43" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F97" s="14"/>
-      <c r="AB97" s="42"/>
-      <c r="AC97" s="43"/>
-    </row>
-    <row r="98" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A98" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B98" s="57" t="s">
+      <c r="AB97" s="42" t="s">
+        <v>453</v>
+      </c>
+      <c r="AC97" s="43" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F98" s="14"/>
+      <c r="AB98" s="42"/>
+      <c r="AC98" s="43"/>
+    </row>
+    <row r="99" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A99" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B99" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="C98" s="55" t="s">
+      <c r="C99" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="F98" s="14" t="s">
+      <c r="F99" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="H98" s="4">
-        <f>H63*H39</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="4">
-        <f>H98 - K81 - K92 - K44 + K39*K87</f>
-        <v>0.85</v>
-      </c>
-      <c r="N98" s="4">
-        <f>K98 - N81 - N92 - N44 + N39*N87</f>
-        <v>5.0986655000000001</v>
-      </c>
-      <c r="Q98" s="4">
-        <f>N98 - Q81 - Q92 - Q44 + Q39*Q87</f>
-        <v>15.290660595164999</v>
-      </c>
-      <c r="T98" s="4">
-        <f>Q98 - T81 - T92 - T44 + T39*T87</f>
-        <v>32.266654258030592</v>
-      </c>
-      <c r="W98" s="4">
-        <f>T98 - W81 - W92 - W44 + W39*W87</f>
-        <v>62.815995610845476</v>
-      </c>
-      <c r="Z98" s="4">
-        <f>W98 - Z81 - Z92 - Z44 + Z39*Z87</f>
-        <v>113.71737449773644</v>
-      </c>
-      <c r="AA98" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="AB98" s="42" t="s">
-        <v>402</v>
-      </c>
-      <c r="AC98" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B99" s="57"/>
-      <c r="C99" s="55"/>
-      <c r="F99" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="H99" s="4">
         <f>H64*H40</f>
@@ -11524,37 +11529,43 @@
       </c>
       <c r="K99" s="4">
         <f>H99 - K82 - K93 - K45 + K40*K88</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="N99" s="4">
         <f>K99 - N82 - N93 - N45 + N40*N88</f>
-        <v>0.8</v>
+        <v>5.0986655000000001</v>
       </c>
       <c r="Q99" s="4">
         <f>N99 - Q82 - Q93 - Q45 + Q40*Q88</f>
-        <v>4.7987440000000001</v>
+        <v>15.290660595164999</v>
       </c>
       <c r="T99" s="4">
         <f>Q99 - T82 - T93 - T45 + T40*T88</f>
-        <v>14.391209971919999</v>
+        <v>32.266654258030592</v>
       </c>
       <c r="W99" s="4">
         <f>T99 - W82 - W93 - W45 + W40*W88</f>
-        <v>30.368615772264086</v>
+        <v>62.815995610845476</v>
       </c>
       <c r="Z99" s="4">
         <f>W99 - Z82 - Z93 - Z45 + Z40*Z88</f>
-        <v>59.120937045501627</v>
-      </c>
-      <c r="AA99" s="37"/>
-      <c r="AB99" s="42"/>
-      <c r="AC99" s="43"/>
+        <v>113.71737449773644</v>
+      </c>
+      <c r="AA99" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="AB99" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC99" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="100" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B100" s="57"/>
       <c r="C100" s="55"/>
       <c r="F100" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H100" s="4">
         <f>H65*H41</f>
@@ -11566,33 +11577,33 @@
       </c>
       <c r="N100" s="4">
         <f>K100 - N83 - N94 - N46 + N41*N89</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q100" s="4">
         <f>N100 - Q83 - Q94 - Q46 + Q41*Q89</f>
-        <v>0.92</v>
+        <v>4.7987440000000001</v>
       </c>
       <c r="T100" s="4">
         <f>Q100 - T83 - T94 - T46 + T41*T89</f>
-        <v>5.5185556000000009</v>
+        <v>14.391209971919999</v>
       </c>
       <c r="W100" s="4">
         <f>T100 - W83 - W94 - W46 + W41*W89</f>
-        <v>16.549891467708001</v>
+        <v>30.368615772264086</v>
       </c>
       <c r="Z100" s="4">
         <f>W100 - Z83 - Z94 - Z46 + Z41*Z89</f>
-        <v>34.923908138103698</v>
+        <v>59.120937045501627</v>
       </c>
       <c r="AA100" s="37"/>
       <c r="AB100" s="42"/>
       <c r="AC100" s="43"/>
     </row>
-    <row r="101" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B101" s="57"/>
       <c r="C101" s="55"/>
       <c r="F101" s="14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H101" s="4">
         <f>H66*H42</f>
@@ -11608,155 +11619,154 @@
       </c>
       <c r="Q101" s="4">
         <f>N101 - Q84 - Q95 - Q47 + Q42*Q90</f>
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="T101" s="4">
         <f>Q101 - T84 - T95 - T47 + T42*T90</f>
-        <v>0.43</v>
+        <v>5.5185556000000009</v>
       </c>
       <c r="W101" s="4">
         <f>T101 - W84 - W95 - W47 + W42*W90</f>
-        <v>2.5793249</v>
+        <v>16.549891467708001</v>
       </c>
       <c r="Z101" s="4">
         <f>W101 - Z84 - Z95 - Z47 + Z42*Z90</f>
-        <v>7.7352753599069999</v>
+        <v>34.923908138103698</v>
       </c>
       <c r="AA101" s="37"/>
       <c r="AB101" s="42"/>
       <c r="AC101" s="43"/>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="E102" s="26"/>
-      <c r="F102" s="14"/>
+    <row r="102" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="57"/>
+      <c r="C102" s="55"/>
+      <c r="F102" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H102" s="4">
+        <f>H67*H43</f>
+        <v>0</v>
+      </c>
+      <c r="K102" s="4">
+        <f>H102 - K85 - K96 - K48 + K43*K91</f>
+        <v>0</v>
+      </c>
+      <c r="N102" s="4">
+        <f>K102 - N85 - N96 - N48 + N43*N91</f>
+        <v>0</v>
+      </c>
+      <c r="Q102" s="4">
+        <f>N102 - Q85 - Q96 - Q48 + Q43*Q91</f>
+        <v>0</v>
+      </c>
+      <c r="T102" s="4">
+        <f>Q102 - T85 - T96 - T48 + T43*T91</f>
+        <v>0.43</v>
+      </c>
+      <c r="W102" s="4">
+        <f>T102 - W85 - W96 - W48 + W43*W91</f>
+        <v>2.5793249</v>
+      </c>
+      <c r="Z102" s="4">
+        <f>W102 - Z85 - Z96 - Z48 + Z43*Z91</f>
+        <v>7.7352753599069999</v>
+      </c>
+      <c r="AA102" s="37"/>
       <c r="AB102" s="42"/>
       <c r="AC102" s="43"/>
     </row>
-    <row r="103" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B103" s="57" t="s">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="E103" s="26"/>
+      <c r="F103" s="14"/>
+      <c r="AB103" s="42"/>
+      <c r="AC103" s="43"/>
+    </row>
+    <row r="104" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A104" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B104" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="C103" s="55" t="s">
+      <c r="C104" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="E103" s="26"/>
-      <c r="F103" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H103" s="4">
-        <f>H98*$H$22</f>
-        <v>0</v>
-      </c>
-      <c r="K103" s="4">
-        <f>K98*$H$22</f>
-        <v>0.21249999999999999</v>
-      </c>
-      <c r="N103" s="4">
-        <f>N98*$H$22</f>
-        <v>1.274666375</v>
-      </c>
-      <c r="Q103" s="4">
-        <f>Q98*$H$22</f>
-        <v>3.8226651487912497</v>
-      </c>
-      <c r="T103" s="4">
-        <f>T98*$H$22</f>
-        <v>8.0666635645076479</v>
-      </c>
-      <c r="W103" s="4">
-        <f>W98*$H$22</f>
-        <v>15.703998902711369</v>
-      </c>
-      <c r="Z103" s="4">
-        <f>Z98*$H$22</f>
-        <v>28.429343624434111</v>
-      </c>
-      <c r="AA103" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="AB103" s="42" t="s">
-        <v>403</v>
-      </c>
-      <c r="AC103" s="43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="104" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="B104" s="57"/>
-      <c r="C104" s="55"/>
       <c r="E104" s="26"/>
       <c r="F104" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H104" s="4">
-        <f t="shared" ref="H104:H106" si="9">H99*$H$22</f>
+        <f>H99*$H$22</f>
         <v>0</v>
       </c>
       <c r="K104" s="4">
-        <f t="shared" ref="K104:K106" si="10">K99*$H$22</f>
-        <v>0</v>
+        <f>K99*$H$22</f>
+        <v>0.21249999999999999</v>
       </c>
       <c r="N104" s="4">
-        <f t="shared" ref="N104:N106" si="11">N99*$H$22</f>
-        <v>0.2</v>
+        <f>N99*$H$22</f>
+        <v>1.274666375</v>
       </c>
       <c r="Q104" s="4">
-        <f t="shared" ref="Q104:Q106" si="12">Q99*$H$22</f>
-        <v>1.199686</v>
+        <f>Q99*$H$22</f>
+        <v>3.8226651487912497</v>
       </c>
       <c r="T104" s="4">
-        <f t="shared" ref="T104:T106" si="13">T99*$H$22</f>
-        <v>3.5978024929799997</v>
+        <f>T99*$H$22</f>
+        <v>8.0666635645076479</v>
       </c>
       <c r="W104" s="4">
-        <f t="shared" ref="W104:W106" si="14">W99*$H$22</f>
-        <v>7.5921539430660214</v>
+        <f>W99*$H$22</f>
+        <v>15.703998902711369</v>
       </c>
       <c r="Z104" s="4">
-        <f t="shared" ref="Z104:Z106" si="15">Z99*$H$22</f>
-        <v>14.780234261375407</v>
-      </c>
-      <c r="AA104" s="37"/>
-      <c r="AB104" s="42"/>
-      <c r="AC104" s="43"/>
+        <f>Z99*$H$22</f>
+        <v>28.429343624434111</v>
+      </c>
+      <c r="AA104" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB104" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="AC104" s="43" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="105" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B105" s="57"/>
       <c r="C105" s="55"/>
       <c r="E105" s="26"/>
       <c r="F105" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H105" s="4">
-        <f>H100*$H$22</f>
+        <f t="shared" ref="H105:H107" si="9">H100*$H$22</f>
         <v>0</v>
       </c>
       <c r="K105" s="4">
-        <f>K100*$H$22</f>
+        <f t="shared" ref="K105:K107" si="10">K100*$H$22</f>
         <v>0</v>
       </c>
       <c r="N105" s="4">
-        <f>N100*$H$22</f>
-        <v>0</v>
+        <f t="shared" ref="N105:N107" si="11">N100*$H$22</f>
+        <v>0.2</v>
       </c>
       <c r="Q105" s="4">
-        <f>Q100*$H$22</f>
-        <v>0.23</v>
+        <f t="shared" ref="Q105:Q107" si="12">Q100*$H$22</f>
+        <v>1.199686</v>
       </c>
       <c r="T105" s="4">
-        <f>T100*$H$22</f>
-        <v>1.3796389000000002</v>
+        <f t="shared" ref="T105:T107" si="13">T100*$H$22</f>
+        <v>3.5978024929799997</v>
       </c>
       <c r="W105" s="4">
-        <f>W100*$H$22</f>
-        <v>4.1374728669270002</v>
+        <f t="shared" ref="W105:W107" si="14">W100*$H$22</f>
+        <v>7.5921539430660214</v>
       </c>
       <c r="Z105" s="4">
-        <f>Z100*$H$22</f>
-        <v>8.7309770345259246</v>
+        <f t="shared" ref="Z105:Z107" si="15">Z100*$H$22</f>
+        <v>14.780234261375407</v>
       </c>
       <c r="AA105" s="37"/>
       <c r="AB105" s="42"/>
@@ -11767,46 +11777,76 @@
       <c r="C106" s="55"/>
       <c r="E106" s="26"/>
       <c r="F106" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H106" s="4">
-        <f t="shared" si="9"/>
+        <f>H101*$H$22</f>
         <v>0</v>
       </c>
       <c r="K106" s="4">
-        <f t="shared" si="10"/>
+        <f>K101*$H$22</f>
         <v>0</v>
       </c>
       <c r="N106" s="4">
-        <f t="shared" si="11"/>
+        <f>N101*$H$22</f>
         <v>0</v>
       </c>
       <c r="Q106" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>Q101*$H$22</f>
+        <v>0.23</v>
       </c>
       <c r="T106" s="4">
-        <f t="shared" si="13"/>
-        <v>0.1075</v>
+        <f>T101*$H$22</f>
+        <v>1.3796389000000002</v>
       </c>
       <c r="W106" s="4">
-        <f t="shared" si="14"/>
-        <v>0.64483122500000001</v>
+        <f>W101*$H$22</f>
+        <v>4.1374728669270002</v>
       </c>
       <c r="Z106" s="4">
-        <f t="shared" si="15"/>
-        <v>1.93381883997675</v>
+        <f>Z101*$H$22</f>
+        <v>8.7309770345259246</v>
       </c>
       <c r="AA106" s="37"/>
       <c r="AB106" s="42"/>
       <c r="AC106" s="43"/>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="B107" s="29"/>
-      <c r="C107" s="35"/>
+    <row r="107" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B107" s="57"/>
+      <c r="C107" s="55"/>
       <c r="E107" s="26"/>
-      <c r="F107" s="14"/>
-      <c r="AA107" s="29"/>
+      <c r="F107" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H107" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K107" s="4">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N107" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q107" s="4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T107" s="4">
+        <f t="shared" si="13"/>
+        <v>0.1075</v>
+      </c>
+      <c r="W107" s="4">
+        <f t="shared" si="14"/>
+        <v>0.64483122500000001</v>
+      </c>
+      <c r="Z107" s="4">
+        <f t="shared" si="15"/>
+        <v>1.93381883997675</v>
+      </c>
+      <c r="AA107" s="37"/>
       <c r="AB107" s="42"/>
       <c r="AC107" s="43"/>
     </row>
@@ -11819,717 +11859,675 @@
       <c r="AB108" s="42"/>
       <c r="AC108" s="43"/>
     </row>
-    <row r="109" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B109" s="29"/>
+      <c r="C109" s="35"/>
       <c r="E109" s="26"/>
-      <c r="F109" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="G109" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="H109" s="8"/>
+      <c r="F109" s="14"/>
+      <c r="AA109" s="29"/>
       <c r="AB109" s="42"/>
       <c r="AC109" s="43"/>
     </row>
     <row r="110" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="B110" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="C110" s="34" t="s">
+      <c r="E110" s="26"/>
+      <c r="F110" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H110" s="8"/>
+      <c r="AB110" s="42"/>
+      <c r="AC110" s="43"/>
+    </row>
+    <row r="111" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B111" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C111" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="E110" s="26"/>
-      <c r="F110" s="14" t="s">
+      <c r="E111" s="26"/>
+      <c r="F111" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="H110" s="4">
+      <c r="H111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="J110" s="4">
+      <c r="J111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="K110" s="4">
+      <c r="K111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="M110" s="4">
+      <c r="M111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="N110" s="4">
+      <c r="N111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="P110" s="4">
+      <c r="P111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="Q110" s="4">
+      <c r="Q111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="S110" s="4">
+      <c r="S111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="T110" s="4">
+      <c r="T111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="V110" s="4">
+      <c r="V111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="W110" s="4">
+      <c r="W111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="Y110" s="4">
+      <c r="Y111" s="4">
         <f>$G$30</f>
         <v>0.3</v>
       </c>
-      <c r="Z110" s="4">
+      <c r="Z111" s="4">
         <f>$H$30</f>
         <v>0.92</v>
       </c>
-      <c r="AA110" s="38"/>
-      <c r="AB110" s="42"/>
-      <c r="AC110" s="43"/>
-    </row>
-    <row r="111" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A111" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B111" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="C111" s="28" t="s">
+      <c r="AA111" s="38"/>
+      <c r="AB111" s="42"/>
+      <c r="AC111" s="43"/>
+    </row>
+    <row r="112" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A112" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B112" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="C112" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F111" s="14" t="s">
+      <c r="F112" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G112" s="4">
         <f>G7*$G$21</f>
         <v>7500000</v>
       </c>
-      <c r="H111" s="4">
+      <c r="H112" s="4">
         <f>H7*$H$21</f>
         <v>25000000</v>
       </c>
-      <c r="J111" s="4">
+      <c r="J112" s="4">
         <f>J7*$G$21</f>
         <v>7492500</v>
       </c>
-      <c r="K111" s="4">
+      <c r="K112" s="4">
         <f>K7*$H$21</f>
         <v>24990000</v>
       </c>
-      <c r="M111" s="4">
+      <c r="M112" s="4">
         <f>M7*$G$21</f>
         <v>7483200</v>
       </c>
-      <c r="N111" s="4">
+      <c r="N112" s="4">
         <f>N7*$H$21</f>
         <v>24979000</v>
       </c>
-      <c r="P111" s="4">
+      <c r="P112" s="4">
         <f>P7*$G$21</f>
         <v>7474500</v>
       </c>
-      <c r="Q111" s="4">
+      <c r="Q112" s="4">
         <f>Q7*$H$21</f>
         <v>24969600</v>
       </c>
-      <c r="S111" s="4">
+      <c r="S112" s="4">
         <f>S7*$G$21</f>
         <v>7464000</v>
       </c>
-      <c r="T111" s="4">
+      <c r="T112" s="4">
         <f>T7*$H$21</f>
         <v>24950400</v>
       </c>
-      <c r="V111" s="4">
+      <c r="V112" s="4">
         <f>V7*$G$21</f>
         <v>7449000</v>
       </c>
-      <c r="W111" s="4">
+      <c r="W112" s="4">
         <f>W7*$H$21</f>
         <v>24946500</v>
       </c>
-      <c r="Y111" s="4">
+      <c r="Y112" s="4">
         <f>Y7*$G$21</f>
         <v>7434300</v>
       </c>
-      <c r="Z111" s="4">
+      <c r="Z112" s="4">
         <f>Z7*$H$21</f>
         <v>24936000</v>
       </c>
-      <c r="AA111" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="AB111" s="42" t="s">
-        <v>370</v>
-      </c>
-      <c r="AC111" s="43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="112" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A112" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B112" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="C112" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F112" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G112" s="4">
-        <v>1</v>
-      </c>
-      <c r="H112" s="4">
-        <v>1</v>
-      </c>
-      <c r="J112" s="4">
-        <f>IF(G114=0,0,MIN(MAX((G114/G111-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="K112" s="4">
-        <f>IF(H114=0,0,MIN(MAX((H114/H111-$H$18)/($G$20-$H$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="M112" s="4">
-        <f>IF(J114=0,0,MIN(MAX((J114/J111-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="N112" s="4">
-        <f>IF(K114=0,0,MIN(MAX((K114/K111-$H$18)/($G$20-$H$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="P112" s="4">
-        <f>IF(M114=0,0,MIN(MAX((M114/M111-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="Q112" s="4">
-        <f>IF(N114=0,0,MIN(MAX((N114/N111-$H$18)/($G$20-$H$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="S112" s="4">
-        <f>IF(P114=0,0,MIN(MAX((P114/P111-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="T112" s="4">
-        <f>IF(Q114=0,0,MIN(MAX((Q114/Q111-$H$18)/($G$20-$H$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="V112" s="4">
-        <f>IF(S114=0,0,MIN(MAX((S114/S111-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="W112" s="4">
-        <f>IF(T114=0,0,MIN(MAX((T114/T111-$H$18)/($G$20-$H$18), 0), 1))</f>
-        <v>1</v>
-      </c>
-      <c r="Y112" s="4">
-        <f>IF(V114=0,0,MIN(MAX((V114/V111-$G$18)/($G$20-$G$18), 0), 1))</f>
-        <v>0.8611518815783703</v>
-      </c>
-      <c r="Z112" s="4">
-        <f>IF(W114=0,0,MIN(MAX((W114/W111-$H$18)/($G$20-$H$18), 0), 1))</f>
-        <v>1</v>
-      </c>
       <c r="AA112" s="38" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="AB112" s="42" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AC112" s="43" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
     </row>
     <row r="113" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B113" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="C113" s="33" t="s">
-        <v>163</v>
+        <v>181</v>
+      </c>
+      <c r="C113" s="28" t="s">
+        <v>174</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="G113" s="4">
-        <f>G110</f>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="H113" s="4">
-        <f>H110</f>
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="J113" s="4">
-        <f xml:space="preserve"> J110*J112</f>
-        <v>0.3</v>
+        <f>IF(G115=0,0,MIN(MAX((G115/G112-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="K113" s="4">
-        <f>K110*K112</f>
-        <v>0.92</v>
+        <f>IF(H115=0,0,MIN(MAX((H115/H112-$H$18)/($G$20-$H$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="M113" s="4">
-        <f xml:space="preserve"> M110*M112</f>
-        <v>0.3</v>
+        <f>IF(J115=0,0,MIN(MAX((J115/J112-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="N113" s="4">
-        <f>N110*N112</f>
-        <v>0.92</v>
+        <f>IF(K115=0,0,MIN(MAX((K115/K112-$H$18)/($G$20-$H$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="P113" s="4">
-        <f xml:space="preserve"> P110*P112</f>
-        <v>0.3</v>
+        <f>IF(M115=0,0,MIN(MAX((M115/M112-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="Q113" s="4">
-        <f>Q110*Q112</f>
-        <v>0.92</v>
+        <f>IF(N115=0,0,MIN(MAX((N115/N112-$H$18)/($G$20-$H$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="S113" s="4">
-        <f xml:space="preserve"> S110*S112</f>
-        <v>0.3</v>
+        <f>IF(P115=0,0,MIN(MAX((P115/P112-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="T113" s="4">
-        <f>T110*T112</f>
-        <v>0.92</v>
+        <f>IF(Q115=0,0,MIN(MAX((Q115/Q112-$H$18)/($G$20-$H$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="V113" s="4">
-        <f xml:space="preserve"> V110*V112</f>
-        <v>0.3</v>
+        <f>IF(S115=0,0,MIN(MAX((S115/S112-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="W113" s="4">
-        <f>W110*W112</f>
-        <v>0.92</v>
+        <f>IF(T115=0,0,MIN(MAX((T115/T112-$H$18)/($G$20-$H$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="Y113" s="4">
-        <f xml:space="preserve"> Y110*Y112</f>
-        <v>0.25834556447351109</v>
+        <f>IF(V115=0,0,MIN(MAX((V115/V112-$G$18)/($G$20-$G$18), 0), 1))</f>
+        <v>0.8611518815783703</v>
       </c>
       <c r="Z113" s="4">
-        <f>Z110*Z112</f>
-        <v>0.92</v>
+        <f>IF(W115=0,0,MIN(MAX((W115/W112-$H$18)/($G$20-$H$18), 0), 1))</f>
+        <v>1</v>
       </c>
       <c r="AA113" s="38" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="AB113" s="42" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AC113" s="43" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B114" s="38" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="C114" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F114" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="G114" s="4">
+        <f>G111</f>
+        <v>0.3</v>
+      </c>
+      <c r="H114" s="4">
+        <f>H111</f>
+        <v>0.92</v>
+      </c>
+      <c r="J114" s="4">
+        <f xml:space="preserve"> J111*J113</f>
+        <v>0.3</v>
+      </c>
+      <c r="K114" s="4">
+        <f>K111*K113</f>
+        <v>0.92</v>
+      </c>
+      <c r="M114" s="4">
+        <f xml:space="preserve"> M111*M113</f>
+        <v>0.3</v>
+      </c>
+      <c r="N114" s="4">
+        <f>N111*N113</f>
+        <v>0.92</v>
+      </c>
+      <c r="P114" s="4">
+        <f xml:space="preserve"> P111*P113</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q114" s="4">
+        <f>Q111*Q113</f>
+        <v>0.92</v>
+      </c>
+      <c r="S114" s="4">
+        <f xml:space="preserve"> S111*S113</f>
+        <v>0.3</v>
+      </c>
+      <c r="T114" s="4">
+        <f>T111*T113</f>
+        <v>0.92</v>
+      </c>
+      <c r="V114" s="4">
+        <f xml:space="preserve"> V111*V113</f>
+        <v>0.3</v>
+      </c>
+      <c r="W114" s="4">
+        <f>W111*W113</f>
+        <v>0.92</v>
+      </c>
+      <c r="Y114" s="4">
+        <f xml:space="preserve"> Y111*Y113</f>
+        <v>0.25834556447351109</v>
+      </c>
+      <c r="Z114" s="4">
+        <f>Z111*Z113</f>
+        <v>0.92</v>
+      </c>
+      <c r="AA114" s="38" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB114" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="AC114" s="43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="115" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A115" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B115" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="C115" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F115" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="G114" s="4">
+      <c r="G115" s="4">
         <f>G7*G21</f>
         <v>7500000</v>
       </c>
-      <c r="H114" s="4">
+      <c r="H115" s="4">
         <f>H7*H21</f>
         <v>25000000</v>
       </c>
-      <c r="J114" s="4">
-        <f>G114 - G135 - G123 - G146+J113*J7</f>
+      <c r="J115" s="4">
+        <f>G115 - G137 - G124 - G148+J114*J7</f>
         <v>6966918.08125271</v>
       </c>
-      <c r="K114" s="4">
-        <f>H114 - H135 - H123 - (H146 - H96)+ K113*K7</f>
+      <c r="K115" s="4">
+        <f>H115 - H137 - H124 - (H148 - H97)+ K114*K7</f>
         <v>23723974.534997292</v>
       </c>
-      <c r="M114" s="4">
-        <f>J114 - J135 - J123 - J146+M113*M7</f>
+      <c r="M115" s="4">
+        <f>J115 - J137 - J124 - J148+M114*M7</f>
         <v>6430976.9232831635</v>
       </c>
-      <c r="N114" s="4">
-        <f>K114 - K135 - K123 - (K146 - K96)+ N113*N7</f>
+      <c r="N115" s="4">
+        <f>K115 - K137 - K124 - (K148 - K97)+ N114*N7</f>
         <v>22403030.169761121</v>
       </c>
-      <c r="P114" s="4">
-        <f>M114 - M135 - M123 - M146+P113*P7</f>
+      <c r="P115" s="4">
+        <f>M115 - M137 - M124 - M148+P114*P7</f>
         <v>5878439.281534086</v>
       </c>
-      <c r="Q114" s="4">
-        <f>N114 - N135 - N123 - (N146 - N96)+ Q113*Q7</f>
+      <c r="Q115" s="4">
+        <f>N115 - N137 - N124 - (N148 - N97)+ Q114*Q7</f>
         <v>21042661.125952005</v>
       </c>
-      <c r="S114" s="4">
-        <f>P114 - P135 - P123 - P146+S113*S7</f>
+      <c r="S115" s="4">
+        <f>P115 - P137 - P124 - P148+S114*S7</f>
         <v>5319767.3070256906</v>
       </c>
-      <c r="T114" s="4">
-        <f>Q114 - Q135 - Q123 - (Q146 - Q96)+ T113*T7</f>
+      <c r="T115" s="4">
+        <f>Q115 - Q137 - Q124 - (Q148 - Q97)+ T114*T7</f>
         <v>19588129.954529207</v>
       </c>
-      <c r="V114" s="4">
-        <f>S114 - S135 - S123 - S146+V113*V7</f>
+      <c r="V115" s="4">
+        <f>S115 - S137 - S124 - S148+V114*V7</f>
         <v>4639771.7554611461</v>
       </c>
-      <c r="W114" s="4">
-        <f>T114 - T135 - T123 - (T146 - T96)+ W113*W7</f>
+      <c r="W115" s="4">
+        <f>T115 - T137 - T124 - (T148 - T97)+ W114*W7</f>
         <v>17473377.857190389</v>
       </c>
-      <c r="Y114" s="4">
-        <f>V114 - V135 - V123 - V146+Y113*Y7</f>
+      <c r="Y115" s="4">
+        <f>V115 - V137 - V124 - V148+Y114*Y7</f>
         <v>4179370.6044759089</v>
       </c>
-      <c r="Z114" s="4">
-        <f>W114 - W135 - W123 - (W146 - W96)+ Z113*Z7</f>
+      <c r="Z115" s="4">
+        <f>W115 - W137 - W124 - (W148 - W97)+ Z114*Z7</f>
         <v>15778712.754563004</v>
       </c>
-      <c r="AA114" s="38" t="s">
-        <v>468</v>
-      </c>
-      <c r="AB114" s="42" t="s">
-        <v>373</v>
-      </c>
-      <c r="AC114" s="43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="115" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A115" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B115" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="C115" s="33" t="s">
+      <c r="AA115" s="38" t="s">
+        <v>465</v>
+      </c>
+      <c r="AB115" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="AC115" s="43" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="116" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A116" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B116" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="C116" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F115" s="14" t="s">
+      <c r="F116" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="G115" s="4">
-        <f>IF(G7=0,0,G114/G7)</f>
+      <c r="G116" s="4">
+        <f>IF(G7=0,0,G115/G7)</f>
         <v>150</v>
       </c>
-      <c r="H115" s="4">
-        <f>IF(H7=0,0,H114/H7)</f>
+      <c r="H116" s="4">
+        <f>IF(H7=0,0,H115/H7)</f>
         <v>100</v>
       </c>
-      <c r="J115" s="4">
-        <f>IF(J7=0,0,J114/J7)</f>
+      <c r="J116" s="4">
+        <f>IF(J7=0,0,J115/J7)</f>
         <v>139.47783946451872</v>
       </c>
-      <c r="K115" s="4">
-        <f>IF(K7=0,0,K114/K7)</f>
+      <c r="K116" s="4">
+        <f>IF(K7=0,0,K115/K7)</f>
         <v>94.933871688664638</v>
       </c>
-      <c r="M115" s="4">
-        <f>IF(M7=0,0,M114/M7)</f>
+      <c r="M116" s="4">
+        <f>IF(M7=0,0,M115/M7)</f>
         <v>128.90829304207753</v>
       </c>
-      <c r="N115" s="4">
-        <f>IF(N7=0,0,N114/N7)</f>
+      <c r="N116" s="4">
+        <f>IF(N7=0,0,N115/N7)</f>
         <v>89.687458143885351</v>
       </c>
-      <c r="P115" s="4">
-        <f>IF(P7=0,0,P114/P7)</f>
+      <c r="P116" s="4">
+        <f>IF(P7=0,0,P115/P7)</f>
         <v>117.96988323367621</v>
       </c>
-      <c r="Q115" s="4">
-        <f>IF(Q7=0,0,Q114/Q7)</f>
+      <c r="Q116" s="4">
+        <f>IF(Q7=0,0,Q115/Q7)</f>
         <v>84.273120618480093</v>
       </c>
-      <c r="S115" s="4">
-        <f>IF(S7=0,0,S114/S7)</f>
+      <c r="S116" s="4">
+        <f>IF(S7=0,0,S115/S7)</f>
         <v>106.90850697398896</v>
       </c>
-      <c r="T115" s="4">
-        <f>IF(T7=0,0,T114/T7)</f>
+      <c r="T116" s="4">
+        <f>IF(T7=0,0,T115/T7)</f>
         <v>78.508280246125139</v>
       </c>
-      <c r="V115" s="4">
-        <f>IF(V7=0,0,V114/V7)</f>
+      <c r="V116" s="4">
+        <f>IF(V7=0,0,V115/V7)</f>
         <v>93.430764306507172</v>
       </c>
-      <c r="W115" s="4">
-        <f>IF(W7=0,0,W114/W7)</f>
+      <c r="W116" s="4">
+        <f>IF(W7=0,0,W115/W7)</f>
         <v>70.043404313993506</v>
       </c>
-      <c r="Y115" s="4">
-        <f>IF(Y7=0,0,Y114/Y7)</f>
+      <c r="Y116" s="4">
+        <f>IF(Y7=0,0,Y115/Y7)</f>
         <v>84.326108802629207</v>
       </c>
-      <c r="Z115" s="4">
-        <f>IF(Z7=0,0,Z114/Z7)</f>
+      <c r="Z116" s="4">
+        <f>IF(Z7=0,0,Z115/Z7)</f>
         <v>63.276839727955583</v>
       </c>
-      <c r="AA115" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="AB115" s="42" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC115" s="43" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="116" spans="1:29" ht="68" x14ac:dyDescent="0.2">
-      <c r="A116" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B116" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="C116" s="28" t="s">
+      <c r="AA116" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="AB116" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="AC116" s="43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="117" spans="1:29" ht="68" x14ac:dyDescent="0.2">
+      <c r="A117" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B117" s="38" t="s">
+        <v>276</v>
+      </c>
+      <c r="C117" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F116" s="10" t="s">
+      <c r="F117" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G116" s="4">
-        <f>MAX(G115-$G23,0)</f>
+      <c r="G117" s="4">
+        <f>MAX(G116-$G23,0)</f>
         <v>100.4134425</v>
       </c>
-      <c r="H116" s="4">
-        <f>MAX(H115-$H23,0)</f>
+      <c r="H117" s="4">
+        <f>MAX(H116-$H23,0)</f>
         <v>62.199106999999998</v>
       </c>
-      <c r="J116" s="4">
-        <f>MAX(J115-$G23,0)</f>
+      <c r="J117" s="4">
+        <f>MAX(J116-$G23,0)</f>
         <v>89.891281964518726</v>
       </c>
-      <c r="K116" s="4">
-        <f>MAX(K115-$H23,0)</f>
+      <c r="K117" s="4">
+        <f>MAX(K116-$H23,0)</f>
         <v>57.132978688664636</v>
       </c>
-      <c r="M116" s="4">
-        <f>MAX(M115-$G23,0)</f>
+      <c r="M117" s="4">
+        <f>MAX(M116-$G23,0)</f>
         <v>79.321735542077533</v>
       </c>
-      <c r="N116" s="4">
-        <f>MAX(N115-$H23,0)</f>
+      <c r="N117" s="4">
+        <f>MAX(N116-$H23,0)</f>
         <v>51.886565143885349</v>
       </c>
-      <c r="P116" s="4">
-        <f>MAX(P115-$G23,0)</f>
+      <c r="P117" s="4">
+        <f>MAX(P116-$G23,0)</f>
         <v>68.383325733676216</v>
       </c>
-      <c r="Q116" s="4">
-        <f>MAX(Q115-$H23,0)</f>
+      <c r="Q117" s="4">
+        <f>MAX(Q116-$H23,0)</f>
         <v>46.47222761848009</v>
       </c>
-      <c r="S116" s="4">
-        <f>MAX(S115-$G23,0)</f>
+      <c r="S117" s="4">
+        <f>MAX(S116-$G23,0)</f>
         <v>57.321949473988965</v>
       </c>
-      <c r="T116" s="4">
-        <f>MAX(T115-$H23,0)</f>
+      <c r="T117" s="4">
+        <f>MAX(T116-$H23,0)</f>
         <v>40.707387246125137</v>
       </c>
-      <c r="V116" s="4">
-        <f>MAX(V115-$G23,0)</f>
+      <c r="V117" s="4">
+        <f>MAX(V116-$G23,0)</f>
         <v>43.844206806507174</v>
       </c>
-      <c r="W116" s="4">
-        <f>MAX(W115-$H23,0)</f>
+      <c r="W117" s="4">
+        <f>MAX(W116-$H23,0)</f>
         <v>32.242511313993504</v>
       </c>
-      <c r="Y116" s="4">
-        <f>MAX(Y115-$G23,0)</f>
+      <c r="Y117" s="4">
+        <f>MAX(Y116-$G23,0)</f>
         <v>34.739551302629209</v>
       </c>
-      <c r="Z116" s="4">
-        <f>MAX(Z115-$H23,0)</f>
+      <c r="Z117" s="4">
+        <f>MAX(Z116-$H23,0)</f>
         <v>25.475946727955581</v>
       </c>
-      <c r="AA116" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="AB116" s="46" t="s">
-        <v>375</v>
-      </c>
-      <c r="AC116" s="43" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F117" s="13"/>
-      <c r="AB117" s="42"/>
-      <c r="AC117" s="43"/>
-    </row>
-    <row r="118" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="F118" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G118" s="12"/>
-      <c r="H118" s="12"/>
-      <c r="J118" s="12"/>
-      <c r="K118" s="12"/>
-      <c r="M118" s="12"/>
-      <c r="N118" s="12"/>
-      <c r="P118" s="12"/>
-      <c r="Q118" s="12"/>
-      <c r="S118" s="12"/>
-      <c r="T118" s="12"/>
-      <c r="V118" s="12"/>
-      <c r="W118" s="12"/>
-      <c r="Y118" s="12"/>
-      <c r="Z118" s="12"/>
+      <c r="AA117" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="AB117" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC117" s="43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F118" s="13"/>
       <c r="AB118" s="42"/>
       <c r="AC118" s="43"/>
     </row>
-    <row r="119" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A119" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B119" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="C119" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G119" s="4">
-        <f>G115*G7</f>
-        <v>7500000</v>
-      </c>
-      <c r="H119" s="4">
-        <f>H115*H7</f>
-        <v>25000000</v>
-      </c>
-      <c r="J119" s="4">
-        <f>J115*J7</f>
-        <v>6966918.08125271</v>
-      </c>
-      <c r="K119" s="4">
-        <f>K115*K7</f>
-        <v>23723974.534997292</v>
-      </c>
-      <c r="M119" s="4">
-        <f>M115*M7</f>
-        <v>6430976.9232831635</v>
-      </c>
-      <c r="N119" s="4">
-        <f>N115*N7</f>
-        <v>22403030.169761121</v>
-      </c>
-      <c r="P119" s="4">
-        <f>P115*P7</f>
-        <v>5878439.281534086</v>
-      </c>
-      <c r="Q119" s="4">
-        <f>Q115*Q7</f>
-        <v>21042661.125952005</v>
-      </c>
-      <c r="S119" s="4">
-        <f>S115*S7</f>
-        <v>5319767.3070256906</v>
-      </c>
-      <c r="T119" s="4">
-        <f>T115*T7</f>
-        <v>19588129.954529207</v>
-      </c>
-      <c r="V119" s="4">
-        <f>V115*V7</f>
-        <v>4639771.7554611461</v>
-      </c>
-      <c r="W119" s="4">
-        <f>W115*W7</f>
-        <v>17473377.857190389</v>
-      </c>
-      <c r="Y119" s="4">
-        <f>Y115*Y7</f>
-        <v>4179370.6044759089</v>
-      </c>
-      <c r="Z119" s="4">
-        <f>Z115*Z7</f>
-        <v>15778712.754563004</v>
-      </c>
-      <c r="AA119" s="38"/>
+    <row r="119" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="F119" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="J119" s="12"/>
+      <c r="K119" s="12"/>
+      <c r="M119" s="12"/>
+      <c r="N119" s="12"/>
+      <c r="P119" s="12"/>
+      <c r="Q119" s="12"/>
+      <c r="S119" s="12"/>
+      <c r="T119" s="12"/>
+      <c r="V119" s="12"/>
+      <c r="W119" s="12"/>
+      <c r="Y119" s="12"/>
+      <c r="Z119" s="12"/>
       <c r="AB119" s="42"/>
       <c r="AC119" s="43"/>
     </row>
     <row r="120" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A120" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B120" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="C120" s="33" t="s">
-        <v>163</v>
+      <c r="C120" s="34" t="s">
+        <v>180</v>
       </c>
       <c r="F120" s="10" t="s">
         <v>216</v>
       </c>
+      <c r="G120" s="4">
+        <f>G116*G7</f>
+        <v>7500000</v>
+      </c>
       <c r="H120" s="4">
-        <f>SUM(H98:H101)</f>
-        <v>0</v>
+        <f>H116*H7</f>
+        <v>25000000</v>
+      </c>
+      <c r="J120" s="4">
+        <f>J116*J7</f>
+        <v>6966918.08125271</v>
       </c>
       <c r="K120" s="4">
-        <f>SUM(K98:K101)</f>
-        <v>0.85</v>
+        <f>K116*K7</f>
+        <v>23723974.534997292</v>
+      </c>
+      <c r="M120" s="4">
+        <f>M116*M7</f>
+        <v>6430976.9232831635</v>
       </c>
       <c r="N120" s="4">
-        <f>SUM(N98:N101)</f>
-        <v>5.8986654999999999</v>
+        <f>N116*N7</f>
+        <v>22403030.169761121</v>
+      </c>
+      <c r="P120" s="4">
+        <f>P116*P7</f>
+        <v>5878439.281534086</v>
       </c>
       <c r="Q120" s="4">
-        <f>SUM(Q98:Q101)</f>
-        <v>21.009404595165002</v>
+        <f>Q116*Q7</f>
+        <v>21042661.125952005</v>
+      </c>
+      <c r="S120" s="4">
+        <f>S116*S7</f>
+        <v>5319767.3070256906</v>
       </c>
       <c r="T120" s="4">
-        <f>SUM(T98:T101)</f>
-        <v>52.606419829950589</v>
+        <f>T116*T7</f>
+        <v>19588129.954529207</v>
+      </c>
+      <c r="V120" s="4">
+        <f>V116*V7</f>
+        <v>4639771.7554611461</v>
       </c>
       <c r="W120" s="4">
-        <f>SUM(W98:W101)</f>
-        <v>112.31382775081757</v>
+        <f>W116*W7</f>
+        <v>17473377.857190389</v>
+      </c>
+      <c r="Y120" s="4">
+        <f>Y116*Y7</f>
+        <v>4179370.6044759089</v>
       </c>
       <c r="Z120" s="4">
-        <f>SUM(Z98:Z101)</f>
-        <v>215.49749504124878</v>
-      </c>
-      <c r="AA120" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB120" s="42" t="s">
-        <v>409</v>
-      </c>
-      <c r="AC120" s="43" t="s">
-        <v>347</v>
-      </c>
+        <f>Z116*Z7</f>
+        <v>15778712.754563004</v>
+      </c>
+      <c r="AA120" s="38"/>
+      <c r="AB120" s="42"/>
+      <c r="AC120" s="43"/>
     </row>
     <row r="121" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A121" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B121" s="38" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C121" s="33" t="s">
         <v>163</v>
@@ -12537,2066 +12535,2157 @@
       <c r="F121" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="G121" s="4">
-        <f>G119+G120</f>
-        <v>7500000</v>
-      </c>
       <c r="H121" s="4">
-        <f>H119+H120</f>
-        <v>25000000</v>
-      </c>
-      <c r="J121" s="4">
-        <f>J119+J120</f>
-        <v>6966918.08125271</v>
+        <f>SUM(H99:H102)</f>
+        <v>0</v>
       </c>
       <c r="K121" s="4">
-        <f>K119+K120</f>
-        <v>23723975.384997293</v>
-      </c>
-      <c r="M121" s="4">
-        <f>M119+M120</f>
-        <v>6430976.9232831635</v>
+        <f>SUM(K99:K102)</f>
+        <v>0.85</v>
       </c>
       <c r="N121" s="4">
-        <f>N119+N120</f>
-        <v>22403036.06842662</v>
-      </c>
-      <c r="P121" s="4">
-        <f>P119+P120</f>
-        <v>5878439.281534086</v>
+        <f>SUM(N99:N102)</f>
+        <v>5.8986654999999999</v>
       </c>
       <c r="Q121" s="4">
-        <f>Q119+Q120</f>
-        <v>21042682.135356601</v>
-      </c>
-      <c r="S121" s="4">
-        <f>S119+S120</f>
-        <v>5319767.3070256906</v>
+        <f>SUM(Q99:Q102)</f>
+        <v>21.009404595165002</v>
       </c>
       <c r="T121" s="4">
-        <f>T119+T120</f>
-        <v>19588182.560949039</v>
-      </c>
-      <c r="V121" s="4">
-        <f>V119+V120</f>
-        <v>4639771.7554611461</v>
+        <f>SUM(T99:T102)</f>
+        <v>52.606419829950589</v>
       </c>
       <c r="W121" s="4">
-        <f>W119+W120</f>
-        <v>17473490.171018139</v>
-      </c>
-      <c r="Y121" s="4">
-        <f>Y119+Y120</f>
-        <v>4179370.6044759089</v>
+        <f>SUM(W99:W102)</f>
+        <v>112.31382775081757</v>
       </c>
       <c r="Z121" s="4">
-        <f>Z119+Z120</f>
-        <v>15778928.252058046</v>
+        <f>SUM(Z99:Z102)</f>
+        <v>215.49749504124878</v>
       </c>
       <c r="AA121" s="38" t="s">
-        <v>463</v>
+        <v>318</v>
       </c>
       <c r="AB121" s="42" t="s">
-        <v>460</v>
+        <v>406</v>
       </c>
       <c r="AC121" s="43" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
     </row>
     <row r="122" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B122" s="38" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C122" s="33" t="s">
         <v>163</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G122" s="4">
-        <f>G121*$G$22</f>
+        <f>G120+G121</f>
+        <v>7500000</v>
+      </c>
+      <c r="H122" s="4">
+        <f>H120+H121</f>
+        <v>25000000</v>
+      </c>
+      <c r="J122" s="4">
+        <f>J120+J121</f>
+        <v>6966918.08125271</v>
+      </c>
+      <c r="K122" s="4">
+        <f>K120+K121</f>
+        <v>23723975.384997293</v>
+      </c>
+      <c r="M122" s="4">
+        <f>M120+M121</f>
+        <v>6430976.9232831635</v>
+      </c>
+      <c r="N122" s="4">
+        <f>N120+N121</f>
+        <v>22403036.06842662</v>
+      </c>
+      <c r="P122" s="4">
+        <f>P120+P121</f>
+        <v>5878439.281534086</v>
+      </c>
+      <c r="Q122" s="4">
+        <f>Q120+Q121</f>
+        <v>21042682.135356601</v>
+      </c>
+      <c r="S122" s="4">
+        <f>S120+S121</f>
+        <v>5319767.3070256906</v>
+      </c>
+      <c r="T122" s="4">
+        <f>T120+T121</f>
+        <v>19588182.560949039</v>
+      </c>
+      <c r="V122" s="4">
+        <f>V120+V121</f>
+        <v>4639771.7554611461</v>
+      </c>
+      <c r="W122" s="4">
+        <f>W120+W121</f>
+        <v>17473490.171018139</v>
+      </c>
+      <c r="Y122" s="4">
+        <f>Y120+Y121</f>
+        <v>4179370.6044759089</v>
+      </c>
+      <c r="Z122" s="4">
+        <f>Z120+Z121</f>
+        <v>15778928.252058046</v>
+      </c>
+      <c r="AA122" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="AB122" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="AC122" s="43" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A123" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B123" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C123" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G123" s="4">
+        <f>G122*$G$22</f>
         <v>2250000</v>
       </c>
-      <c r="H122" s="4">
-        <f>H121*$H$22</f>
+      <c r="H123" s="4">
+        <f>H122*$H$22</f>
         <v>6250000</v>
       </c>
-      <c r="J122" s="4">
-        <f>J121*$G$22</f>
+      <c r="J123" s="4">
+        <f>J122*$G$22</f>
         <v>2090075.424375813</v>
       </c>
-      <c r="K122" s="4">
-        <f>K121*$H$22</f>
+      <c r="K123" s="4">
+        <f>K122*$H$22</f>
         <v>5930993.8462493233</v>
       </c>
-      <c r="M122" s="4">
-        <f>M121*$G$22</f>
+      <c r="M123" s="4">
+        <f>M122*$G$22</f>
         <v>1929293.0769849489</v>
       </c>
-      <c r="N122" s="4">
-        <f>N121*$H$22</f>
+      <c r="N123" s="4">
+        <f>N122*$H$22</f>
         <v>5600759.0171066551</v>
       </c>
-      <c r="P122" s="4">
-        <f>P121*$G$22</f>
+      <c r="P123" s="4">
+        <f>P122*$G$22</f>
         <v>1763531.7844602258</v>
       </c>
-      <c r="Q122" s="4">
-        <f>Q121*$H$22</f>
+      <c r="Q123" s="4">
+        <f>Q122*$H$22</f>
         <v>5260670.5338391503</v>
       </c>
-      <c r="S122" s="4">
-        <f>S121*$G$22</f>
+      <c r="S123" s="4">
+        <f>S122*$G$22</f>
         <v>1595930.192107707</v>
       </c>
-      <c r="T122" s="4">
-        <f>T121*$H$22</f>
+      <c r="T123" s="4">
+        <f>T122*$H$22</f>
         <v>4897045.6402372597</v>
       </c>
-      <c r="V122" s="4">
-        <f>V121*$G$22</f>
+      <c r="V123" s="4">
+        <f>V122*$G$22</f>
         <v>1391931.5266383437</v>
       </c>
-      <c r="W122" s="4">
-        <f>W121*$H$22</f>
+      <c r="W123" s="4">
+        <f>W122*$H$22</f>
         <v>4368372.5427545346</v>
       </c>
-      <c r="Y122" s="4">
-        <f>Y121*$G$22</f>
+      <c r="Y123" s="4">
+        <f>Y122*$G$22</f>
         <v>1253811.1813427727</v>
       </c>
-      <c r="Z122" s="4">
-        <f>Z121*$H$22</f>
+      <c r="Z123" s="4">
+        <f>Z122*$H$22</f>
         <v>3944732.0630145115</v>
       </c>
-      <c r="AA122" s="38" t="s">
-        <v>462</v>
-      </c>
-      <c r="AB122" s="42" t="s">
-        <v>461</v>
-      </c>
-      <c r="AC122" s="43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="123" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="B123" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="C123" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F123" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="G123" s="4">
-        <f>G12*G115</f>
-        <v>7500</v>
-      </c>
-      <c r="H123" s="4">
-        <f>H12*H115</f>
-        <v>10000</v>
-      </c>
-      <c r="J123" s="4">
-        <f>J12*J115</f>
-        <v>8647.6260468001601</v>
-      </c>
-      <c r="K123" s="4">
-        <f>K12*K115</f>
-        <v>10442.725885753111</v>
-      </c>
-      <c r="M123" s="4">
-        <f>M12*M115</f>
-        <v>7476.6809964404965</v>
-      </c>
-      <c r="N123" s="4">
-        <f>N12*N115</f>
-        <v>8430.6210655252235</v>
-      </c>
-      <c r="P123" s="4">
-        <f>P12*P115</f>
-        <v>8257.8918263573341</v>
-      </c>
-      <c r="Q123" s="4">
-        <f>Q12*Q115</f>
-        <v>16180.439158748177</v>
-      </c>
-      <c r="S123" s="4">
-        <f>S12*S115</f>
-        <v>10690.850697398897</v>
-      </c>
-      <c r="T123" s="4">
-        <f>T12*T115</f>
-        <v>3061.8229295988804</v>
-      </c>
-      <c r="V123" s="4">
-        <f>V12*V115</f>
-        <v>9156.2149020377037</v>
-      </c>
-      <c r="W123" s="4">
-        <f>W12*W115</f>
-        <v>7354.5574529693185</v>
-      </c>
-      <c r="Y123" s="4">
-        <f>Y12*Y115</f>
-        <v>8263.958662657662</v>
-      </c>
-      <c r="Z123" s="4">
-        <f>Z12*Z115</f>
-        <v>7340.1134084428477</v>
-      </c>
       <c r="AA123" s="38" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="AB123" s="42" t="s">
-        <v>376</v>
+        <v>458</v>
       </c>
       <c r="AC123" s="43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="124" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A124" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B124" s="38" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="C124" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G124" s="4">
-        <f>MIN(G123,G12*G16)</f>
-        <v>250</v>
+        <f>G12*G116</f>
+        <v>7500</v>
       </c>
       <c r="H124" s="4">
-        <f>MIN(H123,H12*H16)</f>
-        <v>1000</v>
+        <f>H12*H116</f>
+        <v>10000</v>
       </c>
       <c r="J124" s="4">
-        <f>MIN(J123,J12*J16)</f>
-        <v>316.2</v>
+        <f>J12*J116</f>
+        <v>8647.6260468001601</v>
       </c>
       <c r="K124" s="4">
-        <f>MIN(K123,K12*K16)</f>
-        <v>1078</v>
+        <f>K12*K116</f>
+        <v>10442.725885753111</v>
       </c>
       <c r="M124" s="4">
-        <f>MIN(M123,M12*M16)</f>
-        <v>301.60000000000002</v>
+        <f>M12*M116</f>
+        <v>7476.6809964404965</v>
       </c>
       <c r="N124" s="4">
-        <f>MIN(N123,N12*N16)</f>
-        <v>921.2</v>
+        <f>N12*N116</f>
+        <v>8430.6210655252235</v>
       </c>
       <c r="P124" s="4">
-        <f>MIN(P123,P12*P16)</f>
-        <v>329</v>
+        <f>P12*P116</f>
+        <v>8257.8918263573341</v>
       </c>
       <c r="Q124" s="4">
-        <f>MIN(Q123,Q12*Q16)</f>
-        <v>1900.8000000000002</v>
+        <f>Q12*Q116</f>
+        <v>16180.439158748177</v>
       </c>
       <c r="S124" s="4">
-        <f>MIN(S123,S12*S16)</f>
-        <v>520</v>
+        <f>S12*S116</f>
+        <v>10690.850697398897</v>
       </c>
       <c r="T124" s="4">
-        <f>MIN(T123,T12*T16)</f>
-        <v>393.9</v>
+        <f>T12*T116</f>
+        <v>3061.8229295988804</v>
       </c>
       <c r="V124" s="4">
-        <f>MIN(V123,V12*V16)</f>
-        <v>401.79999999999995</v>
+        <f>V12*V116</f>
+        <v>9156.2149020377037</v>
       </c>
       <c r="W124" s="4">
-        <f>MIN(W123,W12*W16)</f>
-        <v>1155</v>
+        <f>W12*W116</f>
+        <v>7354.5574529693185</v>
       </c>
       <c r="Y124" s="4">
-        <f>MIN(Y123,Y12*Y16)</f>
-        <v>499.79999999999995</v>
+        <f>Y12*Y116</f>
+        <v>8263.958662657662</v>
       </c>
       <c r="Z124" s="4">
-        <f>MIN(Z123,Z12*Z16)</f>
-        <v>1044</v>
+        <f>Z12*Z116</f>
+        <v>7340.1134084428477</v>
       </c>
       <c r="AA124" s="38" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AB124" s="42" t="s">
-        <v>479</v>
+        <v>373</v>
       </c>
       <c r="AC124" s="43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="125" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A125" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B125" s="38" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C125" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G125" s="4">
-        <f>(G123-G124)*$G$15</f>
-        <v>5075</v>
+        <f>MIN(G124,G12*G16)</f>
+        <v>250</v>
       </c>
       <c r="H125" s="4">
-        <f>(H123-H124+H55)*$G$15</f>
-        <v>6300</v>
+        <f>MIN(H124,H12*H16)</f>
+        <v>1000</v>
       </c>
       <c r="J125" s="4">
-        <f>(J123-J124)*$G$15</f>
-        <v>5831.998232760111</v>
+        <f>MIN(J124,J12*J16)</f>
+        <v>316.2</v>
       </c>
       <c r="K125" s="4">
-        <f>(K123-K124+K55)*$G$15</f>
-        <v>6555.3081200271772</v>
+        <f>MIN(K124,K12*K16)</f>
+        <v>1078</v>
       </c>
       <c r="M125" s="4">
-        <f>(M123-M124)*$G$15</f>
-        <v>5022.5566975083466</v>
+        <f>MIN(M124,M12*M16)</f>
+        <v>301.60000000000002</v>
       </c>
       <c r="N125" s="4">
-        <f>(N123-N124+N55)*$G$15</f>
-        <v>5256.5947458676565</v>
+        <f>MIN(N124,N12*N16)</f>
+        <v>921.2</v>
       </c>
       <c r="P125" s="4">
-        <f>(P123-P124)*$G$15</f>
-        <v>5550.2242784501332</v>
+        <f>MIN(P124,P12*P16)</f>
+        <v>329</v>
       </c>
       <c r="Q125" s="4">
-        <f>(Q123-Q124+Q55)*$G$15</f>
-        <v>9995.7474111237243</v>
+        <f>MIN(Q124,Q12*Q16)</f>
+        <v>1900.8000000000002</v>
       </c>
       <c r="S125" s="4">
-        <f>(S123-S124)*$G$15</f>
-        <v>7119.5954881792277</v>
+        <f>MIN(S124,S12*S16)</f>
+        <v>520</v>
       </c>
       <c r="T125" s="4">
-        <f>(T123-T124+T55)*$G$15</f>
-        <v>1867.5460507192161</v>
+        <f>MIN(T124,T12*T16)</f>
+        <v>393.9</v>
       </c>
       <c r="V125" s="4">
-        <f>(V123-V124)*$G$15</f>
-        <v>6128.0904314263926</v>
+        <f>MIN(V124,V12*V16)</f>
+        <v>401.79999999999995</v>
       </c>
       <c r="W125" s="4">
-        <f>(W123-W124+W55)*$G$15</f>
-        <v>4339.6902170785224</v>
+        <f>MIN(W124,W12*W16)</f>
+        <v>1155</v>
       </c>
       <c r="Y125" s="4">
-        <f>(Y123-Y124)*$G$15</f>
-        <v>5434.9110638603634</v>
+        <f>MIN(Y124,Y12*Y16)</f>
+        <v>499.79999999999995</v>
       </c>
       <c r="Z125" s="4">
-        <f>(Z123-Z124+Z55)*$G$15</f>
-        <v>4407.2793859099929</v>
+        <f>MIN(Z124,Z12*Z16)</f>
+        <v>1044</v>
       </c>
       <c r="AA125" s="38" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AB125" s="42" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AC125" s="43" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B126" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="C126" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>250</v>
+        <v>277</v>
+      </c>
+      <c r="C126" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="G126" s="4">
-        <f>MIN(G125+H125, G34)</f>
-        <v>11375</v>
+        <f>(G124-G125)*$G$15</f>
+        <v>5075</v>
+      </c>
+      <c r="H126" s="4">
+        <f>(H124-H125+H56)*$G$15</f>
+        <v>6300</v>
       </c>
       <c r="J126" s="4">
-        <f>MIN(J125+K125, J34)</f>
-        <v>12387.306352787287</v>
+        <f>(J124-J125)*$G$15</f>
+        <v>5831.998232760111</v>
+      </c>
+      <c r="K126" s="4">
+        <f>(K124-K125+K56)*$G$15</f>
+        <v>6555.3081200271772</v>
       </c>
       <c r="M126" s="4">
-        <f>MIN(M125+N125, M34)</f>
-        <v>10279.151443376002</v>
+        <f>(M124-M125)*$G$15</f>
+        <v>5022.5566975083466</v>
+      </c>
+      <c r="N126" s="4">
+        <f>(N124-N125+N56)*$G$15</f>
+        <v>5256.5947458676565</v>
       </c>
       <c r="P126" s="4">
-        <f>MIN(P125+Q125, P34)</f>
-        <v>15545.971689573857</v>
+        <f>(P124-P125)*$G$15</f>
+        <v>5550.2242784501332</v>
+      </c>
+      <c r="Q126" s="4">
+        <f>(Q124-Q125+Q56)*$G$15</f>
+        <v>9995.7474111237243</v>
       </c>
       <c r="S126" s="4">
-        <f>MIN(S125+T125, S34)</f>
-        <v>8987.1415388984442</v>
+        <f>(S124-S125)*$G$15</f>
+        <v>7119.5954881792277</v>
+      </c>
+      <c r="T126" s="4">
+        <f>(T124-T125+T56)*$G$15</f>
+        <v>1867.5460507192161</v>
       </c>
       <c r="V126" s="4">
-        <f>MIN(V125+W125, V34)</f>
-        <v>10467.780648504915</v>
+        <f>(V124-V125)*$G$15</f>
+        <v>6128.0904314263926</v>
+      </c>
+      <c r="W126" s="4">
+        <f>(W124-W125+W56)*$G$15</f>
+        <v>4339.6902170785224</v>
       </c>
       <c r="Y126" s="4">
-        <f>MIN(Y125+Z125, Y34)</f>
-        <v>9842.1904497703563</v>
+        <f>(Y124-Y125)*$G$15</f>
+        <v>5434.9110638603634</v>
+      </c>
+      <c r="Z126" s="4">
+        <f>(Z124-Z125+Z56)*$G$15</f>
+        <v>4407.2793859099929</v>
       </c>
       <c r="AA126" s="38" t="s">
-        <v>327</v>
+        <v>479</v>
       </c>
       <c r="AB126" s="42" t="s">
-        <v>328</v>
+        <v>476</v>
       </c>
       <c r="AC126" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="127" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A127" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B127" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="C127" s="28" t="s">
-        <v>174</v>
+        <v>252</v>
+      </c>
+      <c r="C127" s="33" t="s">
+        <v>163</v>
       </c>
       <c r="F127" s="14" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="G127" s="4">
-        <f>G125/(G125+H125)</f>
-        <v>0.44615384615384618</v>
-      </c>
-      <c r="H127" s="4">
-        <f>H125/(G125+H125)</f>
-        <v>0.55384615384615388</v>
+        <f>MIN(G126+H126, G34)</f>
+        <v>11375</v>
       </c>
       <c r="J127" s="4">
-        <f>J125/(J125+K125)</f>
-        <v>0.47080439174315275</v>
-      </c>
-      <c r="K127" s="4">
-        <f>K125/(J125+K125)</f>
-        <v>0.52919560825684731</v>
+        <f>MIN(J126+K126, J34)</f>
+        <v>12387.306352787287</v>
       </c>
       <c r="M127" s="4">
-        <f>M125/(M125+N125)</f>
-        <v>0.48861588674665718</v>
-      </c>
-      <c r="N127" s="4">
-        <f>N125/(M125+N125)</f>
-        <v>0.51138411325334288</v>
+        <f>MIN(M126+N126, M34)</f>
+        <v>10279.151443376002</v>
       </c>
       <c r="P127" s="4">
-        <f>P125/(P125+Q125)</f>
-        <v>0.35702009429056636</v>
-      </c>
-      <c r="Q127" s="4">
-        <f>Q125/(P125+Q125)</f>
-        <v>0.64297990570943375</v>
+        <f>MIN(P126+Q126, P34)</f>
+        <v>15545.971689573857</v>
       </c>
       <c r="S127" s="4">
-        <f>S125/(S125+T125)</f>
-        <v>0.79219799280605052</v>
-      </c>
-      <c r="T127" s="4">
-        <f>T125/(S125+T125)</f>
-        <v>0.2078020071939494</v>
+        <f>MIN(S126+T126, S34)</f>
+        <v>8987.1415388984442</v>
       </c>
       <c r="V127" s="4">
-        <f>V125/(V125+W125)</f>
-        <v>0.58542403945975419</v>
-      </c>
-      <c r="W127" s="4">
-        <f>W125/(V125+W125)</f>
-        <v>0.41457596054024581</v>
+        <f>MIN(V126+W126, V34)</f>
+        <v>10467.780648504915</v>
       </c>
       <c r="Y127" s="4">
-        <f>Y125/(Y125+Z125)</f>
-        <v>0.55220543552753276</v>
-      </c>
-      <c r="Z127" s="4">
-        <f>Z125/(Y125+Z125)</f>
-        <v>0.44779456447246724</v>
+        <f>MIN(Y126+Z126, Y34)</f>
+        <v>9842.1904497703563</v>
       </c>
       <c r="AA127" s="38" t="s">
-        <v>486</v>
+        <v>325</v>
       </c>
       <c r="AB127" s="42" t="s">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="AC127" s="43" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="128" spans="1:29" ht="68" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="128" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="50" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B128" s="38" t="s">
-        <v>183</v>
+        <v>253</v>
       </c>
       <c r="C128" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F128" s="10" t="s">
+      <c r="F128" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G128" s="4">
+        <f>G126/(G126+H126)</f>
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="H128" s="4">
+        <f>H126/(G126+H126)</f>
+        <v>0.55384615384615388</v>
+      </c>
+      <c r="J128" s="4">
+        <f>J126/(J126+K126)</f>
+        <v>0.47080439174315275</v>
+      </c>
+      <c r="K128" s="4">
+        <f>K126/(J126+K126)</f>
+        <v>0.52919560825684731</v>
+      </c>
+      <c r="M128" s="4">
+        <f>M126/(M126+N126)</f>
+        <v>0.48861588674665718</v>
+      </c>
+      <c r="N128" s="4">
+        <f>N126/(M126+N126)</f>
+        <v>0.51138411325334288</v>
+      </c>
+      <c r="P128" s="4">
+        <f>P126/(P126+Q126)</f>
+        <v>0.35702009429056636</v>
+      </c>
+      <c r="Q128" s="4">
+        <f>Q126/(P126+Q126)</f>
+        <v>0.64297990570943375</v>
+      </c>
+      <c r="S128" s="4">
+        <f>S126/(S126+T126)</f>
+        <v>0.79219799280605052</v>
+      </c>
+      <c r="T128" s="4">
+        <f>T126/(S126+T126)</f>
+        <v>0.2078020071939494</v>
+      </c>
+      <c r="V128" s="4">
+        <f>V126/(V126+W126)</f>
+        <v>0.58542403945975419</v>
+      </c>
+      <c r="W128" s="4">
+        <f>W126/(V126+W126)</f>
+        <v>0.41457596054024581</v>
+      </c>
+      <c r="Y128" s="4">
+        <f>Y126/(Y126+Z126)</f>
+        <v>0.55220543552753276</v>
+      </c>
+      <c r="Z128" s="4">
+        <f>Z126/(Y126+Z126)</f>
+        <v>0.44779456447246724</v>
+      </c>
+      <c r="AA128" s="38" t="s">
+        <v>482</v>
+      </c>
+      <c r="AB128" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="AC128" s="43" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="129" spans="1:30" ht="68" x14ac:dyDescent="0.2">
+      <c r="A129" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B129" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F129" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G128" s="4">
-        <f>MAX(G14-G28, 0)*G116</f>
+      <c r="G129" s="4">
+        <f>MAX(G14-G28, 0)*G117</f>
         <v>4513584.2403750001</v>
       </c>
-      <c r="H128" s="4">
-        <f>MAX(H14-H28, 0)*H116</f>
+      <c r="H129" s="4">
+        <f>MAX(H14-H28, 0)*H117</f>
         <v>12433601.4893</v>
       </c>
-      <c r="J128" s="4">
-        <f>MAX(J14-J28, 0)*J116</f>
+      <c r="J129" s="4">
+        <f>MAX(J14-J28, 0)*J117</f>
         <v>4035039.8648233167</v>
       </c>
-      <c r="K128" s="4">
-        <f>MAX(K14-K28, 0)*K116</f>
+      <c r="K129" s="4">
+        <f>MAX(K14-K28, 0)*K117</f>
         <v>11414597.812208308</v>
       </c>
-      <c r="M128" s="4">
-        <f>MAX(M14-M28, 0)*M116</f>
+      <c r="M129" s="4">
+        <f>MAX(M14-M28, 0)*M117</f>
         <v>3516332.5365802972</v>
       </c>
-      <c r="N128" s="4">
-        <f>MAX(N14-N28, 0)*N116</f>
+      <c r="N129" s="4">
+        <f>MAX(N14-N28, 0)*N117</f>
         <v>10361539.512973329</v>
       </c>
-      <c r="P128" s="4">
-        <f>MAX(P14-P28, 0)*P116</f>
+      <c r="P129" s="4">
+        <f>MAX(P14-P28, 0)*P117</f>
         <v>2992454.3341056714</v>
       </c>
-      <c r="Q128" s="4">
-        <f>MAX(Q14-Q28, 0)*Q116</f>
+      <c r="Q129" s="4">
+        <f>MAX(Q14-Q28, 0)*Q117</f>
         <v>9271395.2987972517</v>
       </c>
-      <c r="S128" s="4">
-        <f>MAX(S14-S28, 0)*S116</f>
+      <c r="S129" s="4">
+        <f>MAX(S14-S28, 0)*S117</f>
         <v>2474015.3392973635</v>
       </c>
-      <c r="T128" s="4">
-        <f>MAX(T14-T28, 0)*T116</f>
+      <c r="T129" s="4">
+        <f>MAX(T14-T28, 0)*T117</f>
         <v>8160406.3842944754</v>
       </c>
-      <c r="V128" s="4">
-        <f>MAX(V14-V28, 0)*V116</f>
+      <c r="V129" s="4">
+        <f>MAX(V14-V28, 0)*V117</f>
         <v>1857328.2887372568</v>
       </c>
-      <c r="W128" s="4">
-        <f>MAX(W14-W28, 0)*W116</f>
+      <c r="W129" s="4">
+        <f>MAX(W14-W28, 0)*W117</f>
         <v>6443988.3112147413</v>
       </c>
-      <c r="Y128" s="4">
-        <f>MAX(Y14-Y28, 0)*Y116</f>
+      <c r="Y129" s="4">
+        <f>MAX(Y14-Y28, 0)*Y117</f>
         <v>1468232.3962543209</v>
       </c>
-      <c r="Z128" s="4">
-        <f>MAX(Z14-Z28, 0)*Z116</f>
+      <c r="Z129" s="4">
+        <f>MAX(Z14-Z28, 0)*Z117</f>
         <v>5088667.5032287594</v>
       </c>
-      <c r="AA128" s="38" t="s">
-        <v>484</v>
-      </c>
-      <c r="AB128" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="AC128" s="43" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="129" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB129" s="42"/>
-      <c r="AC129" s="43"/>
-    </row>
-    <row r="130" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="F130" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="8"/>
-      <c r="M130" s="8"/>
-      <c r="N130" s="8"/>
-      <c r="P130" s="8"/>
-      <c r="Q130" s="8"/>
-      <c r="S130" s="8"/>
-      <c r="T130" s="8"/>
-      <c r="V130" s="8"/>
-      <c r="W130" s="8"/>
-      <c r="Y130" s="8"/>
-      <c r="Z130" s="8"/>
+      <c r="AA129" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="AB129" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="AC129" s="43" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="130" spans="1:30" x14ac:dyDescent="0.2">
       <c r="AB130" s="42"/>
       <c r="AC130" s="43"/>
     </row>
-    <row r="131" spans="1:30" ht="51" x14ac:dyDescent="0.2">
-      <c r="B131" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="C131" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="G131" s="4">
-        <f>MAX(G34-G126,0)</f>
-        <v>1988625</v>
-      </c>
-      <c r="J131" s="4">
-        <f>MAX(J34-J126,0)</f>
-        <v>2037612.6936472128</v>
-      </c>
-      <c r="M131" s="4">
-        <f>MAX(M34-M126,0)</f>
-        <v>2099720.8485566238</v>
-      </c>
-      <c r="P131" s="4">
-        <f>MAX(P34-P126,0)</f>
-        <v>2194454.028310426</v>
-      </c>
-      <c r="S131" s="4">
-        <f>MAX(S34-S126,0)</f>
-        <v>2991012.8584611015</v>
-      </c>
-      <c r="V131" s="4">
-        <f>MAX(V34-V126,0)</f>
-        <v>24989532.219351497</v>
-      </c>
-      <c r="Y131" s="4">
-        <f>MAX(Y34-Y126,0)</f>
-        <v>2510157.8095502295</v>
-      </c>
-      <c r="AA131" s="38" t="s">
-        <v>442</v>
-      </c>
-      <c r="AB131" s="42" t="s">
-        <v>410</v>
-      </c>
-      <c r="AC131" s="43" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="132" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="F131" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
+      <c r="M131" s="8"/>
+      <c r="N131" s="8"/>
+      <c r="P131" s="8"/>
+      <c r="Q131" s="8"/>
+      <c r="S131" s="8"/>
+      <c r="T131" s="8"/>
+      <c r="V131" s="8"/>
+      <c r="W131" s="8"/>
+      <c r="Y131" s="8"/>
+      <c r="Z131" s="8"/>
+      <c r="AB131" s="42"/>
+      <c r="AC131" s="43"/>
+    </row>
+    <row r="132" spans="1:30" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="50" t="s">
+        <v>419</v>
+      </c>
       <c r="B132" s="38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C132" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F132" s="10" t="s">
-        <v>165</v>
+      <c r="F132" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="G132" s="4">
-        <f>MIN(G142,G131)</f>
+        <f>MAX(G34-G127,0)</f>
         <v>1988625</v>
       </c>
       <c r="J132" s="4">
-        <f>MIN(J142,J131)</f>
+        <f>MAX(J34-J127,0)</f>
         <v>2037612.6936472128</v>
       </c>
       <c r="M132" s="4">
-        <f>MIN(M142,M131)</f>
+        <f>MAX(M34-M127,0)</f>
         <v>2099720.8485566238</v>
       </c>
       <c r="P132" s="4">
-        <f>MIN(P142,P131)</f>
+        <f>MAX(P34-P127,0)</f>
         <v>2194454.028310426</v>
       </c>
       <c r="S132" s="4">
-        <f>MIN(S142,S131)</f>
+        <f>MAX(S34-S127,0)</f>
         <v>2991012.8584611015</v>
       </c>
       <c r="V132" s="4">
-        <f>MIN(V142,V131)</f>
-        <v>2349768.217245861</v>
+        <f>MAX(V34-V127,0)</f>
+        <v>24989532.219351497</v>
       </c>
       <c r="Y132" s="4">
-        <f>MIN(Y142,Y131)</f>
-        <v>388638.22348903998</v>
+        <f>MAX(Y34-Y127,0)</f>
+        <v>2510157.8095502295</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AB132" s="42" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AC132" s="43" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="133" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="133" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A133" s="50"/>
       <c r="B133" s="38" t="s">
-        <v>267</v>
+        <v>488</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F133" s="10" t="s">
-        <v>123</v>
-      </c>
+      <c r="F133" s="14"/>
       <c r="G133" s="4">
-        <f>G131-G132</f>
+        <f>MIN(G132,G35*H79)</f>
         <v>0</v>
       </c>
       <c r="J133" s="4">
-        <f>J131-J132</f>
+        <f>MIN(J132,J35*K79)</f>
         <v>0</v>
       </c>
       <c r="M133" s="4">
-        <f>M131-M132</f>
+        <f>MIN(M132,M35*N79)</f>
         <v>0</v>
       </c>
       <c r="P133" s="4">
-        <f>P131-P132</f>
+        <f>MIN(P132,P35*Q79)</f>
         <v>0</v>
       </c>
       <c r="S133" s="4">
-        <f>S131-S132</f>
+        <f>MIN(S132,S35*T79)</f>
         <v>0</v>
       </c>
       <c r="V133" s="4">
-        <f>V131-V132</f>
-        <v>22639764.002105635</v>
+        <f>MIN(V132,V35*W79)</f>
+        <v>0</v>
       </c>
       <c r="Y133" s="4">
-        <f>Y131-Y132</f>
-        <v>2121519.5860611894</v>
-      </c>
-      <c r="AA133" s="38" t="s">
-        <v>440</v>
-      </c>
-      <c r="AB133" s="42" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC133" s="43" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="134" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+        <f>MIN(Y132,Y35*Z79)</f>
+        <v>0</v>
+      </c>
+      <c r="AA133" s="38"/>
+      <c r="AB133" s="42"/>
+      <c r="AC133" s="43"/>
+    </row>
+    <row r="134" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B134" s="38" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="C134" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G134" s="4">
-        <f>MIN(G133,H78)</f>
-        <v>0</v>
+        <f>MIN(G144,MAX(G132-G133, 0))</f>
+        <v>1988625</v>
       </c>
       <c r="J134" s="4">
-        <f>MIN(J133,K78)</f>
-        <v>0</v>
+        <f>MIN(J144,MAX(J132-J133, 0))</f>
+        <v>2037612.6936472128</v>
       </c>
       <c r="M134" s="4">
-        <f>MIN(M133,N78)</f>
-        <v>0</v>
+        <f>MIN(M144,MAX(M132-M133, 0))</f>
+        <v>2099720.8485566238</v>
       </c>
       <c r="P134" s="4">
-        <f>MIN(P133,Q78)</f>
-        <v>0</v>
+        <f>MIN(P144,MAX(P132-P133, 0))</f>
+        <v>2194454.028310426</v>
       </c>
       <c r="S134" s="4">
-        <f>MIN(S133,T78)</f>
-        <v>0</v>
+        <f>MIN(S144,MAX(S132-S133, 0))</f>
+        <v>2991012.8584611015</v>
       </c>
       <c r="V134" s="4">
-        <f>MIN(V133,W78)</f>
-        <v>0</v>
+        <f>MIN(V144,MAX(V132-V133, 0))</f>
+        <v>2349768.217245861</v>
       </c>
       <c r="Y134" s="4">
-        <f>MIN(Y133,Z78)</f>
-        <v>0</v>
+        <f>MIN(Y144,MAX(Y132-Y133, 0))</f>
+        <v>388638.22348903998</v>
       </c>
       <c r="AA134" s="38" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AB134" s="42" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AC134" s="43" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="135" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="135" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B135" s="38" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C135" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F135" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G135" s="4">
+        <f>G132-G133-G134</f>
+        <v>0</v>
+      </c>
+      <c r="J135" s="4">
+        <f>J132-J133-J134</f>
+        <v>0</v>
+      </c>
+      <c r="M135" s="4">
+        <f>M132-M133-M134</f>
+        <v>0</v>
+      </c>
+      <c r="P135" s="4">
+        <f>P132-P133-P134</f>
+        <v>0</v>
+      </c>
+      <c r="S135" s="4">
+        <f>S132-S133-S134</f>
+        <v>0</v>
+      </c>
+      <c r="V135" s="4">
+        <f>V132-V133-V134</f>
+        <v>22639764.002105635</v>
+      </c>
+      <c r="Y135" s="4">
+        <f>Y132-Y133-Y134</f>
+        <v>2121519.5860611894</v>
+      </c>
+      <c r="AA135" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="AB135" s="42" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC135" s="43" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="136" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B136" s="38" t="s">
+        <v>489</v>
+      </c>
+      <c r="C136" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="G136" s="4">
+        <f>MIN(G135,H79-G133)</f>
+        <v>0</v>
+      </c>
+      <c r="J136" s="4">
+        <f>MIN(J135,K79-J133)</f>
+        <v>0</v>
+      </c>
+      <c r="M136" s="4">
+        <f>MIN(M135,N79-M133)</f>
+        <v>0</v>
+      </c>
+      <c r="P136" s="4">
+        <f>MIN(P135,Q79-P133)</f>
+        <v>0</v>
+      </c>
+      <c r="S136" s="4">
+        <f>MIN(S135,T79-S133)</f>
+        <v>0</v>
+      </c>
+      <c r="V136" s="4">
+        <f>MIN(V135,W79-V133)</f>
+        <v>0</v>
+      </c>
+      <c r="Y136" s="4">
+        <f>MIN(Y135,Z79-Y133)</f>
+        <v>0</v>
+      </c>
+      <c r="AA136" s="38" t="s">
+        <v>434</v>
+      </c>
+      <c r="AB136" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="AC136" s="43" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="137" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B137" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="C137" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F137" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="G135" s="4">
-        <f>G143*G132</f>
+      <c r="G137" s="4">
+        <f>G145*G134</f>
         <v>529635.22104433016</v>
       </c>
-      <c r="H135" s="4">
-        <f>H143*G132</f>
+      <c r="H137" s="4">
+        <f>H145*G134</f>
         <v>1458989.7789556701</v>
       </c>
-      <c r="J135" s="4">
-        <f>J143*J132</f>
+      <c r="J137" s="4">
+        <f>J145*J134</f>
         <v>532170.95570853585</v>
       </c>
-      <c r="K135" s="4">
-        <f>K143*J132</f>
+      <c r="K137" s="4">
+        <f>K145*J134</f>
         <v>1505441.737938677</v>
       </c>
-      <c r="M135" s="4">
-        <f>M143*M132</f>
+      <c r="M137" s="4">
+        <f>M145*M134</f>
         <v>550789.80536667234</v>
       </c>
-      <c r="N135" s="4">
-        <f>N143*M132</f>
+      <c r="N137" s="4">
+        <f>N145*M134</f>
         <v>1548931.0431899517</v>
       </c>
-      <c r="P135" s="4">
-        <f>P143*P132</f>
+      <c r="P137" s="4">
+        <f>P145*P134</f>
         <v>557000.38851015724</v>
       </c>
-      <c r="Q135" s="4">
-        <f>Q143*P132</f>
+      <c r="Q137" s="4">
+        <f>Q145*P134</f>
         <v>1637453.6398002687</v>
       </c>
-      <c r="S135" s="4">
-        <f>S143*S132</f>
+      <c r="S137" s="4">
+        <f>S145*S134</f>
         <v>676930.2312938408</v>
       </c>
-      <c r="T135" s="4">
-        <f>T143*S132</f>
+      <c r="T137" s="4">
+        <f>T145*S134</f>
         <v>2314082.6271672607</v>
       </c>
-      <c r="V135" s="4">
-        <f>V143*V132</f>
+      <c r="V137" s="4">
+        <f>V145*V134</f>
         <v>457497.26325426705</v>
       </c>
-      <c r="W135" s="4">
-        <f>W143*V132</f>
+      <c r="W137" s="4">
+        <f>W145*V134</f>
         <v>1892270.9539915938</v>
       </c>
-      <c r="Y135" s="4">
-        <f>Y143*Y132</f>
+      <c r="Y137" s="4">
+        <f>Y145*Y134</f>
         <v>52472.144479718736</v>
       </c>
-      <c r="Z135" s="4">
-        <f>Z143*Y132</f>
+      <c r="Z137" s="4">
+        <f>Z145*Y134</f>
         <v>336166.07900932123</v>
       </c>
-      <c r="AA135" s="38" t="s">
-        <v>438</v>
-      </c>
-      <c r="AB135" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="AC135" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="136" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="B136" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="C136" s="33" t="s">
+      <c r="AA137" s="38" t="s">
+        <v>435</v>
+      </c>
+      <c r="AB137" s="42" t="s">
+        <v>375</v>
+      </c>
+      <c r="AC137" s="43" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="138" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="B138" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="C138" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F136" s="10" t="s">
+      <c r="F138" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="G136" s="4">
-        <f>G135</f>
+      <c r="G138" s="4">
+        <f>G137</f>
         <v>529635.22104433016</v>
       </c>
-      <c r="H136" s="4">
-        <f>H135+G134</f>
+      <c r="H138" s="4">
+        <f>H137+G133+G136</f>
         <v>1458989.7789556701</v>
       </c>
-      <c r="J136" s="4">
-        <f>J135</f>
+      <c r="J138" s="4">
+        <f>J137</f>
         <v>532170.95570853585</v>
       </c>
-      <c r="K136" s="4">
-        <f>K135+J134</f>
+      <c r="K138" s="4">
+        <f>K137+J133+J136</f>
         <v>1505441.737938677</v>
       </c>
-      <c r="M136" s="4">
-        <f>M135</f>
+      <c r="M138" s="4">
+        <f>M137</f>
         <v>550789.80536667234</v>
       </c>
-      <c r="N136" s="4">
-        <f>N135+M134</f>
+      <c r="N138" s="4">
+        <f>N137+M133+M136</f>
         <v>1548931.0431899517</v>
       </c>
-      <c r="P136" s="4">
-        <f>P135</f>
+      <c r="P138" s="4">
+        <f>P137</f>
         <v>557000.38851015724</v>
       </c>
-      <c r="Q136" s="4">
-        <f>Q135+P134</f>
+      <c r="Q138" s="4">
+        <f>Q137+P133+P136</f>
         <v>1637453.6398002687</v>
       </c>
-      <c r="S136" s="4">
-        <f>S135</f>
+      <c r="S138" s="4">
+        <f>S137</f>
         <v>676930.2312938408</v>
       </c>
-      <c r="T136" s="4">
-        <f>T135+S134</f>
+      <c r="T138" s="4">
+        <f>T137+S133+S136</f>
         <v>2314082.6271672607</v>
       </c>
-      <c r="V136" s="4">
-        <f>V135</f>
+      <c r="V138" s="4">
+        <f>V137</f>
         <v>457497.26325426705</v>
       </c>
-      <c r="W136" s="4">
-        <f>W135+V134</f>
+      <c r="W138" s="4">
+        <f>W137+V133+V136</f>
         <v>1892270.9539915938</v>
       </c>
-      <c r="Y136" s="4">
-        <f>Y135</f>
+      <c r="Y138" s="4">
+        <f>Y137</f>
         <v>52472.144479718736</v>
       </c>
-      <c r="Z136" s="4">
-        <f>Z135+Y134</f>
+      <c r="Z138" s="4">
+        <f>Z137+Y133+Y136</f>
         <v>336166.07900932123</v>
       </c>
-      <c r="AA136" s="38" t="s">
-        <v>439</v>
-      </c>
-      <c r="AB136" s="42" t="s">
-        <v>444</v>
-      </c>
-      <c r="AC136" s="43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="137" spans="1:30" ht="17" x14ac:dyDescent="0.2">
-      <c r="F137" s="15" t="s">
+      <c r="AA138" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="AB138" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="AC138" s="43" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="139" spans="1:30" ht="17" x14ac:dyDescent="0.2">
+      <c r="F139" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="G137" s="8"/>
-      <c r="H137" s="8"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="8"/>
-      <c r="M137" s="8"/>
-      <c r="N137" s="8"/>
-      <c r="P137" s="8"/>
-      <c r="Q137" s="8"/>
-      <c r="S137" s="8"/>
-      <c r="T137" s="8"/>
-      <c r="V137" s="8"/>
-      <c r="W137" s="8"/>
-      <c r="Y137" s="8"/>
-      <c r="Z137" s="8"/>
-      <c r="AB137" s="42"/>
-      <c r="AC137" s="43"/>
-    </row>
-    <row r="138" spans="1:30" ht="119" x14ac:dyDescent="0.2">
-      <c r="B138" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="C138" s="28" t="s">
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="8"/>
+      <c r="M139" s="8"/>
+      <c r="N139" s="8"/>
+      <c r="P139" s="8"/>
+      <c r="Q139" s="8"/>
+      <c r="S139" s="8"/>
+      <c r="T139" s="8"/>
+      <c r="V139" s="8"/>
+      <c r="W139" s="8"/>
+      <c r="Y139" s="8"/>
+      <c r="Z139" s="8"/>
+      <c r="AB139" s="42"/>
+      <c r="AC139" s="43"/>
+    </row>
+    <row r="140" spans="1:30" ht="119" x14ac:dyDescent="0.2">
+      <c r="A140" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B140" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="C140" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="F138" s="10" t="s">
+      <c r="F140" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="G138" s="4">
-        <f>G116/$G$24</f>
+      <c r="G140" s="4">
+        <f>G117/$G$24</f>
         <v>1</v>
       </c>
-      <c r="H138" s="4">
-        <f>H116/$H$24</f>
+      <c r="H140" s="4">
+        <f>H117/$H$24</f>
         <v>1</v>
       </c>
-      <c r="J138" s="4">
-        <f>J116/$G$24</f>
+      <c r="J140" s="4">
+        <f>J117/$G$24</f>
         <v>0.8952116342841121</v>
       </c>
-      <c r="K138" s="4">
-        <f>K116/$H$24</f>
+      <c r="K140" s="4">
+        <f>K117/$H$24</f>
         <v>0.91854982240604577</v>
       </c>
-      <c r="M138" s="4">
-        <f>M116/$G$24</f>
+      <c r="M140" s="4">
+        <f>M117/$G$24</f>
         <v>0.78995136076604022</v>
       </c>
-      <c r="N138" s="4">
-        <f>N116/$H$24</f>
+      <c r="N140" s="4">
+        <f>N117/$H$24</f>
         <v>0.83420112677639169</v>
       </c>
-      <c r="P138" s="4">
-        <f>P116/$G$24</f>
+      <c r="P140" s="4">
+        <f>P117/$G$24</f>
         <v>0.681017640976468</v>
       </c>
-      <c r="Q138" s="4">
-        <f>Q116/$H$24</f>
+      <c r="Q140" s="4">
+        <f>Q117/$H$24</f>
         <v>0.74715264993241937</v>
       </c>
-      <c r="S138" s="4">
-        <f>S116/$G$24</f>
+      <c r="S140" s="4">
+        <f>S117/$G$24</f>
         <v>0.57085931969705117</v>
       </c>
-      <c r="T138" s="4">
-        <f>T116/$H$24</f>
+      <c r="T140" s="4">
+        <f>T117/$H$24</f>
         <v>0.6544689981823234</v>
       </c>
-      <c r="V138" s="4">
-        <f>V116/$G$24</f>
+      <c r="V140" s="4">
+        <f>V117/$G$24</f>
         <v>0.43663682585633068</v>
       </c>
-      <c r="W138" s="4">
-        <f>W116/$H$24</f>
+      <c r="W140" s="4">
+        <f>W117/$H$24</f>
         <v>0.51837579137580714</v>
       </c>
-      <c r="Y138" s="4">
-        <f>Y116/$G$24</f>
+      <c r="Y140" s="4">
+        <f>Y117/$G$24</f>
         <v>0.34596514607722179</v>
       </c>
-      <c r="Z138" s="4">
-        <f>Z116/$H$24</f>
+      <c r="Z140" s="4">
+        <f>Z117/$H$24</f>
         <v>0.40958701751064658</v>
       </c>
-      <c r="AA138" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="AB138" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="AC138" s="43" t="s">
-        <v>356</v>
-      </c>
-      <c r="AD138">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="139" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="A139" s="48" t="s">
-        <v>286</v>
-      </c>
-      <c r="B139" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="C139" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="G139" s="4">
-        <f>MAX(MIN((G138-$G$18)/$G$19, 1), 0)</f>
-        <v>1</v>
-      </c>
-      <c r="H139" s="4">
-        <f>MAX(MIN((H138-$H$18)/$H$19, 1), 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J139" s="4">
-        <f>MAX(MIN((J138-$G$18)/$G$19, 1), 0)</f>
-        <v>1</v>
-      </c>
-      <c r="K139" s="4">
-        <f>MAX(MIN((K138-$H$18)/$H$19, 1), 0)</f>
-        <v>1</v>
-      </c>
-      <c r="M139" s="4">
-        <f>MAX(MIN((M138-$G$18)/$G$19, 1), 0)</f>
-        <v>1</v>
-      </c>
-      <c r="N139" s="4">
-        <f>MAX(MIN((N138-$H$18)/$H$19, 1), 0)</f>
-        <v>0.95435915135809635</v>
-      </c>
-      <c r="P139" s="4">
-        <f>MAX(MIN((P138-$G$18)/$G$19, 1), 0)</f>
-        <v>0.81388590259622062</v>
-      </c>
-      <c r="Q139" s="4">
-        <f>MAX(MIN((Q138-$H$18)/$H$19, 1), 0)</f>
-        <v>0.77225276927863951</v>
-      </c>
-      <c r="S139" s="4">
-        <f>MAX(MIN((S138-$G$18)/$G$19, 1), 0)</f>
-        <v>0.55804708982295081</v>
-      </c>
-      <c r="T139" s="4">
-        <f>MAX(MIN((T138-$H$18)/$H$19, 1), 0)</f>
-        <v>0.57835753859728811</v>
-      </c>
-      <c r="V139" s="4">
-        <f>MAX(MIN((V138-$G$18)/$G$19, 1), 0)</f>
-        <v>0.2463200856997155</v>
-      </c>
-      <c r="W139" s="4">
-        <f>MAX(MIN((W138-$H$18)/$H$19, 1), 0)</f>
-        <v>0.29364903575296619</v>
-      </c>
-      <c r="Y139" s="4">
-        <f>MAX(MIN((Y138-$G$18)/$G$19, 1), 0)</f>
-        <v>3.5738309966176322E-2</v>
-      </c>
-      <c r="Z139" s="4">
-        <f>MAX(MIN((Z138-$H$18)/$H$19, 1), 0)</f>
-        <v>6.6061710417515754E-2</v>
-      </c>
-      <c r="AA139" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="AB139" s="42" t="s">
-        <v>380</v>
-      </c>
-      <c r="AC139" s="43" t="s">
-        <v>356</v>
-      </c>
-      <c r="AD139">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="B140" s="38"/>
-      <c r="AA140" s="38"/>
-      <c r="AB140" s="42"/>
-      <c r="AC140" s="43"/>
+      <c r="AA140" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="AB140" s="42" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC140" s="43" t="s">
+        <v>354</v>
+      </c>
       <c r="AD140">
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A141" s="50" t="s">
+        <v>419</v>
+      </c>
       <c r="B141" s="38" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C141" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="G141" s="4">
-        <f>G128*G139</f>
-        <v>4513584.2403750001</v>
+        <f>MAX(MIN((G140-$G$18)/$G$19, 1), 0)</f>
+        <v>1</v>
       </c>
       <c r="H141" s="4">
-        <f>H128*H139</f>
-        <v>12433601.4893</v>
+        <f>MAX(MIN((H140-$H$18)/$H$19, 1), 0)</f>
+        <v>1</v>
       </c>
       <c r="J141" s="4">
-        <f>J128*J139</f>
-        <v>4035039.8648233167</v>
+        <f>MAX(MIN((J140-$G$18)/$G$19, 1), 0)</f>
+        <v>1</v>
       </c>
       <c r="K141" s="4">
-        <f>K128*K139</f>
-        <v>11414597.812208308</v>
+        <f>MAX(MIN((K140-$H$18)/$H$19, 1), 0)</f>
+        <v>1</v>
       </c>
       <c r="M141" s="4">
-        <f>M128*M139</f>
-        <v>3516332.5365802972</v>
+        <f>MAX(MIN((M140-$G$18)/$G$19, 1), 0)</f>
+        <v>1</v>
       </c>
       <c r="N141" s="4">
-        <f>N128*N139</f>
-        <v>9888630.0563646089</v>
+        <f>MAX(MIN((N140-$H$18)/$H$19, 1), 0)</f>
+        <v>0.95435915135809635</v>
       </c>
       <c r="P141" s="4">
-        <f>P128*P139</f>
-        <v>2435516.3966915668</v>
+        <f>MAX(MIN((P140-$G$18)/$G$19, 1), 0)</f>
+        <v>0.81388590259622062</v>
       </c>
       <c r="Q141" s="4">
-        <f>Q128*Q139</f>
-        <v>7159860.694573137</v>
+        <f>MAX(MIN((Q140-$H$18)/$H$19, 1), 0)</f>
+        <v>0.77225276927863951</v>
       </c>
       <c r="S141" s="4">
-        <f>S128*S139</f>
-        <v>1380617.060272234</v>
+        <f>MAX(MIN((S140-$G$18)/$G$19, 1), 0)</f>
+        <v>0.55804708982295081</v>
       </c>
       <c r="T141" s="4">
-        <f>T128*T139</f>
-        <v>4719632.5503741484</v>
+        <f>MAX(MIN((T140-$H$18)/$H$19, 1), 0)</f>
+        <v>0.57835753859728811</v>
       </c>
       <c r="V141" s="4">
-        <f>V128*V139</f>
-        <v>457497.26325426705</v>
+        <f>MAX(MIN((V140-$G$18)/$G$19, 1), 0)</f>
+        <v>0.2463200856997155</v>
       </c>
       <c r="W141" s="4">
-        <f>W128*W139</f>
-        <v>1892270.9539915938</v>
+        <f>MAX(MIN((W140-$H$18)/$H$19, 1), 0)</f>
+        <v>0.29364903575296619</v>
       </c>
       <c r="Y141" s="4">
-        <f>Y128*Y139</f>
-        <v>52472.144479718736</v>
+        <f>MAX(MIN((Y140-$G$18)/$G$19, 1), 0)</f>
+        <v>3.5738309966176322E-2</v>
       </c>
       <c r="Z141" s="4">
-        <f>Z128*Z139</f>
-        <v>336166.07900932123</v>
-      </c>
-      <c r="AA141" s="38" t="s">
-        <v>485</v>
+        <f>MAX(MIN((Z140-$H$18)/$H$19, 1), 0)</f>
+        <v>6.6061710417515754E-2</v>
+      </c>
+      <c r="AA141" s="39" t="s">
+        <v>331</v>
       </c>
       <c r="AB141" s="42" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AC141" s="43" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="AD141">
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:30" ht="34" x14ac:dyDescent="0.2">
-      <c r="B142" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="C142" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F142" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G142" s="4">
-        <f>G141+H141</f>
-        <v>16947185.729674999</v>
-      </c>
-      <c r="H142" s="4">
-        <f>G142</f>
-        <v>16947185.729674999</v>
-      </c>
-      <c r="J142" s="4">
-        <f>J141+K141</f>
-        <v>15449637.677031625</v>
-      </c>
-      <c r="K142" s="4">
-        <f>J142</f>
-        <v>15449637.677031625</v>
-      </c>
-      <c r="M142" s="4">
-        <f>M141+N141</f>
-        <v>13404962.592944905</v>
-      </c>
-      <c r="N142" s="4">
-        <f>M142</f>
-        <v>13404962.592944905</v>
-      </c>
-      <c r="P142" s="4">
-        <f>P141+Q141</f>
-        <v>9595377.0912647042</v>
-      </c>
-      <c r="Q142" s="4">
-        <f>P142</f>
-        <v>9595377.0912647042</v>
-      </c>
-      <c r="S142" s="4">
-        <f>S141+T141</f>
-        <v>6100249.610646382</v>
-      </c>
-      <c r="T142" s="4">
-        <f>S142</f>
-        <v>6100249.610646382</v>
-      </c>
-      <c r="V142" s="4">
-        <f>V141+W141</f>
-        <v>2349768.217245861</v>
-      </c>
-      <c r="W142" s="4">
-        <f>V142</f>
-        <v>2349768.217245861</v>
-      </c>
-      <c r="Y142" s="4">
-        <f>Y141+Z141</f>
-        <v>388638.22348903998</v>
-      </c>
-      <c r="Z142" s="4">
-        <f>Y142</f>
-        <v>388638.22348903998</v>
-      </c>
-      <c r="AA142" s="38" t="s">
-        <v>360</v>
-      </c>
-      <c r="AB142" s="42" t="s">
-        <v>331</v>
-      </c>
-      <c r="AC142" s="43" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="143" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="B142" s="38"/>
+      <c r="AA142" s="38"/>
+      <c r="AB142" s="42"/>
+      <c r="AC142" s="43"/>
+      <c r="AD142">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143" spans="1:30" ht="51" x14ac:dyDescent="0.2">
+      <c r="A143" s="50" t="s">
+        <v>419</v>
+      </c>
       <c r="B143" s="38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C143" s="28" t="s">
         <v>174</v>
       </c>
       <c r="F143" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G143" s="4">
+        <f>G129*G141</f>
+        <v>4513584.2403750001</v>
+      </c>
+      <c r="H143" s="4">
+        <f>H129*H141</f>
+        <v>12433601.4893</v>
+      </c>
+      <c r="J143" s="4">
+        <f>J129*J141</f>
+        <v>4035039.8648233167</v>
+      </c>
+      <c r="K143" s="4">
+        <f>K129*K141</f>
+        <v>11414597.812208308</v>
+      </c>
+      <c r="M143" s="4">
+        <f>M129*M141</f>
+        <v>3516332.5365802972</v>
+      </c>
+      <c r="N143" s="4">
+        <f>N129*N141</f>
+        <v>9888630.0563646089</v>
+      </c>
+      <c r="P143" s="4">
+        <f>P129*P141</f>
+        <v>2435516.3966915668</v>
+      </c>
+      <c r="Q143" s="4">
+        <f>Q129*Q141</f>
+        <v>7159860.694573137</v>
+      </c>
+      <c r="S143" s="4">
+        <f>S129*S141</f>
+        <v>1380617.060272234</v>
+      </c>
+      <c r="T143" s="4">
+        <f>T129*T141</f>
+        <v>4719632.5503741484</v>
+      </c>
+      <c r="V143" s="4">
+        <f>V129*V141</f>
+        <v>457497.26325426705</v>
+      </c>
+      <c r="W143" s="4">
+        <f>W129*W141</f>
+        <v>1892270.9539915938</v>
+      </c>
+      <c r="Y143" s="4">
+        <f>Y129*Y141</f>
+        <v>52472.144479718736</v>
+      </c>
+      <c r="Z143" s="4">
+        <f>Z129*Z141</f>
+        <v>336166.07900932123</v>
+      </c>
+      <c r="AA143" s="38" t="s">
+        <v>481</v>
+      </c>
+      <c r="AB143" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="AC143" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD143">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A144" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B144" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C144" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G144" s="4">
+        <f>G143+H143</f>
+        <v>16947185.729674999</v>
+      </c>
+      <c r="H144" s="4">
+        <f>G144</f>
+        <v>16947185.729674999</v>
+      </c>
+      <c r="J144" s="4">
+        <f>J143+K143</f>
+        <v>15449637.677031625</v>
+      </c>
+      <c r="K144" s="4">
+        <f>J144</f>
+        <v>15449637.677031625</v>
+      </c>
+      <c r="M144" s="4">
+        <f>M143+N143</f>
+        <v>13404962.592944905</v>
+      </c>
+      <c r="N144" s="4">
+        <f>M144</f>
+        <v>13404962.592944905</v>
+      </c>
+      <c r="P144" s="4">
+        <f>P143+Q143</f>
+        <v>9595377.0912647042</v>
+      </c>
+      <c r="Q144" s="4">
+        <f>P144</f>
+        <v>9595377.0912647042</v>
+      </c>
+      <c r="S144" s="4">
+        <f>S143+T143</f>
+        <v>6100249.610646382</v>
+      </c>
+      <c r="T144" s="4">
+        <f>S144</f>
+        <v>6100249.610646382</v>
+      </c>
+      <c r="V144" s="4">
+        <f>V143+W143</f>
+        <v>2349768.217245861</v>
+      </c>
+      <c r="W144" s="4">
+        <f>V144</f>
+        <v>2349768.217245861</v>
+      </c>
+      <c r="Y144" s="4">
+        <f>Y143+Z143</f>
+        <v>388638.22348903998</v>
+      </c>
+      <c r="Z144" s="4">
+        <f>Y144</f>
+        <v>388638.22348903998</v>
+      </c>
+      <c r="AA144" s="38" t="s">
+        <v>484</v>
+      </c>
+      <c r="AB144" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="AC144" s="43" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="145" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A145" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="B145" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C145" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F145" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="G143" s="4">
-        <f>G141/G142</f>
+      <c r="G145" s="4">
+        <f>G143/G144</f>
         <v>0.26633237591015407</v>
       </c>
-      <c r="H143" s="4">
-        <f>H141/H142</f>
+      <c r="H145" s="4">
+        <f>H143/H144</f>
         <v>0.73366762408984598</v>
       </c>
-      <c r="J143" s="4">
-        <f>J141/J142</f>
+      <c r="J145" s="4">
+        <f>J143/J144</f>
         <v>0.26117375366168316</v>
       </c>
-      <c r="K143" s="4">
-        <f>K141/K142</f>
+      <c r="K145" s="4">
+        <f>K143/K144</f>
         <v>0.73882624633831684</v>
       </c>
-      <c r="M143" s="4">
-        <f>M141/M142</f>
+      <c r="M145" s="4">
+        <f>M143/M144</f>
         <v>0.26231572913384776</v>
       </c>
-      <c r="N143" s="4">
-        <f>N141/N142</f>
+      <c r="N145" s="4">
+        <f>N143/N144</f>
         <v>0.73768427086615229</v>
       </c>
-      <c r="P143" s="4">
-        <f>P141/P142</f>
+      <c r="P145" s="4">
+        <f>P143/P144</f>
         <v>0.25382185332859675</v>
       </c>
-      <c r="Q143" s="4">
-        <f>Q141/Q142</f>
+      <c r="Q145" s="4">
+        <f>Q143/Q144</f>
         <v>0.74617814667140325</v>
       </c>
-      <c r="S143" s="4">
-        <f>S141/S142</f>
+      <c r="S145" s="4">
+        <f>S143/S144</f>
         <v>0.22632140459674469</v>
       </c>
-      <c r="T143" s="4">
-        <f>T141/T142</f>
+      <c r="T145" s="4">
+        <f>T143/T144</f>
         <v>0.77367859540325534</v>
       </c>
-      <c r="V143" s="4">
-        <f>V141/V142</f>
+      <c r="V145" s="4">
+        <f>V143/V144</f>
         <v>0.19469888982943809</v>
       </c>
-      <c r="W143" s="4">
-        <f>W141/W142</f>
+      <c r="W145" s="4">
+        <f>W143/W144</f>
         <v>0.80530111017056183</v>
       </c>
-      <c r="Y143" s="4">
-        <f>Y141/Y142</f>
+      <c r="Y145" s="4">
+        <f>Y143/Y144</f>
         <v>0.13501539814752295</v>
       </c>
-      <c r="Z143" s="4">
-        <f>Z141/Z142</f>
+      <c r="Z145" s="4">
+        <f>Z143/Z144</f>
         <v>0.86498460185247705</v>
       </c>
-      <c r="AA143" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB143" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="AC143" s="43" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="AB144" s="42"/>
-      <c r="AC144" s="43"/>
-    </row>
-    <row r="145" spans="2:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="F145" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="G145" s="8"/>
-      <c r="H145" s="8"/>
-      <c r="J145" s="8"/>
-      <c r="K145" s="8"/>
-      <c r="M145" s="8"/>
-      <c r="N145" s="8"/>
-      <c r="P145" s="8"/>
-      <c r="Q145" s="8"/>
-      <c r="S145" s="8"/>
-      <c r="T145" s="8"/>
-      <c r="V145" s="8"/>
-      <c r="W145" s="8"/>
-      <c r="Y145" s="8"/>
-      <c r="Z145" s="8"/>
-      <c r="AB145" s="42"/>
-      <c r="AC145" s="43"/>
-    </row>
-    <row r="146" spans="2:29" ht="51" x14ac:dyDescent="0.2">
-      <c r="B146" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="C146" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F146" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="G146" s="4">
-        <f>(G114 - G135 - G123)*$G$31</f>
-        <v>10931.697702960402</v>
-      </c>
-      <c r="H146" s="4">
-        <f>(H114 - H135 - H123)*$H$31+H96</f>
-        <v>36943.686047039599</v>
-      </c>
-      <c r="J146" s="4">
-        <f>(J114 - J135 - J123)*$G$31</f>
-        <v>10088.976214210876</v>
-      </c>
-      <c r="K146" s="4">
-        <f>(K114 - K135 - K123)*$H$31+K96</f>
-        <v>34866.701411741393</v>
-      </c>
-      <c r="M146" s="4">
-        <f>(M114 - M135 - M123)*$G$31</f>
-        <v>9220.1553859644791</v>
-      </c>
-      <c r="N146" s="4">
-        <f>(N114 - N135 - N123)*$H$31+N96</f>
-        <v>32727.700888143867</v>
-      </c>
-      <c r="P146" s="4">
-        <f>(P114 - P135 - P123)*$G$31</f>
-        <v>8341.6941718801863</v>
-      </c>
-      <c r="Q146" s="4">
-        <f>(Q114 - Q135 - Q123)*$H$31+Q96</f>
-        <v>30440.781724683824</v>
-      </c>
-      <c r="S146" s="4">
-        <f>(S114 - S135 - S123)*$G$31</f>
-        <v>7272.4695733040871</v>
-      </c>
-      <c r="T146" s="4">
-        <f>(T114 - T135 - T123)*$H$31+T96</f>
-        <v>27115.480226723997</v>
-      </c>
-      <c r="V146" s="4">
-        <f>(V114 - V135 - V123)*$G$31</f>
-        <v>6551.7956953686007</v>
-      </c>
-      <c r="W146" s="4">
-        <f>(W114 - W135 - W123)*$H$31+W96</f>
-        <v>24450.873774900079</v>
-      </c>
-      <c r="Y146" s="4">
-        <f>(Y114 - Y135 - Y123)*$G$31</f>
-        <v>6466.2561670936466</v>
-      </c>
-      <c r="Z146" s="4">
-        <f>(Z114 - Z135 - Z123)*$H$31+Z96</f>
-        <v>24233.450635277597</v>
-      </c>
-      <c r="AA146" s="38" t="s">
-        <v>453</v>
-      </c>
-      <c r="AB146" s="42" t="s">
-        <v>383</v>
-      </c>
-      <c r="AC146" s="43" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="147" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B147" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="C147" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="G147" s="4">
-        <f>G146*$G22</f>
-        <v>3279.5093108881206</v>
-      </c>
-      <c r="H147" s="4">
-        <f>H146*$H22</f>
-        <v>9235.9215117598997</v>
-      </c>
-      <c r="J147" s="4">
-        <f>J146*$G22</f>
-        <v>3026.6928642632624</v>
-      </c>
-      <c r="K147" s="4">
-        <f>K146*$H22</f>
-        <v>8716.6753529353482</v>
-      </c>
-      <c r="M147" s="4">
-        <f>M146*$G22</f>
-        <v>2766.0466157893438</v>
-      </c>
-      <c r="N147" s="4">
-        <f>N146*$H22</f>
-        <v>8181.9252220359667</v>
-      </c>
-      <c r="P147" s="4">
-        <f>P146*$G22</f>
-        <v>2502.5082515640556</v>
-      </c>
-      <c r="Q147" s="4">
-        <f>Q146*$H22</f>
-        <v>7610.195431170956</v>
-      </c>
-      <c r="S147" s="4">
-        <f>S146*$G22</f>
-        <v>2181.740871991226</v>
-      </c>
-      <c r="T147" s="4">
-        <f>T146*$H22</f>
-        <v>6778.8700566809994</v>
-      </c>
-      <c r="V147" s="4">
-        <f>V146*$G22</f>
-        <v>1965.5387086105802</v>
-      </c>
-      <c r="W147" s="4">
-        <f>W146*$H22</f>
-        <v>6112.7184437250198</v>
-      </c>
-      <c r="Y147" s="4">
-        <f>Y146*$G22</f>
-        <v>1939.8768501280938</v>
-      </c>
-      <c r="Z147" s="4">
-        <f>Z146*$H22</f>
-        <v>6058.3626588193993</v>
-      </c>
-      <c r="AA147" s="38" t="s">
-        <v>454</v>
-      </c>
-      <c r="AB147" s="42" t="s">
-        <v>384</v>
-      </c>
-      <c r="AC147" s="43" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="148" spans="2:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="AA145" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB145" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="AC145" s="43" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="146" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB146" s="42"/>
+      <c r="AC146" s="43"/>
+    </row>
+    <row r="147" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="F147" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="J147" s="8"/>
+      <c r="K147" s="8"/>
+      <c r="M147" s="8"/>
+      <c r="N147" s="8"/>
+      <c r="P147" s="8"/>
+      <c r="Q147" s="8"/>
+      <c r="S147" s="8"/>
+      <c r="T147" s="8"/>
+      <c r="V147" s="8"/>
+      <c r="W147" s="8"/>
+      <c r="Y147" s="8"/>
+      <c r="Z147" s="8"/>
+      <c r="AB147" s="42"/>
+      <c r="AC147" s="43"/>
+    </row>
+    <row r="148" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B148" s="38" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C148" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F148" s="14" t="s">
-        <v>213</v>
+      <c r="F148" s="10" t="s">
+        <v>201</v>
       </c>
       <c r="G148" s="4">
-        <f>G135*$G22</f>
-        <v>158890.56631329903</v>
+        <f>(G115 - G137 - G124)*$G$31</f>
+        <v>10931.697702960402</v>
       </c>
       <c r="H148" s="4">
-        <f>(H135+G134)*$H22</f>
-        <v>364747.44473891752</v>
+        <f>(H115 - H137 - H124)*$H$31+H97</f>
+        <v>36943.686047039599</v>
       </c>
       <c r="J148" s="4">
-        <f>J135*$G22</f>
-        <v>159651.28671256074</v>
+        <f>(J115 - J137 - J124)*$G$31</f>
+        <v>10088.976214210876</v>
       </c>
       <c r="K148" s="4">
-        <f>(K135+J134)*$H22</f>
-        <v>376360.43448466924</v>
+        <f>(K115 - K137 - K124)*$H$31+K97</f>
+        <v>34866.701411741393</v>
       </c>
       <c r="M148" s="4">
-        <f>M135*$G22</f>
-        <v>165236.9416100017</v>
+        <f>(M115 - M137 - M124)*$G$31</f>
+        <v>9220.1553859644791</v>
       </c>
       <c r="N148" s="4">
-        <f>(N135+M134)*$H22</f>
-        <v>387232.76079748792</v>
+        <f>(N115 - N137 - N124)*$H$31+N97</f>
+        <v>32727.700888143867</v>
       </c>
       <c r="P148" s="4">
-        <f>P135*$G22</f>
-        <v>167100.11655304718</v>
+        <f>(P115 - P137 - P124)*$G$31</f>
+        <v>8341.6941718801863</v>
       </c>
       <c r="Q148" s="4">
-        <f>(Q135+P134)*$H22</f>
-        <v>409363.40995006717</v>
+        <f>(Q115 - Q137 - Q124)*$H$31+Q97</f>
+        <v>30440.781724683824</v>
       </c>
       <c r="S148" s="4">
-        <f>S135*$G22</f>
-        <v>203079.06938815225</v>
+        <f>(S115 - S137 - S124)*$G$31</f>
+        <v>7272.4695733040871</v>
       </c>
       <c r="T148" s="4">
-        <f>(T135+S134)*$H22</f>
-        <v>578520.65679181518</v>
+        <f>(T115 - T137 - T124)*$H$31+T97</f>
+        <v>27115.480226723997</v>
       </c>
       <c r="V148" s="4">
-        <f>V135*$G22</f>
-        <v>137249.17897628012</v>
+        <f>(V115 - V137 - V124)*$G$31</f>
+        <v>6551.7956953686007</v>
       </c>
       <c r="W148" s="4">
-        <f>(W135+V134)*$H22</f>
-        <v>473067.73849789845</v>
+        <f>(W115 - W137 - W124)*$H$31+W97</f>
+        <v>24450.873774900079</v>
       </c>
       <c r="Y148" s="4">
-        <f>Y135*$G22</f>
-        <v>15741.643343915621</v>
+        <f>(Y115 - Y137 - Y124)*$G$31</f>
+        <v>6466.2561670936466</v>
       </c>
       <c r="Z148" s="4">
-        <f>(Z135+Y134)*$H22</f>
-        <v>84041.519752330307</v>
+        <f>(Z115 - Z137 - Z124)*$H$31+Z97</f>
+        <v>24233.450635277597</v>
       </c>
       <c r="AA148" s="38" t="s">
-        <v>336</v>
+        <v>450</v>
       </c>
       <c r="AB148" s="42" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AC148" s="43" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="149" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="149" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B149" s="38" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="C149" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F149" s="10" t="s">
-        <v>166</v>
-      </c>
       <c r="G149" s="4">
-        <f>G123-G126*G127-G124</f>
-        <v>2175</v>
+        <f>G148*$G22</f>
+        <v>3279.5093108881206</v>
       </c>
       <c r="H149" s="4">
-        <f>H123-G126*H127-H124+H55</f>
-        <v>2700</v>
+        <f>H148*$H22</f>
+        <v>9235.9215117598997</v>
       </c>
       <c r="J149" s="4">
-        <f>J123-J126*J127-J124</f>
-        <v>2499.4278140400493</v>
+        <f>J148*$G22</f>
+        <v>3026.6928642632624</v>
       </c>
       <c r="K149" s="4">
-        <f>K123-J126*K127-K124+K55</f>
-        <v>2809.4177657259334</v>
+        <f>K148*$H22</f>
+        <v>8716.6753529353482</v>
       </c>
       <c r="M149" s="4">
-        <f>M123-M126*M127-M124</f>
-        <v>2152.52429893215</v>
+        <f>M148*$G22</f>
+        <v>2766.0466157893438</v>
       </c>
       <c r="N149" s="4">
-        <f>N123-M126*N127-N124+N55</f>
-        <v>2252.8263196575672</v>
+        <f>N148*$H22</f>
+        <v>8181.9252220359667</v>
       </c>
       <c r="P149" s="4">
-        <f>P123-P126*P127-P124</f>
-        <v>2378.667547907201</v>
+        <f>P148*$G22</f>
+        <v>2502.5082515640556</v>
       </c>
       <c r="Q149" s="4">
-        <f>Q123-P126*Q127-Q124+Q55</f>
-        <v>4283.8917476244524</v>
+        <f>Q148*$H22</f>
+        <v>7610.195431170956</v>
       </c>
       <c r="S149" s="4">
-        <f>S123-S126*S127-S124</f>
-        <v>3051.2552092196693</v>
+        <f>S148*$G22</f>
+        <v>2181.740871991226</v>
       </c>
       <c r="T149" s="4">
-        <f>T123-S126*T127-T124+T55</f>
-        <v>800.37687887966456</v>
+        <f>T148*$H22</f>
+        <v>6778.8700566809994</v>
       </c>
       <c r="V149" s="4">
-        <f>V123-V126*V127-V124</f>
-        <v>2626.324470611311</v>
+        <f>V148*$G22</f>
+        <v>1965.5387086105802</v>
       </c>
       <c r="W149" s="4">
-        <f>W123-V126*W127-W124+W55</f>
-        <v>1859.8672358907961</v>
+        <f>W148*$H22</f>
+        <v>6112.7184437250198</v>
       </c>
       <c r="Y149" s="4">
-        <f>Y123-Y126*Y127-Y124</f>
-        <v>2329.2475987972985</v>
+        <f>Y148*$G22</f>
+        <v>1939.8768501280938</v>
       </c>
       <c r="Z149" s="4">
-        <f>Z123-Y126*Z127-Z124+Z55</f>
-        <v>1888.8340225328548</v>
+        <f>Z148*$H22</f>
+        <v>6058.3626588193993</v>
       </c>
       <c r="AA149" s="38" t="s">
-        <v>337</v>
+        <v>451</v>
       </c>
       <c r="AB149" s="42" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AC149" s="43" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="150" spans="2:29" ht="34" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="150" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="B150" s="38" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
       <c r="C150" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="F150" s="10" t="s">
-        <v>167</v>
+      <c r="F150" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="G150" s="4">
-        <f>MAX((G123 - G124)*$G22-G17*G9,0)</f>
-        <v>2128.25</v>
+        <f>G137*$G22</f>
+        <v>158890.56631329903</v>
       </c>
       <c r="H150" s="4">
-        <f>MAX((H123-H124+H55)*$H22-H17*H9,0)</f>
-        <v>2058</v>
+        <f>(H137+G133+G136)*$H22</f>
+        <v>364747.44473891752</v>
       </c>
       <c r="J150" s="4">
-        <f>MAX((J123 - J124)*$G22-J17*J9,0)</f>
-        <v>2440.2984140400481</v>
+        <f>J137*$G22</f>
+        <v>159651.28671256074</v>
       </c>
       <c r="K150" s="4">
-        <f>MAX((K123-K124+K55)*$H22-K17*K9,0)</f>
-        <v>2134.2054714382775</v>
+        <f>(K137+J133+J136)*$H22</f>
+        <v>376360.43448466924</v>
       </c>
       <c r="M150" s="4">
-        <f>MAX((M123 - M124)*$G22-M17*M9,0)</f>
-        <v>2096.1250989321488</v>
+        <f>M137*$G22</f>
+        <v>165236.9416100017</v>
       </c>
       <c r="N150" s="4">
-        <f>MAX((N123-N124+N55)*$H22-N17*N9,0)</f>
-        <v>1700.4848663813059</v>
+        <f>(N137+M133+M136)*$H22</f>
+        <v>387232.76079748792</v>
       </c>
       <c r="P150" s="4">
-        <f>MAX((P123 - P124)*$G22-P17*P9,0)</f>
-        <v>2317.1445479071999</v>
+        <f>P137*$G22</f>
+        <v>167100.11655304718</v>
       </c>
       <c r="Q150" s="4">
-        <f>MAX((Q123-Q124+Q55)*$H22-Q17*Q9,0)</f>
-        <v>3204.9561896870446</v>
+        <f>(Q137+P133+P136)*$H22</f>
+        <v>409363.40995006717</v>
       </c>
       <c r="S150" s="4">
-        <f>MAX((S123 - S124)*$G22-S17*S9,0)</f>
-        <v>2954.0152092196686</v>
+        <f>S137*$G22</f>
+        <v>203079.06938815225</v>
       </c>
       <c r="T150" s="4">
-        <f>MAX((T123-T124+T55)*$H22-T17*T9,0)</f>
-        <v>591.35193239972011</v>
+        <f>(T137+S133+S136)*$H22</f>
+        <v>578520.65679181518</v>
       </c>
       <c r="V150" s="4">
-        <f>MAX((V123 - V124)*$G22-V17*V9,0)</f>
-        <v>2551.1878706113116</v>
+        <f>V137*$G22</f>
+        <v>137249.17897628012</v>
       </c>
       <c r="W150" s="4">
-        <f>MAX((W123-W124+W55)*$H22-W17*W9,0)</f>
-        <v>1328.1293632423296</v>
+        <f>(W137+V133+V136)*$H22</f>
+        <v>473067.73849789845</v>
       </c>
       <c r="Y150" s="4">
-        <f>MAX((Y123 - Y124)*$G22-Y17*Y9,0)</f>
-        <v>2235.7849987972986</v>
+        <f>Y137*$G22</f>
+        <v>15741.643343915621</v>
       </c>
       <c r="Z150" s="4">
-        <f>MAX((Z123-Z124+Z55)*$H22-Z17*Z9,0)</f>
-        <v>1373.5803521107118</v>
+        <f>(Z137+Y133+Y136)*$H22</f>
+        <v>84041.519752330307</v>
       </c>
       <c r="AA150" s="38" t="s">
         <v>334</v>
       </c>
       <c r="AB150" s="42" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="AC150" s="43" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="151" spans="2:29" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="151" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B151" s="38" t="s">
-        <v>284</v>
+        <v>176</v>
       </c>
       <c r="C151" s="33" t="s">
         <v>163</v>
       </c>
+      <c r="F151" s="10" t="s">
+        <v>166</v>
+      </c>
       <c r="G151" s="4">
-        <f>J113*J7*(1+$G22)</f>
+        <f>G124-G127*G128-G125</f>
+        <v>2175</v>
+      </c>
+      <c r="H151" s="4">
+        <f>H124-G127*H128-H125+H56</f>
+        <v>2700</v>
+      </c>
+      <c r="J151" s="4">
+        <f>J124-J127*J128-J125</f>
+        <v>2499.4278140400493</v>
+      </c>
+      <c r="K151" s="4">
+        <f>K124-J127*K128-K125+K56</f>
+        <v>2809.4177657259334</v>
+      </c>
+      <c r="M151" s="4">
+        <f>M124-M127*M128-M125</f>
+        <v>2152.52429893215</v>
+      </c>
+      <c r="N151" s="4">
+        <f>N124-M127*N128-N125+N56</f>
+        <v>2252.8263196575672</v>
+      </c>
+      <c r="P151" s="4">
+        <f>P124-P127*P128-P125</f>
+        <v>2378.667547907201</v>
+      </c>
+      <c r="Q151" s="4">
+        <f>Q124-P127*Q128-Q125+Q56</f>
+        <v>4283.8917476244524</v>
+      </c>
+      <c r="S151" s="4">
+        <f>S124-S127*S128-S125</f>
+        <v>3051.2552092196693</v>
+      </c>
+      <c r="T151" s="4">
+        <f>T124-S127*T128-T125+T56</f>
+        <v>800.37687887966456</v>
+      </c>
+      <c r="V151" s="4">
+        <f>V124-V127*V128-V125</f>
+        <v>2626.324470611311</v>
+      </c>
+      <c r="W151" s="4">
+        <f>W124-V127*W128-W125+W56</f>
+        <v>1859.8672358907961</v>
+      </c>
+      <c r="Y151" s="4">
+        <f>Y124-Y127*Y128-Y125</f>
+        <v>2329.2475987972985</v>
+      </c>
+      <c r="Z151" s="4">
+        <f>Z124-Y127*Z128-Z125+Z56</f>
+        <v>1888.8340225328548</v>
+      </c>
+      <c r="AA151" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="AB151" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC151" s="43" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="152" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="B152" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C152" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G152" s="4">
+        <f>MAX((G124 - G125)*$G22-G17*G9,0)</f>
+        <v>2128.25</v>
+      </c>
+      <c r="H152" s="4">
+        <f>MAX((H124-H125+H56)*$H22-H17*H9,0)</f>
+        <v>2058</v>
+      </c>
+      <c r="J152" s="4">
+        <f>MAX((J124 - J125)*$G22-J17*J9,0)</f>
+        <v>2440.2984140400481</v>
+      </c>
+      <c r="K152" s="4">
+        <f>MAX((K124-K125+K56)*$H22-K17*K9,0)</f>
+        <v>2134.2054714382775</v>
+      </c>
+      <c r="M152" s="4">
+        <f>MAX((M124 - M125)*$G22-M17*M9,0)</f>
+        <v>2096.1250989321488</v>
+      </c>
+      <c r="N152" s="4">
+        <f>MAX((N124-N125+N56)*$H22-N17*N9,0)</f>
+        <v>1700.4848663813059</v>
+      </c>
+      <c r="P152" s="4">
+        <f>MAX((P124 - P125)*$G22-P17*P9,0)</f>
+        <v>2317.1445479071999</v>
+      </c>
+      <c r="Q152" s="4">
+        <f>MAX((Q124-Q125+Q56)*$H22-Q17*Q9,0)</f>
+        <v>3204.9561896870446</v>
+      </c>
+      <c r="S152" s="4">
+        <f>MAX((S124 - S125)*$G22-S17*S9,0)</f>
+        <v>2954.0152092196686</v>
+      </c>
+      <c r="T152" s="4">
+        <f>MAX((T124-T125+T56)*$H22-T17*T9,0)</f>
+        <v>591.35193239972011</v>
+      </c>
+      <c r="V152" s="4">
+        <f>MAX((V124 - V125)*$G22-V17*V9,0)</f>
+        <v>2551.1878706113116</v>
+      </c>
+      <c r="W152" s="4">
+        <f>MAX((W124-W125+W56)*$H22-W17*W9,0)</f>
+        <v>1328.1293632423296</v>
+      </c>
+      <c r="Y152" s="4">
+        <f>MAX((Y124 - Y125)*$G22-Y17*Y9,0)</f>
+        <v>2235.7849987972986</v>
+      </c>
+      <c r="Z152" s="4">
+        <f>MAX((Z124-Z125+Z56)*$H22-Z17*Z9,0)</f>
+        <v>1373.5803521107118</v>
+      </c>
+      <c r="AA152" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB152" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC152" s="43" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="153" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B153" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="C153" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="G153" s="4">
+        <f>J114*J7*(1+$G22)</f>
         <v>19480.5</v>
       </c>
-      <c r="H151" s="4">
-        <f>(K113*K7+SUMPRODUCT(H39:H42,H87:H90))*(1+$H22)</f>
+      <c r="H153" s="4">
+        <f>(K114*K7+SUMPRODUCT(H40:H43,H88:H91))*(1+$H22)</f>
         <v>287385</v>
       </c>
-      <c r="J151" s="4">
-        <f>M113*M7*(1+$G22)</f>
+      <c r="J153" s="4">
+        <f>M114*M7*(1+$G22)</f>
         <v>19456.32</v>
       </c>
-      <c r="K151" s="4">
-        <f>(N113*N7+SUMPRODUCT(K39:K42,K87:K90))*(1+$H22)</f>
+      <c r="K153" s="4">
+        <f>(N114*N7+SUMPRODUCT(K40:K43,K88:K91))*(1+$H22)</f>
         <v>287259.5625</v>
       </c>
-      <c r="M151" s="4">
-        <f>P113*P7*(1+$G22)</f>
+      <c r="M153" s="4">
+        <f>P114*P7*(1+$G22)</f>
         <v>19433.7</v>
       </c>
-      <c r="N151" s="4">
-        <f>(Q113*Q7+SUMPRODUCT(N39:N42,N87:N90))*(1+$H22)</f>
+      <c r="N153" s="4">
+        <f>(Q114*Q7+SUMPRODUCT(N40:N43,N88:N91))*(1+$H22)</f>
         <v>287156.71250000002</v>
       </c>
-      <c r="P151" s="4">
-        <f>S113*S7*(1+$G22)</f>
+      <c r="P153" s="4">
+        <f>S114*S7*(1+$G22)</f>
         <v>19406.400000000001</v>
       </c>
-      <c r="Q151" s="4">
-        <f>(T113*T7+SUMPRODUCT(Q39:Q42,Q87:Q90))*(1+$H22)</f>
+      <c r="Q153" s="4">
+        <f>(T114*T7+SUMPRODUCT(Q40:Q43,Q88:Q91))*(1+$H22)</f>
         <v>286948.5</v>
       </c>
-      <c r="S151" s="4">
-        <f>V113*V7*(1+$G22)</f>
+      <c r="S153" s="4">
+        <f>V114*V7*(1+$G22)</f>
         <v>19367.400000000001</v>
       </c>
-      <c r="T151" s="4">
-        <f>(W113*W7+SUMPRODUCT(T39:T42,T87:T90))*(1+$H22)</f>
+      <c r="T153" s="4">
+        <f>(W114*W7+SUMPRODUCT(T40:T43,T88:T91))*(1+$H22)</f>
         <v>286924.28750000003</v>
       </c>
-      <c r="V151" s="4">
-        <f>Y113*Y7*(1+$G22)</f>
+      <c r="V153" s="4">
+        <f>Y114*Y7*(1+$G22)</f>
         <v>16645.359726367005</v>
       </c>
-      <c r="W151" s="4">
-        <f>(Z113*Z7+SUMPRODUCT(W39:W42,W87:W90))*(1+$H22)</f>
+      <c r="W153" s="4">
+        <f>(Z114*Z7+SUMPRODUCT(W40:W43,W88:W91))*(1+$H22)</f>
         <v>286838.73750000005</v>
       </c>
-      <c r="Y151" s="4" t="e">
-        <f>AB113*AB7*(1+$G22)</f>
+      <c r="Y153" s="4" t="e">
+        <f>AB114*AB7*(1+$G22)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z151" s="4" t="e">
-        <f>(AC113*AC7+SUMPRODUCT(Z39:Z42,Z87:Z90))*(1+$H22)</f>
+      <c r="Z153" s="4" t="e">
+        <f>(AC114*AC7+SUMPRODUCT(Z40:Z43,Z88:Z91))*(1+$H22)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA151" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="AB151" s="42" t="s">
-        <v>388</v>
-      </c>
-      <c r="AC151" s="43" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="152" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB152" s="42"/>
-      <c r="AC152" s="43"/>
-    </row>
-    <row r="153" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AB153" s="42"/>
-      <c r="AC153" s="43"/>
-    </row>
-    <row r="154" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B154" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="G154" s="4">
-        <f>G149+G124</f>
-        <v>2425</v>
-      </c>
-      <c r="H154" s="4">
-        <f>H149+H124</f>
-        <v>3700</v>
-      </c>
-      <c r="J154" s="4">
-        <f>J149+J124</f>
-        <v>2815.6278140400491</v>
-      </c>
-      <c r="K154" s="4">
-        <f>K149+K124</f>
-        <v>3887.4177657259334</v>
-      </c>
-      <c r="M154" s="4">
-        <f>M149+M124</f>
-        <v>2454.1242989321499</v>
-      </c>
-      <c r="N154" s="4">
-        <f>N149+N124</f>
-        <v>3174.026319657567</v>
-      </c>
-      <c r="P154" s="4">
-        <f>P149+P124</f>
-        <v>2707.667547907201</v>
-      </c>
-      <c r="Q154" s="4">
-        <f>Q149+Q124</f>
-        <v>6184.6917476244525</v>
-      </c>
-      <c r="S154" s="4">
-        <f>S149+S124</f>
-        <v>3571.2552092196693</v>
-      </c>
-      <c r="T154" s="4">
-        <f>T149+T124</f>
-        <v>1194.2768788796645</v>
-      </c>
-      <c r="V154" s="4">
-        <f>V149+V124</f>
-        <v>3028.1244706113112</v>
-      </c>
-      <c r="W154" s="4">
-        <f>W149+W124</f>
-        <v>3014.8672358907961</v>
-      </c>
-      <c r="Y154" s="4">
-        <f>Y149+Y124</f>
-        <v>2829.0475987972986</v>
-      </c>
-      <c r="Z154" s="4">
-        <f>Z149+Z124</f>
-        <v>2932.8340225328548</v>
-      </c>
+      <c r="AA153" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="AB153" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC153" s="43" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="154" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AB154" s="42"/>
       <c r="AC154" s="43"/>
     </row>
-    <row r="155" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AB155" s="42"/>
       <c r="AC155" s="43"/>
     </row>
-    <row r="156" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B156" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="C156" s="33" t="s">
-        <v>163</v>
+    <row r="156" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B156" s="24" t="s">
+        <v>261</v>
       </c>
       <c r="G156" s="4">
-        <f>G126+G135+H135+G134</f>
-        <v>2000000.0000000002</v>
+        <f>G151+G125</f>
+        <v>2425</v>
+      </c>
+      <c r="H156" s="4">
+        <f>H151+H125</f>
+        <v>3700</v>
       </c>
       <c r="J156" s="4">
-        <f>J126+J135+K135</f>
-        <v>2050000</v>
+        <f>J151+J125</f>
+        <v>2815.6278140400491</v>
+      </c>
+      <c r="K156" s="4">
+        <f>K151+K125</f>
+        <v>3887.4177657259334</v>
       </c>
       <c r="M156" s="4">
-        <f>M126+M135+N135</f>
-        <v>2110000</v>
+        <f>M151+M125</f>
+        <v>2454.1242989321499</v>
+      </c>
+      <c r="N156" s="4">
+        <f>N151+N125</f>
+        <v>3174.026319657567</v>
       </c>
       <c r="P156" s="4">
-        <f>P126+P135+Q135</f>
-        <v>2210000</v>
+        <f>P151+P125</f>
+        <v>2707.667547907201</v>
+      </c>
+      <c r="Q156" s="4">
+        <f>Q151+Q125</f>
+        <v>6184.6917476244525</v>
       </c>
       <c r="S156" s="4">
-        <f>S126+S135+T135</f>
-        <v>3000000</v>
+        <f>S151+S125</f>
+        <v>3571.2552092196693</v>
+      </c>
+      <c r="T156" s="4">
+        <f>T151+T125</f>
+        <v>1194.2768788796645</v>
       </c>
       <c r="V156" s="4">
-        <f>V126+V135+W135</f>
-        <v>2360235.9978943658</v>
+        <f>V151+V125</f>
+        <v>3028.1244706113112</v>
+      </c>
+      <c r="W156" s="4">
+        <f>W151+W125</f>
+        <v>3014.8672358907961</v>
       </c>
       <c r="Y156" s="4">
-        <f>Y126+Y135+Z135</f>
-        <v>398480.41393881035</v>
-      </c>
-      <c r="AA156" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB156" s="42" t="s">
-        <v>414</v>
-      </c>
-      <c r="AC156" s="43" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="157" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="G157" s="4">
-        <f>G156/G34</f>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="J157" s="4">
-        <f>J156/J34</f>
-        <v>1</v>
-      </c>
-      <c r="M157" s="4">
-        <f>M156/M34</f>
-        <v>1</v>
-      </c>
-      <c r="P157" s="4">
-        <f>P156/P34</f>
-        <v>1</v>
-      </c>
-      <c r="S157" s="4">
-        <f>S156/S34</f>
-        <v>1</v>
-      </c>
-      <c r="V157" s="4">
-        <f>V156/V34</f>
-        <v>9.4409439915774634E-2</v>
-      </c>
-      <c r="Y157" s="4">
-        <f>Y156/Y34</f>
-        <v>0.15812714838841679</v>
-      </c>
-      <c r="AA157" s="38"/>
+        <f>Y151+Y125</f>
+        <v>2829.0475987972986</v>
+      </c>
+      <c r="Z156" s="4">
+        <f>Z151+Z125</f>
+        <v>2932.8340225328548</v>
+      </c>
+      <c r="AB156" s="42"/>
+      <c r="AC156" s="43"/>
+    </row>
+    <row r="157" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AB157" s="42"/>
       <c r="AC157" s="43"/>
     </row>
-    <row r="158" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B158" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="C158" s="31" t="s">
-        <v>162</v>
+        <v>271</v>
+      </c>
+      <c r="C158" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="G158" s="4">
+        <f>G127+G137+H137+G136</f>
+        <v>2000000.0000000002</v>
+      </c>
+      <c r="J158" s="4">
+        <f>J127+J137+K137</f>
+        <v>2050000</v>
+      </c>
+      <c r="M158" s="4">
+        <f>M127+M137+N137</f>
+        <v>2110000</v>
+      </c>
+      <c r="P158" s="4">
+        <f>P127+P137+Q137</f>
+        <v>2210000</v>
+      </c>
+      <c r="S158" s="4">
+        <f>S127+S137+T137</f>
+        <v>3000000</v>
+      </c>
+      <c r="V158" s="4">
+        <f>V127+V137+W137</f>
+        <v>2360235.9978943658</v>
+      </c>
+      <c r="Y158" s="4">
+        <f>Y127+Y137+Z137</f>
+        <v>398480.41393881035</v>
       </c>
       <c r="AA158" s="38" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="AB158" s="42" t="s">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="AC158" s="43" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="159" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B159" s="38"/>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="159" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="G159" s="4">
+        <f>G158/G34</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="J159" s="4">
+        <f>J158/J34</f>
+        <v>1</v>
+      </c>
+      <c r="M159" s="4">
+        <f>M158/M34</f>
+        <v>1</v>
+      </c>
+      <c r="P159" s="4">
+        <f>P158/P34</f>
+        <v>1</v>
+      </c>
+      <c r="S159" s="4">
+        <f>S158/S34</f>
+        <v>1</v>
+      </c>
+      <c r="V159" s="4">
+        <f>V158/V34</f>
+        <v>9.4409439915774634E-2</v>
+      </c>
+      <c r="Y159" s="4">
+        <f>Y158/Y34</f>
+        <v>0.15812714838841679</v>
+      </c>
       <c r="AA159" s="38"/>
       <c r="AB159" s="42"/>
       <c r="AC159" s="43"/>
     </row>
-    <row r="160" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="AA160" s="38"/>
-      <c r="AB160" s="42"/>
-      <c r="AC160" s="43"/>
-    </row>
-    <row r="161" spans="27:30" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B160" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="C160" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA160" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB160" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="AC160" s="43" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="161" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B161" s="38"/>
       <c r="AA161" s="38"/>
       <c r="AB161" s="42"/>
       <c r="AC161" s="43"/>
     </row>
-    <row r="162" spans="27:30" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA162" s="38"/>
       <c r="AB162" s="42"/>
       <c r="AC162" s="43"/>
-      <c r="AD162">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="163" spans="27:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA163" s="38"/>
       <c r="AB163" s="42"/>
       <c r="AC163" s="43"/>
-      <c r="AD163">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="164" spans="27:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA164" s="38"/>
       <c r="AB164" s="42"/>
       <c r="AC164" s="43"/>
@@ -14604,48 +14693,64 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="27:30" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA165" s="38"/>
       <c r="AB165" s="42"/>
       <c r="AC165" s="43"/>
-    </row>
-    <row r="166" spans="27:30" x14ac:dyDescent="0.2">
+      <c r="AD165">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="2:30" x14ac:dyDescent="0.2">
       <c r="AA166" s="38"/>
       <c r="AB166" s="42"/>
       <c r="AC166" s="43"/>
+      <c r="AD166">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AA167" s="38"/>
+      <c r="AB167" s="42"/>
+      <c r="AC167" s="43"/>
+    </row>
+    <row r="168" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AA168" s="38"/>
+      <c r="AB168" s="42"/>
+      <c r="AC168" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="C103:C106"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C87:C90"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="C92:C95"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="B69:B72"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="B57:B60"/>
-    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="C104:C107"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="E51:E54"/>
+    <mergeCell ref="C81:C85"/>
+    <mergeCell ref="C88:C91"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="C99:C102"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="C93:C96"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="C58:C61"/>
     <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="E76:E79"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="E77:E80"/>
     <mergeCell ref="Y5:Z5"/>
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="S5:T5"/>

--- a/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
+++ b/sisepuede/ref/validation_workbooks/carbon_ledger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/usuario/git/sisepuede/sisepuede/ref/validation_workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5603A1-8EBF-334C-9F4E-C5B2926DDFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D111AA-CE75-364C-8638-1EC89673CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25580" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
+    <workbookView xWindow="3280" yWindow="760" windowWidth="34200" windowHeight="20040" activeTab="2" xr2:uid="{49B92464-5B50-C04B-B571-E5276F1DC1EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="492">
   <si>
     <t>forest_primary_c_ha</t>
   </si>
@@ -916,9 +916,6 @@
     <t>\overline{Y}^*(t, u)</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fractional threshold for stock loss (compared to undisturbed forest levels) below which sequestration declines. </t>
   </si>
   <si>
@@ -1273,9 +1270,6 @@
     <t>Vector ($n_T$) storing unmet demand for removals from original forests.</t>
   </si>
   <si>
-    <t>Vector ($n_T$) storing removals from young forests, excluding conversions.  Always $\leq d_{rmv}$.</t>
-  </si>
-  <si>
     <t>Vector ($n_T$) giving total removals supplied.</t>
   </si>
   <si>
@@ -1345,9 +1339,6 @@
     <t>\overline{y}_{avail}(t)</t>
   </si>
   <si>
-    <t>r^{(y)}_{rmv}(t)</t>
-  </si>
-  <si>
     <t>R^{(0)}_{rmv}(t, v)</t>
   </si>
   <si>
@@ -1357,9 +1348,6 @@
     <t>u^{(0)}_{rmv}(t)</t>
   </si>
   <si>
-    <t>r^{(0)}_{rmv}(t)</t>
-  </si>
-  <si>
     <t>d_{rmv}(t)</t>
   </si>
   <si>
@@ -1381,9 +1369,6 @@
     <t>A_{out}(t, v)</t>
   </si>
   <si>
-    <t>A^*(t + 1, v)</t>
-  </si>
-  <si>
     <t>\overline{\eta}(t, v)</t>
   </si>
   <si>
@@ -1514,6 +1499,24 @@
   </si>
   <si>
     <t>vec_biomass_c_removals_young_priority_frac</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing removals from young forests, excluding conversions, after original forests.  Always $\leq d_{rmv}$.</t>
+  </si>
+  <si>
+    <t>r^{(y)}_{post}(t)</t>
+  </si>
+  <si>
+    <t>r^{(0)}(t)</t>
+  </si>
+  <si>
+    <t>r^{(y)}_{pre}(t)</t>
+  </si>
+  <si>
+    <t>Vector ($n_T$) storing removals from young forests, excluding conversions, before original forests.  Always $\leq d_{rmv}$.</t>
+  </si>
+  <si>
+    <t>- NOTE: is A^*(t + 1, v)</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1849,6 +1852,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7005,18 +7011,18 @@
     <col min="8" max="8" width="15.1640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
     <col min="10" max="11" width="13.33203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" style="5" customWidth="1"/>
-    <col min="13" max="14" width="13.33203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="21.1640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="21.1640625" style="4" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="22.83203125" style="5" customWidth="1"/>
-    <col min="19" max="20" width="13.33203125" style="4" customWidth="1"/>
-    <col min="21" max="21" width="9.1640625" style="5" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" style="4" customWidth="1"/>
-    <col min="23" max="23" width="12.5" style="4" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" style="5" customWidth="1"/>
-    <col min="25" max="26" width="13.33203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="21.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" style="4" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="22.83203125" style="5" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5" style="4" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="5" hidden="1" customWidth="1"/>
+    <col min="25" max="26" width="13.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="24" style="24" customWidth="1"/>
     <col min="28" max="28" width="64.5" style="47" customWidth="1"/>
     <col min="29" max="29" width="14.6640625" style="48" customWidth="1"/>
@@ -7194,7 +7200,7 @@
     </row>
     <row r="5" spans="1:41" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>155</v>
@@ -7238,13 +7244,13 @@
       </c>
       <c r="Z5" s="52"/>
       <c r="AA5" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB5" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="AB5" s="40" t="s">
-        <v>303</v>
-      </c>
       <c r="AC5" s="27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AD5" s="36" t="s">
         <v>229</v>
@@ -7342,7 +7348,7 @@
     </row>
     <row r="7" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>156</v>
@@ -7408,13 +7414,13 @@
         <v>249360</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AB7" s="42" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AC7" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE7" s="19">
         <v>0.01</v>
@@ -7441,7 +7447,7 @@
     </row>
     <row r="8" spans="1:41" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>157</v>
@@ -7509,13 +7515,13 @@
         <v>249801</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AB8" s="42" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AC8" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE8" s="19">
         <v>0.05</v>
@@ -7542,7 +7548,7 @@
     </row>
     <row r="9" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>221</v>
@@ -7596,13 +7602,13 @@
         <v>116</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AB9" s="42" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AC9" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE9" s="19">
         <v>0.12</v>
@@ -7629,7 +7635,7 @@
     </row>
     <row r="10" spans="1:41" ht="85" x14ac:dyDescent="0.2">
       <c r="A10" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>220</v>
@@ -7672,10 +7678,10 @@
         <v>279</v>
       </c>
       <c r="AB10" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AC10" s="43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AE10" s="19">
         <v>0.2</v>
@@ -7690,7 +7696,7 @@
     </row>
     <row r="11" spans="1:41" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>218</v>
@@ -7733,10 +7739,10 @@
         <v>280</v>
       </c>
       <c r="AB11" s="42" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AC11" s="43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AE11" s="19">
         <v>0.2</v>
@@ -7751,10 +7757,10 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A12" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C12" s="28"/>
       <c r="G12" s="4">
@@ -7814,10 +7820,10 @@
         <v>116</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AB12" s="42" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AC12" s="43"/>
       <c r="AE12" s="19"/>
@@ -7826,7 +7832,7 @@
     </row>
     <row r="13" spans="1:41" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>219</v>
@@ -7862,10 +7868,10 @@
         <v>278</v>
       </c>
       <c r="AB13" s="42" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AC13" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE13" s="19">
         <v>0.36</v>
@@ -7880,7 +7886,7 @@
     </row>
     <row r="14" spans="1:41" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B14" s="38" t="s">
         <v>158</v>
@@ -7947,14 +7953,12 @@
         <f>MAX(Z7-Z9,0)</f>
         <v>249244</v>
       </c>
-      <c r="AA14" s="38" t="s">
-        <v>446</v>
-      </c>
-      <c r="AB14" s="42" t="s">
-        <v>291</v>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="62" t="s">
+        <v>491</v>
       </c>
       <c r="AC14" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE14" s="19"/>
       <c r="AF14" s="19"/>
@@ -7962,7 +7966,7 @@
     </row>
     <row r="15" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B15" s="38" t="s">
         <v>222</v>
@@ -7995,13 +7999,13 @@
         <v>0.7</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AB15" s="42" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AC15" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AE15" s="19">
         <v>0.6</v>
@@ -8016,7 +8020,7 @@
     </row>
     <row r="16" spans="1:41" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>243</v>
@@ -8073,13 +8077,13 @@
         <v>9</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AB16" s="42" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AC16" s="43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
@@ -8087,7 +8091,7 @@
     </row>
     <row r="17" spans="1:33" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B17" s="38" t="s">
         <v>282</v>
@@ -8152,13 +8156,13 @@
         <v>1.728</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AB17" s="42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AC17" s="43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AE17" s="19"/>
       <c r="AF17" s="19"/>
@@ -8166,10 +8170,10 @@
     </row>
     <row r="18" spans="1:33" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>162</v>
@@ -8184,13 +8188,13 @@
         <v>0.37800893000000002</v>
       </c>
       <c r="AA18" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB18" s="42" t="s">
         <v>414</v>
       </c>
-      <c r="AB18" s="42" t="s">
-        <v>416</v>
-      </c>
       <c r="AC18" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AE18" s="19">
         <v>1.8</v>
@@ -8205,10 +8209,10 @@
     </row>
     <row r="19" spans="1:33" ht="102" x14ac:dyDescent="0.2">
       <c r="A19" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>162</v>
@@ -8226,13 +8230,13 @@
         <v>0.47800893</v>
       </c>
       <c r="AA19" s="38" t="s">
+        <v>413</v>
+      </c>
+      <c r="AB19" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="AB19" s="42" t="s">
-        <v>417</v>
-      </c>
       <c r="AC19" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AE19" s="19">
         <v>3</v>
@@ -8247,7 +8251,7 @@
     </row>
     <row r="20" spans="1:33" ht="136" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>223</v>
@@ -8266,10 +8270,10 @@
         <v>281</v>
       </c>
       <c r="AB20" s="42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC20" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AE20" s="19">
         <v>6</v>
@@ -8284,7 +8288,7 @@
     </row>
     <row r="21" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>225</v>
@@ -8302,13 +8306,13 @@
         <v>100</v>
       </c>
       <c r="AA21" s="38" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AB21" s="42" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AC21" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AE21" s="19">
         <v>10</v>
@@ -8323,7 +8327,7 @@
     </row>
     <row r="22" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>227</v>
@@ -8341,13 +8345,13 @@
         <v>0.25</v>
       </c>
       <c r="AA22" s="38" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AB22" s="42" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AC22" s="44" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AE22" s="19"/>
       <c r="AF22" s="19"/>
@@ -8355,7 +8359,7 @@
     </row>
     <row r="23" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>274</v>
@@ -8375,13 +8379,13 @@
         <v>37.800893000000002</v>
       </c>
       <c r="AA23" s="38" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AB23" s="42" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AC23" s="43" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AE23" s="19">
         <v>12</v>
@@ -8396,7 +8400,7 @@
     </row>
     <row r="24" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>226</v>
@@ -8416,13 +8420,13 @@
         <v>62.199106999999998</v>
       </c>
       <c r="AA24" s="38" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AB24" s="42" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AC24" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AE24" s="19">
         <v>13.5</v>
@@ -8451,7 +8455,7 @@
     </row>
     <row r="26" spans="1:33" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B26" s="38" t="s">
         <v>159</v>
@@ -8505,13 +8509,13 @@
         <v>49500</v>
       </c>
       <c r="AA26" s="38" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AB26" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AC26" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE26" s="19">
         <v>10</v>
@@ -8526,7 +8530,7 @@
     </row>
     <row r="27" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>273</v>
@@ -8566,13 +8570,13 @@
         <v>0</v>
       </c>
       <c r="AA27" s="38" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AB27" s="42" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AC27" s="43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AE27" s="19">
         <v>6</v>
@@ -8587,7 +8591,7 @@
     </row>
     <row r="28" spans="1:33" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B28" s="38" t="s">
         <v>160</v>
@@ -8655,13 +8659,13 @@
         <v>49500</v>
       </c>
       <c r="AA28" s="38" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AB28" s="42" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AC28" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AE28" s="19">
         <v>3</v>
@@ -8707,7 +8711,7 @@
     </row>
     <row r="30" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B30" s="38" t="s">
         <v>272</v>
@@ -8728,18 +8732,18 @@
         <v>0.92</v>
       </c>
       <c r="AA30" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB30" s="42" t="s">
         <v>319</v>
       </c>
-      <c r="AB30" s="42" t="s">
-        <v>320</v>
-      </c>
       <c r="AC30" s="43" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B31" s="38" t="s">
         <v>228</v>
@@ -8764,13 +8768,13 @@
         <v>2E-3</v>
       </c>
       <c r="AA31" s="38" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AB31" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AC31" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -8801,7 +8805,7 @@
     </row>
     <row r="34" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B34" s="38" t="s">
         <v>168</v>
@@ -8837,15 +8841,18 @@
         <v>285</v>
       </c>
       <c r="AB34" s="42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AC34" s="43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A35" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B35" s="38" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>162</v>
@@ -8873,10 +8880,10 @@
         <v>0.5</v>
       </c>
       <c r="AA35" s="38" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AB35" s="42" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AC35" s="43"/>
     </row>
@@ -8988,10 +8995,10 @@
     </row>
     <row r="40" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C40" s="55" t="s">
         <v>174</v>
@@ -9079,21 +9086,21 @@
         <v>85</v>
       </c>
       <c r="AA40" s="38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AB40" s="42" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AC40" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C41" s="55"/>
       <c r="F41" s="14" t="s">
@@ -9178,21 +9185,21 @@
         <v>80</v>
       </c>
       <c r="AA41" s="38" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AB41" s="42" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC41" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C42" s="55"/>
       <c r="F42" s="14" t="s">
@@ -9276,13 +9283,13 @@
         <v>92</v>
       </c>
       <c r="AA42" s="38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AB42" s="42" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AC42" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -9380,7 +9387,7 @@
     </row>
     <row r="45" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B45" s="56" t="s">
         <v>189</v>
@@ -9422,10 +9429,10 @@
         <v>286</v>
       </c>
       <c r="AB45" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AC45" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -9541,7 +9548,7 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B49" s="38" t="s">
         <v>190</v>
@@ -9582,10 +9589,10 @@
         <v>287</v>
       </c>
       <c r="AB49" s="42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AC49" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -9597,7 +9604,7 @@
     </row>
     <row r="51" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A51" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B51" s="56" t="s">
         <v>257</v>
@@ -9640,13 +9647,13 @@
         <v>0</v>
       </c>
       <c r="AA51" s="38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AB51" s="42" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AC51" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="1:29" ht="51" x14ac:dyDescent="0.2">
@@ -9768,7 +9775,7 @@
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A55" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B55" s="38" t="s">
         <v>258</v>
@@ -9806,18 +9813,18 @@
         <v>0</v>
       </c>
       <c r="AA55" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AB55" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AC55" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A56" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B56" s="38" t="s">
         <v>260</v>
@@ -9853,13 +9860,13 @@
         <v>0</v>
       </c>
       <c r="AA56" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AB56" s="42" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AC56" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.2">
@@ -9869,7 +9876,7 @@
     </row>
     <row r="58" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B58" s="56" t="s">
         <v>191</v>
@@ -9912,10 +9919,10 @@
         <v>288</v>
       </c>
       <c r="AB58" s="42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AC58" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -10034,7 +10041,7 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B62" s="38" t="s">
         <v>192</v>
@@ -10075,10 +10082,10 @@
         <v>289</v>
       </c>
       <c r="AB62" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AC62" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
@@ -10088,7 +10095,7 @@
     </row>
     <row r="64" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A64" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B64" s="56" t="s">
         <v>178</v>
@@ -10128,13 +10135,13 @@
         <v>0.6</v>
       </c>
       <c r="AA64" s="38" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB64" s="42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AC64" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -10244,10 +10251,10 @@
     </row>
     <row r="68" spans="1:32" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C68" s="31" t="s">
         <v>162</v>
@@ -10256,13 +10263,13 @@
         <v>49</v>
       </c>
       <c r="AA68" s="38" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AB68" s="42" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AC68" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.2">
@@ -10272,7 +10279,7 @@
     </row>
     <row r="70" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A70" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B70" s="56" t="s">
         <v>232</v>
@@ -10315,10 +10322,10 @@
         <v>290</v>
       </c>
       <c r="AB70" s="42" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AC70" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -10425,7 +10432,7 @@
     </row>
     <row r="75" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A75" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B75" s="56" t="s">
         <v>230</v>
@@ -10464,13 +10471,13 @@
         <v>0</v>
       </c>
       <c r="AA75" s="38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AB75" s="42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AC75" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:32" ht="34" x14ac:dyDescent="0.2">
@@ -10590,7 +10597,7 @@
     </row>
     <row r="79" spans="1:32" ht="34" x14ac:dyDescent="0.2">
       <c r="A79" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B79" s="38" t="s">
         <v>231</v>
@@ -10630,13 +10637,13 @@
         <v>0</v>
       </c>
       <c r="AA79" s="45" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AB79" s="42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AC79" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AF79" t="s">
         <v>106</v>
@@ -10656,10 +10663,10 @@
     </row>
     <row r="81" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B81" s="37" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C81" s="55" t="s">
         <v>174</v>
@@ -10689,13 +10696,13 @@
         <v>0</v>
       </c>
       <c r="AA81" s="38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AB81" s="42" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AC81" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AD81" t="s">
         <v>86</v>
@@ -10703,10 +10710,10 @@
     </row>
     <row r="82" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A82" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B82" s="37" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C82" s="55"/>
       <c r="F82" s="14" t="s">
@@ -10769,13 +10776,13 @@
         <v>0</v>
       </c>
       <c r="AA82" s="38" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AB82" s="42" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AC82" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -11018,10 +11025,10 @@
     </row>
     <row r="88" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A88" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B88" s="37" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C88" s="55" t="s">
         <v>174</v>
@@ -11082,21 +11089,21 @@
         <v>0.6</v>
       </c>
       <c r="AA88" s="37" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AB88" s="42" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AC88" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="89" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B89" s="37" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C89" s="55"/>
       <c r="F89" s="14" t="s">
@@ -11155,13 +11162,13 @@
         <v>0.36</v>
       </c>
       <c r="AA89" s="37" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AB89" s="42" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AC89" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:30" ht="34" x14ac:dyDescent="0.2">
@@ -11295,7 +11302,7 @@
     </row>
     <row r="93" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B93" s="57" t="s">
         <v>202</v>
@@ -11335,13 +11342,13 @@
         <v>9.8621113109027395E-2</v>
       </c>
       <c r="AA93" s="37" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="AB93" s="42" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AC93" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94" spans="1:30" ht="51" x14ac:dyDescent="0.2">
@@ -11460,10 +11467,10 @@
     </row>
     <row r="97" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A97" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B97" s="37" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C97" s="28"/>
       <c r="F97" s="14"/>
@@ -11496,13 +11503,13 @@
         <v>0.17633270956878355</v>
       </c>
       <c r="AA97" s="37" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AB97" s="42" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AC97" s="43" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.2">
@@ -11512,7 +11519,7 @@
     </row>
     <row r="99" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A99" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B99" s="57" t="s">
         <v>207</v>
@@ -11552,13 +11559,13 @@
         <v>113.71737449773644</v>
       </c>
       <c r="AA99" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AB99" s="42" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AC99" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="100" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -11683,7 +11690,7 @@
     </row>
     <row r="104" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A104" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B104" s="57" t="s">
         <v>208</v>
@@ -11724,13 +11731,13 @@
         <v>28.429343624434111</v>
       </c>
       <c r="AA104" s="38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AB104" s="42" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AC104" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="105" spans="1:29" ht="17" x14ac:dyDescent="0.2">
@@ -11953,7 +11960,7 @@
     </row>
     <row r="112" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B112" s="38" t="s">
         <v>234</v>
@@ -12021,18 +12028,18 @@
         <v>24936000</v>
       </c>
       <c r="AA112" s="38" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AB112" s="42" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AC112" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B113" s="38" t="s">
         <v>181</v>
@@ -12098,18 +12105,18 @@
         <v>1</v>
       </c>
       <c r="AA113" s="38" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AB113" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AC113" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="114" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B114" s="38" t="s">
         <v>182</v>
@@ -12177,18 +12184,18 @@
         <v>0.92</v>
       </c>
       <c r="AA114" s="38" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="AB114" s="42" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AC114" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A115" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B115" s="38" t="s">
         <v>235</v>
@@ -12256,18 +12263,18 @@
         <v>15778712.754563004</v>
       </c>
       <c r="AA115" s="38" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AB115" s="42" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AC115" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="116" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B116" s="38" t="s">
         <v>238</v>
@@ -12335,18 +12342,18 @@
         <v>63.276839727955583</v>
       </c>
       <c r="AA116" s="38" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AB116" s="42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AC116" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="1:29" ht="68" x14ac:dyDescent="0.2">
       <c r="A117" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B117" s="38" t="s">
         <v>276</v>
@@ -12414,13 +12421,13 @@
         <v>25.475946727955581</v>
       </c>
       <c r="AA117" s="38" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AB117" s="46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AC117" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.2">
@@ -12451,7 +12458,7 @@
     </row>
     <row r="120" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A120" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B120" s="38" t="s">
         <v>240</v>
@@ -12524,7 +12531,7 @@
     </row>
     <row r="121" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A121" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B121" s="38" t="s">
         <v>239</v>
@@ -12564,18 +12571,18 @@
         <v>215.49749504124878</v>
       </c>
       <c r="AA121" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AB121" s="42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AC121" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="122" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B122" s="38" t="s">
         <v>236</v>
@@ -12643,18 +12650,18 @@
         <v>15778928.252058046</v>
       </c>
       <c r="AA122" s="38" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AB122" s="42" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="AC122" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="123" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A123" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B123" s="38" t="s">
         <v>237</v>
@@ -12722,18 +12729,18 @@
         <v>3944732.0630145115</v>
       </c>
       <c r="AA123" s="38" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AB123" s="42" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="AC123" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="124" spans="1:29" ht="17" x14ac:dyDescent="0.2">
       <c r="A124" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B124" s="38" t="s">
         <v>275</v>
@@ -12801,18 +12808,18 @@
         <v>7340.1134084428477</v>
       </c>
       <c r="AA124" s="38" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AB124" s="42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AC124" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="125" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A125" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B125" s="38" t="s">
         <v>259</v>
@@ -12880,18 +12887,18 @@
         <v>1044</v>
       </c>
       <c r="AA125" s="38" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="AB125" s="42" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="AC125" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="126" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B126" s="38" t="s">
         <v>277</v>
@@ -12959,18 +12966,18 @@
         <v>4407.2793859099929</v>
       </c>
       <c r="AA126" s="38" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="AB126" s="42" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AC126" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="127" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A127" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B127" s="38" t="s">
         <v>252</v>
@@ -13010,18 +13017,18 @@
         <v>9842.1904497703563</v>
       </c>
       <c r="AA127" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB127" s="42" t="s">
         <v>325</v>
       </c>
-      <c r="AB127" s="42" t="s">
-        <v>326</v>
-      </c>
       <c r="AC127" s="43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="128" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B128" s="38" t="s">
         <v>253</v>
@@ -13089,18 +13096,18 @@
         <v>0.44779456447246724</v>
       </c>
       <c r="AA128" s="38" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AB128" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AC128" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="129" spans="1:30" ht="68" x14ac:dyDescent="0.2">
       <c r="A129" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B129" s="38" t="s">
         <v>183</v>
@@ -13168,13 +13175,13 @@
         <v>5088667.5032287594</v>
       </c>
       <c r="AA129" s="38" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AB129" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AC129" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="130" spans="1:30" x14ac:dyDescent="0.2">
@@ -13204,7 +13211,7 @@
     </row>
     <row r="132" spans="1:30" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B132" s="38" t="s">
         <v>254</v>
@@ -13244,19 +13251,21 @@
         <v>2510157.8095502295</v>
       </c>
       <c r="AA132" s="38" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AB132" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AC132" s="43" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="133" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A133" s="50"/>
+      <c r="A133" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B133" s="38" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C133" s="28" t="s">
         <v>174</v>
@@ -13290,11 +13299,20 @@
         <f>MIN(Y132,Y35*Z79)</f>
         <v>0</v>
       </c>
-      <c r="AA133" s="38"/>
-      <c r="AB133" s="42"/>
-      <c r="AC133" s="43"/>
+      <c r="AA133" s="38" t="s">
+        <v>489</v>
+      </c>
+      <c r="AB133" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="AC133" s="43" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="134" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B134" s="38" t="s">
         <v>255</v>
       </c>
@@ -13333,16 +13351,19 @@
         <v>388638.22348903998</v>
       </c>
       <c r="AA134" s="38" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
       <c r="AB134" s="42" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AC134" s="43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B135" s="38" t="s">
         <v>266</v>
       </c>
@@ -13381,18 +13402,21 @@
         <v>2121519.5860611894</v>
       </c>
       <c r="AA135" s="38" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AB135" s="42" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC135" s="43" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="136" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B136" s="38" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C136" s="28" t="s">
         <v>174</v>
@@ -13429,16 +13453,19 @@
         <v>0</v>
       </c>
       <c r="AA136" s="38" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="AB136" s="42" t="s">
-        <v>410</v>
+        <v>486</v>
       </c>
       <c r="AC136" s="43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="137" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B137" s="38" t="s">
         <v>262</v>
       </c>
@@ -13505,16 +13532,19 @@
         <v>336166.07900932123</v>
       </c>
       <c r="AA137" s="38" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AB137" s="42" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AC137" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="138" spans="1:30" ht="34" x14ac:dyDescent="0.2">
+      <c r="A138" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B138" s="38" t="s">
         <v>267</v>
       </c>
@@ -13581,13 +13611,13 @@
         <v>336166.07900932123</v>
       </c>
       <c r="AA138" s="38" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AB138" s="42" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AC138" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="139" spans="1:30" ht="17" x14ac:dyDescent="0.2">
@@ -13613,7 +13643,7 @@
     </row>
     <row r="140" spans="1:30" ht="119" x14ac:dyDescent="0.2">
       <c r="A140" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B140" s="38" t="s">
         <v>270</v>
@@ -13681,13 +13711,13 @@
         <v>0.40958701751064658</v>
       </c>
       <c r="AA140" s="38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB140" s="42" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AC140" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AD140">
         <v>20</v>
@@ -13695,7 +13725,7 @@
     </row>
     <row r="141" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A141" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B141" s="38" t="s">
         <v>184</v>
@@ -13763,13 +13793,13 @@
         <v>6.6061710417515754E-2</v>
       </c>
       <c r="AA141" s="39" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AB141" s="42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AC141" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AD141">
         <v>20</v>
@@ -13786,7 +13816,7 @@
     </row>
     <row r="143" spans="1:30" ht="51" x14ac:dyDescent="0.2">
       <c r="A143" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B143" s="38" t="s">
         <v>186</v>
@@ -13854,13 +13884,13 @@
         <v>336166.07900932123</v>
       </c>
       <c r="AA143" s="38" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AB143" s="42" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AC143" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AD143">
         <v>20</v>
@@ -13868,7 +13898,7 @@
     </row>
     <row r="144" spans="1:30" ht="34" x14ac:dyDescent="0.2">
       <c r="A144" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B144" s="38" t="s">
         <v>187</v>
@@ -13936,18 +13966,18 @@
         <v>388638.22348903998</v>
       </c>
       <c r="AA144" s="38" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AB144" s="42" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AC144" s="43" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="145" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A145" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B145" s="38" t="s">
         <v>188</v>
@@ -14015,13 +14045,13 @@
         <v>0.86498460185247705</v>
       </c>
       <c r="AA145" s="38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AB145" s="42" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AC145" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="146" spans="1:29" x14ac:dyDescent="0.2">
@@ -14050,6 +14080,9 @@
       <c r="AC147" s="43"/>
     </row>
     <row r="148" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="A148" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B148" s="38" t="s">
         <v>268</v>
       </c>
@@ -14116,16 +14149,19 @@
         <v>24233.450635277597</v>
       </c>
       <c r="AA148" s="38" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AB148" s="42" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AC148" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="149" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A149" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B149" s="38" t="s">
         <v>284</v>
       </c>
@@ -14189,16 +14225,19 @@
         <v>6058.3626588193993</v>
       </c>
       <c r="AA149" s="38" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AB149" s="42" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AC149" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="150" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="A150" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B150" s="38" t="s">
         <v>269</v>
       </c>
@@ -14265,16 +14304,19 @@
         <v>84041.519752330307</v>
       </c>
       <c r="AA150" s="38" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AB150" s="42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AC150" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A151" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B151" s="38" t="s">
         <v>176</v>
       </c>
@@ -14341,16 +14383,19 @@
         <v>1888.8340225328548</v>
       </c>
       <c r="AA151" s="38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AB151" s="42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AC151" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="152" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A152" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B152" s="38" t="s">
         <v>177</v>
       </c>
@@ -14417,16 +14462,19 @@
         <v>1373.5803521107118</v>
       </c>
       <c r="AA152" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AB152" s="42" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AC152" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="153" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A153" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B153" s="38" t="s">
         <v>283</v>
       </c>
@@ -14490,13 +14538,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="AA153" s="38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AB153" s="42" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AC153" s="43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="154" spans="1:29" x14ac:dyDescent="0.2">
@@ -14575,6 +14623,9 @@
       <c r="AC157" s="43"/>
     </row>
     <row r="158" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A158" s="50" t="s">
+        <v>417</v>
+      </c>
       <c r="B158" s="38" t="s">
         <v>271</v>
       </c>
@@ -14582,41 +14633,41 @@
         <v>163</v>
       </c>
       <c r="G158" s="4">
-        <f>G127+G137+H137+G136</f>
+        <f>G127+G133+G136+G137+H137</f>
         <v>2000000.0000000002</v>
       </c>
       <c r="J158" s="4">
-        <f>J127+J137+K137</f>
+        <f>J127+J133+J136+J137+K137</f>
         <v>2050000</v>
       </c>
       <c r="M158" s="4">
-        <f>M127+M137+N137</f>
+        <f>M127+M133+M136+M137+N137</f>
         <v>2110000</v>
       </c>
       <c r="P158" s="4">
-        <f>P127+P137+Q137</f>
+        <f>P127+P133+P136+P137+Q137</f>
         <v>2210000</v>
       </c>
       <c r="S158" s="4">
-        <f>S127+S137+T137</f>
+        <f>S127+S133+S136+S137+T137</f>
         <v>3000000</v>
       </c>
       <c r="V158" s="4">
-        <f>V127+V137+W137</f>
+        <f>V127+V133+V136+V137+W137</f>
         <v>2360235.9978943658</v>
       </c>
       <c r="Y158" s="4">
-        <f>Y127+Y137+Z137</f>
+        <f>Y127+Y133+Y136+Y137+Z137</f>
         <v>398480.41393881035</v>
       </c>
       <c r="AA158" s="38" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AB158" s="42" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AC158" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="159" spans="1:29" x14ac:dyDescent="0.2">
@@ -14654,19 +14705,19 @@
     </row>
     <row r="160" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B160" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C160" s="31" t="s">
         <v>162</v>
       </c>
       <c r="AA160" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB160" s="42" t="s">
         <v>359</v>
       </c>
-      <c r="AB160" s="42" t="s">
+      <c r="AC160" s="43" t="s">
         <v>360</v>
-      </c>
-      <c r="AC160" s="43" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="161" spans="2:30" x14ac:dyDescent="0.2">
